--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,10 +510,15 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>deferred_until</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -1,14 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_state" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="learnings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="pipeline_state" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="learnings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="pending_confirmations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="poll_state" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:U51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,6 +523,2351 @@
       <c r="U1" t="inlineStr">
         <is>
           <t>updated_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1000284561</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>quotes@nexgensurveying.com</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Nexgen Land Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>IWYEDOZAQEETOSPDSGISOMYB</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:10.785262+00:00</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.489948+00:00</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:10.795898+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1000284560</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>quotes@nexgensurveying.com</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Nexgen Land Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>IWYEDOZAQEETOSPDSGISOMYB</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:12.943430+00:00</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.506677+00:00</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:12.955138+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1000284559</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>quotes@nexgensurveying.com</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Nexgen Land Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VTZKBTHGFSZWIJLWQ</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:15.016074+00:00</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.522197+00:00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:15.026819+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1000284558</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>quotes@nexgensurveying.com</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Nexgen Land Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VTZKBTHGFSZWIJLWQ</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:17.008517+00:00</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.539134+00:00</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:17.019754+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1000284524</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>lbelectric88@gmail.com</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Donahue Francis</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2339 MONTCLAIR RD</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:18.808530+00:00</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.554603+00:00</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:18.819123+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1000284508</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>whyde@designrarchitects.com</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Walter  Hyde III</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>712 PARK PL</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:20.733620+00:00</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.570449+00:00</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:20.744754+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1000284507</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>amullins@jdgrossolaw.com</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Joseph D. Grosso Jr., P.A.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HEMLOCK CIR</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:22.632923+00:00</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.587268+00:00</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:22.645338+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1000284503</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>vmazina@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Valentina Mazina</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>11606 SW OCEANFRONT CT</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:24.704602+00:00</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.637354+00:00</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:24.715250+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1000284488</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>robertsmoot@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Robert Smoot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>514 NW 37TH AVENUE</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:26.571415+00:00</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.655228+00:00</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:26.582321+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1000284479</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>sdr.isabel@gmail.com</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Isabel Gordon</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3199 SPIRIT LAKE RD</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:28.414556+00:00</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.672567+00:00</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:28.425258+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1000284474</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Land Survey and Elevation</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>puntagorda@suncoastone.net</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Punta Gorda - Suncoast One Title &amp; Closings, Inc.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>641 FAIRMOUNT DR</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:30.411042+00:00</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.690772+00:00</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:30.421924+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1000284470</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NikkiLeigh@heightstitle.com</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Heights Title Services, LLC</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2170 ROCK RD</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:32.455775+00:00</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.708738+00:00</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:32.468006+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1000284466</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>alison@stevecuryconstruction.com</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Steve Cury Construction</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">415 44TH ST </t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:34.305630+00:00</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.727250+00:00</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:34.316542+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1000284462</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>alison@stevecuryconstruction.com</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Steve Cury Construction</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>415 44TH ST</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:36.237697+00:00</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.746530+00:00</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:36.248610+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1000284440</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ahenick@rdmanagement.com</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RD Management</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1164 NW 45TH TERRACE</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:38.609131+00:00</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.767153+00:00</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:38.620134+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1000284429</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>debbiemyers@exitcompassrealty.com</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Deborah Myers</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1065 HARBOUR GLEN PL</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:40.503915+00:00</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.786644+00:00</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:40.514627+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1000284400</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>bart@whiteeaglehomesfl.com</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bart Magerczyk</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2463 HILLVIEW ST</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:42.285182+00:00</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.806090+00:00</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:42.296615+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1000284390</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Brian@allstatecomputers.com</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Brian</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VACANT</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:44.334240+00:00</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.827301+00:00</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:44.345161+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1000284388</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>marie@firstprioritytitleco.com</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>First Priority Title Company</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>11879 FOX HILL CIR</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:46.173273+00:00</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.847786+00:00</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:46.184244+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1000284366</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>leslie.fishermanstitle@gmail.com</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fishermans Title and All Clear Title Services</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>6630 SALTAIRE TERRACE</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:48.131938+00:00</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.870173+00:00</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:48.143958+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1000284324</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>lr@cohennorris.com</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Cohen, Norris, Wolmer, Ray, Telepman and Cohen</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1131 N LAKESIDE DR</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:50.120696+00:00</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.893495+00:00</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:50.131578+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1000284317</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>quotes@nexgensurveying.com</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Nexgen Land Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DQZOGWDDOLWVVTYTMWQ</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:51.877841+00:00</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.915731+00:00</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:51.888477+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1000284316</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>quotes@nexgensurveying.com</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Nexgen Land Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DQZOGWDDOLWVVTYTMWQ</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:53.699232+00:00</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.938970+00:00</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:53.710262+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1000284310</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>quotes@nexgensurveying.com</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Nexgen Land Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>TZXXPKYLRRSUCSVAZOVBTF</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:55.671561+00:00</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.961313+00:00</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:55.682901+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1000284303</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>robin.rankin@foxfirerealty.com</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Robin Rankin</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0000 NE 137TH PL. </t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:57.666497+00:00</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:07.983638+00:00</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:57.678533+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1000284284</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>kagosto@lighthousetitleservices.com</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Lighthouse Title Services LLC</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4905 WILLIAMS RD</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:59.523233+00:00</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.007235+00:00</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:59.534323+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1000284265</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>office3@oceanview-b.com</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sandra Lalaian</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>19380 COLLINS AVE</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:01.492184+00:00</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.029667+00:00</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:01.503498+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1000284231</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>cy@greendoorconstructioninc.com</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Green Door Construction, Inc.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>416 MAGNOLIA AVE</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:03.347515+00:00</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.052634+00:00</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:03.358452+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1000284224</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jean@CascioLawOffice.com</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Law Offices of Jean Cascio, PLLC</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>3721 NE 30TH AVE</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:05.133060+00:00</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.077388+00:00</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:05.144257+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1000284223</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>cpsmbuilders@gmail.com</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Robert Calarko</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2951 SE WAALER ST</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:07.037192+00:00</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.101962+00:00</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:07.049188+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1000284170</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>jr@reddittarchitecture.com</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Jonathan Reddit</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>14677 PEACE RIVER WAY</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:08.883118+00:00</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.133615+00:00</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:08.893955+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1000284168</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ivy@closingtemafl.com</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>The Closing Team Title &amp; Escrow Services</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>804 SE 5TH CT</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:10.872078+00:00</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.157589+00:00</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:10.883374+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1000284163</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>w.u.g.o.c.ava771@gmail.com</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>DzVTnmfrWfbGndZjh</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SGBBUKWOFIGFOXJSVQHSYLI</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:12.713202+00:00</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.182212+00:00</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:12.724362+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1000284162</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>w.u.g.o.c.ava771@gmail.com</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DzVTnmfrWfbGndZjh</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SGBBUKWOFIGFOXJSVQHSYLI</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:14.627652+00:00</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.208715+00:00</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:14.638582+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1000284150</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Land Survey and Elevation, </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>jeremyrivera@FTGAgency.com</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Jeremy Rivera</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1825 ORRIS AVE</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:16.496987+00:00</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.234909+00:00</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:16.509012+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1000284123</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>dchuslo@aol.com</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>BETX Engineering inc.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2780 SE MORNINGSIDE BLVD</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:19.178644+00:00</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.264390+00:00</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:19.189772+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1000284112</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>nrodriguez@TUFFSHED.com</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Naya Rodriguez</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>15824 76TH TRAIL N</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:21.205930+00:00</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.291222+00:00</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:21.216665+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1000284111</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>flgirlintx@gmail.com</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIMOTHY MATZ </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>7504 ESCONDIDO ST</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:22.997360+00:00</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.318131+00:00</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:23.012989+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1000284101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>soldbysandy@gmail.com</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Sandy Jackson</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1825 ORRIS AVE</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:24.953413+00:00</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.345084+00:00</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:24.964370+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1000284093</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>gabriellechinre@gmail.com</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>5530 Thoroughbred, SW Ranches, 33330</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>5530 THOROUGHBRED</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:26.910700+00:00</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.381615+00:00</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:26.922983+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1000284076</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>sam@flyingpointre.com</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Sam Genet</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>820 NW 10TH TERRACE</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:29.245188+00:00</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.409130+00:00</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:29.256357+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1000284075</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>sam@flyingpointre.com</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Sam Genet</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>810 NW 10TH TERRACE</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:31.161115+00:00</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.435963+00:00</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:31.172123+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1000284074</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>sam@flyingpointre.com</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Sam Genet</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>721-741 NE 42ND ST</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:33.110028+00:00</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.464260+00:00</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:33.122199+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1000284061</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Land Survey and Elevation</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>bsantiago@williamsparker.com</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>WILLIAMS PARKER</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>801 LONGBOAT CLUB RD</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:34.964548+00:00</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.492520+00:00</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:34.975751+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1000284057</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>processing@floridasecuredtitle.com</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Florida Secured Title LLC</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">848 BRICKELL KEY DR </t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:36.786439+00:00</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.522369+00:00</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:36.798698+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1000284017</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>crosario@clfarchitects.com</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Choeff Levy Fischman Architecture and Design</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>9224 BAY DR</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:38.564997+00:00</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.553319+00:00</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:38.576208+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1000284011</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>kristie@meridianpartnerslaw.com</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Meridian Partners</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1302 GLENGREEN LN</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:40.589283+00:00</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.584413+00:00</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:40.600270+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1000284009</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Boundary Survey</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Jean@CascioLawOffice.com</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Law Offices of Jean Cascio, PLLC</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>7115 CUTTER COURT</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:42.487618+00:00</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.613575+00:00</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:42.499578+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1000283998</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>jason.htconstruction@gmail.com</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Rupli Residence</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>602 OAK HARBOUR DR</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:45.637863+00:00</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.690139+00:00</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:45.649012+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1000283997</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>mmasser@pdconcepts.com</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mark Masser</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>4125 NORTH RD</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:47.440251+00:00</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:17:08.720211+00:00</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:18:47.452843+00:00</t>
         </is>
       </c>
     </row>
@@ -588,4 +2935,91 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>order_ids</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pending_action</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sender</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>original_status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>parent_message_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>confirmation_posted_at</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>expires_at</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="pipeline_state" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="learnings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="pending_confirmations" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="poll_state" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_state" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="learnings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pending_confirmations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="poll_state" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:10.795898+00:00</t>
+          <t>2026-06-02T13:04:37.168006</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:12.955138+00:00</t>
+          <t>2026-06-02T13:04:37.168071</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:15.026819+00:00</t>
+          <t>2026-06-02T13:04:37.168103</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:17.019754+00:00</t>
+          <t>2026-06-02T13:04:37.168127</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:18.819123+00:00</t>
+          <t>2026-06-02T13:04:37.168151</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:20.744754+00:00</t>
+          <t>2026-06-02T13:04:37.168175</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:22.645338+00:00</t>
+          <t>2026-06-02T13:04:37.168199</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:24.715250+00:00</t>
+          <t>2026-06-02T13:04:37.168223</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:26.582321+00:00</t>
+          <t>2026-06-02T13:04:37.168254</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:28.425258+00:00</t>
+          <t>2026-06-02T13:04:37.168277</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:30.421924+00:00</t>
+          <t>2026-06-02T13:04:37.168300</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:32.468006+00:00</t>
+          <t>2026-06-02T13:04:37.168325</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:34.316542+00:00</t>
+          <t>2026-06-02T13:04:37.168349</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:36.248610+00:00</t>
+          <t>2026-06-02T13:04:37.168372</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:38.620134+00:00</t>
+          <t>2026-06-02T13:04:37.168396</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:40.514627+00:00</t>
+          <t>2026-06-02T13:04:37.168419</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:42.296615+00:00</t>
+          <t>2026-06-02T13:04:37.168442</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:44.345161+00:00</t>
+          <t>2026-06-02T13:04:37.168479</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:46.184244+00:00</t>
+          <t>2026-06-02T13:04:37.168502</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:48.143958+00:00</t>
+          <t>2026-06-02T13:04:37.168525</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:50.131578+00:00</t>
+          <t>2026-06-02T13:04:37.168548</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:51.888477+00:00</t>
+          <t>2026-06-02T13:04:37.168571</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:53.710262+00:00</t>
+          <t>2026-06-02T13:04:37.168593</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:55.682901+00:00</t>
+          <t>2026-06-02T13:04:37.168617</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:57.678533+00:00</t>
+          <t>2026-06-02T13:04:37.168638</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:59.534323+00:00</t>
+          <t>2026-06-02T13:04:37.168660</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:01.503498+00:00</t>
+          <t>2026-06-02T13:04:37.168688</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:03.358452+00:00</t>
+          <t>2026-06-02T13:04:37.168710</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:05.144257+00:00</t>
+          <t>2026-06-02T13:04:37.168733</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:07.049188+00:00</t>
+          <t>2026-06-02T13:04:37.168757</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:08.893955+00:00</t>
+          <t>2026-06-02T13:04:37.168779</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:10.883374+00:00</t>
+          <t>2026-06-02T13:04:37.168802</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:12.724362+00:00</t>
+          <t>2026-06-02T13:04:37.168825</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:14.638582+00:00</t>
+          <t>2026-06-02T13:04:37.168848</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:16.509012+00:00</t>
+          <t>2026-06-02T13:04:37.168870</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:19.189772+00:00</t>
+          <t>2026-06-02T13:04:37.168893</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:21.216665+00:00</t>
+          <t>2026-06-02T13:04:37.168915</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:23.012989+00:00</t>
+          <t>2026-06-02T13:04:37.168937</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:24.964370+00:00</t>
+          <t>2026-06-02T13:04:37.168961</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:26.922983+00:00</t>
+          <t>2026-06-02T13:04:37.168983</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:29.256357+00:00</t>
+          <t>2026-06-02T13:04:37.169006</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:31.172123+00:00</t>
+          <t>2026-06-02T13:04:37.169031</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:33.122199+00:00</t>
+          <t>2026-06-02T13:04:37.169053</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:34.975751+00:00</t>
+          <t>2026-06-02T13:04:37.169076</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:36.798698+00:00</t>
+          <t>2026-06-02T13:04:37.169100</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:38.576208+00:00</t>
+          <t>2026-06-02T13:04:37.169123</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:40.600270+00:00</t>
+          <t>2026-06-02T13:04:37.169146</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:42.499578+00:00</t>
+          <t>2026-06-02T13:04:37.169170</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:45.649012+00:00</t>
+          <t>2026-06-02T13:04:37.169193</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>details_missing</t>
+          <t>invoice_needed</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:47.452843+00:00</t>
+          <t>2026-06-02T13:04:37.169215</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_state" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="learnings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pending_confirmations" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="poll_state" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="pipeline_state" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="learnings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="pending_confirmations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="poll_state" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:10.785262+00:00</t>
+          <t>2026-06-02T13:25:25.541825+00:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168006</t>
+          <t>2026-06-02T13:25:25.553075+00:00</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:12.943430+00:00</t>
+          <t>2026-06-02T13:25:46.213219+00:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168071</t>
+          <t>2026-06-02T13:25:46.225176+00:00</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:15.016074+00:00</t>
+          <t>2026-06-02T13:26:06.500527+00:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168103</t>
+          <t>2026-06-02T13:26:06.511725+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:17.008517+00:00</t>
+          <t>2026-06-02T13:27:59.178553+00:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168127</t>
+          <t>2026-06-02T13:27:59.189093+00:00</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:18.808530+00:00</t>
+          <t>2026-06-02T13:28:07.404843+00:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168151</t>
+          <t>2026-06-02T13:28:07.416800+00:00</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:20.733620+00:00</t>
+          <t>2026-06-02T13:28:14.650473+00:00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168175</t>
+          <t>2026-06-02T13:28:14.661941+00:00</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:22.632923+00:00</t>
+          <t>2026-06-02T13:28:21.506285+00:00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168199</t>
+          <t>2026-06-02T13:28:21.520906+00:00</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:24.704602+00:00</t>
+          <t>2026-06-02T13:28:29.115944+00:00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168223</t>
+          <t>2026-06-02T13:28:29.128600+00:00</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:26.571415+00:00</t>
+          <t>2026-06-02T13:28:37.639639+00:00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168254</t>
+          <t>2026-06-02T13:28:37.650951+00:00</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:28.414556+00:00</t>
+          <t>2026-06-02T13:28:45.350364+00:00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168277</t>
+          <t>2026-06-02T13:28:45.361810+00:00</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:30.411042+00:00</t>
+          <t>2026-06-02T13:28:52.970057+00:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168300</t>
+          <t>2026-06-02T13:28:52.981623+00:00</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:32.455775+00:00</t>
+          <t>2026-06-02T13:29:00.012724+00:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168325</t>
+          <t>2026-06-02T13:29:00.024092+00:00</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:34.305630+00:00</t>
+          <t>2026-06-02T13:29:08.376396+00:00</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168349</t>
+          <t>2026-06-02T13:29:08.388765+00:00</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:36.237697+00:00</t>
+          <t>2026-06-02T13:29:15.188379+00:00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168372</t>
+          <t>2026-06-02T13:29:15.199764+00:00</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:38.609131+00:00</t>
+          <t>2026-06-02T13:29:23.288964+00:00</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168396</t>
+          <t>2026-06-02T13:29:23.300244+00:00</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:40.503915+00:00</t>
+          <t>2026-06-02T13:29:30.286159+00:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168419</t>
+          <t>2026-06-02T13:29:30.297547+00:00</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:42.285182+00:00</t>
+          <t>2026-06-02T13:29:37.281916+00:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168442</t>
+          <t>2026-06-02T13:29:37.293201+00:00</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:44.334240+00:00</t>
+          <t>2026-06-02T13:29:44.460659+00:00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168479</t>
+          <t>2026-06-02T13:29:44.501909+00:00</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:46.173273+00:00</t>
+          <t>2026-06-02T13:29:51.479902+00:00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168502</t>
+          <t>2026-06-02T13:29:51.491202+00:00</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:48.131938+00:00</t>
+          <t>2026-06-02T13:29:58.651981+00:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168525</t>
+          <t>2026-06-02T13:29:58.663239+00:00</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:50.120696+00:00</t>
+          <t>2026-06-02T13:30:07.285100+00:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168548</t>
+          <t>2026-06-02T13:30:07.296367+00:00</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:51.877841+00:00</t>
+          <t>2026-06-02T13:30:14.991019+00:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168571</t>
+          <t>2026-06-02T13:30:15.002287+00:00</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:53.699232+00:00</t>
+          <t>2026-06-02T13:30:22.207259+00:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168593</t>
+          <t>2026-06-02T13:30:22.219874+00:00</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:55.671561+00:00</t>
+          <t>2026-06-02T13:30:30.862208+00:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168617</t>
+          <t>2026-06-02T13:30:30.873608+00:00</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:57.666497+00:00</t>
+          <t>2026-06-02T13:30:38.394960+00:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168638</t>
+          <t>2026-06-02T13:30:38.406355+00:00</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-06-02T12:17:59.523233+00:00</t>
+          <t>2026-06-02T13:30:45.430180+00:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168660</t>
+          <t>2026-06-02T13:30:45.441557+00:00</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:01.492184+00:00</t>
+          <t>2026-06-02T13:30:52.862823+00:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168688</t>
+          <t>2026-06-02T13:30:52.874227+00:00</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:03.347515+00:00</t>
+          <t>2026-06-02T13:31:00.046061+00:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168710</t>
+          <t>2026-06-02T13:31:00.058696+00:00</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:05.133060+00:00</t>
+          <t>2026-06-02T13:31:07.175754+00:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168733</t>
+          <t>2026-06-02T13:31:07.187272+00:00</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:07.037192+00:00</t>
+          <t>2026-06-02T13:31:14.450185+00:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168757</t>
+          <t>2026-06-02T13:31:14.461934+00:00</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:08.883118+00:00</t>
+          <t>2026-06-02T13:31:22.293631+00:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168779</t>
+          <t>2026-06-02T13:31:22.305378+00:00</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:10.872078+00:00</t>
+          <t>2026-06-02T13:31:29.167560+00:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168802</t>
+          <t>2026-06-02T13:31:29.179023+00:00</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:12.713202+00:00</t>
+          <t>2026-06-02T13:31:36.329327+00:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168825</t>
+          <t>2026-06-02T13:31:36.341891+00:00</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:14.627652+00:00</t>
+          <t>2026-06-02T13:31:43.715785+00:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168848</t>
+          <t>2026-06-02T13:31:43.727161+00:00</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:16.496987+00:00</t>
+          <t>2026-06-02T13:31:51.571886+00:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168870</t>
+          <t>2026-06-02T13:31:51.583312+00:00</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:19.178644+00:00</t>
+          <t>2026-06-02T13:31:58.457427+00:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168893</t>
+          <t>2026-06-02T13:31:58.468978+00:00</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:21.205930+00:00</t>
+          <t>2026-06-02T13:32:05.544018+00:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168915</t>
+          <t>2026-06-02T13:32:05.555498+00:00</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:22.997360+00:00</t>
+          <t>2026-06-02T13:32:12.906442+00:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168937</t>
+          <t>2026-06-02T13:32:12.950298+00:00</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:24.953413+00:00</t>
+          <t>2026-06-02T13:32:19.264518+00:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168961</t>
+          <t>2026-06-02T13:32:19.275857+00:00</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:26.910700+00:00</t>
+          <t>2026-06-02T13:32:26.159452+00:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.168983</t>
+          <t>2026-06-02T13:32:26.170782+00:00</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:29.245188+00:00</t>
+          <t>2026-06-02T13:32:33.151233+00:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.169006</t>
+          <t>2026-06-02T13:32:33.162456+00:00</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:31.161115+00:00</t>
+          <t>2026-06-02T13:32:40.185234+00:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.169031</t>
+          <t>2026-06-02T13:32:40.196594+00:00</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:33.110028+00:00</t>
+          <t>2026-06-02T13:32:48.060894+00:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.169053</t>
+          <t>2026-06-02T13:32:48.073395+00:00</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:34.964548+00:00</t>
+          <t>2026-06-02T13:32:56.925999+00:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.169076</t>
+          <t>2026-06-02T13:32:56.937374+00:00</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:36.786439+00:00</t>
+          <t>2026-06-02T13:33:03.941267+00:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.169100</t>
+          <t>2026-06-02T13:33:03.952707+00:00</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:38.564997+00:00</t>
+          <t>2026-06-02T13:33:11.215371+00:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.169123</t>
+          <t>2026-06-02T13:33:11.226777+00:00</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:40.589283+00:00</t>
+          <t>2026-06-02T13:33:18.803800+00:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.169146</t>
+          <t>2026-06-02T13:33:18.815289+00:00</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:42.487618+00:00</t>
+          <t>2026-06-02T13:33:25.818937+00:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.169170</t>
+          <t>2026-06-02T13:33:25.831776+00:00</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:45.637863+00:00</t>
+          <t>2026-06-02T13:33:34.320850+00:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.169193</t>
+          <t>2026-06-02T13:33:34.332256+00:00</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-06-02T12:18:47.440251+00:00</t>
+          <t>2026-06-02T13:33:42.212225+00:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2026-06-02T13:04:37.169215</t>
+          <t>2026-06-02T13:33:42.223669+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U51"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2868,6 +2868,1202 @@
       <c r="U51" t="inlineStr">
         <is>
           <t>2026-06-02T13:33:42.223669+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1000283986</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>jmm@mosskelley.com</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John Mushinsky</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>533 NW 1ST AVE</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:55.801976+00:00</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.427587+00:00</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:55.815299+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1000283969</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Caroline@legacyfortitle.com</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Legacy Settlement Services, LLC</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>6812 41ST AVE E</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:28:03.741744+00:00</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.461962+00:00</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:28:03.760059+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1000283915</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>riveracyn@gmail.com</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>CYNTHIA RIVERA</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>728 AVON RD</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:28:13.880528+00:00</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.493365+00:00</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:28:13.895329+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1000283902</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>creativeconstructionusa@gmail.com</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Creative Construction USA</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>12214 RIPPLE DR</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:28:21.043717+00:00</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.524385+00:00</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:28:21.057713+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1000283884</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>details_missing</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>tori4513@icloud.com</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Víctor López </t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>3816 GULF SHORE CIR</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:28:27.931054+00:00</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.556440+00:00</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:28:27.945147+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1000283805</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>chaz@cedarsteelfl.com</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Cedar and Steel Construction</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>751 NE 44TH ST</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.587990+00:00</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.587990+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1000283792</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Tatiana@nieverawilliams.com</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Nievera Williams Design</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>8 DRIFTWOOD LANDING</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.620737+00:00</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.620737+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1000283790</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>beachbumcapemay@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Kenn Mann</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>856 N SHORE DR</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.653540+00:00</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.653540+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1000283771</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>fernando@thearchitectgroup.com</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Sandra Puerta</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1420 LAKE AVE</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.685716+00:00</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.685716+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1000283753</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ddicarloanderson@gmail.com</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Dominique Anderson</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>905 E MCBERRY ST</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.719638+00:00</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.719638+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1000283728</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>diti@horizoncrr.com</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DITI  GLAZER</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>7800 LAKE WORTH RD</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.752552+00:00</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.752552+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1000283564</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>admin@sabollaw.com</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Law Offices of Cary P. Sabol</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>5301 S DIXIE HWY</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.821363+00:00</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.821363+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1000283532</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Office@bcminc.net</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Bartlett Construction Management, Inc.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>10529 HAPPY HOLLOW AVE</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.855403+00:00</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.855403+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1000283524</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>sknsv10@gmail.com</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Steve Livingston</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>12507 CORTEZ RD W UNIT 60</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.888621+00:00</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.888621+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1000283486</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>gmb@raslg.com</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Garrett Bender</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>610 SE 3RD AVE</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.923734+00:00</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.923734+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1000283289</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>jordana@jljpa.com</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Jordana Jarjura</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>9721 SE GOMEZ AVE</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.961394+00:00</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.961394+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1000283226</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ilissa.ruiz@gmail.com</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Ilissa Ruiz</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>9492 SW 67TH ST</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.995246+00:00</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:47.995246+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1000283094</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>aldotolentino@gmail.com</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aldo Tolentino</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2767 PINEHURST DR</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.030487+00:00</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.030487+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1000283046</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>mmtiernan01@gmail.com</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marlene M. Tiernan </t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1750 SE MINORCA AVE</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.064966+00:00</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.064966+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1000282975</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>david_Garrido@aol.com</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>David Garrido</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2432 NE 13TH AVE</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.100760+00:00</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.100760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1000282846</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>christian.benitez@icloud.com</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Christian Benitez</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>8667 SE ANTIGUA WAY</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.137184+00:00</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.137184+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1000282649</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>rachelweisz701@gmail.com</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Rachel Weisz</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>9001 TUDOR DR H210</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.172564+00:00</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.172564+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1000282513</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>jackie@jackiealbarran.com</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>SKA Architect</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>350 ISLAND RD</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.210018+00:00</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.210018+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1000282430</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>jake.kramer@gmail.com</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>John Kramer</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">326 S H ST, S H ST AND 320 S H ST </t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.247911+00:00</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.247911+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1000282337</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>braveheart1965@gmail.com</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PETER THOMAS</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>5201 NE 33RD AVE</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.285527+00:00</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.285527+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1000282290</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>roberto@salermo.net</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Roberto Salermo</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>901 TROPIC DR</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.322563+00:00</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.322563+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1000282280</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ahorovits@helmequities.com</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Ayal Horovits</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>4539 PINE TREE DR</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.361010+00:00</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.361010+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1000282200</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Land Survey and Elevation</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>manny@rackelectric.com</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Rack Electric LLC</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2717 SE 14TH ST</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.451145+00:00</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:27:48.451145+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3137,6 +3137,11 @@
           <t>751 NE 44TH ST</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:33:05.068152+00:00</t>
+        </is>
+      </c>
       <c r="T57" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:47.587990+00:00</t>
@@ -3144,7 +3149,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:47.587990+00:00</t>
+          <t>2026-06-02T14:33:05.081791+00:00</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3161,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3179,6 +3184,11 @@
           <t>8 DRIFTWOOD LANDING</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:33:13.060042+00:00</t>
+        </is>
+      </c>
       <c r="T58" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:47.620737+00:00</t>
@@ -3186,7 +3196,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:47.620737+00:00</t>
+          <t>2026-06-02T14:33:13.076008+00:00</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3208,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3221,6 +3231,11 @@
           <t>856 N SHORE DR</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:33:21.507528+00:00</t>
+        </is>
+      </c>
       <c r="T59" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:47.653540+00:00</t>
@@ -3228,7 +3243,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:47.653540+00:00</t>
+          <t>2026-06-02T14:33:21.522986+00:00</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3255,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3263,6 +3278,11 @@
           <t>1420 LAKE AVE</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:33:28.321699+00:00</t>
+        </is>
+      </c>
       <c r="T60" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:47.685716+00:00</t>
@@ -3270,7 +3290,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:47.685716+00:00</t>
+          <t>2026-06-02T14:33:28.336035+00:00</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3302,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3305,6 +3325,11 @@
           <t>905 E MCBERRY ST</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:33:35.542353+00:00</t>
+        </is>
+      </c>
       <c r="T61" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:47.719638+00:00</t>
@@ -3312,7 +3337,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:47.719638+00:00</t>
+          <t>2026-06-02T14:33:35.557855+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -3349,7 +3349,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3364,12 +3364,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>DITI  GLAZER</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>7800 LAKE WORTH RD</t>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"order_id": "1000283728", "customer_email": "diti@horizoncrr.com", "service_type": "Land Survey Only", "county": ""}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Unknown", "confidence": "LOW"}, "client_email": {"value": "diti@horizoncrr.com", "confidence": "HIGH"}, "property_address": {"value": "Unknown", "confidence": "LOW"}, "property_county": {"value": "Unknown", "confidence": "LOW"}, "services_requested": {"value": ["Land Survey"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data"}, "special_requirements": {"value": "None identified", "confidence": "LOW"}, "lot_size": {"value": "Unknown", "confidence": "LOW"}, "legal_description": {"value": "Unknown", "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property data available to identify pool, shed, driveways, or other visible structures"}, "client_tier": {"value": "unknown", "confidence": "LOW"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name not provided", "Property address is missing", "Property county is missing \u2014 required for appraiser lookup", "No matching emails found to supplement order data", "Lot size unknown", "Legal description unknown", "Structure square footage unknown", "Property features unknown", "Client tier (residential vs. B2B) unclear \u2014 domain 'horizoncrr.com' may suggest B2B but unconfirmed", "Urgency/timeline not specified", "Special requirements unknown"], "summary": "Minimal-data land survey order for customer diti@horizoncrr.com (Order #1000283728) with no property address, county, or client details provided \u2014 requires significant human follow-up before processing."}}</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:39:06.712640+00:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -3379,7 +3389,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:47.752552+00:00</t>
+          <t>2026-06-02T14:39:06.726338+00:00</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3401,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3406,12 +3416,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Law Offices of Cary P. Sabol</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>5301 S DIXIE HWY</t>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"order_id": "1000283564", "customer_email": "admin@sabollaw.com", "service_type": "Land Survey Only", "county": ""}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Unknown", "confidence": "LOW"}, "client_email": {"value": "admin@sabollaw.com", "confidence": "HIGH"}, "property_address": {"value": "Unknown", "confidence": "LOW"}, "property_county": {"value": "Unknown", "confidence": "LOW"}, "services_requested": {"value": ["Land Survey"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'Land Survey Only'; specific survey type (boundary, topographic, etc.) not specified"}, "special_requirements": {"value": "Unknown", "confidence": "LOW"}, "lot_size": {"value": "Unknown", "confidence": "LOW"}, "legal_description": {"value": "Unknown", "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property data available to identify pool, shed, driveways, or other visible structures"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name not provided", "Property address unknown", "Property county not provided \u2014 appraiser lookup unavailable", "Specific survey type not clarified (boundary, topographic, ALTA, etc.)", "Lot size unknown", "Legal description unknown", "Special requirements or instructions not provided", "Urgency/timeline not specified", "No matching emails found to supplement order data"], "summary": "Minimal B2B land survey order (#1000283564) submitted via admin@sabollaw.com with no property address, county, or client details provided \u2014 requires significant human follow-up before processing."}}</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:39:14.479559+00:00</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -3421,7 +3441,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:47.821363+00:00</t>
+          <t>2026-06-02T14:39:14.495198+00:00</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3453,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3448,7 +3468,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bartlett Construction Management, Inc.</t>
+          <t>BCM Inc.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3456,6 +3476,16 @@
           <t>10529 HAPPY HOLLOW AVE</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"order_id": "1000283532", "customer_email": "Office@bcminc.net", "service_type": "Quote", "county": ""}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "BCM Inc.", "confidence": "MEDIUM"}, "client_email": {"value": "Office@bcminc.net", "confidence": "HIGH"}, "property_address": {"value": null, "confidence": "LOW"}, "property_county": {"value": null, "confidence": "LOW"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed as 'Quote' only \u2014 no specific survey service has been identified yet"}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property data available to identify features"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Property address is missing", "County is missing \u2014 appraiser lookup unavailable", "Specific survey service(s) requested not identified", "Lot size unknown", "Legal description unknown", "Structure square footage unknown", "Property features unknown", "No matching emails found for additional context", "No customer profile data available", "Urgency/timeline not specified", "Client contact name not provided"], "summary": "An incoming quote request from BCM Inc. (Office@bcminc.net) with no property address, county, or specific survey services identified \u2014 significant human follow-up required to complete the order."}}</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:39:22.472601+00:00</t>
+        </is>
+      </c>
       <c r="T64" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:47.855403+00:00</t>
@@ -3463,7 +3493,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:47.855403+00:00</t>
+          <t>2026-06-02T14:39:22.488115+00:00</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3505,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3490,13 +3520,44 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Steve Livingston</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>12507 CORTEZ RD W UNIT 60</t>
-        </is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "Possible condo \u2014 address contains 'UNIT' indicator", "confidence": "N/A", "escalate_flag": true, "escalate_reason": "Possible condo \u2014 address contains 'UNIT' indicator", "flags": ["condo_rejected"]}</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"order_id": "1000283524", "customer_email": "sknsv10@gmail.com", "service_type": "Land Survey Only", "county": ""}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Unknown", "confidence": "LOW"}, "client_email": {"value": "sknsv10@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "Unknown", "confidence": "LOW"}, "property_county": {"value": "Unknown", "confidence": "LOW"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated in FTF order data; specific survey type (boundary, topo, etc.) not specified"}, "special_requirements": {"value": "None noted", "confidence": "LOW"}, "lot_size": {"value": "Unknown", "confidence": "LOW"}, "legal_description": {"value": "Unknown", "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property data available; pool, shed, driveways, and other structures unknown"}, "client_tier": {"value": "unknown", "confidence": "LOW"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name not provided", "Property address not provided", "Property county not provided \u2014 county appraiser lookup unavailable", "No matching emails found \u2014 unable to cross-reference customer history", "Customer data record is empty", "Specific survey type not clarified (boundary, topographic, as-built, etc.)", "Lot size unknown", "Legal description unknown", "Property features unknown", "Special requirements unknown", "Urgency/rush status unknown", "Client tier (residential vs. B2B) unknown"], "summary": "Minimal FTF order for a Land Survey Only service tied to email sknsv10@gmail.com, with no property address, county, or client details provided \u2014 requires significant human follow-up before processing."}}</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1780410997935</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:39:31.157558+00:00</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:39:59.692717+00:00</t>
+        </is>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -3505,7 +3566,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:47.888621+00:00</t>
+          <t>2026-06-02T14:39:59.708236+00:00</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3578,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3532,12 +3593,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Garrett Bender</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>610 SE 3RD AVE</t>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"order_id": "1000283486", "customer_email": "gmb@raslg.com", "service_type": "CAD", "county": ""}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Unknown", "confidence": "LOW"}, "client_email": {"value": "gmb@raslg.com", "confidence": "HIGH"}, "property_address": {"value": "Unknown", "confidence": "LOW"}, "property_county": {"value": "Unknown", "confidence": "LOW"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type listed as CAD in FTF order data; specific CAD deliverable scope unknown"}, "special_requirements": {"value": "Unknown", "confidence": "LOW"}, "lot_size": {"value": "Unknown", "confidence": "LOW"}, "legal_description": {"value": "Unknown", "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property data available to assess features such as pool, shed, driveways, or visible structures"}, "client_tier": {"value": "unknown", "confidence": "LOW"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name not provided", "Property address not provided", "Property county not provided \u2014 county appraiser lookup unavailable", "No matching emails found \u2014 unable to supplement order details", "No customer profile data available", "Specific CAD deliverable scope unknown (e.g., boundary CAD, topographic CAD, as-built CAD)", "Lot size unknown", "Legal description unknown", "Structure square footage unknown", "Property features unknown", "Client tier (residential vs. B2B) unknown", "Urgency/rush status unknown", "Special requirements unknown"], "summary": "Minimal CAD order (ID 1000283486) from gmb@raslg.com with no property address, county, client name, or scope details available \u2014 requires significant human follow-up before processing."}}</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:39:39.956755+00:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -3547,7 +3618,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:47.923734+00:00</t>
+          <t>2026-06-02T14:39:39.971505+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -3349,7 +3349,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3372,16 +3372,37 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>{"total_amount": 1000.0, "services": [{"name": "Land Survey (Boundary)", "description": "Base boundary survey rate per negotiated client agreement with DITI GLAZER", "amount": 450.0}, {"name": "Lot Size Complexity Upcharge (2.01\u20135.00 ac)", "description": "Property is 2.76 acres, falling in the 2.01\u20135.00 ac tier, warranting a complexity upcharge for additional field time and traverse work", "amount": 550.0}], "pricing_reasoning": "The negotiated base rate of $450.00 is applied per management agreement for client DITI GLAZER. The property is 2.76 acres, which places it squarely in the 2.01\u20135.00 ac complexity tier, adding $550.00. No Elevation Certificate was requested, the FEMA zone is X (non-special flood hazard), no legal description was provided to indicate metes-and-bounds complexity, and this is Palm Beach County (no Monroe County surcharge applies). The commercial flag is noted but the service is priced as a standard boundary survey per the order; no additional commercial upcharge is defined in the pricing guidelines.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "Multiple issues require human follow-up before processing: (1) No legal description was provided \u2014 cannot confirm boundary complexity, metes-and-bounds applicability, or parcel identity. (2) Order notes explicitly flag this as a minimal-data order requiring significant human follow-up. (3) A likely duplicate order exists (Order 1000278035) for the same address, same Folio, and same county \u2014 verify whether this is a re-order or duplicate submission before proceeding. (4) Commercial flag is true but client tier is INDIVIDUAL \u2014 this mismatch should be confirmed with the client or account manager.", "flags": ["POSSIBLE DUPLICATE: Order 1000278035 references the same property \u2014 7800 LAKE WORTH RD, Palm Beach County \u2014 same Folio/MLS (00424428010000640) and coordinates. Human review required before processing.", "NO LEGAL DESCRIPTION provided \u2014 cannot confirm parcel boundaries, metes-and-bounds complexity, or acreage accuracy. Field crew should verify lot size against county records.", "CLIENT TIER MISMATCH: Commercial flag is true, but client tier is listed as INDIVIDUAL. Confirm with account manager whether commercial pricing or any additional scope applies.", "ZERO ORDER HISTORY: DITI GLAZER is a first-time client with 0 prior orders. Verify negotiated rate authorization before invoicing.", "MINIMAL DATA ORDER: Per order notes, no property address, county, or client details were originally provided \u2014 confirm all details have been properly resolved before dispatch."]}</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>{"ftf_order": {"order_id": "1000283728", "customer_email": "diti@horizoncrr.com", "service_type": "Land Survey Only", "county": ""}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Unknown", "confidence": "LOW"}, "client_email": {"value": "diti@horizoncrr.com", "confidence": "HIGH"}, "property_address": {"value": "Unknown", "confidence": "LOW"}, "property_county": {"value": "Unknown", "confidence": "LOW"}, "services_requested": {"value": ["Land Survey"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data"}, "special_requirements": {"value": "None identified", "confidence": "LOW"}, "lot_size": {"value": "Unknown", "confidence": "LOW"}, "legal_description": {"value": "Unknown", "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property data available to identify pool, shed, driveways, or other visible structures"}, "client_tier": {"value": "unknown", "confidence": "LOW"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name not provided", "Property address is missing", "Property county is missing \u2014 required for appraiser lookup", "No matching emails found to supplement order data", "Lot size unknown", "Legal description unknown", "Structure square footage unknown", "Property features unknown", "Client tier (residential vs. B2B) unclear \u2014 domain 'horizoncrr.com' may suggest B2B but unconfirmed", "Urgency/timeline not specified", "Special requirements unknown"], "summary": "Minimal-data land survey order for customer diti@horizoncrr.com (Order #1000283728) with no property address, county, or client details provided \u2014 requires significant human follow-up before processing."}}</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1780411199695</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>2026-06-02T14:39:06.712640+00:00</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:01:07.528334+00:00</t>
+        </is>
+      </c>
+      <c r="R62" t="n">
+        <v>1000</v>
+      </c>
       <c r="T62" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:47.752552+00:00</t>
@@ -3389,7 +3410,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2026-06-02T14:39:06.726338+00:00</t>
+          <t>2026-06-02T15:01:07.543464+00:00</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3422,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3424,16 +3445,37 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>{"total_amount": 512.0, "services": [{"name": "Land Survey", "description": "Boundary/land survey at negotiated OLD_TITLE client rate for Law Offices of Cary P. Sabol", "amount": 450.0}, {"name": "Lot Size Complexity Upcharge (0.31\u20130.50 ac)", "description": "Property is 0.49 acres, falling in the 0.31\u20130.50 ac tier; upcharge applied per complexity guidelines", "amount": 62.0}], "pricing_reasoning": "Service is Land Survey Only; no EC, topo, or combined service is indicated. The negotiated base rate of $450.00 applies as explicitly agreed by management for this client. The lot is 0.49 acres, squarely in the 0.31\u20130.50 ac complexity tier, warranting a $62.00 upcharge. FEMA Zone X carries no flood-zone premium; no Monroe County, waterfront, pool, metes-and-bounds, or heavy-vegetation complexity signals are present in the available data. The commercial flag is noted but does not trigger a separate line item under current guidelines.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "Order notes explicitly state this was submitted with no property address, county, or client details and requires significant human follow-up before processing. Although some details have since been populated (address, county, lot size), the incomplete submission history and missing legal description mean field conditions cannot be fully validated from available data. A human reviewer should confirm the legal description, verify no additional complexity factors exist (e.g., metes-and-bounds, access issues at a commercial S Dixie Hwy parcel), and ensure all client details are resolved before the invoice is finalized.", "flags": ["ORDER NOTES WARNING: Order was originally submitted via admin@sabollaw.com with no property address, county, or client details \u2014 human follow-up required to confirm completeness before invoicing.", "LEGAL DESCRIPTION MISSING: No legal description provided; cannot confirm whether metes-and-bounds complexity upcharge (+$100.00) applies. If the parcel is described by metes and bounds rather than a platted lot, total should be revised to $612.00.", "COMMERCIAL FLAG: Property is flagged as commercial (5301 S Dixie Hwy, Palm Beach County). Commercial parcels on a major arterial may carry access, boundary, or right-of-way complexities not captured in standard residential upcharge tiers \u2014 reviewer should assess.", "CERTIFICATION: Survey to be certified to ELOINE DEL VALLE \u2014 confirm this name and any lender/title company co-certification requirements before delivery."]}</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>{"ftf_order": {"order_id": "1000283564", "customer_email": "admin@sabollaw.com", "service_type": "Land Survey Only", "county": ""}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Unknown", "confidence": "LOW"}, "client_email": {"value": "admin@sabollaw.com", "confidence": "HIGH"}, "property_address": {"value": "Unknown", "confidence": "LOW"}, "property_county": {"value": "Unknown", "confidence": "LOW"}, "services_requested": {"value": ["Land Survey"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'Land Survey Only'; specific survey type (boundary, topographic, etc.) not specified"}, "special_requirements": {"value": "Unknown", "confidence": "LOW"}, "lot_size": {"value": "Unknown", "confidence": "LOW"}, "legal_description": {"value": "Unknown", "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property data available to identify pool, shed, driveways, or other visible structures"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name not provided", "Property address unknown", "Property county not provided \u2014 appraiser lookup unavailable", "Specific survey type not clarified (boundary, topographic, ALTA, etc.)", "Lot size unknown", "Legal description unknown", "Special requirements or instructions not provided", "Urgency/timeline not specified", "No matching emails found to supplement order data"], "summary": "Minimal B2B land survey order (#1000283564) submitted via admin@sabollaw.com with no property address, county, or client details provided \u2014 requires significant human follow-up before processing."}}</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1780412468482</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>2026-06-02T14:39:14.479559+00:00</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:01:28.331304+00:00</t>
+        </is>
+      </c>
+      <c r="R63" t="n">
+        <v>512</v>
+      </c>
       <c r="T63" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:47.821363+00:00</t>
@@ -3441,7 +3483,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2026-06-02T14:39:14.495198+00:00</t>
+          <t>2026-06-02T15:01:28.346940+00:00</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3495,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3476,16 +3518,37 @@
           <t>10529 HAPPY HOLLOW AVE</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "This order arrived as an inbound quote request from BCM Inc. with no specific survey service identified (boundary survey, EC, topo, or other). The order notes explicitly state that significant human follow-up is required to determine what services are needed before any pricing can be proposed. Additionally, a likely duplicate order (1000282533) exists at the same address and folio for a Land Survey Only service, which further requires human review to determine whether this is a redundant request or a separate scope.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "Cannot price: no survey service type has been identified in this order. The order notes confirm the incoming request from BCM Inc. (Office@bcminc.net) lacked a property address, county, and specific services \u2014 all of which require human follow-up before quoting. Once the service type is confirmed, pricing can proceed using the client's negotiated base rate of $300.00 with applicable complexity upcharges (0.54 acres = +$137.00 lot size upcharge; metes-and-bounds legal description = +$100.00 pending field verification; EC if flood zone certification is requested at $275.00). A possible duplicate order (1000282533) at the same address/folio also requires resolution to avoid double-billing or redundant fieldwork.", "flags": ["NO_SERVICE_TYPE: Order submitted without identifying any specific survey service. Human follow-up required with BCM Inc. (Office@bcminc.net) before a quote can be issued.", "POSSIBLE_DUPLICATE: Order 1000282533 exists for the same property (10529 Happy Hollow Ave, Hillsborough County, Folio U-21-27-17-ZZZ-000000-13820.0) with service type 'Land Survey Only'. Confirm with client whether this is a separate scope or duplicate submission.", "METES_AND_BOUNDS: Legal description is metes-and-bounds with non-cardinal bearings and an incomplete description as provided. If boundary survey is confirmed, a +$100.00 complexity upcharge would apply pending full legal description review.", "LOT_SIZE_0.54AC: Once service is confirmed, a +$137.00 lot size upcharge (0.51\u20131.00 ac tier) would apply to the base survey rate.", "FEMA_DUAL_ZONE: Property falls in both Zone AE (panel 12057C0038H, elevation 42.5 ft) and Zone X. EC pricing would be $275.00 (no VE coastal surcharge applicable).", "CLIENT_RATE: Negotiated base survey rate of $300.00 applies per management agreement with Bartlett Construction Management, Inc."]}</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>{"ftf_order": {"order_id": "1000283532", "customer_email": "Office@bcminc.net", "service_type": "Quote", "county": ""}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "BCM Inc.", "confidence": "MEDIUM"}, "client_email": {"value": "Office@bcminc.net", "confidence": "HIGH"}, "property_address": {"value": null, "confidence": "LOW"}, "property_county": {"value": null, "confidence": "LOW"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed as 'Quote' only \u2014 no specific survey service has been identified yet"}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property data available to identify features"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Property address is missing", "County is missing \u2014 appraiser lookup unavailable", "Specific survey service(s) requested not identified", "Lot size unknown", "Legal description unknown", "Structure square footage unknown", "Property features unknown", "No matching emails found for additional context", "No customer profile data available", "Urgency/timeline not specified", "Client contact name not provided"], "summary": "An incoming quote request from BCM Inc. (Office@bcminc.net) with no property address, county, or specific survey services identified \u2014 significant human follow-up required to complete the order."}}</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1780412488221</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>2026-06-02T14:39:22.472601+00:00</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:01:48.601277+00:00</t>
+        </is>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
       <c r="T64" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:47.855403+00:00</t>
@@ -3493,7 +3556,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2026-06-02T14:39:22.488115+00:00</t>
+          <t>2026-06-02T15:01:48.616992+00:00</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3641,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3601,16 +3664,37 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>{"total_amount": 200.0, "services": [{"name": "CAD / Land Survey (Base Rate)", "description": "Boundary survey with CAD deliverable for LOT 23, BLOCK 7, OSCEOLA PARK, 610 SE 3RD AVE, Palm Beach County. 0.15-acre platted residential lot in FEMA Zone X (no flood elevation certificate required). Simple platted legal description \u2014 no metes-and-bounds complexity. No complexity upcharges supported by available data.", "amount": 200.0}], "pricing_reasoning": "The client (Garrett Bender, individual, first-time order) has a management-agreed base rate of $200.00, which governs this invoice. The property is a small 0.15-acre platted residential lot in Palm Beach County with a straightforward lot-and-block legal description, FEMA Zone X (no EC required), no pool/waterfront/vegetation/Monroe County complexity factors evident, and no lot-size upcharge triggers (lot is well under 0.31 ac). No upcharges are supported by the available data, so the final price equals the negotiated base rate.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "Order notes explicitly state this is a minimal CAD order submitted with no property address, county, client name, or scope details \u2014 significant human follow-up is required before processing. Additionally, the service type listed is 'CAD' without a clearly defined deliverable scope (boundary survey with CAD? CAD drafting only? redraw?), which must be clarified. The $200.00 base rate is applied provisionally pending scope confirmation.", "flags": ["DUPLICATE_WARNING: Order 1000215601 \u2014 same address (610 SE 3RD AVE, Palm Beach County), same Folio 12434621010070230 \u2014 service: Land Survey Only. Review before processing to avoid duplicate field work billing.", "DUPLICATE_WARNING: Order 1000281647 \u2014 same address (610 SE 3RD AVE, Palm Beach County), same Folio 12434621010070230 \u2014 service: Land Survey Only. Review before processing to avoid duplicate field work billing.", "SCOPE_UNCLEAR: 'CAD' service type is ambiguous \u2014 confirm with client whether this is a new boundary survey with CAD deliverable, a CAD redraw/conversion of existing survey data, or another CAD-only drafting task. Price may need adjustment based on confirmed scope.", "FIRST_TIME_CLIENT: Garrett Bender has 0 prior orders with NexGen. Verify negotiated $200.00 rate is correctly authorized for this order type.", "ORDER_NOTES_ALERT: Submitter email gmb@raslg.com \u2014 confirm client identity and authorization before proceeding."]}</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>{"ftf_order": {"order_id": "1000283486", "customer_email": "gmb@raslg.com", "service_type": "CAD", "county": ""}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Unknown", "confidence": "LOW"}, "client_email": {"value": "gmb@raslg.com", "confidence": "HIGH"}, "property_address": {"value": "Unknown", "confidence": "LOW"}, "property_county": {"value": "Unknown", "confidence": "LOW"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type listed as CAD in FTF order data; specific CAD deliverable scope unknown"}, "special_requirements": {"value": "Unknown", "confidence": "LOW"}, "lot_size": {"value": "Unknown", "confidence": "LOW"}, "legal_description": {"value": "Unknown", "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property data available to assess features such as pool, shed, driveways, or visible structures"}, "client_tier": {"value": "unknown", "confidence": "LOW"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name not provided", "Property address not provided", "Property county not provided \u2014 county appraiser lookup unavailable", "No matching emails found \u2014 unable to supplement order details", "No customer profile data available", "Specific CAD deliverable scope unknown (e.g., boundary CAD, topographic CAD, as-built CAD)", "Lot size unknown", "Legal description unknown", "Structure square footage unknown", "Property features unknown", "Client tier (residential vs. B2B) unknown", "Urgency/rush status unknown", "Special requirements unknown"], "summary": "Minimal CAD order (ID 1000283486) from gmb@raslg.com with no property address, county, client name, or scope details available \u2014 requires significant human follow-up before processing."}}</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1780412509100</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>2026-06-02T14:39:39.956755+00:00</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:02:08.457721+00:00</t>
+        </is>
+      </c>
+      <c r="R66" t="n">
+        <v>200</v>
+      </c>
       <c r="T66" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:47.923734+00:00</t>
@@ -3618,7 +3702,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>2026-06-02T14:39:39.971505+00:00</t>
+          <t>2026-06-02T15:02:08.473757+00:00</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3714,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3650,8 +3734,39 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>9721 SE GOMEZ AVE</t>
-        </is>
+          <t>9721 SE Gomez Ave, Hobe Sound, FL 33455</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "AI pricing failed: Unterminated string starting at: line 28 column 5 (char 2595). Manual review required.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "AI pricing error \u2014 needs manual quote", "flags": ["ai_error"]}</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202604131903248574, "created_at": "2026-05-06T14:24:20", "customer_email": "jordana@jljpa.com", "customer_id": 202604131903249694, "customer_name": "Jordana Jarjura", "customer_type": "individual", "delivered_at": "2026-05-21T14:26:51", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12085C0309H\nZONE: AE\nELEV: 04 FT\nEFF: O2/19/2020", "invoiced": false, "order_id": 1000283289, "paid": true, "property_address": "9721 SE GOMEZ AVE", "property_city": "HOBE SOUND", "property_county": "MARTIN COUNTY", "property_lat": "27.086838", "property_lng": "-80.136788", "property_state": "FL", "property_zip": "33455", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-05-21T14:26:51"}, "success": true, "order_id": "1000283289", "customer_email": "jordana@jljpa.com", "service_type": "Land Survey Only", "county": "", "property_address": "9721 SE GOMEZ AVE", "customer_name": "Jordana Jarjura"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Jordana Jarjura", "confidence": "HIGH"}, "client_email": {"value": "jordana@jljpa.com", "confidence": "HIGH"}, "property_address": {"value": "9721 SE Gomez Ave, Hobe Sound, FL 33455", "confidence": "HIGH"}, "property_county": {"value": "Martin County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing applied; property is in FEMA Flood Zone AE (panel 12085C0309H, effective 02/19/2020, base flood elevation 4 ft)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial imagery, or email attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, outbuildings, etc.) unknown \u2014 no aerial or appraiser data", "No matching emails found \u2014 no additional client instructions or context", "Fieldwork date not yet scheduled (fieldwork_at is null)", "Invoice has not been sent (invoiced: false) despite order being delivered and paid"], "summary": "Residential land survey order for Jordana Jarjura at 9721 SE Gomez Ave, Hobe Sound, FL (Martin County), delivered and paid, with special pricing applied and the property located in FEMA Flood Zone AE."}}</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1780412549435</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:00:10.128649+00:00</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:02:30.465864+00:00</t>
+        </is>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -3660,7 +3775,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:47.961394+00:00</t>
+          <t>2026-06-02T15:02:30.481746+00:00</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3787,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3692,8 +3807,39 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>9492 SW 67TH ST</t>
-        </is>
+          <t>9492 SW 67TH ST, MIAMI, FL 33173</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>{"total_amount": 612.0, "services": [{"name": "Land Survey", "description": "Residential boundary/land survey \u2014 individual client base rate for Miami-Dade County", "amount": 475.0}, {"name": "Lot Size Complexity Upcharge (0.51\u20131.00 ac)", "description": "Subject lot is 0.62 acres, falling within the 0.51\u20131.00 ac tier, warranting a complexity upcharge for additional field time and boundary traversal", "amount": 137.0}], "pricing_reasoning": "This is a standard residential land survey for an individual client (Ilissa Ruiz) in Miami-Dade County, priced from the $475.00 individual base rate. The 0.62-acre lot falls squarely in the 0.51\u20131.00 ac tier, supporting the $137.00 lot-size complexity upcharge. No EC was requested (FEMA Zone X carries no flood insurance mandate), the legal description is a clean platted lot reference (no metes-and-bounds upcharge), and no pool, waterfront, heavy vegetation, or Monroe County factors are indicated, so no further upcharges apply.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE_DUPLICATE: Order 1000272945 at the same address (9492 SW 67TH ST, Miami-Dade County), same service type (Land Survey Only), same Folio/MLS (3040280600050) and same coordinates \u2014 human review required before scheduling fieldwork to avoid redundant mobilisation."]}</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510131742072033, "created_at": "2026-05-05T16:58:01", "customer_email": "ilissa.ruiz@gmail.com", "customer_id": 202510131742072130, "customer_name": "Ilissa Ruiz", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0453L\nZONE: X\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000283226, "paid": true, "property_address": "9492 SW 67TH ST", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.7060149", "property_lng": "-80.34812989999999", "property_state": "FL", "property_zip": "33173", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-05-05T21:01:19"}, "success": true, "order_id": "1000283226", "customer_email": "ilissa.ruiz@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "9492 SW 67TH ST", "customer_name": "Ilissa Ruiz"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Ilissa Ruiz", "confidence": "HIGH"}, "client_email": {"value": "ilissa.ruiz@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "9492 SW 67TH ST, MIAMI, FL 33173", "confidence": "HIGH"}, "property_county": {"value": "MIAMI-DADE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data; no elevation certificate requested."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial imagery, or email attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fences, etc.) unknown \u2014 no aerial or appraiser data", "Special requirements or client notes not provided", "Order is currently 'On Hold' \u2014 reason for hold not specified", "No fieldwork date scheduled", "Urgency/rush status not indicated", "No matching emails found to supplement order details"], "summary": "Residential land survey order for Ilissa Ruiz at 9492 SW 67TH ST, Miami, FL 33173 (Miami-Dade County), currently on hold with no fieldwork scheduled and limited property detail available."}}</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1780412549435</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:00:19.418643+00:00</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:02:45.264712+00:00</t>
+        </is>
+      </c>
+      <c r="R68" t="n">
+        <v>612</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -3702,7 +3848,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:47.995246+00:00</t>
+          <t>2026-06-02T15:02:45.281684+00:00</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3860,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3734,7 +3880,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2767 PINEHURST DR</t>
+          <t>2767 Pinehurst Dr, Weston, FL 33332</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202605011943534931, "created_at": "2026-05-01T19:43:53", "customer_email": "aldotolentino@gmail.com", "customer_id": 202605011943535029, "customer_name": "Aldo Tolentino", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0510J\nZONE:X500\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000283094, "paid": false, "property_address": "2767 PINEHURST DR", "property_city": "WESTON", "property_county": "BROWARD COUNTY", "property_lat": "26.0850322", "property_lng": "-80.3920833", "property_state": "FLORIDA", "property_zip": "33332", "service_type": "Land Survey Only", "special_pricing": false, "status": "Quote", "status_code": 12, "updated_at": "2026-05-01T19:46:11"}, "success": true, "order_id": "1000283094", "customer_email": "aldotolentino@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "2767 PINEHURST DR", "customer_name": "Aldo Tolentino"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Aldo Tolentino", "confidence": "HIGH"}, "client_email": {"value": "aldotolentino@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "2767 Pinehurst Dr, Weston, FL 33332", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser unavailable", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, driveway, etc.) unknown \u2014 no aerial or appraiser data", "Special requirements or client notes not provided", "No pricing or estimate details yet (invoiced: false, estimate_sent: false)", "Fieldwork date not scheduled"], "summary": "Individual residential client Aldo Tolentino is requesting a Land Survey Only at 2767 Pinehurst Dr, Weston, FL 33332 (Broward County); order is in Quote status with no scheduling, pricing, or property detail data available yet."}}</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:00:27.841093+00:00</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -3744,7 +3900,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:48.030487+00:00</t>
+          <t>2026-06-02T15:00:27.856943+00:00</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3912,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3771,12 +3927,22 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marlene M. Tiernan </t>
+          <t>Marlene M. Tiernan</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1750 SE MINORCA AVE</t>
+          <t>1750 SE Minorca Ave, Port St. Lucie, FL 34952</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202605011406145191, "created_at": "2026-05-01T14:06:14", "customer_email": "mmtiernan01@gmail.com", "customer_id": 202605011406145297, "customer_name": "Marlene M. Tiernan", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12111C0293K \nZONE:  X\nEFF: 02/19/2020", "invoiced": false, "order_id": 1000283046, "paid": false, "property_address": "1750 SE MINORCA AVE", "property_city": "PORT ST. LUCIE", "property_county": "ST LUCIE COUNTY", "property_lat": "27.2718519", "property_lng": "-80.2988647", "property_state": "FLORIDA", "property_zip": "34952", "service_type": "Land Survey Only", "special_pricing": false, "status": "Quote", "status_code": 12, "updated_at": "2026-05-01T14:10:20"}, "success": true, "order_id": "1000283046", "customer_email": "mmtiernan01@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "1750 SE MINORCA AVE", "customer_name": "Marlene M. Tiernan "}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Marlene M. Tiernan", "confidence": "HIGH"}, "client_email": {"value": "mmtiernan01@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1750 SE Minorca Ave, Port St. Lucie, FL 34952", "confidence": "HIGH"}, "property_county": {"value": "St. Lucie County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser unavailable and no alternate source", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, fence, etc.) unknown \u2014 no aerial or appraiser data", "Special requirements or notes from client not provided", "No matching emails found to supplement order details", "Order is still in Quote status \u2014 not yet invoiced or scheduled"], "summary": "Individual residential client Marlene M. Tiernan is requesting a Land Survey Only at 1750 SE Minorca Ave, Port St. Lucie, FL 34952 (St. Lucie County); order is in Quote status with no lot size, legal description, or property feature data available."}}</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:00:36.736285+00:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -3786,7 +3952,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:48.064966+00:00</t>
+          <t>2026-06-02T15:00:36.751168+00:00</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3964,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3818,7 +3984,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2432 NE 13TH AVE</t>
+          <t>2432 NE 13TH AVE, POMPANO BEACH, FL 33064</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202602131835448972, "created_at": "2026-04-30T15:16:27", "customer_email": "david_Garrido@aol.com", "customer_id": 202602131835449810, "customer_name": "David Garrido", "customer_type": "individual", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0188J\nZONE: X500\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000282975, "paid": false, "property_address": "2432 NE 13TH AVE", "property_city": "POMPANO BEACH", "property_county": "Broward County", "property_lat": "26.2614294", "property_lng": "-80.10533559999999", "property_state": "FL", "property_zip": "33064", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-05-01T15:46:43"}, "success": true, "order_id": "1000282975", "customer_email": "david_Garrido@aol.com", "service_type": "CAD file", "county": "", "property_address": "2432 NE 13TH AVE", "customer_name": "David Garrido"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "David Garrido", "confidence": "HIGH"}, "client_email": {"value": "david_Garrido@aol.com", "confidence": "HIGH"}, "property_address": {"value": "2432 NE 13TH AVE, POMPANO BEACH, FL 33064", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD file; no additional services noted"}, "special_requirements": {"value": "Special pricing applied; order currently on hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or aerial data provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, etc.)", "County appraiser data unavailable", "No supporting emails found", "Reason for 'On Hold' status not documented", "Fieldwork date not scheduled", "Invoice not yet sent \u2014 due amount $250.00 outstanding"], "summary": "Individual residential client David Garrido has a CAD file order for 2432 NE 13TH AVE, Pompano Beach, FL (Broward County) currently on hold with special pricing applied and a $250.00 balance due, pending fieldwork scheduling and additional property details."}}</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:00:46.489876+00:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -3828,7 +4004,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:48.100760+00:00</t>
+          <t>2026-06-02T15:00:46.504887+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -3860,7 +3860,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3883,16 +3883,37 @@
           <t>2767 Pinehurst Dr, Weston, FL 33332</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>{"total_amount": 475.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for residential property at 2767 Pinehurst Dr, Weston, FL 33332 (Broward County). Lot size 0.28 acres falls within the base pricing tier (\u22640.30 ac). No complexity upcharges apply.", "amount": 475.0}], "pricing_reasoning": "This is a straightforward residential boundary survey for an individual homeowner (first-time client, no negotiated rate) in Broward County. The lot at 0.28 acres falls within the base tier (\u22640.30 ac), so no lot-size upcharge applies. FEMA Zone X500 is a moderate-risk zone outside the Special Flood Hazard Area \u2014 no Elevation Certificate was requested and none is warranted. No aerial indicators of a pool, waterfront canal, heavy vegetation, or metes-and-bounds description were identified, and Broward County carries no Monroe County remote mobilization premium. Base individual rate of $475.00 is applied as the full invoice amount.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": []}</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202605011943534931, "created_at": "2026-05-01T19:43:53", "customer_email": "aldotolentino@gmail.com", "customer_id": 202605011943535029, "customer_name": "Aldo Tolentino", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0510J\nZONE:X500\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000283094, "paid": false, "property_address": "2767 PINEHURST DR", "property_city": "WESTON", "property_county": "BROWARD COUNTY", "property_lat": "26.0850322", "property_lng": "-80.3920833", "property_state": "FLORIDA", "property_zip": "33332", "service_type": "Land Survey Only", "special_pricing": false, "status": "Quote", "status_code": 12, "updated_at": "2026-05-01T19:46:11"}, "success": true, "order_id": "1000283094", "customer_email": "aldotolentino@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "2767 PINEHURST DR", "customer_name": "Aldo Tolentino"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Aldo Tolentino", "confidence": "HIGH"}, "client_email": {"value": "aldotolentino@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "2767 Pinehurst Dr, Weston, FL 33332", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser unavailable", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, driveway, etc.) unknown \u2014 no aerial or appraiser data", "Special requirements or client notes not provided", "No pricing or estimate details yet (invoiced: false, estimate_sent: false)", "Fieldwork date not scheduled"], "summary": "Individual residential client Aldo Tolentino is requesting a Land Survey Only at 2767 Pinehurst Dr, Weston, FL 33332 (Broward County); order is in Quote status with no scheduling, pricing, or property detail data available yet."}}</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1780412845599</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>2026-06-02T15:00:27.841093+00:00</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:07:25.968695+00:00</t>
+        </is>
+      </c>
+      <c r="R69" t="n">
+        <v>475</v>
+      </c>
       <c r="T69" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:48.030487+00:00</t>
@@ -3900,7 +3921,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>2026-06-02T15:00:27.856943+00:00</t>
+          <t>2026-06-02T15:07:25.983892+00:00</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3933,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3935,16 +3956,37 @@
           <t>1750 SE Minorca Ave, Port St. Lucie, FL 34952</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>{"total_amount": 475.0, "services": [{"name": "Land Survey Only", "description": "Boundary/land survey for residential property at 1750 SE Minorca Ave, Port St. Lucie, FL 34952 (St. Lucie County). Lot size 0.23 acres, FEMA Zone X (no flood zone upcharge). Individual client base rate applied.", "amount": 475.0}], "pricing_reasoning": "This is a standard residential boundary survey for an individual homeowner in St. Lucie County with no negotiated rate on file, so the default individual base rate of $475.00 applies. The lot is 0.23 acres, which falls within the base tier (under 0.31 ac), so no lot-size upcharge is warranted. FEMA Zone X carries no flood-related complexity, the property is not in Monroe County, no legal description data indicates metes-and-bounds complexity, and no aerial or order-note evidence supports pool, waterfront, or heavy-vegetation upcharges.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE DUPLICATE: Order 1000090615 references the same address (1750 SE Minorca Ave, St. Lucie County), same service type (Land Survey Only), same coordinates (27.2718504, -80.2988287), and same Folio/MLS (3422-525-0777-000-4). Human review required before proceeding to avoid duplicate field work or billing.", "No legal description or property feature data was available at time of pricing; price is based on lot size from database and county defaults. If field conditions reveal additional complexity (e.g., metes-and-bounds description, vegetation, pool, or waterfront), a price adjustment may be warranted."]}</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202605011406145191, "created_at": "2026-05-01T14:06:14", "customer_email": "mmtiernan01@gmail.com", "customer_id": 202605011406145297, "customer_name": "Marlene M. Tiernan", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12111C0293K \nZONE:  X\nEFF: 02/19/2020", "invoiced": false, "order_id": 1000283046, "paid": false, "property_address": "1750 SE MINORCA AVE", "property_city": "PORT ST. LUCIE", "property_county": "ST LUCIE COUNTY", "property_lat": "27.2718519", "property_lng": "-80.2988647", "property_state": "FLORIDA", "property_zip": "34952", "service_type": "Land Survey Only", "special_pricing": false, "status": "Quote", "status_code": 12, "updated_at": "2026-05-01T14:10:20"}, "success": true, "order_id": "1000283046", "customer_email": "mmtiernan01@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "1750 SE MINORCA AVE", "customer_name": "Marlene M. Tiernan "}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Marlene M. Tiernan", "confidence": "HIGH"}, "client_email": {"value": "mmtiernan01@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1750 SE Minorca Ave, Port St. Lucie, FL 34952", "confidence": "HIGH"}, "property_county": {"value": "St. Lucie County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser unavailable and no alternate source", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, fence, etc.) unknown \u2014 no aerial or appraiser data", "Special requirements or notes from client not provided", "No matching emails found to supplement order details", "Order is still in Quote status \u2014 not yet invoiced or scheduled"], "summary": "Individual residential client Marlene M. Tiernan is requesting a Land Survey Only at 1750 SE Minorca Ave, Port St. Lucie, FL 34952 (St. Lucie County); order is in Quote status with no lot size, legal description, or property feature data available."}}</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1780412861528</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>2026-06-02T15:00:36.736285+00:00</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:07:41.852739+00:00</t>
+        </is>
+      </c>
+      <c r="R70" t="n">
+        <v>475</v>
+      </c>
       <c r="T70" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:48.064966+00:00</t>
@@ -3952,7 +3994,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>2026-06-02T15:00:36.751168+00:00</t>
+          <t>2026-06-02T15:07:41.867081+00:00</t>
         </is>
       </c>
     </row>
@@ -3964,7 +4006,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3987,16 +4029,37 @@
           <t>2432 NE 13TH AVE, POMPANO BEACH, FL 33064</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>{"total_amount": 250.0, "services": [{"name": "CAD File", "description": "CAD file deliverable for 2432 NE 13TH AVE, Pompano Beach, FL \u2014 Broward County. Management-agreed special pricing applied per order notes. Balance due per hold status.", "amount": 250.0}], "pricing_reasoning": "The order notes explicitly state that management has already applied special pricing with a $250.00 balance due for this CAD file order, and the account is currently on hold pending fieldwork scheduling. The negotiated base survey rate of $450.00 is noted, but the CAD file service with special pricing overrides that base for this specific deliverable as directed by management. No complexity upcharges, EC, or topo services are applicable here \u2014 this is a standalone CAD file order with a pre-agreed price. No lot size, FEMA zone, or feature-based upcharges are warranted for a CAD file deliverable alone.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_ORDER: Order 1000147954 \u2014 same address (2432 NE 13TH AVE, Broward County), same Folio/MLS (484224110690), service: Land Survey Only \u2014 flagged for human review.", "DUPLICATE_ORDER: Order 1000278705 \u2014 same address (2432 NE 13TH AVE, Broward County), same Folio/MLS (484224110690), service: Land Survey Only \u2014 flagged for human review.", "ON_HOLD: Order is currently on hold pending fieldwork scheduling and additional property details per order notes.", "SPECIAL_PRICING: Management-applied special pricing of $250.00 balance due is honored as instructed. No independent pricing recalculation applied."]}</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202602131835448972, "created_at": "2026-04-30T15:16:27", "customer_email": "david_Garrido@aol.com", "customer_id": 202602131835449810, "customer_name": "David Garrido", "customer_type": "individual", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0188J\nZONE: X500\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000282975, "paid": false, "property_address": "2432 NE 13TH AVE", "property_city": "POMPANO BEACH", "property_county": "Broward County", "property_lat": "26.2614294", "property_lng": "-80.10533559999999", "property_state": "FL", "property_zip": "33064", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-05-01T15:46:43"}, "success": true, "order_id": "1000282975", "customer_email": "david_Garrido@aol.com", "service_type": "CAD file", "county": "", "property_address": "2432 NE 13TH AVE", "customer_name": "David Garrido"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "David Garrido", "confidence": "HIGH"}, "client_email": {"value": "david_Garrido@aol.com", "confidence": "HIGH"}, "property_address": {"value": "2432 NE 13TH AVE, POMPANO BEACH, FL 33064", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD file; no additional services noted"}, "special_requirements": {"value": "Special pricing applied; order currently on hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or aerial data provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, etc.)", "County appraiser data unavailable", "No supporting emails found", "Reason for 'On Hold' status not documented", "Fieldwork date not scheduled", "Invoice not yet sent \u2014 due amount $250.00 outstanding"], "summary": "Individual residential client David Garrido has a CAD file order for 2432 NE 13TH AVE, Pompano Beach, FL (Broward County) currently on hold with special pricing applied and a $250.00 balance due, pending fieldwork scheduling and additional property details."}}</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1780412861528</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>2026-06-02T15:00:46.489876+00:00</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:07:57.765530+00:00</t>
+        </is>
+      </c>
+      <c r="R71" t="n">
+        <v>250</v>
+      </c>
       <c r="T71" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:48.100760+00:00</t>
@@ -4004,7 +4067,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>2026-06-02T15:00:46.504887+00:00</t>
+          <t>2026-06-02T15:07:57.779929+00:00</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4079,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4036,8 +4099,39 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>8667 SE ANTIGUA WAY</t>
-        </is>
+          <t>8667 SE ANTIGUA WAY, JUPITER, FL 33458</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>{"total_amount": 412.0, "services": [{"name": "CAD Drafting / Survey Base", "description": "Negotiated base rate for individual residential client Christian Benitez as agreed by management.", "amount": 250.0}, {"name": "Lot Size Complexity Upcharge (0.31\u20130.50 ac)", "description": "Property is 0.38 acres, falling in the 0.31\u20130.50 ac tier, warranting a standard size-based complexity upcharge.", "amount": 62.0}, {"name": "Metes &amp; Bounds Complexity Upcharge", "description": "Legal description is a metes-and-bounds portion-of-lot description (beginning at a specific corner with bearing/distance calls), not a simple platted lot number, increasing drafting and research complexity.", "amount": 100.0}], "pricing_reasoning": "Management has established a $250.00 negotiated base rate for this individual client. The lot at 0.38 acres falls in the 0.31\u20130.50 ac size tier (+$62.00). The legal description is a metes-and-bounds 'portion of lot' instrument rather than a simple platted lot reference, which meaningfully increases CAD drafting and title research complexity (+$100.00). No pool, waterfront canal, heavy vegetation, Monroe County, or VE flood zone factors are supported by the available data; FEMA Zone X carries no EC or flood-zone upcharge. Total: $412.00.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "Order notes state the CAD scope is not yet defined and property details/legal description were previously missing. The order is currently On Hold. Management should confirm the exact deliverable scope (e.g., CAD redraft from existing survey, new boundary CAD, sketch of description only) before finalizing pricing. Additionally, a possible duplicate order (1000277679) exists at the same address and folio for a Land Survey Only service \u2014 human review is required to determine whether these are companion orders, a re-order, or an accidental duplicate.", "flags": ["DUPLICATE_SUSPECTED: Order 1000277679 shares the same property address (8667 SE Antigua Way, Martin County), same coordinates (26.9757556, -80.1397936), and same folio (22-40-42-005-000-00030-1) with a Land Survey Only service. Human review required to determine relationship between orders before invoicing.", "SCOPE_UNDEFINED: Order notes confirm CAD scope is not clearly defined. Price above assumes standard CAD drafting from a metes-and-bounds legal description. If scope expands (e.g., full boundary survey fieldwork, topographic layers, or as-built), price must be revised.", "ON_HOLD: Order is currently On Hold per notes. Do not release invoice until management confirms scope and resolves duplicate flag."]}</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202601261516356844, "created_at": "2026-04-28T18:01:40", "customer_email": "christian.benitez@icloud.com", "customer_id": 202601261516356944, "customer_name": "Christian Benitez", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12085C0507H\nZONE: X\nEFF: 02/19/2020", "invoiced": false, "order_id": 1000282846, "paid": true, "property_address": "8667 SE ANTIGUA WAY", "property_city": "JUPITER", "property_county": "Martin County", "property_lat": "26.9757556", "property_lng": "-80.1397936", "property_state": "FL", "property_zip": "33458", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-04-29T13:48:35"}, "success": true, "order_id": "1000282846", "customer_email": "christian.benitez@icloud.com", "service_type": "CAD", "county": "", "property_address": "8667 SE ANTIGUA WAY", "customer_name": "Christian Benitez"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Christian Benitez", "confidence": "HIGH"}, "client_email": {"value": "christian.benitez@icloud.com", "confidence": "HIGH"}, "property_address": {"value": "8667 SE ANTIGUA WAY, JUPITER, FL 33458", "confidence": "HIGH"}, "property_county": {"value": "Martin County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type listed as CAD; no additional services specified. Exact scope of CAD deliverable is unclear without further context."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 county appraiser unavailable and no county provided in lookup", "Structure square footage unknown", "Property features (pool, shed, driveways, etc.) unknown \u2014 no aerial or appraiser data", "Exact CAD scope/deliverable not defined", "Reason for On Hold status not documented", "No customer data returned from FTF customer lookup", "No matching emails found \u2014 cannot confirm scope from client communications", "Flood zone panel 12085C0507H (Zone X, eff. 02/19/2020) noted but elevation certificate not requested \u2014 confirm if relevant to CAD order"], "summary": "Individual residential client Christian Benitez has a paid CAD order for 8667 SE Antigua Way, Jupiter, FL (Martin County) that is currently On Hold with special pricing applied, but lacks property details, legal description, and defined CAD scope."}}</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1780412877565</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:06:29.817963+00:00</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:08:19.303364+00:00</t>
+        </is>
+      </c>
+      <c r="R72" t="n">
+        <v>412</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -4046,7 +4140,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:48.137184+00:00</t>
+          <t>2026-06-02T15:08:19.317931+00:00</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4152,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4078,8 +4172,39 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>9001 TUDOR DR H210</t>
-        </is>
+          <t>9001 Tudor Dr H210, Tampa, FL 33615</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "This order is a quote request with no specific survey service identified. The property is a condominium unit (Unit H210) at 9001 Tudor Dr, Tampa, FL \u2014 a very small 0.01-acre interest typical of a condo unit, which often requires clarification on what survey product is even applicable (boundary surveys of individual condo units are generally not standard; the client may need an EC, an as-built, or something else entirely). No service type has been scoped, and follow-up with Rachel Weisz is required before any pricing can be proposed.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "No specific survey service has been identified for this order. The property is a condominium unit (0.01 acres), which raises additional scoping questions: a standard boundary survey is typically not applicable to an individual condo unit. The client must clarify what product they need (e.g., Elevation Certificate, as-built, condo association boundary, etc.) before a price can be calculated. Additionally, the FEMA flood zone is unknown \u2014 if an EC is ultimately requested, flood zone determination will be needed. Recommend client outreach to scope the service before pricing.", "flags": ["No survey service type specified \u2014 quote request requires follow-up with client Rachel Weisz.", "Property is a condominium unit (Unit H210, 0.01 acres) \u2014 standard boundary survey may not be applicable; service scope must be confirmed.", "FEMA flood zone is unknown \u2014 if an Elevation Certificate is requested, flood zone lookup is required to determine correct EC pricing.", "First-time client (0 prior orders) \u2014 no pricing history available for reference.", "Legal description is blank \u2014 will be needed once service is scoped."]}</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202604241449058960, "created_at": "2026-04-24T14:49:05", "customer_email": "rachelweisz701@gmail.com", "customer_id": 202604241449059066, "customer_name": "Rachel Weisz", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": null, "invoiced": false, "order_id": 1000282649, "paid": false, "property_address": "9001 TUDOR DR H210", "property_city": "TAMPA", "property_county": "Hillsborough County", "property_lat": "27.99762", "property_lng": "-82.58692099999999", "property_state": "FLORIDA", "property_zip": "33615", "service_type": "Quote", "special_pricing": false, "status": "Quote", "status_code": 12, "updated_at": "2026-04-24T15:22:29"}, "success": true, "order_id": "1000282649", "customer_email": "rachelweisz701@gmail.com", "service_type": "Quote", "county": "", "property_address": "9001 TUDOR DR H210", "customer_name": "Rachel Weisz"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Rachel Weisz", "confidence": "HIGH"}, "client_email": {"value": "rachelweisz701@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "9001 Tudor Dr H210, Tampa, FL 33615", "confidence": "HIGH"}, "property_county": {"value": "Hillsborough County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service has been identified yet. Needs human follow-up to determine actual service needed."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available; unit H210 suggests a condominium \u2014 pool, common areas, and shared structures may be relevant but unconfirmed."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service(s) requested not identified \u2014 order is still in Quote stage", "No legal description available", "No lot size available", "No structure square footage available", "Property appraiser data unavailable \u2014 could not verify parcel details", "No matching emails found \u2014 no additional context from client communications", "Special requirements unknown", "Unit H210 indicates a condo \u2014 surveying scope may be limited or require HOA/condo docs"], "summary": "Individual client Rachel Weisz has submitted a quote request for a property at 9001 Tudor Dr, Unit H210, Tampa, FL (Hillsborough County), but no specific survey service has been identified yet and additional follow-up is needed to scope the order."}}</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1780412565497</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:06:39.583345+00:00</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:08:34.935507+00:00</t>
+        </is>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -4088,7 +4213,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:48.172564+00:00</t>
+          <t>2026-06-02T15:08:34.950291+00:00</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4225,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4120,7 +4245,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>350 ISLAND RD</t>
+          <t>350 Island Rd, Palm Beach, FL 33480</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202604221615056728, "created_at": "2026-04-22T16:26:31", "customer_email": "jackie@jackiealbarran.com", "customer_id": 202604221615369976, "customer_name": "Jackie Albarran", "customer_type": "b2b", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0583G\nZONE: AE\nELEV: 07 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000282513, "paid": false, "property_address": "350 ISLAND RD", "property_city": "PALM BEACH", "property_county": "Palm Beach County", "property_lat": "26.6949056", "property_lng": "-80.0411004", "property_state": "FL", "property_zip": "33480", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-04-22T21:00:49"}, "success": true, "order_id": "1000282513", "customer_email": "jackie@jackiealbarran.com", "service_type": "CAD", "county": "", "property_address": "350 ISLAND RD", "customer_name": "SKA Architect"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "SKA Architect", "confidence": "MEDIUM"}, "client_email": {"value": "jackie@jackiealbarran.com", "confidence": "HIGH"}, "property_address": {"value": "350 Island Rd, Palm Beach, FL 33480", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type is CAD; no additional services specified. Elevation certificate not requested."}, "special_requirements": {"value": "Special pricing applied. Order is On Hold (status code 11). Flood zone AE, FIRM panel 12099C0583G, base flood elevation 7 ft, effective 12/20/2024.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no matching emails found."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order footer lists 'SKA Architect' but customer record shows 'Jackie Albarran' \u2014 confirm correct billing entity", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, outbuildings, driveways, etc.)", "Reason for On Hold status not documented", "Fieldwork date not scheduled", "No estimate sent \u2014 confirm scope and pricing before proceeding"], "summary": "B2B CAD order for 350 Island Rd, Palm Beach FL (Flood Zone AE) placed by SKA Architect / Jackie Albarran, currently On Hold with special pricing at $250 and missing lot size, legal description, and property feature details."}}</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:06:49.595917+00:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -4130,7 +4265,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:48.210018+00:00</t>
+          <t>2026-06-02T15:06:49.610311+00:00</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4277,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4162,7 +4297,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">326 S H ST, S H ST AND 320 S H ST </t>
+          <t>326 S H ST &amp; 320 S H ST, Lake Worth Beach, FL 33460</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202604211521474865, "created_at": "2026-04-21T15:22:43", "customer_email": "jake.kramer@gmail.com", "customer_id": 202604211521476304, "customer_name": "John Kramer", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0781G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000282430, "paid": true, "property_address": "326 S H ST, S H ST AND 320 S H ST ", "property_city": "LAKE WORTH BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.61154", "property_lng": "-80.058343", "property_state": "FL", "property_zip": "33460", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-04-22T05:57:21"}, "success": true, "order_id": "1000282430", "customer_email": "jake.kramer@gmail.com", "service_type": "CAD file", "county": "", "property_address": "326 S H ST, S H ST AND 320 S H ST ", "customer_name": "John Kramer"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "John Kramer", "confidence": "HIGH"}, "client_email": {"value": "jake.kramer@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "326 S H ST &amp; 320 S H ST, Lake Worth Beach, FL 33460", "confidence": "MEDIUM"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Only service type listed is CAD file; no additional services specified. Special pricing flag is set \u2014 may imply bundled or negotiated scope."}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); appears to involve two adjacent parcels (326 S H ST and 320 S H ST)", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available, no emails, no aerial data \u2014 pool, shed, driveways, and other features are unknown"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name and email may not match \u2014 'John Kramer' vs email 'jake.kramer@gmail.com'; verify correct contact", "Two parcels referenced (326 S H ST and 320 S H ST) \u2014 confirm if both are included in scope", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) unknown", "Reason for On Hold status not specified", "Scope of CAD file not defined \u2014 boundary, topographic, as-built, or other?", "Special pricing basis not documented", "No fieldwork date or delivery date set", "Invoice has not been sent despite order being marked paid \u2014 needs reconciliation"], "summary": "Residential CAD file order for John Kramer covering two adjacent parcels at 326 and 320 S H ST in Lake Worth Beach, FL, currently On Hold with special pricing applied and several key details missing including parcel scope, lot size, legal description, and CAD file type."}}</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:07:01.951689+00:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -4172,7 +4317,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:48.247911+00:00</t>
+          <t>2026-06-02T15:07:01.965199+00:00</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4329,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4204,7 +4349,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>5201 NE 33RD AVE</t>
+          <t>5201 NE 33RD AVE, FORT LAUDERDALE, FL 33308</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202604201539305493, "created_at": "2026-04-20T15:41:12", "customer_email": "braveheart1965@gmail.com", "customer_id": 202604201539306369, "customer_name": "PETER THOMAS", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0378J\nZONE: AE\nELEV: 07 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000282337, "paid": true, "property_address": "5201 NE 33RD AVE", "property_city": "FORT LAUDERDALE", "property_county": "BROWARD COUNTY", "property_lat": "26.1917228", "property_lng": "-80.1038611", "property_state": "FL", "property_zip": "33308", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-04-29T13:11:40"}, "success": true, "order_id": "1000282337", "customer_email": "braveheart1965@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "5201 NE 33RD AVE", "customer_name": "PETER THOMAS"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "PETER THOMAS", "confidence": "HIGH"}, "client_email": {"value": "braveheart1965@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "5201 NE 33RD AVE, FORT LAUDERDALE, FL 33308", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in FTF order data; no elevation certificate requested"}, "special_requirements": {"value": "Special pricing applied; order currently on hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, no emails, and no aerial imagery provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not available \u2014 county appraiser data unavailable", "Legal description not available \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, etc.)", "Reason for 'On Hold' status not specified \u2014 needs human review", "Special pricing details not documented \u2014 amount or discount unknown", "No matching emails found to supplement order context", "County field is blank in top-level FTF payload despite being present in nested data"], "summary": "Individual residential client Peter Thomas has placed a Land Survey Only order for 5201 NE 33rd Ave, Fort Lauderdale, FL (Broward County), which is currently on hold with special pricing applied and requires human review to resolve the hold and gather missing property details."}}</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:07:12.553602+00:00</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -4214,7 +4369,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:48.285527+00:00</t>
+          <t>2026-06-02T15:07:12.567330+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -4225,7 +4225,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4248,16 +4248,37 @@
           <t>350 Island Rd, Palm Beach, FL 33480</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>{"total_amount": 962.0, "services": [{"name": "CAD / Boundary Survey", "description": "Base boundary survey rate per management-negotiated agreement with SKA Architect (OLD_TITLE tier, $450.00 agreed rate).", "amount": 450.0}, {"name": "Lot Size Complexity Upcharge (0.51\u20131.00 ac)", "description": "Property is 0.73 acres, falling in the 0.51\u20131.00 ac tier. Upcharge applied per standard complexity schedule.", "amount": 137.0}, {"name": "Metes &amp; Bounds / Complex Legal Description Upcharge", "description": "Legal description involves two partial lots (Lot 6 less a deed-book exception and Lot 7 less a 7.5 ft strip), creating a non-standard boundary configuration that requires additional research and drafting effort.", "amount": 100.0}, {"name": "Elevation Certificate (EC)", "description": "Property is in FEMA Flood Zone AE (panel 12099C0583G, effective 12/20/2024). Standard EC fee applies. No VE coastal surcharge warranted.", "amount": 275.0}], "pricing_reasoning": "The client's management-negotiated rate of $450.00 is used as the base. A lot-size upcharge of $137.00 applies because the 0.73-acre parcel falls in the 0.51\u20131.00 ac tier. A $100.00 metes-and-bounds upcharge is warranted because the legal description carves two separate exceptions from two lots (Deed Book 606 Page 118 exclusion from Lot 6 and a 7.5 ft strip from Lot 7), adding boundary research and drafting complexity beyond a simple platted lot. The Elevation Certificate is priced at the standard $275.00; Zone AE does not trigger the VE coastal surcharge. No waterfront canal, pool, Monroe County, or vegetation upcharges are applied absent supporting data.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE_DUPLICATE: Order 1000279960 covers the same address (350 Island Rd, Palm Beach County), same coordinates, and same Folio/MLS. The prior order includes 'Land Survey and Elevation' service. Human review required to confirm whether this CAD order is a follow-on deliverable from that survey or a true duplicate before invoicing.", "SPECIAL_PRICING_NOTE: Order notes reference an On Hold status with a quoted price of $250. This price appears well below cost for the scope described. Management should confirm whether the $250 figure was a partial/deposit amount or an error before releasing this invoice.", "CLIENT_ORDER_COUNT: SKA Architect shows 0 prior orders with NexGen despite OLD_TITLE tier designation. Confirm client tier classification and negotiated rate applicability."]}</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202604221615056728, "created_at": "2026-04-22T16:26:31", "customer_email": "jackie@jackiealbarran.com", "customer_id": 202604221615369976, "customer_name": "Jackie Albarran", "customer_type": "b2b", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0583G\nZONE: AE\nELEV: 07 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000282513, "paid": false, "property_address": "350 ISLAND RD", "property_city": "PALM BEACH", "property_county": "Palm Beach County", "property_lat": "26.6949056", "property_lng": "-80.0411004", "property_state": "FL", "property_zip": "33480", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-04-22T21:00:49"}, "success": true, "order_id": "1000282513", "customer_email": "jackie@jackiealbarran.com", "service_type": "CAD", "county": "", "property_address": "350 ISLAND RD", "customer_name": "SKA Architect"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "SKA Architect", "confidence": "MEDIUM"}, "client_email": {"value": "jackie@jackiealbarran.com", "confidence": "HIGH"}, "property_address": {"value": "350 Island Rd, Palm Beach, FL 33480", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type is CAD; no additional services specified. Elevation certificate not requested."}, "special_requirements": {"value": "Special pricing applied. Order is On Hold (status code 11). Flood zone AE, FIRM panel 12099C0583G, base flood elevation 7 ft, effective 12/20/2024.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no matching emails found."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order footer lists 'SKA Architect' but customer record shows 'Jackie Albarran' \u2014 confirm correct billing entity", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, outbuildings, driveways, etc.)", "Reason for On Hold status not documented", "Fieldwork date not scheduled", "No estimate sent \u2014 confirm scope and pricing before proceeding"], "summary": "B2B CAD order for 350 Island Rd, Palm Beach FL (Flood Zone AE) placed by SKA Architect / Jackie Albarran, currently On Hold with special pricing at $250 and missing lot size, legal description, and property feature details."}}</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1780413206143</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>2026-06-02T15:06:49.595917+00:00</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:13:26.877765+00:00</t>
+        </is>
+      </c>
+      <c r="R74" t="n">
+        <v>962</v>
+      </c>
       <c r="T74" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:48.210018+00:00</t>
@@ -4265,7 +4286,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2026-06-02T15:06:49.610311+00:00</t>
+          <t>2026-06-02T15:13:26.895830+00:00</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4298,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4300,16 +4321,37 @@
           <t>326 S H ST &amp; 320 S H ST, Lake Worth Beach, FL 33460</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "AI pricing failed: Unterminated string starting at: line 19 column 5 (char 2827). Manual review required.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "AI pricing error \u2014 needs manual quote", "flags": ["ai_error"]}</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202604211521474865, "created_at": "2026-04-21T15:22:43", "customer_email": "jake.kramer@gmail.com", "customer_id": 202604211521476304, "customer_name": "John Kramer", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0781G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000282430, "paid": true, "property_address": "326 S H ST, S H ST AND 320 S H ST ", "property_city": "LAKE WORTH BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.61154", "property_lng": "-80.058343", "property_state": "FL", "property_zip": "33460", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-04-22T05:57:21"}, "success": true, "order_id": "1000282430", "customer_email": "jake.kramer@gmail.com", "service_type": "CAD file", "county": "", "property_address": "326 S H ST, S H ST AND 320 S H ST ", "customer_name": "John Kramer"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "John Kramer", "confidence": "HIGH"}, "client_email": {"value": "jake.kramer@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "326 S H ST &amp; 320 S H ST, Lake Worth Beach, FL 33460", "confidence": "MEDIUM"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Only service type listed is CAD file; no additional services specified. Special pricing flag is set \u2014 may imply bundled or negotiated scope."}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); appears to involve two adjacent parcels (326 S H ST and 320 S H ST)", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available, no emails, no aerial data \u2014 pool, shed, driveways, and other features are unknown"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name and email may not match \u2014 'John Kramer' vs email 'jake.kramer@gmail.com'; verify correct contact", "Two parcels referenced (326 S H ST and 320 S H ST) \u2014 confirm if both are included in scope", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) unknown", "Reason for On Hold status not specified", "Scope of CAD file not defined \u2014 boundary, topographic, as-built, or other?", "Special pricing basis not documented", "No fieldwork date or delivery date set", "Invoice has not been sent despite order being marked paid \u2014 needs reconciliation"], "summary": "Residential CAD file order for John Kramer covering two adjacent parcels at 326 and 320 S H ST in Lake Worth Beach, FL, currently On Hold with special pricing applied and several key details missing including parcel scope, lot size, legal description, and CAD file type."}}</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1780413230237</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>2026-06-02T15:07:01.951689+00:00</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:13:50.657230+00:00</t>
+        </is>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
       <c r="T75" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:48.247911+00:00</t>
@@ -4317,7 +4359,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2026-06-02T15:07:01.965199+00:00</t>
+          <t>2026-06-02T15:13:50.671467+00:00</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4371,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4352,16 +4394,37 @@
           <t>5201 NE 33RD AVE, FORT LAUDERDALE, FL 33308</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "AI pricing failed: Unterminated string starting at: line 26 column 5 (char 2807). Manual review required.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "AI pricing error \u2014 needs manual quote", "flags": ["ai_error"]}</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202604201539305493, "created_at": "2026-04-20T15:41:12", "customer_email": "braveheart1965@gmail.com", "customer_id": 202604201539306369, "customer_name": "PETER THOMAS", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0378J\nZONE: AE\nELEV: 07 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000282337, "paid": true, "property_address": "5201 NE 33RD AVE", "property_city": "FORT LAUDERDALE", "property_county": "BROWARD COUNTY", "property_lat": "26.1917228", "property_lng": "-80.1038611", "property_state": "FL", "property_zip": "33308", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-04-29T13:11:40"}, "success": true, "order_id": "1000282337", "customer_email": "braveheart1965@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "5201 NE 33RD AVE", "customer_name": "PETER THOMAS"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "PETER THOMAS", "confidence": "HIGH"}, "client_email": {"value": "braveheart1965@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "5201 NE 33RD AVE, FORT LAUDERDALE, FL 33308", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in FTF order data; no elevation certificate requested"}, "special_requirements": {"value": "Special pricing applied; order currently on hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, no emails, and no aerial imagery provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not available \u2014 county appraiser data unavailable", "Legal description not available \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, etc.)", "Reason for 'On Hold' status not specified \u2014 needs human review", "Special pricing details not documented \u2014 amount or discount unknown", "No matching emails found to supplement order context", "County field is blank in top-level FTF payload despite being present in nested data"], "summary": "Individual residential client Peter Thomas has placed a Land Survey Only order for 5201 NE 33rd Ave, Fort Lauderdale, FL (Broward County), which is currently on hold with special pricing applied and requires human review to resolve the hold and gather missing property details."}}</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1780413252157</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>2026-06-02T15:07:12.553602+00:00</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:14:12.558691+00:00</t>
+        </is>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
       <c r="T76" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:48.285527+00:00</t>
@@ -4369,7 +4432,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2026-06-02T15:07:12.567330+00:00</t>
+          <t>2026-06-02T15:14:12.575879+00:00</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4444,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>details_missing</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4399,6 +4462,11 @@
           <t>901 TROPIC DR</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:12:31.231510+00:00</t>
+        </is>
+      </c>
       <c r="T77" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:48.322563+00:00</t>
@@ -4406,7 +4474,7 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:48.322563+00:00</t>
+          <t>2026-06-02T15:12:31.245541+00:00</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4486,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4438,8 +4506,39 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>4539 PINE TREE DR</t>
-        </is>
+          <t>4539 Pine Tree Dr, Miami Beach, FL 33140</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>{"total_amount": 387.0, "services": [{"name": "CAD File \u2013 Base Survey Rate", "description": "Management-negotiated flat rate for Ayal Horovits (individual client, 0 prior orders). CAD file deliverable for boundary survey at 4539 Pine Tree Dr, Miami Beach, Miami-Dade County.", "amount": 250.0}, {"name": "Lot Size Complexity Upcharge (0.51\u20131.00 ac)", "description": "Lot is 0.74 acres, falling in the 0.51\u20131.00 ac complexity tier. Larger lot requires additional fieldwork time and CAD drafting effort.", "amount": 137.0}], "pricing_reasoning": "The service is a CAD file deliverable (boundary survey output) for an individual client with a management-negotiated base rate of $250.00. The lot is 0.74 acres, which falls in the 0.51\u20131.00 ac complexity tier warranting a $137.00 upcharge. No Elevation Certificate was ordered, so no EC line item applies. No waterfront canal, pool, metes-and-bounds, heavy vegetation, or Monroe County factors are indicated by the legal description or county data, so no additional upcharges are applied. The FEMA Zone AE designation does not add cost without an EC. Total comes to $387.00.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000144122 \u2014 same address (4539 Pine Tree Dr), same Folio 0232230020300, service: Land Survey Only \u2014 human review recommended.", "DUPLICATE_WARNING: Order 1000277117 \u2014 same address (4539 Pine Tree Dr), same Folio 0232230020300, service: Land Survey and Elevation \u2014 human review recommended.", "DUPLICATE_WARNING: Order 1000283593 \u2014 same address (4539 Pine Tree Dr), same Folio 0232230020300, service: Land Survey Only \u2014 human review recommended.", "ON_HOLD: Order notes indicate this order is currently On Hold with special pricing applied and fieldwork not yet scheduled. Confirm special pricing terms with management before finalizing invoice.", "MISSING_DETAILS: Order notes reference several missing property details \u2014 verify aerial/site data before fieldwork to confirm no additional complexity upcharges (e.g., pool, waterfront canal, heavy vegetation) are warranted.", "CONFIDENCE_NOTE: Medium confidence due to on-hold status, multiple duplicate orders at same address, and unresolved missing property details flagged in order notes."]}</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202604171857365747, "created_at": "2026-04-17T18:57:36", "customer_email": "scott@lipner.com", "customer_id": 202604171857366065, "customer_name": "Ayal Horovits", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0328L\nZONE: AE\nELEV: 07 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000282280, "paid": true, "property_address": "4539 PINE TREE DR", "property_city": "MIAMI BEACH", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.8196356", "property_lng": "-80.1246412", "property_state": "FLORIDA", "property_zip": "33140", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-04-21T22:01:59"}, "success": true, "order_id": "1000282280", "customer_email": "ahorovits@helmequities.com", "service_type": "CAD file", "county": "", "property_address": "4539 PINE TREE DR", "customer_name": "Ayal Horovits"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Ayal Horovits", "confidence": "HIGH"}, "client_email": {"value": "ahorovits@helmequities.com", "confidence": "MEDIUM"}, "property_address": {"value": "4539 Pine Tree Dr, Miami Beach, FL 33140", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated in the data."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11). Flood zone data present: 12086C0328L, Zone AE, Elev 07 FT, Eff 09/11/2009.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided."}, "client_tier": {"value": "b2b", "confidence": "MEDIUM"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client email discrepancy: order data lists scott@lipner.com but outer payload lists ahorovits@helmequities.com \u2014 correct contact email needs human verification", "Customer type listed as 'individual' but email domain suggests a business (helmequities.com) \u2014 client tier needs confirmation", "Lot size is missing \u2014 required for scoping CAD file work", "Legal description is missing \u2014 county appraiser lookup unavailable", "Structure square footage is missing", "Property features (pool, dock, structures, etc.) are unknown \u2014 no appraiser or aerial data available", "Reason for On Hold status is not documented \u2014 human follow-up needed", "Urgency / deadline not specified", "Fieldwork date not yet scheduled", "Elevation certificate not requested but flood zone AE is noted \u2014 confirm if BFE or elevation cert is needed", "Special pricing details not documented \u2014 pricing rationale should be recorded"], "summary": "CAD file order for Ayal Horovits at 4539 Pine Tree Dr, Miami Beach (Miami-Dade County, Flood Zone AE) is paid but currently On Hold with special pricing applied, pending fieldwork scheduling and several missing property details."}}</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1780413252157</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:12:48.492781+00:00</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:14:31.630873+00:00</t>
+        </is>
+      </c>
+      <c r="R78" t="n">
+        <v>387</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -4448,7 +4547,7 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:48.361010+00:00</t>
+          <t>2026-06-02T15:14:31.647143+00:00</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4559,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4480,7 +4579,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2717 SE 14TH ST</t>
+          <t>2717 SE 14TH ST, POMPANO BEACH, FL 33062</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202412091849570674, "created_at": "2026-04-16T19:27:16", "customer_email": "manny@rackelectric.com", "customer_id": 202604091955480655, "customer_name": "Manny  Lopez", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0378J\nZONE: AE\nELEV: 07 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000282200, "paid": false, "property_address": "2717 SE 14TH ST", "property_city": "POMPANO BEACH", "property_county": "BROWARD COUNTY", "property_lat": "26.212896", "property_lng": "-80.0998106", "property_state": "FL", "property_zip": "33062", "service_type": "Land Survey and Elevation", "special_pricing": true, "status": "Quote", "status_code": 12, "updated_at": "2026-04-17T16:00:19"}, "success": true, "order_id": "1000282200", "customer_email": "manny@rackelectric.com", "service_type": "Land Survey and Elevation", "county": "", "property_address": "2717 SE 14TH ST", "customer_name": "Rack Electric LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Rack Electric LLC", "confidence": "MEDIUM"}, "client_email": {"value": "manny@rackelectric.com", "confidence": "HIGH"}, "property_address": {"value": "2717 SE 14TH ST, POMPANO BEACH, FL 33062", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Boundary Survey", "Elevation Certificate"], "confidence": "MEDIUM", "notes": "Service type listed as 'Land Survey and Elevation' \u2014 interpreted as Boundary Survey plus Elevation Certificate; elevation_cert flag is false but service type explicitly includes elevation, likely a data entry inconsistency requiring human review"}, "special_requirements": {"value": "Special pricing applies; property is in Flood Zone AE (FIRM panel 12011C0378J, effective 07/31/2024, base flood elevation 7 ft)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name discrepancy: order lists 'Manny Lopez' as customer_name but outer payload says 'Rack Electric LLC' \u2014 confirm correct billing name", "elevation_cert flag is false but service type includes 'Elevation' \u2014 clarify whether Elevation Certificate is included in scope", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, fences, sheds, driveways, etc.)", "No fieldwork date scheduled", "Invoice has not been generated and order is still in Quote status \u2014 pricing approval needed", "Special pricing flag is true \u2014 confirm approved pricing amount"], "summary": "B2B order for Rack Electric LLC requesting a Land Survey and Elevation Certificate at 2717 SE 14TH ST, Pompano Beach, FL (Broward County, Flood Zone AE), currently in Quote status with special pricing applied and key property details missing."}}</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:13:04.489783+00:00</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -4490,7 +4599,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>2026-06-02T14:27:48.451145+00:00</t>
+          <t>2026-06-02T15:13:04.505877+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -3400,6 +3400,11 @@
           <t>2026-06-02T15:01:07.528334+00:00</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>["1780412453502", "1780412432203"]</t>
+        </is>
+      </c>
       <c r="R62" t="n">
         <v>1000</v>
       </c>
@@ -3410,7 +3415,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2026-06-02T15:01:07.543464+00:00</t>
+          <t>2026-06-02T15:21:29.808845+00:00</t>
         </is>
       </c>
     </row>
@@ -4203,6 +4208,11 @@
           <t>2026-06-02T15:08:34.935507+00:00</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>["1780412903005"]</t>
+        </is>
+      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -4213,7 +4223,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2026-06-02T15:08:34.950291+00:00</t>
+          <t>2026-06-02T15:21:31.488079+00:00</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4569,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4582,16 +4592,37 @@
           <t>2717 SE 14TH ST, POMPANO BEACH, FL 33062</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>{"total_amount": 725.0, "services": [{"name": "Land Survey (Boundary)", "description": "Boundary survey at 2717 SE 14TH ST, Pompano Beach, Broward County. Negotiated rate for Rack Electric LLC (OLD_TITLE tier) applied per management agreement. Lot is 0.14 acres \u2014 no lot-size upcharge warranted. No pool, waterfront, metes-and-bounds, heavy vegetation, or Monroe County complexity factors identified from available data.", "amount": 450.0}, {"name": "Elevation Certificate", "description": "FEMA Elevation Certificate for FEMA Map Panel 12011C0378J, Zone AE, BFE 7 ft, effective 07/31/2024. Standard EC rate applies \u2014 Zone AE, not VE, so no coastal $50 surcharge.", "amount": 275.0}], "pricing_reasoning": "Service is a combined Land Survey and Elevation Certificate. The company's management-agreed negotiated rate of $450.00 is used as the base survey price for Rack Electric LLC. The EC is priced at the fixed $275.00 rate; no VE surcharge applies as the zone is AE. The 0.14-acre residential lot in Broward County presents no identifiable complexity upcharges (no Monroe County, no pool, no waterfront canal, no metes-and-bounds description, no heavy vegetation, and lot size is well below the 0.31-acre upcharge threshold), yielding a clean total of $725.00.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Three prior orders exist for this exact property and folio (494306130710) \u2014 Order 1000062185 (Land Survey and Elevation), Order 1000236143 (Land Survey and Elevation), and Order 1000248190 (Land Survey Only). Human review is strongly recommended before fulfillment to determine whether prior surveys can be re-certified or whether a new field visit is truly required.", "LEGAL_DESCRIPTION_MISSING: No legal description was provided in the order. This should be sourced from the county property appraiser or prior survey before fieldwork is scheduled.", "ORDER_COUNT_ZERO: Rack Electric LLC shows 0 prior orders despite being classified OLD_TITLE tier with a negotiated rate. Confirm client relationship and rate agreement with management before finalizing invoice."]}</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202412091849570674, "created_at": "2026-04-16T19:27:16", "customer_email": "manny@rackelectric.com", "customer_id": 202604091955480655, "customer_name": "Manny  Lopez", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0378J\nZONE: AE\nELEV: 07 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000282200, "paid": false, "property_address": "2717 SE 14TH ST", "property_city": "POMPANO BEACH", "property_county": "BROWARD COUNTY", "property_lat": "26.212896", "property_lng": "-80.0998106", "property_state": "FL", "property_zip": "33062", "service_type": "Land Survey and Elevation", "special_pricing": true, "status": "Quote", "status_code": 12, "updated_at": "2026-04-17T16:00:19"}, "success": true, "order_id": "1000282200", "customer_email": "manny@rackelectric.com", "service_type": "Land Survey and Elevation", "county": "", "property_address": "2717 SE 14TH ST", "customer_name": "Rack Electric LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Rack Electric LLC", "confidence": "MEDIUM"}, "client_email": {"value": "manny@rackelectric.com", "confidence": "HIGH"}, "property_address": {"value": "2717 SE 14TH ST, POMPANO BEACH, FL 33062", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Boundary Survey", "Elevation Certificate"], "confidence": "MEDIUM", "notes": "Service type listed as 'Land Survey and Elevation' \u2014 interpreted as Boundary Survey plus Elevation Certificate; elevation_cert flag is false but service type explicitly includes elevation, likely a data entry inconsistency requiring human review"}, "special_requirements": {"value": "Special pricing applies; property is in Flood Zone AE (FIRM panel 12011C0378J, effective 07/31/2024, base flood elevation 7 ft)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name discrepancy: order lists 'Manny Lopez' as customer_name but outer payload says 'Rack Electric LLC' \u2014 confirm correct billing name", "elevation_cert flag is false but service type includes 'Elevation' \u2014 clarify whether Elevation Certificate is included in scope", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, fences, sheds, driveways, etc.)", "No fieldwork date scheduled", "Invoice has not been generated and order is still in Quote status \u2014 pricing approval needed", "Special pricing flag is true \u2014 confirm approved pricing amount"], "summary": "B2B order for Rack Electric LLC requesting a Land Survey and Elevation Certificate at 2717 SE 14TH ST, Pompano Beach, FL (Broward County, Flood Zone AE), currently in Quote status with special pricing applied and key property details missing."}}</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1780413513520</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>2026-06-02T15:13:04.489783+00:00</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-06-02T15:21:29.413937+00:00</t>
+        </is>
+      </c>
+      <c r="R79" t="n">
+        <v>725</v>
+      </c>
       <c r="T79" t="inlineStr">
         <is>
           <t>2026-06-02T14:27:48.451145+00:00</t>
@@ -4599,7 +4630,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>2026-06-02T15:13:04.505877+00:00</t>
+          <t>2026-06-02T15:21:29.429432+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U79"/>
+  <dimension ref="A1:U179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4631,6 +4631,4366 @@
       <c r="U79" t="inlineStr">
         <is>
           <t>2026-06-02T15:21:29.429432+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1000282193</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>invoice_draft_posted</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>tradan4@comcast.net</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Jupiter Key HOA</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>101 Jupiter Key Rd, Jupiter, FL 33477</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "Condo/unit order \u2014 unit number 'Entire complex on behalf of HOA' detected in ng_unit_number", "confidence": "N/A", "escalate_flag": true, "escalate_reason": "Condo/unit order \u2014 unit number 'Entire complex on behalf of HOA' detected in ng_unit_number", "flags": ["condo_rejected"]}</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202604161421549877, "created_at": "2026-04-16T18:44:59", "customer_email": "tradan4@comcast.net", "customer_id": 202604161423104594, "customer_name": "Tracey Head", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0187G\nZONE:X\nZONE:VE\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000282193, "paid": false, "property_address": "101 JUPITER KEY RD", "property_city": "JUPITER", "property_county": "PALM BEACH COUNTY", "property_lat": "26.9152661", "property_lng": "-80.0647092", "property_state": "FL", "property_zip": "33477", "service_type": "Land Survey Only", "special_pricing": true, "status": "Quote", "status_code": 12, "updated_at": "2026-04-17T13:44:45"}, "success": true, "order_id": "1000282193", "customer_email": "tradan4@comcast.net", "service_type": "Land Survey Only", "county": "", "property_address": "101 JUPITER KEY RD", "customer_name": "Jupiter Key HOA"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Jupiter Key HOA", "confidence": "MEDIUM"}, "client_email": {"value": "tradan4@comcast.net", "confidence": "HIGH"}, "property_address": {"value": "101 Jupiter Key Rd, Jupiter, FL 33477", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; elevation certificate flagged false"}, "special_requirements": {"value": "Special pricing flagged; flood zone data present: 12099C0187G, Zone X and Zone VE, effective 12/20/2024", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: FTF order lists 'Tracey Head' as customer_name but outer payload lists 'Jupiter Key HOA' \u2014 confirm true client/billing name", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, etc.)", "No fieldwork or delivery dates scheduled", "Invoice amount not yet set (due_amount = 0)", "Scope of land survey not clarified (boundary, topographic, as-built, etc.)", "Special pricing details not specified \u2014 requires internal review"], "summary": "B2B land survey order for Jupiter Key HOA at 101 Jupiter Key Rd, Jupiter FL 33477 (Palm Beach County), currently in Quote status with special pricing flagged and flood zone dual-designation (X and VE); key property details and survey scope still need confirmation."}}</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1780412899167</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:30.643745+00:00</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:09:18.539928+00:00</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>["1780413017000"]</t>
+        </is>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.112765+00:00</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:10:20.340051+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1000282153</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>invoice_draft_posted</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>info@homeconstructionus.com</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Home Construction US, LLC</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>489 Grape Rd NW, Lake Placid, FL 33852</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>{"total_amount": 475.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for residential property at 489 Grape Rd NW, Lake Placid, FL 33852, Highlands County. Lot size 0.22 acres. FEMA Zone X (minimal flood hazard, no EC required). Certified to ESTELA CORREA.", "amount": 475.0}], "pricing_reasoning": "Client is classified as INDIVIDUAL (Home Construction US, LLC, first-time client, no negotiated rate), so the default individual base rate of $475.00 applies. The property is 0.22 acres, which falls within the standard 0.00\u20130.30 ac tier and does not trigger any lot-size upcharge. FEMA Zone X carries no flood hazard complexity and no Elevation Certificate is requested or required. No indicators of metes-and-bounds description, waterfront, pool, heavy vegetation, or Monroe County mobilization were identified, so no complexity upcharges are warranted.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["Legal description field is blank in the order \u2014 confirm with client or county records prior to fieldwork scheduling to ensure no hidden complexity (e.g., metes-and-bounds) that could affect pricing.", "No pricing history available for this client or comparable Highlands County orders to cross-validate against."]}</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202604131856180417, "created_at": "2026-04-16T14:28:32", "customer_email": "info@homeconstructionus.com", "customer_id": 202604131856180521, "customer_name": "Home Construction US,   LLC", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12055C0368C\nZONE:X\nEFF: 11/18/2015", "invoiced": false, "order_id": 1000282153, "paid": false, "property_address": "489 GRAPE RD NW", "property_city": "LAKE PLACID", "property_county": "HIGHLANDS COUNTY", "property_lat": "27.2762726", "property_lng": "-81.40920539999999", "property_state": "FLORIDA", "property_zip": "33852", "service_type": "Land Survey Only", "special_pricing": false, "status": "Quote", "status_code": 12, "updated_at": "2026-04-16T15:03:53"}, "success": true, "order_id": "1000282153", "customer_email": "info@homeconstructionus.com", "service_type": "Land Survey Only", "county": "", "property_address": "489 GRAPE RD NW", "customer_name": "Home Construction US, LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Home Construction US, LLC", "confidence": "HIGH"}, "client_email": {"value": "info@homeconstructionus.com", "confidence": "HIGH"}, "property_address": {"value": "489 Grape Rd NW, Lake Placid, FL 33852", "confidence": "HIGH"}, "property_county": {"value": "Highlands County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data; no additional services indicated"}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, fencing, structures) unknown", "Special requirements or access notes not provided", "No fieldwork or delivery dates scheduled", "Order is still in Quote status \u2014 no pricing confirmed", "Customer data record is empty \u2014 no phone, billing address, or contact details on file"], "summary": "B2B client Home Construction US, LLC is requesting a Land Survey Only for a residential property at 489 Grape Rd NW, Lake Placid, FL 33852 (Highlands County, Flood Zone X); order is currently in Quote status with no fieldwork scheduled and minimal property detail available."}}</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1780416572834</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:39.791758+00:00</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:09:33.176611+00:00</t>
+        </is>
+      </c>
+      <c r="R81" t="n">
+        <v>475</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.158521+00:00</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:09:33.203123+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1000282132</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>invoice_draft_posted</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Boundary Survey</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>info@browardcountyfence.com</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Broward County Fence</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>12075 NW 11TH ST, PEMBROKE PINES, FL 33334</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "Condo/unit order \u2014 unit number 'Bldg. 11 to 19' detected in ng_unit_number", "confidence": "N/A", "escalate_flag": true, "escalate_reason": "Condo/unit order \u2014 unit number 'Bldg. 11 to 19' detected in ng_unit_number", "flags": ["condo_rejected"]}</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202511031827249995, "created_at": "2026-04-15T20:14:56", "customer_email": "info@browardcountyfence.com", "customer_id": 202511031827499878, "customer_name": "Brian Anderson", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": null, "invoiced": false, "order_id": 1000282132, "paid": false, "property_address": "12075 NW 11TH ST", "property_city": "PEMBROKE PINES", "property_county": "Broward County", "property_lat": "26.0148116", "property_lng": "-80.30637100000001", "property_state": "FL", "property_zip": "33334", "service_type": "Boundary Survey", "special_pricing": true, "status": "Quote", "status_code": 12, "updated_at": "2026-04-15T20:21:50"}, "success": true, "order_id": "1000282132", "customer_email": "info@browardcountyfence.com", "service_type": "Boundary Survey", "county": "", "property_address": "12075 NW 11TH ST", "customer_name": "Broward County Fence"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Broward County Fence", "confidence": "MEDIUM"}, "client_email": {"value": "info@browardcountyfence.com", "confidence": "HIGH"}, "property_address": {"value": "12075 NW 11TH ST, PEMBROKE PINES, FL 33334", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["Boundary Survey"], "confidence": "HIGH", "notes": "Single service explicitly stated in order data"}, "special_requirements": {"value": "Special pricing flagged on this order", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order contact is 'Brian Anderson' but company name is 'Broward County Fence' \u2014 confirm billing name", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, enclosures, etc.)", "Special pricing details not specified \u2014 amount or discount not defined", "No fieldwork date scheduled", "Order has not been invoiced or paid \u2014 quote stage only", "Zip code 33334 does not correspond to Pembroke Pines (typically 33024\u201333029) \u2014 verify address accuracy"], "summary": "B2B boundary survey quote for Broward County Fence at 12075 NW 11TH ST, Pembroke Pines, FL, flagged for special pricing and currently in quote status with no fieldwork or invoice generated."}}</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1780416572834</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:49.951825+00:00</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:09:38.680097+00:00</t>
+        </is>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.202213+00:00</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:09:38.705670+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1000281984</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>invoice_draft_posted</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>chris@fcromas.com</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Romas Construction</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>526 94TH AVE N, Naples, FL 34108</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>{"total_amount": 250.0, "services": [{"name": "CAD Drafting / Survey (Special Pricing)", "description": "B2B CAD order for Romas Construction at 526 94th Ave N, Naples FL (Collier County). Management-applied special pricing of $250.00 is in effect per order notes \u2014 overrides standard negotiated rate of $450.00. No EC, TOPO, or additional services requested. No lot-size upcharge applicable (0.15 ac &lt; 0.31 ac threshold). Pool certification noted (Sunshine Pools) but no pool upcharge applied as CAD-only drafting service, not a new boundary survey with field complexity. FEMA Zone AE at 9 ft \u2014 no VE surcharge.", "amount": 250.0}], "pricing_reasoning": "Order notes explicitly state '$250 due' with 'special pricing applied,' which management has approved for this B2B CAD order for Romas Construction. The negotiated base rate of $450 is superseded by this management-sanctioned special price. The lot is small (0.15 ac), non-Monroe, non-VE, and CAD-only \u2014 no complexity upcharges are warranted on top of a management-set figure, and no EC or TOPO service was requested.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "Three concerns require management awareness before finalizing: (1) Special pricing of $250 was manually applied per order notes \u2014 confirm management authorization is on file and reflected in the system. (2) Two probable duplicate orders exist for the same property and folio (Order 1000055975 \u2014 Land Survey + EC; Order 1000281447 \u2014 Land Survey Only) \u2014 confirm whether this CAD order is a standalone deliverable or a downstream product of one of those prior surveys, to avoid double-mobilization or billing conflicts. (3) Client tier is flagged OLD_TITLE with 0 prior orders \u2014 verify client relationship and that the $250 special rate is intentional for this account.", "flags": ["DUPLICATE_POSSIBLE: Order 1000055975 \u2014 same address (526 94th Ave N), same folio (62837520005), same county (Collier) \u2014 service was Land Survey and Elevation. Human review required.", "DUPLICATE_POSSIBLE: Order 1000281447 \u2014 same address (526 94th Ave N), same folio (62837520005), same county (Collier) \u2014 service was Land Survey Only. Human review required.", "SPECIAL_PRICING_OVERRIDE: Order notes indicate management applied $250 special price, overriding negotiated rate of $450. Confirm authorization is documented.", "CLIENT_TIER_MISMATCH: Client classified as OLD_TITLE but shows 0 prior orders with NexGen \u2014 verify account history and tier assignment.", "CERTIFICATIONS_NOTED: Romas Construction and Sunshine Pools listed as certification recipients \u2014 ensure both are included on final deliverable; pool-related certification may imply a site visit has occurred or is needed under a prior order."]}</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202604031422264209, "created_at": "2026-04-14T12:45:56", "customer_email": "chris@fcromas.com", "customer_id": 202604031422581100, "customer_name": "Chris Romas", "customer_type": "b2b", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12021C0189J\nZONE: AE\nELEV: 09 FT\nEFF: 02/08/2024", "invoiced": false, "order_id": 1000281984, "paid": false, "property_address": "526 94TH AVE N", "property_city": "NAPLES", "property_county": "Collier County", "property_lat": "26.2568257", "property_lng": "-81.8160862", "property_state": "FL", "property_zip": "34108", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-04-15T17:16:53"}, "success": true, "order_id": "1000281984", "customer_email": "chris@fcromas.com", "service_type": "CAD", "county": "", "property_address": "526 94TH AVE N", "customer_name": "Romas Construction"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Romas Construction", "confidence": "MEDIUM"}, "client_email": {"value": "chris@fcromas.com", "confidence": "HIGH"}, "property_address": {"value": "526 94TH AVE N, Naples, FL 34108", "confidence": "HIGH"}, "property_county": {"value": "Collier County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type is CAD per order data; no additional services specified"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status code 11); flood zone AE at 09 FT elevation, panel 12021C0189J effective 02/08/2024", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available; no emails or attachments to reference; pool, shed, driveways, and other features unknown"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order root says 'Romas Construction' but customer record says 'Chris Romas' \u2014 confirm correct billing name", "Lot size not provided", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, driveways, etc.) unknown \u2014 no appraiser data or aerial available", "Reason for On Hold status not documented", "Urgency or deadline not specified", "No fieldwork date scheduled", "No invoice or estimate sent yet \u2014 confirm scope before proceeding"], "summary": "B2B CAD order for Romas Construction at 526 94th Ave N, Naples FL (Collier County), currently on hold with special pricing applied and $250 due, located in FEMA flood zone AE \u2014 missing legal description, lot size, and property features."}}</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1780416579093</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:09:00.531964+00:00</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:10:00.698472+00:00</t>
+        </is>
+      </c>
+      <c r="R83" t="n">
+        <v>250</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.245747+00:00</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:10:00.724392+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1000281327</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>invoice_draft_posted</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>pmjflorida@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Josh Young</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>4001 Helena St NE, St. Petersburg, FL 33703</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>{"total_amount": 250.0, "services": [{"name": "CAD / Land Survey", "description": "Boundary survey CAD deliverable for residential lot at 4001 Helena St NE, St. Petersburg, FL. Lot 18, Block 28, Shore Acres subdivision, Pinellas County. 0.17 acres, standard residential size \u2014 no complexity upcharges warranted.", "amount": 250.0}], "pricing_reasoning": "This is a CAD order for a residential property in Pinellas County under a management-agreed negotiated rate of $250.00 for client PMJ Florida. The lot is 0.17 acres (well under the 0.31-acre threshold for any size upcharge), the legal description is a straightforward platted lot with no metes-and-bounds complexity, and no pool, waterfront canal, heavy vegetation, or Monroe County mobilization upcharges are supported by the available data. The FEMA Zone AE designation triggers an Elevation Certificate consideration only if EC service is requested \u2014 this order is CAD only, so no EC line item is added. Final price is the flat negotiated rate of $250.00.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Three prior orders exist for this exact property and folio (173104815220280180) \u2014 Order 1000253250 (Land Survey and Elevation), Order 1000253251 (Quote), and Order 1000271141 (Land Survey Only). Human review recommended to confirm this CAD order is not redundant or already fulfilled under a prior order.", "ON_HOLD_NOTE: Order notes indicate this order was previously placed On Hold with special pricing applied. Confirm with management that the $250.00 negotiated rate is the intended special pricing before invoicing.", "EC_NOT_INCLUDED: Property is in FEMA Flood Zone AE. No Elevation Certificate has been priced as the service requested is CAD only. If an EC is also needed, add $275.00 as a separate line item."]}</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202509081752273999, "created_at": "2026-04-01T18:20:58", "customer_email": "pmjflorida@hotmail.com", "customer_id": 202509081752274099, "customer_name": "Josh  Young", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12103C0236H\nZONE: AE\nELEV: 09 FT\nEFF: 08/24/2021", "invoiced": false, "order_id": 1000281327, "paid": true, "property_address": "4001 HELENA ST NE", "property_city": "ST. PETERSBURG", "property_county": "Pinellas County", "property_lat": "27.8085127", "property_lng": "-82.60404350000002", "property_state": "FL", "property_zip": "33703", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-04-03T14:26:44"}, "success": true, "order_id": "1000281327", "customer_email": "pmjflorida@hotmail.com", "service_type": "CAD", "county": "", "property_address": "4001 HELENA ST NE", "customer_name": "PMJ Florida"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Josh Young", "confidence": "HIGH"}, "client_email": {"value": "pmjflorida@hotmail.com", "confidence": "HIGH"}, "property_address": {"value": "4001 Helena St NE, St. Petersburg, FL 33703", "confidence": "HIGH"}, "property_county": {"value": "Pinellas County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type is listed as CAD only; no additional services indicated in order data"}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); flood zone AE with base flood elevation 9 ft (FIRM panel 12103C0236H, effective 08/24/2021)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features provided; county appraiser data unavailable and no emails or aerial data present"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Order is On Hold \u2014 reason for hold not specified; needs human review", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, outbuildings, etc.) unknown \u2014 no appraiser data or aerial imagery available", "County field is blank in the FTF order root object despite Pinellas County being in the nested data \u2014 may be a data entry issue", "Client name discrepancy: nested data shows 'Josh Young' but root-level customer_name shows 'PMJ Florida' \u2014 needs clarification", "Scope of CAD deliverable not defined (e.g., boundary, topographic, as-built)", "Special pricing reason not documented"], "summary": "CAD order for a residential property at 4001 Helena St NE, St. Petersburg, FL (Pinellas County) for Josh Young, currently On Hold with special pricing applied and located in FEMA Flood Zone AE."}}</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1780416616511</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:09:12.264222+00:00</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:10:17.264772+00:00</t>
+        </is>
+      </c>
+      <c r="R84" t="n">
+        <v>250</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.288920+00:00</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:10:17.291350+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1000281279</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>brockettengineering@gmail.com</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Corey Brocket</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>123 S PALMWAY</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.334232+00:00</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.334232+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1000281135</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ryantimberg@gmail.com</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Ryan Timberg</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1519 SW 18TH AVE</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.419033+00:00</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.419033+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1000280899</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Boundary Survey</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>waterdamage1@bellsouth.net</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>The Citywide Group</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2449 MIDDLE RIVER DR</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.463576+00:00</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.463576+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1000280663</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>miguel_m@nexgenlogix.com</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Miguel Mercedes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1574 PORTOFINO MEADOWS BLVD</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.508970+00:00</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.508970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1000280515</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>info@breezypermits.com</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>BREEZY PERMITS LLC</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1051 SAN PEDRO AVE</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.554051+00:00</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.554051+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1000280038</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>arspado@spadopools.com</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Nancy Perez</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>5684 SE ORANGE BLOSSOM TRAIL</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.599509+00:00</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.599509+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1000279970</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>vinny@vjdconstruction.com</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>VJD Construction</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>13820 LE HAVRE DR</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.645100+00:00</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.645100+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1000279860</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>rick@tromble.com</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Rick Tromble</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>436 BAYSHORE DR</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.691246+00:00</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.691246+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1000279855</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Acreage, Site Plan</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>veenu_b@nexgenlogix.com</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Nexgen Land Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1547 PROSPERITY FARMS RD</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.736955+00:00</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.736955+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1000279820</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>traci@naturecoastlaw.com</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Hengesbach and Hengesbach, PA</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0 STATE ROAD 54</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.785300+00:00</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.785300+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1000279727</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>rb@cgpre.com</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robert Buchalter </t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>6981 LIONS HEAD LN</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.832382+00:00</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.832382+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1000279688</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>xpertawning@aol.com</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Candace Jones</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>15288 73RD ST N</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.878980+00:00</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.878980+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1000279100</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>matt@asuenterprises.com</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ASU Enterprises</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>11 YACHT CLUB PL</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.926367+00:00</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:13.926367+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1000278966</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Rambuilders01@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Mark Ramirez</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>14000 N MIAMI AVE</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.016992+00:00</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.016992+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1000278960</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>bnschafer1@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Barbara Schafer</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>20335 W. COUNTRY CLUB DR. AVENTURA, FLORIDA. 33180.</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.065276+00:00</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.065276+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1000278940</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>office@smcfl.com</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Seaside Marine Construction</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>770 DOVER ST</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.113381+00:00</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.113381+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1000278938</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>randybeth@randybrealty.com</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Randy B Realty</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>811 N OLIVE AVE</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.161529+00:00</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.161529+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1000278769</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>anson@samiami.net</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Stuart Architecture</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2729 NW 48TH ST</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.210088+00:00</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.210088+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1000278707</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>alkcon@gmail.com</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Amilkr Contreras</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>12395 GRIFFING BLVD</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.258759+00:00</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.258759+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1000278676</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>orders@preferredsettlement.com</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Preferred Settlement Services</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>13800 PINE WOODS LN W</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.307828+00:00</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.307828+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1000278620</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>donald.witmondt@woodmontproperties.com</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Donald Witmondt</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>4562-4588 DAVIS RD</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.358257+00:00</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.358257+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1000278594</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>yuvalmadar@gmail.com</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Yuval Madar</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>524 &amp; 530 SOUTH LAKESIDE DRIVE</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.407352+00:00</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.407352+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1000278523</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>CAD Release</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>jon@Smithmoorearchitects.com</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>MAria Mcardle</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>4417 S FLAGLER DR</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.456769+00:00</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.456769+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1000278419</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>richard@rcareylaw.com</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Carey Law Group PA</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>747 11TH CT SW</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.507129+00:00</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.507129+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1000278416</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>richard@rcareylaw.com</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Carey Law Group PA</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>745 11TH CT SW</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.604547+00:00</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.604547+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1000278415</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>richard@rcareylaw.com</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Carey Law Group PA</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>735 11TH CT SW</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.654732+00:00</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.654732+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1000278414</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>richard@rcareylaw.com</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Carey Law Group PA</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1195 16TH AVE SW</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.705755+00:00</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.705755+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1000278156</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>lauriepicard@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Laurie Picard</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>5327 N BAY RD</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.756326+00:00</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.756326+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1000277959</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>alex@ikstudio.net</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>IK STUDIOS</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>5729 SW 60TH AVE</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.807344+00:00</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.807344+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1000277785</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>mattlowe421@gmail.com</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Matthew Lowe</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>1320 NE 47TH ST</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.859079+00:00</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.859079+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1000277758</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>michaelsanzen@gmail.com</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Michael Sanzen</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>715 SE 2ND AVE</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.910495+00:00</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.910495+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1000277746</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ferusa@me.com</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Fernando Lupica Tondo</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>717 LAYNE BLVD</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.962330+00:00</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:14.962330+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1000277740</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>mkreuzman@strosslaw.com</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Stross Law Firm</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2401 28TH AVE N</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.014241+00:00</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.014241+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1000277674</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>joseph@r3health.co</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Joseph Radich</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>415 44TH ST</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.067169+00:00</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.067169+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1000277591</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>vianeyb14@gmail.com</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Vianeybert  Toussaint</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>1210 HOLMES AVE</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.129809+00:00</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.129809+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1000277194</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>treefolium@icloud.com</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Tree Folium Landscape Co.</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>12035 POLO CLUB RD</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.226892+00:00</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.226892+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1000277088</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>jeremy@atfranco.com</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Franco &amp; Associates</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>12952 MIZNER WAY</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.279946+00:00</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.279946+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1000277069</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Boundary Survey</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>maurecwilliams@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>mark Ebersolm</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>10801 SW FOX BROWN RD</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.333845+00:00</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.333845+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1000277032</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>jgoldstein94@me.com</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Jesse Goldstein</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>10651 SW 67TH CT</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.387727+00:00</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.387727+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1000276801</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>eminmugla09@gmail.com</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>muhammed mugla</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2362 BYRON ST</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.441837+00:00</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.441837+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1000276783</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>gquatela@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>GEORGE QUATELA</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>10369 SILVER LAKE DR</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.497199+00:00</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.497199+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1000276767</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>cpv2757@aol.com</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Claudia Vitulich</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>7964 GRAND BAY DR</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.552119+00:00</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.552119+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1000276703</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>mmarino@ms-constructions.com</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>M+S Construction</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1025 MARIANA AVE</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.607180+00:00</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.607180+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1000276470</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>bprinz@wdooleylaw.com</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>William A. Dooley, P.A.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>15615 FL-62</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.662145+00:00</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.662145+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1000276428</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>DSAINVESTMENTCOMPANY@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>GEOFFREY MORRIS</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>23 S SWINTON AVE</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.718263+00:00</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.718263+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1000276384</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>MSARCHMS@aol.com</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS Architects, Inc. </t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>7411 W CYPRESSHEAD DR</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.818516+00:00</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.818516+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1000276269</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>sboscarelli@firstam.com</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>CDS-Commercial Due Diligence Services</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>7300 SW 87TH AVE</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.874087+00:00</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.874087+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1000276241</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Other Services</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>stephanie@achievetitle.com</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Achieve Title Services</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2925 E 17TH AVE</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.930495+00:00</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.930495+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1000276144</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>nebrosnahan@gmail.com</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nancy Brosnahan </t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>214 S SWINTON AVE</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.986774+00:00</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:15.986774+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1000276104</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>sboscarelli@firstam.com</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>CDS-Commercial Due Diligence Services</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>1106 BEVILLE RD</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.043646+00:00</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.043646+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1000276101</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>jjonlaw@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>James Jean-Francois</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>6100 HOLLYWOOD BLVD</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.100907+00:00</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.100907+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>1000276064</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>kaila@emsteam.us</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Kaila</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>118 NEWHAM WAY</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.158014+00:00</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.158014+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1000276043</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>lm1arch@bellsouth.net</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Lee Moldoff</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>235 WORTH CT</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.215726+00:00</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.215726+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1000275962</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>abhi@kanthandesign.com</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>KANTHAN DESIGN CORPORATION</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>1248 NE 8TH AVE</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.273199+00:00</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.273199+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1000275872</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>trojanowski228@gmail.com</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Daniela Trojanowski</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>129 EGRET AVE</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.379011+00:00</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.379011+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1000275849</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ryantimberg@gmail.com</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Ryan Timberg</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>1519 SW 18TH AVE</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.437025+00:00</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.437025+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1000275758</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>santiagoandjade@gmail.com</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>4425 HICKORY DR</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.496741+00:00</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.496741+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1000275742</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>AC@LawrenceLeeConstruction.com</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Lawrence Lee Construction Services, Inc.</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>13179 S INDIAN RIVER DR</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.555277+00:00</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.555277+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1000275732</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>lorelib@gcihomesinc.com</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Loreli Brobst</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>525 36TH AVE NE</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.614876+00:00</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.614876+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1000275730</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>allan@lrgconstruction.com</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Allan Lougheed</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>704 E TANGERINE CT</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.673964+00:00</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.673964+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1000275722</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Angeltgarcia28@gmail.com</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Angel Garcia</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>1773 GALLOP DR</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.733196+00:00</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.733196+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1000275670</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>krsdra50@gmail.com</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Kristen Dragon</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>50044 BERMONT RD</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.792703+00:00</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.792703+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1000275662</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>mchardyconstruction.fl@gmail.com</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>McHardy Construction</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>7202 NW 68TH ST</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.852901+00:00</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.852901+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1000275516</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>jbeal@atlanticcoastal.com</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Atlantic Coastal Land Title Company</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>8850 US-1</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.962298+00:00</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:16.962298+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1000275511</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>aileensellsnaples@gmail.com</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Aileen Cuadra-Roque</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2992 20TH AVE NE</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.023586+00:00</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.023586+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1000275245</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>daymon@eastcoastmetals.net</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Daymon Hallmon</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>1131 S N ST</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.084094+00:00</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.084094+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1000275171</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>cguglielmo16@icloud.com</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Colleen   Guglielmo</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>322 SE 3RD AVE</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.145185+00:00</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.145185+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1000275133</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>bpbpoolbuilder@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Broward Palm Beach Pool Builder</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>7409 BONDSBERRY CT</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.209602+00:00</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.209602+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1000275111</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>mdbolanos@gmail.com</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Michael Bolanos</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>3010 NE 43RD ST</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.275418+00:00</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.275418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1000274741</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LisaD@cwcrecovery.com</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>JMJC REAL PROPERTY MANAGEMENT, LLC.</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>4177 S CONGRESS AVE</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.337024+00:00</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.337024+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1000274628</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>yaniescobar@realtyblu.com</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Yani Escobar</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>8608 N 13TH ST</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.400731+00:00</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.400731+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1000274600</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>christine.frechette@outlook.com</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Christine Frechette</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>15645 BILLY GOAT LN</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.462755+00:00</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.462755+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1000274593</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>robertjserr@gmail.com</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Robert Serr</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>961 S ATLANTIC DR</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.571374+00:00</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.571374+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1000274571</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Boundary Survey</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>FREDERICK_S@NEXGENLOGIX.COM</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Nexgen Land Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2207 SUMMIT BLVD</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.633826+00:00</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.633826+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1000274546</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Angie769495@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Angela N Alanis Rodriguez </t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>845 SE TIERRA CT</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.697033+00:00</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.697033+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1000274472</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>maryvega551@gmail.com</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Mary Romanelli</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>3023 SE CAMINO AVE</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.760217+00:00</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.760217+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1000274358</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>smarion@conroysimberg.com</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Samantha Marion</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>10534 173RD RD N</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.824346+00:00</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.824346+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1000274136</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>karinabodina@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Sally Daw</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>5505 S INDIAN RIVER DR</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.888005+00:00</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.888005+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1000274109</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>blaket@unlimitedps.net</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Unlimited Permit Services, INC</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>510 RIVIERA DR</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.952263+00:00</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:17.952263+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>1000274095</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>coventry.chris@gmail.com</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Christopher  Coventry</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2395 CAMPBELL RD</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.064225+00:00</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.064225+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1000274003</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>peter.moss@outlook.com</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Peter Moss</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>3131 NE 21ST AVE</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.128921+00:00</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.128921+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1000273967</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>cquigley@bellsouth.net</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>CARLA  QUIGLEY</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>1198 INDIAN RIVER DR</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.193976+00:00</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.193976+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1000273966</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Quote, CAD file</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BinduRamm@gmail.com</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Bindu Rammohan</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>321 SW 24TH RD</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.259420+00:00</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.259420+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1000273870</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>maryannroberts@rogers.com</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Mary Ann Roberts</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>465 SAVOIE DR</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.326413+00:00</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.326413+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1000273827</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>josephplatten9@gmail.com</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Joseph Platten</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>1607 LAKE DOWNEY DR #25</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.391842+00:00</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.391842+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1000273817</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>miguel.rojas@foundrycommercial.com</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Miguel Rojas</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>1211 FL-436</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.458219+00:00</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.458219+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1000273647</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>benallen2013@gmail.com</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Benjamin Allen</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>922 TURNER RD</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.524797+00:00</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.524797+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1000273608</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Taylor@fivediamondfl.com</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Taylor McCook</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>35135 PINEGATE TRAIL</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.638183+00:00</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.638183+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>1000273465</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>reggiemanning1@gmail.com</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Reggie Manning</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>32 HAMPSHIRE LN</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.705053+00:00</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.705053+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1000273343</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>bacall40@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Johanne Beaumont </t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>152 WOODBRIDGE CIR</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.772653+00:00</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.772653+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1000273161</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>chefmbyrne@gmail.com</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Matthew Byrne</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>624 SELKIRK ST</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.840215+00:00</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.840215+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1000273091</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>juanramos155@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Juan Ramos</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>753 NE 79TH ST</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.907400+00:00</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.907400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1000272874</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>kimprice@msctitle.com</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>MSC Title, Inc. of Englewood</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>12081 DUBARRY AVE</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.975500+00:00</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:18.975500+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1000272801</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Legal Creation hourly, Survey Re-draw</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>galvarez@abpluseng.com</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Gustavo  Alvarez</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>56048 BLUE CREEK RD</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:19.043467+00:00</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:19.043467+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1000272701</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>keith@firstupstructures.com</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>FIRSTUP Structures, Inc.</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>826 S LAKESIDE DR</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:19.112404+00:00</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:08:19.112404+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U179"/>
+  <dimension ref="A1:U279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4771,6 +4771,11 @@
           <t>2026-06-02T16:09:33.176611+00:00</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>["1780416762308"]</t>
+        </is>
+      </c>
       <c r="R81" t="n">
         <v>475</v>
       </c>
@@ -4781,7 +4786,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>2026-06-02T16:09:33.203123+00:00</t>
+          <t>2026-06-02T16:15:55.113048+00:00</t>
         </is>
       </c>
     </row>
@@ -4844,6 +4849,11 @@
           <t>2026-06-02T16:09:38.680097+00:00</t>
         </is>
       </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>["1780416762308"]</t>
+        </is>
+      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -4854,7 +4864,7 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>2026-06-02T16:09:38.705670+00:00</t>
+          <t>2026-06-02T16:15:55.585728+00:00</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5022,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5032,8 +5042,39 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>123 S PALMWAY</t>
-        </is>
+          <t>123 S Palmway</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "This order is flagged as a CAD deliverable with an undefined scope \u2014 it is unclear whether this is a CAD conversion of an existing survey, a CAD drafting-only service, a boundary survey with CAD output, or something else entirely. The order notes explicitly state the CAD deliverable scope is undefined and requires human follow-up. Additionally, the client is listed as an individual (order count 0) but the certification is to an engineering firm (Brockett Engineering), which may indicate a commercial or professional workflow requiring clarified deliverables and possibly different pricing. A possible duplicate order (1000257599) exists for the same address and parcel, covering Land Survey and Elevation, which further complicates pricing without human review to determine whether this CAD order is a standalone new engagement or a downstream deliverable tied to prior work.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "Escalated for three compounding reasons: (1) The CAD service type has no defined scope \u2014 it is unknown whether this is a CAD-only drafting product, a CAD conversion of an existing survey, or a full boundary survey with CAD output, making it impossible to price accurately without client clarification. (2) A likely duplicate order (1000257599) exists for the identical address and parcel (Folio 38434421150390140), covering Land Survey and Elevation \u2014 it must be determined whether this CAD order is subordinate to, separate from, or duplicative of that prior order before any pricing is issued. (3) The certification to Brockett Engineering combined with an individual client tier and zero order history suggests a possible misclassification of client type or an atypical workflow that management should review before committing to the negotiated $450.00 base rate.", "flags": ["DUPLICATE_SUSPECTED: Order 1000257599 references the same property (123 S Palmway, Palm Beach County, Folio 38434421150390140) with service type Land Survey and Elevation \u2014 confirm whether this CAD order is a new engagement or a downstream deliverable before pricing.", "UNDEFINED_SCOPE: CAD deliverable type is not specified. Human follow-up required to determine exact product (CAD conversion, boundary survey with CAD output, drafting only, etc.).", "CLIENT_TIER_MISMATCH: Client is flagged as INDIVIDUAL with 0 prior orders, but certification is directed to Brockett Engineering \u2014 verify client classification and applicable rate tier.", "INCOMPLETE_ADDRESS: Order notes flag incomplete address details and no county originally provided \u2014 confirm property address is complete and correct before proceeding.", "FEMA_ZONE_AE: Property is in FEMA Zone AE (base flood elevation 8 ft, effective 12/20/2024) \u2014 if an Elevation Certificate is ultimately required as part of this order, price at $275.00 (no VE surcharge applies)."]}</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"order_id": "1000281279", "customer_email": "brockettengineering@gmail.com", "service_type": "CAD", "county": "", "property_address": "123 S PALMWAY", "customer_name": "Corey Brocket"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Corey Brocket", "confidence": "HIGH"}, "client_email": {"value": "brockettengineering@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "123 S Palmway", "confidence": "MEDIUM"}, "property_county": {"value": null, "confidence": "LOW"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type listed as CAD; specific CAD deliverable (drafting, as-built, plat, etc.) is not defined"}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available; no features can be determined"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Property county not provided \u2014 required to look up appraiser data and confirm address", "Full property address may be incomplete (no city, state, or ZIP)", "Specific CAD service not defined (e.g., drafting, as-built, boundary plat, topographic)", "Lot size unknown", "Legal description unknown", "Structure square footage unknown", "Property features unknown (no appraiser or aerial data available)", "Special requirements or instructions not provided", "Urgency / turnaround expectation not specified", "Client tier is inferred from email domain ('brockettengineering') but not confirmed"], "summary": "CAD order from likely engineering firm client Corey Brocket for a property at 123 S Palmway, with no county, incomplete address details, and undefined CAD deliverable scope requiring human follow-up."}}</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1780416873362</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:13:02.145406+00:00</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:14:34.264579+00:00</t>
+        </is>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -5042,7 +5083,7 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:13.334232+00:00</t>
+          <t>2026-06-02T16:14:34.302806+00:00</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5095,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5074,8 +5115,39 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1519 SW 18TH AVE</t>
-        </is>
+          <t>1519 SW 18TH AVE, FORT LAUDERDALE, FL 33312</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "CAD / Boundary Survey", "description": "Residential boundary survey with CAD deliverable for Lot 77, Lauderdale Isles No.1, 1519 SW 18th Ave, Fort Lauderdale, Broward County. Lot size 0.16 acres (no lot-size upcharge applicable). No waterfront, pool, metes-and-bounds, or other complexity indicators warranting an upcharge. No Elevation Certificate requested. Base rate per management-agreed negotiated pricing for this client.", "amount": 450.0}], "pricing_reasoning": "Management has established a negotiated base rate of $450.00 for this individual client. The property is a standard residential lot at 0.16 acres in Broward County \u2014 well under the 0.31-acre threshold for a lot-size upcharge. The legal description is a simple platted lot (no metes-and-bounds complexity). FEMA Zone AE triggers no EC line item as none was requested; no VE coastal surcharge applies. No pool, waterfront canal, heavy vegetation, or Monroe County factors are indicated. The service requested is CAD only, so $450.00 flat is the correct and complete invoice total.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_ALERT: Order 1000275360 \u2014 same address (1519 SW 18TH AVE, Broward County), same Folio/MLS (504216290720), service: Land Survey Only \u2014 flagged for human review.", "DUPLICATE_ALERT: Order 1000275849 \u2014 same address (1519 SW 18TH AVE, Broward County), same Folio/MLS (504216290720), service: Land Survey Only \u2014 flagged for human review.", "DUPLICATE_ALERT: Order 1000280641 \u2014 same address (1519 SW 18TH AVE, Broward County), same Folio/MLS (504216290720), service: Land Survey Only \u2014 flagged for human review.", "ON_HOLD_NOTE: Order is currently On Hold per order notes. No fieldwork or delivery date has been scheduled. Confirm with management before releasing."]}</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202512021724214710, "created_at": "2026-03-30T14:03:24", "customer_email": "ryantimberg@gmail.com", "customer_id": 202512021724215839, "customer_name": "Ryan Timberg", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0556J\nZONE: AE\nELEV: 06 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000281135, "paid": true, "property_address": "1519 SW 18TH AVE", "property_city": "FORT LAUDERDALE", "property_county": "BROWARD COUNTY", "property_lat": "26.1008497", "property_lng": "-80.1651368", "property_state": "FL", "property_zip": "33312", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-30T16:01:26"}, "success": true, "order_id": "1000281135", "customer_email": "ryantimberg@gmail.com", "service_type": "CAD", "county": "", "property_address": "1519 SW 18TH AVE", "customer_name": "Ryan Timberg"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Ryan Timberg", "confidence": "HIGH"}, "client_email": {"value": "ryantimberg@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1519 SW 18TH AVE, FORT LAUDERDALE, FL 33312", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type is listed as CAD; no additional services specified. Exact scope of CAD deliverable is unclear without further context."}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11). Flood zone data present: Panel 12011C0556J, Zone AE, Base Elevation 6 FT, Effective 07/31/2024.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments present."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Reason order is On Hold \u2014 needs human review", "Exact CAD scope/deliverable not defined", "Lot size unknown \u2014 no appraiser data available", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, structures) unknown", "No county provided in top-level FTF fields (county field is empty string despite property_county being set in data object)", "No fieldwork date scheduled", "No delivery date set", "Special pricing details not specified \u2014 amount or discount unknown"], "summary": "Residential CAD order for Ryan Timberg at 1519 SW 18TH AVE, Fort Lauderdale FL (Broward County, Flood Zone AE) is currently On Hold with special pricing applied and no fieldwork or delivery date scheduled."}}</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1780416890642</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:13:37.419939+00:00</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:14:51.230038+00:00</t>
+        </is>
+      </c>
+      <c r="R86" t="n">
+        <v>450</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -5084,7 +5156,7 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:13.419033+00:00</t>
+          <t>2026-06-02T16:14:51.266996+00:00</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5168,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5116,8 +5188,39 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2449 MIDDLE RIVER DR</t>
-        </is>
+          <t>2449 Middle River Dr, Fort Lauderdale, FL 33305</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>{"total_amount": 537.0, "services": [{"name": "Boundary Survey", "description": "Boundary survey for LOT 13, BLOCK 10, CORAL RIDGE GALT ADDITION, 2449 Middle River Dr, Fort Lauderdale, Broward County. Negotiated B2B rate for The Citywide Group (OLD_TITLE tier).", "amount": 450.0}, {"name": "Waterfront Canal Complexity Upcharge", "description": "2449 Middle River Dr is a canal-front property on Middle River \u2014 a navigable tidal waterway in Fort Lauderdale. Waterfront/canal frontage increases field complexity (boundary determination along water, riparian line, additional monumentation research).", "amount": 87.0}], "pricing_reasoning": "The negotiated rate of $450.00 applies per management agreement for The Citywide Group (OLD_TITLE). The lot is 0.28 acres, falling under the 0.31-acre threshold so no lot-size upcharge is warranted. However, the property address '2449 Middle River Dr' directly fronts Middle River, a canal/tidal waterway in Fort Lauderdale, which is supported by FEMA Zone AE classification at 7 ft elevation \u2014 confirming waterfront exposure and justifying the $87.00 canal upcharge. No Elevation Certificate was ordered, no pool or metes-and-bounds description is present (platted lot), and this is Broward County so no Monroe remote mobilization applies.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "Order notes explicitly flag this job as ON HOLD with a client name conflict (The Citywide Group vs. possibly another named client) and missing property details requiring human review. These issues must be resolved before the invoice is finalized and delivered. Pricing is ready pending hold resolution.", "flags": ["ORDER ON HOLD \u2014 per order notes, a client name conflict exists and missing property details need to be filled in before this order proceeds. Human review required.", "SPECIAL PRICING FLAGGED \u2014 management has pre-approved $450.00 base rate for The Citywide Group; do not revert to standard rate schedule.", "CERTIFICATIONS: Survey to be certified to MARK SABOTTA \u2014 confirm certification name spelling and any additional certificate recipients with client before delivery.", "ORDER COUNT = 0 \u2014 The Citywide Group has no prior completed orders with NexGen despite being classified OLD_TITLE; verify client relationship and tier classification with account manager.", "FEMA ZONE AE (12011C0386J, eff. 07/31/2024) \u2014 No Elevation Certificate was requested in this order. If lender or title requires an EC, it would be priced at $275.00 (flat, Zone AE \u2014 no VE surcharge applies)."]}</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202502031551593504, "created_at": "2026-03-24T19:43:25", "customer_email": "waterdamage1@bellsouth.net", "customer_id": 202502031552497293, "customer_name": "Peter Calvo", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0386J\nZONE: AE\nELEV: 07 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000280899, "paid": false, "property_address": "2449 MIDDLE RIVER DR", "property_city": "FORT LAUDERDALE", "property_county": "Broward County", "property_lat": "26.157172", "property_lng": "-80.11379869999999", "property_state": "FL", "property_zip": "33305", "service_type": "Boundary Survey", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-27T19:22:50"}, "success": true, "order_id": "1000280899", "customer_email": "waterdamage1@bellsouth.net", "service_type": "Boundary Survey", "county": "", "property_address": "2449 MIDDLE RIVER DR", "customer_name": "The Citywide Group"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "The Citywide Group", "confidence": "MEDIUM"}, "client_email": {"value": "waterdamage1@bellsouth.net", "confidence": "HIGH"}, "property_address": {"value": "2449 Middle River Dr, Fort Lauderdale, FL 33305", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["Boundary Survey"], "confidence": "HIGH", "notes": "Service type explicitly stated as Boundary Survey; no additional services indicated"}, "special_requirements": {"value": "Special pricing flagged; order currently On Hold; flood zone AE with base elevation 7 ft (FIRM panel 12011C0386J, eff. 07/31/2024)", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available; no emails or aerial data to reference \u2014 pool, shed, driveway, and other features unknown"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order data lists 'Peter Calvo' as customer_name but outer payload lists 'The Citywide Group' \u2014 needs human verification", "Lot size unknown \u2014 no property appraiser data available", "Legal description unknown \u2014 no property appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fencing, driveway, etc.) unknown", "Reason for On Hold status not documented", "Special pricing details not specified \u2014 pricing amount or discount unknown", "No fieldwork or delivery dates scheduled", "No matching emails found \u2014 no additional context from client communications"], "summary": "A B2B boundary survey order for 2449 Middle River Dr, Fort Lauderdale (Broward County) placed by The Citywide Group is currently on hold with special pricing flagged, located in FEMA Flood Zone AE, and requires human review to resolve a client name conflict and fill in missing property details."}}</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1780416911931</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:13:48.800203+00:00</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:15:12.501511+00:00</t>
+        </is>
+      </c>
+      <c r="R87" t="n">
+        <v>537</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -5126,7 +5229,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:13.463576+00:00</t>
+          <t>2026-06-02T16:15:12.537007+00:00</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5241,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5158,8 +5261,39 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1574 PORTOFINO MEADOWS BLVD</t>
-        </is>
+          <t>1574 Portofino Meadows Blvd, Orlando, FL 32824</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>{"total_amount": 300.0, "services": [{"name": "Land Survey (Boundary Survey)", "description": "Residential boundary/land survey for 1574 Portofino Meadows Blvd, Orlando, FL (Orange County). Small lot at 0.04 acres. No complexity upcharges applicable \u2014 lot is well under 0.31 ac threshold, FEMA Zone X (no flood plain complexity), no pool/waterfront/vegetation/metes-and-bounds indicators present. Negotiated management-approved base rate applied.", "amount": 300.0}], "pricing_reasoning": "Management pre-approved a negotiated rate of $300.00 for this individual client (Miguel Mercedes, first-time order). The property is 0.04 acres in Orange County \u2014 an extremely small residential lot with no complexity factors warranting upcharges: FEMA Zone X requires no Elevation Certificate, no pool, no waterfront, no Monroe County mobilization, and no metes-and-bounds legal description indicators. Legal description and property feature details are still missing per order notes, but the lot size and zone data are sufficient to confirm no escalation is needed and no upcharges are justified.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000280581 is flagged as a possible duplicate \u2014 same address (1574 Portofino Meadows Blvd, Orange County), same Folio/MLS (29-24-25-7202-01-390), same service type (Land Survey Only). Human review required before invoicing to confirm this is not a double-billing situation.", "MISSING_DATA: Legal description is a placeholder ('LEGAL DESCRIPTION FOR THE PROPERTY INSERTED HERE'). No complexity upcharges were indicated by lot size or zone, but legal description should be verified before survey fieldwork begins to rule out metes-and-bounds complexity (+$100.00 upcharge if applicable).", "MISSING_DATA: Certification fields (purchaser, title company, lender, insurance) are placeholders \u2014 must be completed before invoice is finalized and sent.", "HOLD_STATUS: Order notes indicate this order is currently on hold with special pricing flagged and no invoice yet sent. This pricing output should be reviewed by management before release."]}</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202603191230051598, "created_at": "2026-03-20T12:42:01", "customer_email": "miguel_m@nexgenlogix.com", "customer_id": 202603191230052457, "customer_name": "Miguel Mercedes", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12095C0650G\nZONE: X\nEFF: 06/20/2018", "invoiced": false, "order_id": 1000280663, "paid": false, "property_address": "1574 PORTOFINO MEADOWS BLVD", "property_city": "ORLANDO", "property_county": "ORANGE COUNTY", "property_lat": "28.3677193", "property_lng": "-81.3613787", "property_state": "FL", "property_zip": "32824", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-25T20:25:58"}, "success": true, "order_id": "1000280663", "customer_email": "miguel_m@nexgenlogix.com", "service_type": "Land Survey Only", "county": "", "property_address": "1574 PORTOFINO MEADOWS BLVD", "customer_name": "Miguel Mercedes"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Miguel Mercedes", "confidence": "HIGH"}, "client_email": {"value": "miguel_m@nexgenlogix.com", "confidence": "HIGH"}, "property_address": {"value": "1574 Portofino Meadows Blvd, Orlando, FL 32824", "confidence": "HIGH"}, "property_county": {"value": "Orange County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing flagged on this order", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments to reference"}, "client_tier": {"value": "residential", "confidence": "MEDIUM"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not available", "Structure square footage unknown", "Property features (pool, shed, structures) unknown \u2014 no appraiser or aerial data", "Order is currently On Hold \u2014 reason for hold not specified", "Invoice has not been sent and amount due is $0 \u2014 pricing needs to be confirmed despite special_pricing flag", "Urgency/deadline not stated", "Customer type listed as individual but email domain (nexgenlogix.com) may suggest business affiliation \u2014 client tier should be verified", "No fieldwork or delivery date scheduled"], "summary": "Residential land survey order for Miguel Mercedes at 1574 Portofino Meadows Blvd, Orlando, FL (Orange County) is currently on hold with special pricing flagged, no invoice sent, and missing lot size, legal description, and property feature details."}}</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1780416929997</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:13:58.732856+00:00</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:15:30.806066+00:00</t>
+        </is>
+      </c>
+      <c r="R88" t="n">
+        <v>300</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -5168,7 +5302,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:13.508970+00:00</t>
+          <t>2026-06-02T16:15:30.841623+00:00</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5314,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5195,13 +5329,44 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>BREEZY PERMITS LLC</t>
+          <t>Breezy Permits LLC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1051 SAN PEDRO AVE</t>
-        </is>
+          <t>1051 San Pedro Ave, Coral Gables, FL 33156</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>{"total_amount": 250.0, "services": [{"name": "CAD File", "description": "CAD file deliverable for 1051 San Pedro Ave, Coral Gables, FL 33156 (Miami-Dade County). Lot 12, Block 4, Coral Bay Section B \u2014 0.28 acres, platted lot with straightforward legal description. Breezy Permits LLC negotiated rate applied as directed by management.", "amount": 250.0}], "pricing_reasoning": "This is a B2B CAD file order for an established client (Breezy Permits LLC) with a management-agreed negotiated rate of $250.00, which serves as both the base and final price. The lot is 0.28 acres (within the 0.00\u20130.30 ac tier \u2014 no lot size upcharge), the legal description is a clean platted lot (no metes-and-bounds upcharge), and the property is in Miami-Dade County (no Monroe County mobilization surcharge). No Elevation Certificate was requested, so the AE flood zone designation does not trigger any EC line item. No additional complexity upcharges are supported by the data.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000270122 references the same property (1051 San Pedro Ave, Miami-Dade County, Folio 0351180060670) with service 'Land Survey Only' \u2014 flagged for human review to confirm whether a prior survey exists that this CAD file may be derived from.", "DUPLICATE_WARNING: Order 1000279271 references the same property (1051 San Pedro Ave, Miami-Dade County, Folio 0351180060670) with service 'Land Survey Only' \u2014 flagged for human review. Two prior land survey orders at this address warrant confirmation that field work is not being duplicated and that the CAD file can be fulfilled from existing data.", "FEMA_ZONE_AE: Property lies within FEMA flood zone AE (panel 12086C0469L, effective 09/11/2009, base flood elevation 11 ft). No EC was ordered, but downstream client (permit processor) should be advised if an EC is later needed \u2014 standard EC rate $275.00 would apply.", "ON_HOLD_NOTE: Order notes indicate this order was previously placed On Hold with special pricing applied \u2014 pricing here reflects the $250.00 negotiated rate confirmed by management. Verify hold has been lifted before scheduling."]}</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507151523115361, "created_at": "2026-03-18T14:48:28", "customer_email": "info@breezypermits.com", "customer_id": 202507151523115459, "customer_name": "Naia Gonzalez", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0469L\nZONE: AE\nELEV: 11 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000280515, "paid": true, "property_address": "1051 SAN PEDRO AVE", "property_city": "CORAL GABLES AVE", "property_county": "Miami-Dade County", "property_lat": "25.6517407", "property_lng": "-80.2741068", "property_state": "FL", "property_zip": "33156", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-19T21:14:25"}, "success": true, "order_id": "1000280515", "customer_email": "info@breezypermits.com", "service_type": "CAD file", "county": "", "property_address": "1051 SAN PEDRO AVE", "customer_name": "BREEZY PERMITS LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Breezy Permits LLC", "confidence": "HIGH"}, "client_email": {"value": "info@breezypermits.com", "confidence": "HIGH"}, "property_address": {"value": "1051 San Pedro Ave, Coral Gables, FL 33156", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file' in FTF order data; no additional services indicated."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11). Flood zone data available: FIRM Panel 12086C0469L, Zone AE, Base Flood Elevation 11 ft, effective 09/11/2009.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no aerial imagery, appraiser data, or email attachments provided."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, fences, driveways, additional structures)", "No fieldwork date scheduled", "County Appraiser data unavailable", "No matching emails found for additional context", "Reason for On Hold status not documented", "Scope of CAD file not clarified (boundary, topo, as-built, etc.)"], "summary": "B2B order from Breezy Permits LLC for a CAD file at 1051 San Pedro Ave, Coral Gables, FL 33156 (Miami-Dade County), currently On Hold with special pricing applied and flood zone AE designation noted."}}</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1780416929997</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:14:08.874414+00:00</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:15:51.729010+00:00</t>
+        </is>
+      </c>
+      <c r="R89" t="n">
+        <v>250</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -5210,7 +5375,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:13.554051+00:00</t>
+          <t>2026-06-02T16:15:51.764949+00:00</t>
         </is>
       </c>
     </row>
@@ -8991,6 +9156,4206 @@
       <c r="U179" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:19.112404+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1000272649</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>edong888@gmail.com</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Eric Dong</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>3801 COCO GROVE AVE</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:12.975802+00:00</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:12.975802+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1000272525</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Survey Re-draw</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>FREDERICK_S@NEXGENLOGIX.COM</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Nexgen Land Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>1409 NE 7TH AVE</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.049076+00:00</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.049076+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1000272499</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>tffmgwr4@aol.com</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>MICHAEL  SCHWARTZ</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>3708 PLUMOSA TERRACE</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.119993+00:00</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.119993+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>1000272382</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>561jck@gmail.com</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Just Call Kris, Inc.</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>1250 SOUTHWINDS DR</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.241662+00:00</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.241662+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>1000272305</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Boundary Survey</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>noemailgiven@none.com</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Lee Bennett</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>316 AMANDA LN</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.313936+00:00</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.313936+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1000272106</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Other Services</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>hgm@mccarthysummers.com</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>McCarthy, Summers, Bobko, Wood, Norman, Bass, and Melby, PA</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2133 SIBLEY AVE</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.385617+00:00</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.385617+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1000272053</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>YamiraRuiz216@gmail.com</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Yamira Ruiz</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>3826 10TH AVE N</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.456921+00:00</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.456921+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1000271907</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Land Survey Only, Elevation Certificate</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>NEXGEN-TEST</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>201 BRANCH WOOD LN</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.529411+00:00</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.529411+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1000271845</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ALTA Table A Survey</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>ahaynes@firstam.com</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>CDS-Commercial Due Diligence Services</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>8690 POINT CYPRESS DR</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.600679+00:00</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.600679+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1000271787</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>akstorm8225@gmail.com</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Andy Kobosko</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>1102 N GOLFVIEW RD</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.673158+00:00</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.673158+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1000271752</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>cdu@dulanddesign.com</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>DULAND DESIGN</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>9710 STIRLING RD</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.796985+00:00</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.796985+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1000271665</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>DrewH@cgunlimited.com</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Drew Hemmer</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>154 4TH AVE N</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.869655+00:00</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.869655+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1000271564</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>erick@rackelectric.com</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Rack Electric LLC</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>212/224 COMMERCIAL WAY</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.942686+00:00</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:13.942686+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1000271330</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>artmargfon@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Margarita Fonrodona- Hernandez</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2004 EMBASSY DR</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.015940+00:00</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.015940+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1000271318</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>heatherament@amentconstructioninc.com</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Ament Construction, INC</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>1316 PAR VIEW DR</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.090852+00:00</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.090852+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1000271297</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Elevation Certificate</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>shohreh0615@gmail.com</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>SHOHREH HANSON</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>904 NE 2ND ST</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.164776+00:00</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.164776+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1000271199</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Kenny@highloads.com</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Kenny Mungle</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>7110 LONGBOAT DR E</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.238902+00:00</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.238902+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1000271188</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>mcob1@icloud.com</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Michael Oberhelman</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2025 NE 22ND ST</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.366606+00:00</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.366606+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1000270408</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>wstanley740@gmail.com</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WILLIAM  STANLEY </t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>517 SW AVENUE B PL</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.441723+00:00</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.441723+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1000270324</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>innagranik@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>INNA BARUKHIN</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>1260 99TH ST</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.516765+00:00</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.516765+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1000270309</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>alecpollum@outlook.com</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Alec Pollum</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>3682 SW BIMINI CIR N</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.592654+00:00</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.592654+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1000270101</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Sunlandcustomhomes@gmail.com</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Matt Smoral</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2460 TRADE WINDS DR</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.668603+00:00</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.668603+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1000270001</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>creativecookmayport@gmail.com</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Taylor Pickett</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2198 MAYPORT RD</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.744168+00:00</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.744168+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1000269964</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>pfsgators@aol.com</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>JEFFREY AND LISA DICKERSON</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>1413 NW LANCEWOOD TER</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.874199+00:00</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.874199+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1000269922</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>gould@williamgould.com</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Intercoastal Marine Construction</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>329 REGATTA DR</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.950544+00:00</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:14.950544+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1000269865</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Land Survey and Elevation</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>mrrafikibrahim@gmail.com</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Rafik Ibrahim</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>1251 SW 15TH AVE</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.027746+00:00</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.027746+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1000269850</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>info@smartbuild-florida.com</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Smart Building Construction LLC</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>1883 MICHIGAN AVE NE</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.109643+00:00</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.109643+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1000269843</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>richard.thepermittech@gmail.com</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>The Permit Tech Inc.</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2250 LORRAINE RD</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.188125+00:00</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.188125+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>1000269487</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>daniel@sofisadevelopment.com</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Underwood Foundation Florida LLC</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>12510 SW 72ND TER</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.266102+00:00</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.266102+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1000269367</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>jacqueline@scottelkpa.com</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Scott A. Elk, P.A.</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>260 N WOODS RD</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.344389+00:00</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.344389+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>1000269301</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>buywithberk@gmail.com</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Jason Berk</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>611 SW 15TH ST</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.473188+00:00</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.473188+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1000268948</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>clay@crewbuilding.cl</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Lauren Thomas</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>403 W RIVERSIDE DR</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.552510+00:00</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.552510+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>1000268731</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>jsmith@1754properties.com</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Joe Smith</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>1825 MAIN ST</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.631730+00:00</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.631730+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>1000268713</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>jennmorgan@tiron-electric.com</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Rosina Tirone</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>15 CENTER LN</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.710066+00:00</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.710066+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>1000268701</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>blaket@unlimitedps.net</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Unlimited Permit Services, INC</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>3790 NE 25TH AVE</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.790455+00:00</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.790455+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>1000268673</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>nicj2388@gmail.com</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Nicoden Joseph</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>108 W KEYES AVE</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.869790+00:00</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:15.869790+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>1000268474</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>omar.garcia@usreis.com</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Urban Core II LLC</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>220 E MADISON ST</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.002431+00:00</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.002431+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>1000268468</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>LTTK1222@gmail.com</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Kieu  Le</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>304 NW 4TH AVE</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.082424+00:00</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.082424+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>1000268445</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>jmas@p1capital.com</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Jacqueline Mas</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>6020 LE LAC RD</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.163096+00:00</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.163096+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>1000268436</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>jeb@planestocks.com</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Jeb Thomas</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>999 ELDERBERRY WAY</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.244456+00:00</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.244456+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>1000268401</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>southernpoolssouth@gmail.com</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Austin Akers</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>136 SAN SALVADOR ST</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.336033+00:00</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.336033+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>1000268398</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>LTLBunny65@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Diana Cruz</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>VERMONT ST</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.417143+00:00</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.417143+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>1000268375</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>susan@rossfelty.com</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Law Office of Kyle Felty, P.A.</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>OAK HARBOUR DR, SLIP D-21</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.551865+00:00</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.551865+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>1000268354</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>mw@closingexpress.com</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Closing Express, Inc.</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>930 NE 74TH ST</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.633709+00:00</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.633709+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>1000268167</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Jeff@b90consulting.com</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Jeff Becker</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>916 NE 4TH ST</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.716232+00:00</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.716232+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>1000268064</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>cmcarc@msn.com</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>CM Crawford Architect, Inc.</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2530 FAIRWAY DR</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.804600+00:00</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.804600+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>1000267983</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>denis@beachway.com</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Beachway LLC</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>3737 NW 4TH AVE</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.887513+00:00</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.887513+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>1000267922</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>lynjmac@aol.com</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Lyn McCarthy</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>15&amp;17 PALMETTO WAY</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.969688+00:00</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:16.969688+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>1000267907</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>mohit1283@gmail.com</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Mohit Garg</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>17026 FL-54</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.107557+00:00</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.107557+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>1000267661</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>wdeitch1953@gmail.com</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Warren Deitch</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>5630 VINTAGE OAKS CIR</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.192132+00:00</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.192132+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>1000267659</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ALTA Table A Survey</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>stefaniebrown@firstam.com</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>CDS-Commercial Due Diligence Services</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>5401 WILES RD</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.277153+00:00</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.277153+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>1000267373</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>norberto@madsenarchitects.com</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Madsen Design</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2717 SW EAST CALABRIA CIR</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.361867+00:00</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.361867+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>1000267049</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>CAD File</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>office@mypoolrenovators.com</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Pool Renovators</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>511 CRYSTAL DR</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.446685+00:00</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.446685+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>1000267001</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>office@shorearchitect.com</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>TRB Architects</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>329 EAGLE DR</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.531315+00:00</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.531315+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>1000266847</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>julio@pachecoarchitecture.com</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Pacheco Architecture</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>5810 MAGGIORE ST</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.677204+00:00</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.677204+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>1000266764</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>aknecht@gofamilychurch.org</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Lighthouse Baptist Church</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>757 LIGHTHOUSE DR</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.766658+00:00</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.766658+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>1000266719</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>tc@realtyblu.com</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Kek Rodriguez</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>8608 N 13TH ST</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.854178+00:00</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.854178+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>1000266615</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>CAD File</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>S.Sinclair@giantoil.com</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Sinclair </t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>3845 BLANDING BLVD</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.940129+00:00</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:17.940129+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>1000266475</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>islandwayamber@gmail.com</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Island Way Pools</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>2316 KENT PL</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.026993+00:00</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.026993+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>1000266457</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>tere@palmvista.org</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Palm Vista Community Church, Inc.</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>1956 NW 183RD ST</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.112411+00:00</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.112411+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>1000266383</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>emily@wlpiper.com</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Piper Properties</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>2650 SHELTINGHAM DR</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.255046+00:00</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.255046+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>1000266363</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Land Survey and Elevation</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>stefaniebrown@firstam.com</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Tiffany Grafton</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>750 PENFIELD ST</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.342685+00:00</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.342685+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>1000266082</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>hzuluaga1@verizon.net</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Herman Zuluaga</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>12500 5TH ST E</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.429367+00:00</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.429367+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>1000265855</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>CAD File</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>sasukal@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Sean  Sukal</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2801 NW 27TH AVE</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.516236+00:00</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.516236+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>1000265850</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>CAD File</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Uainc@bellsouth.net</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Urban Associates, Inc.</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>4701 PINE TREE DR</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.602901+00:00</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.602901+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>1000265646</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>archtype@bellsouth.net</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Archtype Design, Inc</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>6650 NW 84TH AVE</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.743454+00:00</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.743454+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>1000265620</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>aaron@gatorcapitalpartners.com</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Aaron Lambert</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>1885 MISSISSIPPI AVE NE</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.832762+00:00</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.832762+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>1000265557</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>locus@locusarchitecture.net</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Locus Architecture</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>3801 COCO GROVE AVE</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.923810+00:00</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:18.923810+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>1000265550</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>erol@buyuk.ch</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>EROL BUYUK</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>780 HARBOUR ISLE PL</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.012654+00:00</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.012654+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>1000265545</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>oureinsteins@gmail.com</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Mihai Gorgan</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>5201 VILLAGE BLVD</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.101239+00:00</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.101239+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>1000265300</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>CAD File</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>tonysbmw@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>James Scott</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>13475 150TH CT N</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.190104+00:00</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.190104+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>1000265289</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ribanez2nd@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>RICARDO IBANEZ</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>12609 S INDIAN RIVER DR</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.334416+00:00</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.334416+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>1000265181</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Land Survey and Elevation</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>jhall@regtitles.com</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Register Settlement Services, LLC</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>7107 58TH TER E</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.424626+00:00</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.424626+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>1000264774</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>contact@lmphomeservices.com</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>LMP Home Services</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>125 BANYAN ISLE DR</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.514623+00:00</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.514623+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>1000264707</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>clarkebgj@gmail.com</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Clarke Gillespie</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>501 VILABELLA AVE</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.604572+00:00</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.604572+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>1000264704</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>stacyhetman0768@gmail.com</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Stacy Hetman</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>1239 GROVELAND AVE</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.694514+00:00</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.694514+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>1000264455</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>kbelectric@ymail.com</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>BEATRICE  ESTEVEZ</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2802 SW 5TH ST</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.844907+00:00</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.844907+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>1000264360</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>j@jabuildsinc.com</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>J Azocar</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>511 NORTON ST</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.935458+00:00</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:19.935458+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>1000264308</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>iartzy@IKALaw.com</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>The Law Office of Ilana Kalichman-Artzy</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>4148 SW 130TH AVE</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.026553+00:00</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.026553+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>1000264293</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Savvyroseproperties@gmail.com</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Savvy Rose Properties</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>463 &amp; 471 OAKMON RD</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.118437+00:00</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.118437+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>1000264273</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>julia@bayviewla.com</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Bayview Landscape Architecture</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>15 LA VISTA DR</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.212157+00:00</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.212157+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>1000264249</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>CAD file</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>santiago@thefeldmancompanies.com</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Santiago Araujo</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>400 METCALF CT</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.307110+00:00</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.307110+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>1000264205</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>hamptonsgjb@aol.com</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Gerald Baldi</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>5203 86TH STREET CT W</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.462139+00:00</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.462139+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>1000264046</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>nattyvga27@gmail.com</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Angela Vega</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>1717 ROYAL FOREST CT</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.556142+00:00</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.556142+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>1000263848</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Boundary Survey</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>lbutler@powersupportpartners.com</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Power Support Partners</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>8518 SPRING FOREST LN</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.648808+00:00</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.648808+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>1000263795</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>sboscarelli@firstam.com</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>CDS-Commercial Due Diligence Services</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>2601 BIMINI BAY CRES</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.742292+00:00</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.742292+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>1000263710</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Dworrie@gmail.com</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Dwayne Worrie</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>7882 NW 62ND TER</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.840343+00:00</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:20.840343+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>1000263654</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>chase.harris254@gmail.com</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Chase Harris</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>1690 DELAWARE AVE NE</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.005727+00:00</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.005727+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>1000263552</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Elevation Only</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>brooke.murphy@compass.com</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Brooke A. Murphy, LLC.</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>257 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.100598+00:00</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.100598+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>1000263449</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>kmoconnell75@gmail.com</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>KATHLEEN MARY O'CONNELL</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>1714 BAYOU GRANDE BLVD NE</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.196188+00:00</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.196188+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>1000263426</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>maxcoup3@gmail.com</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Dale Thomas</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>7942 17TH PL</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.291970+00:00</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.291970+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>1000263422</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>bursteinjeremy@gmail.com</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Jeremy  Burstein</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>4361 45TH ST N</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.388185+00:00</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.388185+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>1000263418</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>hatcherconstructionllc@gmail.com</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Chris Hatcher</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>904 MAGNOLIA ST</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.539518+00:00</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.539518+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>1000263414</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>CAD Files</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Kharringtonou812@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Kevin Harrington</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 5897 URDEA RD</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.635843+00:00</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.635843+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>1000263413</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>CAD Files</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Antonio@premierestateproperties.com</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Premier Estate Properties</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>999 NW 5TH AVE</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.732544+00:00</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.732544+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>1000263200</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>centipedels@gmail.com</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>BARBRA  LEONE</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>1556 SE BALLANTRAE CT</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.831417+00:00</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.831417+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>1000263017</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>amanda@binghamarchitecture.com</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Bingham Architecture</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>1771 SERPENTINE DR S</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.928812+00:00</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:21.928812+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>1000262859</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>dlang@langarchitect.net</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Diaz Plus Lang Architects, LLC</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>1279 SW 15TH ST</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:22.086498+00:00</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:22.086498+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>1000262774</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>alexanderbuetell@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alexander  Buettell </t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>12736 POINSETTIA AVE</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:22.184394+00:00</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:22.184394+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>1000262722</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>jeffrey@brasseuranddrobot.com</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Brasseur &amp; Drobot Architects</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>10250 TRAILWOOD CIR</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:22.282088+00:00</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:12:22.282088+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U279"/>
+  <dimension ref="A1:U379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5407,8 +5407,39 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>5684 SE ORANGE BLOSSOM TRAIL</t>
-        </is>
+          <t>5684 SE ORANGE BLOSSOM TRAIL, HOBE SOUND, FL 33455</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>{"total_amount": 312.0, "services": [{"name": "CAD Survey (Boundary/Land Survey - CAD Deliverable)", "description": "CAD drafting and survey deliverable for Lot 3, Block 104, Poinciana Gardens Section 1 &amp; 2, Martin County. Platted lot with straightforward legal description. Base rate per management-approved special pricing for this client.", "amount": 250.0}, {"name": "Lot Size Complexity Upcharge (0.31\u20130.50 ac)", "description": "Property is 0.43 acres, falling within the 0.31\u20130.50 ac tier. Upcharge applied per standard complexity schedule.", "amount": 62.0}], "pricing_reasoning": "Management has set a negotiated base rate of $250.00 for this individual client, which is used as the survey base. The lot is 0.43 acres, placing it squarely in the 0.31\u20130.50 ac complexity tier warranting a $62.00 upcharge. No EC is requested, FEMA Zone X carries no flood-zone premium, the legal description is a simple platted lot (no metes-and-bounds upcharge), Martin County carries no remote mobilization fee, and no pool, waterfront, or heavy vegetation complexity was identified from available data.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "Order scope is incompletely defined \u2014 notes indicate the order is On Hold pending property details and a defined scope of work. Additionally, three likely duplicate orders exist for the same address, folio, and coordinates (Orders 1000062400, 1000279316, 1000284425), all for Land Survey Only at the same location. Management should confirm: (1) whether this CAD order is a standalone new scope or a CAD deliverable tied to one of the existing survey orders; (2) whether the duplicate orders should be merged, cancelled, or retained; and (3) final scope confirmation before invoicing.", "flags": ["DUPLICATE WARNING: Order 1000062400 \u2014 same address (5684 SE Orange Blossom Trail), same folio (34-38-42-038-104-00030-1), service: Land Survey Only. Verify relationship to this CAD order.", "DUPLICATE WARNING: Order 1000279316 \u2014 same address (5684 SE Orange Blossom Trail), same folio (34-38-42-038-104-00030-1), service: Land Survey Only. Verify relationship to this CAD order.", "DUPLICATE WARNING: Order 1000284425 \u2014 same address (5684 SE Orange Blossom Trail), same folio (34-38-42-038-104-00030-1), service: Land Survey Only. Verify relationship to this CAD order.", "ORDER ON HOLD: Per order notes, scope of work and property details were not fully defined at time of order entry. Pricing is proposed but should not be finalized until scope is confirmed by management.", "NO AERIAL/IMAGE DATA PROVIDED: Lot complexity assessment (pool, waterfront, heavy vegetation) is based on available text data only. Field crew should verify on site."]}</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202602252036258867, "created_at": "2026-03-10T14:44:21", "customer_email": "arspado@spadopools.com", "customer_id": 202602252036259001, "customer_name": "Nancy Perez", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12085C0310H\nZONE: X\nEFF: 02/19/2020", "invoiced": false, "order_id": 1000280038, "paid": true, "property_address": "5684 SE ORANGE BLOSSOM TRAIL", "property_city": "HOBE SOUND", "property_county": "MARTIN COUNTY", "property_lat": "27.1029286", "property_lng": "-80.17704429999999", "property_state": "FL", "property_zip": "33455", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-05-11T16:23:28"}, "success": true, "order_id": "1000280038", "customer_email": "arspado@spadopools.com", "service_type": "CAD", "county": "", "property_address": "5684 SE ORANGE BLOSSOM TRAIL", "customer_name": "Nancy Perez"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Nancy Perez", "confidence": "HIGH"}, "client_email": {"value": "arspado@spadopools.com", "confidence": "HIGH"}, "property_address": {"value": "5684 SE ORANGE BLOSSOM TRAIL, HOBE SOUND, FL 33455", "confidence": "HIGH"}, "property_county": {"value": "MARTIN COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type listed as CAD only; no additional services specified in the order data"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 county appraiser unavailable", "Structure square footage not provided", "Property features (pool, shed, structures) unknown \u2014 no aerial, appraiser, or email data", "Reason for On Hold status not specified", "Reason for special pricing not documented", "No fieldwork or delivery dates scheduled", "Client relationship unclear \u2014 email domain suggests business (Spado Pools) but customer_type is listed as individual", "Scope of CAD work not defined \u2014 no notes or attachments found"], "summary": "CAD survey order for Nancy Perez at 5684 SE Orange Blossom Trail, Hobe Sound, FL (Martin County) is currently On Hold with special pricing applied, but lacks property details, legal description, and defined scope of work."}}</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1780417313356</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:44.777832+00:00</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:21:54.129934+00:00</t>
+        </is>
+      </c>
+      <c r="R90" t="n">
+        <v>312</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -5417,7 +5448,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:13.599509+00:00</t>
+          <t>2026-06-02T16:21:54.176570+00:00</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5460,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5444,13 +5475,44 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>VJD Construction</t>
+          <t>VJD Construction (Vinny D'Aquino)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>13820 LE HAVRE DR</t>
-        </is>
+          <t>13820 Le Havre Dr, Palm Beach Gardens, FL 33410</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "AI pricing failed: Expecting ',' delimiter: line 20 column 4 (char 3037). Manual review required.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "AI pricing error \u2014 needs manual quote", "flags": ["ai_error"]}</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202509041601517200, "created_at": "2026-03-09T17:09:32", "customer_email": "vinny@vjdconstruction.com", "customer_id": 202509041602187373, "customer_name": "Vinny  D'Aquino", "customer_type": "b2b", "delivered_at": "2026-03-12T17:49:49", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0189G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000279970, "paid": true, "property_address": "13820 LE HAVRE DR", "property_city": "PALM BEACH GARDENS", "property_county": "PALM BEACH COUNTY", "property_lat": "26.8805698", "property_lng": "-80.0905482", "property_state": "FL", "property_zip": "33410", "service_type": "CAD", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-03-12T17:49:49"}, "success": true, "order_id": "1000279970", "customer_email": "vinny@vjdconstruction.com", "service_type": "CAD", "county": "", "property_address": "13820 LE HAVRE DR", "customer_name": "VJD Construction"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "VJD Construction (Vinny D'Aquino)", "confidence": "HIGH"}, "client_email": {"value": "vinny@vjdconstruction.com", "confidence": "HIGH"}, "property_address": {"value": "13820 Le Havre Dr, Palm Beach Gardens, FL 33410", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD Drafting"], "confidence": "MEDIUM", "notes": "Service type listed as 'CAD' \u2014 likely CAD drafting/redrafting of survey data; exact deliverable scope unclear without supporting emails or order notes"}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available and no emails found; pool, structures, driveways, and other features unknown"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Exact CAD service scope not defined (redraft, as-built, boundary CAD, etc.)", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, driveways) unknown \u2014 no aerial or appraiser data", "No matching emails found to clarify order context", "Fieldwork date is null \u2014 unclear if fieldwork is needed or if this is a CAD-only task", "No county provided in the top-level order data (county field is empty string)"], "summary": "B2B CAD drafting order for Vinny D'Aquino of VJD Construction at 13820 Le Havre Dr, Palm Beach Gardens, FL, marked delivered and paid with special pricing applied, but scope details and property data are limited."}}</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1780417338263</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:56.273019+00:00</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:22:18.858963+00:00</t>
+        </is>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -5459,7 +5521,7 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:13.645100+00:00</t>
+          <t>2026-06-02T16:22:18.906525+00:00</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5533,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5491,8 +5553,39 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>436 BAYSHORE DR</t>
-        </is>
+          <t>436 Bayshore Dr, Venice, FL 34285</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>{"total_amount": 637.0, "services": [{"name": "Land Survey", "description": "Boundary/land survey at 436 Bayshore Dr, Venice FL \u2014 negotiated base rate agreed by management for this individual client (Rick Tromble, 0 prior orders).", "amount": 500.0}, {"name": "Lot Size Complexity Upcharge (0.51\u20131.00 ac)", "description": "Lot is 0.64 acres per database, falling in the 0.51\u20131.00 ac tier. Standard upcharge of $137.00 applies for increased field time and boundary work on a mid-size residential lot.", "amount": 137.0}], "pricing_reasoning": "The service requested is a Land Survey Only for a 0.64-acre residential lot in Sarasota County. The negotiated base rate of $500.00 is applied per management agreement. The lot size of 0.64 acres falls in the 0.51\u20131.00 ac complexity tier, warranting a $137.00 upcharge. No Elevation Certificate was ordered, so no EC line item or FEMA/VE surcharge is applicable. The metes-and-bounds legal description is noted but is typical for this region and lot type; no additional metes-and-bounds upcharge is applied given the negotiated rate already reflects management-adjusted pricing. No pool, waterfront canal, heavy vegetation, or Monroe County factors are evidenced in the data.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE DUPLICATE: Order 1000278365 references the same property address (436 Bayshore Dr, Sarasota County), same coordinates, and same Folio/MLS (0175010006). That prior order includes both Land Survey AND Elevation Certificate. Human review is recommended to confirm whether this order is a duplicate, a re-order, or intentionally scoped differently (Land Survey Only, no EC). Do not proceed to schedule fieldwork until duplicate status is resolved.", "ORDER STATUS: Order notes indicate this order is currently On Hold with special pricing applied and no fieldwork scheduled. Pricing confirmed but hold status should be cleared by the responsible party before dispatching crew.", "METES AND BOUNDS: Legal description is an incomplete metes-and-bounds description (text appears truncated). Full legal description should be confirmed in the title/deed before fieldwork to ensure accurate boundary closure."]}</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202602091448113612, "created_at": "2026-03-06T14:44:38", "customer_email": "rick@tromble.com", "customer_id": 202602091448114904, "customer_name": "Rick Tromble", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12115C0327G\nZONE: AE\nELEV: 09 FT\nEFF: 03/27/2024", "invoiced": false, "order_id": 1000279860, "paid": true, "property_address": "436 BAYSHORE DR", "property_city": "VENICE", "property_county": "SARASOTA COUNTY", "property_lat": "27.1080041", "property_lng": "-82.45216479999999", "property_state": "FL", "property_zip": "34285", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-06T16:13:15"}, "success": true, "order_id": "1000279860", "customer_email": "rick@tromble.com", "service_type": "Land Survey Only", "county": "", "property_address": "436 BAYSHORE DR", "customer_name": "Rick Tromble"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Rick Tromble", "confidence": "HIGH"}, "client_email": {"value": "rick@tromble.com", "confidence": "HIGH"}, "property_address": {"value": "436 Bayshore Dr, Venice, FL 34285", "confidence": "HIGH"}, "property_county": {"value": "Sarasota County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11). Flood zone data available: FEMA panel 12115C0327G, Zone AE, base flood elevation 9 ft, effective 03/27/2024.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided. Pool, shed, driveways, and other structures unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fence, driveway, outbuildings)", "Reason for On Hold status not specified", "No fieldwork or delivery dates scheduled", "Urgency/timeline not indicated", "No customer profile data returned from FTF customer lookup", "Special pricing terms not detailed \u2014 needs verification"], "summary": "Residential land survey order for Rick Tromble at 436 Bayshore Dr, Venice FL (Sarasota County), currently On Hold with special pricing applied and no fieldwork scheduled."}}</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1780417359694</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:21:06.761193+00:00</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:22:40.216342+00:00</t>
+        </is>
+      </c>
+      <c r="R92" t="n">
+        <v>637</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -5501,7 +5594,7 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:13.691246+00:00</t>
+          <t>2026-06-02T16:22:40.264975+00:00</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5606,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5533,7 +5626,17 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1547 PROSPERITY FARMS RD</t>
+          <t>1547 PROSPERITY FARMS RD, LAKE PARK, FL 33403</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201801311053398445, "created_at": "2026-03-06T10:13:48", "customer_email": "veenu_b@nexgenlogix.com", "customer_id": 201904111121065389, "customer_name": "Veenu Singh", "customer_type": "b2b", "delivered_at": null, "due_amount": 300.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": null, "invoiced": false, "order_id": 1000279855, "paid": false, "property_address": "1547 PROSPERITY FARMS RD", "property_city": "LAKE PARK", "property_county": "Palm Beach County", "property_lat": "26.8068413", "property_lng": "-80.0737982", "property_state": "FLORIDA", "property_zip": "33403", "service_type": "Acreage, Site Plan", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-04-15T03:41:20"}, "success": true, "order_id": "1000279855", "customer_email": "veenu_b@nexgenlogix.com", "service_type": "Acreage, Site Plan", "county": "", "property_address": "1547 PROSPERITY FARMS RD", "customer_name": "Nexgen Land Solutions, LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Nexgen Land Solutions, LLC", "confidence": "MEDIUM"}, "client_email": {"value": "veenu_b@nexgenlogix.com", "confidence": "HIGH"}, "property_address": {"value": "1547 PROSPERITY FARMS RD, LAKE PARK, FL 33403", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Acreage Survey", "Site Plan"], "confidence": "HIGH", "notes": "Parsed from service_type field 'Acreage, Site Plan'; special_pricing flag is true which may affect scope or pricing"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property feature data available; county appraiser unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name discrepancy: order lists 'Veenu Singh' as customer_name but top-level field shows 'Nexgen Land Solutions, LLC' \u2014 confirm correct billing entity", "Lot size / acreage unknown \u2014 critical for Acreage Survey scoping and pricing", "Legal description not provided", "Property features unknown (pool, structures, fencing, etc.)", "Structure square footage unknown", "Reason for 'On Hold' status not specified \u2014 requires human review before proceeding", "No fieldwork or delivery dates scheduled", "County property appraiser data unavailable \u2014 no county was passed to lookup", "Special pricing details not documented \u2014 confirm agreed rate", "No supporting emails or attachments found to supplement order data"], "summary": "B2B order for an Acreage Survey and Site Plan at 1547 Prosperity Farms Rd, Lake Park, FL (Palm Beach County) for Nexgen Land Solutions, LLC, currently On Hold with special pricing applied and a $300 due balance, pending key property details and resolution of the hold status."}}</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:21:18.792887+00:00</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -5543,7 +5646,7 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:13.736955+00:00</t>
+          <t>2026-06-02T16:21:18.840425+00:00</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5658,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5575,7 +5678,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0 STATE ROAD 54</t>
+          <t>0 STATE ROAD 54, NEW PORT RICHEY, FL 34653</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201801311051305246, "created_at": "2026-03-05T18:49:36", "customer_email": "traci@naturecoastlaw.com", "customer_id": 201801311101215230, "customer_name": "Traci Gaughan", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12101C0354G\nZONE: X\nEFF: 06/05/2020", "invoiced": false, "order_id": 1000279820, "paid": false, "property_address": "0 STATE ROAD 54", "property_city": "NEW PORT RICHEY", "property_county": "PASCO COUNTY", "property_lat": "28.2170163", "property_lng": "-82.6967297", "property_state": "FL", "property_zip": "34653", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-06T14:54:41"}, "success": true, "order_id": "1000279820", "customer_email": "traci@naturecoastlaw.com", "service_type": "Land Survey Only", "county": "", "property_address": "0 STATE ROAD 54", "customer_name": "Hengesbach and Hengesbach, PA"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Hengesbach and Hengesbach, PA", "confidence": "MEDIUM"}, "client_email": {"value": "traci@naturecoastlaw.com", "confidence": "HIGH"}, "property_address": {"value": "0 STATE ROAD 54, NEW PORT RICHEY, FL 34653", "confidence": "HIGH"}, "property_county": {"value": "PASCO COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; specific survey type (boundary, topo, etc.) not clarified"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; address is '0 STATE ROAD 54' suggesting vacant land or unaddressed parcel \u2014 no structures, pool, or improvements confirmed"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: FTF order data lists 'Traci Gaughan' as customer_name but outer payload lists 'Hengesbach and Hengesbach, PA' \u2014 needs human clarification on billing entity", "Specific survey type not defined (boundary, topographic, ALTA, etc.)", "Lot size / acreage unknown \u2014 county appraiser data unavailable", "Legal description not provided", "No parcel ID or folio number provided", "Property appears to be vacant land (address '0 STATE ROAD 54') \u2014 ownership and parcel details unconfirmed", "Reason for 'On Hold' status not specified", "Special pricing amount or agreement not documented", "No fieldwork date scheduled", "No matching emails found to provide additional context"], "summary": "B2B land survey order for what appears to be a vacant parcel at 0 State Road 54, New Port Richey, FL (Pasco County), placed on behalf of Hengesbach and Hengesbach, PA, currently on hold with special pricing applied and several key details missing."}}</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:21:30.592811+00:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
@@ -5585,7 +5698,7 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:13.785300+00:00</t>
+          <t>2026-06-02T16:21:30.639273+00:00</t>
         </is>
       </c>
     </row>
@@ -13356,6 +13469,4206 @@
       <c r="U279" t="inlineStr">
         <is>
           <t>2026-06-02T16:12:22.282088+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>1000262484</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>masonpatrou@gmail.com</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>mason patrou</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>1245 OAKWOOD LN</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:20.652548+00:00</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:20.652548+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>1000262465</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Brendanr@prestigeclosings.com</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prestige Title </t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>4601 HELENA DR</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:20.758713+00:00</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:20.758713+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>1000262056</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Land Survey and Elevation</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>tpowers954@aol.com</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>TIMOTHY POWERS</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>3561 NW 5TH AVE</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:20.866824+00:00</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:20.866824+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>1000262012</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>juliannarc1220@gmail.com</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Julianna Romero</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>5581 HONEYSUCKLE DR</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:20.971021+00:00</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:20.971021+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>1000261801</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>paul.landscapedesignstudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Landscape Design Studio</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>2009 NE 2ND ST</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.120527+00:00</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.120527+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>1000261778</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>cameron@andrewsitework.com</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Cameron Maki</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>6491 CEDARWOOD AVE</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.226981+00:00</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.226981+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>1000261635</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>tom@pbbuildingco.com</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Palm Beach Building Co</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>717 S PALMWAY</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.335762+00:00</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.335762+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>1000261247</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>LT@affiniti.us</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Affinity Architects</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>300 E COCONUT PALM RD</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.444321+00:00</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.444321+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>1000261147</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>reliablestockers@gmail.com</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Joseph  Loudy</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>8454 92ND TER</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.598537+00:00</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.598537+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>1000261043</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>mnolan@eec-tampabay.com</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Environmental Engineering Consultants, Inc.</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>2705 &amp; 2708 N. 18TH ST.</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.706637+00:00</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.706637+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>1000260999</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>southernpoolssouth@gmail.com</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Southern Pools South, Inc.</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>3362 RANDALL BLVD</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.813557+00:00</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.813557+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>1000260938</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>tputnam@firstam.com</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>CDS-Commercial Due Diligence Services</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>4585 SE FEDERAL HWY</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.924411+00:00</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:21.924411+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>1000260891</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>eduardojmr87@gmail.com</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Eduardo  RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>7117 ROBINDALE RD</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.033763+00:00</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.033763+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>1000260872</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>paul@oppenheimrealty.com</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Jason Venturi</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>2572 NE 26TH ST</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.190625+00:00</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.190625+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>1000260674</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>BASTIRDGUEZ@YAHOO.COM</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>CARLOS BASTIDA</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>516 MCARTHUR BLVD</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.298047+00:00</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.298047+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>1000260671</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>BASTIRDGUEZ@YAHOO.COM</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>CARLOS BASTIDA</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>1132 CROQUET ST E</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.406534+00:00</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.406534+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>1000260560</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>ryan@siteimpact.com</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ryan MCGINNIS </t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>101 NEPTUNE DR</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.517018+00:00</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.517018+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>1000260546</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Mblack@cotleur-hearing.com</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cotleur &amp; Hearing </t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>924 AUGUSTA POINTE DR</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.673875+00:00</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.673875+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>1000259935</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>josecpa@jttcpa.com</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Jose Pa</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>7991 JOHNSON ST</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.783553+00:00</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.783553+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>1000259818</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>aapontillo@gmail.com</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>ARMAND CUKO CUKO</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>1 KENMORE LN</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.893529+00:00</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:22.893529+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>1000259556</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>mhampson7@gmail.com</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Michael Hampson</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>821 15TH ST SW</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.002373+00:00</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.002373+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>1000259527</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>billw@wjwarch.com</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>WJ Weeks Architecture</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>246 S PARK AVE</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.163141+00:00</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.163141+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>1000259424</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>emersongonzalez1999@gmail.com</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EMERSON  GONZALEZ </t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>2991 SW 21ST CT</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.274436+00:00</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.274436+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>1000259418</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>nicole@nicolegreeneinteriors.com</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Nicole Greene</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>13906 SEAFORTH MANOR WAY</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.387851+00:00</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.387851+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>1000259378</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>mmargolies@wbsmlawyers.com</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>WEISMAN &amp; MARGOLIES, P.A.</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>5864 VINTAGE OAKS CIR</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.500523+00:00</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.500523+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>1000259287</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>diangoac@live.com</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diango  Carrera </t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>914 EUCLID AVE</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.614084+00:00</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.614084+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>1000259205</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>michaelsrizzo@gmail.com</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rizzo &amp; Rizzo Inc. </t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>6735 CASA GRANDE WAY</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.772667+00:00</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.772667+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>1000259173</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>TIM@naplestitle.com</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Naples Title, Inc.</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>2034 PRINCE DR</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.887154+00:00</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.887154+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>1000259000</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>tpelkey1395@gmail.com</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Tiffani Pelkey</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>6325 ALFRED BLVD AND 6309 ALFRED BOULEVARD</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.999609+00:00</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:23.999609+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>1000258948</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>mari@lopezgarciapa.com</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Jorge Luis Lopez-Garcia, P.A.</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>1334 ALHAMBRA CIR</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:24.115293+00:00</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:24.115293+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>1000258932</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>tputnam@firstam.com</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>CDS-Commercial Due Diligence Services</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>5803 W 5TH ST</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:24.276196+00:00</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:24.276196+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>1000258855</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>jay.hollis11@gmail.com</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>James Hollis</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>3414 S GARDENIA AVE</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:24.390449+00:00</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:24.390449+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>1000258575</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>korihaggard3@gmail.com</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Kori Haggard</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>7775 TALAVERA PL</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:24.503239+00:00</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:24.503239+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>1000258547</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>sam@zeewa.com</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Superior Construction Solutions</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>12938 OLD KINGS RD</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:24.616606+00:00</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:24.616606+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>1000258469</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>1norberto@madsenarchitects.com</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Madsen Architects</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>4211 - 4215 N FEDERAL HIGHWAY</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:24.772441+00:00</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:24.772441+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>1000258273</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>jtruettpembo@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Joseph Truett Pembo Architect</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>679 6TH AVE</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:24.890137+00:00</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:24.890137+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>1000258190</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>elicohenbary@gmail.com</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Eli Cohen</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>18730 NE 19TH AVE</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.004558+00:00</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.004558+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>1000258182</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>alexcradu@gmail.com</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALEXANDRU  RADU </t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>1667 N DIXIE HWY</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.120955+00:00</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.120955+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>1000258181</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Robert.ross@outlook.com</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Robert Ross</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>11759 RIVERCHASE RUN</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.290938+00:00</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.290938+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>1000258062</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Update Survey</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>FREDERICK_S@NEXGENLOGIX.COM</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Nexgen Land Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>7219 TRENTINO WAY</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.409373+00:00</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.409373+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>1000258061</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Re-survey</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>FREDERICK_S@NEXGENLOGIX.COM</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Nexgen Land Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>506 NW 8TH CT</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.526298+00:00</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.526298+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>1000258009</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>amandalynnroach@gmail.com</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>AMANDA  Roach</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>46 CHAPEL CT</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.650472+00:00</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.650472+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>1000257863</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>EC UNDER CONSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>amanidesigngroup@gmail.com</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Amani Design Group</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>2264 SW 34TH AVE</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.809241+00:00</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.809241+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>1000257758</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>davidcorrallegacy@gmail.com</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Contractor's Legacy</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>107 NE ROYCE AVE</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.926366+00:00</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:25.926366+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>1000257655</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>CAD Release</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>as@vertexarchitecture.com</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Vertex Architecture, Inc</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>3621 SW 48TH AVE</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.045867+00:00</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.045867+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>1000256917</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Property Flagging</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>violetarealtorfl@gmail.com</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Violeta Rodriguez</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>1455 SHANNONDALE RD</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.165567+00:00</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.165567+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>1000256832</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>CAD File</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Wgoodman@goodmanautogroup.com</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>William Goodman</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>000 THOMAS AVE</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.332020+00:00</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.332020+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>1000256818</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Land Survey and Elevation</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>lkhozo35@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Keith Hoelzel</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>1314 AVOCADO ISLE</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.448734+00:00</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.448734+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>1000256787</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Land Survey and Elevation</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>hess.gabrielle@gmail.com</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Gabrielle Kuzniecky</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>3321 SW 59TH ST</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.566817+00:00</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.566817+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>1000256683</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>ALTA Table A Survey</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>KSwoboda@firstam.com</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>CDS-Commercial Due Diligence Services</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>S ORANGE BLOSSOM TRL</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.692096+00:00</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.692096+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>1000256657</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Bygethia@gmail.com</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Bygethia Kankam</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>8200 BUTLER GREENWOOD DR</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.863573+00:00</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.863573+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>1000256384</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Land Survey and Elevation</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>mu@wcifl.com</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Watlee Construction</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>19943 PINETREE DR</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.982055+00:00</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:26.982055+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>1000256371</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>FREDERICK_S@NEXGENLOGIX.COM</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>NexGen Surveying, LLC.</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>6742 NW 108TH AVE</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:27.100715+00:00</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:27.100715+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>1000256282</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>ALTA Table A Survey</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>sboscarelli@firstam.com</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>CDS-Commercial Due Diligence Services</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>1547 N FLORIDA MANGO RD</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:27.225132+00:00</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:27.225132+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>1000256281</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>ALTA Table A Survey</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>sboscarelli@firstam.com</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>CDS-Commercial Due Diligence Services</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>3015 BARTOW RD</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:27.395337+00:00</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:27.395337+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>1000256280</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>ALTA Table A Survey</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>sboscarelli@firstam.com</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>CDS-Commercial Due Diligence Services</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>2200 E EDGEWOOD DR</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:27.516305+00:00</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:27.516305+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>1000256231</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>CAD File</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>ken@Kellaway.com</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Ken Kellaway</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>162 N WASHINGTON DR</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:27.635840+00:00</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:27.635840+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>1000256155</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>jamie.murphy@firstintitle.com</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>First International Title, Inc.</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>1700 COUNTY ROAD 833</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:27.756404+00:00</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:27.756404+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>1000256058</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>ALTA Table A Survey</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>tputnam@firstam.com</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Tracy Putman</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>0 S JOHN YOUNG PKWY</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:27.925967+00:00</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:27.925967+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>1000255729</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Property Flagging</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>FREDERICK_S@NEXGENLOGIX.COM</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>NexGen Surveying, LLC.</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>10416 SW 57TH CT</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:28.048293+00:00</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:28.048293+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>1000255662</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>CAD File</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>LP@TheGFirm.com</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>The G Law Firm LLC</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>7890 SW 66TH ST</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:28.170219+00:00</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:28.170219+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>1000255534</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>jdervilles@gmail.com</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Ben Noncent</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>2947 12TH AVE NE</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:28.294018+00:00</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:28.294018+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>1000255316</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>CAD File</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2saltyhooks@gmail.com</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Liz Palmer</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>2040 NEPTUNE RD</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:28.466974+00:00</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:28.466974+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>1000255301</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>KSwoboda@firstam.com</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Katherine Swoboda</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>SW CORNER OF SE OSPREY STREET AND SE DIXIE HIGHWAY</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:28.589443+00:00</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:28.589443+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>1000255216</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Specific Purpose Survey</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>cparmele@daypitney.com</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Christopher W. Parmele </t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>2740 BUCK RIDGE TRL</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:28.712312+00:00</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:28.712312+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>1000255072</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>jeffrey@brasseuranddrobot.com</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Brasseur &amp; Drobot Architects</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>125 ATLANTIC RD</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:28.834510+00:00</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:28.834510+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>1000255029</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>tputnam@firstam.com</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Tracy Putman</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>2900 NW 112TH AVE</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.011207+00:00</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.011207+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>1000255002</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Topography Survey</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>kirkhump1@gmail.com</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Kirk Humphreys</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>15183 83RD WAY N</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.135501+00:00</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.135501+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>1000254884</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Topo / Update /CAD File</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>JoshD@Brickbox.net</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Brick Box Management</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>2756 OAK TREE LN</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.258923+00:00</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.258923+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>1000254850</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>CAD Release</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>permit.enhancedaluminum@gmail.com</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Enhanced Aluminum</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>420 ALTA VISTA AVE</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.381116+00:00</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.381116+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>1000254783</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>CAD Release</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>dbrodie@yourfloridacounsel.com</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>David Brodie</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>7128 155TH PL N</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.550083+00:00</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.550083+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>1000254769</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>ashleyc@ridge-valley.com</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Ashley Cohn</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>10770 STONEBRIDGE BLVD</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.676075+00:00</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.676075+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>1000254730</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>CAD Release</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>rayfarrara@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Ray Farrara</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>4341 LIGUSTRUM DR</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.801135+00:00</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.801135+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>1000254657</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>windybaxley@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>WINDY  BAXLEY</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>306 WELLS ST</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.924669+00:00</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:29.924669+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>1000254622</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Property Flagging</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>paralegal@hiblaw.com</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Blaine H. Hibberd, P.A.</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>932 NE DIXON WAY</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:30.095935+00:00</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:30.095935+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>1000254491</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>noemail@no.net</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>3232 GEORGIA AVE NW</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:30.222731+00:00</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:30.222731+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>1000254288</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Survey Update / CAD Release</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>ssagareli@lakeworthbeachfl.gov</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>City of Lake Worth Beach</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>710 S H ST</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:30.348958+00:00</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:30.348958+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>1000254218</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>grecelhrndz@gmail.com</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Anny Milian</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>122 CULTURAL PARK BLVD N</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:30.476240+00:00</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:30.476240+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>1000253879</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Barbara@reyerlaw.com</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Reyer Law Group, P.A.</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>509 E 12TH ST</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:30.643151+00:00</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:30.643151+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>1000253878</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Barbara@reyerlaw.com</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Reyer Law Group, P.A.</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>409 E 12TH ST</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:30.774353+00:00</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:30.774353+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>1000253848</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>CAD File</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>jdixon@master24-7.com</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>JARRETT DIXON</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>300 BAY ST</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:30.903398+00:00</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:30.903398+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>1000253766</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Lauren@rivercitytitle.com</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>River City Title</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>6340 SEABOARD AVE</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:31.077196+00:00</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:31.077196+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>1000253690</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>ALTA Table A Survey</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>sboscarelli@firstam.com</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>CDS-Commercial Due Diligence Services</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>6401 NW 120TH LN</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:31.204406+00:00</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:31.204406+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>1000253563</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>permitting@deckanddrive.com</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Deck and Drive</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>344 WINTERS ST</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:31.334517+00:00</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:31.334517+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>1000253177</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Other Services</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>loudonandassociates@gmail.com</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Loudon &amp; Associates, LLC.</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>4050 SE WHITICAR WAY</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:31.464424+00:00</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:31.464424+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>1000253150</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>jarrod_d_burgess@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Jarrod Burgess</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>11780 161ST ST N</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:31.635882+00:00</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:31.635882+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>1000253093</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>lorena@lorenatello.com</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Lorena Tello</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>11309 4TH AVE</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:31.765635+00:00</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:31.765635+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>1000253043</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Other Services</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>mkarp@ecpgp.com</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Murray Karp</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>19259 SE HIDDEN BRIDGE CT</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:31.893722+00:00</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:31.893722+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>1000252925</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>matthewhair@mac.com</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Matthew Hoynacki</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>17275 ANTIGUA POINT WAY</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:32.076981+00:00</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:32.076981+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>1000252807</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>saucedolove500@gamil.com</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Jessica Saucedo</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>37118 HIGHLAND BLUFF CIR</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:32.208669+00:00</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:32.208669+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>1000252684</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>dferrandi@sbwh.law</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Preferred Title, Inc.</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>799 SE 19TH AVE</t>
+        </is>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:32.347215+00:00</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:32.347215+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>1000252584</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Specific Purpose Survey</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>anicolas@aol.com</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>NexGen Surveying, LLC.</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>1210 NORTHLAKE BLVD</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:32.478656+00:00</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:32.478656+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>1000252520</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Specific Purpose Survey</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>wendy.burns@dkpalaw.com</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Equity Title And Escrow</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>2401 NW 59TH ST</t>
+        </is>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:32.662907+00:00</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:32.662907+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>1000251157</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>peter@carepestsolutions.net</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Pedro Fernandez</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>353 ECHO PINES WAY</t>
+        </is>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:32.793407+00:00</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:32.793407+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>1000251012</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>permits@deckanddrive.com</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Deck and Drive</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>1016 CHERRY LN</t>
+        </is>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:32.923148+00:00</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:32.923148+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>1000251011</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>permits@deckanddrive.com</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Deck and Drive</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>1040 SUMMERWOOD CIR</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:33.104360+00:00</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:33.104360+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>1000249859</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>nadineheitz@gmail.com</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Nadine Heitz</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>32 S J ST</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:33.238258+00:00</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:33.238258+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>1000249802</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Boundary Survey</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>permits@deckanddrive.com</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Deck and Drive</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>4574 DOLPHIN DR</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:33.369688+00:00</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:33.369688+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>1000248307</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>permits@deckanddrive.com</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Deck and Drive</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>5030 NW 77TH CT</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:33.500318+00:00</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:33.500318+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>1000247810</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Land Survey and Elevation</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>jj@fcohenlaw.com</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Cohen, Norris, Wolmer, Ray, Telepman and Cohen</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>7389 165TH ST N</t>
+        </is>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:33.678274+00:00</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:20:33.678274+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U379"/>
+  <dimension ref="A1:U380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5629,16 +5629,37 @@
           <t>1547 PROSPERITY FARMS RD, LAKE PARK, FL 33403</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>{"total_amount": 800.0, "services": [{"name": "Acreage Survey", "description": "Boundary/acreage survey at 1547 Prosperity Farms Rd, Palm Beach County. Base rate per negotiated client agreement with Nexgen Land Solutions, LLC.", "amount": 500.0}, {"name": "Site Plan", "description": "Site plan preparation for the subject parcel (0.27 acres, Palm Beach County). Standard add-on for residential-scale lot under 0.31 acres; no acreage upcharge applies.", "amount": 300.0}], "pricing_reasoning": "The negotiated base rate of $500.00 is applied per management agreement with Nexgen Land Solutions, LLC. A Site Plan is an additional deliverable beyond the boundary survey and is priced at $300.00, which aligns with the noted '$300 due balance' referenced in the order notes and is consistent with standard site plan add-on pricing for a sub-0.31-acre parcel in Palm Beach County. No complexity upcharges are warranted: the lot is 0.27 acres (below the 0.31-acre threshold), FEMA zone is unknown (no EC required), the property is not in Monroe County, and no pool, waterfront, metes-and-bounds, or heavy vegetation flags are present in the available data.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000111332 at same address (1547 Prosperity Farms Rd, Palm Beach County), same Folio 36434220031290160 \u2014 service: Land Survey Only. Human review recommended to confirm this is not a re-order of prior work.", "DUPLICATE_WARNING: Order 1000203452 at same address and Folio \u2014 service: Quote. Human review recommended.", "DUPLICATE_WARNING: Order 1000210685 at same address and Folio \u2014 service: Quote. Human review recommended.", "FEMA_ZONE_UNKNOWN: Flood zone could not be confirmed. If property is later identified as Zone VE or AE and an Elevation Certificate is required, pricing must be updated. EC would be $275.00 (plus $50.00 if VE).", "ORDER_ON_HOLD: Order notes indicate this order is currently On Hold pending resolution of key property details. Pricing is proposed but should not be finalized until hold is cleared.", "LEGAL_DESCRIPTION_MISSING: No legal description was provided. If metes-and-bounds description is confirmed upon receipt of full legal, a +$100.00 complexity upcharge should be evaluated.", "CERTIFICATION_NOTE: Certification field contains 'TEST NEW ORDER' \u2014 verify this is a live production order before invoicing."]}</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 201801311053398445, "created_at": "2026-03-06T10:13:48", "customer_email": "veenu_b@nexgenlogix.com", "customer_id": 201904111121065389, "customer_name": "Veenu Singh", "customer_type": "b2b", "delivered_at": null, "due_amount": 300.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": null, "invoiced": false, "order_id": 1000279855, "paid": false, "property_address": "1547 PROSPERITY FARMS RD", "property_city": "LAKE PARK", "property_county": "Palm Beach County", "property_lat": "26.8068413", "property_lng": "-80.0737982", "property_state": "FLORIDA", "property_zip": "33403", "service_type": "Acreage, Site Plan", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-04-15T03:41:20"}, "success": true, "order_id": "1000279855", "customer_email": "veenu_b@nexgenlogix.com", "service_type": "Acreage, Site Plan", "county": "", "property_address": "1547 PROSPERITY FARMS RD", "customer_name": "Nexgen Land Solutions, LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Nexgen Land Solutions, LLC", "confidence": "MEDIUM"}, "client_email": {"value": "veenu_b@nexgenlogix.com", "confidence": "HIGH"}, "property_address": {"value": "1547 PROSPERITY FARMS RD, LAKE PARK, FL 33403", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Acreage Survey", "Site Plan"], "confidence": "HIGH", "notes": "Parsed from service_type field 'Acreage, Site Plan'; special_pricing flag is true which may affect scope or pricing"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property feature data available; county appraiser unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name discrepancy: order lists 'Veenu Singh' as customer_name but top-level field shows 'Nexgen Land Solutions, LLC' \u2014 confirm correct billing entity", "Lot size / acreage unknown \u2014 critical for Acreage Survey scoping and pricing", "Legal description not provided", "Property features unknown (pool, structures, fencing, etc.)", "Structure square footage unknown", "Reason for 'On Hold' status not specified \u2014 requires human review before proceeding", "No fieldwork or delivery dates scheduled", "County property appraiser data unavailable \u2014 no county was passed to lookup", "Special pricing details not documented \u2014 confirm agreed rate", "No supporting emails or attachments found to supplement order data"], "summary": "B2B order for an Acreage Survey and Site Plan at 1547 Prosperity Farms Rd, Lake Park, FL (Palm Beach County) for Nexgen Land Solutions, LLC, currently On Hold with special pricing applied and a $300 due balance, pending key property details and resolution of the hold status."}}</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1780417675543</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>2026-06-02T16:21:18.792887+00:00</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:27:56.511989+00:00</t>
+        </is>
+      </c>
+      <c r="R93" t="n">
+        <v>800</v>
+      </c>
       <c r="T93" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:13.736955+00:00</t>
@@ -5646,7 +5667,7 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>2026-06-02T16:21:18.840425+00:00</t>
+          <t>2026-06-02T16:27:56.556655+00:00</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5679,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5681,16 +5702,37 @@
           <t>0 STATE ROAD 54, NEW PORT RICHEY, FL 34653</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>{"total_amount": 437.0, "services": [{"name": "Land Survey (Boundary)", "description": "Base negotiated survey rate for Hengesbach and Hengesbach, PA (OLD_TITLE tier, 9 prior orders, management-agreed rate)", "amount": 300.0}, {"name": "Lot Size Complexity Upcharge (0.51\u20131.00 ac)", "description": "Property is 0.61 acres, falling within the 0.51\u20131.00 ac range; upcharge applied per pricing guidelines", "amount": 137.0}], "pricing_reasoning": "The client has a management-agreed base rate of $300.00. The property is 0.61 acres, which triggers the 0.51\u20131.00 ac complexity upcharge of $137.00. The legal description is metes-and-bounds in nature (commencing from a section corner with bearings and distances), but as a vacant parcel in Pasco County with no pool, waterfront, or heavy vegetation indicators noted, and FEMA Zone X (no flood zone premium), no additional upcharges beyond lot size are warranted. No EC is requested. Total is $437.00.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_ORDER: Order 1000279824 flagged as a possible duplicate \u2014 same Folio/MLS (16-26-16-0000-01600-0030), same county and service type (Land Survey Only, Pasco County, vacant parcel). Human review required before proceeding to avoid redundant field work or double-billing.", "HOLD_STATUS: Order notes indicate this order is currently on hold with special pricing applied and several key details missing. Confirm with management that the $300.00 negotiated rate and scope are finalized before invoicing.", "METES_AND_BOUNDS: Legal description uses bearings and distances from a section corner; metes-and-bounds upcharge of $100.00 was considered but not applied as the lot size upcharge is the primary complexity driver and the parcel appears straightforward and vacant. Revisit if field crew reports additional complexity.", "INCOMPLETE_LEGAL_DESCRIPTION: The legal description in the order appears truncated (ends mid-sentence at 'ALONG THE N'). Full legal should be confirmed before survey commences."]}</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 201801311051305246, "created_at": "2026-03-05T18:49:36", "customer_email": "traci@naturecoastlaw.com", "customer_id": 201801311101215230, "customer_name": "Traci Gaughan", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12101C0354G\nZONE: X\nEFF: 06/05/2020", "invoiced": false, "order_id": 1000279820, "paid": false, "property_address": "0 STATE ROAD 54", "property_city": "NEW PORT RICHEY", "property_county": "PASCO COUNTY", "property_lat": "28.2170163", "property_lng": "-82.6967297", "property_state": "FL", "property_zip": "34653", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-06T14:54:41"}, "success": true, "order_id": "1000279820", "customer_email": "traci@naturecoastlaw.com", "service_type": "Land Survey Only", "county": "", "property_address": "0 STATE ROAD 54", "customer_name": "Hengesbach and Hengesbach, PA"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Hengesbach and Hengesbach, PA", "confidence": "MEDIUM"}, "client_email": {"value": "traci@naturecoastlaw.com", "confidence": "HIGH"}, "property_address": {"value": "0 STATE ROAD 54, NEW PORT RICHEY, FL 34653", "confidence": "HIGH"}, "property_county": {"value": "PASCO COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; specific survey type (boundary, topo, etc.) not clarified"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; address is '0 STATE ROAD 54' suggesting vacant land or unaddressed parcel \u2014 no structures, pool, or improvements confirmed"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: FTF order data lists 'Traci Gaughan' as customer_name but outer payload lists 'Hengesbach and Hengesbach, PA' \u2014 needs human clarification on billing entity", "Specific survey type not defined (boundary, topographic, ALTA, etc.)", "Lot size / acreage unknown \u2014 county appraiser data unavailable", "Legal description not provided", "No parcel ID or folio number provided", "Property appears to be vacant land (address '0 STATE ROAD 54') \u2014 ownership and parcel details unconfirmed", "Reason for 'On Hold' status not specified", "Special pricing amount or agreement not documented", "No fieldwork date scheduled", "No matching emails found to provide additional context"], "summary": "B2B land survey order for what appears to be a vacant parcel at 0 State Road 54, New Port Richey, FL (Pasco County), placed on behalf of Hengesbach and Hengesbach, PA, currently on hold with special pricing applied and several key details missing."}}</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1780417696266</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>2026-06-02T16:21:30.592811+00:00</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:28:16.727826+00:00</t>
+        </is>
+      </c>
+      <c r="R94" t="n">
+        <v>437</v>
+      </c>
       <c r="T94" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:13.785300+00:00</t>
@@ -5698,7 +5740,7 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>2026-06-02T16:21:30.639273+00:00</t>
+          <t>2026-06-02T16:28:16.770981+00:00</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5752,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5725,13 +5767,44 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Buchalter </t>
+          <t>Robert Buchalter</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>6981 LIONS HEAD LN</t>
-        </is>
+          <t>6981 Lions Head Ln, Boca Raton, FL 33496</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>{"total_amount": 562.0, "services": [{"name": "Land Survey (Boundary)", "description": "Residential boundary/land survey for LOT 763, St. Andrews Country Club Plat No. 14, Palm Beach County. Negotiated flat rate agreed upon by management for client Robert Buchalter.", "amount": 500.0}, {"name": "Lot Size Complexity Upcharge (0.31\u20130.50 ac)", "description": "Property is 0.34 acres, falling in the 0.31\u20130.50 ac range. Standard upcharge applied per complexity schedule to reflect additional field time relative to a sub-0.30 ac lot.", "amount": 62.0}], "pricing_reasoning": "Management pre-negotiated a $500.00 base survey rate for this individual client, which serves as the floor for the land survey line item. The lot is 0.34 acres, placing it in the 0.31\u20130.50 ac complexity band (+$62.00). No EC is requested and FEMA Zone X carries no flood certificate requirement. The legal description is a platted lot (not metes and bounds), Palm Beach County carries no remote mobilization premium, and there are no indicators of pool, waterfront canal, or heavy vegetation from the available data, so no additional upcharges apply.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_ORDER: Order 1000278649 covers the same property \u2014 6981 Lions Head Lane, Palm Beach County \u2014 same service (Land Survey Only), same coordinates (26.4175877, -80.1541441), and same Folio/MLS (00424633110007630). Human review required before proceeding to avoid double-billing or duplicate field dispatch.", "ORDER_NOTES: Original order was marked paid with special pricing applied but was missing lot size, legal description, and property feature details at time of entry. Verify that the negotiated $500.00 rate on this order is consistent with what was collected on any prior paid order tied to this property.", "NO_EC_REQUESTED: Property is in FEMA Zone X \u2014 no Elevation Certificate required or ordered."]}</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202603041813155189, "created_at": "2026-03-04T18:14:07", "customer_email": "rb@cgpre.com", "customer_id": 202603041813156173, "customer_name": "Robert Buchalter", "customer_type": "individual", "delivered_at": "2026-03-12T18:43:35", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0967F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000279727, "paid": true, "property_address": "6981 LIONS HEAD LN", "property_city": "BOCA RATON", "property_county": "PALM BEACH COUNTY", "property_lat": "26.4175877", "property_lng": "-80.1541441", "property_state": "FL", "property_zip": "33496", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-03-12T18:43:35"}, "success": true, "order_id": "1000279727", "customer_email": "rb@cgpre.com", "service_type": "Land Survey Only", "county": "", "property_address": "6981 LIONS HEAD LN", "customer_name": "Robert Buchalter "}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Robert Buchalter", "confidence": "HIGH"}, "client_email": {"value": "rb@cgpre.com", "confidence": "HIGH"}, "property_address": {"value": "6981 Lions Head Ln, Boca Raton, FL 33496", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; special_pricing flag is true which may indicate a negotiated or discounted rate"}, "special_requirements": {"value": "Special pricing applied", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "residential", "confidence": "MEDIUM"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, driveway, etc.)", "Fieldwork date not recorded (fieldwork_at is null)", "Client type is 'individual' but email domain 'cgpre.com' suggests possible business affiliation \u2014 verify client tier", "Special pricing reason not documented \u2014 needs human review", "Invoice not yet generated despite order being delivered and paid"], "summary": "Delivered land survey order for residential client Robert Buchalter at 6981 Lions Head Ln, Boca Raton FL (Palm Beach County), marked paid with special pricing applied but missing lot size, legal description, and property feature details."}}</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1780417696266</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:26:52.164795+00:00</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:28:35.457023+00:00</t>
+        </is>
+      </c>
+      <c r="R95" t="n">
+        <v>562</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -5740,7 +5813,7 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:13.832382+00:00</t>
+          <t>2026-06-02T16:28:35.499906+00:00</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5825,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5772,7 +5845,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>15288 73RD ST N</t>
+          <t>15288 73RD ST N, LOXAHATCHEE, FL 33470</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508201335558708, "created_at": "2026-03-04T15:02:09", "customer_email": "xpertawning@aol.com", "customer_id": 202508201335558815, "customer_name": "Candace Jones", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0345F \nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000279688, "paid": false, "property_address": "15288 73RD ST N", "property_city": "LOXAHATCHEE", "property_county": "Palm Beach County", "property_lat": "26.7844851", "property_lng": "-80.28286849999999", "property_state": "FL", "property_zip": "33470", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-06T15:25:19"}, "success": true, "order_id": "1000279688", "customer_email": "xpertawning@aol.com", "service_type": "Land Survey Only", "county": "", "property_address": "15288 73RD ST N", "customer_name": "Candace Jones"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Candace Jones", "confidence": "HIGH"}, "client_email": {"value": "xpertawning@aol.com", "confidence": "HIGH"}, "property_address": {"value": "15288 73RD ST N, LOXAHATCHEE, FL 33470", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 county appraiser unavailable and no supplemental source", "Structure square footage unknown", "Property features unknown (pool, shed, outbuildings, driveway, etc.)", "Reason for On Hold status not documented", "Fieldwork date not yet scheduled", "Invoice has not been sent and order has not been paid \u2014 pricing needs to be finalized given special_pricing flag", "No customer profile data returned from FTF customer lookup"], "summary": "Individual client Candace Jones has placed a Land Survey Only order for a residential property at 15288 73RD ST N, Loxahatchee, FL (Palm Beach County), currently on hold with special pricing applied and no fieldwork or invoicing completed."}}</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:27:02.461418+00:00</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
@@ -5782,7 +5865,7 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:13.878980+00:00</t>
+          <t>2026-06-02T16:27:02.507776+00:00</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5877,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5809,12 +5892,22 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ASU Enterprises</t>
+          <t>ASU Enterprises (Matt Lanman)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>11 YACHT CLUB PL</t>
+          <t>11 Yacht Club Pl, Jupiter, FL 33469</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202601121924554628, "created_at": "2026-02-20T21:26:08", "customer_email": "matt@asuenterprises.com", "customer_id": 202601121925254521, "customer_name": "Matt  Lanman", "customer_type": "b2b", "delivered_at": "2026-02-20T22:04:37", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0178G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000279100, "paid": true, "property_address": "11 YACHT CLUB PL", "property_city": "JUPITER", "property_county": "PALM BEACH COUNTY", "property_lat": "26.9555132", "property_lng": "-80.110298", "property_state": "FL", "property_zip": "33469", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-02-20T22:04:37"}, "success": true, "order_id": "1000279100", "customer_email": "matt@asuenterprises.com", "service_type": "Land Survey Only", "county": "", "property_address": "11 YACHT CLUB PL", "customer_name": "ASU Enterprises"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "ASU Enterprises (Matt Lanman)", "confidence": "HIGH"}, "client_email": {"value": "matt@asuenterprises.com", "confidence": "HIGH"}, "property_address": {"value": "11 Yacht Club Pl, Jupiter, FL 33469", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing applied", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, fences, driveways) unknown", "Reason for special pricing not documented", "No invoice amount recorded \u2014 order marked paid but invoiced=false; billing details need reconciliation", "Fieldwork date not set"], "summary": "B2B land survey order for ASU Enterprises at 11 Yacht Club Pl, Jupiter, FL (Palm Beach County) \u2014 delivered same day with special pricing applied, but property details and billing reconciliation require human review."}}</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:27:11.447141+00:00</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
@@ -5824,7 +5917,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:13.926367+00:00</t>
+          <t>2026-06-02T16:27:11.489913+00:00</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5929,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5856,7 +5949,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>14000 N MIAMI AVE</t>
+          <t>14000 N Miami Ave, Miami, FL 33168</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202602191413467509, "created_at": "2026-02-19T14:14:44", "customer_email": "Rambuilders01@yahoo.com", "customer_id": 202602191413468538, "customer_name": "Mark Ramirez", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0139L\nZONE: AE\nELEV: 07 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000278966, "paid": true, "property_address": "14000 N MIAMI AVE", "property_city": "MIAMI", "property_county": "Miami-Dade County", "property_lat": "25.9035903", "property_lng": "-80.1997633", "property_state": "FL", "property_zip": "33168", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-02-20T18:31:09"}, "success": true, "order_id": "1000278966", "customer_email": "Rambuilders01@yahoo.com", "service_type": "CAD", "county": "", "property_address": "14000 N MIAMI AVE", "customer_name": "Mark Ramirez"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Mark Ramirez", "confidence": "HIGH"}, "client_email": {"value": "Rambuilders01@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "14000 N Miami Ave, Miami, FL 33168", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type is listed as CAD; no additional services specified. Elevation certificate is explicitly false."}, "special_requirements": {"value": "Special pricing applied. Order is currently On Hold (status code 11). Flood zone data present: 12086C0139L, Zone AE, Elev 07 FT, Eff 09/11/2009.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no aerial or email data provided."}, "client_tier": {"value": "residential", "confidence": "MEDIUM", "notes": "Customer type is listed as 'individual', but email domain 'Rambuilders01' suggests possible contractor or builder; classified residential pending confirmation."}, "urgency": {"value": "normal", "confidence": "MEDIUM", "notes": "No rush indicators present; order is On Hold which may suggest a delay rather than urgency."}, "source_of_truth": "ftf_only", "gaps": ["Lot size not available \u2014 needs county appraiser or legal document lookup", "Legal description not available \u2014 needs county appraiser or title document", "Structure square footage unknown \u2014 no appraiser or aerial data", "Property features (pool, shed, structures) unknown \u2014 no aerial or appraiser data", "County appraiser data unavailable \u2014 county field was blank in FTF export despite being present in order data", "Client type ambiguous \u2014 'Rambuilders01' email suggests possible builder/contractor; confirm if B2B pricing applies despite 'individual' classification", "Reason for On Hold status unknown \u2014 needs human review", "No matching emails found \u2014 no supplemental communication context available", "Fieldwork and delivery dates not set \u2014 timeline unclear"], "summary": "CAD order for individual client Mark Ramirez at 14000 N Miami Ave, Miami, FL 33168 (Zone AE flood zone), currently On Hold with special pricing applied and no fieldwork or delivery dates scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:27:25.444891+00:00</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -5866,7 +5969,7 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.016992+00:00</t>
+          <t>2026-06-02T16:27:25.487951+00:00</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5981,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5898,7 +6001,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>20335 W. COUNTRY CLUB DR. AVENTURA, FLORIDA. 33180.</t>
+          <t>20335 W. Country Club Dr., Aventura, FL 33180</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202602190310279473, "created_at": "2026-02-19T03:10:28", "customer_email": "bnschafer1@yahoo.com", "customer_id": 202602190310279656, "customer_name": "Barbara Schafer", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": null, "invoiced": false, "order_id": 1000278960, "paid": false, "property_address": "20335 W. COUNTRY CLUB DR. AVENTURA, FLORIDA. 33180.", "property_city": "AVENTURA, FLORIDA", "property_county": "Miami-Dade County", "property_lat": "25.9630163", "property_lng": "-80.13796959999999", "property_state": "FLORIDA", "property_zip": "", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-06T15:12:24"}, "success": true, "order_id": "1000278960", "customer_email": "bnschafer1@yahoo.com", "service_type": "Land Survey Only", "county": "", "property_address": "20335 W. COUNTRY CLUB DR. AVENTURA, FLORIDA. 33180.", "customer_name": "Barbara Schafer"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Barbara Schafer", "confidence": "HIGH"}, "client_email": {"value": "bnschafer1@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "20335 W. Country Club Dr., Aventura, FL 33180", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in FTF order data."}, "special_requirements": {"value": "None noted", "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no emails or attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Property ZIP code is missing from FTF data", "Lot size unknown \u2014 county appraiser unavailable", "Legal description unknown \u2014 county appraiser unavailable", "Structure square footage unknown", "Property features (pool, shed, driveway, etc.) unknown \u2014 no aerial or appraiser data", "Special requirements or client notes not provided", "No matching emails found to supplement order details", "Order is currently 'On Hold' \u2014 reason for hold not documented", "No fieldwork date scheduled", "No invoice or payment information established"], "summary": "Individual residential client Barbara Schafer has placed a Land Survey Only order for a property at 20335 W. Country Club Dr., Aventura, FL 33180 (Miami-Dade County), currently on hold with no fieldwork scheduled, invoice, or property detail data available."}}</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:27:35.024895+00:00</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
@@ -5908,7 +6021,7 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.065276+00:00</t>
+          <t>2026-06-02T16:27:35.067536+00:00</t>
         </is>
       </c>
     </row>
@@ -17669,6 +17782,48 @@
       <c r="U379" t="inlineStr">
         <is>
           <t>2026-06-02T16:20:33.678274+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>1000245231</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>invoice_needed</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Land Survey Only</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>seattlefootdoctor@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>MIKHAIL BURAKOVSKIY AND ALLA BURAKOVSKIY</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>8548 GRAND PRIX LN</t>
+        </is>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:26:42.131098+00:00</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:26:42.131098+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -5825,7 +5825,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5848,16 +5848,37 @@
           <t>15288 73RD ST N, LOXAHATCHEE, FL 33470</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>{"total_amount": 1025.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for residential property at 15288 73RD ST N, Loxahatchee, FL 33470. Negotiated base rate agreed upon by management for individual client Candace Jones.", "amount": 750.0}, {"name": "Acreage Complexity Upcharge (1.01\u20132.00 ac)", "description": "Lot size is 1.47 acres per database, confirmed by metes-and-bounds legal description (S 269 ft \u00d7 W 239 ft = ~1.48 ac). Falls squarely in the 1.01\u20132.00 ac tier, requiring extended field traversal and additional monument recovery in a rural Loxahatchee setting.", "amount": 275.0}], "pricing_reasoning": "The negotiated base rate of $750.00 is applied per management agreement for individual client Candace Jones. The property is 1.47 acres, placing it in the 1.01\u20132.00 ac complexity tier warranting a $275.00 upcharge. No EC is ordered (FEMA Zone X \u2014 no flood zone certification required), no pool or waterfront features are noted, the property is in Palm Beach County (no Monroe remote mobilisation), and no topographic service was requested. The metes-and-bounds description was considered but is intrinsic to the acreage complexity already captured in the lot-size upcharge rather than a standalone addition, as the legal is a straightforward aliquot-style rectangular metes call rather than a complex irregular boundary.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_ORDER: Order 1000169953 \u2014 same address (15288 73RD ST N, Palm Beach County), same service (Land Survey Only), same folio 00414230000005550 \u2014 flagged for human review before fieldwork proceeds.", "DUPLICATE_ORDER: Order 1000270173 \u2014 same address (15288 73RD ST N, Palm Beach County), same service (Land Survey Only), same folio 00414230000005550 \u2014 flagged for human review before fieldwork proceeds.", "ORDER ON HOLD: Per order notes, this order is currently on hold with special pricing applied and no fieldwork or invoicing completed. Confirm hold release with management before dispatching crew.", "EASEMENT NOTE: Legal description references an easement for road and drainage purposes to Indian Trail Water Control District over the East 30 ft, North 30 ft \u2014 surveyor should research and depict easement extents on the final sketch."]}</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202508201335558708, "created_at": "2026-03-04T15:02:09", "customer_email": "xpertawning@aol.com", "customer_id": 202508201335558815, "customer_name": "Candace Jones", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0345F \nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000279688, "paid": false, "property_address": "15288 73RD ST N", "property_city": "LOXAHATCHEE", "property_county": "Palm Beach County", "property_lat": "26.7844851", "property_lng": "-80.28286849999999", "property_state": "FL", "property_zip": "33470", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-06T15:25:19"}, "success": true, "order_id": "1000279688", "customer_email": "xpertawning@aol.com", "service_type": "Land Survey Only", "county": "", "property_address": "15288 73RD ST N", "customer_name": "Candace Jones"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Candace Jones", "confidence": "HIGH"}, "client_email": {"value": "xpertawning@aol.com", "confidence": "HIGH"}, "property_address": {"value": "15288 73RD ST N, LOXAHATCHEE, FL 33470", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 county appraiser unavailable and no supplemental source", "Structure square footage unknown", "Property features unknown (pool, shed, outbuildings, driveway, etc.)", "Reason for On Hold status not documented", "Fieldwork date not yet scheduled", "Invoice has not been sent and order has not been paid \u2014 pricing needs to be finalized given special_pricing flag", "No customer profile data returned from FTF customer lookup"], "summary": "Individual client Candace Jones has placed a Land Survey Only order for a residential property at 15288 73RD ST N, Loxahatchee, FL (Palm Beach County), currently on hold with special pricing applied and no fieldwork or invoicing completed."}}</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1780417917913</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>2026-06-02T16:27:02.461418+00:00</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:36:40.985615+00:00</t>
+        </is>
+      </c>
+      <c r="R96" t="n">
+        <v>1025</v>
+      </c>
       <c r="T96" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:13.878980+00:00</t>
@@ -5865,7 +5886,7 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>2026-06-02T16:27:02.507776+00:00</t>
+          <t>2026-06-02T16:36:41.031882+00:00</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5898,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5900,16 +5921,37 @@
           <t>11 Yacht Club Pl, Jupiter, FL 33469</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>{"total_amount": 475.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for Lot 3, Replat of Part Plat of Tequesta, 11 Yacht Club Pl, Jupiter, FL \u2014 Palm Beach County. 0.28 acres, FEMA Zone X (no EC required). Negotiated rate applied per management agreement for ASU Enterprises (OLD_TITLE tier).", "amount": 475.0}], "pricing_reasoning": "The negotiated base rate of $475.00 is applied per management's agreed pricing for ASU Enterprises. The lot is 0.28 acres, which falls within the base tier (\u22640.30 ac) and does not trigger a lot-size upcharge. The legal description is a straightforward platted lot reference (not metes and bounds), FEMA Zone X requires no Elevation Certificate, the property is in Palm Beach County (no Monroe County surcharge), and no pool, waterfront canal, or heavy vegetation complexity is indicated in the available data \u2014 so no upcharges are warranted. No EC is ordered or needed.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "Three possible duplicate orders exist for the identical property and service type (Orders 1000090700, 1000277079, and 1000278684 \u2014 all at 11 Yacht Club Pl, Palm Beach County, Land Survey Only, sharing the same coordinates and Folio/MLS 60424026020000030). Human review is required to determine whether this is a legitimate re-order, a billing reconciliation issue, or an accidental duplicate before invoicing or dispatching field crews. Additionally, order notes explicitly state that 'property details and billing reconciliation require human review,' and the client shows 0 prior orders despite being flagged as an established OLD_TITLE tier company, which is anomalous.", "flags": ["DUPLICATE_WARNING: Order 1000090700 \u2014 same address (11 Yacht Club Pl, Palm Beach County), same service (Land Survey Only), coordinates (26.9555423, -80.1102732) \u2014 confirm with management before proceeding.", "DUPLICATE_WARNING: Order 1000277079 \u2014 same address, same service, same Folio/MLS (60424026020000030), coordinates (26.9555132, -80.110298) \u2014 possible duplicate or re-order.", "DUPLICATE_WARNING: Order 1000278684 \u2014 same address, same service, same Folio/MLS (60424026020000030), coordinates (26.9555132, -80.110298) \u2014 possible duplicate or re-order.", "ORDER_NOTES_ALERT: Notes indicate same-day delivery with special pricing applied and that billing reconciliation requires human review \u2014 do not auto-invoice without manager sign-off.", "CLIENT_ANOMALY: ASU Enterprises flagged as OLD_TITLE tier but shows 0 prior orders \u2014 verify client account history and tier assignment before finalizing."]}</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202601121924554628, "created_at": "2026-02-20T21:26:08", "customer_email": "matt@asuenterprises.com", "customer_id": 202601121925254521, "customer_name": "Matt  Lanman", "customer_type": "b2b", "delivered_at": "2026-02-20T22:04:37", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0178G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000279100, "paid": true, "property_address": "11 YACHT CLUB PL", "property_city": "JUPITER", "property_county": "PALM BEACH COUNTY", "property_lat": "26.9555132", "property_lng": "-80.110298", "property_state": "FL", "property_zip": "33469", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-02-20T22:04:37"}, "success": true, "order_id": "1000279100", "customer_email": "matt@asuenterprises.com", "service_type": "Land Survey Only", "county": "", "property_address": "11 YACHT CLUB PL", "customer_name": "ASU Enterprises"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "ASU Enterprises (Matt Lanman)", "confidence": "HIGH"}, "client_email": {"value": "matt@asuenterprises.com", "confidence": "HIGH"}, "property_address": {"value": "11 Yacht Club Pl, Jupiter, FL 33469", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing applied", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, fences, driveways) unknown", "Reason for special pricing not documented", "No invoice amount recorded \u2014 order marked paid but invoiced=false; billing details need reconciliation", "Fieldwork date not set"], "summary": "B2B land survey order for ASU Enterprises at 11 Yacht Club Pl, Jupiter, FL (Palm Beach County) \u2014 delivered same day with special pricing applied, but property details and billing reconciliation require human review."}}</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1780418221802</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>2026-06-02T16:27:11.447141+00:00</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:37:02.590174+00:00</t>
+        </is>
+      </c>
+      <c r="R97" t="n">
+        <v>475</v>
+      </c>
       <c r="T97" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:13.926367+00:00</t>
@@ -5917,7 +5959,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>2026-06-02T16:27:11.489913+00:00</t>
+          <t>2026-06-02T16:37:02.636486+00:00</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5971,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5952,16 +5994,37 @@
           <t>14000 N Miami Ave, Miami, FL 33168</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>{"total_amount": 862.0, "services": [{"name": "CAD / Land Survey", "description": "Base boundary survey rate per management-agreed pricing for individual client Mark Ramirez at 14000 N Miami Ave, Miami-Dade County.", "amount": 450.0}, {"name": "Elevation Certificate", "description": "Standard EC for FEMA Flood Zone AE (non-coastal VE), fixed rate per pricing guidelines.", "amount": 275.0}, {"name": "Lot Size Complexity Upcharge (0.51\u20131.00 ac)", "description": "Property is 0.72 acres, falling in the 0.51\u20131.00 ac tier. Upcharge applied to reflect additional fieldwork scope.", "amount": 137.0}], "pricing_reasoning": "The service is a CAD/boundary survey combined with an Elevation Certificate, warranted by the AE flood zone designation. The base rate of $450.00 is locked per management agreement for this individual client. The lot at 0.72 acres triggers the 0.51\u20131.00 ac complexity upcharge of $137.00, and the legal description \u2014 while moderately complex (partial lots with metes-style references) \u2014 does not clearly rise to a standalone metes-and-bounds upcharge absent a full deed review, so that is not applied. Zone AE (not VE) means no coastal EC surcharge applies.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000275536 at 14000 N Miami Ave, Miami-Dade County shares the same coordinates (25.9035903, -80.1997633) and Folio/MLS (3021240111010) with service 'Land Survey and Elevation'. Human review required to confirm this CAD order is not a duplicate or re-issue of that prior order before finalizing invoice.", "LEGAL_DESC_NOTE: Legal description references multiple partial lots (S 15 ft of Lot 89, Lot 88 less S 22.05 ft, and N 8.5 ft of S 22.5 ft of Lot 8) from Biscayne Gardens Sec H Part 2 \u2014 moderately fragmented. If fieldwork reveals true metes-and-bounds complexity requiring extended boundary research, a +$100.00 upcharge may be warranted and should be revisited.", "ON_HOLD_NOTE: Order is currently On Hold per order notes. No fieldwork or delivery dates are scheduled. Pricing is proposed pending hold resolution.", "CAD_ONLY_NOTE: Order is flagged as CAD service type. If this is a drafting/CAD-only order (no new fieldwork), base rate and complexity upcharges should be confirmed with management as field-based upcharges may not apply."]}</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202602191413467509, "created_at": "2026-02-19T14:14:44", "customer_email": "Rambuilders01@yahoo.com", "customer_id": 202602191413468538, "customer_name": "Mark Ramirez", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0139L\nZONE: AE\nELEV: 07 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000278966, "paid": true, "property_address": "14000 N MIAMI AVE", "property_city": "MIAMI", "property_county": "Miami-Dade County", "property_lat": "25.9035903", "property_lng": "-80.1997633", "property_state": "FL", "property_zip": "33168", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-02-20T18:31:09"}, "success": true, "order_id": "1000278966", "customer_email": "Rambuilders01@yahoo.com", "service_type": "CAD", "county": "", "property_address": "14000 N MIAMI AVE", "customer_name": "Mark Ramirez"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Mark Ramirez", "confidence": "HIGH"}, "client_email": {"value": "Rambuilders01@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "14000 N Miami Ave, Miami, FL 33168", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type is listed as CAD; no additional services specified. Elevation certificate is explicitly false."}, "special_requirements": {"value": "Special pricing applied. Order is currently On Hold (status code 11). Flood zone data present: 12086C0139L, Zone AE, Elev 07 FT, Eff 09/11/2009.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no aerial or email data provided."}, "client_tier": {"value": "residential", "confidence": "MEDIUM", "notes": "Customer type is listed as 'individual', but email domain 'Rambuilders01' suggests possible contractor or builder; classified residential pending confirmation."}, "urgency": {"value": "normal", "confidence": "MEDIUM", "notes": "No rush indicators present; order is On Hold which may suggest a delay rather than urgency."}, "source_of_truth": "ftf_only", "gaps": ["Lot size not available \u2014 needs county appraiser or legal document lookup", "Legal description not available \u2014 needs county appraiser or title document", "Structure square footage unknown \u2014 no appraiser or aerial data", "Property features (pool, shed, structures) unknown \u2014 no aerial or appraiser data", "County appraiser data unavailable \u2014 county field was blank in FTF export despite being present in order data", "Client type ambiguous \u2014 'Rambuilders01' email suggests possible builder/contractor; confirm if B2B pricing applies despite 'individual' classification", "Reason for On Hold status unknown \u2014 needs human review", "No matching emails found \u2014 no supplemental communication context available", "Fieldwork and delivery dates not set \u2014 timeline unclear"], "summary": "CAD order for individual client Mark Ramirez at 14000 N Miami Ave, Miami, FL 33168 (Zone AE flood zone), currently On Hold with special pricing applied and no fieldwork or delivery dates scheduled."}}</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1780418242986</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>2026-06-02T16:27:25.444891+00:00</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:37:23.792362+00:00</t>
+        </is>
+      </c>
+      <c r="R98" t="n">
+        <v>862</v>
+      </c>
       <c r="T98" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.016992+00:00</t>
@@ -5969,7 +6032,7 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>2026-06-02T16:27:25.487951+00:00</t>
+          <t>2026-06-02T16:37:23.837662+00:00</t>
         </is>
       </c>
     </row>
@@ -5981,7 +6044,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6004,16 +6067,37 @@
           <t>20335 W. Country Club Dr., Aventura, FL 33180</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "The property at 20335 W. Country Club Dr., Aventura, FL is listed at 7.10 acres, which exceeds the 5.00-acre threshold defined in the pricing guidelines. Per policy, any lot greater than 5.00 acres must be escalated regardless of service type and cannot be priced by the automated system. Additionally, a possible duplicate order (1000280688) exists for a nearby address at 20301 W. Country Club Dr. with the same Folio/MLS number, which requires human review to confirm whether these are the same parcel or distinct properties before any fieldwork or invoicing proceeds.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "Lot size of 7.10 acres exceeds the 5.00-acre pricing ceiling. Per guidelines, all service types for lots greater than 5.00 acres must be escalated to management for manual quoting. Additionally, a suspected duplicate order (1000280688) references the same Folio/MLS (2812340540670) at a nearby address (20301 W. Country Club Dr., Miami-Dade County), raising the possibility that both orders reference the same parcel. Management must (1) verify whether 20335 and 20301 W. Country Club Dr. are the same legal parcel or distinct, (2) confirm lot size and legal description via county records, and (3) provide a custom quote appropriate for a 7+ acre residential or mixed-use parcel in Miami-Dade County.", "flags": ["ESCALATE: Lot size 7.10 acres exceeds 5.00-acre automated pricing limit. Management quote required.", "DUPLICATE SUSPECTED: Order 1000280688 (20301 W. Country Club Dr., Miami-Dade) shares Folio/MLS 2812340540670 with this order. Human review required to determine if these are the same parcel.", "FEMA flood zone is unknown. If located in a flood zone, an Elevation Certificate may be required \u2014 confirm at time of management review.", "No legal description on file. Must be obtained before fieldwork can be scheduled.", "Order is currently on hold with no fieldwork scheduled or property detail data available."]}</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202602190310279473, "created_at": "2026-02-19T03:10:28", "customer_email": "bnschafer1@yahoo.com", "customer_id": 202602190310279656, "customer_name": "Barbara Schafer", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": null, "invoiced": false, "order_id": 1000278960, "paid": false, "property_address": "20335 W. COUNTRY CLUB DR. AVENTURA, FLORIDA. 33180.", "property_city": "AVENTURA, FLORIDA", "property_county": "Miami-Dade County", "property_lat": "25.9630163", "property_lng": "-80.13796959999999", "property_state": "FLORIDA", "property_zip": "", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-06T15:12:24"}, "success": true, "order_id": "1000278960", "customer_email": "bnschafer1@yahoo.com", "service_type": "Land Survey Only", "county": "", "property_address": "20335 W. COUNTRY CLUB DR. AVENTURA, FLORIDA. 33180.", "customer_name": "Barbara Schafer"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Barbara Schafer", "confidence": "HIGH"}, "client_email": {"value": "bnschafer1@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "20335 W. Country Club Dr., Aventura, FL 33180", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in FTF order data."}, "special_requirements": {"value": "None noted", "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no emails or attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Property ZIP code is missing from FTF data", "Lot size unknown \u2014 county appraiser unavailable", "Legal description unknown \u2014 county appraiser unavailable", "Structure square footage unknown", "Property features (pool, shed, driveway, etc.) unknown \u2014 no aerial or appraiser data", "Special requirements or client notes not provided", "No matching emails found to supplement order details", "Order is currently 'On Hold' \u2014 reason for hold not documented", "No fieldwork date scheduled", "No invoice or payment information established"], "summary": "Individual residential client Barbara Schafer has placed a Land Survey Only order for a property at 20335 W. Country Club Dr., Aventura, FL 33180 (Miami-Dade County), currently on hold with no fieldwork scheduled, invoice, or property detail data available."}}</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1780418260414</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>2026-06-02T16:27:35.024895+00:00</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:37:40.981695+00:00</t>
+        </is>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
       <c r="T99" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.065276+00:00</t>
@@ -6021,7 +6105,7 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>2026-06-02T16:27:35.067536+00:00</t>
+          <t>2026-06-02T16:37:41.028692+00:00</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6117,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6053,7 +6137,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>770 DOVER ST</t>
+          <t>770 Dover St, Boca Raton, FL 33487</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202602182034031192, "created_at": "2026-02-18T20:36:16", "customer_email": "office@smcfl.com", "customer_id": 202602182034264579, "customer_name": "Catharina Machado", "customer_type": "b2b", "delivered_at": "2026-02-20T21:37:44", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0987G\nZONE: AE\nELEV: 07 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000278940, "paid": true, "property_address": "770 DOVER ST", "property_city": "BOCA RATON", "property_county": "PALM BEACH COUNTY", "property_lat": "26.4072138", "property_lng": "-80.0726626", "property_state": "FL", "property_zip": "33487", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-02-20T21:37:44"}, "success": true, "order_id": "1000278940", "customer_email": "office@smcfl.com", "service_type": "Land Survey Only", "county": "", "property_address": "770 DOVER ST", "customer_name": "Seaside Marine Construction"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Seaside Marine Construction", "confidence": "HIGH"}, "client_email": {"value": "office@smcfl.com", "confidence": "HIGH"}, "property_address": {"value": "770 Dover St, Boca Raton, FL 33487", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing applied; flood zone AE at elevation 7 ft (FIRM panel 12099C0987G, effective 12/20/2024)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, driveways, structures) unknown \u2014 no appraiser or aerial data available", "Fieldwork date not yet scheduled (fieldwork_at is null)", "Invoice has not been sent (invoiced: false) \u2014 pricing details not confirmed despite special_pricing flag", "No county provided in top-level FTF fields, though property_county is present in nested data"], "summary": "B2B land survey order for Seaside Marine Construction at 770 Dover St, Boca Raton FL (Palm Beach County), located in FEMA flood zone AE, with special pricing applied and no elevation certificate requested."}}</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:35:41.102524+00:00</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
@@ -6063,7 +6157,7 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.113381+00:00</t>
+          <t>2026-06-02T16:35:41.146994+00:00</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6169,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6090,12 +6184,22 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Randy B Realty</t>
+          <t>Randy Beth Breitman / Randy B Realty</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>811 N OLIVE AVE</t>
+          <t>811 N Olive Ave, West Palm Beach, FL 33401</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510011504100630, "created_at": "2026-02-18T20:25:20", "customer_email": "randybeth@randybrealty.com", "customer_id": 202510011504434287, "customer_name": "Randy Beth Breitman", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0581G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000278938, "paid": true, "property_address": "811 N OLIVE AVE", "property_city": "WEST PALM BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.7201875", "property_lng": "-80.0520531", "property_state": "FL", "property_zip": "33401", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-03T16:12:22"}, "success": true, "order_id": "1000278938", "customer_email": "randybeth@randybrealty.com", "service_type": "CAD", "county": "", "property_address": "811 N OLIVE AVE", "customer_name": "Randy B Realty"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Randy Beth Breitman / Randy B Realty", "confidence": "HIGH"}, "client_email": {"value": "randybeth@randybrealty.com", "confidence": "HIGH"}, "property_address": {"value": "811 N Olive Ave, West Palm Beach, FL 33401", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "MEDIUM", "notes": "Service type is listed as CAD \u2014 likely CAD drafting of a survey; specific deliverable scope (boundary, topo, ALTA, etc.) is not defined and needs clarification"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 no appraiser data, no emails, no aerial info provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["CAD service scope not defined \u2014 boundary, topo, ALTA, or other?", "Reason for On Hold status unknown", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, fences, etc.) unknown", "No fieldwork date scheduled", "No estimate sent \u2014 pricing details unclear beyond 'special pricing'", "County property appraiser data unavailable", "No matching emails found to clarify scope or requirements"], "summary": "B2B CAD order for Randy Beth Breitman at 811 N Olive Ave, West Palm Beach FL 33401 (Palm Beach County) is currently On Hold with special pricing applied, but the specific CAD deliverable scope and property details are undefined and require human follow-up."}}</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:35:51.046380+00:00</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
@@ -6105,7 +6209,7 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.161529+00:00</t>
+          <t>2026-06-02T16:35:51.092313+00:00</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6221,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6132,12 +6236,22 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Stuart Architecture</t>
+          <t>Stuart Anson</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2729 NW 48TH ST</t>
+          <t>2729 NW 48TH ST, MIAMI, FL 33142</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202602161958085167, "created_at": "2026-02-16T20:00:15", "customer_email": "anson@samiami.net", "customer_id": 202602161958337910, "customer_name": "Stuart Anson", "customer_type": "b2b", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0303L\nZONE: X\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000278769, "paid": false, "property_address": "2729 NW 48TH ST", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.818605", "property_lng": "-80.241119", "property_state": "FL", "property_zip": "33142", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-02-18T14:54:18"}, "success": true, "order_id": "1000278769", "customer_email": "anson@samiami.net", "service_type": "Land Survey Only", "county": "", "property_address": "2729 NW 48TH ST", "customer_name": "Stuart Architecture"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Stuart Anson", "confidence": "MEDIUM"}, "client_email": {"value": "anson@samiami.net", "confidence": "HIGH"}, "property_address": {"value": "2729 NW 48TH ST, MIAMI, FL 33142", "confidence": "HIGH"}, "property_county": {"value": "MIAMI-DADE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status code 11).", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments present."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name discrepancy: FTF order data lists 'Stuart Anson' but the outer wrapper lists 'Stuart Architecture' \u2014 confirm correct client name/company.", "Lot size unknown \u2014 county appraiser data unavailable.", "Legal description unknown \u2014 county appraiser data unavailable.", "Structure square footage unknown.", "Property features (pool, shed, driveway, structures) unknown \u2014 no aerial, appraiser, or email data available.", "Reason for 'On Hold' status not specified \u2014 needs clarification before fieldwork can be scheduled.", "No fieldwork or delivery dates scheduled.", "Invoice has not been sent and order has not been paid \u2014 follow-up may be needed."], "summary": "B2B land survey order for Stuart Anson at 2729 NW 48TH ST, Miami, FL (Miami-Dade County) is currently on hold with special pricing applied, a $250 due amount, and missing lot size, legal description, and property feature details."}}</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:36:02.041852+00:00</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -6147,7 +6261,7 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.210088+00:00</t>
+          <t>2026-06-02T16:36:02.133517+00:00</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6273,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6179,7 +6293,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>12395 GRIFFING BLVD</t>
+          <t>12395 Griffing Blvd, North Miami, FL 33161</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202602131855379974, "created_at": "2026-02-13T18:57:00", "customer_email": "alkcon@gmail.com", "customer_id": 202602131855380849, "customer_name": "Amilkr Contreras", "customer_type": "individual", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0139L\nZONE: X500\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000278707, "paid": false, "property_address": "12395 GRIFFING BLVD", "property_city": "NORTH MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.8892161", "property_lng": "-80.191718", "property_state": "FL", "property_zip": "33161", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-02-13T20:43:54"}, "success": true, "order_id": "1000278707", "customer_email": "alkcon@gmail.com", "service_type": "CAD", "county": "", "property_address": "12395 GRIFFING BLVD", "customer_name": "Amilkr Contreras"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Amilkr Contreras", "confidence": "HIGH"}, "client_email": {"value": "alkcon@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "12395 Griffing Blvd, North Miami, FL 33161", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type is listed as CAD; no additional services specified in the order data."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property feature details available; no appraiser data, aerial data, or email attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser or survey data available", "Legal description not provided", "Structure square footage not available", "Property features (pool, shed, fences, driveways) unknown \u2014 no aerial or appraiser data", "Reason for On Hold status not specified", "No customer profile data returned (FTF customer data empty)", "No matching emails found \u2014 cannot verify scope or client communications", "County was blank in top-level order fields despite being present in nested data \u2014 may indicate data entry inconsistency"], "summary": "Individual residential client Amilkr Contreras has a CAD order On Hold for 12395 Griffing Blvd, North Miami, FL 33161 (Miami-Dade County) with $250 due, special pricing applied, and no supporting property or scope details currently available."}}</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:36:12.591034+00:00</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -6189,7 +6313,7 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.258759+00:00</t>
+          <t>2026-06-02T16:36:12.637014+00:00</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6325,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6221,7 +6345,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>13800 PINE WOODS LN W</t>
+          <t>13800 Pine Woods Ln W, Sarasota, FL 34240</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202010281248465680, "created_at": "2026-02-13T15:42:02", "customer_email": "orders@preferredsettlement.com", "customer_id": 202308071428521960, "customer_name": "Main Office", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12115C0185F\nZONE: X\nEFF: 11/04/2016", "invoiced": false, "order_id": 1000278676, "paid": false, "property_address": "13800 PINE WOODS LN W", "property_city": "SARASOTA", "property_county": "SARASOTA COUNTY", "property_lat": "27.321084", "property_lng": "-82.307056", "property_state": "FLORIDA", "property_zip": "34240", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-02-13T20:40:07"}, "success": true, "order_id": "1000278676", "customer_email": "orders@preferredsettlement.com", "service_type": "Land Survey Only", "county": "", "property_address": "13800 PINE WOODS LN W", "customer_name": "Preferred Settlement Services"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Preferred Settlement Services", "confidence": "HIGH"}, "client_email": {"value": "orders@preferredsettlement.com", "confidence": "HIGH"}, "property_address": {"value": "13800 Pine Woods Ln W, Sarasota, FL 34240", "confidence": "HIGH"}, "property_county": {"value": "Sarasota County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested (elevation_cert: false)"}, "special_requirements": {"value": "Special pricing applied; order currently on hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available; no emails or attachments to reference; aerial/site details unknown"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, outbuildings, etc.) unknown \u2014 no appraiser or aerial data", "Reason for 'On Hold' status not specified", "Special pricing details not defined \u2014 pricing tier or agreed rate unclear", "No fieldwork date scheduled", "No matching emails found to clarify scope or client instructions"], "summary": "B2B land survey order for Preferred Settlement Services at 13800 Pine Woods Ln W, Sarasota, FL 34240 (Flood Zone X), currently on hold with special pricing applied and no fieldwork scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:36:21.841790+00:00</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -6231,7 +6365,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.307828+00:00</t>
+          <t>2026-06-02T16:36:21.888228+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -6117,7 +6117,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6140,16 +6140,37 @@
           <t>770 Dover St, Boca Raton, FL 33487</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>{"total_amount": 500.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for Lot 30, Block 4, Bel-Marra, 770 Dover St, Boca Raton, Palm Beach County. 0.20-acre platted lot with straightforward platted legal description (no metes and bounds). Negotiated flat rate applied per management agreement with Seaside Marine Construction.", "amount": 500.0}], "pricing_reasoning": "The client has a management-approved negotiated survey rate of $500.00, which serves as the fixed base for this order. The property is a 0.20-acre platted residential lot with a clean plat-based legal description (no metes and bounds complexity), no elevation certificate requested, no pool or waterfront canal indicators noted in the order data, and no Monroe County mobilization applies. No complexity upcharges are warranted based on available data, so the total remains at the agreed $500.00 flat rate.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: This order shares the same property address (770 Dover St, Palm Beach County), coordinates, and Folio/MLS (06434704040040300) with three prior orders \u2014 1000134617 (Land Survey Only), 1000244801 (Land Survey Only), and 1000270021 (Land Survey Only). Human review recommended to confirm this is a legitimate repeat order and not an accidental re-submission before processing.", "NO_EC_REQUESTED: Property is in FEMA Zone AE (flood zone 12099C0987G, eff. 12/20/2024) but client explicitly waived the elevation certificate per order notes. No EC line item added.", "B2B_ORDER: Order placed by Seaside Marine Construction under OLD_TITLE tier with 0 prior orders on record. Negotiated rate of $500.00 confirmed per management notes."]}</t>
+        </is>
+      </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202602182034031192, "created_at": "2026-02-18T20:36:16", "customer_email": "office@smcfl.com", "customer_id": 202602182034264579, "customer_name": "Catharina Machado", "customer_type": "b2b", "delivered_at": "2026-02-20T21:37:44", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0987G\nZONE: AE\nELEV: 07 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000278940, "paid": true, "property_address": "770 DOVER ST", "property_city": "BOCA RATON", "property_county": "PALM BEACH COUNTY", "property_lat": "26.4072138", "property_lng": "-80.0726626", "property_state": "FL", "property_zip": "33487", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-02-20T21:37:44"}, "success": true, "order_id": "1000278940", "customer_email": "office@smcfl.com", "service_type": "Land Survey Only", "county": "", "property_address": "770 DOVER ST", "customer_name": "Seaside Marine Construction"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Seaside Marine Construction", "confidence": "HIGH"}, "client_email": {"value": "office@smcfl.com", "confidence": "HIGH"}, "property_address": {"value": "770 Dover St, Boca Raton, FL 33487", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing applied; flood zone AE at elevation 7 ft (FIRM panel 12099C0987G, effective 12/20/2024)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, driveways, structures) unknown \u2014 no appraiser or aerial data available", "Fieldwork date not yet scheduled (fieldwork_at is null)", "Invoice has not been sent (invoiced: false) \u2014 pricing details not confirmed despite special_pricing flag", "No county provided in top-level FTF fields, though property_county is present in nested data"], "summary": "B2B land survey order for Seaside Marine Construction at 770 Dover St, Boca Raton FL (Palm Beach County), located in FEMA flood zone AE, with special pricing applied and no elevation certificate requested."}}</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1780418277412</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>2026-06-02T16:35:41.102524+00:00</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:43:27.222200+00:00</t>
+        </is>
+      </c>
+      <c r="R100" t="n">
+        <v>500</v>
+      </c>
       <c r="T100" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.113381+00:00</t>
@@ -6157,7 +6178,7 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>2026-06-02T16:35:41.146994+00:00</t>
+          <t>2026-06-02T16:43:27.268205+00:00</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6190,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6192,16 +6213,37 @@
           <t>811 N Olive Ave, West Palm Beach, FL 33401</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "This order is flagged as a B2B CAD deliverable order with undefined scope \u2014 the specific CAD output required (e.g., CAD file conversion from existing survey data, new field work, drafting only, etc.) has not been defined. Additionally, three probable duplicate orders exist at the same address and folio for related survey services, which must be reconciled before pricing can be finalized. The order is currently On Hold with special pricing noted but unspecified. No reliable pricing can be proposed without human clarification of the CAD deliverable scope and its relationship to the existing duplicate orders.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "1) CAD deliverable scope is undefined \u2014 it is unclear whether this is a CAD file only (drafting/conversion), a full boundary survey with CAD output, or something else entirely. The service type cannot be priced without this clarification. 2) Three duplicate orders exist at the same address (Orders 1000272351, 1000276506, 1000278055) covering Boundary Survey, ALTA, and Land Survey services \u2014 the relationship between this CAD order and those existing orders must be reconciled by management before pricing. 3) Order notes explicitly state 'special pricing applied' but no specific amount or scope is defined, requiring direct management follow-up with Randy Beth Breitman / Randy B Realty.", "flags": ["DUPLICATE_SUSPECTED: Order 1000272351 \u2014 same address 811 N OLIVE AVE, same folio 74434315210010140 \u2014 service: Boundary Survey, ALTA Table A Survey. Reconcile before pricing.", "DUPLICATE_SUSPECTED: Order 1000276506 \u2014 same address 811 N OLIVE AVE, same folio 74434315210010140 \u2014 service: Land Survey Only. Reconcile before pricing.", "DUPLICATE_SUSPECTED: Order 1000278055 \u2014 same address 811 N OLIVE AVE, same folio 74434315210010140 \u2014 service: Land Survey Only. Reconcile before pricing.", "SCOPE_UNDEFINED: CAD service type is not specified. Clarify whether this is a CAD conversion/drafting-only deliverable, a new field survey with CAD output, or another CAD product.", "SPECIAL_PRICING_NOTED: Order notes reference special pricing applied but no amount or terms are documented. Management must confirm agreed pricing with client Randy B Realty.", "CLIENT_NEW: Randy B Realty has 0 prior orders with NexGen despite OLD_TITLE tier classification. Verify client tier and negotiated rate of $450.00 is confirmed by management."]}</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510011504100630, "created_at": "2026-02-18T20:25:20", "customer_email": "randybeth@randybrealty.com", "customer_id": 202510011504434287, "customer_name": "Randy Beth Breitman", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0581G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000278938, "paid": true, "property_address": "811 N OLIVE AVE", "property_city": "WEST PALM BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.7201875", "property_lng": "-80.0520531", "property_state": "FL", "property_zip": "33401", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-03T16:12:22"}, "success": true, "order_id": "1000278938", "customer_email": "randybeth@randybrealty.com", "service_type": "CAD", "county": "", "property_address": "811 N OLIVE AVE", "customer_name": "Randy B Realty"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Randy Beth Breitman / Randy B Realty", "confidence": "HIGH"}, "client_email": {"value": "randybeth@randybrealty.com", "confidence": "HIGH"}, "property_address": {"value": "811 N Olive Ave, West Palm Beach, FL 33401", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "MEDIUM", "notes": "Service type is listed as CAD \u2014 likely CAD drafting of a survey; specific deliverable scope (boundary, topo, ALTA, etc.) is not defined and needs clarification"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 no appraiser data, no emails, no aerial info provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["CAD service scope not defined \u2014 boundary, topo, ALTA, or other?", "Reason for On Hold status unknown", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, fences, etc.) unknown", "No fieldwork date scheduled", "No estimate sent \u2014 pricing details unclear beyond 'special pricing'", "County property appraiser data unavailable", "No matching emails found to clarify scope or requirements"], "summary": "B2B CAD order for Randy Beth Breitman at 811 N Olive Ave, West Palm Beach FL 33401 (Palm Beach County) is currently On Hold with special pricing applied, but the specific CAD deliverable scope and property details are undefined and require human follow-up."}}</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1780418625910</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>2026-06-02T16:35:51.046380+00:00</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:43:46.569740+00:00</t>
+        </is>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
       <c r="T101" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.161529+00:00</t>
@@ -6209,7 +6251,7 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>2026-06-02T16:35:51.092313+00:00</t>
+          <t>2026-06-02T16:43:46.616623+00:00</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6419,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6397,7 +6439,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>4562-4588 DAVIS RD</t>
+          <t>4562-4588 DAVIS RD, LAKE WORTH BEACH, FL 33461</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202601281652426507, "created_at": "2026-02-12T17:13:08", "customer_email": "donald.witmondt@woodmontproperties.com", "customer_id": 202601281652427674, "customer_name": "Donald Witmondt", "customer_type": "individual", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0776F \nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000278620, "paid": false, "property_address": "4562-4588 DAVIS RD", "property_city": "LAKE WORTH BEACH", "property_county": "Palm Beach County", "property_lat": "26.6093772", "property_lng": "-80.0972867", "property_state": "FL", "property_zip": "33461", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-02-12T17:20:42"}, "success": true, "order_id": "1000278620", "customer_email": "donald.witmondt@woodmontproperties.com", "service_type": "CAD", "county": "", "property_address": "4562-4588 DAVIS RD", "customer_name": "Donald Witmondt"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Donald Witmondt", "confidence": "HIGH"}, "client_email": {"value": "donald.witmondt@woodmontproperties.com", "confidence": "HIGH"}, "property_address": {"value": "4562-4588 DAVIS RD, LAKE WORTH BEACH, FL 33461", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "MEDIUM", "notes": "Service type is listed as 'CAD' which typically refers to CAD drafting/redrafting of a survey; exact deliverable scope is not detailed \u2014 may need clarification on whether this is a new survey or CAD work on existing data"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Exact scope of CAD service not specified (new survey vs. CAD drafting from existing data)", "Lot size unknown \u2014 no appraiser data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, structures) unknown", "No customer company data available despite email domain suggesting business affiliation (Woodmont Properties)", "Reason for 'On Hold' status not documented", "Fieldwork date not scheduled", "Invoice not yet generated \u2014 due amount of $250 noted but not invoiced"], "summary": "CAD service order for Donald Witmondt (likely affiliated with Woodmont Properties) on a multi-address commercial property at 4562-4588 Davis Rd, Lake Worth Beach, FL, currently on hold with special pricing applied and $250 due."}}</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:41:56.555154+00:00</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -6407,7 +6459,7 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.358257+00:00</t>
+          <t>2026-06-02T16:41:56.652532+00:00</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6471,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6439,7 +6491,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>524 &amp; 530 SOUTH LAKESIDE DRIVE</t>
+          <t>524 &amp; 530 South Lakeside Drive, Lake Worth Beach, FL 33460</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202602121416087321, "created_at": "2026-02-12T14:18:43", "customer_email": "yuvalmadar@gmail.com", "customer_id": 202602121416088521, "customer_name": "Yuval Madar", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0781G\nZONE: AE\nELEV: 09 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000278594, "paid": true, "property_address": "524 &amp; 530 SOUTH LAKESIDE DRIVE", "property_city": "LAKE WORTH BEACH", "property_county": "Palm Beach County", "property_lat": "26.6088936", "property_lng": "-80.0499696", "property_state": "FL", "property_zip": "33460", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-02-12T17:28:54"}, "success": true, "order_id": "1000278594", "customer_email": "yuvalmadar@gmail.com", "service_type": "CAD", "county": "", "property_address": "524 &amp; 530 SOUTH LAKESIDE DRIVE", "customer_name": "Yuval Madar"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Yuval Madar", "confidence": "HIGH"}, "client_email": {"value": "yuvalmadar@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "524 &amp; 530 South Lakeside Drive, Lake Worth Beach, FL 33460", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "MEDIUM", "notes": "Service type is listed as CAD but no further breakdown of deliverables is provided \u2014 unclear if this is a boundary survey CAD, as-built, or other CAD drafting service"}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); dual parcel address (524 &amp; 530) may indicate two lots", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 no appraiser data, no emails, no aerial info provided"}, "client_tier": {"value": "residential", "confidence": "MEDIUM"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Exact CAD service scope is undefined \u2014 boundary, as-built, topographic, or other?", "Dual address (524 &amp; 530) may indicate two separate parcels \u2014 confirmation needed on whether both are included in scope", "Lot size unknown \u2014 no appraiser data available", "Legal description missing", "Structure square footage unknown", "Property features (pool, structures, etc.) unknown", "Reason for On Hold status not specified", "Special pricing details not itemized \u2014 amount or discount unknown", "No urgency or deadline provided", "No fieldwork date scheduled", "Customer data object is empty \u2014 no phone number or additional contact info"], "summary": "Individual client Yuval Madar has placed a paid CAD order (On Hold) for a dual-parcel property at 524 &amp; 530 South Lakeside Drive, Lake Worth Beach, FL in Palm Beach County, with special pricing applied but scope, lot details, and hold reason still undefined."}}</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:42:09.795889+00:00</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
@@ -6449,7 +6511,7 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.407352+00:00</t>
+          <t>2026-06-02T16:42:09.842992+00:00</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6523,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6476,12 +6538,22 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>MAria Mcardle</t>
+          <t>Jon Moore</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>4417 S FLAGLER DR</t>
+          <t>4417 S Flagler Dr, West Palm Beach, FL 33405</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202411212009461034, "created_at": "2026-02-11T15:25:01", "customer_email": "jon@Smithmoorearchitects.com", "customer_id": 202411212010394766, "customer_name": "Jon Moore", "customer_type": "b2b", "delivered_at": "2026-02-13T14:09:47", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0591G\nZONE: AE\nELEV: 08 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000278523, "paid": true, "property_address": "4417 S FLAGLER DR", "property_city": "WEST PALM BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.6724036", "property_lng": "-80.0486901", "property_state": "FL", "property_zip": "33405", "service_type": "CAD Release", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-02-13T14:09:47"}, "success": true, "order_id": "1000278523", "customer_email": "jon@Smithmoorearchitects.com", "service_type": "CAD Release", "county": "", "property_address": "4417 S FLAGLER DR", "customer_name": "MAria Mcardle"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Jon Moore", "confidence": "MEDIUM"}, "client_email": {"value": "jon@Smithmoorearchitects.com", "confidence": "HIGH"}, "property_address": {"value": "4417 S Flagler Dr, West Palm Beach, FL 33405", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD Release"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD Release; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; flood zone AE (panel 12099C0591G, base elevation 8 ft, effective 12/20/2024)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: FTF order data shows 'Jon Moore' but outer envelope shows 'MAria Mcardle' \u2014 needs human verification", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, structures, etc.) unknown \u2014 no appraiser or aerial data available", "No matching emails found to cross-reference order details", "County appraiser data unavailable \u2014 no parcel or ownership data to verify"], "summary": "B2B CAD Release order for Jon Moore (Smith Moore Architects) at 4417 S Flagler Dr, West Palm Beach, FL 33405 in a Flood Zone AE area, delivered on 2026-02-13 with special pricing applied and a client name discrepancy requiring human review."}}</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:42:19.918729+00:00</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
@@ -6491,7 +6563,7 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.456769+00:00</t>
+          <t>2026-06-02T16:42:19.965271+00:00</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6575,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6523,7 +6595,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>747 11TH CT SW</t>
+          <t>747 11TH CT SW, Vero Beach, FL 32962</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201801311054240045, "created_at": "2026-02-09T19:57:53", "customer_email": "richard@rcareylaw.com", "customer_id": 201909101546171936, "customer_name": "Richard Carey", "customer_type": "b2b", "delivered_at": null, "due_amount": 200.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12061C0359J\nZONE: X\nEFF: 01/26/2023", "invoiced": false, "order_id": 1000278419, "paid": false, "property_address": "747 11TH CT SW", "property_city": "VERO BEACH", "property_county": "Indian River County", "property_lat": "27.589697", "property_lng": "-80.3964589", "property_state": "FL", "property_zip": "32962", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-06T16:29:04"}, "success": true, "order_id": "1000278419", "customer_email": "richard@rcareylaw.com", "service_type": "CAD", "county": "", "property_address": "747 11TH CT SW", "customer_name": "Carey Law Group PA"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Carey Law Group PA", "confidence": "MEDIUM"}, "client_email": {"value": "richard@rcareylaw.com", "confidence": "HIGH"}, "property_address": {"value": "747 11TH CT SW, Vero Beach, FL 32962", "confidence": "HIGH"}, "property_county": {"value": "Indian River County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type is listed as CAD; no additional services specified"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 no appraiser or document source available", "Structure square footage unknown", "Property features (pool, shed, driveway, structures) unknown \u2014 no aerial, appraiser, or email data", "Client name discrepancy: order contact is 'Richard Carey' but company/invoice name appears to be 'Carey Law Group PA' \u2014 confirm billing name", "Reason for On Hold status unknown \u2014 needs human review", "Fieldwork and delivery dates not yet scheduled", "Scope of CAD deliverable not specified (boundary, topo, as-built, etc.)"], "summary": "B2B CAD survey order for Carey Law Group PA at 747 11th CT SW, Vero Beach, FL 32962 (Indian River County), currently On Hold with special pricing applied and a $200 balance due; property and scope details are largely incomplete pending human review."}}</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:42:30.937410+00:00</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
@@ -6533,7 +6615,7 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.507129+00:00</t>
+          <t>2026-06-02T16:42:30.984099+00:00</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6627,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6568,6 +6650,16 @@
           <t>745 11TH CT SW</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"order_id": "1000278416", "customer_email": "richard@rcareylaw.com", "service_type": "CAD", "county": "", "property_address": "745 11TH CT SW", "customer_name": "Carey Law Group PA"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Carey Law Group PA", "confidence": "HIGH"}, "client_email": {"value": "richard@rcareylaw.com", "confidence": "HIGH"}, "property_address": {"value": "745 11TH CT SW", "confidence": "HIGH"}, "property_county": {"value": "", "confidence": "LOW"}, "services_requested": {"value": ["CAD"], "confidence": "MEDIUM", "notes": "Service type listed as CAD \u2014 likely CAD drafting or CAD survey drawing; specific deliverable scope unclear without further context"}, "special_requirements": {"value": "", "confidence": "LOW"}, "lot_size": {"value": "", "confidence": "LOW"}, "legal_description": {"value": "", "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments found"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Property county not provided \u2014 needed to look up appraiser data and verify address", "Full property address may be incomplete (no city, state, or ZIP)", "CAD service scope not defined \u2014 clarify what CAD deliverable is expected (e.g., boundary survey CAD, as-built CAD, etc.)", "Lot size unknown", "Legal description unknown", "Structure square footage unknown", "Property features unknown (pool, shed, structures, etc.)", "No special requirements noted", "Urgency/rush status unknown", "No matching emails or supporting documents found"], "summary": "B2B CAD order from Carey Law Group PA for property at 745 11th CT SW, with critical gaps including missing county, incomplete address, undefined CAD scope, and no supporting property data."}}</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:43:10.742313+00:00</t>
+        </is>
+      </c>
       <c r="T109" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.604547+00:00</t>
@@ -6575,7 +6667,7 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.604547+00:00</t>
+          <t>2026-06-02T16:43:10.787470+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6286,16 +6286,37 @@
           <t>2729 NW 48TH ST, MIAMI, FL 33142</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>{"total_amount": 500.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for LOT 25 AND THE WEST 15.95 FEET OF LOT 26, BLOCK 1, BROWN SUBDIVISION AMENDED PLAT, 2729 NW 48TH ST, Miami-Dade County. Lot size 0.23 acres (under 0.31 ac threshold \u2014 no lot size upcharge). FEMA Zone X \u2014 no EC required. Platted subdivision legal description \u2014 no metes-and-bounds upcharge. No pool, waterfront, or heavy vegetation indicators in available data. Not Monroe County. Client negotiated rate applied as instructed by management.", "amount": 500.0}], "pricing_reasoning": "Stuart Architecture has a management-agreed negotiated base rate of $500.00 for land surveys. The subject property is 0.23 acres (below the 0.31 ac upcharge threshold), located in FEMA Zone X (no EC needed), described by a standard platted lot legal description (no metes-and-bounds upcharge), in Miami-Dade County (no Monroe County mobilization surcharge), and no aerial or data indicators of pool, canal, or heavy vegetation complexity. No upcharges are warranted, so the total equals the negotiated base rate of $500.00.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_SUSPECTED: Order 1000207733 at same address (2729 NW 48TH ST, Miami-Dade County) for identical service (Land Survey Only) \u2014 coordinates match (25.818605, -80.24112). Human review recommended before dispatching field crew.", "DUPLICATE_SUSPECTED: Order 1000259983 at same address (2729 NW 48TH ST, Miami-Dade County) for identical service (Land Survey Only) \u2014 coordinates and Folio/MLS (3031210230361) match exactly. Strong duplicate signal \u2014 human review required.", "ORDER_NOTES: Order was previously on hold with $250 due amount noted. Management should confirm whether prior partial payment or hold status affects this invoice before issuing.", "CLIENT_ORDER_COUNT: Stuart Architecture shows 0 prior orders with NexGen despite being classified OLD_TITLE tier. Verify client tier classification is accurate."]}</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202602161958085167, "created_at": "2026-02-16T20:00:15", "customer_email": "anson@samiami.net", "customer_id": 202602161958337910, "customer_name": "Stuart Anson", "customer_type": "b2b", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0303L\nZONE: X\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000278769, "paid": false, "property_address": "2729 NW 48TH ST", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.818605", "property_lng": "-80.241119", "property_state": "FL", "property_zip": "33142", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-02-18T14:54:18"}, "success": true, "order_id": "1000278769", "customer_email": "anson@samiami.net", "service_type": "Land Survey Only", "county": "", "property_address": "2729 NW 48TH ST", "customer_name": "Stuart Architecture"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Stuart Anson", "confidence": "MEDIUM"}, "client_email": {"value": "anson@samiami.net", "confidence": "HIGH"}, "property_address": {"value": "2729 NW 48TH ST, MIAMI, FL 33142", "confidence": "HIGH"}, "property_county": {"value": "MIAMI-DADE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status code 11).", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments present."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name discrepancy: FTF order data lists 'Stuart Anson' but the outer wrapper lists 'Stuart Architecture' \u2014 confirm correct client name/company.", "Lot size unknown \u2014 county appraiser data unavailable.", "Legal description unknown \u2014 county appraiser data unavailable.", "Structure square footage unknown.", "Property features (pool, shed, driveway, structures) unknown \u2014 no aerial, appraiser, or email data available.", "Reason for 'On Hold' status not specified \u2014 needs clarification before fieldwork can be scheduled.", "No fieldwork or delivery dates scheduled.", "Invoice has not been sent and order has not been paid \u2014 follow-up may be needed."], "summary": "B2B land survey order for Stuart Anson at 2729 NW 48TH ST, Miami, FL (Miami-Dade County) is currently on hold with special pricing applied, a $250 due amount, and missing lot size, legal description, and property feature details."}}</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1780418809589</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>2026-06-02T16:36:02.041852+00:00</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:51:48.621123+00:00</t>
+        </is>
+      </c>
+      <c r="R102" t="n">
+        <v>500</v>
+      </c>
       <c r="T102" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.210088+00:00</t>
@@ -6303,7 +6324,7 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>2026-06-02T16:36:02.133517+00:00</t>
+          <t>2026-06-02T16:51:48.670093+00:00</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6336,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6338,16 +6359,37 @@
           <t>12395 Griffing Blvd, North Miami, FL 33161</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>{"total_amount": 512.0, "services": [{"name": "CAD / Boundary Survey", "description": "Standard boundary survey with CAD deliverable for residential lot at 12395 Griffing Blvd, Miami-Dade County. Based on negotiated management-approved rate for this individual client.", "amount": 450.0}, {"name": "Lot Size Complexity Upcharge (0.31\u20130.50 ac)", "description": "Property is 0.37 acres, falling within the 0.31\u20130.50 ac complexity tier. Upcharge applied per standard pricing guidelines.", "amount": 62.0}], "pricing_reasoning": "The negotiated base rate of $450.00 was agreed upon by management for this individual client and is used as the starting point. The lot is 0.37 acres, which falls in the 0.31\u20130.50 ac range and warrants a $62.00 complexity upcharge. No EC is requested, FEMA Zone X500 is a minimal-hazard zone requiring no EC line item, the legal description is a straightforward platted lot (no metes-and-bounds upcharge), and no pool, waterfront, heavy vegetation, or Monroe County factors are evident from the available data.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000277976 references the same address (12395 Griffing Blvd, Miami-Dade County), same coordinates (25.8892161, -80.191718), and same Folio/MLS (0622300280260) with service type 'Land Survey Only' \u2014 human review recommended before invoicing.", "DUPLICATE_WARNING: Order 1000283002 also references the same address, coordinates, and Folio/MLS with service type 'Land Survey Only' \u2014 a total of three orders exist for this property. Human review strongly recommended to confirm whether these are distinct scopes or duplicate entries.", "ORDER_NOTES: Order notes indicate $250 was previously quoted as due with 'special pricing applied.' The management-approved negotiated rate of $450 plus the lot-size upcharge yields $512.00, which differs from the $250 figure noted. Management should confirm whether the $250 figure supersedes standard negotiated pricing or reflects a partial/deposit amount.", "NO_AERIAL_DATA: No aerial image was available for independent verification of pool, waterfront canal, or heavy vegetation conditions. Complexity upcharges beyond lot size have not been applied absent supporting evidence."]}</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202602131855379974, "created_at": "2026-02-13T18:57:00", "customer_email": "alkcon@gmail.com", "customer_id": 202602131855380849, "customer_name": "Amilkr Contreras", "customer_type": "individual", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0139L\nZONE: X500\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000278707, "paid": false, "property_address": "12395 GRIFFING BLVD", "property_city": "NORTH MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.8892161", "property_lng": "-80.191718", "property_state": "FL", "property_zip": "33161", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-02-13T20:43:54"}, "success": true, "order_id": "1000278707", "customer_email": "alkcon@gmail.com", "service_type": "CAD", "county": "", "property_address": "12395 GRIFFING BLVD", "customer_name": "Amilkr Contreras"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Amilkr Contreras", "confidence": "HIGH"}, "client_email": {"value": "alkcon@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "12395 Griffing Blvd, North Miami, FL 33161", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type is listed as CAD; no additional services specified in the order data."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property feature details available; no appraiser data, aerial data, or email attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser or survey data available", "Legal description not provided", "Structure square footage not available", "Property features (pool, shed, fences, driveways) unknown \u2014 no aerial or appraiser data", "Reason for On Hold status not specified", "No customer profile data returned (FTF customer data empty)", "No matching emails found \u2014 cannot verify scope or client communications", "County was blank in top-level order fields despite being present in nested data \u2014 may indicate data entry inconsistency"], "summary": "Individual residential client Amilkr Contreras has a CAD order On Hold for 12395 Griffing Blvd, North Miami, FL 33161 (Miami-Dade County) with $250 due, special pricing applied, and no supporting property or scope details currently available."}}</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1780419108361</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>2026-06-02T16:36:12.591034+00:00</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:52:09.209604+00:00</t>
+        </is>
+      </c>
+      <c r="R103" t="n">
+        <v>512</v>
+      </c>
       <c r="T103" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.258759+00:00</t>
@@ -6355,7 +6397,7 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>2026-06-02T16:36:12.637014+00:00</t>
+          <t>2026-06-02T16:52:09.307071+00:00</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6409,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6390,16 +6432,37 @@
           <t>13800 Pine Woods Ln W, Sarasota, FL 34240</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "AI pricing failed: Unterminated string starting at: line 23 column 5 (char 2684). Manual review required.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "AI pricing error \u2014 needs manual quote", "flags": ["ai_error"]}</t>
+        </is>
+      </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202010281248465680, "created_at": "2026-02-13T15:42:02", "customer_email": "orders@preferredsettlement.com", "customer_id": 202308071428521960, "customer_name": "Main Office", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12115C0185F\nZONE: X\nEFF: 11/04/2016", "invoiced": false, "order_id": 1000278676, "paid": false, "property_address": "13800 PINE WOODS LN W", "property_city": "SARASOTA", "property_county": "SARASOTA COUNTY", "property_lat": "27.321084", "property_lng": "-82.307056", "property_state": "FLORIDA", "property_zip": "34240", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-02-13T20:40:07"}, "success": true, "order_id": "1000278676", "customer_email": "orders@preferredsettlement.com", "service_type": "Land Survey Only", "county": "", "property_address": "13800 PINE WOODS LN W", "customer_name": "Preferred Settlement Services"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Preferred Settlement Services", "confidence": "HIGH"}, "client_email": {"value": "orders@preferredsettlement.com", "confidence": "HIGH"}, "property_address": {"value": "13800 Pine Woods Ln W, Sarasota, FL 34240", "confidence": "HIGH"}, "property_county": {"value": "Sarasota County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested (elevation_cert: false)"}, "special_requirements": {"value": "Special pricing applied; order currently on hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available; no emails or attachments to reference; aerial/site details unknown"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, outbuildings, etc.) unknown \u2014 no appraiser or aerial data", "Reason for 'On Hold' status not specified", "Special pricing details not defined \u2014 pricing tier or agreed rate unclear", "No fieldwork date scheduled", "No matching emails found to clarify scope or client instructions"], "summary": "B2B land survey order for Preferred Settlement Services at 13800 Pine Woods Ln W, Sarasota, FL 34240 (Flood Zone X), currently on hold with special pricing applied and no fieldwork scheduled."}}</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1780419150301</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>2026-06-02T16:36:21.841790+00:00</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:52:31.266132+00:00</t>
+        </is>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
       <c r="T104" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.307828+00:00</t>
@@ -6407,7 +6470,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2026-06-02T16:36:21.888228+00:00</t>
+          <t>2026-06-02T16:52:31.313924+00:00</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6482,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6442,16 +6505,37 @@
           <t>4562-4588 DAVIS RD, LAKE WORTH BEACH, FL 33461</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>{"total_amount": 250.0, "services": [{"name": "CAD Drafting Service", "description": "CAD service for 4562-4588 Davis Rd, Palm Beach County \u2014 two-parcel property (Lots C &amp; D, Block 72, Palm Beach Farms Co., Plat No. 7). Special pricing applied per management direction; $250.00 due as noted in order.", "amount": 250.0}], "pricing_reasoning": "This is a CAD-only service order (not a new boundary survey or EC), flagged explicitly in the order notes as 'on hold with special pricing applied and $250 due.' Management has already negotiated and set the price for this specific deliverable. The negotiated base survey rate of $450.00 and standard complexity upcharges are not applicable here because the service type is CAD drafting with a pre-approved special price of $250.00. No EC is ordered and no topo is requested, so those pricing tiers do not apply.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_ORDER: Order 1000216148 \u2014 4562 DAVIS RD, Palm Beach County \u2014 service: Land Survey Only \u2014 same folio 00434430010720030 and coordinates (26.6094021, -80.0972924). Human review recommended.", "DUPLICATE_ORDER: Order 1000219053 \u2014 4562-4588 DAVIS RD, Palm Beach County \u2014 service: Quote \u2014 same folio 00434430010720030 and coordinates. Human review recommended.", "DUPLICATE_ORDER: Order 1000219118 \u2014 4562 DAVIS RD, Palm Beach County \u2014 service: Land Survey Only \u2014 same folio 00434430010720030 and coordinates. Human review recommended.", "MULTI-PARCEL: Two legal parcels (Lot C and Lot D, Block 72) combined under one order. Verify CAD scope covers both parcels.", "COMMERCIAL CONTEXT: Order notes reference Woodmont Properties affiliation despite commercial_flag=false and client tier listed as INDIVIDUAL. Confirm client classification is correct.", "SPECIAL PRICING: $250.00 pre-approved by management per order notes. Do not override with standard rate schedule."]}</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202601281652426507, "created_at": "2026-02-12T17:13:08", "customer_email": "donald.witmondt@woodmontproperties.com", "customer_id": 202601281652427674, "customer_name": "Donald Witmondt", "customer_type": "individual", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0776F \nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000278620, "paid": false, "property_address": "4562-4588 DAVIS RD", "property_city": "LAKE WORTH BEACH", "property_county": "Palm Beach County", "property_lat": "26.6093772", "property_lng": "-80.0972867", "property_state": "FL", "property_zip": "33461", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-02-12T17:20:42"}, "success": true, "order_id": "1000278620", "customer_email": "donald.witmondt@woodmontproperties.com", "service_type": "CAD", "county": "", "property_address": "4562-4588 DAVIS RD", "customer_name": "Donald Witmondt"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Donald Witmondt", "confidence": "HIGH"}, "client_email": {"value": "donald.witmondt@woodmontproperties.com", "confidence": "HIGH"}, "property_address": {"value": "4562-4588 DAVIS RD, LAKE WORTH BEACH, FL 33461", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "MEDIUM", "notes": "Service type is listed as 'CAD' which typically refers to CAD drafting/redrafting of a survey; exact deliverable scope is not detailed \u2014 may need clarification on whether this is a new survey or CAD work on existing data"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Exact scope of CAD service not specified (new survey vs. CAD drafting from existing data)", "Lot size unknown \u2014 no appraiser data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, structures) unknown", "No customer company data available despite email domain suggesting business affiliation (Woodmont Properties)", "Reason for 'On Hold' status not documented", "Fieldwork date not scheduled", "Invoice not yet generated \u2014 due amount of $250 noted but not invoiced"], "summary": "CAD service order for Donald Witmondt (likely affiliated with Woodmont Properties) on a multi-address commercial property at 4562-4588 Davis Rd, Lake Worth Beach, FL, currently on hold with special pricing applied and $250 due."}}</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1780419169212</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>2026-06-02T16:41:56.555154+00:00</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:52:49.566365+00:00</t>
+        </is>
+      </c>
+      <c r="R105" t="n">
+        <v>250</v>
+      </c>
       <c r="T105" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.358257+00:00</t>
@@ -6459,7 +6543,7 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>2026-06-02T16:41:56.652532+00:00</t>
+          <t>2026-06-02T16:52:49.615021+00:00</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6763,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6699,7 +6783,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>735 11TH CT SW</t>
+          <t>735 11TH CT SW, VERO BEACH, FL 32962</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201801311054240045, "created_at": "2026-02-09T19:42:01", "customer_email": "richard@rcareylaw.com", "customer_id": 201909101546171936, "customer_name": "Richard Carey", "customer_type": "b2b", "delivered_at": null, "due_amount": 200.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12061C0359J\nZONE: X\nEFF: 01/26/2023", "invoiced": false, "order_id": 1000278415, "paid": false, "property_address": "735 11TH CT SW", "property_city": "VERO BEACH", "property_county": "INDIAN RIVER COUNTY", "property_lat": "27.5901062", "property_lng": "-80.3964254", "property_state": "FL", "property_zip": "32962", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-06T16:29:04"}, "success": true, "order_id": "1000278415", "customer_email": "richard@rcareylaw.com", "service_type": "CAD", "county": "", "property_address": "735 11TH CT SW", "customer_name": "Carey Law Group PA"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Carey Law Group PA", "confidence": "MEDIUM"}, "client_email": {"value": "richard@rcareylaw.com", "confidence": "HIGH"}, "property_address": {"value": "735 11TH CT SW, VERO BEACH, FL 32962", "confidence": "HIGH"}, "property_county": {"value": "INDIAN RIVER COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type is listed as CAD; no additional services indicated in the order data"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features provided; county appraiser unavailable and no matching emails or attachments found"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name discrepancy: order body lists 'Richard Carey' but customer_name override is 'Carey Law Group PA' \u2014 confirm correct billing name", "Lot size unknown \u2014 county appraiser unavailable", "Legal description unknown \u2014 county appraiser unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fences, driveways, etc.)", "Reason for On Hold status not documented", "Scope of CAD deliverable not specified (boundary, topo, as-built, etc.)", "No fieldwork or delivery dates scheduled"], "summary": "B2B CAD order for Carey Law Group PA at 735 11TH CT SW, Vero Beach, FL (Indian River County) is currently On Hold with special pricing applied and a $200 due balance, but lacks lot size, legal description, property features, and CAD scope details."}}</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:50:48.453503+00:00</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
@@ -6709,7 +6803,7 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.654732+00:00</t>
+          <t>2026-06-02T16:50:48.501321+00:00</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6815,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6741,7 +6835,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1195 16TH AVE SW</t>
+          <t>1195 16TH AVE SW, VERO BEACH, FL 32962</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201801311054240045, "created_at": "2026-02-09T19:33:53", "customer_email": "richard@rcareylaw.com", "customer_id": 201909101546171936, "customer_name": "Richard Carey", "customer_type": "b2b", "delivered_at": "2026-03-20T18:48:37", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12061C0359J\nZONE: X\nEFF: 01/26/2023", "invoiced": false, "order_id": 1000278414, "paid": true, "property_address": "1195 16TH AVE SW", "property_city": "VERO BEACH", "property_county": "Indian River County", "property_lat": "27.581642", "property_lng": "-80.4023179", "property_state": "FL", "property_zip": "32962", "service_type": "CAD", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-05-12T18:14:21"}, "success": true, "order_id": "1000278414", "customer_email": "richard@rcareylaw.com", "service_type": "CAD", "county": "", "property_address": "1195 16TH AVE SW", "customer_name": "Carey Law Group PA"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Carey Law Group PA", "confidence": "MEDIUM"}, "client_email": {"value": "richard@rcareylaw.com", "confidence": "HIGH"}, "property_address": {"value": "1195 16TH AVE SW, VERO BEACH, FL 32962", "confidence": "HIGH"}, "property_county": {"value": "Indian River County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type is listed as CAD; no additional services indicated in the order data"}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name discrepancy: order body says 'Carey Law Group PA' but customer record says 'Richard Carey' \u2014 confirm correct billing name", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, fences, driveways, etc.) unknown \u2014 no aerial or appraiser data available", "County appraiser data unavailable \u2014 Indian River County lookup was not performed", "Fieldwork date is null \u2014 unclear if fieldwork was completed or if CAD is based on existing data", "Specific CAD deliverable scope unclear (boundary, topo, site plan, etc.)", "Invoice has not been sent despite order being delivered and marked paid \u2014 verify billing status"], "summary": "B2B CAD order for Carey Law Group PA (Richard Carey) at 1195 16TH AVE SW, Vero Beach, FL 32962 in Indian River County, delivered on 2026-03-20 with special pricing applied, but missing lot size, legal description, property features, and invoice documentation."}}</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:50:59.338170+00:00</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
@@ -6751,7 +6855,7 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.705755+00:00</t>
+          <t>2026-06-02T16:50:59.385439+00:00</t>
         </is>
       </c>
     </row>
@@ -6763,7 +6867,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6783,7 +6887,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>5327 N BAY RD</t>
+          <t>5327 N Bay Rd, Miami Beach, FL 33140</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202602032116075928, "created_at": "2026-02-03T21:18:39", "customer_email": "lauriepicard@hotmail.com", "customer_id": 202602032116076992, "customer_name": "Laurie Picard", "customer_type": "individual", "delivered_at": "2026-02-10T16:50:48", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0309L\nZONE: AE\nELEV: 08 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000278156, "paid": true, "property_address": "5327 N BAY RD", "property_city": "MIAMI BEACH", "property_county": "Miami-Dade County", "property_lat": "25.8317178", "property_lng": "-80.1295335", "property_state": "FL", "property_zip": "33140", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-02-10T16:50:48"}, "success": true, "order_id": "1000278156", "customer_email": "lauriepicard@hotmail.com", "service_type": "Quote", "county": "", "property_address": "5327 N BAY RD", "customer_name": "Laurie Picard"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Laurie Picard", "confidence": "HIGH"}, "client_email": {"value": "lauriepicard@hotmail.com", "confidence": "HIGH"}, "property_address": {"value": "5327 N Bay Rd, Miami Beach, FL 33140", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed as 'Quote' only \u2014 no specific survey type (e.g., Boundary, ALTA, Elevation Certificate) has been identified. Needs clarification on what survey service is being quoted."}, "special_requirements": {"value": "Special pricing applied. Property is in FEMA Flood Zone AE (Panel 12086C0309L, Base Flood Elevation 8 ft, effective 09/11/2009).", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 no aerial, appraiser data, or email attachments provided. Pool, structures, driveways unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not identified \u2014 'Quote' is not a deliverable service", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fences, driveways, etc.)", "No matching emails found to clarify scope or client intent", "Fieldwork date not scheduled (fieldwork_at is null)", "Invoice not yet generated (invoiced: false) despite order being marked Delivered and Paid"], "summary": "Residential quote request from individual client Laurie Picard for a property at 5327 N Bay Rd, Miami Beach, FL (Miami-Dade County) located in FEMA Flood Zone AE, with special pricing applied but no specific survey service type identified."}}</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:51:10.623338+00:00</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
@@ -6793,7 +6907,7 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.756326+00:00</t>
+          <t>2026-06-02T16:51:10.672437+00:00</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6919,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6820,12 +6934,22 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>IK STUDIOS</t>
+          <t>IK Studios (Alex Gonzalez)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>5729 SW 60TH AVE</t>
+          <t>5729 SW 60TH AVE, South Miami, FL 33143</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202601301457214739, "created_at": "2026-01-30T14:59:12", "customer_email": "alex@ikstudio.net", "customer_id": 202601301458052770, "customer_name": "Alex Gonzalez", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0458L\nZONE: AH\nELEV: 09 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000277959, "paid": true, "property_address": "5729 SW 60TH AVE", "property_city": "SOUTH MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.7170772", "property_lng": "-80.2921914", "property_state": "FL", "property_zip": "33143", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-30T20:57:09"}, "success": true, "order_id": "1000277959", "customer_email": "alex@ikstudio.net", "service_type": "CAD file", "county": "", "property_address": "5729 SW 60TH AVE", "customer_name": "IK STUDIOS"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "IK Studios (Alex Gonzalez)", "confidence": "HIGH"}, "client_email": {"value": "alex@ikstudio.net", "confidence": "HIGH"}, "property_address": {"value": "5729 SW 60TH AVE, South Miami, FL 33143", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order currently on hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features provided; county appraiser data unavailable and no matching emails or attachments found"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, etc.)", "County appraiser data unavailable", "No matching emails found for additional context", "Reason for 'On Hold' status unclear", "Scope of CAD file deliverable not defined (boundary, topo, as-built, etc.)", "Urgency/deadline not specified"], "summary": "B2B order from IK Studios (Alex Gonzalez) for a CAD file at 5729 SW 60th Ave, South Miami, FL 33143 (Miami-Dade County), currently on hold with special pricing applied and minimal property details available."}}</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:51:20.050333+00:00</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
@@ -6835,7 +6959,7 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.807344+00:00</t>
+          <t>2026-06-02T16:51:20.098543+00:00</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6971,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6867,7 +6991,17 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1320 NE 47TH ST</t>
+          <t>1320 NE 47TH ST, OAKLAND PARK, FL 33334</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202601271837249869, "created_at": "2026-01-27T18:37:25", "customer_email": "mattlowe421@gmail.com", "customer_id": 202601271837250347, "customer_name": "Matthew Lowe", "customer_type": "individual", "delivered_at": null, "due_amount": 400.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0367J\nZONE: AE\nELEV: 06 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000277785, "paid": false, "property_address": "1320 NE 47TH ST", "property_city": "OAKLAND PARK", "property_county": "BROWARD COUNTY", "property_lat": "26.1845829", "property_lng": "-80.1294899", "property_state": "FLORIDA", "property_zip": "33334", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-28T19:52:07"}, "success": true, "order_id": "1000277785", "customer_email": "mattlowe421@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "1320 NE 47TH ST", "customer_name": "Matthew Lowe"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Matthew Lowe", "confidence": "HIGH"}, "client_email": {"value": "mattlowe421@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1320 NE 47TH ST, OAKLAND PARK, FL 33334", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested (elevation_cert: false)"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status_code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, etc.)", "Reason for On Hold status not documented", "Reason for special pricing not documented", "No fieldwork or delivery dates scheduled", "County was blank in top-level FTF fields despite being present in nested data \u2014 data inconsistency to review"], "summary": "Individual residential client Matthew Lowe has ordered a Land Survey Only for 1320 NE 47TH ST in Oakland Park, Broward County, FL 33334, with special pricing applied and the order currently on hold at $400 due."}}</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:51:29.516356+00:00</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
@@ -6877,7 +7011,7 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.859079+00:00</t>
+          <t>2026-06-02T16:51:29.616603+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -6555,7 +6555,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6578,16 +6578,37 @@
           <t>524 &amp; 530 South Lakeside Drive, Lake Worth Beach, FL 33460</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "AI pricing failed: Unterminated string starting at: line 26 column 5 (char 2823). Manual review required.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "AI pricing error \u2014 needs manual quote", "flags": ["ai_error"]}</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202602121416087321, "created_at": "2026-02-12T14:18:43", "customer_email": "yuvalmadar@gmail.com", "customer_id": 202602121416088521, "customer_name": "Yuval Madar", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0781G\nZONE: AE\nELEV: 09 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000278594, "paid": true, "property_address": "524 &amp; 530 SOUTH LAKESIDE DRIVE", "property_city": "LAKE WORTH BEACH", "property_county": "Palm Beach County", "property_lat": "26.6088936", "property_lng": "-80.0499696", "property_state": "FL", "property_zip": "33460", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-02-12T17:28:54"}, "success": true, "order_id": "1000278594", "customer_email": "yuvalmadar@gmail.com", "service_type": "CAD", "county": "", "property_address": "524 &amp; 530 SOUTH LAKESIDE DRIVE", "customer_name": "Yuval Madar"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Yuval Madar", "confidence": "HIGH"}, "client_email": {"value": "yuvalmadar@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "524 &amp; 530 South Lakeside Drive, Lake Worth Beach, FL 33460", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "MEDIUM", "notes": "Service type is listed as CAD but no further breakdown of deliverables is provided \u2014 unclear if this is a boundary survey CAD, as-built, or other CAD drafting service"}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); dual parcel address (524 &amp; 530) may indicate two lots", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 no appraiser data, no emails, no aerial info provided"}, "client_tier": {"value": "residential", "confidence": "MEDIUM"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Exact CAD service scope is undefined \u2014 boundary, as-built, topographic, or other?", "Dual address (524 &amp; 530) may indicate two separate parcels \u2014 confirmation needed on whether both are included in scope", "Lot size unknown \u2014 no appraiser data available", "Legal description missing", "Structure square footage unknown", "Property features (pool, structures, etc.) unknown", "Reason for On Hold status not specified", "Special pricing details not itemized \u2014 amount or discount unknown", "No urgency or deadline provided", "No fieldwork date scheduled", "Customer data object is empty \u2014 no phone number or additional contact info"], "summary": "Individual client Yuval Madar has placed a paid CAD order (On Hold) for a dual-parcel property at 524 &amp; 530 South Lakeside Drive, Lake Worth Beach, FL in Palm Beach County, with special pricing applied but scope, lot details, and hold reason still undefined."}}</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1780419359269</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>2026-06-02T16:42:09.795889+00:00</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:58:08.216204+00:00</t>
+        </is>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
       <c r="T106" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.407352+00:00</t>
@@ -6595,7 +6616,7 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>2026-06-02T16:42:09.842992+00:00</t>
+          <t>2026-06-02T16:58:08.265583+00:00</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6628,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6630,16 +6651,37 @@
           <t>4417 S Flagler Dr, West Palm Beach, FL 33405</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "CAD Release", "description": "Release of existing CAD survey file for 4417 S Flagler Dr, West Palm Beach, FL 33405 (Lot 26, Worth Court 1st Addition, PB 24/85) to Smith and Moore Architects, Inc. for architectural use. Based on client negotiated rate.", "amount": 450.0}], "pricing_reasoning": "This is a B2B CAD Release order \u2014 delivery of an existing CAD file to an architect (Jon Moore / Smith Moore Architects), not a new field survey. The client (Smith and Moore Architects, Inc.) has a management-negotiated flat rate of $450.00 which is used as the base. No field work is being performed, so lot-size complexity upcharges, EC fees, and FEMA/flood zone surcharges do not apply to this deliverable type. The lot is 0.45 acres (AE zone, Palm Beach County) and prior surveys exist per the duplicate order flags, confirming an existing CAD file is available for release.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "Two issues require human review before invoicing: (1) Client name discrepancy \u2014 the order notes reference 'Jon Moore (Smith Moore Architects)' but the company on file is 'Smith and Moore Architects, Inc.' \u2014 confirm these are the same entity and that Jon Moore is authorized to receive the CAD file. (2) The negotiated rate of $450.00 is noted as having 'special pricing applied' per order notes; management should confirm this rate is appropriate for a CAD Release specifically and not just for a full boundary survey. Additionally, this order has three flagged duplicate prior orders at the same address and folio, which should be reviewed to confirm the correct/most current CAD file is being released.", "flags": ["DUPLICATE_WARNING: Order 1000093001 \u2014 4417 S Flagler Dr, Palm Beach County \u2014 service: Land Survey and Elevation \u2014 same location (26.6723763, -80.0486461) and folio 74434403030000260. Existing CAD file likely originates from this order.", "DUPLICATE_WARNING: Order 1000136989 \u2014 4417 S Flagler Dr, Palm Beach County \u2014 service: Elevation Certificate \u2014 same location and folio. EC data exists on file.", "DUPLICATE_WARNING: Order 1000216642 \u2014 4417 S Flagler Dr, Palm Beach County \u2014 service: Land Survey Only \u2014 same location and folio. Most recent boundary survey CAD file may originate here; confirm which file version is being released.", "CLIENT_NAME_DISCREPANCY: Order notes reference 'Smith Moore Architects' but company record is 'Smith and Moore Architects, Inc.' \u2014 human verification required before releasing CAD file.", "SPECIAL_PRICING_NOTED: Order notes indicate special pricing applied. Management confirmation that $450.00 negotiated rate applies to CAD Release (not just full survey) is recommended.", "ORDER_COUNT_ZERO: Client tier is OLD_TITLE but order count shows 0 orders with NexGen \u2014 verify client history and tier assignment are correct."]}</t>
+        </is>
+      </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202411212009461034, "created_at": "2026-02-11T15:25:01", "customer_email": "jon@Smithmoorearchitects.com", "customer_id": 202411212010394766, "customer_name": "Jon Moore", "customer_type": "b2b", "delivered_at": "2026-02-13T14:09:47", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0591G\nZONE: AE\nELEV: 08 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000278523, "paid": true, "property_address": "4417 S FLAGLER DR", "property_city": "WEST PALM BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.6724036", "property_lng": "-80.0486901", "property_state": "FL", "property_zip": "33405", "service_type": "CAD Release", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-02-13T14:09:47"}, "success": true, "order_id": "1000278523", "customer_email": "jon@Smithmoorearchitects.com", "service_type": "CAD Release", "county": "", "property_address": "4417 S FLAGLER DR", "customer_name": "MAria Mcardle"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Jon Moore", "confidence": "MEDIUM"}, "client_email": {"value": "jon@Smithmoorearchitects.com", "confidence": "HIGH"}, "property_address": {"value": "4417 S Flagler Dr, West Palm Beach, FL 33405", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD Release"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD Release; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; flood zone AE (panel 12099C0591G, base elevation 8 ft, effective 12/20/2024)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: FTF order data shows 'Jon Moore' but outer envelope shows 'MAria Mcardle' \u2014 needs human verification", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, structures, etc.) unknown \u2014 no appraiser or aerial data available", "No matching emails found to cross-reference order details", "County appraiser data unavailable \u2014 no parcel or ownership data to verify"], "summary": "B2B CAD Release order for Jon Moore (Smith Moore Architects) at 4417 S Flagler Dr, West Palm Beach, FL 33405 in a Flood Zone AE area, delivered on 2026-02-13 with special pricing applied and a client name discrepancy requiring human review."}}</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1780419489260</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>2026-06-02T16:42:19.918729+00:00</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:58:30.987135+00:00</t>
+        </is>
+      </c>
+      <c r="R107" t="n">
+        <v>450</v>
+      </c>
       <c r="T107" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.456769+00:00</t>
@@ -6647,7 +6689,7 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>2026-06-02T16:42:19.965271+00:00</t>
+          <t>2026-06-02T16:58:31.038699+00:00</t>
         </is>
       </c>
     </row>
@@ -6659,7 +6701,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6682,16 +6724,37 @@
           <t>747 11TH CT SW, Vero Beach, FL 32962</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "CAD / Boundary Survey", "description": "Standard boundary survey with CAD deliverable for LOT 18, BLOCK J, OSLO PARK SUBDIVISION, Indian River County. Small residential lot (0.11 ac), platted subdivision, FEMA Zone X (no flood zone complexity), non-commercial, no Monroe County mobilization surcharge applicable.", "amount": 450.0}], "pricing_reasoning": "Carey Law Group PA holds a negotiated management-approved base rate of $450.00, which is applied directly as the survey price. The property is a small (0.11 ac) platted residential lot in Indian River County with a clean legal description (lot and block, no metes and bounds), FEMA Zone X (no EC required or flood complexity), and no flags for pool, waterfront, heavy vegetation, or acreage upcharges \u2014 so no complexity surcharges are warranted. The order is priced at the flat negotiated client rate of $450.00.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE_DUPLICATE: Order 1000275259 covers the same property address (747 11TH CT SW, Indian River County), same GPS coordinates (27.589697, -80.3964589), and same Folio/MLS (33392400011001000018.0) with a service of Land Survey and Elevation \u2014 human review required to confirm whether this CAD order is a standalone deliverable reuse, a re-order, or a duplicate that should be merged or cancelled.", "ORDER_ON_HOLD: Per order notes, this order is currently On Hold with a $200 balance due and special pricing applied \u2014 confirm with management that the $450.00 negotiated rate satisfies the stated $200 balance or whether the balance represents a partial payment on a previously agreed total.", "INCOMPLETE_SCOPE: Order notes indicate property and scope details are largely incomplete pending human review \u2014 verify no additional services (e.g., Elevation Certificate, topographic survey) are expected beyond the CAD boundary survey deliverable."]}</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 201801311054240045, "created_at": "2026-02-09T19:57:53", "customer_email": "richard@rcareylaw.com", "customer_id": 201909101546171936, "customer_name": "Richard Carey", "customer_type": "b2b", "delivered_at": null, "due_amount": 200.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12061C0359J\nZONE: X\nEFF: 01/26/2023", "invoiced": false, "order_id": 1000278419, "paid": false, "property_address": "747 11TH CT SW", "property_city": "VERO BEACH", "property_county": "Indian River County", "property_lat": "27.589697", "property_lng": "-80.3964589", "property_state": "FL", "property_zip": "32962", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-06T16:29:04"}, "success": true, "order_id": "1000278419", "customer_email": "richard@rcareylaw.com", "service_type": "CAD", "county": "", "property_address": "747 11TH CT SW", "customer_name": "Carey Law Group PA"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Carey Law Group PA", "confidence": "MEDIUM"}, "client_email": {"value": "richard@rcareylaw.com", "confidence": "HIGH"}, "property_address": {"value": "747 11TH CT SW, Vero Beach, FL 32962", "confidence": "HIGH"}, "property_county": {"value": "Indian River County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type is listed as CAD; no additional services specified"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 no appraiser or document source available", "Structure square footage unknown", "Property features (pool, shed, driveway, structures) unknown \u2014 no aerial, appraiser, or email data", "Client name discrepancy: order contact is 'Richard Carey' but company/invoice name appears to be 'Carey Law Group PA' \u2014 confirm billing name", "Reason for On Hold status unknown \u2014 needs human review", "Fieldwork and delivery dates not yet scheduled", "Scope of CAD deliverable not specified (boundary, topo, as-built, etc.)"], "summary": "B2B CAD survey order for Carey Law Group PA at 747 11th CT SW, Vero Beach, FL 32962 (Indian River County), currently On Hold with special pricing applied and a $200 balance due; property and scope details are largely incomplete pending human review."}}</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1780419529919</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>2026-06-02T16:42:30.937410+00:00</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:58:50.504849+00:00</t>
+        </is>
+      </c>
+      <c r="R108" t="n">
+        <v>450</v>
+      </c>
       <c r="T108" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.507129+00:00</t>
@@ -6699,7 +6762,7 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>2026-06-02T16:42:30.984099+00:00</t>
+          <t>2026-06-02T16:58:50.555270+00:00</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7086,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7043,7 +7106,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>715 SE 2ND AVE</t>
+          <t>715 SE 2nd Ave, Delray Beach, FL 33483</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202601141812154089, "created_at": "2026-01-27T15:48:52", "customer_email": "michaelsanzen@gmail.com", "customer_id": 202601141812154237, "customer_name": "Michael Sanzen", "customer_type": "individual", "delivered_at": "2026-01-27T22:16:31", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0979G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000277758, "paid": true, "property_address": "715 SE 2ND AVE", "property_city": "DELRAY BEACH", "property_county": "Palm Beach County", "property_lat": "26.4505752", "property_lng": "-80.0707206", "property_state": "FL", "property_zip": "33483", "service_type": "Quote", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-27T22:16:31"}, "success": true, "order_id": "1000277758", "customer_email": "michaelsanzen@gmail.com", "service_type": "Quote", "county": "", "property_address": "715 SE 2ND AVE", "customer_name": "Michael Sanzen"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Michael Sanzen", "confidence": "HIGH"}, "client_email": {"value": "michaelsanzen@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "715 SE 2nd Ave, Delray Beach, FL 33483", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., boundary, elevation cert, topographic) has been identified. Human review needed to determine what was quoted."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial imagery, or email attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service(s) requested are unknown \u2014 'Quote' is not a deliverable service type", "No lot size or parcel dimensions available", "No legal description available", "No structure square footage available", "No property features identified (pool, outbuildings, etc.)", "No special requirements or notes from client", "County property appraiser data unavailable", "No matching emails found to clarify scope", "Elevation certificate not requested \u2014 confirm if needed given flood zone X (low risk but still noted)"], "summary": "Individual residential client Michael Sanzen submitted a quote request for a property at 715 SE 2nd Ave, Delray Beach, FL (Palm Beach County), but the specific survey services requested have not been identified and require human follow-up."}}</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:57:04.251852+00:00</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -7053,7 +7126,7 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.910495+00:00</t>
+          <t>2026-06-02T16:57:04.301181+00:00</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7138,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7085,7 +7158,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>717 LAYNE BLVD</t>
+          <t>717 Layne Blvd, Hallandale Beach, FL 33009</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202601061948402508, "created_at": "2026-01-27T14:08:01", "customer_email": "ferusa@me.com", "customer_id": 202601061948402608, "customer_name": "Fernando Lupica Tondo", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0732J\nZONE: AE\nELEV: 07 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000277746, "paid": true, "property_address": "717 LAYNE BLVD", "property_city": "HALLANDALE BEACH", "property_county": "BROWARD COUNTY", "property_lat": "25.9754542", "property_lng": "-80.1327428", "property_state": "FL", "property_zip": "33009", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-28T20:46:09"}, "success": true, "order_id": "1000277746", "customer_email": "ferusa@me.com", "service_type": "CAD file", "county": "", "property_address": "717 LAYNE BLVD", "customer_name": "Fernando Lupica Tondo"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Fernando Lupica Tondo", "confidence": "HIGH"}, "client_email": {"value": "ferusa@me.com", "confidence": "HIGH"}, "property_address": {"value": "717 Layne Blvd, Hallandale Beach, FL 33009", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD file; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order status is On Hold; property is in FEMA Flood Zone AE (Panel 12011C0732J, Elev 07 FT, Eff 07/31/2024)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no emails or aerial data provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser or parcel data available", "Legal description missing \u2014 no appraiser lookup performed", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, etc.)", "Order is On Hold \u2014 reason for hold not specified; needs human review", "No fieldwork date scheduled", "Scope of CAD file not clarified (boundary CAD, as-built CAD, etc.)", "Special pricing applied but pricing amount/reason not documented"], "summary": "Individual residential client Fernando Lupica Tondo has requested a CAD file for 717 Layne Blvd, Hallandale Beach, FL (Broward County), a property in FEMA Flood Zone AE; the order is currently On Hold with special pricing applied and no fieldwork scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:57:14.712157+00:00</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -7095,7 +7178,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:14.962330+00:00</t>
+          <t>2026-06-02T16:57:14.762691+00:00</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7190,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7127,7 +7210,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2401 28TH AVE N</t>
+          <t>2401 28TH AVE N, ST. PETERSBURG, FL 33713</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201801311056152653, "created_at": "2026-01-26T21:55:01", "customer_email": "mkreuzman@strosslaw.com", "customer_id": 202207051448472795, "customer_name": "Mariann  Kreuzman", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12103C0216G\nZONE: X\nEFF: 09/03/2003", "invoiced": false, "order_id": 1000277740, "paid": false, "property_address": "2401 28TH AVE N", "property_city": "ST. PETERSBURG", "property_county": "PINELLAS COUNTY", "property_lat": "27.7975988", "property_lng": "-82.66498560000001", "property_state": "FL", "property_zip": "33713", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-02-05T07:23:13"}, "success": true, "order_id": "1000277740", "customer_email": "mkreuzman@strosslaw.com", "service_type": "Land Survey Only", "county": "", "property_address": "2401 28TH AVE N", "customer_name": "Stross Law Firm"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Stross Law Firm", "confidence": "MEDIUM"}, "client_email": {"value": "mkreuzman@strosslaw.com", "confidence": "HIGH"}, "property_address": {"value": "2401 28TH AVE N, ST. PETERSBURG, FL 33713", "confidence": "HIGH"}, "property_county": {"value": "Pinellas County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data"}, "special_requirements": {"value": "Special pricing applies; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no matching emails found"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order contact is 'Mariann Kreuzman' but company name listed as 'Stross Law Firm' \u2014 confirm billing name", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fences, driveways, etc.)", "Reason for 'On Hold' status not specified \u2014 needs human review", "Special pricing terms not defined \u2014 confirm pricing with team", "No fieldwork or delivery dates scheduled", "County was blank in outer FTF object despite being present in nested data \u2014 verify data integrity"], "summary": "A B2B land survey order for Stross Law Firm at 2401 28th Ave N, St. Petersburg, FL 33713 (Pinellas County) is currently on hold with special pricing applied and no fieldwork or invoice details yet established."}}</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:57:25.446880+00:00</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -7137,7 +7230,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.014241+00:00</t>
+          <t>2026-06-02T16:57:25.498065+00:00</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7242,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7169,7 +7262,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>415 44TH ST</t>
+          <t>415 44TH ST, WEST PALM BEACH, FL 33407</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202601261503004961, "created_at": "2026-01-26T15:07:37", "customer_email": "joseph@r3health.co", "customer_id": 202601261503006047, "customer_name": "Joseph Radich", "customer_type": "individual", "delivered_at": "2026-01-28T17:48:11", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0393G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000277674, "paid": true, "property_address": "415 44TH ST", "property_city": "WEST PALM BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.7522405", "property_lng": "-80.05344509999999", "property_state": "FL", "property_zip": "33407", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-28T17:48:11"}, "success": true, "order_id": "1000277674", "customer_email": "joseph@r3health.co", "service_type": "Land Survey Only", "county": "", "property_address": "415 44TH ST", "customer_name": "Joseph Radich"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Joseph Radich", "confidence": "HIGH"}, "client_email": {"value": "joseph@r3health.co", "confidence": "HIGH"}, "property_address": {"value": "415 44TH ST, WEST PALM BEACH, FL 33407", "confidence": "HIGH"}, "property_county": {"value": "PALM BEACH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, structures) unknown \u2014 no aerial or appraiser data", "No county provided in top-level FTF fields (though property_county is in order data)", "Reason for special pricing not documented", "No fieldwork date scheduled (fieldwork_at is null)", "No invoice has been generated despite order being delivered and paid"], "summary": "Delivered and paid Land Survey Only order for individual client Joseph Radich at 415 44TH ST, West Palm Beach, FL (Palm Beach County, Flood Zone X), with special pricing applied and no invoice yet generated."}}</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:57:34.574856+00:00</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
@@ -7179,7 +7282,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.067169+00:00</t>
+          <t>2026-06-02T16:57:34.624664+00:00</t>
         </is>
       </c>
     </row>
@@ -7191,7 +7294,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7206,12 +7309,22 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vianeybert  Toussaint</t>
+          <t>Vianeybert Toussaint</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1210 HOLMES AVE</t>
+          <t>1210 Holmes Ave, Tampa, FL 33605</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510201325368864, "created_at": "2026-01-23T14:23:48", "customer_email": "vianeyb14@gmail.com", "customer_id": 202510201325370288, "customer_name": "Vianeybert  Toussaint", "customer_type": "individual", "delivered_at": "2026-01-28T16:39:12", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12057C0352J\nZONE: X\nEFF: 10/07/2021", "invoiced": false, "order_id": 1000277591, "paid": true, "property_address": "1210 HOLMES AVE", "property_city": "TAMPA", "property_county": "HILLSBOROUGH COUNTY", "property_lat": "27.9703369", "property_lng": "-82.44645349999999", "property_state": "FL", "property_zip": "33605", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-28T16:39:12"}, "success": true, "order_id": "1000277591", "customer_email": "vianeyb14@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "1210 HOLMES AVE", "customer_name": "Vianeybert  Toussaint"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Vianeybert Toussaint", "confidence": "HIGH"}, "client_email": {"value": "vianeyb14@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1210 Holmes Ave, Tampa, FL 33605", "confidence": "HIGH"}, "property_county": {"value": "Hillsborough County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as Land Survey Only in FTF order data"}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no matching emails found"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, etc.)", "Reason for special pricing not documented", "Fieldwork date not yet scheduled (fieldwork_at is null)", "Invoice has not been generated (invoiced: false)"], "summary": "Residential land survey order for Vianeybert Toussaint at 1210 Holmes Ave, Tampa FL 33605 (Hillsborough County), already delivered and paid with special pricing applied, but property details and legal description are unavailable pending appraiser data."}}</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:57:43.158138+00:00</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
@@ -7221,7 +7334,7 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.129809+00:00</t>
+          <t>2026-06-02T16:57:43.250014+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -6774,7 +6774,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6797,16 +6797,37 @@
           <t>745 11TH CT SW</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "CAD Survey - Boundary/Land Survey", "description": "CAD deliverable for boundary/land survey at 745 11th CT SW, Indian River County. Lot 17, Block J, Oslo Park Subdivision \u2014 platted lot, 0.11 acres, FEMA Zone X (no EC required). Client negotiated rate applied.", "amount": 450.0}], "pricing_reasoning": "Service type is CAD, interpreted as a standard boundary/land survey CAD deliverable for an established title company client (Carey Law Group PA) with a management-negotiated flat rate of $450.00. The lot is 0.11 acres (small platted subdivision lot), FEMA Zone X (no flood/EC component warranted), Indian River County (no Monroe premium), and the legal description is a simple lot-and-block reference with no metes-and-bounds complexity. No pool, waterfront, heavy vegetation, or acreage upcharges are supported by the available data. No complexity upcharges are applied.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "Order notes explicitly flag critical gaps: undefined CAD scope (boundary survey vs. as-built vs. other deliverable type is unconfirmed), incomplete original address submission, missing county in original order, and no supporting property data provided by client. Additionally, a probable duplicate exists (Order 1000275257) for the same address, county, coordinates, and folio \u2014 which includes a Land Survey AND Elevation Certificate service. Management should confirm whether this CAD order is a standalone new request, a duplicate, or a CAD-only add-on to the prior order before proceeding. Price of $450.00 is proposed contingent on scope clarification.", "flags": ["POSSIBLE_DUPLICATE: Order 1000275257 \u2014 same address (745 11TH CT SW), same county (Indian River), same coordinates (27.589835, -80.396457), same folio (33392400011001000017.0) \u2014 service on prior order was Land Survey and Elevation Certificate. Human review required before invoicing.", "SCOPE_UNDEFINED: Order notes confirm CAD scope is not clearly defined. Confirm whether this is a boundary survey CAD, as-built CAD, or another deliverable type.", "DATA_GAPS: Original order submitted with missing county and incomplete address \u2014 data was resolved but client intake quality is low; confirm all property details with Carey Law Group PA.", "NO_EC_REQUIRED: FEMA Zone X \u2014 no Elevation Certificate warranted unless client specifically requests one."]}</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>{"ftf_order": {"order_id": "1000278416", "customer_email": "richard@rcareylaw.com", "service_type": "CAD", "county": "", "property_address": "745 11TH CT SW", "customer_name": "Carey Law Group PA"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Carey Law Group PA", "confidence": "HIGH"}, "client_email": {"value": "richard@rcareylaw.com", "confidence": "HIGH"}, "property_address": {"value": "745 11TH CT SW", "confidence": "HIGH"}, "property_county": {"value": "", "confidence": "LOW"}, "services_requested": {"value": ["CAD"], "confidence": "MEDIUM", "notes": "Service type listed as CAD \u2014 likely CAD drafting or CAD survey drawing; specific deliverable scope unclear without further context"}, "special_requirements": {"value": "", "confidence": "LOW"}, "lot_size": {"value": "", "confidence": "LOW"}, "legal_description": {"value": "", "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments found"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Property county not provided \u2014 needed to look up appraiser data and verify address", "Full property address may be incomplete (no city, state, or ZIP)", "CAD service scope not defined \u2014 clarify what CAD deliverable is expected (e.g., boundary survey CAD, as-built CAD, etc.)", "Lot size unknown", "Legal description unknown", "Structure square footage unknown", "Property features unknown (pool, shed, structures, etc.)", "No special requirements noted", "Urgency/rush status unknown", "No matching emails or supporting documents found"], "summary": "B2B CAD order from Carey Law Group PA for property at 745 11th CT SW, with critical gaps including missing county, incomplete address, undefined CAD scope, and no supporting property data."}}</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1780419844979</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>2026-06-02T16:43:10.742313+00:00</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:04:06.185622+00:00</t>
+        </is>
+      </c>
+      <c r="R109" t="n">
+        <v>450</v>
+      </c>
       <c r="T109" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.604547+00:00</t>
@@ -6814,7 +6835,7 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>2026-06-02T16:43:10.787470+00:00</t>
+          <t>2026-06-02T17:04:06.237551+00:00</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6847,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6849,16 +6870,37 @@
           <t>735 11TH CT SW, VERO BEACH, FL 32962</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "CAD / Boundary Survey", "description": "CAD drafting and boundary survey for Lot 16, Block J, Oslo Park, 735 11th Ct SW, Vero Beach, Indian River County. 0.23-acre platted residential lot. Negotiated B2B rate applied for Carey Law Group PA (OLD_TITLE tier, 97 orders).", "amount": 450.0}], "pricing_reasoning": "This is a standard CAD/boundary survey order for an established title company client (Carey Law Group PA) with a management-agreed negotiated rate of $450.00. The property is a small 0.23-acre platted residential lot in Indian River County with a simple lot description (platted lot, no metes and bounds), FEMA Zone X (no flood zone upcharge applicable), no commercial flag, no pool or waterfront indicators evident, and no Monroe County mobilization. No complexity upcharges are warranted by the available data. The order notes confirm special pricing of $200 due balance on hold \u2014 however, the negotiated rate of $450.00 is the management-approved base for this client and supersedes any partial-balance notation; the $200 on-hold balance is flagged for human review rather than used as the invoice total.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE_DUPLICATE: Order 1000275256 shares the same address (735 11TH CT SW, Indian River County), same coordinates (27.5900935, -80.396456), and same Folio/MLS (33392400011001000016.0). Service on that order was Land Survey and Elevation. Human review required to confirm whether this CAD order is a follow-on deliverable to that prior survey or a true duplicate billing.", "ON_HOLD_BALANCE: Order notes reference a $200 due balance with special pricing applied and the order currently on hold. It is unclear whether the $200 represents a remaining balance on a partially paid $450 invoice or a separately negotiated one-time price. Management should confirm the correct billing amount before invoicing.", "MISSING_SCOPE_DETAIL: Order notes flag that CAD scope details, property features, and lot size were originally absent. Lot size and legal description have since been populated (0.23 ac, platted lot). Confirm with client or field crew whether any additional CAD deliverables (e.g., title exhibit, sketch, digitized boundary only) are expected beyond standard boundary CAD output."]}</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 201801311054240045, "created_at": "2026-02-09T19:42:01", "customer_email": "richard@rcareylaw.com", "customer_id": 201909101546171936, "customer_name": "Richard Carey", "customer_type": "b2b", "delivered_at": null, "due_amount": 200.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12061C0359J\nZONE: X\nEFF: 01/26/2023", "invoiced": false, "order_id": 1000278415, "paid": false, "property_address": "735 11TH CT SW", "property_city": "VERO BEACH", "property_county": "INDIAN RIVER COUNTY", "property_lat": "27.5901062", "property_lng": "-80.3964254", "property_state": "FL", "property_zip": "32962", "service_type": "CAD", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-03-06T16:29:04"}, "success": true, "order_id": "1000278415", "customer_email": "richard@rcareylaw.com", "service_type": "CAD", "county": "", "property_address": "735 11TH CT SW", "customer_name": "Carey Law Group PA"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Carey Law Group PA", "confidence": "MEDIUM"}, "client_email": {"value": "richard@rcareylaw.com", "confidence": "HIGH"}, "property_address": {"value": "735 11TH CT SW, VERO BEACH, FL 32962", "confidence": "HIGH"}, "property_county": {"value": "INDIAN RIVER COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type is listed as CAD; no additional services indicated in the order data"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features provided; county appraiser unavailable and no matching emails or attachments found"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name discrepancy: order body lists 'Richard Carey' but customer_name override is 'Carey Law Group PA' \u2014 confirm correct billing name", "Lot size unknown \u2014 county appraiser unavailable", "Legal description unknown \u2014 county appraiser unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fences, driveways, etc.)", "Reason for On Hold status not documented", "Scope of CAD deliverable not specified (boundary, topo, as-built, etc.)", "No fieldwork or delivery dates scheduled"], "summary": "B2B CAD order for Carey Law Group PA at 735 11TH CT SW, Vero Beach, FL (Indian River County) is currently On Hold with special pricing applied and a $200 due balance, but lacks lot size, legal description, property features, and CAD scope details."}}</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1780419867691</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>2026-06-02T16:50:48.453503+00:00</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:04:28.520395+00:00</t>
+        </is>
+      </c>
+      <c r="R110" t="n">
+        <v>450</v>
+      </c>
       <c r="T110" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.654732+00:00</t>
@@ -6866,7 +6908,7 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>2026-06-02T16:50:48.501321+00:00</t>
+          <t>2026-06-02T17:04:28.569626+00:00</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6920,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6901,16 +6943,37 @@
           <t>1195 16TH AVE SW, VERO BEACH, FL 32962</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "CAD / Boundary Survey", "description": "CAD deliverable for boundary survey at 1195 16th Ave SW, Vero Beach, FL 32962 \u2014 Lot 13, Block O, Oslo Park Unit No. 2, Indian River County. Small residential lot (0.11 ac), FEMA Zone X (no EC required), vacant/unimproved land, no complexity upcharges warranted.", "amount": 450.0}], "pricing_reasoning": "Carey Law Group PA is an established OLD_TITLE client with a management-negotiated flat rate of $450.00, which serves as the controlling base price for this order. The property is a small (0.11 ac), vacant, unimproved residential lot in Indian River County \u2014 FEMA Zone X means no Elevation Certificate is needed, the legal description is a simple platted lot (no metes-and-bounds upcharge), and no pool, waterfront, heavy vegetation, or other complexity factors are evident. No upcharges are applicable, so the invoice is $450.00 flat.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: This order shares the same property address (1195 16th Ave SW, Indian River County), coordinates (27.581642, -80.4023179), and Folio/MLS (33392600002001500013.0) with three other orders: 1000275260 (Land Survey and Elevation), 1000279875 (Land Survey Only, CAD), and 1000283261 (Land Survey Only). Human review is recommended to confirm this is not a duplicate billing or redundant field visit before invoicing.", "NOTE: Order notes reference 'special pricing applied' and flag missing lot size, legal description, property features, and invoice documentation \u2014 all have been resolved from DB data and legal description provided. No additional action required unless client-facing documentation needs to be regenerated.", "NOTE: No pricing history records were available for this client/property combination to cross-validate against prior invoices."]}</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 201801311054240045, "created_at": "2026-02-09T19:33:53", "customer_email": "richard@rcareylaw.com", "customer_id": 201909101546171936, "customer_name": "Richard Carey", "customer_type": "b2b", "delivered_at": "2026-03-20T18:48:37", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12061C0359J\nZONE: X\nEFF: 01/26/2023", "invoiced": false, "order_id": 1000278414, "paid": true, "property_address": "1195 16TH AVE SW", "property_city": "VERO BEACH", "property_county": "Indian River County", "property_lat": "27.581642", "property_lng": "-80.4023179", "property_state": "FL", "property_zip": "32962", "service_type": "CAD", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-05-12T18:14:21"}, "success": true, "order_id": "1000278414", "customer_email": "richard@rcareylaw.com", "service_type": "CAD", "county": "", "property_address": "1195 16TH AVE SW", "customer_name": "Carey Law Group PA"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Carey Law Group PA", "confidence": "MEDIUM"}, "client_email": {"value": "richard@rcareylaw.com", "confidence": "HIGH"}, "property_address": {"value": "1195 16TH AVE SW, VERO BEACH, FL 32962", "confidence": "HIGH"}, "property_county": {"value": "Indian River County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD"], "confidence": "HIGH", "notes": "Service type is listed as CAD; no additional services indicated in the order data"}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name discrepancy: order body says 'Carey Law Group PA' but customer record says 'Richard Carey' \u2014 confirm correct billing name", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, fences, driveways, etc.) unknown \u2014 no aerial or appraiser data available", "County appraiser data unavailable \u2014 Indian River County lookup was not performed", "Fieldwork date is null \u2014 unclear if fieldwork was completed or if CAD is based on existing data", "Specific CAD deliverable scope unclear (boundary, topo, site plan, etc.)", "Invoice has not been sent despite order being delivered and marked paid \u2014 verify billing status"], "summary": "B2B CAD order for Carey Law Group PA (Richard Carey) at 1195 16TH AVE SW, Vero Beach, FL 32962 in Indian River County, delivered on 2026-03-20 with special pricing applied, but missing lot size, legal description, property features, and invoice documentation."}}</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1780419888125</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>2026-06-02T16:50:59.338170+00:00</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:04:48.645386+00:00</t>
+        </is>
+      </c>
+      <c r="R111" t="n">
+        <v>450</v>
+      </c>
       <c r="T111" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.705755+00:00</t>
@@ -6918,7 +6981,7 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>2026-06-02T16:50:59.385439+00:00</t>
+          <t>2026-06-02T17:04:48.695639+00:00</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7409,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7366,7 +7429,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>12035 POLO CLUB RD</t>
+          <t>12035 Polo Club Rd, Wellington, FL 33414</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202601141641564449, "created_at": "2026-01-14T11:50:03", "customer_email": "treefolium@icloud.com", "customer_id": 202601141642491223, "customer_name": "Johana Payot", "customer_type": "b2b", "delivered_at": "2026-01-20T15:15:58", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0563F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000277194, "paid": true, "property_address": "12035 POLO CLUB RD", "property_city": "WELLINGTON", "property_county": "Palm Beach County", "property_lat": "26.6413026", "property_lng": "-80.2372546", "property_state": "FL", "property_zip": "33414", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-20T15:15:58"}, "success": true, "order_id": "1000277194", "customer_email": "treefolium@icloud.com", "service_type": "Quote", "county": "", "property_address": "12035 POLO CLUB RD", "customer_name": "Tree Folium Landscape Co."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Tree Folium Landscape Co.", "confidence": "HIGH"}, "client_email": {"value": "treefolium@icloud.com", "confidence": "HIGH"}, "property_address": {"value": "12035 Polo Club Rd, Wellington, FL 33414", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., boundary, topographic, elevation certificate) has been identified. Needs clarification."}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not defined \u2014 'Quote' is not a deliverable service", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, outbuildings, etc.)", "No matching emails found \u2014 unable to confirm scope from client communications", "Fieldwork date not scheduled", "Invoice has not been sent \u2014 billing details incomplete", "Client contact name discrepancy: FTF order shows 'Johana Payot' as customer name but company name is 'Tree Folium Landscape Co.' \u2014 confirm correct billing contact"], "summary": "A B2B quote order for Tree Folium Landscape Co. at 12035 Polo Club Rd, Wellington, FL (Palm Beach County) has been delivered with special pricing applied, but the specific survey service requested has not been identified and key property details are missing."}}</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:03:02.322969+00:00</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -7376,7 +7449,7 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.226892+00:00</t>
+          <t>2026-06-02T17:03:02.372963+00:00</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7461,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7408,7 +7481,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>12952 MIZNER WAY</t>
+          <t>12952 Mizner Way, Wellington, FL 33414</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202601122012476131, "created_at": "2026-01-12T15:16:00", "customer_email": "jeremy@atfranco.com", "customer_id": 202601122013460244, "customer_name": "Jeremy Harrissmith", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0544F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000277088, "paid": true, "property_address": "12952 MIZNER WAY", "property_city": "WELLINGTON", "property_county": "Palm Beach County", "property_lat": "26.64221", "property_lng": "-80.2515763", "property_state": "FL", "property_zip": "33414", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000277088", "customer_email": "jeremy@atfranco.com", "service_type": "Land Survey Only", "county": "", "property_address": "12952 MIZNER WAY", "customer_name": "Franco &amp; Associates"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Franco &amp; Associates", "confidence": "MEDIUM"}, "client_email": {"value": "jeremy@atfranco.com", "confidence": "HIGH"}, "property_address": {"value": "12952 Mizner Way, Wellington, FL 33414", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing flagged; order currently On Hold (status_code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments found"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: FTF order lists 'Jeremy Harrissmith' as customer_name but outer payload lists 'Franco &amp; Associates' \u2014 needs human verification", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, etc.)", "Reason for On Hold status not specified", "Scope of 'Land Survey Only' not clarified (boundary, topographic, etc.)", "No fieldwork date scheduled", "No invoice sent \u2014 pricing needs to be confirmed given special_pricing flag"], "summary": "B2B Land Survey Only order for 12952 Mizner Way, Wellington FL (Palm Beach County) placed by Franco &amp; Associates, currently On Hold with special pricing flagged and no fieldwork scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:03:12.222586+00:00</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
@@ -7418,7 +7501,7 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.279946+00:00</t>
+          <t>2026-06-02T17:03:12.272359+00:00</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7513,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7445,12 +7528,22 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>mark Ebersolm</t>
+          <t>Maurece Williams</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>10801 SW FOX BROWN RD</t>
+          <t>10801 SW FOX BROWN RD, INDIANTOWN, FL 34956</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202601162040440121, "created_at": "2026-01-12T13:15:00", "customer_email": "maurecewilliams@yahoo.com", "customer_id": 202601162040441013, "customer_name": "Maurece Williams", "customer_type": "individual", "delivered_at": null, "due_amount": 8500.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12085C0250G\nZONE: X\nEFF: 03/16/2015", "invoiced": false, "order_id": 1000277069, "paid": false, "property_address": "10801 SW FOX BROWN RD", "property_city": "INDIANTOWN", "property_county": "Martin County", "property_lat": "27.0757825", "property_lng": "-80.5123416", "property_state": "FL", "property_zip": "34956", "service_type": "Boundary Survey", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-20T17:05:07"}, "success": true, "order_id": "1000277069", "customer_email": "maurecwilliams@yahoo.com", "service_type": "Boundary Survey", "county": "", "property_address": "10801 SW FOX BROWN RD", "customer_name": "mark Ebersolm"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Maurece Williams", "confidence": "MEDIUM"}, "client_email": {"value": "maurecewilliams@yahoo.com", "confidence": "MEDIUM"}, "property_address": {"value": "10801 SW FOX BROWN RD, INDIANTOWN, FL 34956", "confidence": "HIGH"}, "property_county": {"value": "Martin County", "confidence": "HIGH"}, "services_requested": {"value": ["Boundary Survey"], "confidence": "HIGH", "notes": "Explicitly stated in order data. Elevation certificate is not requested (elevation_cert: false)."}, "special_requirements": {"value": "Special pricing applied. Order is currently On Hold (status_code 11).", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available. County appraiser unavailable and no aerial or email data provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: FTF order data shows 'Maurece Williams' but outer FTF payload shows 'mark Ebersolm' \u2014 requires human verification", "Client email conflict: order data shows 'maurecewilliams@yahoo.com' but outer payload shows 'maurecwilliams@yahoo.com' (possible typo) \u2014 requires human verification", "Lot size unknown \u2014 no appraiser or parcel data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, structures, etc.) unknown \u2014 no aerial or appraiser data", "Reason for On Hold status not documented", "Fieldwork and delivery dates not yet scheduled", "No matching customer email records found \u2014 customer identity unverified"], "summary": "Boundary survey order for Maurece Williams (identity unverified due to name/email conflicts) at 10801 SW Fox Brown Rd, Indiantown, FL 34956 (Martin County), currently On Hold with special pricing applied and $8,500 due."}}</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:03:23.369002+00:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
@@ -7460,7 +7553,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.333845+00:00</t>
+          <t>2026-06-02T17:03:23.420786+00:00</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7565,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7492,7 +7585,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>10651 SW 67TH CT</t>
+          <t>10651 SW 67TH CT, MIAMI, FL 33156</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508142004390852, "created_at": "2026-01-12T08:46:00", "customer_email": "jgoldstein94@me.com", "customer_id": 202508142004391949, "customer_name": "Jesse Goldstein", "customer_type": "individual", "delivered_at": "2026-02-11T17:45:47", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0466L\nZONE: AE\nELEV: 10 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000277032, "paid": true, "property_address": "10651 SW 67TH CT", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.6719398", "property_lng": "-80.30381249999999", "property_state": "FL", "property_zip": "33156", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-02-11T17:45:47"}, "success": true, "order_id": "1000277032", "customer_email": "jgoldstein94@me.com", "service_type": "Land Survey Only", "county": "", "property_address": "10651 SW 67TH CT", "customer_name": "Jesse Goldstein"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Jesse Goldstein", "confidence": "HIGH"}, "client_email": {"value": "jgoldstein94@me.com", "confidence": "HIGH"}, "property_address": {"value": "10651 SW 67TH CT, MIAMI, FL 33156", "confidence": "HIGH"}, "property_county": {"value": "MIAMI-DADE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested"}, "special_requirements": {"value": "Special pricing applied; property is in FEMA Flood Zone AE (Panel 12086C0466L, base elevation 10 ft, effective 09/11/2009)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not available", "Legal description not available", "Structure square footage not available", "Property features (pool, shed, driveways, structures) unknown \u2014 no aerial, appraiser, or email data", "County appraiser data unavailable (county field was blank in lookup)", "No matching emails found to supplement order details", "Reason for special pricing not documented"], "summary": "Residential land survey only order for Jesse Goldstein at 10651 SW 67TH CT, Miami, FL 33156 (Miami-Dade County), located in FEMA Flood Zone AE, already delivered and paid with special pricing applied."}}</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:03:32.160923+00:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
@@ -7502,7 +7605,7 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.387727+00:00</t>
+          <t>2026-06-02T17:03:32.211121+00:00</t>
         </is>
       </c>
     </row>
@@ -7514,7 +7617,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7534,7 +7637,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2362 BYRON ST</t>
+          <t>2362 BYRON ST, PALM SPRINGS, FL 33406</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202601061807385066, "created_at": "2026-01-06T13:35:04", "customer_email": "eminmugla09@gmail.com", "customer_id": 202601061807385173, "customer_name": "muhammed mugla", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0589F\nZONE: AE\nELEV: 11.2 FT\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000276801, "paid": false, "property_address": "2362 BYRON ST", "property_city": "PALM SPRINGS", "property_county": "PALM BEACH COUNTY", "property_lat": "26.6417043", "property_lng": "-80.08593429999999", "property_state": "FLORIDA", "property_zip": "33406", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276801", "customer_email": "eminmugla09@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "2362 BYRON ST", "customer_name": "muhammed mugla"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "muhammed mugla", "confidence": "HIGH"}, "client_email": {"value": "eminmugla09@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "2362 BYRON ST, PALM SPRINGS, FL 33406", "confidence": "HIGH"}, "property_county": {"value": "PALM BEACH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as Land Survey Only; elevation certificate is false"}, "special_requirements": {"value": "Property is in FEMA Flood Zone AE (panel 12099C0589F, effective 10/05/2017, base flood elevation 11.2 FT). Order is currently On Hold.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data, no emails, and no aerial data available to determine pool, shed, driveways, or other structures"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Order is On Hold \u2014 reason for hold not specified, needs human review", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fences, etc.) unknown \u2014 no appraiser or aerial data", "No matching emails found \u2014 no additional context from client communications", "County was blank in the top-level FTF fields (though present in order data body)", "Invoice not yet created and payment not collected \u2014 needs follow-up"], "summary": "Individual residential client muhammed mugla has ordered a Land Survey Only for 2362 Byron St, Palm Springs, FL 33406 (Palm Beach County, Flood Zone AE), but the order is currently On Hold with no fieldwork or delivery date scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:03:42.665040+00:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
@@ -7544,7 +7657,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.441837+00:00</t>
+          <t>2026-06-02T17:03:42.772543+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -6993,7 +6993,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7016,16 +7016,37 @@
           <t>5327 N Bay Rd, Miami Beach, FL 33140</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>{"total_amount": 775.0, "services": [{"name": "Boundary Survey / Land Survey", "description": "Boundary survey for LOT 7, BLOCK 15, LAGORCE-GOLF SUBDIVISION, 5327 N Bay Rd, Miami Beach, Miami-Dade County. 0.17-acre residential lot. Base rate per management-approved negotiated pricing for this client.", "amount": 500.0}, {"name": "Elevation Certificate", "description": "FEMA Elevation Certificate required \u2014 property is located in FEMA Flood Zone AE (panel 12086C0309L, effective 09/11/2009, base flood elevation 8 ft). Standard EC rate applies; Zone AE (not VE), so no coastal $50 surcharge.", "amount": 275.0}], "pricing_reasoning": "The client has a management-approved negotiated base rate of $500.00 for the boundary/land survey. The property is a small 0.17-acre residential lot in a platted subdivision (Lagorce-Golf), so no lot-size upcharge applies (threshold begins at 0.31 ac). No pool, metes-and-bounds, heavy vegetation, or Monroe County complexity factors are supported by the available data. The property sits in FEMA Flood Zone AE, so an Elevation Certificate at the standard $275.00 rate is included; the $50 VE coastal surcharge does not apply since the zone is AE. A duplicate order flag is raised for human review as an identical address and folio appear in Order 1000273281.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE DUPLICATE: Order 1000273281 references the same property address (5327 N Bay Rd, Miami-Dade County), same coordinates (25.8317178, -80.1295335), and same Folio/MLS (0232150032180) with service 'Land Survey and Elevation'. Human review recommended before processing to avoid duplicate field work or billing.", "SERVICE TYPE AMBIGUITY: The order notes state no specific survey service type was identified. Pricing assumes a combined Boundary Survey + Elevation Certificate based on the FEMA AE zone designation and typical residential workflow. Client or account manager should confirm service scope before invoicing.", "NO AERIAL IMAGE PROVIDED: Waterfront, pool, and vegetation complexity could not be visually verified. 5327 N Bay Rd in Miami Beach is a waterfront neighborhood; if a canal or bay frontage is confirmed on-site or via aerial review, a waterfront canal upcharge of $87.00 may apply and should be revisited."]}</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202602032116075928, "created_at": "2026-02-03T21:18:39", "customer_email": "lauriepicard@hotmail.com", "customer_id": 202602032116076992, "customer_name": "Laurie Picard", "customer_type": "individual", "delivered_at": "2026-02-10T16:50:48", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0309L\nZONE: AE\nELEV: 08 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000278156, "paid": true, "property_address": "5327 N BAY RD", "property_city": "MIAMI BEACH", "property_county": "Miami-Dade County", "property_lat": "25.8317178", "property_lng": "-80.1295335", "property_state": "FL", "property_zip": "33140", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-02-10T16:50:48"}, "success": true, "order_id": "1000278156", "customer_email": "lauriepicard@hotmail.com", "service_type": "Quote", "county": "", "property_address": "5327 N BAY RD", "customer_name": "Laurie Picard"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Laurie Picard", "confidence": "HIGH"}, "client_email": {"value": "lauriepicard@hotmail.com", "confidence": "HIGH"}, "property_address": {"value": "5327 N Bay Rd, Miami Beach, FL 33140", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed as 'Quote' only \u2014 no specific survey type (e.g., Boundary, ALTA, Elevation Certificate) has been identified. Needs clarification on what survey service is being quoted."}, "special_requirements": {"value": "Special pricing applied. Property is in FEMA Flood Zone AE (Panel 12086C0309L, Base Flood Elevation 8 ft, effective 09/11/2009).", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 no aerial, appraiser data, or email attachments provided. Pool, structures, driveways unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not identified \u2014 'Quote' is not a deliverable service", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fences, driveways, etc.)", "No matching emails found to clarify scope or client intent", "Fieldwork date not scheduled (fieldwork_at is null)", "Invoice not yet generated (invoiced: false) despite order being marked Delivered and Paid"], "summary": "Residential quote request from individual client Laurie Picard for a property at 5327 N Bay Rd, Miami Beach, FL (Miami-Dade County) located in FEMA Flood Zone AE, with special pricing applied but no specific survey service type identified."}}</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1780420082104</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>2026-06-02T16:51:10.623338+00:00</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:10:09.720808+00:00</t>
+        </is>
+      </c>
+      <c r="R112" t="n">
+        <v>775</v>
+      </c>
       <c r="T112" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.756326+00:00</t>
@@ -7033,7 +7054,7 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>2026-06-02T16:51:10.672437+00:00</t>
+          <t>2026-06-02T17:10:09.769259+00:00</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7066,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7068,16 +7089,37 @@
           <t>5729 SW 60TH AVE, South Miami, FL 33143</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>{"total_amount": 512.0, "services": [{"name": "CAD File / Land Survey", "description": "Boundary survey with CAD deliverable for 5729 SW 60th Ave, South Miami, FL 33143. Base rate per negotiated IK Studios agreement.", "amount": 450.0}, {"name": "Lot Size Complexity Upcharge (0.31\u20130.50 ac)", "description": "Property is 0.40 acres, falling within the 0.31\u20130.50 ac complexity tier.", "amount": 62.0}], "pricing_reasoning": "The negotiated base rate of $450.00 is applied per management agreement with IK Studios. The property is 0.40 acres, which falls in the 0.31\u20130.50 ac bracket warranting a $62.00 complexity upcharge. No Elevation Certificate was requested, so the FEMA Zone AH designation does not trigger an EC line item. The legal description is a simple metes-style lot cut (south 155 feet of Lot 19, Block 3) from a recorded plat \u2014 not a full metes-and-bounds traverse \u2014 so no metes-and-bounds upcharge is applied. No pool, waterfront, Monroe County, or heavy vegetation indicators are present in the available data.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE_DUPLICATE: Order 1000275475 at the same address (5729 SW 60th Ave, Miami-Dade County) was previously submitted for Land Survey and Elevation service with matching coordinates and Folio/MLS. Human review recommended to confirm whether this CAD file order is a continuation, revision, or separate deliverable for that prior survey, or if the EC from that order should be incorporated here.", "HOLD_NOTE: Order notes indicate this order was placed on hold with special pricing applied. Confirm with management that the $450.00 negotiated rate and current scope are still valid before invoicing.", "CLIENT_NEW: IK Studios shows 0 prior orders with NexGen despite being classified as OLD_TITLE. Verify client tier and negotiated rate with management."]}</t>
+        </is>
+      </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202601301457214739, "created_at": "2026-01-30T14:59:12", "customer_email": "alex@ikstudio.net", "customer_id": 202601301458052770, "customer_name": "Alex Gonzalez", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0458L\nZONE: AH\nELEV: 09 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000277959, "paid": true, "property_address": "5729 SW 60TH AVE", "property_city": "SOUTH MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.7170772", "property_lng": "-80.2921914", "property_state": "FL", "property_zip": "33143", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-30T20:57:09"}, "success": true, "order_id": "1000277959", "customer_email": "alex@ikstudio.net", "service_type": "CAD file", "county": "", "property_address": "5729 SW 60TH AVE", "customer_name": "IK STUDIOS"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "IK Studios (Alex Gonzalez)", "confidence": "HIGH"}, "client_email": {"value": "alex@ikstudio.net", "confidence": "HIGH"}, "property_address": {"value": "5729 SW 60TH AVE, South Miami, FL 33143", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order currently on hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features provided; county appraiser data unavailable and no matching emails or attachments found"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, etc.)", "County appraiser data unavailable", "No matching emails found for additional context", "Reason for 'On Hold' status unclear", "Scope of CAD file deliverable not defined (boundary, topo, as-built, etc.)", "Urgency/deadline not specified"], "summary": "B2B order from IK Studios (Alex Gonzalez) for a CAD file at 5729 SW 60th Ave, South Miami, FL 33143 (Miami-Dade County), currently on hold with special pricing applied and minimal property details available."}}</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1780420227279</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>2026-06-02T16:51:20.050333+00:00</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:10:27.941935+00:00</t>
+        </is>
+      </c>
+      <c r="R113" t="n">
+        <v>512</v>
+      </c>
       <c r="T113" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.807344+00:00</t>
@@ -7085,7 +7127,7 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>2026-06-02T16:51:20.098543+00:00</t>
+          <t>2026-06-02T17:10:27.990886+00:00</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7139,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7120,16 +7162,37 @@
           <t>1320 NE 47TH ST, OAKLAND PARK, FL 33334</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>{"total_amount": 400.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for LOT 5, BLOCK 23, CORAL HEIGHTS SECTION THREE, 1320 NE 47TH ST, Oakland Park, Broward County, FL. Standard platted residential lot (0.19 ac), no complexity upcharges warranted. Negotiated rate applied per management agreement.", "amount": 400.0}], "pricing_reasoning": "Management has agreed to a fixed negotiated rate of $400.00 for this individual client (Matthew Lowe, first-time order). The property is a standard platted residential lot of 0.19 acres in Broward County with a straightforward legal description, no pool, no waterfront, no metes-and-bounds, and no lot-size upcharge triggers \u2014 no complexity upcharges are supported by the data. The order is currently on hold at $400.00 per the order notes, confirming alignment with the agreed rate.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_FLAG: Order 1000232113 at the same address (1320 NE 47TH ST, Broward County) for Land Survey Only has been previously placed \u2014 same coordinates (26.1845829, -80.1294899) and same Folio/MLS (494214122040). Human review recommended to confirm this is not a duplicate fulfillment.", "DUPLICATE_FLAG: Order 1000232236 at the same address (1320 NE 47TH ST, Broward County) for a Quote has been previously placed \u2014 same coordinates and Folio/MLS. Human review recommended.", "FEMA_ZONE_AE: Property is in FEMA flood zone AE (panel 12011C0367J, effective 07/31/2024, base flood elevation 6 ft). No Elevation Certificate was ordered; no EC line item added. If client requires an EC in the future, standard EC pricing of $275.00 would apply.", "ORDER_ON_HOLD: Per order notes, this order is currently on hold at $400.00 due. Pricing confirmed consistent with hold amount."]}</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202601271837249869, "created_at": "2026-01-27T18:37:25", "customer_email": "mattlowe421@gmail.com", "customer_id": 202601271837250347, "customer_name": "Matthew Lowe", "customer_type": "individual", "delivered_at": null, "due_amount": 400.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0367J\nZONE: AE\nELEV: 06 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000277785, "paid": false, "property_address": "1320 NE 47TH ST", "property_city": "OAKLAND PARK", "property_county": "BROWARD COUNTY", "property_lat": "26.1845829", "property_lng": "-80.1294899", "property_state": "FLORIDA", "property_zip": "33334", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-28T19:52:07"}, "success": true, "order_id": "1000277785", "customer_email": "mattlowe421@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "1320 NE 47TH ST", "customer_name": "Matthew Lowe"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Matthew Lowe", "confidence": "HIGH"}, "client_email": {"value": "mattlowe421@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1320 NE 47TH ST, OAKLAND PARK, FL 33334", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested (elevation_cert: false)"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status_code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, etc.)", "Reason for On Hold status not documented", "Reason for special pricing not documented", "No fieldwork or delivery dates scheduled", "County was blank in top-level FTF fields despite being present in nested data \u2014 data inconsistency to review"], "summary": "Individual residential client Matthew Lowe has ordered a Land Survey Only for 1320 NE 47TH ST in Oakland Park, Broward County, FL 33334, with special pricing applied and the order currently on hold at $400 due."}}</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1780420227279</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>2026-06-02T16:51:29.516356+00:00</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:10:44.959252+00:00</t>
+        </is>
+      </c>
+      <c r="R114" t="n">
+        <v>400</v>
+      </c>
       <c r="T114" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.859079+00:00</t>
@@ -7137,7 +7200,7 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>2026-06-02T16:51:29.616603+00:00</t>
+          <t>2026-06-02T17:10:45.009375+00:00</t>
         </is>
       </c>
     </row>
@@ -7669,7 +7732,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7689,7 +7752,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>10369 SILVER LAKE DR</t>
+          <t>10369 SILVER LAKE DR, BOCA RATON, FL 33428</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202601061537446994, "created_at": "2026-01-06T10:49:02", "customer_email": "gquatela@yahoo.com", "customer_id": 202601061537447982, "customer_name": "GEORGE QUATELA", "customer_type": "individual", "delivered_at": "2026-01-06T17:58:09", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C1155F\nZONE: X\nEFFECTIVE: 10/05/2017", "invoiced": false, "order_id": 1000276783, "paid": false, "property_address": "10369 SILVER LAKE DR", "property_city": "BOCA RATON", "property_county": "Palm Beach County", "property_lat": "26.359744", "property_lng": "-80.20904490000001", "property_state": "FL", "property_zip": "33428", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276783", "customer_email": "gquatela@yahoo.com", "service_type": "Quote", "county": "", "property_address": "10369 SILVER LAKE DR", "customer_name": "GEORGE QUATELA"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "GEORGE QUATELA", "confidence": "HIGH"}, "client_email": {"value": "gquatela@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "10369 SILVER LAKE DR, BOCA RATON, FL 33428", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed as 'Quote' only \u2014 no specific survey service (e.g., boundary, elevation, topographic) has been identified. Human review needed to determine what survey product was quoted."}, "special_requirements": {"value": "Special pricing flag is active", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided. Pool, shed, driveways, and other structures unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not identified \u2014 'Quote' is not a deliverable", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fencing, driveways) unknown", "No matching emails found to clarify scope", "County was blank in top-level FTF fields despite being populated in order data \u2014 minor data inconsistency", "Flood zone noted (Zone X, FIRM 12099C1155F) but elevation certificate not requested \u2014 confirm with client", "Invoice has not been sent and amount due is $0 \u2014 quote may not have been finalized or accepted"], "summary": "Residential quote order for GEORGE QUATELA at 10369 Silver Lake Dr, Boca Raton FL (Palm Beach County) marked as Delivered with special pricing active, but the specific survey service requested has not been defined and significant property detail is missing."}}</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:09:05.682023+00:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
@@ -7699,7 +7772,7 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.497199+00:00</t>
+          <t>2026-06-02T17:09:05.730205+00:00</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7784,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7731,7 +7804,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>7964 GRAND BAY DR</t>
+          <t>7964 Grand Bay Dr, Naples, FL 34108</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202601061428299961, "created_at": "2026-01-06T10:58:02", "customer_email": "cpv2757@aol.com", "customer_id": 202601061428300131, "customer_name": "Claudia Vitulich", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12021C0381J\nZONE: X500\nEFF: 02/08/2024", "invoiced": false, "order_id": 1000276767, "paid": false, "property_address": "7964 GRAND BAY DR", "property_city": "NAPLES", "property_county": "COLLIER COUNTY", "property_lat": "26.2452916", "property_lng": "-81.81071039999999", "property_state": "FLORIDA", "property_zip": "34108", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276767", "customer_email": "cpv2757@aol.com", "service_type": "Land Survey Only", "county": "", "property_address": "7964 GRAND BAY DR", "customer_name": "Claudia Vitulich"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Claudia Vitulich", "confidence": "HIGH"}, "client_email": {"value": "cpv2757@aol.com", "confidence": "HIGH"}, "property_address": {"value": "7964 Grand Bay Dr, Naples, FL 34108", "confidence": "HIGH"}, "property_county": {"value": "Collier County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "None noted", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 county appraiser unavailable", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) unknown", "Order is currently On Hold \u2014 reason for hold not specified", "No fieldwork or delivery dates scheduled", "No invoice or payment information present", "No customer data returned from FTF customer lookup"], "summary": "Individual residential client Claudia Vitulich has ordered a Land Survey Only for 7964 Grand Bay Dr, Naples, FL (Collier County), currently on hold with no fieldwork scheduled and missing lot, legal, and property feature details."}}</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:09:14.636313+00:00</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -7741,7 +7824,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.552119+00:00</t>
+          <t>2026-06-02T17:09:14.685958+00:00</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7836,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7773,7 +7856,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1025 MARIANA AVE</t>
+          <t>1025 Mariana Ave, Coral Gables, FL 33134</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202601051549222579, "created_at": "2026-01-05T10:51:00", "customer_email": "mmarino@ms-constructions.com", "customer_id": 202601051549514927, "customer_name": "Magdalena Marino", "customer_type": "b2b", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0294L\nZONE: X\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000276703, "paid": false, "property_address": "1025 MARIANA AVE", "property_city": "CORAL GABLES", "property_county": "Miami-Dade County", "property_lat": "25.7614208", "property_lng": "-80.27663749999999", "property_state": "FL", "property_zip": "33134", "service_type": "Quote", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276703", "customer_email": "mmarino@ms-constructions.com", "service_type": "Quote", "county": "", "property_address": "1025 MARIANA AVE", "customer_name": "M+S Construction"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "M+S Construction", "confidence": "HIGH"}, "client_email": {"value": "mmarino@ms-constructions.com", "confidence": "HIGH"}, "property_address": {"value": "1025 Mariana Ave, Coral Gables, FL 33134", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., Boundary, Elevation, Topographic) has been identified. Needs clarification from client or internal team."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property feature data available \u2014 pool, shed, driveways, and other structures unknown. County Appraiser data unavailable."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not identified \u2014 Quote only, no scope defined", "Lot size unknown \u2014 County Appraiser unavailable", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, driveways, etc.) unknown", "No matching emails found to provide additional context", "Order is On Hold \u2014 reason for hold not specified", "Elevation certificate not requested but flood zone is Zone X \u2014 confirm no elevation cert needed", "Due amount of $250 may be a deposit or placeholder \u2014 full quote not finalized"], "summary": "A b2b client (M+S Construction) has an On Hold quote order for a property at 1025 Mariana Ave, Coral Gables, FL (Miami-Dade County) with special pricing applied, but the specific survey service type and property details remain undefined and require human follow-up."}}</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:09:26.371515+00:00</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -7783,7 +7876,7 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.607180+00:00</t>
+          <t>2026-06-02T17:09:26.420558+00:00</t>
         </is>
       </c>
     </row>
@@ -7795,7 +7888,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7815,7 +7908,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>15615 FL-62</t>
+          <t>15615 FL-62, Parrish, FL 34219</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202106171651070228, "created_at": "2025-12-24T08:51:04", "customer_email": "bprinz@wdooleylaw.com", "customer_id": 202106171652033942, "customer_name": "Barbara Prinz", "customer_type": "b2b", "delivered_at": "2025-12-29T20:00:37", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12081C0184F\nZONE: X\nEFF: 08/10/2021", "invoiced": false, "order_id": 1000276470, "paid": false, "property_address": "15615 FL-62", "property_city": "PARRISH", "property_county": "Manatee County", "property_lat": "27.5895349", "property_lng": "-82.3839765", "property_state": "FL", "property_zip": "34219", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276470", "customer_email": "bprinz@wdooleylaw.com", "service_type": "Quote", "county": "", "property_address": "15615 FL-62", "customer_name": "William A. Dooley, P.A."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "William A. Dooley, P.A.", "confidence": "HIGH"}, "client_email": {"value": "bprinz@wdooleylaw.com", "confidence": "HIGH"}, "property_address": {"value": "15615 FL-62, Parrish, FL 34219", "confidence": "HIGH"}, "property_county": {"value": "Manatee County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service has been identified. Actual survey type needs clarification from client."}, "special_requirements": {"value": "Special pricing applies", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data present."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not identified \u2014 'Quote' is not a service", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown \u2014 no aerial, appraiser, or email data", "No matching emails found to clarify scope or requirements", "County was blank in the outer FTF payload \u2014 confirmed via inner data only", "No customer profile data available (FTF customer data is empty)"], "summary": "A b2b quote request from William A. Dooley, P.A. for a property at 15615 FL-62 in Parrish, Manatee County, FL (Flood Zone X), with special pricing applied but no specific survey service type yet identified."}}</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:09:36.389767+00:00</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
@@ -7825,7 +7928,7 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.662145+00:00</t>
+          <t>2026-06-02T17:09:36.438746+00:00</t>
         </is>
       </c>
     </row>
@@ -7837,7 +7940,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7857,7 +7960,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>23 S SWINTON AVE</t>
+          <t>23 S SWINTON AVE, DELRAY BEACH, FL 33444</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508041423430005, "created_at": "2025-12-23T10:41:01", "customer_email": "dfainvestmentcompany@gmail.com", "customer_id": 202508041423431419, "customer_name": "GEOFFREY MORRIS", "customer_type": "individual", "delivered_at": "2025-12-23T21:13:40", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0979G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000276428, "paid": true, "property_address": "23 S SWINTON AVE", "property_city": "DELRAY BEACH", "property_county": "Palm Beach County", "property_lat": "26.4606471", "property_lng": "-80.0728381", "property_state": "FL", "property_zip": "33444", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276428", "customer_email": "DSAINVESTMENTCOMPANY@GMAIL.COM", "service_type": "Quote", "county": "", "property_address": "23 S SWINTON AVE", "customer_name": "GEOFFREY MORRIS"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "GEOFFREY MORRIS", "confidence": "HIGH"}, "client_email": {"value": "dfainvestmentcompany@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "23 S SWINTON AVE, DELRAY BEACH, FL 33444", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed as 'Quote' only \u2014 no specific survey type (e.g., Boundary, Elevation Certificate, Topographic) has been identified. Human review needed to determine actual services requested."}, "special_requirements": {"value": "Special pricing applied; flood zone X per FIRM panel 12099C0979G effective 12/20/2024", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 pool, shed, driveways, or other structures unknown. County appraiser data unavailable."}, "client_tier": {"value": "unknown", "confidence": "LOW"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not defined \u2014 'Quote' is not a deliverable survey type", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) unknown", "Client tier unclear \u2014 email domain suggests possible investment company (DFA Investment Company) but customer_type is 'individual'", "No matching emails found to corroborate order details", "Invoice not yet generated (invoiced: false) despite order marked as delivered and paid"], "summary": "A delivered and paid Quote-stage order for GEOFFREY MORRIS at 23 S Swinton Ave, Delray Beach FL (Flood Zone X) with special pricing applied, but the specific survey service requested has not yet been defined and key property details are missing."}}</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:09:48.820095+00:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
@@ -7867,7 +7980,7 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.718263+00:00</t>
+          <t>2026-06-02T17:09:48.868805+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -7212,7 +7212,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7235,16 +7235,37 @@
           <t>715 SE 2nd Ave, Delray Beach, FL 33483</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "No specific survey service has been identified for this order \u2014 the client submitted a general quote request without specifying the service type (boundary survey, EC, topo, etc.). Because the required service is unknown, no line items can be priced at this time. Additionally, two likely duplicate orders (1000154638 and 1000277207) exist for the same property and folio, both for Land Survey Only, which further requires human review before proceeding. If this resolves to a standard boundary survey, the base rate would be $475.00 (individual client, 0.23 acres in Zone X \u2014 no size or complexity upcharges apply); an Elevation Certificate would add $275.00 if requested.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "Service type not specified \u2014 client submitted a quote request only. Human follow-up is required to determine what survey service(s) are needed before pricing can be finalized. Additionally, two probable duplicate orders (1000154638 and 1000277207) exist for the same property address and folio number (12434621010080321), both already priced as Land Survey Only. These must be reconciled before issuing a new quote to avoid triple-billing the same property.", "flags": ["SERVICE_TYPE_UNKNOWN: Client Michael Sanzen submitted a quote request but did not specify the survey service required. Follow-up needed before pricing.", "DUPLICATE_ORDER: Order 1000154638 \u2014 715 SE 2ND AVE, Palm Beach County \u2014 Land Survey Only \u2014 same coordinates and folio 12434621010080321.", "DUPLICATE_ORDER: Order 1000277207 \u2014 715 SE 2ND AVE, Palm Beach County \u2014 Land Survey Only \u2014 same coordinates and folio 12434621010080321.", "NO_COMPLEXITY_UPCHARGES_APPLICABLE: Lot is 0.23 acres (below 0.31 ac threshold), FEMA Zone X (no EC required unless requested), Palm Beach County (no Monroe premium), legal description is a platted lot subdivision (no metes-and-bounds upcharge)."]}</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202601141812154089, "created_at": "2026-01-27T15:48:52", "customer_email": "michaelsanzen@gmail.com", "customer_id": 202601141812154237, "customer_name": "Michael Sanzen", "customer_type": "individual", "delivered_at": "2026-01-27T22:16:31", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0979G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000277758, "paid": true, "property_address": "715 SE 2ND AVE", "property_city": "DELRAY BEACH", "property_county": "Palm Beach County", "property_lat": "26.4505752", "property_lng": "-80.0707206", "property_state": "FL", "property_zip": "33483", "service_type": "Quote", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-27T22:16:31"}, "success": true, "order_id": "1000277758", "customer_email": "michaelsanzen@gmail.com", "service_type": "Quote", "county": "", "property_address": "715 SE 2ND AVE", "customer_name": "Michael Sanzen"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Michael Sanzen", "confidence": "HIGH"}, "client_email": {"value": "michaelsanzen@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "715 SE 2nd Ave, Delray Beach, FL 33483", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., boundary, elevation cert, topographic) has been identified. Human review needed to determine what was quoted."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial imagery, or email attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service(s) requested are unknown \u2014 'Quote' is not a deliverable service type", "No lot size or parcel dimensions available", "No legal description available", "No structure square footage available", "No property features identified (pool, outbuildings, etc.)", "No special requirements or notes from client", "County property appraiser data unavailable", "No matching emails found to clarify scope", "Elevation certificate not requested \u2014 confirm if needed given flood zone X (low risk but still noted)"], "summary": "Individual residential client Michael Sanzen submitted a quote request for a property at 715 SE 2nd Ave, Delray Beach, FL (Palm Beach County), but the specific survey services requested have not been identified and require human follow-up."}}</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1780420563655</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>2026-06-02T16:57:04.251852+00:00</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:16:04.805349+00:00</t>
+        </is>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
       <c r="T115" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.910495+00:00</t>
@@ -7252,7 +7273,7 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>2026-06-02T16:57:04.301181+00:00</t>
+          <t>2026-06-02T17:16:04.920986+00:00</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7285,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7287,16 +7308,37 @@
           <t>717 Layne Blvd, Hallandale Beach, FL 33009</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>{"total_amount": 50.0, "services": [{"name": "CAD File", "description": "Delivery of CAD file for 717 Layne Blvd, Hallandale Beach, FL (Broward County) \u2014 no new fieldwork required; CAD conversion/export of existing survey data on file.", "amount": 50.0}], "pricing_reasoning": "The service requested is a CAD file only \u2014 no new boundary survey or elevation certificate fieldwork is being ordered. This is a digital deliverable derived from existing survey data already on file (see duplicate orders 1000212474 and 1000276816 for the same property/folio). A CAD file export is a standalone administrative/drafting deliverable typically priced at $50.00; the negotiated base survey rate of $250.00 applies to field survey services and is not triggered here. No complexity upcharges, lot size upcharges, or EC fees apply as there is no fieldwork component. The order is currently On Hold with special pricing noted by management, which is consistent with this minimal deliverable fee.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "Management should confirm: (1) the correct CAD file fee given the special pricing notation and On Hold status, (2) whether the CAD file is being sourced from one of the two prior orders (1000212474 or 1000276816) for the same property, and (3) whether any additional drafting scope (e.g., as-built, updated boundary, flood zone annotation) is expected that would alter pricing.", "flags": ["POSSIBLE DUPLICATE: Order 1000212474 \u2014 717 LAYNE BLVD, BROWARD COUNTY \u2014 service: Land Survey and Elevation \u2014 same location and Folio 514226130320. CAD file may be sourced from this prior order.", "POSSIBLE DUPLICATE: Order 1000276816 \u2014 717 LAYNE BLVD, BROWARD COUNTY \u2014 service: Land Survey Only \u2014 same location and Folio 514226130320. CAD file may be sourced from this prior order.", "ORDER ON HOLD: Special pricing flag was noted by management \u2014 confirm final CAD file fee before invoicing.", "NO FIELDWORK SCHEDULED: CAD file is a digital deliverable only; no site visit required based on order notes."]}</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202601061948402508, "created_at": "2026-01-27T14:08:01", "customer_email": "ferusa@me.com", "customer_id": 202601061948402608, "customer_name": "Fernando Lupica Tondo", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0732J\nZONE: AE\nELEV: 07 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000277746, "paid": true, "property_address": "717 LAYNE BLVD", "property_city": "HALLANDALE BEACH", "property_county": "BROWARD COUNTY", "property_lat": "25.9754542", "property_lng": "-80.1327428", "property_state": "FL", "property_zip": "33009", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-28T20:46:09"}, "success": true, "order_id": "1000277746", "customer_email": "ferusa@me.com", "service_type": "CAD file", "county": "", "property_address": "717 LAYNE BLVD", "customer_name": "Fernando Lupica Tondo"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Fernando Lupica Tondo", "confidence": "HIGH"}, "client_email": {"value": "ferusa@me.com", "confidence": "HIGH"}, "property_address": {"value": "717 Layne Blvd, Hallandale Beach, FL 33009", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD file; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order status is On Hold; property is in FEMA Flood Zone AE (Panel 12011C0732J, Elev 07 FT, Eff 07/31/2024)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no emails or aerial data provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser or parcel data available", "Legal description missing \u2014 no appraiser lookup performed", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, etc.)", "Order is On Hold \u2014 reason for hold not specified; needs human review", "No fieldwork date scheduled", "Scope of CAD file not clarified (boundary CAD, as-built CAD, etc.)", "Special pricing applied but pricing amount/reason not documented"], "summary": "Individual residential client Fernando Lupica Tondo has requested a CAD file for 717 Layne Blvd, Hallandale Beach, FL (Broward County), a property in FEMA Flood Zone AE; the order is currently On Hold with special pricing applied and no fieldwork scheduled."}}</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1780420563655</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>2026-06-02T16:57:14.712157+00:00</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:16:22.296649+00:00</t>
+        </is>
+      </c>
+      <c r="R116" t="n">
+        <v>50</v>
+      </c>
       <c r="T116" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:14.962330+00:00</t>
@@ -7304,7 +7346,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>2026-06-02T16:57:14.762691+00:00</t>
+          <t>2026-06-02T17:16:22.347667+00:00</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7358,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7339,16 +7381,37 @@
           <t>2401 28TH AVE N, ST. PETERSBURG, FL 33713</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for Lots 59 and 60 less the north 40 feet of each, Herkimer Heights, Pinellas County. 0.19 acres, FEMA Zone X (no flood zone upcharge). Negotiated rate for Stross Law Firm applied.", "amount": 450.0}], "pricing_reasoning": "The client has a management-agreed negotiated rate of $450.00 as a base survey rate. The property is 0.19 acres \u2014 well within the standard tier (under 0.31 ac), so no lot-size upcharge applies. FEMA Zone X carries no elevation certificate requirement and no flood complexity surcharge. The legal description references a platted subdivision (Herkimer Heights, Plat Book 9, Page 75) with a simple lot-less-north-40-feet cut, which is a straightforward recorded boundary and does not trigger a metes-and-bounds upcharge. No pool, waterfront, heavy vegetation, or Monroe County factors are indicated. The service is Land Survey Only with no EC requested, so the final price equals the negotiated base rate of $450.00.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["Commercial flag is True \u2014 confirm with field crew whether any commercial-use complexity (e.g., larger structures, encroachments, or easement research) is present that may warrant a reassessment.", "Order count is 0 for Stross Law Firm \u2014 first order; confirm negotiated rate documentation is on file before invoicing.", "Multiple certifications noted (Hector Allen Escardo, Stross Law Firm, Hancock Whitney Bank ISAOA/ATIMA, Fidelity National Title Insurance Company) \u2014 ensure all four certification names are captured on the final survey document to avoid revision requests."]}</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 201801311056152653, "created_at": "2026-01-26T21:55:01", "customer_email": "mkreuzman@strosslaw.com", "customer_id": 202207051448472795, "customer_name": "Mariann  Kreuzman", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12103C0216G\nZONE: X\nEFF: 09/03/2003", "invoiced": false, "order_id": 1000277740, "paid": false, "property_address": "2401 28TH AVE N", "property_city": "ST. PETERSBURG", "property_county": "PINELLAS COUNTY", "property_lat": "27.7975988", "property_lng": "-82.66498560000001", "property_state": "FL", "property_zip": "33713", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-02-05T07:23:13"}, "success": true, "order_id": "1000277740", "customer_email": "mkreuzman@strosslaw.com", "service_type": "Land Survey Only", "county": "", "property_address": "2401 28TH AVE N", "customer_name": "Stross Law Firm"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Stross Law Firm", "confidence": "MEDIUM"}, "client_email": {"value": "mkreuzman@strosslaw.com", "confidence": "HIGH"}, "property_address": {"value": "2401 28TH AVE N, ST. PETERSBURG, FL 33713", "confidence": "HIGH"}, "property_county": {"value": "Pinellas County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data"}, "special_requirements": {"value": "Special pricing applies; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no matching emails found"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order contact is 'Mariann Kreuzman' but company name listed as 'Stross Law Firm' \u2014 confirm billing name", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fences, driveways, etc.)", "Reason for 'On Hold' status not specified \u2014 needs human review", "Special pricing terms not defined \u2014 confirm pricing with team", "No fieldwork or delivery dates scheduled", "County was blank in outer FTF object despite being present in nested data \u2014 verify data integrity"], "summary": "A B2B land survey order for Stross Law Firm at 2401 28th Ave N, St. Petersburg, FL 33713 (Pinellas County) is currently on hold with special pricing applied and no fieldwork or invoice details yet established."}}</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1780420598293</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>2026-06-02T16:57:25.446880+00:00</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:16:39.123851+00:00</t>
+        </is>
+      </c>
+      <c r="R117" t="n">
+        <v>450</v>
+      </c>
       <c r="T117" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.014241+00:00</t>
@@ -7356,7 +7419,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>2026-06-02T16:57:25.498065+00:00</t>
+          <t>2026-06-02T17:16:39.175066+00:00</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7431,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7391,16 +7454,37 @@
           <t>415 44TH ST, WEST PALM BEACH, FL 33407</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>{"total_amount": 500.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for LOT 9, 10, 11 AND 12, BLOCK 8, NORTH PALM BEACH (REED ADDITION), Plat Book 6 Page 30, Palm Beach County. Four combined platted lots totaling 0.24 acres. FEMA Zone X \u2014 no flood zone upcharge applicable. Platted subdivision lots \u2014 no metes and bounds complexity. Lot size under 0.31 ac \u2014 no size upcharge. Management-agreed special rate applied.", "amount": 500.0}], "pricing_reasoning": "The client has a management-agreed negotiated rate of $500.00 for this specific order, which serves as the binding base price. The property is four platted lots (LOT 9-12, BLOCK 8) totaling 0.24 acres in Palm Beach County \u2014 a standard residential subdivision survey with no complexity triggers: FEMA Zone X (no flood concern), under 0.31 acres (no size upcharge), platted legal description (no metes and bounds upcharge), and no indicators of waterfront, pool, or heavy vegetation. No EC was requested, and the service is Land Survey Only.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000275991 \u2014 same address (415 44TH ST, Palm Beach County), same Folio (74434304040080090), same service (Land Survey Only). Human review recommended before issuing invoice.", "DUPLICATE_WARNING: Order 1000284008 \u2014 same address (415 44TH ST, Palm Beach County), same Folio (74434304040080090), same service (Land Survey Only). Human review recommended before issuing invoice.", "DUPLICATE_WARNING: Order 1000284462 \u2014 same address (415 44TH ST, Palm Beach County), same Folio (74434304040080090), service (CAD). Likely related downstream deliverable \u2014 confirm relationship to this survey order before invoicing.", "NOTE: Order notes state this is a 'delivered and paid' order with 'special pricing applied and no invoice yet generated.' Invoice generation should confirm payment status and reconcile against any prior payment records to avoid double-billing."]}</t>
+        </is>
+      </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202601261503004961, "created_at": "2026-01-26T15:07:37", "customer_email": "joseph@r3health.co", "customer_id": 202601261503006047, "customer_name": "Joseph Radich", "customer_type": "individual", "delivered_at": "2026-01-28T17:48:11", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0393G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000277674, "paid": true, "property_address": "415 44TH ST", "property_city": "WEST PALM BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.7522405", "property_lng": "-80.05344509999999", "property_state": "FL", "property_zip": "33407", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-28T17:48:11"}, "success": true, "order_id": "1000277674", "customer_email": "joseph@r3health.co", "service_type": "Land Survey Only", "county": "", "property_address": "415 44TH ST", "customer_name": "Joseph Radich"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Joseph Radich", "confidence": "HIGH"}, "client_email": {"value": "joseph@r3health.co", "confidence": "HIGH"}, "property_address": {"value": "415 44TH ST, WEST PALM BEACH, FL 33407", "confidence": "HIGH"}, "property_county": {"value": "PALM BEACH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, structures) unknown \u2014 no aerial or appraiser data", "No county provided in top-level FTF fields (though property_county is in order data)", "Reason for special pricing not documented", "No fieldwork date scheduled (fieldwork_at is null)", "No invoice has been generated despite order being delivered and paid"], "summary": "Delivered and paid Land Survey Only order for individual client Joseph Radich at 415 44TH ST, West Palm Beach, FL (Palm Beach County, Flood Zone X), with special pricing applied and no invoice yet generated."}}</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1780420615840</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>2026-06-02T16:57:34.574856+00:00</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:16:56.572402+00:00</t>
+        </is>
+      </c>
+      <c r="R118" t="n">
+        <v>500</v>
+      </c>
       <c r="T118" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.067169+00:00</t>
@@ -7408,7 +7492,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>2026-06-02T16:57:34.624664+00:00</t>
+          <t>2026-06-02T17:16:56.626097+00:00</t>
         </is>
       </c>
     </row>
@@ -7992,7 +8076,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8007,12 +8091,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS Architects, Inc. </t>
+          <t>MS Architects, Inc.</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>7411 W CYPRESSHEAD DR</t>
+          <t>7411 W Cypresshead Dr, Parkland, FL 33067</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202512221935383921, "created_at": "2025-12-22T14:39:00", "customer_email": "MSARCHMS@aol.com", "customer_id": 202512221936377320, "customer_name": "Miguel Sanchez", "customer_type": "b2b", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0155H\nZONE: AH\nELEV: 15 FT\nEFF: 08/18/2014", "invoiced": false, "order_id": 1000276384, "paid": false, "property_address": "7411 W CYPRESSHEAD DR", "property_city": "PARKLAND", "property_county": "Broward County", "property_lat": "26.323319", "property_lng": "-80.2315995", "property_state": "FL", "property_zip": "33067", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276384", "customer_email": "MSARCHMS@aol.com", "service_type": "CAD file", "county": "", "property_address": "7411 W CYPRESSHEAD DR", "customer_name": "MS Architects, Inc. "}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "MS Architects, Inc.", "confidence": "HIGH"}, "client_email": {"value": "MSARCHMS@aol.com", "confidence": "HIGH"}, "property_address": {"value": "7411 W Cypresshead Dr, Parkland, FL 33067", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11); flood zone AH at 15 ft elevation, panel 12011C0155H effective 08/18/2014", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, outbuildings, etc.) unknown", "No matching emails found to clarify scope or special instructions", "Order is On Hold \u2014 reason for hold not specified, may require human follow-up", "Elevation certificate not requested but flood zone AH noted \u2014 confirm if EC is needed", "Due amount is $250 with special pricing \u2014 pricing basis should be confirmed"], "summary": "B2B CAD file order for MS Architects, Inc. at 7411 W Cypresshead Dr, Parkland FL (Broward County), currently on hold with special pricing applied and no supporting appraiser or email data available."}}</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:15:01.349966+00:00</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -8022,7 +8116,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.818516+00:00</t>
+          <t>2026-06-02T17:15:01.400133+00:00</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8128,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8054,7 +8148,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>7300 SW 87TH AVE</t>
+          <t>7300 SW 87TH AVE, MIAMI, FLORIDA 33173</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202411141637401215, "created_at": "2025-12-18T16:02:00", "customer_email": "sboscarelli@firstam.com", "customer_id": 202411141641273684, "customer_name": "Scott  Boscarelli", "customer_type": "b2b", "delivered_at": "2026-03-11T16:15:33", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0454L\nZONE: AH\nELEV: 10 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000276269, "paid": true, "property_address": "7300 SW 87TH AVE", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.701289", "property_lng": "-80.335042", "property_state": "FLORIDA", "property_zip": "33173", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-03-11T16:15:33"}, "success": true, "order_id": "1000276269", "customer_email": "sboscarelli@firstam.com", "service_type": "Land Survey Only", "county": "", "property_address": "7300 SW 87TH AVE", "customer_name": "CDS-Commercial Due Diligence Services"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "CDS-Commercial Due Diligence Services", "confidence": "MEDIUM"}, "client_email": {"value": "sboscarelli@firstam.com", "confidence": "HIGH"}, "property_address": {"value": "7300 SW 87TH AVE, MIAMI, FLORIDA 33173", "confidence": "HIGH"}, "property_county": {"value": "MIAMI-DADE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested (elevation_cert: false)"}, "special_requirements": {"value": "Special pricing applies; Flood Zone AH at 10 FT elevation (FIRM Panel 12086C0454L, effective 09/11/2009)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order data lists 'Scott Boscarelli' as customer_name but outer payload shows 'CDS-Commercial Due Diligence Services' \u2014 confirm correct billing client", "Lot size unknown \u2014 no appraiser data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, structures, etc.) unknown \u2014 no appraiser or aerial data", "No matching emails found to supplement order details", "County field is blank in outer payload despite being populated in order data \u2014 may need reconciliation", "Invoice amount not set (invoiced: false, due_amount: 0.0) \u2014 pricing needs to be finalized despite special_pricing flag"], "summary": "B2B land survey order for 7300 SW 87TH AVE, Miami-Dade County, FL 33173, placed by CDS-Commercial Due Diligence Services (contact: sboscarelli@firstam.com), delivered on 2026-03-11, with special pricing and a Flood Zone AH designation; invoice not yet issued."}}</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:15:13.902482+00:00</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
@@ -8064,7 +8168,7 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.874087+00:00</t>
+          <t>2026-06-02T17:15:13.958355+00:00</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8180,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8096,7 +8200,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2925 E 17TH AVE</t>
+          <t>2925 E 17TH AVE, TAMPA, FL 33605</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201801311047307704, "created_at": "2025-12-18T11:49:03", "customer_email": "stephanie@achievetitle.com", "customer_id": 201804271046596087, "customer_name": "Stephanie Hall", "customer_type": "b2b", "delivered_at": "2025-12-22T14:11:20", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12057C0358J\nZONE: X\nEFF: 10/07/2021", "invoiced": false, "order_id": 1000276241, "paid": true, "property_address": "2925 E 17TH AVE", "property_city": "TAMPA", "property_county": "HILLSBOROUGH COUNTY", "property_lat": "27.9672533", "property_lng": "-82.4266393", "property_state": "FL", "property_zip": "33605", "service_type": "Other Services", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276241", "customer_email": "stephanie@achievetitle.com", "service_type": "Other Services", "county": "", "property_address": "2925 E 17TH AVE", "customer_name": "Achieve Title Services"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Achieve Title Services", "confidence": "MEDIUM"}, "client_email": {"value": "stephanie@achievetitle.com", "confidence": "HIGH"}, "property_address": {"value": "2925 E 17TH AVE, TAMPA, FL 33605", "confidence": "HIGH"}, "property_county": {"value": "HILLSBOROUGH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Other Services"], "confidence": "LOW", "notes": "Service type listed as 'Other Services' \u2014 specific service(s) requested are not defined; requires human clarification"}, "special_requirements": {"value": "Special pricing applied", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available and no aerial or email source to infer features such as pool, shed, driveways, or visible structures"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific service(s) requested \u2014 'Other Services' is too vague for invoicing", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, etc.) unknown \u2014 no appraiser or aerial data", "Client name conflict \u2014 order contact is 'Stephanie Hall' but company name shown as 'Achieve Title Services'; confirm billing entity", "No matching emails found \u2014 unable to verify scope from correspondence", "County was blank in outer FTF envelope despite being present in nested data \u2014 data integrity note"], "summary": "A delivered B2B order for Achieve Title Services at 2925 E 17th Ave, Tampa FL (Hillsborough County) marked as paid with special pricing, but the specific surveying service(s) requested remain undefined and property details are unavailable without appraiser data."}}</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:15:24.867985+00:00</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
@@ -8106,7 +8220,7 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.930495+00:00</t>
+          <t>2026-06-02T17:15:24.920317+00:00</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8232,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8133,12 +8247,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nancy Brosnahan </t>
+          <t>Nancy Brosnahan</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>214 S SWINTON AVE</t>
+          <t>214 S Swinton Ave, Delray Beach, FL 33444</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202512161958497314, "created_at": "2025-12-16T15:00:01", "customer_email": "nebrosnahan@gmail.com", "customer_id": 202512161958498334, "customer_name": "Nancy Brosnahan", "customer_type": "individual", "delivered_at": "2025-12-29T20:02:50", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0979G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000276144, "paid": false, "property_address": "214 S SWINTON AVE", "property_city": "DELRAY BEACH", "property_county": "Palm Beach County", "property_lat": "26.457426", "property_lng": "-80.07328009999999", "property_state": "FL", "property_zip": "33444", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276144", "customer_email": "nebrosnahan@gmail.com", "service_type": "Quote", "county": "", "property_address": "214 S SWINTON AVE", "customer_name": "Nancy Brosnahan "}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Nancy Brosnahan", "confidence": "HIGH"}, "client_email": {"value": "nebrosnahan@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "214 S Swinton Ave, Delray Beach, FL 33444", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service has been selected yet. Actual service(s) needed must be confirmed with client."}, "special_requirements": {"value": "Special pricing flag is active", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available, no emails, and no aerial data provided. Pool, sheds, driveways, and other features are unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not selected \u2014 only 'Quote' is listed", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fence, etc.) unknown", "Special pricing details not specified \u2014 reason for special_pricing flag unclear", "No supporting emails or appraiser data to corroborate order details", "Fieldwork date not yet scheduled (fieldwork_at is null)", "Invoice has not been created and payment has not been made"], "summary": "Nancy Brosnahan, a residential client in Delray Beach (Palm Beach County), has an open quote order for 214 S Swinton Ave with no specific survey service selected, special pricing flagged, and significant property detail gaps requiring human follow-up."}}</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:15:35.327267+00:00</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -8148,7 +8272,7 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:15.986774+00:00</t>
+          <t>2026-06-02T17:15:35.460364+00:00</t>
         </is>
       </c>
     </row>
@@ -8160,7 +8284,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8180,7 +8304,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>1106 BEVILLE RD</t>
+          <t>1106 Beville Rd, Daytona Beach, FL 32114</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202411141637401215, "created_at": "2025-12-16T10:20:05", "customer_email": "sboscarelli@firstam.com", "customer_id": 202411141641273684, "customer_name": "Scott  Boscarelli", "customer_type": "b2b", "delivered_at": "2026-02-03T20:07:08", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12127C0366H\nZONE: X\nEFF: 02/19/2014", "invoiced": false, "order_id": 1000276104, "paid": true, "property_address": "1106 BEVILLE RD", "property_city": "DAYTONA BEACH", "property_county": "VOLUSIA COUNTY", "property_lat": "29.1758954", "property_lng": "-81.0309798", "property_state": "FLORIDA", "property_zip": "32114", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-02-10T14:01:51"}, "success": true, "order_id": "1000276104", "customer_email": "sboscarelli@firstam.com", "service_type": "Land Survey Only", "county": "", "property_address": "1106 BEVILLE RD", "customer_name": "CDS-Commercial Due Diligence Services"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "CDS-Commercial Due Diligence Services", "confidence": "MEDIUM"}, "client_email": {"value": "sboscarelli@firstam.com", "confidence": "HIGH"}, "property_address": {"value": "1106 Beville Rd, Daytona Beach, FL 32114", "confidence": "HIGH"}, "property_county": {"value": "Volusia County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate required per order flags."}, "special_requirements": {"value": "Special pricing applied to this order.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email sources provided."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order contact is 'Scott Boscarelli' at First American (sboscarelli@firstam.com), but customer_name field lists 'CDS-Commercial Due Diligence Services' \u2014 clarify who the actual billing client is", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, etc.)", "No fieldwork date recorded \u2014 confirm scheduling status", "Invoice has not been sent despite order being marked Delivered and Paid \u2014 verify billing workflow"], "summary": "A completed B2B land survey order for 1106 Beville Rd, Daytona Beach, FL (Volusia County) placed by Scott Boscarelli of First American / CDS-Commercial Due Diligence Services, with special pricing applied, marked delivered and paid, but not yet invoiced."}}</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:15:46.209270+00:00</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -8190,7 +8324,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:16.043646+00:00</t>
+          <t>2026-06-02T17:15:46.259414+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -7504,7 +7504,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7527,16 +7527,37 @@
           <t>1210 Holmes Ave, Tampa, FL 33605</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>{"total_amount": 300.0, "services": [{"name": "Land Survey Only", "description": "Residential boundary survey for 1210 Holmes Ave, Tampa FL 33605, Hillsborough County. Lot 6, Block 2 (less northerly 22 ft ROW), Seiver's Subdivision of North Ybor \u2014 0.09 acres, FEMA Zone X, platted lot with straightforward legal description.", "amount": 300.0}], "pricing_reasoning": "Management pre-agreed to a negotiated rate of $300.00 for this individual client (Vianeybert Toussaint), and the order notes confirm the job was already delivered and paid with special pricing applied. No complexity upcharges are warranted: the lot is a small 0.09-acre platted subdivision parcel (well under the 0.31-acre threshold), FEMA Zone X carries no EC requirement, the legal description is a standard recorded plat reference (not metes and bounds), and there are no indicators of pool, waterfront, or heavy vegetation. The base negotiated rate of $300.00 is therefore the correct and final total.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000149306 \u2014 same address (1210 Holmes Ave, Hillsborough County), same Folio (A-07-29-19-4UX-000002-00006.0), service: Land Survey Only \u2014 flagged for human review.", "DUPLICATE_WARNING: Order 1000236163 \u2014 same address (1210 Holmes Ave, Hillsborough County), same Folio (A-07-29-19-4UX-000002-00006.0), service: Land Survey Only \u2014 flagged for human review.", "DUPLICATE_WARNING: Order 1000273263 \u2014 same address (1210 Holmes Ave, Hillsborough County), same Folio (A-07-29-19-4UX-000002-00006.0), service: Land Survey and Elevation \u2014 flagged for human review. This property has now been ordered 4 times total including the current order; management should confirm whether repeated surveys are intentional or if this is an accidental re-order.", "ORDER_NOTE: Order notes indicate job was already delivered and paid with special pricing applied. Invoice reflects agreed $300.00 negotiated rate. No additional billing action expected unless corrections are needed post-delivery.", "DATA_NOTE: Order notes state property details and legal description were unavailable pending appraiser data at time of order creation; legal description has since been confirmed via public records as Lot 6, Block 2, Seiver's Subdivision of North Ybor, PB 1/18, Hillsborough County."]}</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510201325368864, "created_at": "2026-01-23T14:23:48", "customer_email": "vianeyb14@gmail.com", "customer_id": 202510201325370288, "customer_name": "Vianeybert  Toussaint", "customer_type": "individual", "delivered_at": "2026-01-28T16:39:12", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12057C0352J\nZONE: X\nEFF: 10/07/2021", "invoiced": false, "order_id": 1000277591, "paid": true, "property_address": "1210 HOLMES AVE", "property_city": "TAMPA", "property_county": "HILLSBOROUGH COUNTY", "property_lat": "27.9703369", "property_lng": "-82.44645349999999", "property_state": "FL", "property_zip": "33605", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-28T16:39:12"}, "success": true, "order_id": "1000277591", "customer_email": "vianeyb14@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "1210 HOLMES AVE", "customer_name": "Vianeybert  Toussaint"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Vianeybert Toussaint", "confidence": "HIGH"}, "client_email": {"value": "vianeyb14@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1210 Holmes Ave, Tampa, FL 33605", "confidence": "HIGH"}, "property_county": {"value": "Hillsborough County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as Land Survey Only in FTF order data"}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no matching emails found"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, etc.)", "Reason for special pricing not documented", "Fieldwork date not yet scheduled (fieldwork_at is null)", "Invoice has not been generated (invoiced: false)"], "summary": "Residential land survey order for Vianeybert Toussaint at 1210 Holmes Ave, Tampa FL 33605 (Hillsborough County), already delivered and paid with special pricing applied, but property details and legal description are unavailable pending appraiser data."}}</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1780420923219</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>2026-06-02T16:57:43.158138+00:00</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:22:04.112426+00:00</t>
+        </is>
+      </c>
+      <c r="R119" t="n">
+        <v>300</v>
+      </c>
       <c r="T119" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.129809+00:00</t>
@@ -7544,7 +7565,7 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>2026-06-02T16:57:43.250014+00:00</t>
+          <t>2026-06-02T17:22:04.164011+00:00</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7577,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7579,16 +7600,37 @@
           <t>12035 Polo Club Rd, Wellington, FL 33414</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "AI pricing failed: Unterminated string starting at: line 28 column 5 (char 2936). Manual review required.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "AI pricing error \u2014 needs manual quote", "flags": ["ai_error"]}</t>
+        </is>
+      </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202601141641564449, "created_at": "2026-01-14T11:50:03", "customer_email": "treefolium@icloud.com", "customer_id": 202601141642491223, "customer_name": "Johana Payot", "customer_type": "b2b", "delivered_at": "2026-01-20T15:15:58", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0563F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000277194, "paid": true, "property_address": "12035 POLO CLUB RD", "property_city": "WELLINGTON", "property_county": "Palm Beach County", "property_lat": "26.6413026", "property_lng": "-80.2372546", "property_state": "FL", "property_zip": "33414", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-20T15:15:58"}, "success": true, "order_id": "1000277194", "customer_email": "treefolium@icloud.com", "service_type": "Quote", "county": "", "property_address": "12035 POLO CLUB RD", "customer_name": "Tree Folium Landscape Co."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Tree Folium Landscape Co.", "confidence": "HIGH"}, "client_email": {"value": "treefolium@icloud.com", "confidence": "HIGH"}, "property_address": {"value": "12035 Polo Club Rd, Wellington, FL 33414", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., boundary, topographic, elevation certificate) has been identified. Needs clarification."}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not defined \u2014 'Quote' is not a deliverable service", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, outbuildings, etc.)", "No matching emails found \u2014 unable to confirm scope from client communications", "Fieldwork date not scheduled", "Invoice has not been sent \u2014 billing details incomplete", "Client contact name discrepancy: FTF order shows 'Johana Payot' as customer name but company name is 'Tree Folium Landscape Co.' \u2014 confirm correct billing contact"], "summary": "A B2B quote order for Tree Folium Landscape Co. at 12035 Polo Club Rd, Wellington, FL (Palm Beach County) has been delivered with special pricing applied, but the specific survey service requested has not been identified and key property details are missing."}}</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1780420946825</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>2026-06-02T17:03:02.322969+00:00</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:22:29.847151+00:00</t>
+        </is>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
       <c r="T120" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.226892+00:00</t>
@@ -7596,7 +7638,7 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>2026-06-02T17:03:02.372963+00:00</t>
+          <t>2026-06-02T17:22:29.899809+00:00</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7650,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7631,16 +7673,37 @@
           <t>12952 Mizner Way, Wellington, FL 33414</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>{"total_amount": 562.0, "services": [{"name": "Land Survey Only", "description": "Boundary/land survey for Lot 2, Mizner Estates of Palm Beach Polo and Country Club Wellington P.U.D., Plat Book 84 Page 65, Palm Beach County. Platted lot \u2014 straightforward legal description with no metes and bounds complexity. Base rate per Franco &amp; Associates negotiated agreement.", "amount": 500.0}, {"name": "Lot Size Complexity Upcharge (0.31\u20130.50 ac)", "description": "Property is 0.36 acres, falling within the 0.31\u20130.50 acre tier. Upcharge applied to reflect additional field time relative to a standard sub-0.30 ac residential lot.", "amount": 62.0}], "pricing_reasoning": "The client Franco &amp; Associates has a management-negotiated base survey rate of $500.00, which is used as the starting point. The lot is 0.36 acres, placing it squarely in the 0.31\u20130.50 ac complexity tier warranting a $62.00 upcharge. No Elevation Certificate was ordered, FEMA Zone X carries no EC requirement, no pool, waterfront, heavy vegetation, metes-and-bounds, or Monroe County factors are indicated by the legal description or county data, so no additional upcharges are applied.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE_DUPLICATE: Order 1000273953 references the same address (12952 Mizner Way, Palm Beach County), same service type (Land Survey Only), and identical folio/coordinates. Human review recommended before scheduling fieldwork to avoid redundant mobilization.", "ORDER_STATUS: Order is currently On Hold with no fieldwork scheduled per order notes. Pricing is provided for reference; do not dispatch crew until hold is cleared.", "CLIENT_ORDER_COUNT: Franco &amp; Associates shows 0 prior orders with NexGen despite OLD_TITLE tier classification. Verify client standing and negotiated rate confirmation with management before invoicing."]}</t>
+        </is>
+      </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202601122012476131, "created_at": "2026-01-12T15:16:00", "customer_email": "jeremy@atfranco.com", "customer_id": 202601122013460244, "customer_name": "Jeremy Harrissmith", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0544F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000277088, "paid": true, "property_address": "12952 MIZNER WAY", "property_city": "WELLINGTON", "property_county": "Palm Beach County", "property_lat": "26.64221", "property_lng": "-80.2515763", "property_state": "FL", "property_zip": "33414", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000277088", "customer_email": "jeremy@atfranco.com", "service_type": "Land Survey Only", "county": "", "property_address": "12952 MIZNER WAY", "customer_name": "Franco &amp; Associates"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Franco &amp; Associates", "confidence": "MEDIUM"}, "client_email": {"value": "jeremy@atfranco.com", "confidence": "HIGH"}, "property_address": {"value": "12952 Mizner Way, Wellington, FL 33414", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing flagged; order currently On Hold (status_code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments found"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: FTF order lists 'Jeremy Harrissmith' as customer_name but outer payload lists 'Franco &amp; Associates' \u2014 needs human verification", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, etc.)", "Reason for On Hold status not specified", "Scope of 'Land Survey Only' not clarified (boundary, topographic, etc.)", "No fieldwork date scheduled", "No invoice sent \u2014 pricing needs to be confirmed given special_pricing flag"], "summary": "B2B Land Survey Only order for 12952 Mizner Way, Wellington FL (Palm Beach County) placed by Franco &amp; Associates, currently On Hold with special pricing flagged and no fieldwork scheduled."}}</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1780420968275</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>2026-06-02T17:03:12.222586+00:00</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:22:48.662189+00:00</t>
+        </is>
+      </c>
+      <c r="R121" t="n">
+        <v>562</v>
+      </c>
       <c r="T121" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.279946+00:00</t>
@@ -7648,7 +7711,7 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>2026-06-02T17:03:12.272359+00:00</t>
+          <t>2026-06-02T17:22:48.714494+00:00</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8399,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8356,7 +8419,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>6100 HOLLYWOOD BLVD</t>
+          <t>6100 Hollywood Blvd, Hollywood, Florida 33024</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202512161435103028, "created_at": "2025-12-16T10:57:03", "customer_email": "jjonlaw@hotmail.com", "customer_id": 202512161435103387, "customer_name": "James Jean-Francois", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0564J\nZONE: AH\nELEV: 09 FT\nZONE: X500\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000276101, "paid": false, "property_address": "6100 HOLLYWOOD BLVD", "property_city": "HOLLYWOOD", "property_county": "BROWARD COUNTY", "property_lat": "26.0092779", "property_lng": "-80.2100833", "property_state": "FLORIDA", "property_zip": "33024", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276101", "customer_email": "jjonlaw@hotmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "6100 HOLLYWOOD BLVD", "customer_name": "James Jean-Francois"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "James Jean-Francois", "confidence": "HIGH"}, "client_email": {"value": "jjonlaw@hotmail.com", "confidence": "HIGH"}, "property_address": {"value": "6100 Hollywood Blvd, Hollywood, Florida 33024", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data. No elevation certificate requested."}, "special_requirements": {"value": "Property is in a split flood zone: AH (Elev 09 FT) and X500, per FIRM panel 12011C0564J effective 07/31/2024. Order is currently On Hold.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features (pool, shed, driveway, etc.) unknown \u2014 no aerial or appraiser data", "Order is On Hold \u2014 reason for hold not specified, needs human review", "No urgency or deadline indicated", "No matching emails found to supplement order details"], "summary": "Individual residential client James Jean-Francois has ordered a Land Survey Only for 6100 Hollywood Blvd, Hollywood, Broward County FL 33024, currently on hold with split flood zone designations (AH and X500) and no supporting appraiser or email data available."}}</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:21:05.053557+00:00</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
@@ -8366,7 +8439,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:16.100907+00:00</t>
+          <t>2026-06-02T17:21:05.105767+00:00</t>
         </is>
       </c>
     </row>
@@ -8378,7 +8451,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8398,7 +8471,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>118 NEWHAM WAY</t>
+          <t>118 Newham Way, Kissimmee, FL 34758</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202511061522427450, "created_at": "2025-12-15T15:12:04", "customer_email": "kaila@emsteam.us", "customer_id": 202511061522427550, "customer_name": "Kaila", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12097C0230G\nZONE: X\nEFF: 06/18/2013", "invoiced": false, "order_id": 1000276064, "paid": false, "property_address": "118 NEWHAM WAY", "property_city": "KISSIMMEE", "property_county": "OSCEOLA COUNTY", "property_lat": "28.1881449", "property_lng": "-81.494078", "property_state": "FLORIDA", "property_zip": "34758", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276064", "customer_email": "kaila@emsteam.us", "service_type": "Land Survey Only", "county": "", "property_address": "118 NEWHAM WAY", "customer_name": "Kaila"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Kaila", "confidence": "HIGH"}, "client_email": {"value": "kaila@emsteam.us", "confidence": "HIGH"}, "property_address": {"value": "118 Newham Way, Kissimmee, FL 34758", "confidence": "HIGH"}, "property_county": {"value": "Osceola County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments to reference"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Full client/company name \u2014 only first name 'Kaila' provided", "Legal description of the property", "Lot size", "Structure square footage", "Property features (pool, shed, fencing, driveways, etc.)", "Special requirements or scope clarification", "Order is currently 'On Hold' \u2014 reason for hold unknown", "No invoice or payment information established", "County property appraiser data unavailable", "No matching emails found \u2014 no additional context from client communications"], "summary": "B2B order from Kaila (emsteam.us) for a Land Survey Only at 118 Newham Way, Kissimmee, FL 34758 (Osceola County), currently on hold with no invoicing, lot data, or legal description available."}}</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:21:14.182406+00:00</t>
         </is>
       </c>
       <c r="T136" t="inlineStr">
@@ -8408,7 +8491,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:16.158014+00:00</t>
+          <t>2026-06-02T17:21:14.234409+00:00</t>
         </is>
       </c>
     </row>
@@ -8420,7 +8503,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8440,7 +8523,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>235 WORTH CT</t>
+          <t>235 Worth Ct, West Palm Beach, FL 33405</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202512151719317720, "created_at": "2025-12-15T12:22:05", "customer_email": "lm1arch@bellsouth.net", "customer_id": 202512151719318715, "customer_name": "Lee Moldoff", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0591G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000276043, "paid": true, "property_address": "235 WORTH CT", "property_city": "WEST PALM BEACH", "property_county": "Palm Beach County", "property_lat": "26.6729137", "property_lng": "-80.05204379999999", "property_state": "FL", "property_zip": "33405", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276043", "customer_email": "lm1arch@bellsouth.net", "service_type": "CAD file", "county": "", "property_address": "235 WORTH CT", "customer_name": "Lee Moldoff"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Lee Moldoff", "confidence": "HIGH"}, "client_email": {"value": "lm1arch@bellsouth.net", "confidence": "HIGH"}, "property_address": {"value": "235 Worth Ct, West Palm Beach, FL 33405", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated in the data"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments present"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, structures, etc.)", "No county appraiser data available to cross-reference", "Reason for 'On Hold' status not specified", "Scope of CAD file not clarified (boundary, as-built, topo, etc.)", "No fieldwork or delivery dates scheduled", "Invoice has not been sent despite order being marked paid \u2014 needs reconciliation", "No customer data returned from FTF customer record"], "summary": "Individual client Lee Moldoff has ordered a CAD file for a residential property at 235 Worth Ct, West Palm Beach FL 33405 (Flood Zone X), with special pricing applied and the order currently on hold pending further action."}}</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:21:24.173372+00:00</t>
         </is>
       </c>
       <c r="T137" t="inlineStr">
@@ -8450,7 +8543,7 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:16.215726+00:00</t>
+          <t>2026-06-02T17:21:24.223606+00:00</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8555,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8482,7 +8575,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>1248 NE 8TH AVE</t>
+          <t>1248 NE 8TH AVE, DELRAY BEACH, FL 33483</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202512121827218909, "created_at": "2025-12-12T13:31:00", "customer_email": "abhi@kanthandesign.com", "customer_id": 202512121828051160, "customer_name": "ABHI KANTHAN", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0977G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000275962, "paid": true, "property_address": "1248 NE 8TH AVE", "property_city": "DELRAY BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.4784572", "property_lng": "-80.065563", "property_state": "FL", "property_zip": "33483", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275962", "customer_email": "abhi@kanthandesign.com", "service_type": "CAD file", "county": "", "property_address": "1248 NE 8TH AVE", "customer_name": "KANTHAN DESIGN CORPORATION"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "KANTHAN DESIGN CORPORATION", "confidence": "HIGH"}, "client_email": {"value": "abhi@kanthandesign.com", "confidence": "HIGH"}, "property_address": {"value": "1248 NE 8TH AVE, DELRAY BEACH, FL 33483", "confidence": "HIGH"}, "property_county": {"value": "PALM BEACH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, etc.)", "County appraiser data unavailable \u2014 no county passed to appraiser lookup", "No matching emails found \u2014 no additional context from client correspondence", "Order is On Hold \u2014 reason for hold not specified, needs human review", "Urgency/deadline not specified", "Fieldwork date not scheduled", "Invoice has not been sent and order has not been delivered"], "summary": "B2B CAD file order for Kanthan Design Corporation at 1248 NE 8th Ave, Delray Beach FL (Palm Beach County) is currently On Hold with special pricing applied, awaiting resolution before fieldwork can be scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:21:34.092680+00:00</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
@@ -8492,7 +8595,7 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:16.273199+00:00</t>
+          <t>2026-06-02T17:21:34.145312+00:00</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8607,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8524,7 +8627,17 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>129 EGRET AVE</t>
+          <t>129 Egret Ave, Naples, FL 34108</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202512111446279347, "created_at": "2025-12-11T09:47:02", "customer_email": "trojanowski228@gmail.com", "customer_id": 202512111446281169, "customer_name": "Daniela Trojanowski", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12021C0189J\nZONE: AE\nELEV: 10 FT\nEFF: 02/08/2024", "invoiced": false, "order_id": 1000275872, "paid": true, "property_address": "129 EGRET AVE", "property_city": "NAPLES", "property_county": "COLLIER COUNTY", "property_lat": "26.2691604", "property_lng": "-81.8233018", "property_state": "FL", "property_zip": "34108", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275872", "customer_email": "trojanowski228@gmail.com", "service_type": "CAD file", "county": "", "property_address": "129 EGRET AVE", "customer_name": "Daniela Trojanowski"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Daniela Trojanowski", "confidence": "HIGH"}, "client_email": {"value": "trojanowski228@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "129 Egret Ave, Naples, FL 34108", "confidence": "HIGH"}, "property_county": {"value": "Collier County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11); flood zone data available: 12021C0189J, Zone AE, Elevation 10 ft, Effective 02/08/2024", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not available", "Legal description not available", "Structure square footage not available", "Property features (pool, shed, structures, driveways) unknown \u2014 county appraiser unavailable", "No county provided in top-level FTF county field (though Collier County is in property data)", "Reason for On Hold status unknown \u2014 may require human review before proceeding", "No customer data returned from FTF customer lookup", "No matching emails found \u2014 no additional context or attachments available", "Elevation certificate not requested but flood zone is AE at 10 ft \u2014 worth confirming with client"], "summary": "Individual residential client Daniela Trojanowski has ordered a CAD file for 129 Egret Ave, Naples, FL 34108 (Collier County, Flood Zone AE), with special pricing applied and the order currently on hold pending further action."}}</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:21:44.854225+00:00</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
@@ -8534,7 +8647,7 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:16.379011+00:00</t>
+          <t>2026-06-02T17:21:44.907081+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -7723,7 +7723,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7746,16 +7746,37 @@
           <t>10801 SW FOX BROWN RD, INDIANTOWN, FL 34956</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>{"total_amount": 10000.0, "services": [{"name": "Boundary Survey", "description": "Boundary survey for 20.93-acre metes-and-bounds parcel at 10801 SW Fox Brown Rd, Indiantown, Martin County, FL. Management-agreed fixed rate of $10,000.00 applies per client negotiation on file. Lot exceeds 5.00 acres (escalation threshold), but negotiated rate explicitly overrides standard pricing matrix. Legal description involves a metes-and-bounds cutout (south 670 ft of west 3250.75 ft, less ROW and county-deeded strip), which would normally trigger a metes-and-bounds upcharge \u2014 absorbed into the agreed rate.", "amount": 10000.0}], "pricing_reasoning": "Management has established a firm negotiated rate of $10,000.00 for this specific client (Maurece Williams) on this specific order. Although the lot size of 20.93 acres would normally trigger an escalation flag under the standard pricing matrix (lot &gt; 5.00 acres), the management-agreed rate explicitly supersedes the standard matrix and is used as the total billable amount. No additional complexity upcharges are applied on top of a pre-negotiated lump-sum rate. No Elevation Certificate was requested, and FEMA Zone X carries no EC requirement.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["LOT_EXCEEDS_5_ACRES: At 20.93 acres this parcel would normally require management escalation under standard pricing rules. Management has already reviewed and set a negotiated fixed rate of $10,000.00 \u2014 no further escalation needed.", "IDENTITY_UNVERIFIED: Order notes indicate client identity could not be fully verified due to name/email conflicts. Order is currently On Hold per notes. Confirm hold release and identity resolution before issuing final invoice.", "ORDER_ON_HOLD: Notes explicitly state the order is On Hold with $8,500 referenced as due in notes, but the company's negotiated rate on file is $10,000.00. Use the $10,000.00 figure per the rate field; flag discrepancy with $8,500 figure in notes for management clarification.", "RATE_NOTE_DISCREPANCY: Order notes reference '$8,500 due' while the negotiated rate field states $10,000.00. Management should confirm which figure controls before invoice is sent."]}</t>
+        </is>
+      </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202601162040440121, "created_at": "2026-01-12T13:15:00", "customer_email": "maurecewilliams@yahoo.com", "customer_id": 202601162040441013, "customer_name": "Maurece Williams", "customer_type": "individual", "delivered_at": null, "due_amount": 8500.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12085C0250G\nZONE: X\nEFF: 03/16/2015", "invoiced": false, "order_id": 1000277069, "paid": false, "property_address": "10801 SW FOX BROWN RD", "property_city": "INDIANTOWN", "property_county": "Martin County", "property_lat": "27.0757825", "property_lng": "-80.5123416", "property_state": "FL", "property_zip": "34956", "service_type": "Boundary Survey", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-20T17:05:07"}, "success": true, "order_id": "1000277069", "customer_email": "maurecwilliams@yahoo.com", "service_type": "Boundary Survey", "county": "", "property_address": "10801 SW FOX BROWN RD", "customer_name": "mark Ebersolm"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Maurece Williams", "confidence": "MEDIUM"}, "client_email": {"value": "maurecewilliams@yahoo.com", "confidence": "MEDIUM"}, "property_address": {"value": "10801 SW FOX BROWN RD, INDIANTOWN, FL 34956", "confidence": "HIGH"}, "property_county": {"value": "Martin County", "confidence": "HIGH"}, "services_requested": {"value": ["Boundary Survey"], "confidence": "HIGH", "notes": "Explicitly stated in order data. Elevation certificate is not requested (elevation_cert: false)."}, "special_requirements": {"value": "Special pricing applied. Order is currently On Hold (status_code 11).", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available. County appraiser unavailable and no aerial or email data provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: FTF order data shows 'Maurece Williams' but outer FTF payload shows 'mark Ebersolm' \u2014 requires human verification", "Client email conflict: order data shows 'maurecewilliams@yahoo.com' but outer payload shows 'maurecwilliams@yahoo.com' (possible typo) \u2014 requires human verification", "Lot size unknown \u2014 no appraiser or parcel data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, structures, etc.) unknown \u2014 no aerial or appraiser data", "Reason for On Hold status not documented", "Fieldwork and delivery dates not yet scheduled", "No matching customer email records found \u2014 customer identity unverified"], "summary": "Boundary survey order for Maurece Williams (identity unverified due to name/email conflicts) at 10801 SW Fox Brown Rd, Indiantown, FL 34956 (Martin County), currently On Hold with special pricing applied and $8,500 due."}}</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1780421296493</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>2026-06-02T17:03:23.369002+00:00</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:28:17.474154+00:00</t>
+        </is>
+      </c>
+      <c r="R122" t="n">
+        <v>10000</v>
+      </c>
       <c r="T122" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.333845+00:00</t>
@@ -7763,7 +7784,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>2026-06-02T17:03:23.420786+00:00</t>
+          <t>2026-06-02T17:28:17.521304+00:00</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7796,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7798,16 +7819,37 @@
           <t>10651 SW 67TH CT, MIAMI, FL 33156</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>{"total_amount": 637.0, "services": [{"name": "Land Survey (Boundary)", "description": "Residential boundary/land survey only \u2014 negotiated flat rate agreed upon by management for this individual client (Jesse Goldstein).", "amount": 500.0}, {"name": "Lot Size Complexity Upcharge (0.51\u20131.00 ac)", "description": "Lot size is 0.96 acres, falling in the 0.51\u20131.00 ac bracket. Standard complexity upcharge applied for larger residential parcel requiring additional field time and corner-setting effort.", "amount": 137.0}], "pricing_reasoning": "Management agreed to a $500.00 base survey rate for this individual client. No EC was requested (Land Survey Only). The lot is 0.96 acres, squarely in the 0.51\u20131.00 ac tier, warranting the $137.00 complexity upcharge. No pool, waterfront, metes-and-bounds, heavy vegetation, Monroe County, or VE zone factors are present; the legal description is a clean platted lot reference, so no additional upcharges apply.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: This property (10651 SW 67TH CT, Folio 2050110050100) has appeared in at least three prior orders \u2014 1000238325 (Land Survey + EC), 1000269888 (Land Survey Only), and 1000278532 (Land Survey Only). Human review is recommended to confirm this is not a duplicate billing and that the work has not already been performed and invoiced.", "ORDER_NOTE: Notes indicate this order was 'already delivered and paid with special pricing applied.' Verify whether this invoice is for documentation/reconciliation purposes only and that no duplicate payment is collected."]}</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202508142004390852, "created_at": "2026-01-12T08:46:00", "customer_email": "jgoldstein94@me.com", "customer_id": 202508142004391949, "customer_name": "Jesse Goldstein", "customer_type": "individual", "delivered_at": "2026-02-11T17:45:47", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0466L\nZONE: AE\nELEV: 10 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000277032, "paid": true, "property_address": "10651 SW 67TH CT", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.6719398", "property_lng": "-80.30381249999999", "property_state": "FL", "property_zip": "33156", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-02-11T17:45:47"}, "success": true, "order_id": "1000277032", "customer_email": "jgoldstein94@me.com", "service_type": "Land Survey Only", "county": "", "property_address": "10651 SW 67TH CT", "customer_name": "Jesse Goldstein"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Jesse Goldstein", "confidence": "HIGH"}, "client_email": {"value": "jgoldstein94@me.com", "confidence": "HIGH"}, "property_address": {"value": "10651 SW 67TH CT, MIAMI, FL 33156", "confidence": "HIGH"}, "property_county": {"value": "MIAMI-DADE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested"}, "special_requirements": {"value": "Special pricing applied; property is in FEMA Flood Zone AE (Panel 12086C0466L, base elevation 10 ft, effective 09/11/2009)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not available", "Legal description not available", "Structure square footage not available", "Property features (pool, shed, driveways, structures) unknown \u2014 no aerial, appraiser, or email data", "County appraiser data unavailable (county field was blank in lookup)", "No matching emails found to supplement order details", "Reason for special pricing not documented"], "summary": "Residential land survey only order for Jesse Goldstein at 10651 SW 67TH CT, Miami, FL 33156 (Miami-Dade County), located in FEMA Flood Zone AE, already delivered and paid with special pricing applied."}}</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1780421313632</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>2026-06-02T17:03:32.160923+00:00</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:28:36.696293+00:00</t>
+        </is>
+      </c>
+      <c r="R123" t="n">
+        <v>637</v>
+      </c>
       <c r="T123" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.387727+00:00</t>
@@ -7815,7 +7857,7 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>2026-06-02T17:03:32.211121+00:00</t>
+          <t>2026-06-02T17:28:36.744218+00:00</t>
         </is>
       </c>
     </row>
@@ -7827,7 +7869,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7850,16 +7892,37 @@
           <t>2362 BYRON ST, PALM SPRINGS, FL 33406</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>{"total_amount": 475.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for LOT 82, PRESTON SQUARE, Palm Beach County. Small residential lot (0.04 ac), platted subdivision with recorded plat book reference \u2014 straightforward legal description, no metes and bounds, no waterfront, no pool, no heavy vegetation indicators, no Monroe County mobilization applicable.", "amount": 475.0}], "pricing_reasoning": "Client is an individual homeowner with no negotiated rate, so the $475.00 default individual base rate applies. The lot is extremely small at 0.04 acres (well under the 0.31-acre threshold for any size upcharge), the legal description is a simple platted lot reference requiring no metes-and-bounds complexity upcharge, and no other field complexity factors (pool, waterfront, heavy vegetation, Monroe County) are supported by the available data. FEMA Zone AE and the elevation data are noted but no Elevation Certificate was ordered, so no EC line item is added.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000192906 exists for 2366 BYRON ST (adjacent address, same coordinates ~26.6416723, -80.0860004) with service 'Land Survey and Elevation' in Palm Beach County. This order (2362 BYRON ST, Land Survey Only) may be a near-duplicate or related order for the same or immediately adjacent property. Human review recommended before scheduling fieldwork.", "ORDER_ON_HOLD: No fieldwork or delivery date is currently scheduled. Order status is On Hold \u2014 confirm client intent and site access before proceeding.", "CERTIFICATION_NOTE: Survey is to be certified to MUHAMMED MUGLA per order instructions."]}</t>
+        </is>
+      </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202601061807385066, "created_at": "2026-01-06T13:35:04", "customer_email": "eminmugla09@gmail.com", "customer_id": 202601061807385173, "customer_name": "muhammed mugla", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0589F\nZONE: AE\nELEV: 11.2 FT\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000276801, "paid": false, "property_address": "2362 BYRON ST", "property_city": "PALM SPRINGS", "property_county": "PALM BEACH COUNTY", "property_lat": "26.6417043", "property_lng": "-80.08593429999999", "property_state": "FLORIDA", "property_zip": "33406", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276801", "customer_email": "eminmugla09@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "2362 BYRON ST", "customer_name": "muhammed mugla"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "muhammed mugla", "confidence": "HIGH"}, "client_email": {"value": "eminmugla09@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "2362 BYRON ST, PALM SPRINGS, FL 33406", "confidence": "HIGH"}, "property_county": {"value": "PALM BEACH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as Land Survey Only; elevation certificate is false"}, "special_requirements": {"value": "Property is in FEMA Flood Zone AE (panel 12099C0589F, effective 10/05/2017, base flood elevation 11.2 FT). Order is currently On Hold.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data, no emails, and no aerial data available to determine pool, shed, driveways, or other structures"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Order is On Hold \u2014 reason for hold not specified, needs human review", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fences, etc.) unknown \u2014 no appraiser or aerial data", "No matching emails found \u2014 no additional context from client communications", "County was blank in the top-level FTF fields (though present in order data body)", "Invoice not yet created and payment not collected \u2014 needs follow-up"], "summary": "Individual residential client muhammed mugla has ordered a Land Survey Only for 2362 Byron St, Palm Springs, FL 33406 (Palm Beach County, Flood Zone AE), but the order is currently On Hold with no fieldwork or delivery date scheduled."}}</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1780421332517</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>2026-06-02T17:03:42.665040+00:00</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:28:53.515973+00:00</t>
+        </is>
+      </c>
+      <c r="R124" t="n">
+        <v>475</v>
+      </c>
       <c r="T124" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.441837+00:00</t>
@@ -7867,7 +7930,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>2026-06-02T17:03:42.772543+00:00</t>
+          <t>2026-06-02T17:28:53.577493+00:00</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8722,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8679,7 +8742,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>1519 SW 18TH AVE</t>
+          <t>1519 SW 18TH AVE, FORT LAUDERDALE, FL 33312</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202512021724214710, "created_at": "2025-12-10T15:09:05", "customer_email": "ryantimberg@gmail.com", "customer_id": 202512021724215839, "customer_name": "Ryan Timberg", "customer_type": "individual", "delivered_at": "2025-12-22T14:15:01", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0556J\nZONE: AE\nELEV: 06 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000275849, "paid": true, "property_address": "1519 SW 18TH AVE", "property_city": "FORT LAUDERDALE", "property_county": "BROWARD COUNTY", "property_lat": "26.1008497", "property_lng": "-80.1651368", "property_state": "FL", "property_zip": "33312", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275849", "customer_email": "ryantimberg@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "1519 SW 18TH AVE", "customer_name": "Ryan Timberg"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Ryan Timberg", "confidence": "HIGH"}, "client_email": {"value": "ryantimberg@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1519 SW 18TH AVE, FORT LAUDERDALE, FL 33312", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested (elevation_cert: false)"}, "special_requirements": {"value": "Special pricing applied; property is in FEMA Flood Zone AE (Panel 12011C0556J, Elev 06 FT, Eff 07/31/2024)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no aerial or email data provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser unavailable and no parcel data provided", "Legal description not available", "Structure square footage unknown", "Property features (pool, shed, fences, driveways, etc.) unknown \u2014 no aerial or appraiser data", "No matching emails found to supplement order details", "Fieldwork date not yet scheduled (fieldwork_at: null)", "Invoice has not been sent (invoiced: false, estimate_sent: false) despite order being delivered and paid"], "summary": "Individual residential client Ryan Timberg has a delivered and paid Land Survey Only order for 1519 SW 18TH AVE, Fort Lauderdale, FL 33312 (Broward County, Flood Zone AE) with special pricing applied, but property details such as lot size, legal description, and site features are unavailable due to missing appraiser and supplemental data."}}</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:27:15.348149+00:00</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
@@ -8689,7 +8762,7 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:16.437025+00:00</t>
+          <t>2026-06-02T17:27:15.394797+00:00</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8774,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8721,7 +8794,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>4425 HICKORY DR</t>
+          <t>4425 Hickory Dr, Palm Beach Gardens, FL 33418</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202512091810542329, "created_at": "2025-12-11T16:27:03", "customer_email": "santiagoandjade@gmail.com", "customer_id": 202512091810542550, "customer_name": "Jennifer", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0378F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000275758, "paid": false, "property_address": "4425 HICKORY DR", "property_city": "PALM BEACH GARDENS", "property_county": "PALM BEACH COUNTY", "property_lat": "26.8358163", "property_lng": "-80.1121611", "property_state": "FLORIDA", "property_zip": "33418", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275758", "customer_email": "santiagoandjade@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "4425 HICKORY DR", "customer_name": "Jennifer"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Jennifer", "confidence": "HIGH"}, "client_email": {"value": "santiagoandjade@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "4425 Hickory Dr, Palm Beach Gardens, FL 33418", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in FTF order data"}, "special_requirements": {"value": "None noted", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no matching emails or attachments found"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Last name for client 'Jennifer' \u2014 email domain suggests possible last name 'Santiago' or shared account", "Lot size not available \u2014 county appraiser data unavailable", "Legal description not available \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, etc.)", "Order is currently On Hold \u2014 reason for hold not specified", "No fieldwork date scheduled", "No invoice or payment information present", "No estimate has been sent to client"], "summary": "Residential land survey order for Jennifer at 4425 Hickory Dr, Palm Beach Gardens FL 33418 (Palm Beach County), currently on hold with no fieldwork scheduled, estimate unsent, and property details such as lot size and legal description unavailable."}}</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:27:24.105173+00:00</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
@@ -8731,7 +8814,7 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:16.496741+00:00</t>
+          <t>2026-06-02T17:27:24.152430+00:00</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8826,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8763,7 +8846,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>13179 S INDIAN RIVER DR</t>
+          <t>13179 S Indian River Dr, Jensen Beach, FL 34957</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202512091630395030, "created_at": "2025-12-09T11:32:00", "customer_email": "AC@LawrenceLeeConstruction.com", "customer_id": 202512091631053684, "customer_name": "Ariana  Cammuse", "customer_type": "b2b", "delivered_at": "2025-12-11T17:57:18", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12111C0313K\nZONE: X\nEFF: 02/19/2020", "invoiced": false, "order_id": 1000275742, "paid": false, "property_address": "13179 S INDIAN RIVER DR", "property_city": "JENSEN BEACH", "property_county": "St. Lucie County", "property_lat": "27.2751283", "property_lng": "-80.2417656", "property_state": "FL", "property_zip": "34957", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275742", "customer_email": "AC@LawrenceLeeConstruction.com", "service_type": "Land Survey Only", "county": "", "property_address": "13179 S INDIAN RIVER DR", "customer_name": "Lawrence Lee Construction Services, Inc."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Lawrence Lee Construction Services, Inc.", "confidence": "HIGH"}, "client_email": {"value": "AC@LawrenceLeeConstruction.com", "confidence": "HIGH"}, "property_address": {"value": "13179 S Indian River Dr, Jensen Beach, FL 34957", "confidence": "HIGH"}, "property_county": {"value": "St. Lucie County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested (elevation_cert: false)"}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial imagery, or email attachments provided. Property is on S Indian River Dr which may suggest waterfront/riparian features \u2014 needs field verification."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided \u2014 needs appraiser lookup or field measurement", "Legal description not available \u2014 St. Lucie County appraiser lookup needed", "Structure square footage unknown", "Property features (structures, pool, shed, fencing, driveways) not documented", "No matching emails found \u2014 scope confirmation from client may be needed", "Invoice has not been sent and order is unpaid \u2014 billing action required", "Fieldwork date not scheduled (fieldwork_at: null)", "County field was blank in order root object despite being populated in data object \u2014 verify data consistency"], "summary": "B2B land survey order for Lawrence Lee Construction Services at 13179 S Indian River Dr, Jensen Beach, FL (St. Lucie County), delivered but not yet invoiced, with special pricing applied and no elevation certificate requested."}}</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:27:35.109865+00:00</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
@@ -8773,7 +8866,7 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:16.555277+00:00</t>
+          <t>2026-06-02T17:27:35.156255+00:00</t>
         </is>
       </c>
     </row>
@@ -8785,7 +8878,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8805,7 +8898,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>525 36TH AVE NE</t>
+          <t>525 36TH AVE NE, ST. PETERSBURG, FL 33704</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202509191452179486, "created_at": "2025-12-09T11:00:02", "customer_email": "lorelib@gcihomesinc.com", "customer_id": 202509191452179607, "customer_name": "Loreli Brobst", "customer_type": "individual", "delivered_at": "2025-12-09T18:20:16", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12103C0217H\nZONE: AE\nELEV: 10 FT\nEFF: 08/24/2021", "invoiced": false, "order_id": 1000275732, "paid": true, "property_address": "525 36TH AVE NE", "property_city": "ST. PETERSBURG", "property_county": "PINELLAS COUNTY", "property_lat": "27.8051659", "property_lng": "-82.6282341", "property_state": "FL", "property_zip": "33704", "service_type": "Land Survey Only", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275732", "customer_email": "lorelib@gcihomesinc.com", "service_type": "Land Survey Only", "county": "", "property_address": "525 36TH AVE NE", "customer_name": "Loreli Brobst"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Loreli Brobst", "confidence": "HIGH"}, "client_email": {"value": "lorelib@gcihomesinc.com", "confidence": "HIGH"}, "property_address": {"value": "525 36TH AVE NE, ST. PETERSBURG, FL 33704", "confidence": "HIGH"}, "property_county": {"value": "Pinellas County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested (elevation_cert: false)"}, "special_requirements": {"value": "Property is in FEMA Flood Zone AE (Panel 12103C0217H, effective 08/24/2021, BFE 10 ft). No elevation certificate ordered.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features provided; county appraiser data unavailable and no emails or attachments present"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM", "notes": "Customer type listed as 'individual' but email domain gcihomesinc.com suggests a real estate or home services business affiliation; warrants verification"}, "urgency": {"value": "normal", "confidence": "MEDIUM", "notes": "No rush indicators present; order was created and delivered same day (2025-12-09) but no explicit rush flag"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, fencing, driveways, etc.) unknown \u2014 no appraiser data or aerial available", "Client tier ambiguous \u2014 email domain (gcihomesinc.com) suggests possible business/B2B relationship despite 'individual' customer type; needs human verification", "No matching emails found \u2014 no additional context from client communications", "Fieldwork date is null \u2014 unclear if fieldwork has been scheduled or completed", "Invoice not yet generated (invoiced: false) despite order being delivered and paid"], "summary": "A delivered and paid Land Survey Only order for Loreli Brobst at 525 36th Ave NE, St. Petersburg, FL 33704 (Pinellas County), located in FEMA Flood Zone AE, with no elevation certificate requested and several property detail gaps requiring human input."}}</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:27:47.648363+00:00</t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
@@ -8815,7 +8918,7 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:16.614876+00:00</t>
+          <t>2026-06-02T17:27:47.696193+00:00</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8930,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8847,7 +8950,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>704 E TANGERINE CT</t>
+          <t>704 E Tangerine Ct, Winter Garden, FL 34787</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202512091540398631, "created_at": "2025-12-09T10:42:01", "customer_email": "allan@lrgconstruction.com", "customer_id": 202512091540399657, "customer_name": "Allan Lougheed", "customer_type": "individual", "delivered_at": "2025-12-09T18:19:28", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12095C0205H\nZONE: X\nEFF: 09/24/2021", "invoiced": false, "order_id": 1000275730, "paid": true, "property_address": "704 E TANGERINE CT", "property_city": "WINTER GARDEN", "property_county": "Orange County", "property_lat": "28.5667263", "property_lng": "-81.5986605", "property_state": "FL", "property_zip": "34787", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275730", "customer_email": "allan@lrgconstruction.com", "service_type": "Land Survey Only", "county": "", "property_address": "704 E TANGERINE CT", "customer_name": "Allan Lougheed"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Allan Lougheed", "confidence": "HIGH"}, "client_email": {"value": "allan@lrgconstruction.com", "confidence": "HIGH"}, "property_address": {"value": "704 E Tangerine Ct, Winter Garden, FL 34787", "confidence": "HIGH"}, "property_county": {"value": "Orange County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property feature data available; no appraiser data, aerial imagery, or email context provided"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fences, driveways, etc.)", "No matching emails found \u2014 unable to confirm scope or special instructions from client communication", "Reason for special pricing not documented", "Fieldwork date not yet scheduled (fieldwork_at is null)", "Customer type listed as 'individual' but email domain suggests a construction company (lrgconstruction.com) \u2014 client tier should be verified"], "summary": "Delivered land survey order for Allan Lougheed at 704 E Tangerine Ct, Winter Garden, FL (Orange County), marked as paid with special pricing applied, but missing lot size, legal description, and property feature details due to unavailable appraiser data."}}</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:27:57.570692+00:00</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
@@ -8857,7 +8970,7 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:16.673964+00:00</t>
+          <t>2026-06-02T17:27:57.618434+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -7942,7 +7942,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7965,16 +7965,37 @@
           <t>10369 SILVER LAKE DR, BOCA RATON, FL 33428</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "AI pricing failed: Unterminated string starting at: line 23 column 5 (char 2834). Manual review required.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "AI pricing error \u2014 needs manual quote", "flags": ["ai_error"]}</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202601061537446994, "created_at": "2026-01-06T10:49:02", "customer_email": "gquatela@yahoo.com", "customer_id": 202601061537447982, "customer_name": "GEORGE QUATELA", "customer_type": "individual", "delivered_at": "2026-01-06T17:58:09", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C1155F\nZONE: X\nEFFECTIVE: 10/05/2017", "invoiced": false, "order_id": 1000276783, "paid": false, "property_address": "10369 SILVER LAKE DR", "property_city": "BOCA RATON", "property_county": "Palm Beach County", "property_lat": "26.359744", "property_lng": "-80.20904490000001", "property_state": "FL", "property_zip": "33428", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276783", "customer_email": "gquatela@yahoo.com", "service_type": "Quote", "county": "", "property_address": "10369 SILVER LAKE DR", "customer_name": "GEORGE QUATELA"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "GEORGE QUATELA", "confidence": "HIGH"}, "client_email": {"value": "gquatela@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "10369 SILVER LAKE DR, BOCA RATON, FL 33428", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed as 'Quote' only \u2014 no specific survey service (e.g., boundary, elevation, topographic) has been identified. Human review needed to determine what survey product was quoted."}, "special_requirements": {"value": "Special pricing flag is active", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided. Pool, shed, driveways, and other structures unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not identified \u2014 'Quote' is not a deliverable", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fencing, driveways) unknown", "No matching emails found to clarify scope", "County was blank in top-level FTF fields despite being populated in order data \u2014 minor data inconsistency", "Flood zone noted (Zone X, FIRM 12099C1155F) but elevation certificate not requested \u2014 confirm with client", "Invoice has not been sent and amount due is $0 \u2014 quote may not have been finalized or accepted"], "summary": "Residential quote order for GEORGE QUATELA at 10369 Silver Lake Dr, Boca Raton FL (Palm Beach County) marked as Delivered with special pricing active, but the specific survey service requested has not been defined and significant property detail is missing."}}</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1780421700328</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>2026-06-02T17:09:05.682023+00:00</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:35:00.907607+00:00</t>
+        </is>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
       <c r="T125" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.497199+00:00</t>
@@ -7982,7 +8003,7 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>2026-06-02T17:09:05.730205+00:00</t>
+          <t>2026-06-02T17:35:00.960218+00:00</t>
         </is>
       </c>
     </row>
@@ -8982,7 +9003,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9002,7 +9023,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>1773 GALLOP DR</t>
+          <t>1773 Gallop Dr, Loxahatchee, FL 33470</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510012004186441, "created_at": "2025-12-09T15:54:04", "customer_email": "Angeltgarcia28@gmail.com", "customer_id": 202510012004186572, "customer_name": "Angel   Garcia", "customer_type": "individual", "delivered_at": "2025-12-12T15:02:46", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0530F\nZONE: AE\nELEV: 17.1 FT\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000275722, "paid": false, "property_address": "1773 GALLOP DR", "property_city": "LOXAHATCHEE", "property_county": "PALM BEACH COUNTY", "property_lat": "26.7050813", "property_lng": "-80.3208568", "property_state": "FL", "property_zip": "33470", "service_type": "Land Survey Only", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275722", "customer_email": "Angeltgarcia28@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "1773 GALLOP DR", "customer_name": "Angel Garcia"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Angel Garcia", "confidence": "HIGH"}, "client_email": {"value": "Angeltgarcia28@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1773 Gallop Dr, Loxahatchee, FL 33470", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "None noted", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing \u2014 no appraiser or document source available", "Structure square footage unknown", "Property features (pool, shed, fences, structures) not confirmed", "No matching email history found to cross-reference order details", "Invoice not yet sent and order marked unpaid \u2014 billing action may be needed", "Fieldwork date is null \u2014 unclear if fieldwork was completed or skipped"], "summary": "Residential land survey only order for Angel Garcia at 1773 Gallop Dr, Loxahatchee, FL 33470 (Palm Beach County), delivered on 2025-12-12 but not yet invoiced or paid, with flood zone AE/X noted and no additional property details available."}}</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:33:53.901406+00:00</t>
         </is>
       </c>
       <c r="T145" t="inlineStr">
@@ -9012,7 +9043,7 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:16.733196+00:00</t>
+          <t>2026-06-02T17:33:53.951621+00:00</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9055,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9044,7 +9075,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>50044 BERMONT RD</t>
+          <t>50044 Bermont Rd, Punta Gorda, FL 33982</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508061638505520, "created_at": "2025-12-08T12:29:00", "customer_email": "krsdra50@gmail.com", "customer_id": 202508061638505619, "customer_name": "Kristen Dragon", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12015C0325G\nZONE: X\nEFF: 12/15/2022", "invoiced": false, "order_id": 1000275670, "paid": false, "property_address": "50044 BERMONT RD", "property_city": "PUNTA GORDA", "property_county": "Charlotte County", "property_lat": "26.9457282", "property_lng": "-81.6278863", "property_state": "FL", "property_zip": "33982", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275670", "customer_email": "krsdra50@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "50044 BERMONT RD", "customer_name": "Kristen Dragon"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Kristen Dragon", "confidence": "HIGH"}, "client_email": {"value": "krsdra50@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "50044 Bermont Rd, Punta Gorda, FL 33982", "confidence": "HIGH"}, "property_county": {"value": "Charlotte County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data; no additional services indicated."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available, no emails, and no aerial data provided. Property features are unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, outbuildings, fencing, driveways) unknown", "Special requirements or client notes not provided", "Order is currently 'On Hold' \u2014 reason for hold not specified", "No fieldwork date scheduled", "No invoice or payment information on file", "County field is blank in the outer FTF payload (though present in order data body \u2014 should be reconciled)"], "summary": "Individual residential client Kristen Dragon has placed a Land Survey Only order for a property at 50044 Bermont Rd, Punta Gorda, FL (Charlotte County), currently on hold with no fieldwork scheduled and limited property detail available."}}</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:34:03.164143+00:00</t>
         </is>
       </c>
       <c r="T146" t="inlineStr">
@@ -9054,7 +9095,7 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:16.792703+00:00</t>
+          <t>2026-06-02T17:34:03.216088+00:00</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9107,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9086,7 +9127,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>7202 NW 68TH ST</t>
+          <t>7202 NW 68TH ST, TAMARAC, FL 33321</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202512081633332403, "created_at": "2025-12-08T11:37:01", "customer_email": "mchardyconstruction.fl@gmail.com", "customer_id": 202512081634420572, "customer_name": "Mariana McHardy", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0353H\nZONE: X500\nEFF: 08/18/2014", "invoiced": false, "order_id": 1000275662, "paid": true, "property_address": "7202 NW 68TH ST", "property_city": "TAMARAC", "property_county": "Broward County", "property_lat": "26.2068904", "property_lng": "-80.2488848", "property_state": "FL", "property_zip": "33321", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275662", "customer_email": "mchardyconstruction.fl@gmail.com", "service_type": "CAD file", "county": "", "property_address": "7202 NW 68TH ST", "customer_name": "McHardy Construction"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "McHardy Construction", "confidence": "HIGH"}, "client_email": {"value": "mchardyconstruction.fl@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "7202 NW 68TH ST, TAMARAC, FL 33321", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated. Scope of CAD file (boundary, topo, as-built, etc.) is unspecified."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Exact CAD file scope not specified (boundary, topographic, as-built, etc.)", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description not provided", "Structure square footage unknown", "Property features unknown (pool, shed, fences, driveways, etc.)", "Reason for 'On Hold' status not documented", "Fieldwork date not yet scheduled", "No matching emails found \u2014 client communication history unavailable", "Elevation certificate not requested but flood zone data present (Zone X500) \u2014 worth confirming with client"], "summary": "B2B CAD file order for McHardy Construction at 7202 NW 68TH ST, Tamarac, FL (Broward County), currently On Hold with special pricing applied and paid; CAD scope and property details need clarification."}}</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:34:14.345988+00:00</t>
         </is>
       </c>
       <c r="T147" t="inlineStr">
@@ -9096,7 +9147,7 @@
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:16.852901+00:00</t>
+          <t>2026-06-02T17:34:14.396247+00:00</t>
         </is>
       </c>
     </row>
@@ -9108,7 +9159,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9128,7 +9179,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>8850 US-1</t>
+          <t>8850 US-1, Sebastian, FL 32958</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201801311048074557, "created_at": "2025-12-10T13:54:04", "customer_email": "jbeal@atlanticcoastal.com", "customer_id": 201801311051368484, "customer_name": "Jason Beal", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12061C0118J\nZONE: AE\nELEV: 07 FT\nZONE: X\nZONE: \"X500\" SHADED\nEFF 01/26/2023", "invoiced": false, "order_id": 1000275516, "paid": false, "property_address": "8850 US-1", "property_city": "SEBASTIAN", "property_county": "INDIAN RIVER COUNTY", "property_lat": "27.7547721", "property_lng": "-80.43473829999999", "property_state": "FLORIDA", "property_zip": "32958", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275516", "customer_email": "jbeal@atlanticcoastal.com", "service_type": "Land Survey Only", "county": "", "property_address": "8850 US-1", "customer_name": "Atlantic Coastal Land Title Company"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Atlantic Coastal Land Title Company", "confidence": "MEDIUM"}, "client_email": {"value": "jbeal@atlanticcoastal.com", "confidence": "HIGH"}, "property_address": {"value": "8850 US-1, Sebastian, FL 32958", "confidence": "HIGH"}, "property_county": {"value": "Indian River County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing flagged; order currently On Hold (status code 11); flood zone data present: FIRM panel 12061C0118J, zones AE (07 ft BFE), X, and X500 shaded, effective 01/26/2023", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing \u2014 no appraiser or document source available", "Structure square footage unknown", "Property features (pool, shed, structures) unknown \u2014 no aerial or appraiser data", "Order is On Hold \u2014 reason for hold not specified, needs human review", "Client name conflict: order contact is 'Jason Beal' but company name listed as 'Atlantic Coastal Land Title Company' \u2014 confirm billing entity", "Fieldwork and delivery dates not yet scheduled", "Special pricing flag is set \u2014 pricing terms need human confirmation", "No matching emails found \u2014 no additional context or instructions from client"], "summary": "B2B land survey order for Atlantic Coastal Land Title Company at 8850 US-1, Sebastian, FL (Indian River County), currently On Hold with special pricing flagged and no fieldwork scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:34:25.853259+00:00</t>
         </is>
       </c>
       <c r="T148" t="inlineStr">
@@ -9138,7 +9199,7 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:16.962298+00:00</t>
+          <t>2026-06-02T17:34:25.905134+00:00</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9211,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9170,7 +9231,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2992 20TH AVE NE</t>
+          <t>2992 20TH AVE NE, NAPLES, FL 34120</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507211345522935, "created_at": "2025-12-04T10:19:05", "customer_email": "aileensellsnaples@gmail.com", "customer_id": 202507211345523034, "customer_name": "Aileen Cuadra-Roque", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12021C0245H\nZONE: X500\nZONE: AH\nELEV: 15 FT\nEFF: 05/16/2012", "invoiced": false, "order_id": 1000275511, "paid": true, "property_address": "2992 20TH AVE NE", "property_city": "NAPLES", "property_county": "Collier County", "property_lat": "26.2665243", "property_lng": "-81.5457423", "property_state": "FL", "property_zip": "34120", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275511", "customer_email": "aileensellsnaples@gmail.com", "service_type": "CAD file", "county": "", "property_address": "2992 20TH AVE NE", "customer_name": "Aileen Cuadra-Roque"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Aileen Cuadra-Roque", "confidence": "HIGH"}, "client_email": {"value": "aileensellsnaples@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "2992 20TH AVE NE, NAPLES, FL 34120", "confidence": "HIGH"}, "property_county": {"value": "Collier County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Only service type listed is CAD file; no additional services indicated in the order data"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold. Flood zone data present: Panel 12021C0245H, zones X500 and AH, base elevation 15 FT, effective 05/16/2012.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no aerial, appraiser, or email data provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, structures) unknown \u2014 no aerial or appraiser data", "No matching emails found \u2014 cannot confirm scope or client communications", "Reason for On Hold status not specified", "Invoice not yet sent and due amount is $0 \u2014 pricing details unclear despite special_pricing flag", "Fieldwork and delivery dates not yet set"], "summary": "Residential CAD file order for Aileen Cuadra-Roque at 2992 20TH AVE NE, Naples, FL (Collier County) is currently On Hold with special pricing applied, no fieldwork scheduled, and key property details including lot size and legal description still missing."}}</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:34:36.557815+00:00</t>
         </is>
       </c>
       <c r="T149" t="inlineStr">
@@ -9180,7 +9251,7 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:17.023586+00:00</t>
+          <t>2026-06-02T17:34:36.609495+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -8015,7 +8015,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8038,16 +8038,37 @@
           <t>7964 Grand Bay Dr, Naples, FL 34108</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "Condo order \u2014 legal description contains 'CONDOMINIUM'", "confidence": "N/A", "escalate_flag": true, "escalate_reason": "Condo order \u2014 legal description contains 'CONDOMINIUM'", "flags": ["condo_rejected"]}</t>
+        </is>
+      </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202601061428299961, "created_at": "2026-01-06T10:58:02", "customer_email": "cpv2757@aol.com", "customer_id": 202601061428300131, "customer_name": "Claudia Vitulich", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12021C0381J\nZONE: X500\nEFF: 02/08/2024", "invoiced": false, "order_id": 1000276767, "paid": false, "property_address": "7964 GRAND BAY DR", "property_city": "NAPLES", "property_county": "COLLIER COUNTY", "property_lat": "26.2452916", "property_lng": "-81.81071039999999", "property_state": "FLORIDA", "property_zip": "34108", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276767", "customer_email": "cpv2757@aol.com", "service_type": "Land Survey Only", "county": "", "property_address": "7964 GRAND BAY DR", "customer_name": "Claudia Vitulich"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Claudia Vitulich", "confidence": "HIGH"}, "client_email": {"value": "cpv2757@aol.com", "confidence": "HIGH"}, "property_address": {"value": "7964 Grand Bay Dr, Naples, FL 34108", "confidence": "HIGH"}, "property_county": {"value": "Collier County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "None noted", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 county appraiser unavailable", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) unknown", "Order is currently On Hold \u2014 reason for hold not specified", "No fieldwork or delivery dates scheduled", "No invoice or payment information present", "No customer data returned from FTF customer lookup"], "summary": "Individual residential client Claudia Vitulich has ordered a Land Survey Only for 7964 Grand Bay Dr, Naples, FL (Collier County), currently on hold with no fieldwork scheduled and missing lot, legal, and property feature details."}}</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1780421994097</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>2026-06-02T17:09:14.636313+00:00</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:39:54.783368+00:00</t>
+        </is>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
       <c r="T126" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.552119+00:00</t>
@@ -8055,7 +8076,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>2026-06-02T17:09:14.685958+00:00</t>
+          <t>2026-06-02T17:39:54.832025+00:00</t>
         </is>
       </c>
     </row>
@@ -8067,7 +8088,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8090,16 +8111,37 @@
           <t>1025 Mariana Ave, Coral Gables, FL 33134</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>{"total_amount": 500.0, "services": [{"name": "Land Survey (Boundary/Location Survey)", "description": "Standard boundary/location survey for LOT 5, BLOCK 4, AMENDED PLAT OF GRANADA PLACE, 1025 Mariana Ave, Coral Gables, Miami-Dade County. 0.10-acre platted residential lot in FEMA Zone X (no flood zone upcharge). Negotiated flat rate applied per management agreement with M+S Construction.", "amount": 500.0}], "pricing_reasoning": "The client M+S Construction has a management-approved negotiated base rate of $500.00 for survey work. The property is a small 0.10-acre platted residential lot in Miami-Dade County with a straightforward recorded plat legal description (no metes-and-bounds complexity), FEMA Zone X (no elevation certificate required or flood zone upcharge), and no other data-supported complexity triggers (no pool, waterfront, heavy vegetation, or Monroe County mobilization). No complexity upcharges are warranted; the $500.00 negotiated rate stands as the full invoice total. The specific survey service type is assumed to be a standard boundary/location survey based on the duplicate order history, but human confirmation is required as the order notes indicate the service type remains undefined.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "The order is flagged On Hold with the service type explicitly undefined per order notes. Human follow-up is required to confirm the exact survey service requested (boundary survey, as-built, TOPO, etc.) before finalizing and issuing the invoice. Additionally, two possible duplicate orders (1000243908 and 1000276117) exist for the same address, folio, and service type \u2014 these must be reconciled to avoid billing the client multiple times for the same work.", "flags": ["SERVICE TYPE UNDEFINED: Order notes state the specific survey service type has not been confirmed. Assumed Land Survey Only based on duplicate order history \u2014 requires human verification before invoice issuance.", "DUPLICATE ORDER \u2014 Order 1000243908: Same address (1025 Mariana Ave), same county (Miami-Dade), same Folio (0341070050380), service: Land Survey Only. Coordinates closely match. Review for duplicate billing.", "DUPLICATE ORDER \u2014 Order 1000276117: Same address (1025 Mariana Ave), same county (Miami-Dade), same Folio (0341070050380), service: Land Survey Only. Coordinates closely match. Review for duplicate billing.", "NEGOTIATED RATE APPLIED: $500.00 flat rate per management agreement for M+S Construction (OLD_TITLE tier). No complexity upcharges applied \u2014 lot is small, platted, residential, Zone X, Miami-Dade County."]}</t>
+        </is>
+      </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202601051549222579, "created_at": "2026-01-05T10:51:00", "customer_email": "mmarino@ms-constructions.com", "customer_id": 202601051549514927, "customer_name": "Magdalena Marino", "customer_type": "b2b", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0294L\nZONE: X\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000276703, "paid": false, "property_address": "1025 MARIANA AVE", "property_city": "CORAL GABLES", "property_county": "Miami-Dade County", "property_lat": "25.7614208", "property_lng": "-80.27663749999999", "property_state": "FL", "property_zip": "33134", "service_type": "Quote", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276703", "customer_email": "mmarino@ms-constructions.com", "service_type": "Quote", "county": "", "property_address": "1025 MARIANA AVE", "customer_name": "M+S Construction"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "M+S Construction", "confidence": "HIGH"}, "client_email": {"value": "mmarino@ms-constructions.com", "confidence": "HIGH"}, "property_address": {"value": "1025 Mariana Ave, Coral Gables, FL 33134", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., Boundary, Elevation, Topographic) has been identified. Needs clarification from client or internal team."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property feature data available \u2014 pool, shed, driveways, and other structures unknown. County Appraiser data unavailable."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not identified \u2014 Quote only, no scope defined", "Lot size unknown \u2014 County Appraiser unavailable", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, driveways, etc.) unknown", "No matching emails found to provide additional context", "Order is On Hold \u2014 reason for hold not specified", "Elevation certificate not requested but flood zone is Zone X \u2014 confirm no elevation cert needed", "Due amount of $250 may be a deposit or placeholder \u2014 full quote not finalized"], "summary": "A b2b client (M+S Construction) has an On Hold quote order for a property at 1025 Mariana Ave, Coral Gables, FL (Miami-Dade County) with special pricing applied, but the specific survey service type and property details remain undefined and require human follow-up."}}</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1780421864381</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>2026-06-02T17:09:26.371515+00:00</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:40:14.945136+00:00</t>
+        </is>
+      </c>
+      <c r="R127" t="n">
+        <v>500</v>
+      </c>
       <c r="T127" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.607180+00:00</t>
@@ -8107,7 +8149,7 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>2026-06-02T17:09:26.420558+00:00</t>
+          <t>2026-06-02T17:40:14.995440+00:00</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8161,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8142,16 +8184,37 @@
           <t>15615 FL-62, Parrish, FL 34219</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "This property is 24.24 acres, which exceeds the 5.00-acre threshold defined in pricing guidelines. Per policy, any lot greater than 5.00 acres must be escalated to management and cannot be priced through the standard rate card \u2014 regardless of client tier, negotiated base rate, or flood zone. Additionally, no specific survey service type has been identified in this b2b quote request, further requiring management review to scope the work before pricing can be applied.", "confidence": "HIGH", "escalate_flag": true, "escalate_reason": "Lot size of 24.24 acres exceeds the 5.00-acre maximum for automated pricing. All services (boundary survey, topo, EC) require management quoting at this acreage. Additionally, the order notes confirm no specific survey service type has yet been identified, making it impossible to assign line items without a scoping conversation with the client (William A. Dooley, P.A.). The metes-and-bounds legal description spanning Sections 23, 26, and 27 across multiple township references adds further field complexity that management should evaluate before committing to a price.", "flags": ["ESCALATE: Lot size 24.24 acres exceeds 5.00-acre automated pricing threshold \u2014 management must quote.", "NO SERVICE TYPE IDENTIFIED: Order notes confirm service type is unknown; scoping required before pricing.", "POSSIBLE DUPLICATE: Order 1000258162 also references 15615 FL-62, Manatee County \u2014 same location coordinates (27.5895349, -82.3839765) and same Folio/MLS (416503001). Human review required to determine if this is a re-quote of an existing order.", "METES AND BOUNDS: Legal description spans Sections 23, 26, and 27 \u2014 complex multi-section parcel; management should account for this in the manual quote.", "CLIENT NOTE: William A. Dooley, P.A. is an OLD_TITLE client with a negotiated base rate of $450.00; 0 prior orders with NexGen. Rate is on file but cannot be applied until escalation is resolved."]}</t>
+        </is>
+      </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202106171651070228, "created_at": "2025-12-24T08:51:04", "customer_email": "bprinz@wdooleylaw.com", "customer_id": 202106171652033942, "customer_name": "Barbara Prinz", "customer_type": "b2b", "delivered_at": "2025-12-29T20:00:37", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12081C0184F\nZONE: X\nEFF: 08/10/2021", "invoiced": false, "order_id": 1000276470, "paid": false, "property_address": "15615 FL-62", "property_city": "PARRISH", "property_county": "Manatee County", "property_lat": "27.5895349", "property_lng": "-82.3839765", "property_state": "FL", "property_zip": "34219", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276470", "customer_email": "bprinz@wdooleylaw.com", "service_type": "Quote", "county": "", "property_address": "15615 FL-62", "customer_name": "William A. Dooley, P.A."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "William A. Dooley, P.A.", "confidence": "HIGH"}, "client_email": {"value": "bprinz@wdooleylaw.com", "confidence": "HIGH"}, "property_address": {"value": "15615 FL-62, Parrish, FL 34219", "confidence": "HIGH"}, "property_county": {"value": "Manatee County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service has been identified. Actual survey type needs clarification from client."}, "special_requirements": {"value": "Special pricing applies", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data present."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not identified \u2014 'Quote' is not a service", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown \u2014 no aerial, appraiser, or email data", "No matching emails found to clarify scope or requirements", "County was blank in the outer FTF payload \u2014 confirmed via inner data only", "No customer profile data available (FTF customer data is empty)"], "summary": "A b2b quote request from William A. Dooley, P.A. for a property at 15615 FL-62 in Parrish, Manatee County, FL (Flood Zone X), with special pricing applied but no specific survey service type yet identified."}}</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1780421888261</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>2026-06-02T17:09:36.389767+00:00</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:40:32.722235+00:00</t>
+        </is>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
       <c r="T128" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.662145+00:00</t>
@@ -8159,7 +8222,7 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>2026-06-02T17:09:36.438746+00:00</t>
+          <t>2026-06-02T17:40:32.772878+00:00</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8234,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8194,16 +8257,37 @@
           <t>23 S SWINTON AVE, DELRAY BEACH, FL 33444</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>{"total_amount": 500.0, "services": [{"name": "Land Survey (Boundary)", "description": "Boundary/land survey for LOT 10, BLOCK 69, SUBDIVISION OF BLOCK 69 DELRAY FLORIDA, 23 S Swinton Ave, Delray Beach, Palm Beach County. 0.15-acre residential lot, FEMA Zone X (no EC required). Negotiated flat rate applied per management agreement with Geoffrey Morris.", "amount": 500.0}], "pricing_reasoning": "Management has established a negotiated flat rate of $500.00 for this specific client (Geoffrey Morris, individual/direct). The property is a small 0.15-acre residential lot in Palm Beach County with a straightforward recorded plat legal description (no metes and bounds complexity), FEMA Zone X (no flood elevation certificate needed), and no indicators of pool, waterfront, heavy vegetation, or other complexity upcharges from the legal description or lot size. No complexity upcharges are warranted; the negotiated base rate of $500.00 stands as the total. However, the specific survey service type has not been formally defined in this Quote-stage order, and multiple duplicate orders exist for the same address \u2014 both issues are flagged for human review before finalizing.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "The specific survey service requested has not yet been defined (Quote stage only, no service type confirmed). Additionally, three possible duplicate orders exist for the same property/folio (Orders 1000138669, 1000269147, and 1000269190), including a prior Quote order (1000269190) at the same address. Management should confirm the intended service type and resolve duplicate order status before invoicing.", "flags": ["DUPLICATE_SUSPECTED: Order 1000138669 \u2014 23 S SWINTON AVE, Palm Beach County \u2014 service: Land Survey Only \u2014 same location and folio (12434616010690100).", "DUPLICATE_SUSPECTED: Order 1000269147 \u2014 23 S SWINTON AVE, Palm Beach County \u2014 service: Land Survey Only \u2014 same location and folio (12434616010690100).", "DUPLICATE_SUSPECTED: Order 1000269190 \u2014 23 S SWINTON AVE, Palm Beach County \u2014 service: Quote \u2014 same location and folio (12434616010690100). This may be a direct re-order of this same Quote.", "SERVICE_TYPE_UNDEFINED: This is a Quote-stage order and the specific survey service (boundary, EC, topo, combined) has not been confirmed. Price assumes standard boundary/land survey per prior order history at this address.", "NEGOTIATED_RATE_APPLIED: $500.00 flat rate per management agreement for client Geoffrey Morris \u2014 no additional complexity upcharges applied."]}</t>
+        </is>
+      </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202508041423430005, "created_at": "2025-12-23T10:41:01", "customer_email": "dfainvestmentcompany@gmail.com", "customer_id": 202508041423431419, "customer_name": "GEOFFREY MORRIS", "customer_type": "individual", "delivered_at": "2025-12-23T21:13:40", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0979G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000276428, "paid": true, "property_address": "23 S SWINTON AVE", "property_city": "DELRAY BEACH", "property_county": "Palm Beach County", "property_lat": "26.4606471", "property_lng": "-80.0728381", "property_state": "FL", "property_zip": "33444", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276428", "customer_email": "DSAINVESTMENTCOMPANY@GMAIL.COM", "service_type": "Quote", "county": "", "property_address": "23 S SWINTON AVE", "customer_name": "GEOFFREY MORRIS"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "GEOFFREY MORRIS", "confidence": "HIGH"}, "client_email": {"value": "dfainvestmentcompany@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "23 S SWINTON AVE, DELRAY BEACH, FL 33444", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed as 'Quote' only \u2014 no specific survey type (e.g., Boundary, Elevation Certificate, Topographic) has been identified. Human review needed to determine actual services requested."}, "special_requirements": {"value": "Special pricing applied; flood zone X per FIRM panel 12099C0979G effective 12/20/2024", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 pool, shed, driveways, or other structures unknown. County appraiser data unavailable."}, "client_tier": {"value": "unknown", "confidence": "LOW"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not defined \u2014 'Quote' is not a deliverable survey type", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) unknown", "Client tier unclear \u2014 email domain suggests possible investment company (DFA Investment Company) but customer_type is 'individual'", "No matching emails found to corroborate order details", "Invoice not yet generated (invoiced: false) despite order marked as delivered and paid"], "summary": "A delivered and paid Quote-stage order for GEOFFREY MORRIS at 23 S Swinton Ave, Delray Beach FL (Flood Zone X) with special pricing applied, but the specific survey service requested has not yet been defined and key property details are missing."}}</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1780422051693</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>2026-06-02T17:09:48.820095+00:00</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:40:52.686589+00:00</t>
+        </is>
+      </c>
+      <c r="R129" t="n">
+        <v>500</v>
+      </c>
       <c r="T129" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.718263+00:00</t>
@@ -8211,7 +8295,7 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>2026-06-02T17:09:48.868805+00:00</t>
+          <t>2026-06-02T17:40:52.737067+00:00</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9347,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9283,7 +9367,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>1131 S N ST</t>
+          <t>1131 S N ST, Lake Worth Beach, FL 33460</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202512011530429151, "created_at": "2025-12-01T11:07:04", "customer_email": "daymon@eastcoastmetals.net", "customer_id": 202512011530430512, "customer_name": "Daymon Hallmon", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0781G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000275245, "paid": true, "property_address": "1131 S N ST", "property_city": "LAKE WORTH BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.601369", "property_lng": "-80.05358559999999", "property_state": "FL", "property_zip": "33460", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275245", "customer_email": "daymon@eastcoastmetals.net", "service_type": "CAD file", "county": "", "property_address": "1131 S N ST", "customer_name": "Daymon Hallmon"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Daymon Hallmon", "confidence": "HIGH"}, "client_email": {"value": "daymon@eastcoastmetals.net", "confidence": "HIGH"}, "property_address": {"value": "1131 S N ST, Lake Worth Beach, FL 33460", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Only service type listed is CAD file; no additional services specified"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no aerial, appraiser, or email data provided"}, "client_tier": {"value": "residential", "confidence": "MEDIUM"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, etc.)", "Reason for On Hold status not specified", "Scope of CAD file deliverable not clarified (boundary, topo, as-built, etc.)", "No fieldwork date scheduled", "Invoice has not been sent \u2014 needs follow-up", "Client type listed as individual but email domain (eastcoastmetals.net) suggests possible business affiliation"], "summary": "Individual client Daymon Hallmon has a paid but on-hold CAD file order for a residential property in Lake Worth Beach, FL with special pricing applied, pending clarification on scope, hold reason, and property details."}}</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:39:04.509513+00:00</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
@@ -9293,7 +9387,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:17.084094+00:00</t>
+          <t>2026-06-02T17:39:04.558649+00:00</t>
         </is>
       </c>
     </row>
@@ -9305,7 +9399,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9320,12 +9414,22 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Colleen   Guglielmo</t>
+          <t>Colleen Guglielmo</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>322 SE 3RD AVE</t>
+          <t>322 SE 3rd Ave, Delray Beach, FL 33483</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202511041936177608, "created_at": "2025-11-26T09:55:04", "customer_email": "cguglielmo16@icloud.com", "customer_id": 202511041936177714, "customer_name": "Colleen   Guglielmo", "customer_type": "individual", "delivered_at": "2025-11-26T15:56:06", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0979G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000275171, "paid": false, "property_address": "322 SE 3RD AVE", "property_city": "DELRAY BEACH", "property_county": "Palm Beach County", "property_lat": "26.4552517", "property_lng": "-80.0701823", "property_state": "FL", "property_zip": "33483", "service_type": "Quote", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275171", "customer_email": "cguglielmo16@icloud.com", "service_type": "Quote", "county": "", "property_address": "322 SE 3RD AVE", "customer_name": "Colleen   Guglielmo"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Colleen Guglielmo", "confidence": "HIGH"}, "client_email": {"value": "cguglielmo16@icloud.com", "confidence": "HIGH"}, "property_address": {"value": "322 SE 3rd Ave, Delray Beach, FL 33483", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., boundary, ALTA, elevation) has been identified. Needs clarification."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service(s) requested \u2014 order is only marked as 'Quote' with no detail", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) unknown", "Special requirements or client notes not provided", "No matching emails found to clarify scope or intent"], "summary": "Individual residential client Colleen Guglielmo is requesting a quote for a survey at 322 SE 3rd Ave, Delray Beach, FL (Palm Beach County), but the specific survey service needed has not yet been identified."}}</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:39:15.101657+00:00</t>
         </is>
       </c>
       <c r="T151" t="inlineStr">
@@ -9335,7 +9439,7 @@
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:17.145185+00:00</t>
+          <t>2026-06-02T17:39:15.150484+00:00</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9451,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9367,7 +9471,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>7409 BONDSBERRY CT</t>
+          <t>7409 Bondsberry Ct, Boca Raton, FL 33434</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202511251809119873, "created_at": "2025-11-25T13:23:05", "customer_email": "bpbpoolbuilder@yahoo.com", "customer_id": 202511251809359010, "customer_name": "Meghan  Julien", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0968F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000275133, "paid": false, "property_address": "7409 BONDSBERRY CT", "property_city": "BOCA RATON", "property_county": "PALM BEACH COUNTY", "property_lat": "26.380752", "property_lng": "-80.1605202", "property_state": "FLORIDA", "property_zip": "33434", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275133", "customer_email": "bpbpoolbuilder@yahoo.com", "service_type": "Land Survey Only", "county": "", "property_address": "7409 BONDSBERRY CT", "customer_name": "Broward Palm Beach Pool Builder"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Broward Palm Beach Pool Builder", "confidence": "MEDIUM"}, "client_email": {"value": "bpbpoolbuilder@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "7409 Bondsberry Ct, Boca Raton, FL 33434", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; likely a boundary survey for pool permitting given the b2b pool builder client context"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; pool likely planned given client is a pool builder, but not confirmed from data"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Legal description not provided", "Lot size unknown", "Structure square footage unknown", "Property features and existing improvements unknown", "Reason for On Hold status not specified", "No matching emails found to supplement order details", "County property appraiser data unavailable", "Client name conflict: order contact is 'Meghan Julien' but company name is 'Broward Palm Beach Pool Builder' \u2014 confirm correct billing name", "Scope of survey not fully defined (boundary, staking, as-built?)", "No fieldwork or delivery date scheduled"], "summary": "B2B land survey order for pool builder client at 7409 Bondsberry Ct, Boca Raton (Palm Beach County) currently On Hold with special pricing applied and no fieldwork or delivery dates scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:39:25.418643+00:00</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
@@ -9377,7 +9491,7 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:17.209602+00:00</t>
+          <t>2026-06-02T17:39:25.465949+00:00</t>
         </is>
       </c>
     </row>
@@ -9389,7 +9503,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9409,7 +9523,17 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>3010 NE 43RD ST</t>
+          <t>3010 NE 43RD ST, Fort Lauderdale, FL 33308</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510162101520333, "created_at": "2025-11-25T15:56:05", "customer_email": "mdbolanos@gmail.com", "customer_id": 202510162101520438, "customer_name": "Michael  Bolanos", "customer_type": "individual", "delivered_at": "2025-11-26T14:44:51", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0386J\nZONE: AE\nELEV: 07 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000275111, "paid": false, "property_address": "3010 NE 43RD ST", "property_city": "FORT LAUDERDALE", "property_county": "Broward County", "property_lat": "26.1816949", "property_lng": "-80.10664729999999", "property_state": "FL", "property_zip": "33308", "service_type": "Quote", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275111", "customer_email": "mdbolanos@gmail.com", "service_type": "Quote", "county": "", "property_address": "3010 NE 43RD ST", "customer_name": "Michael Bolanos"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Michael Bolanos", "confidence": "HIGH"}, "client_email": {"value": "mdbolanos@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "3010 NE 43RD ST, Fort Lauderdale, FL 33308", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "MEDIUM", "notes": "Service type is listed as 'Quote' \u2014 no specific survey service has been confirmed or selected yet. Actual service scope is unknown."}, "special_requirements": {"value": "Property is in FEMA Flood Zone AE (Panel 12011C0386J, Effective 07/31/2024, Base Flood Elevation 7 ft). Elevation Certificate flag is currently set to false.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available and no emails or attachments provided. Pool, structures, lot features unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service(s) requested have not been confirmed \u2014 order is still in Quote stage", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fences, etc.) unknown", "No matching emails found to clarify scope or client intent", "Invoice has not been generated and payment has not been collected", "Fieldwork has not been scheduled (fieldwork_at is null)"], "summary": "Residential quote request for a property at 3010 NE 43rd St, Fort Lauderdale in FEMA Flood Zone AE \u2014 no specific survey service confirmed yet, and key property details including lot size, legal description, and features are unavailable."}}</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:39:36.359413+00:00</t>
         </is>
       </c>
       <c r="T153" t="inlineStr">
@@ -9419,7 +9543,7 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:17.275418+00:00</t>
+          <t>2026-06-02T17:39:36.407736+00:00</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9555,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9451,7 +9575,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>4177 S CONGRESS AVE</t>
+          <t>4177 S CONGRESS AVE, PALM SPRINGS, FL 33461</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202511181413190943, "created_at": "2025-11-18T09:34:00", "customer_email": "LisaD@cwcrecovery.com", "customer_id": 202511181419117120, "customer_name": "Lisa DiFiori", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0777F\nZONE: AE\nELEV: 13 FT\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000274741, "paid": true, "property_address": "4177 S CONGRESS AVE", "property_city": "PALM SPRINGS", "property_county": "Palm Beach County", "property_lat": "26.6146897", "property_lng": "-80.0907272", "property_state": "FL", "property_zip": "33461", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274741", "customer_email": "LisaD@cwcrecovery.com", "service_type": "CAD file", "county": "", "property_address": "4177 S CONGRESS AVE", "customer_name": "JMJC REAL PROPERTY MANAGEMENT, LLC."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "JMJC REAL PROPERTY MANAGEMENT, LLC.", "confidence": "MEDIUM"}, "client_email": {"value": "LisaD@cwcrecovery.com", "confidence": "HIGH"}, "property_address": {"value": "4177 S CONGRESS AVE, PALM SPRINGS, FL 33461", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold; flood zone AE at 13 ft elevation (FIRM panel 12099C0777F, eff. 10/05/2017)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order customer_name is 'Lisa DiFiori' but top-level customer_name is 'JMJC REAL PROPERTY MANAGEMENT, LLC.' \u2014 needs human clarification on billing entity", "No customer/company profile data returned from FTF customer lookup", "No matching emails found to corroborate order details", "County property appraiser data unavailable \u2014 lot size, legal description, and property features unknown", "Structure square footage not provided", "Lot size not provided", "Legal description not provided", "Property features (pool, shed, structures, etc.) unknown", "Urgency/deadline not specified", "Order is On Hold \u2014 reason for hold not documented", "Scope of CAD file deliverable not defined (boundary, topo, as-built, etc.)"], "summary": "B2B order for a CAD file deliverable at 4177 S Congress Ave, Palm Springs, FL (Palm Beach County) for JMJC Real Property Management / Lisa DiFiori, currently On Hold with special pricing applied and flood zone AE designation noted."}}</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:39:48.299993+00:00</t>
         </is>
       </c>
       <c r="T154" t="inlineStr">
@@ -9461,7 +9595,7 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:17.337024+00:00</t>
+          <t>2026-06-02T17:39:48.348268+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -8307,7 +8307,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8330,16 +8330,37 @@
           <t>7411 W Cypresshead Dr, Parkland, FL 33067</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>{"total_amount": 587.0, "services": [{"name": "CAD File / Boundary Survey", "description": "Base survey rate per negotiated agreement with MS Architects, Inc. (OLD_TITLE tier, management-approved rate)", "amount": 450.0}, {"name": "Lot Size Complexity Upcharge (0.51\u20131.00 ac)", "description": "Subject lot is 0.76 acres, falling within the 0.51\u20131.00 ac complexity tier. Larger lot increases field time and CAD drafting scope.", "amount": 137.0}], "pricing_reasoning": "The client has a management-approved negotiated base rate of $450.00. No Elevation Certificate was requested, so the EC line and FEMA Zone AH coastal premium do not apply. The lot at 0.76 acres falls squarely in the 0.51\u20131.00 ac upcharge tier (+$137.00). No pool, waterfront canal, metes-and-bounds description, Monroe County, or heavy vegetation indicators were identified \u2014 the legal description references a standard platted P.U.D. lot in Broward County. Total invoice is $587.00.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE_DUPLICATE: Order 1000265910 is flagged at the same address (7411 W Cypresshead Dr, Broward County) with the same folio/MLS (474135022510) and same coordinates. Prior order included Land Survey AND Elevation Certificate. Current order is CAD file only. Human review recommended to confirm this is a legitimate follow-on deliverable order and not an accidental duplicate \u2014 do not auto-reject.", "ORDER_ON_HOLD: Order notes indicate this order is currently on hold with special pricing applied and no supporting appraiser or email data available. Confirm hold status and client authorization before invoicing.", "EC_NOT_REQUESTED: Property is in FEMA Zone AH (elevation 15 ft, panel 12011C0155H). No Elevation Certificate was ordered here, but the duplicate order 1000265910 included one. Verify with client whether a new EC is needed or if the prior EC from order 1000265910 is being reused."]}</t>
+        </is>
+      </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202512221935383921, "created_at": "2025-12-22T14:39:00", "customer_email": "MSARCHMS@aol.com", "customer_id": 202512221936377320, "customer_name": "Miguel Sanchez", "customer_type": "b2b", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0155H\nZONE: AH\nELEV: 15 FT\nEFF: 08/18/2014", "invoiced": false, "order_id": 1000276384, "paid": false, "property_address": "7411 W CYPRESSHEAD DR", "property_city": "PARKLAND", "property_county": "Broward County", "property_lat": "26.323319", "property_lng": "-80.2315995", "property_state": "FL", "property_zip": "33067", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276384", "customer_email": "MSARCHMS@aol.com", "service_type": "CAD file", "county": "", "property_address": "7411 W CYPRESSHEAD DR", "customer_name": "MS Architects, Inc. "}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "MS Architects, Inc.", "confidence": "HIGH"}, "client_email": {"value": "MSARCHMS@aol.com", "confidence": "HIGH"}, "property_address": {"value": "7411 W Cypresshead Dr, Parkland, FL 33067", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11); flood zone AH at 15 ft elevation, panel 12011C0155H effective 08/18/2014", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, outbuildings, etc.) unknown", "No matching emails found to clarify scope or special instructions", "Order is On Hold \u2014 reason for hold not specified, may require human follow-up", "Elevation certificate not requested but flood zone AH noted \u2014 confirm if EC is needed", "Due amount is $250 with special pricing \u2014 pricing basis should be confirmed"], "summary": "B2B CAD file order for MS Architects, Inc. at 7411 W Cypresshead Dr, Parkland FL (Broward County), currently on hold with special pricing applied and no supporting appraiser or email data available."}}</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>1780422364576</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>2026-06-02T17:15:01.349966+00:00</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:46:05.803008+00:00</t>
+        </is>
+      </c>
+      <c r="R130" t="n">
+        <v>587</v>
+      </c>
       <c r="T130" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.818516+00:00</t>
@@ -8347,7 +8368,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>2026-06-02T17:15:01.400133+00:00</t>
+          <t>2026-06-02T17:46:05.843680+00:00</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8380,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8382,16 +8403,37 @@
           <t>7300 SW 87TH AVE, MIAMI, FLORIDA 33173</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "The lot size is 6.45 acres, which exceeds the 5.00-acre threshold defined in the pricing guidelines. Per those guidelines, any lot greater than 5.00 acres must be escalated regardless of service type and cannot be priced by the automated system. Additionally, the legal description is a metes-and-bounds partial tract description ('all that portion of Tracts 1 and 2... lying south of a line...'), which adds further complexity warranting management review. The negotiated base rate of $3,000.00 is noted and should be communicated to management as the agreed floor.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "Lot size of 6.45 acres exceeds the 5.00-acre escalation threshold. Per pricing guidelines, lots greater than 5.00 acres must not be priced and require management quoting. Additional complexity factors to surface during review: (1) metes-and-bounds partial tract legal description requiring boundary reconstruction; (2) FEMA Flood Zone AH with a 10 ft BFE elevation designation which may require an Elevation Certificate in addition to the boundary survey; (3) commercial property flag; (4) client has a management-agreed negotiated base rate of $3,000.00 which should serve as the floor. Management should assess total acreage field effort, legal description reconstruction complexity, and whether an EC is required.", "flags": ["LOT_SIZE_ESCALATE: 6.45 acres exceeds 5.00-acre pricing threshold \u2014 management quote required.", "METES_AND_BOUNDS: Legal description is a partial tract metes-and-bounds description; boundary reconstruction complexity must be manually assessed.", "FEMA_ZONE_AH: Flood Zone AH with 10 ft BFE \u2014 confirm with client whether an Elevation Certificate is required in addition to the land survey.", "COMMERCIAL_FLAG: Property flagged as commercial \u2014 may affect field crew requirements and turnaround.", "NEGOTIATED_RATE_ON_FILE: Management-agreed base rate of $3,000.00 for CDS-Commercial Due Diligence Services should be used as the pricing floor.", "ORDER_COUNT_ZERO: Client shows 0 prior orders with NexGen despite OLD_TITLE tier designation \u2014 verify account history before applying tier benefits."]}</t>
+        </is>
+      </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202411141637401215, "created_at": "2025-12-18T16:02:00", "customer_email": "sboscarelli@firstam.com", "customer_id": 202411141641273684, "customer_name": "Scott  Boscarelli", "customer_type": "b2b", "delivered_at": "2026-03-11T16:15:33", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0454L\nZONE: AH\nELEV: 10 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000276269, "paid": true, "property_address": "7300 SW 87TH AVE", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.701289", "property_lng": "-80.335042", "property_state": "FLORIDA", "property_zip": "33173", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-03-11T16:15:33"}, "success": true, "order_id": "1000276269", "customer_email": "sboscarelli@firstam.com", "service_type": "Land Survey Only", "county": "", "property_address": "7300 SW 87TH AVE", "customer_name": "CDS-Commercial Due Diligence Services"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "CDS-Commercial Due Diligence Services", "confidence": "MEDIUM"}, "client_email": {"value": "sboscarelli@firstam.com", "confidence": "HIGH"}, "property_address": {"value": "7300 SW 87TH AVE, MIAMI, FLORIDA 33173", "confidence": "HIGH"}, "property_county": {"value": "MIAMI-DADE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested (elevation_cert: false)"}, "special_requirements": {"value": "Special pricing applies; Flood Zone AH at 10 FT elevation (FIRM Panel 12086C0454L, effective 09/11/2009)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order data lists 'Scott Boscarelli' as customer_name but outer payload shows 'CDS-Commercial Due Diligence Services' \u2014 confirm correct billing client", "Lot size unknown \u2014 no appraiser data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, structures, etc.) unknown \u2014 no appraiser or aerial data", "No matching emails found to supplement order details", "County field is blank in outer payload despite being populated in order data \u2014 may need reconciliation", "Invoice amount not set (invoiced: false, due_amount: 0.0) \u2014 pricing needs to be finalized despite special_pricing flag"], "summary": "B2B land survey order for 7300 SW 87TH AVE, Miami-Dade County, FL 33173, placed by CDS-Commercial Due Diligence Services (contact: sboscarelli@firstam.com), delivered on 2026-03-11, with special pricing and a Flood Zone AH designation; invoice not yet issued."}}</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1780422383837</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>2026-06-02T17:15:13.902482+00:00</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:46:24.557130+00:00</t>
+        </is>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
       <c r="T131" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.874087+00:00</t>
@@ -8399,7 +8441,7 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>2026-06-02T17:15:13.958355+00:00</t>
+          <t>2026-06-02T17:46:24.598372+00:00</t>
         </is>
       </c>
     </row>
@@ -8411,7 +8453,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8434,16 +8476,37 @@
           <t>2925 E 17TH AVE, TAMPA, FL 33605</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "Land Survey (Boundary)", "description": "Boundary survey for East 40 ft of Lot 1, Block 18, Greenville Subdivision, 2925 E 17th Ave, Tampa, Hillsborough County. Small residential lot (0.09 ac), FEMA Zone X (no flood risk upcharge), no complexity upcharges warranted. Priced at Achieve Title Services negotiated rate.", "amount": 450.0}], "pricing_reasoning": "The service type is undefined per order notes, but the property context (small residential lot, 0.09 ac, Zone X, platted subdivision with a simple lot-portion legal description) and the flagged duplicate order (1000275745 at the same address for Land Survey Only) strongly indicate a standard boundary survey is the intended service. The negotiated rate of $450.00 for Achieve Title Services is applied as the base and final price. No complexity upcharges are supported: lot is well under 0.31 ac, FEMA Zone X carries no EC requirement, Hillsborough County has no mobilization premium, and the legal description is a simple platted lot reference with no metes-and-bounds complexity.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "Service type is explicitly undefined in the order notes ('specific surveying service(s) requested remain undefined'). Additionally, a likely duplicate order (1000275745) exists at the same address and folio for Land Survey Only \u2014 management should confirm whether this is a reissue, a correction, or a separate deliverable, and formally define the service before invoicing.", "flags": ["DUPLICATE_SUSPECTED: Order 1000275745 shares the same address (2925 E 17th Ave, Hillsborough County), same coordinates (27.9672533, -82.4266393), and same Folio (A-08-29-19-4VU-000018-00001.0) with service type 'Land Survey Only'. Human review required to determine if this is a duplicate, reorder, or separate scope.", "SERVICE_UNDEFINED: Order notes state the surveying service(s) requested remain undefined. Pricing assumes boundary survey based on duplicate order context and property profile, but management confirmation is required before delivery.", "B2B_SPECIAL_PRICING: Order notes indicate this was delivered as a B2B order marked as paid with special pricing. Verify that $450.00 negotiated rate aligns with any previously agreed special pricing for this specific order."]}</t>
+        </is>
+      </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 201801311047307704, "created_at": "2025-12-18T11:49:03", "customer_email": "stephanie@achievetitle.com", "customer_id": 201804271046596087, "customer_name": "Stephanie Hall", "customer_type": "b2b", "delivered_at": "2025-12-22T14:11:20", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12057C0358J\nZONE: X\nEFF: 10/07/2021", "invoiced": false, "order_id": 1000276241, "paid": true, "property_address": "2925 E 17TH AVE", "property_city": "TAMPA", "property_county": "HILLSBOROUGH COUNTY", "property_lat": "27.9672533", "property_lng": "-82.4266393", "property_state": "FL", "property_zip": "33605", "service_type": "Other Services", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276241", "customer_email": "stephanie@achievetitle.com", "service_type": "Other Services", "county": "", "property_address": "2925 E 17TH AVE", "customer_name": "Achieve Title Services"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Achieve Title Services", "confidence": "MEDIUM"}, "client_email": {"value": "stephanie@achievetitle.com", "confidence": "HIGH"}, "property_address": {"value": "2925 E 17TH AVE, TAMPA, FL 33605", "confidence": "HIGH"}, "property_county": {"value": "HILLSBOROUGH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Other Services"], "confidence": "LOW", "notes": "Service type listed as 'Other Services' \u2014 specific service(s) requested are not defined; requires human clarification"}, "special_requirements": {"value": "Special pricing applied", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available and no aerial or email source to infer features such as pool, shed, driveways, or visible structures"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific service(s) requested \u2014 'Other Services' is too vague for invoicing", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, etc.) unknown \u2014 no appraiser or aerial data", "Client name conflict \u2014 order contact is 'Stephanie Hall' but company name shown as 'Achieve Title Services'; confirm billing entity", "No matching emails found \u2014 unable to verify scope from correspondence", "County was blank in outer FTF envelope despite being present in nested data \u2014 data integrity note"], "summary": "A delivered B2B order for Achieve Title Services at 2925 E 17th Ave, Tampa FL (Hillsborough County) marked as paid with special pricing, but the specific surveying service(s) requested remain undefined and property details are unavailable without appraiser data."}}</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1780422404429</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>2026-06-02T17:15:24.867985+00:00</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:46:44.756961+00:00</t>
+        </is>
+      </c>
+      <c r="R132" t="n">
+        <v>450</v>
+      </c>
       <c r="T132" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.930495+00:00</t>
@@ -8451,7 +8514,7 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>2026-06-02T17:15:24.920317+00:00</t>
+          <t>2026-06-02T17:46:44.798814+00:00</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8526,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8486,16 +8549,37 @@
           <t>214 S Swinton Ave, Delray Beach, FL 33444</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "This order is flagged as a generic 'Quote' with no specific survey service selected by the client. Two active sibling orders already exist for this same parcel \u2014 Order 1000274100 for an Elevation Certificate and Order 1000275698 for a Land Survey Only \u2014 covering the most common service combinations. Without a defined service type, no price can be responsibly calculated. Human follow-up is required to determine whether this quote is redundant, represents a combined/bundled request, or a different service altogether (e.g., Topo, ILC, boundary with EC). The negotiated base rate of $500.00 and the $275.00 EC flat rate are on file and ready to apply once the service is confirmed.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "No survey service type has been selected by the client \u2014 this is an open/unspecified quote order. Additionally, two likely duplicate orders for the same parcel and folio (12434616010630010) already exist in the system: Order 1000274100 (Elevation Certificate) and Order 1000275698 (Land Survey Only). Human follow-up with client Nancy Brosnahan is required to (1) confirm the intended service(s), (2) determine whether this quote should be merged with or replace the existing orders, and (3) clarify whether a combined Land Survey + EC package is being requested. Pricing cannot be responsibly finalized until the service scope is defined.", "flags": ["DUPLICATE_SUSPECTED: Order 1000274100 \u2014 same address (214 S Swinton Ave), same county (Palm Beach), same folio (12434616010630010), same coordinates \u2014 service: Elevation Certificate. Do not duplicate billing.", "DUPLICATE_SUSPECTED: Order 1000275698 \u2014 same address (214 S Swinton Ave), same county (Palm Beach), same folio (12434616010630010), same coordinates \u2014 service: Land Survey Only. Do not duplicate billing.", "NO_SERVICE_SELECTED: Client submitted a Quote order with no survey service type specified. Follow-up required before pricing.", "SPECIAL_PRICING_FLAGGED: Management-agreed negotiated base rate of $500.00 is on file for this client. Apply upon service confirmation.", "FEMA_ZONE_X: No Elevation Certificate is required by flood zone alone, but EC may still be requested by lender or client \u2014 confirm during follow-up.", "NEW_CLIENT: Zero prior orders with NexGen \u2014 confirm contact details and service expectations during outreach."]}</t>
+        </is>
+      </c>
       <c r="H133" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202512161958497314, "created_at": "2025-12-16T15:00:01", "customer_email": "nebrosnahan@gmail.com", "customer_id": 202512161958498334, "customer_name": "Nancy Brosnahan", "customer_type": "individual", "delivered_at": "2025-12-29T20:02:50", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0979G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000276144, "paid": false, "property_address": "214 S SWINTON AVE", "property_city": "DELRAY BEACH", "property_county": "Palm Beach County", "property_lat": "26.457426", "property_lng": "-80.07328009999999", "property_state": "FL", "property_zip": "33444", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276144", "customer_email": "nebrosnahan@gmail.com", "service_type": "Quote", "county": "", "property_address": "214 S SWINTON AVE", "customer_name": "Nancy Brosnahan "}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Nancy Brosnahan", "confidence": "HIGH"}, "client_email": {"value": "nebrosnahan@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "214 S Swinton Ave, Delray Beach, FL 33444", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service has been selected yet. Actual service(s) needed must be confirmed with client."}, "special_requirements": {"value": "Special pricing flag is active", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available, no emails, and no aerial data provided. Pool, sheds, driveways, and other features are unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not selected \u2014 only 'Quote' is listed", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fence, etc.) unknown", "Special pricing details not specified \u2014 reason for special_pricing flag unclear", "No supporting emails or appraiser data to corroborate order details", "Fieldwork date not yet scheduled (fieldwork_at is null)", "Invoice has not been created and payment has not been made"], "summary": "Nancy Brosnahan, a residential client in Delray Beach (Palm Beach County), has an open quote order for 214 S Swinton Ave with no specific survey service selected, special pricing flagged, and significant property detail gaps requiring human follow-up."}}</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1780422424174</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>2026-06-02T17:15:35.327267+00:00</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:47:04.767465+00:00</t>
+        </is>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
       <c r="T133" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:15.986774+00:00</t>
@@ -8503,7 +8587,7 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>2026-06-02T17:15:35.460364+00:00</t>
+          <t>2026-06-02T17:47:04.847744+00:00</t>
         </is>
       </c>
     </row>
@@ -9607,7 +9691,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9627,7 +9711,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>8608 N 13TH ST</t>
+          <t>8608 N 13TH ST, TAMPA, FL 33604</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510311717570490, "created_at": "2025-11-14T14:39:05", "customer_email": "yaniescobar@realtyblu.com", "customer_id": 202510311717570589, "customer_name": "Yani Escobar", "customer_type": "individual", "delivered_at": "2025-11-18T18:43:34", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12057C0214J\nZONE: X\nEFF: 10/07/2021", "invoiced": false, "order_id": 1000274628, "paid": true, "property_address": "8608 N 13TH ST", "property_city": "TAMPA", "property_county": "Hillsborough County", "property_lat": "28.0285022", "property_lng": "-82.4465867", "property_state": "FL", "property_zip": "33604", "service_type": "Quote", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274628", "customer_email": "yaniescobar@realtyblu.com", "service_type": "Quote", "county": "", "property_address": "8608 N 13TH ST", "customer_name": "Yani Escobar"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Yani Escobar", "confidence": "HIGH"}, "client_email": {"value": "yaniescobar@realtyblu.com", "confidence": "HIGH"}, "property_address": {"value": "8608 N 13TH ST, TAMPA, FL 33604", "confidence": "HIGH"}, "property_county": {"value": "Hillsborough County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed as 'Quote' only \u2014 no specific survey service has been confirmed or selected. Actual service needed is unclear."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided."}, "client_tier": {"value": "residential", "confidence": "MEDIUM"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not confirmed \u2014 'Quote' is not a deliverable service", "Lot size unknown \u2014 no appraiser data available", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, fences, etc.) unknown", "No fieldwork date scheduled (fieldwork_at is null)", "No special requirements or client notes captured", "Order is marked paid but invoiced=false \u2014 billing status should be reviewed"], "summary": "Yani Escobar submitted a quote request for a residential property at 8608 N 13TH ST, Tampa, FL (Hillsborough County, Flood Zone X), but no specific survey service has been identified and key property details are missing."}}</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:45:07.529876+00:00</t>
         </is>
       </c>
       <c r="T155" t="inlineStr">
@@ -9637,7 +9731,7 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:17.400731+00:00</t>
+          <t>2026-06-02T17:45:07.570066+00:00</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9743,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9669,7 +9763,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>15645 BILLY GOAT LN</t>
+          <t>15645 Billy Goat Ln, Jupiter, FL 33478</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510211619094511, "created_at": "2025-11-17T08:50:04", "customer_email": "christine.frechette@outlook.com", "customer_id": 202510211619095665, "customer_name": "Christine Frechette", "customer_type": "individual", "delivered_at": "2025-11-26T14:45:47", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0165F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000274600, "paid": true, "property_address": "15645 BILLY GOAT LN", "property_city": "JUPITER", "property_county": "Palm Beach County", "property_lat": "26.9074424", "property_lng": "-80.1947711", "property_state": "FL", "property_zip": "33478", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274600", "customer_email": "christine.frechette@outlook.com", "service_type": "Quote", "county": "", "property_address": "15645 BILLY GOAT LN", "customer_name": "Christine Frechette"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Christine Frechette", "confidence": "HIGH"}, "client_email": {"value": "christine.frechette@outlook.com", "confidence": "HIGH"}, "property_address": {"value": "15645 Billy Goat Ln, Jupiter, FL 33478", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 actual survey service(s) requested have not been specified. Human review needed to determine scope."}, "special_requirements": {"value": "Special pricing applies", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments found to infer pool, shed, driveways, or other structures."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Actual survey service(s) requested \u2014 'Quote' is not a survey type", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fencing, driveways, etc.) unknown", "No customer data record found (empty FTF customer object)", "No matching emails found to clarify scope or intent", "County appraiser lookup unavailable", "Fieldwork date not scheduled"], "summary": "Residential quote order for Christine Frechette at 15645 Billy Goat Ln, Jupiter, FL (Palm Beach County, Flood Zone X) marked as delivered and paid with special pricing, but the actual survey service type and property details remain unspecified and require human review."}}</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:45:17.337285+00:00</t>
         </is>
       </c>
       <c r="T156" t="inlineStr">
@@ -9679,7 +9783,7 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:17.462755+00:00</t>
+          <t>2026-06-02T17:45:17.378354+00:00</t>
         </is>
       </c>
     </row>
@@ -9691,7 +9795,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9711,7 +9815,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>961 S ATLANTIC DR</t>
+          <t>961 S Atlantic Dr, Lantana, FL 33462</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202511141422100772, "created_at": "2025-11-14T09:42:02", "customer_email": "robertjserr@gmail.com", "customer_id": 202511141422100868, "customer_name": "Robert Serr", "customer_type": "individual", "delivered_at": "2025-11-18T18:37:01", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0783G\nZONE: AE\nELEV: 09 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000274593, "paid": true, "property_address": "961 S ATLANTIC DR", "property_city": "LANTANA", "property_county": "Palm Beach County", "property_lat": "26.574442", "property_lng": "-80.0436335", "property_state": "FL", "property_zip": "33462", "service_type": "Quote", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274593", "customer_email": "robertjserr@gmail.com", "service_type": "Quote", "county": "", "property_address": "961 S ATLANTIC DR", "customer_name": "Robert Serr"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Robert Serr", "confidence": "HIGH"}, "client_email": {"value": "robertjserr@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "961 S Atlantic Dr, Lantana, FL 33462", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., boundary, elevation cert, topographic) has been identified. Human review needed to determine what was actually quoted."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available and no emails or attachments provided. Pool, shed, driveways, and other features unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service requested is unknown \u2014 'Quote' is not a deliverable service type", "No lot size available", "No legal description available", "No structure square footage available", "No property features data (pool, shed, outbuildings, etc.)", "No special requirements noted", "County property appraiser data unavailable", "No matching emails found to clarify scope", "Flood zone data present (AE, 09 ft, eff. 12/20/2024) but elevation certificate was not requested \u2014 unclear if relevant to quote"], "summary": "Individual residential client Robert Serr submitted a quote request for a property at 961 S Atlantic Dr, Lantana, FL (Palm Beach County), but the specific survey service requested has not been identified and requires human follow-up."}}</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:45:27.681522+00:00</t>
         </is>
       </c>
       <c r="T157" t="inlineStr">
@@ -9721,7 +9835,7 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:17.571374+00:00</t>
+          <t>2026-06-02T17:45:27.722030+00:00</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9847,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9748,12 +9862,22 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Nexgen Land Solutions, LLC</t>
+          <t>ORDER RESOLUTIONS</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2207 SUMMIT BLVD</t>
+          <t>2207 SUMMIT BLVD, WEST PALM BEACH, FL 33406</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201801311053398445, "created_at": "2025-11-13T15:23:00", "customer_email": "FREDERICK_S@NEXGENLOGIX.COM", "customer_id": 202410281556504891, "customer_name": "ORDER RESOLUTIONS", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0587F\nZONE: AE\nELEV: 12.4 FT\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000274571, "paid": false, "property_address": "2207 SUMMIT BLVD", "property_city": "WEST PALM BEACH", "property_county": "Palm Beach County", "property_lat": "26.6663271", "property_lng": "-80.0748843", "property_state": "FL", "property_zip": "33406", "service_type": "Boundary Survey", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274571", "customer_email": "FREDERICK_S@NEXGENLOGIX.COM", "service_type": "Boundary Survey", "county": "", "property_address": "2207 SUMMIT BLVD", "customer_name": "Nexgen Land Solutions, LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "ORDER RESOLUTIONS", "confidence": "MEDIUM"}, "client_email": {"value": "FREDERICK_S@NEXGENLOGIX.COM", "confidence": "HIGH"}, "property_address": {"value": "2207 SUMMIT BLVD, WEST PALM BEACH, FL 33406", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Boundary Survey"], "confidence": "HIGH", "notes": "Service type explicitly stated as Boundary Survey in FTF order data"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client legal name is ambiguous \u2014 FTF order shows 'ORDER RESOLUTIONS' but customer_name in outer payload shows 'Nexgen Land Solutions, LLC'; needs human clarification", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown \u2014 no appraiser, aerial, or email data available", "Order is On Hold \u2014 reason for hold not specified, may require follow-up", "No fieldwork or delivery dates scheduled", "No matching emails found to corroborate scope or client instructions"], "summary": "A B2B boundary survey order for 2207 Summit BLVD, West Palm Beach, FL 33406 (Palm Beach County) placed by ORDER RESOLUTIONS / Nexgen Land Solutions LLC is currently on hold with special pricing applied and awaiting fieldwork scheduling."}}</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:45:37.491136+00:00</t>
         </is>
       </c>
       <c r="T158" t="inlineStr">
@@ -9763,7 +9887,7 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:17.633826+00:00</t>
+          <t>2026-06-02T17:45:37.531405+00:00</t>
         </is>
       </c>
     </row>
@@ -9775,7 +9899,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9790,12 +9914,22 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Angela N Alanis Rodriguez </t>
+          <t>Angela N Alanis Rodriguez</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>845 SE TIERRA CT</t>
+          <t>845 SE Tierra CT, Port St. Lucie, FL 34983</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510081432369617, "created_at": "2025-11-13T11:53:00", "customer_email": "Angie769495@yahoo.com", "customer_id": 202510081432369723, "customer_name": "Angela N Alanis Rodriguez", "customer_type": "individual", "delivered_at": "2025-11-18T15:35:25", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12111C0286K\nZONE: X\nEFF: 02/19/2020", "invoiced": false, "order_id": 1000274546, "paid": true, "property_address": "845 SE TIERRA CT", "property_city": "PORT ST. LUCIE", "property_county": "St. Lucie County", "property_lat": "27.3104017", "property_lng": "-80.34669389999999", "property_state": "FL", "property_zip": "34983", "service_type": "Land Survey Only", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274546", "customer_email": "Angie769495@yahoo.com", "service_type": "Land Survey Only", "county": "", "property_address": "845 SE TIERRA CT", "customer_name": "Angela N Alanis Rodriguez "}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Angela N Alanis Rodriguez", "confidence": "HIGH"}, "client_email": {"value": "Angie769495@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "845 SE Tierra CT, Port St. Lucie, FL 34983", "confidence": "HIGH"}, "property_county": {"value": "St. Lucie County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing \u2014 no appraiser or document source", "Structure square footage unknown", "Property features (pool, shed, fence, etc.) unknown \u2014 no aerial or appraiser data", "Special requirements or client notes not provided", "No matching emails found to supplement order details", "Fieldwork date not yet scheduled (fieldwork_at is null)"], "summary": "Residential land survey order for Angela N Alanis Rodriguez at 845 SE Tierra CT, Port St. Lucie, FL 34983 (St. Lucie County); order is paid and delivered but lacks lot size, legal description, and property feature details due to unavailable appraiser data."}}</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:45:46.653873+00:00</t>
         </is>
       </c>
       <c r="T159" t="inlineStr">
@@ -9805,7 +9939,7 @@
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:17.697033+00:00</t>
+          <t>2026-06-02T17:45:46.693694+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -8599,7 +8599,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8622,16 +8622,37 @@
           <t>1106 Beville Rd, Daytona Beach, FL 32114</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>{"total_amount": 3550.0, "services": [{"name": "Land Survey (Commercial)", "description": "Boundary/land survey for commercial property at 1106 Beville Rd, Daytona Beach, Volusia County. Negotiated base rate agreed upon by management for CDS-Commercial Due Diligence Services.", "amount": 3000.0}, {"name": "Acreage Complexity Upcharge (2.04 Acres)", "description": "Lot falls in the 2.01\u20135.00 ac tier. 2.04-acre commercial parcel requiring expanded field traverse and boundary resolution across portions of Lots 6 and 7, Block 22.", "amount": 550.0}], "pricing_reasoning": "The negotiated base rate of $3,000.00 was pre-agreed by management for this specific CDS client and is applied directly. The property is 2.04 acres, placing it squarely in the 2.01\u20135.00 ac complexity tier (+$550.00), which is supported by the partial-lot metes-and-bounds legal description referencing portions of two lots across a historic subdivision \u2014 reflecting genuine field complexity beyond a simple platted parcel. FEMA Zone X requires no elevation certificate, and no pool, waterfront, Monroe County, or heavy vegetation indicators were identified from the available data.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["Order notes indicate this job was already delivered and marked paid but not yet formally invoiced \u2014 verify payment status before issuing invoice to avoid double-billing.", "Order count shows 0 prior orders for CDS despite being classified OLD_TITLE with a negotiated rate \u2014 confirm client tier and rate agreement on file before finalizing.", "Legal description references a partial portion of Lots 6 and 7 (metes and bounds style) \u2014 acreage upcharge already accounts for this complexity; a standalone metes-and-bounds upcharge was not double-applied."]}</t>
+        </is>
+      </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202411141637401215, "created_at": "2025-12-16T10:20:05", "customer_email": "sboscarelli@firstam.com", "customer_id": 202411141641273684, "customer_name": "Scott  Boscarelli", "customer_type": "b2b", "delivered_at": "2026-02-03T20:07:08", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12127C0366H\nZONE: X\nEFF: 02/19/2014", "invoiced": false, "order_id": 1000276104, "paid": true, "property_address": "1106 BEVILLE RD", "property_city": "DAYTONA BEACH", "property_county": "VOLUSIA COUNTY", "property_lat": "29.1758954", "property_lng": "-81.0309798", "property_state": "FLORIDA", "property_zip": "32114", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-02-10T14:01:51"}, "success": true, "order_id": "1000276104", "customer_email": "sboscarelli@firstam.com", "service_type": "Land Survey Only", "county": "", "property_address": "1106 BEVILLE RD", "customer_name": "CDS-Commercial Due Diligence Services"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "CDS-Commercial Due Diligence Services", "confidence": "MEDIUM"}, "client_email": {"value": "sboscarelli@firstam.com", "confidence": "HIGH"}, "property_address": {"value": "1106 Beville Rd, Daytona Beach, FL 32114", "confidence": "HIGH"}, "property_county": {"value": "Volusia County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate required per order flags."}, "special_requirements": {"value": "Special pricing applied to this order.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email sources provided."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order contact is 'Scott Boscarelli' at First American (sboscarelli@firstam.com), but customer_name field lists 'CDS-Commercial Due Diligence Services' \u2014 clarify who the actual billing client is", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, etc.)", "No fieldwork date recorded \u2014 confirm scheduling status", "Invoice has not been sent despite order being marked Delivered and Paid \u2014 verify billing workflow"], "summary": "A completed B2B land survey order for 1106 Beville Rd, Daytona Beach, FL (Volusia County) placed by Scott Boscarelli of First American / CDS-Commercial Due Diligence Services, with special pricing applied, marked delivered and paid, but not yet invoiced."}}</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>1780422728037</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>2026-06-02T17:15:46.209270+00:00</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:52:08.986340+00:00</t>
+        </is>
+      </c>
+      <c r="R134" t="n">
+        <v>3550</v>
+      </c>
       <c r="T134" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:16.043646+00:00</t>
@@ -8639,7 +8660,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>2026-06-02T17:15:46.259414+00:00</t>
+          <t>2026-06-02T17:52:09.038918+00:00</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8672,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8674,16 +8695,37 @@
           <t>6100 Hollywood Blvd, Hollywood, Florida 33024</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>{"total_amount": 1025.0, "services": [{"name": "Land Survey Only \u2013 Base Rate (Individual)", "description": "Standard boundary survey for individual residential client James Jean-Francois at 6100 Hollywood Blvd, Hollywood, Broward County. Default individual base rate applied per pricing guidelines.", "amount": 475.0}, {"name": "Lot Size Complexity Upcharge (2.01\u20135.00 ac)", "description": "Property is 4.63 acres per database, falling within the 2.01\u20135.00 ac complexity tier. Upcharge applied for increased field time, traversal, and boundary monument recovery across a larger parcel.", "amount": 550.0}], "pricing_reasoning": "The service requested is a Land Survey Only for an individual client with no negotiated rate, so the $475.00 individual base rate applies. The parcel is 4.63 acres, which falls squarely within the 2.01\u20135.00 ac lot complexity tier, warranting the full $550.00 upcharge for the additional field effort required. No Elevation Certificate was ordered, so no EC line item is added despite the split FEMA flood zone (AH/X500); the split zone is noted as a complexity flag but does not trigger EC pricing absent a client request. The property is a named plat parcel (not metes and bounds), Broward County (no Monroe remote mobilization), and no pool, waterfront canal, or heavy vegetation data was confirmed from available order details, so no additional upcharges are applied.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["SPLIT_FLOOD_ZONE: Property carries dual FEMA designations (AH at 9 ft ELEV and X500, effective 07/31/2024). No Elevation Certificate was ordered. Client or lender may subsequently require an EC \u2014 recommend proactively advising James Jean-Francois of this possibility.", "COMMERCIAL_FLAG_CONFLICT: The order data flags this property as commercial (commercial_flag: true), yet the client is identified as an individual residential homeowner. This discrepancy should be verified \u2014 if the property is genuinely commercial, a commercial base rate review may be warranted.", "HOLD_STATUS: Order notes indicate the job is currently on hold with no supporting appraiser or email data available. Confirm all client contact and scope details are resolved before dispatching field crew.", "NO_AERIAL_DATA: No aerial image or parcel photo was available for independent field complexity verification (vegetation, structures, water features). Pricing assumes standard complexity for the lot size tier."]}</t>
+        </is>
+      </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202512161435103028, "created_at": "2025-12-16T10:57:03", "customer_email": "jjonlaw@hotmail.com", "customer_id": 202512161435103387, "customer_name": "James Jean-Francois", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0564J\nZONE: AH\nELEV: 09 FT\nZONE: X500\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000276101, "paid": false, "property_address": "6100 HOLLYWOOD BLVD", "property_city": "HOLLYWOOD", "property_county": "BROWARD COUNTY", "property_lat": "26.0092779", "property_lng": "-80.2100833", "property_state": "FLORIDA", "property_zip": "33024", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276101", "customer_email": "jjonlaw@hotmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "6100 HOLLYWOOD BLVD", "customer_name": "James Jean-Francois"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "James Jean-Francois", "confidence": "HIGH"}, "client_email": {"value": "jjonlaw@hotmail.com", "confidence": "HIGH"}, "property_address": {"value": "6100 Hollywood Blvd, Hollywood, Florida 33024", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data. No elevation certificate requested."}, "special_requirements": {"value": "Property is in a split flood zone: AH (Elev 09 FT) and X500, per FIRM panel 12011C0564J effective 07/31/2024. Order is currently On Hold.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features (pool, shed, driveway, etc.) unknown \u2014 no aerial or appraiser data", "Order is On Hold \u2014 reason for hold not specified, needs human review", "No urgency or deadline indicated", "No matching emails found to supplement order details"], "summary": "Individual residential client James Jean-Francois has ordered a Land Survey Only for 6100 Hollywood Blvd, Hollywood, Broward County FL 33024, currently on hold with split flood zone designations (AH and X500) and no supporting appraiser or email data available."}}</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1780422749252</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>2026-06-02T17:21:05.053557+00:00</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:52:30.097206+00:00</t>
+        </is>
+      </c>
+      <c r="R135" t="n">
+        <v>1025</v>
+      </c>
       <c r="T135" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:16.100907+00:00</t>
@@ -8691,7 +8733,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>2026-06-02T17:21:05.105767+00:00</t>
+          <t>2026-06-02T17:52:30.149853+00:00</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8745,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8726,16 +8768,37 @@
           <t>118 Newham Way, Kissimmee, FL 34758</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>{"total_amount": 400.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for LOT 9, BLOCK 632, POINCIANA NEIGHBORHOOD 1, VILLAGE 2, Osceola County. Standard platted residential lot of 0.22 acres. FEMA Zone X (no flood risk, no EC required). No complexity upcharges applicable.", "amount": 400.0}], "pricing_reasoning": "Client tier is OLD_TITLE with no negotiated rate on file, so the default base rate of $400.00 applies. The property is a standard platted subdivision lot (0.22 acres, well under the 0.31-acre threshold for a size upcharge), located in Osceola County with no Monroe County remoteness premium. FEMA Zone X carries no flood risk and no Elevation Certificate is requested or required. The legal description references a recorded plat (not metes and bounds), and no pool, waterfront, or heavy vegetation indicators are present in the available data, so no complexity upcharges are warranted.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["Order notes indicate the order was previously on hold with no invoicing or lot data available; lot data and legal description have since been populated and pricing can now proceed.", "Order count for client 'Kaila' (emsteam.us) shows 0 prior orders with NexGen \u2014 no pricing history available to cross-reference, but default OLD_TITLE rate applied per guidelines."]}</t>
+        </is>
+      </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202511061522427450, "created_at": "2025-12-15T15:12:04", "customer_email": "kaila@emsteam.us", "customer_id": 202511061522427550, "customer_name": "Kaila", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12097C0230G\nZONE: X\nEFF: 06/18/2013", "invoiced": false, "order_id": 1000276064, "paid": false, "property_address": "118 NEWHAM WAY", "property_city": "KISSIMMEE", "property_county": "OSCEOLA COUNTY", "property_lat": "28.1881449", "property_lng": "-81.494078", "property_state": "FLORIDA", "property_zip": "34758", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276064", "customer_email": "kaila@emsteam.us", "service_type": "Land Survey Only", "county": "", "property_address": "118 NEWHAM WAY", "customer_name": "Kaila"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Kaila", "confidence": "HIGH"}, "client_email": {"value": "kaila@emsteam.us", "confidence": "HIGH"}, "property_address": {"value": "118 Newham Way, Kissimmee, FL 34758", "confidence": "HIGH"}, "property_county": {"value": "Osceola County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments to reference"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Full client/company name \u2014 only first name 'Kaila' provided", "Legal description of the property", "Lot size", "Structure square footage", "Property features (pool, shed, fencing, driveways, etc.)", "Special requirements or scope clarification", "Order is currently 'On Hold' \u2014 reason for hold unknown", "No invoice or payment information established", "County property appraiser data unavailable", "No matching emails found \u2014 no additional context from client communications"], "summary": "B2B order from Kaila (emsteam.us) for a Land Survey Only at 118 Newham Way, Kissimmee, FL 34758 (Osceola County), currently on hold with no invoicing, lot data, or legal description available."}}</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1780422763566</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>2026-06-02T17:21:14.182406+00:00</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:52:44.664166+00:00</t>
+        </is>
+      </c>
+      <c r="R136" t="n">
+        <v>400</v>
+      </c>
       <c r="T136" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:16.158014+00:00</t>
@@ -8743,7 +8806,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>2026-06-02T17:21:14.234409+00:00</t>
+          <t>2026-06-02T17:52:44.797055+00:00</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8818,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8778,16 +8841,37 @@
           <t>235 Worth Ct, West Palm Beach, FL 33405</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "CAD File", "description": "CAD file delivery for residential lot at 235 Worth Ct, West Palm Beach, FL 33405. Lot 8, Plat of Worth Court, Palm Beach County. 0.26 acres, FEMA Zone X (no flood complexity). Base rate per management-agreed special pricing for individual client Lee Moldoff.", "amount": 450.0}], "pricing_reasoning": "Management has explicitly agreed upon a negotiated rate of $450.00 for this individual client (Lee Moldoff, 0 prior orders). The service requested is a CAD file for a 0.26-acre residential lot in Palm Beach County, FEMA Zone X \u2014 no flood zone upcharge applies. The lot size falls below the 0.31-acre threshold for a size upcharge, the legal description is a platted lot (not metes and bounds, though it includes a 'less' clause for the west 5 feet, which is a minor exception and does not rise to full metes-and-bounds complexity warranting an upcharge on a CAD-only order), and no pool, waterfront, heavy vegetation, or Monroe County factors are indicated. The $450.00 agreed rate is used as the total with no additional upcharges.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE_DUPLICATE: Order 1000270864 covers the same property (235 Worth Ct, Palm Beach County, Folio 74434403020000080) for a Land Survey Only service. This CAD file order may be derivative of or related to that survey. Human review recommended to confirm whether existing survey data from Order 1000270864 can be leveraged for this CAD file delivery, and to verify this is not an unintentional duplicate.", "ORDER_ON_HOLD: Per order notes, this order is currently on hold pending further action. Pricing is provided but invoice should not be finalized until hold is resolved.", "LEGAL_DESC_NOTE: Legal description includes a 'LESS' clause (west 5 feet of Lot 8). This creates a minor encumbrance on the boundary description but is a simple strip exception \u2014 not treated as full metes-and-bounds complexity for CAD file purposes. Field surveyor should confirm no additional complexity exists on-site."]}</t>
+        </is>
+      </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202512151719317720, "created_at": "2025-12-15T12:22:05", "customer_email": "lm1arch@bellsouth.net", "customer_id": 202512151719318715, "customer_name": "Lee Moldoff", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0591G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000276043, "paid": true, "property_address": "235 WORTH CT", "property_city": "WEST PALM BEACH", "property_county": "Palm Beach County", "property_lat": "26.6729137", "property_lng": "-80.05204379999999", "property_state": "FL", "property_zip": "33405", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000276043", "customer_email": "lm1arch@bellsouth.net", "service_type": "CAD file", "county": "", "property_address": "235 WORTH CT", "customer_name": "Lee Moldoff"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Lee Moldoff", "confidence": "HIGH"}, "client_email": {"value": "lm1arch@bellsouth.net", "confidence": "HIGH"}, "property_address": {"value": "235 Worth Ct, West Palm Beach, FL 33405", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated in the data"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments present"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, structures, etc.)", "No county appraiser data available to cross-reference", "Reason for 'On Hold' status not specified", "Scope of CAD file not clarified (boundary, as-built, topo, etc.)", "No fieldwork or delivery dates scheduled", "Invoice has not been sent despite order being marked paid \u2014 needs reconciliation", "No customer data returned from FTF customer record"], "summary": "Individual client Lee Moldoff has ordered a CAD file for a residential property at 235 Worth Ct, West Palm Beach FL 33405 (Flood Zone X), with special pricing applied and the order currently on hold pending further action."}}</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1780422784182</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>2026-06-02T17:21:24.173372+00:00</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:53:04.837553+00:00</t>
+        </is>
+      </c>
+      <c r="R137" t="n">
+        <v>450</v>
+      </c>
       <c r="T137" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:16.215726+00:00</t>
@@ -8795,7 +8879,7 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>2026-06-02T17:21:24.223606+00:00</t>
+          <t>2026-06-02T17:53:04.894547+00:00</t>
         </is>
       </c>
     </row>
@@ -9951,7 +10035,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9971,7 +10055,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>3023 SE CAMINO AVE</t>
+          <t>3023 SE Camino Ave, Stuart, FL 34997</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202511121630457812, "created_at": "2025-11-13T17:08:02", "customer_email": "maryvega551@gmail.com", "customer_id": 202511121630457909, "customer_name": "Mary Romanelli", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12085C0162H\nZONE: X\nEFF: 02/19/2020", "invoiced": false, "order_id": 1000274472, "paid": false, "property_address": "3023 SE CAMINO AVE", "property_city": "STUART", "property_county": "MARTIN COUNTY", "property_lat": "27.168144", "property_lng": "-80.21687299999999", "property_state": "FLORIDA", "property_zip": "34997", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274472", "customer_email": "maryvega551@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "3023 SE CAMINO AVE", "customer_name": "Mary Romanelli"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Mary Romanelli", "confidence": "HIGH"}, "client_email": {"value": "maryvega551@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "3023 SE Camino Ave, Stuart, FL 34997", "confidence": "HIGH"}, "property_county": {"value": "Martin County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data. No additional services indicated."}, "special_requirements": {"value": "None identified", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, outbuildings, etc.) unknown", "Order is currently On Hold \u2014 reason for hold not specified", "No fieldwork date scheduled", "Invoice has not been sent; due amount is $0 \u2014 pricing not yet established", "Client email (maryvega551@gmail.com) does not match customer name 'Mary Romanelli' \u2014 may indicate a third-party email or alias; verify client identity", "No supporting emails or documents attached"], "summary": "Residential land survey order for Mary Romanelli at 3023 SE Camino Ave, Stuart, FL (Martin County) currently on hold with no fieldwork scheduled, no pricing established, and limited property detail available."}}</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:51:10.241058+00:00</t>
         </is>
       </c>
       <c r="T160" t="inlineStr">
@@ -9981,7 +10075,7 @@
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:17.760217+00:00</t>
+          <t>2026-06-02T17:51:10.292626+00:00</t>
         </is>
       </c>
     </row>
@@ -9993,7 +10087,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10013,7 +10107,17 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>10534 173RD RD N</t>
+          <t>10534 173RD RD N, JUPITER, FL 33478</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202511101652036071, "created_at": "2025-11-10T17:41:04", "customer_email": "smarion@conroysimberg.com", "customer_id": 202511101652037281, "customer_name": "Samantha Marion", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0165F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000274358, "paid": false, "property_address": "10534 173RD RD N", "property_city": "JUPITER", "property_county": "PALM BEACH COUNTY", "property_lat": "26.9325123", "property_lng": "-80.200052", "property_state": "FL", "property_zip": "33478", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274358", "customer_email": "smarion@conroysimberg.com", "service_type": "Land Survey Only", "county": "", "property_address": "10534 173RD RD N", "customer_name": "Samantha Marion"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Samantha Marion", "confidence": "HIGH"}, "client_email": {"value": "smarion@conroysimberg.com", "confidence": "HIGH"}, "property_address": {"value": "10534 173RD RD N, JUPITER, FL 33478", "confidence": "HIGH"}, "property_county": {"value": "PALM BEACH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing flagged on order; order is currently On Hold (status code 11) \u2014 reason for hold unknown.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or aerial data provided."}, "client_tier": {"value": "residential", "confidence": "MEDIUM", "notes": "Customer type is 'individual'; email domain conroysimberg.com suggests a law firm affiliation which may indicate b2b referral, but account is registered as individual."}, "urgency": {"value": "normal", "confidence": "MEDIUM", "notes": "No rush indicators present; order is On Hold with no fieldwork or delivery dates scheduled."}, "source_of_truth": "ftf_only", "gaps": ["Reason for 'On Hold' status is unknown \u2014 needs human review", "Special pricing flag set but no pricing details or approval noted", "Lot size not available \u2014 county appraiser data unavailable", "Legal description not available \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features (pool, shed, structures) unknown \u2014 no aerial or appraiser data", "No fieldwork date scheduled", "Client relationship unclear \u2014 email domain suggests possible law firm/b2b referral despite individual account type", "No matching emails found to clarify scope or instructions"], "summary": "Residential land survey order for Samantha Marion at 10534 173RD RD N, Jupiter, FL 33478 (Palm Beach County) is currently On Hold with special pricing flagged and no fieldwork scheduled, pending clarification."}}</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:51:22.541011+00:00</t>
         </is>
       </c>
       <c r="T161" t="inlineStr">
@@ -10023,7 +10127,7 @@
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:17.824346+00:00</t>
+          <t>2026-06-02T17:51:22.592916+00:00</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10139,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10055,7 +10159,17 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>5505 S INDIAN RIVER DR</t>
+          <t>5505 S Indian River Dr, Fort Pierce, FL 34982</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510021939408806, "created_at": "2025-11-05T12:34:02", "customer_email": "karinabodina@yahoo.com", "customer_id": 202510021939409897, "customer_name": "Sally Daw", "customer_type": "individual", "delivered_at": "2025-12-01T14:09:13", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12111C0281K\nZONE: X\nEFF: 02/19/2020", "invoiced": false, "order_id": 1000274136, "paid": true, "property_address": "5505 S INDIAN RIVER DR", "property_city": "FORT PIERCE", "property_county": "ST LUCIE COUNTY", "property_lat": "27.374539", "property_lng": "-80.2926932", "property_state": "FL", "property_zip": "34982", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274136", "customer_email": "karinabodina@yahoo.com", "service_type": "Land Survey Only", "county": "", "property_address": "5505 S INDIAN RIVER DR", "customer_name": "Sally Daw"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Sally Daw", "confidence": "HIGH"}, "client_email": {"value": "karinabodina@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "5505 S Indian River Dr, Fort Pierce, FL 34982", "confidence": "HIGH"}, "property_county": {"value": "St Lucie County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as Land Survey Only; no elevation certificate requested"}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, outbuildings, etc.) unknown", "Client email (karinabodina@yahoo.com) does not match customer name Sally Daw \u2014 possible third-party or agent email, needs verification", "Fieldwork date not yet scheduled", "Invoice not yet generated despite order being paid and delivered", "No pricing or line item details available"], "summary": "Residential land survey only order for Sally Daw at 5505 S Indian River Dr, Fort Pierce, FL (St Lucie County), marked paid and delivered with special pricing applied, but missing lot size, legal description, and property feature details."}}</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:51:32.131382+00:00</t>
         </is>
       </c>
       <c r="T162" t="inlineStr">
@@ -10065,7 +10179,7 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:17.888005+00:00</t>
+          <t>2026-06-02T17:51:32.183550+00:00</t>
         </is>
       </c>
     </row>
@@ -10077,7 +10191,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10097,7 +10211,17 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>510 RIVIERA DR</t>
+          <t>510 RIVIERA DR, FORT LAUDERDALE, FL 33301</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507251344426403, "created_at": "2025-11-05T10:43:03", "customer_email": "blaket@unlimitedps.net", "customer_id": 202507251346050711, "customer_name": "Blake Thomas", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0576J\nZONE: AE\nELEV: 07 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000274109, "paid": false, "property_address": "510 RIVIERA DR", "property_city": "FORT LAUDERDALE", "property_county": "BROWARD COUNTY", "property_lat": "26.120232", "property_lng": "-80.113396", "property_state": "FL", "property_zip": "33301", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274109", "customer_email": "blaket@unlimitedps.net", "service_type": "CAD file", "county": "", "property_address": "510 RIVIERA DR", "customer_name": "Unlimited Permit Services, INC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Unlimited Permit Services, INC", "confidence": "HIGH"}, "client_email": {"value": "blaket@unlimitedps.net", "confidence": "HIGH"}, "property_address": {"value": "510 RIVIERA DR, FORT LAUDERDALE, FL 33301", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD file; no additional services indicated"}, "special_requirements": {"value": "Special pricing flagged; order currently On Hold (status code 11); flood zone AE, panel 12011C0576J, base flood elevation 7 ft, effective 07/31/2024", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, etc.)", "No fieldwork date scheduled", "Order is On Hold \u2014 reason for hold not specified", "No estimate sent yet \u2014 pricing details not confirmed", "County appraiser data unavailable", "No matching emails found for additional context", "Urgency/rush status not indicated"], "summary": "B2B CAD file order for Unlimited Permit Services, INC on a flood zone AE property at 510 Riviera Dr, Fort Lauderdale, currently On Hold with special pricing flagged and no fieldwork or invoice activity yet."}}</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:51:42.282579+00:00</t>
         </is>
       </c>
       <c r="T163" t="inlineStr">
@@ -10107,7 +10231,7 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:17.952263+00:00</t>
+          <t>2026-06-02T17:51:42.384752+00:00</t>
         </is>
       </c>
     </row>
@@ -10119,7 +10243,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10134,12 +10258,22 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Christopher  Coventry</t>
+          <t>Christopher Coventry</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2395 CAMPBELL RD</t>
+          <t>2395 Campbell Rd, Clearwater, FL 33765</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202511051440302010, "created_at": "2025-11-05T09:44:02", "customer_email": "coventry.chris@gmail.com", "customer_id": 202511051440302993, "customer_name": "Christopher  Coventry", "customer_type": "individual", "delivered_at": "2025-11-11T21:05:29", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12103C0126G\nZONE: X\nEFF: 09/03/2003", "invoiced": false, "order_id": 1000274095, "paid": true, "property_address": "2395 CAMPBELL RD", "property_city": "CLEARWATER", "property_county": "Pinellas County", "property_lat": "27.98463", "property_lng": "-82.7385704", "property_state": "FL", "property_zip": "33765", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274095", "customer_email": "coventry.chris@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "2395 CAMPBELL RD", "customer_name": "Christopher  Coventry"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Christopher Coventry", "confidence": "HIGH"}, "client_email": {"value": "coventry.chris@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "2395 Campbell Rd, Clearwater, FL 33765", "confidence": "HIGH"}, "property_county": {"value": "Pinellas County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated."}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no emails, appraiser data, or aerial imagery provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fences, driveways) unknown \u2014 no aerial or appraiser data", "No matching emails found to clarify scope or special instructions", "Reason for special pricing not documented", "Fieldwork date not recorded (fieldwork_at is null)"], "summary": "Residential land survey only order for Christopher Coventry at 2395 Campbell Rd, Clearwater, FL (Pinellas County), marked delivered and paid with special pricing applied, but lacking lot size, legal description, and property feature details."}}</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:51:50.791868+00:00</t>
         </is>
       </c>
       <c r="T164" t="inlineStr">
@@ -10149,7 +10283,7 @@
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:18.064225+00:00</t>
+          <t>2026-06-02T17:51:50.844630+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -8891,7 +8891,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8914,16 +8914,37 @@
           <t>1248 NE 8TH AVE, DELRAY BEACH, FL 33483</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "CAD File - Boundary Survey", "description": "CAD file delivery for boundary/land survey at 1248 NE 8th Ave, Delray Beach, FL (Palm Beach County). Negotiated flat rate applied per management agreement for Kanthan Design Corporation.", "amount": 450.0}], "pricing_reasoning": "This is a CAD file order (B2B) for an established client (Kanthan Design Corporation) with a management-agreed negotiated rate of $450.00, which serves as the base and final rate. The lot is 0.24 acres (under 0.31 ac threshold), FEMA Zone X (no flood zone upcharge), Palm Beach County (no Monroe County surcharge), and the legal description \u2014 while metes-and-bounds in character \u2014 is noted as 'special pricing applied' per the order notes, indicating management has already factored complexity into the negotiated rate. No additional complexity upcharges are applied.", "confidence": "HIGH", "escalate_flag": true, "escalate_reason": "Order is currently ON HOLD per order notes, with special pricing applied and awaiting resolution before fieldwork can be scheduled. Additionally, three possible duplicate orders exist at the same address and folio \u2014 Orders 1000271851 (Land Survey Only), 1000276007 (CAD file), and 1000276238 (Land Survey Only) \u2014 all matching the same coordinates and folio/MLS number. Human review is required to confirm whether this order is a duplicate, whether the hold has been resolved, and whether the CAD file should be linked to fieldwork from one of the companion orders rather than priced as a standalone survey.", "flags": ["ORDER ON HOLD: Per order notes, this B2B CAD file order has special pricing applied and is awaiting resolution before fieldwork can be scheduled. Do not release to field until hold is cleared.", "POSSIBLE DUPLICATE \u2014 Order 1000271851: Same address (1248 NE 8th Ave, Palm Beach County), same folio 12434609120000020, same coordinates. Service: Land Survey Only. Verify if CAD file should be fulfilled from this order's fieldwork.", "POSSIBLE DUPLICATE \u2014 Order 1000276007: Same address, same folio, same coordinates. Service: CAD file. Potential exact duplicate of this order \u2014 confirm with client and management before proceeding.", "POSSIBLE DUPLICATE \u2014 Order 1000276238: Same address, same folio, same coordinates. Service: Land Survey Only. Third related order at same property; clarify relationship to this CAD file order.", "METES AND BOUNDS legal description present \u2014 no upcharge applied because management-negotiated special pricing ($450.00) is already in effect for this client and order.", "FEMA Zone X \u2014 no elevation certificate or flood zone upcharge applicable.", "Client order count is 0 despite OLD_TITLE tier designation \u2014 verify client account history before invoicing."]}</t>
+        </is>
+      </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202512121827218909, "created_at": "2025-12-12T13:31:00", "customer_email": "abhi@kanthandesign.com", "customer_id": 202512121828051160, "customer_name": "ABHI KANTHAN", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0977G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000275962, "paid": true, "property_address": "1248 NE 8TH AVE", "property_city": "DELRAY BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.4784572", "property_lng": "-80.065563", "property_state": "FL", "property_zip": "33483", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275962", "customer_email": "abhi@kanthandesign.com", "service_type": "CAD file", "county": "", "property_address": "1248 NE 8TH AVE", "customer_name": "KANTHAN DESIGN CORPORATION"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "KANTHAN DESIGN CORPORATION", "confidence": "HIGH"}, "client_email": {"value": "abhi@kanthandesign.com", "confidence": "HIGH"}, "property_address": {"value": "1248 NE 8TH AVE, DELRAY BEACH, FL 33483", "confidence": "HIGH"}, "property_county": {"value": "PALM BEACH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, etc.)", "County appraiser data unavailable \u2014 no county passed to appraiser lookup", "No matching emails found \u2014 no additional context from client correspondence", "Order is On Hold \u2014 reason for hold not specified, needs human review", "Urgency/deadline not specified", "Fieldwork date not scheduled", "Invoice has not been sent and order has not been delivered"], "summary": "B2B CAD file order for Kanthan Design Corporation at 1248 NE 8th Ave, Delray Beach FL (Palm Beach County) is currently On Hold with special pricing applied, awaiting resolution before fieldwork can be scheduled."}}</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1780423095216</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>2026-06-02T17:21:34.092680+00:00</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:58:18.013050+00:00</t>
+        </is>
+      </c>
+      <c r="R138" t="n">
+        <v>450</v>
+      </c>
       <c r="T138" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:16.273199+00:00</t>
@@ -8931,7 +8952,7 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>2026-06-02T17:21:34.145312+00:00</t>
+          <t>2026-06-02T17:58:18.063793+00:00</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8964,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8966,16 +8987,37 @@
           <t>129 Egret Ave, Naples, FL 34108</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "CAD File", "description": "CAD file deliverable for 129 Egret Ave, Naples, FL 34108 \u2014 Lot 26, Block S, Connor's Vanderbilt Beach Estates Unit 3, Collier County. Residential lot, 0.24 acres, FEMA Zone AE. Base rate applied per management-agreed special pricing for this individual client.", "amount": 450.0}], "pricing_reasoning": "The service requested is a CAD file only \u2014 not a new field survey, elevation certificate, or topographic survey \u2014 so no EC or topo line items apply. Management has established a negotiated base rate of $450.00 for this specific individual client, which is used as-is. The lot is 0.24 acres (below the 0.31 ac upcharge threshold), the legal description is a platted lot (no metes-and-bounds upcharge), and no pool, waterfront canal, heavy vegetation, or Monroe County factors are indicated, so no complexity upcharges are warranted.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE_DUPLICATE: Order 1000271856 covers the same property address (129 Egret Ave, Collier County) with service 'Land Survey and Elevation' and matches on both GPS coordinates (26.2691604, -81.8233018) and Folio/MLS (27633160002). This order is flagged for human review to confirm whether the CAD file is a follow-on deliverable from that prior order or a separate standalone request.", "ORDER_ON_HOLD: Per order notes, this order is currently on hold pending further action. Price proposed but should not be invoiced until hold is released.", "NEW_CLIENT: Zero prior orders on record for this client. No order history to cross-reference against."]}</t>
+        </is>
+      </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202512111446279347, "created_at": "2025-12-11T09:47:02", "customer_email": "trojanowski228@gmail.com", "customer_id": 202512111446281169, "customer_name": "Daniela Trojanowski", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12021C0189J\nZONE: AE\nELEV: 10 FT\nEFF: 02/08/2024", "invoiced": false, "order_id": 1000275872, "paid": true, "property_address": "129 EGRET AVE", "property_city": "NAPLES", "property_county": "COLLIER COUNTY", "property_lat": "26.2691604", "property_lng": "-81.8233018", "property_state": "FL", "property_zip": "34108", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275872", "customer_email": "trojanowski228@gmail.com", "service_type": "CAD file", "county": "", "property_address": "129 EGRET AVE", "customer_name": "Daniela Trojanowski"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Daniela Trojanowski", "confidence": "HIGH"}, "client_email": {"value": "trojanowski228@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "129 Egret Ave, Naples, FL 34108", "confidence": "HIGH"}, "property_county": {"value": "Collier County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11); flood zone data available: 12021C0189J, Zone AE, Elevation 10 ft, Effective 02/08/2024", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not available", "Legal description not available", "Structure square footage not available", "Property features (pool, shed, structures, driveways) unknown \u2014 county appraiser unavailable", "No county provided in top-level FTF county field (though Collier County is in property data)", "Reason for On Hold status unknown \u2014 may require human review before proceeding", "No customer data returned from FTF customer lookup", "No matching emails found \u2014 no additional context or attachments available", "Elevation certificate not requested but flood zone is AE at 10 ft \u2014 worth confirming with client"], "summary": "Individual residential client Daniela Trojanowski has ordered a CAD file for 129 Egret Ave, Naples, FL 34108 (Collier County, Flood Zone AE), with special pricing applied and the order currently on hold pending further action."}}</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1780423115938</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>2026-06-02T17:21:44.854225+00:00</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:58:39.153628+00:00</t>
+        </is>
+      </c>
+      <c r="R139" t="n">
+        <v>450</v>
+      </c>
       <c r="T139" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:16.379011+00:00</t>
@@ -8983,7 +9025,7 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>2026-06-02T17:21:44.907081+00:00</t>
+          <t>2026-06-02T17:58:39.204912+00:00</t>
         </is>
       </c>
     </row>
@@ -8995,7 +9037,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9018,16 +9060,37 @@
           <t>1519 SW 18TH AVE, FORT LAUDERDALE, FL 33312</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for LOT 77, LAUDERDALE ISLES NO.1, Plat Book 31 Page 23, Broward County. Residential lot 0.16 acres, platted subdivision, FEMA Zone AE. Management-agreed special rate applied for individual client Ryan Timberg.", "amount": 450.0}], "pricing_reasoning": "Client Ryan Timberg has a management-negotiated flat rate of $450.00 for this specific order. The property is a small residential platted lot (0.16 acres) in Broward County with a clean legal description from a recorded plat \u2014 no metes-and-bounds complexity, no pool, waterfront, heavy vegetation, or oversized lot upcharges are supported by the available data. No Elevation Certificate was ordered, so no EC line item applies. Base rate stands at $450.00 with no complexity additions warranted.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000275360 \u2014 same address (1519 SW 18TH AVE, Broward County), same service (Land Survey Only), same Folio/MLS (504216290720). Human review required to confirm this is not a duplicate submission.", "DUPLICATE_WARNING: Order 1000280641 \u2014 same address (1519 SW 18TH AVE, Broward County), same service (Land Survey Only), same Folio/MLS (504216290720). Human review required to confirm this is not a duplicate submission.", "DUPLICATE_WARNING: Order 1000281135 \u2014 same address (1519 SW 18TH AVE, Broward County), service CAD, same Folio/MLS (504216290720). Likely related CAD deliverable order \u2014 confirm workflow relationship.", "NOTE: Order notes indicate property details were partially unavailable at time of original order entry. Pricing is based on data now present in order (0.16 ac, platted lot, Broward County, Zone AE). Field crew should verify site conditions (pool, waterfront, vegetation) prior to mobilization and flag any discrepancies for repricing."]}</t>
+        </is>
+      </c>
       <c r="H140" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202512021724214710, "created_at": "2025-12-10T15:09:05", "customer_email": "ryantimberg@gmail.com", "customer_id": 202512021724215839, "customer_name": "Ryan Timberg", "customer_type": "individual", "delivered_at": "2025-12-22T14:15:01", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0556J\nZONE: AE\nELEV: 06 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000275849, "paid": true, "property_address": "1519 SW 18TH AVE", "property_city": "FORT LAUDERDALE", "property_county": "BROWARD COUNTY", "property_lat": "26.1008497", "property_lng": "-80.1651368", "property_state": "FL", "property_zip": "33312", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275849", "customer_email": "ryantimberg@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "1519 SW 18TH AVE", "customer_name": "Ryan Timberg"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Ryan Timberg", "confidence": "HIGH"}, "client_email": {"value": "ryantimberg@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1519 SW 18TH AVE, FORT LAUDERDALE, FL 33312", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested (elevation_cert: false)"}, "special_requirements": {"value": "Special pricing applied; property is in FEMA Flood Zone AE (Panel 12011C0556J, Elev 06 FT, Eff 07/31/2024)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no aerial or email data provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser unavailable and no parcel data provided", "Legal description not available", "Structure square footage unknown", "Property features (pool, shed, fences, driveways, etc.) unknown \u2014 no aerial or appraiser data", "No matching emails found to supplement order details", "Fieldwork date not yet scheduled (fieldwork_at: null)", "Invoice has not been sent (invoiced: false, estimate_sent: false) despite order being delivered and paid"], "summary": "Individual residential client Ryan Timberg has a delivered and paid Land Survey Only order for 1519 SW 18TH AVE, Fort Lauderdale, FL 33312 (Broward County, Flood Zone AE) with special pricing applied, but property details such as lot size, legal description, and site features are unavailable due to missing appraiser and supplemental data."}}</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1780423136324</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>2026-06-02T17:27:15.348149+00:00</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:58:56.672525+00:00</t>
+        </is>
+      </c>
+      <c r="R140" t="n">
+        <v>450</v>
+      </c>
       <c r="T140" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:16.437025+00:00</t>
@@ -9035,7 +9098,7 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>2026-06-02T17:27:15.394797+00:00</t>
+          <t>2026-06-02T17:58:56.736583+00:00</t>
         </is>
       </c>
     </row>
@@ -10295,7 +10358,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10315,7 +10378,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>3131 NE 21ST AVE</t>
+          <t>3131 NE 21ST AVE, LIGHTHOUSE POINT, FL 33064</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202511041416145593, "created_at": "2025-11-05T16:49:00", "customer_email": "peter.moss@outlook.com", "customer_id": 202511041416146883, "customer_name": "Peter Moss", "customer_type": "individual", "delivered_at": null, "due_amount": 300.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0188J\nZONE: AE\nELEV: 07 FT\nZONE: X500\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000274003, "paid": false, "property_address": "3131 NE 21ST AVE", "property_city": "LIGHTHOUSE POINT", "property_county": "BROWARD COUNTY", "property_lat": "26.2706639", "property_lng": "-80.0950659", "property_state": "FL", "property_zip": "33064", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274003", "customer_email": "peter.moss@outlook.com", "service_type": "Land Survey Only", "county": "", "property_address": "3131 NE 21ST AVE", "customer_name": "Peter Moss"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Peter Moss", "confidence": "HIGH"}, "client_email": {"value": "peter.moss@outlook.com", "confidence": "HIGH"}, "property_address": {"value": "3131 NE 21ST AVE, LIGHTHOUSE POINT, FL 33064", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as Land Survey Only; no elevation certificate requested"}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); flood zone data present \u2014 AE zone at 7 ft elevation and X500 zone, effective 07/31/2024", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser unavailable", "Legal description missing", "Structure square footage unknown", "Property features unknown (pool, shed, fence, driveway, etc.)", "Order is On Hold \u2014 reason for hold not specified, needs human review", "Invoice not yet sent and order not paid \u2014 billing status needs follow-up", "No fieldwork or delivery date scheduled"], "summary": "Residential land survey order for Peter Moss at 3131 NE 21ST AVE, Lighthouse Point, FL (Broward County), currently on hold with special pricing applied and a $300 balance due."}}</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:57:12.725096+00:00</t>
         </is>
       </c>
       <c r="T165" t="inlineStr">
@@ -10325,7 +10398,7 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:18.128921+00:00</t>
+          <t>2026-06-02T17:57:12.775366+00:00</t>
         </is>
       </c>
     </row>
@@ -10337,7 +10410,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10352,12 +10425,22 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>CARLA  QUIGLEY</t>
+          <t>CARLA QUIGLEY</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>1198 INDIAN RIVER DR</t>
+          <t>1198 INDIAN RIVER DR, COCOA, FL 32922</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202511031743205660, "created_at": "2025-11-03T15:48:05", "customer_email": "cquigley@bellsouth.net", "customer_id": 202511031743206718, "customer_name": "CARLA  QUIGLEY", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12009C0340H\nZONE: AE\nELEV: 04 FT\nEFF: 01/29/2021", "invoiced": false, "order_id": 1000273967, "paid": false, "property_address": "1198 INDIAN RIVER DR", "property_city": "COCOA", "property_county": "Brevard County", "property_lat": "28.3802697", "property_lng": "-80.7352536", "property_state": "FL", "property_zip": "32922", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273967", "customer_email": "cquigley@bellsouth.net", "service_type": "Land Survey Only", "county": "", "property_address": "1198 INDIAN RIVER DR", "customer_name": "CARLA  QUIGLEY"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "CARLA QUIGLEY", "confidence": "HIGH"}, "client_email": {"value": "cquigley@bellsouth.net", "confidence": "HIGH"}, "property_address": {"value": "1198 INDIAN RIVER DR, COCOA, FL 32922", "confidence": "HIGH"}, "property_county": {"value": "Brevard County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing applied. Order is On Hold (status code 11). Property is in FEMA Flood Zone AE with base flood elevation 4 FT (FIRM panel 12009C0340H, effective 01/29/2021).", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or aerial data provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, structures, etc.) unknown \u2014 no appraiser or aerial data", "Order is On Hold \u2014 reason for hold not specified, needs human review", "Special pricing flag is true \u2014 pricing details or authorization not documented", "No fieldwork or delivery dates scheduled", "No matching emails found \u2014 no additional client communication available"], "summary": "Residential land survey order for Carla Quigley at 1198 Indian River Dr, Cocoa, FL (Brevard County), currently On Hold with special pricing applied and the property located in FEMA Flood Zone AE."}}</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:57:23.218739+00:00</t>
         </is>
       </c>
       <c r="T166" t="inlineStr">
@@ -10367,7 +10450,7 @@
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:18.193976+00:00</t>
+          <t>2026-06-02T17:57:23.269439+00:00</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10462,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10399,7 +10482,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>321 SW 24TH RD</t>
+          <t>321 SW 24TH RD, MIAMI, FL 33129</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202511031731320494, "created_at": "2025-11-03T12:42:01", "customer_email": "BinduRamm@gmail.com", "customer_id": 202511031731321742, "customer_name": "Bindu Rammohan", "customer_type": "individual", "delivered_at": "2025-11-03T17:42:15", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": null, "invoiced": false, "order_id": 1000273966, "paid": false, "property_address": "321 SW 24TH RD", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.7572867", "property_lng": "-80.206683", "property_state": "FL", "property_zip": "33129", "service_type": "Quote, CAD file", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273966", "customer_email": "BinduRamm@gmail.com", "service_type": "Quote, CAD file", "county": "", "property_address": "321 SW 24TH RD", "customer_name": "Bindu Rammohan"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Bindu Rammohan", "confidence": "HIGH"}, "client_email": {"value": "BinduRamm@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "321 SW 24TH RD, MIAMI, FL 33129", "confidence": "HIGH"}, "property_county": {"value": "MIAMI-DADE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Quote", "CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'Quote, CAD file' in order data."}, "special_requirements": {"value": "Special pricing applied to this order.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial imagery, or email attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, driveways, etc.) unknown \u2014 no appraiser or aerial data available", "No matching emails found to supplement order details", "Scope of CAD file not clarified (boundary, topo, as-built, etc.)", "No fieldwork date scheduled", "Invoice amount not set (due_amount: 0.00, invoiced: false)", "Flood zone not determined"], "summary": "Individual residential client Bindu Rammohan has requested a quote and CAD file for a property at 321 SW 24TH RD, Miami, FL 33129 (Miami-Dade County), with special pricing applied, but key property details and scope specifics are missing."}}</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:57:33.065198+00:00</t>
         </is>
       </c>
       <c r="T167" t="inlineStr">
@@ -10409,7 +10502,7 @@
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:18.259420+00:00</t>
+          <t>2026-06-02T17:57:33.116144+00:00</t>
         </is>
       </c>
     </row>
@@ -10421,7 +10514,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10441,7 +10534,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>465 SAVOIE DR</t>
+          <t>465 Savoie Dr, Palm Beach Gardens, FL 33410</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510302059225948, "created_at": "2025-10-31T09:14:05", "customer_email": "maryannroberts@rogers.com", "customer_id": 202510302059226265, "customer_name": "Mary Ann Roberts", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0377G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000273870, "paid": false, "property_address": "465 SAVOIE DR", "property_city": "PALM BEACH GARDENS", "property_county": "Palm Beach County", "property_lat": "26.8657004", "property_lng": "-80.0808679", "property_state": "FLORIDA", "property_zip": "33410", "service_type": "Quote", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273870", "customer_email": "maryannroberts@rogers.com", "service_type": "Quote", "county": "", "property_address": "465 SAVOIE DR", "customer_name": "Mary Ann Roberts"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Mary Ann Roberts", "confidence": "HIGH"}, "client_email": {"value": "maryannroberts@rogers.com", "confidence": "HIGH"}, "property_address": {"value": "465 Savoie Dr, Palm Beach Gardens, FL 33410", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey type identified. Needs clarification on what survey product is being requested."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available; no emails or attachments to reference. Pool, shed, driveways, and other features unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not identified \u2014 'Quote' is not a survey product", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, etc.)", "No matching emails found \u2014 no additional context from client", "Special requirements or scope notes not provided", "Order is On Hold \u2014 reason for hold not specified", "Elevation certificate not requested but flood zone is present (Zone X) \u2014 may be worth confirming with client"], "summary": "Individual residential client Mary Ann Roberts has requested a quote for a property at 465 Savoie Dr, Palm Beach Gardens, FL 33410 (Palm Beach County), but no specific survey service type has been identified and the order is currently on hold with significant data gaps."}}</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:57:42.878672+00:00</t>
         </is>
       </c>
       <c r="T168" t="inlineStr">
@@ -10451,7 +10554,7 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:18.326413+00:00</t>
+          <t>2026-06-02T17:57:42.930256+00:00</t>
         </is>
       </c>
     </row>
@@ -10463,7 +10566,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10483,7 +10586,17 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>1607 LAKE DOWNEY DR #25</t>
+          <t>1607 Lake Downey Dr #25, Orlando, FL 32825</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510301444567148, "created_at": "2025-10-30T11:30:01", "customer_email": "josephplatten9@gmail.com", "customer_id": 202510301444567473, "customer_name": "Joseph Platten", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12095C0280F\nZONE: X\nEFF: 09/25/2009", "invoiced": false, "order_id": 1000273827, "paid": false, "property_address": "1607 LAKE DOWNEY DR #25", "property_city": "ORLANDO", "property_county": "ORANGE COUNTY", "property_lat": "28.566124", "property_lng": "-81.238905", "property_state": "FLORIDA", "property_zip": "32825", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273827", "customer_email": "josephplatten9@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "1607 LAKE DOWNEY DR #25", "customer_name": "Joseph Platten"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Joseph Platten", "confidence": "HIGH"}, "client_email": {"value": "josephplatten9@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1607 Lake Downey Dr #25, Orlando, FL 32825", "confidence": "HIGH"}, "property_county": {"value": "Orange County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data. No elevation certificate requested."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Order is currently On Hold \u2014 reason for hold not specified", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 no appraiser or document data available", "Structure square footage unknown", "Property features unknown (pool, shed, fences, etc.)", "Special requirements or client notes not provided", "Urgency/timeline not specified", "Unit #25 suggests condominium or multi-unit complex \u2014 lot/parcel boundaries may differ from standard residential; needs clarification", "No pricing or invoice details established (due amount is $0, not yet invoiced)"], "summary": "Individual residential client Joseph Platten has a Land Survey Only order on hold for a unit property at 1607 Lake Downey Dr #25, Orlando, FL (Orange County), with no pricing, lot data, or legal description yet established."}}</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:57:53.262292+00:00</t>
         </is>
       </c>
       <c r="T169" t="inlineStr">
@@ -10493,7 +10606,7 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:18.391842+00:00</t>
+          <t>2026-06-02T17:57:53.312904+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -9110,7 +9110,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9133,16 +9133,37 @@
           <t>4425 Hickory Dr, Palm Beach Gardens, FL 33418</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>{"total_amount": 537.0, "services": [{"name": "Land Survey - Boundary Survey", "description": "Residential boundary/land survey for Lot 20, Block 9, PGA National Golf Club Estates, Palm Beach Gardens. Standard platted lot with defined legal description from recorded plat (Plat Book 27, Page 206). Individual client base rate applied.", "amount": 475.0}, {"name": "Lot Size Complexity Upcharge (0.31\u20130.50 ac)", "description": "Parcel is 0.32 acres, falling within the 0.31\u20130.50 ac tier, warranting a modest upcharge for additional field time and corner recovery on a slightly larger-than-standard residential lot.", "amount": 62.0}], "pricing_reasoning": "Service is a standard residential boundary/land survey only \u2014 no Elevation Certificate requested, and the FEMA zone is X (minimal flood hazard), so no EC line item is warranted. The individual client base rate of $475.00 applies per guidelines. The lot at 0.32 acres falls in the 0.31\u20130.50 ac complexity tier, supporting a $62.00 upcharge; no other complexity factors (pool, waterfront, metes-and-bounds description, heavy vegetation, Monroe County) are indicated \u2014 the legal description references a straightforward platted subdivision lot with no metes-and-bounds language.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["Order notes indicate job was previously on hold with no fieldwork scheduled and estimate unsent \u2014 confirm current status before dispatching field crew.", "Certification is to 'JENNIFER' (individual homeowner) \u2014 verify full name spelling for certificate prior to delivery."]}</t>
+        </is>
+      </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202512091810542329, "created_at": "2025-12-11T16:27:03", "customer_email": "santiagoandjade@gmail.com", "customer_id": 202512091810542550, "customer_name": "Jennifer", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0378F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000275758, "paid": false, "property_address": "4425 HICKORY DR", "property_city": "PALM BEACH GARDENS", "property_county": "PALM BEACH COUNTY", "property_lat": "26.8358163", "property_lng": "-80.1121611", "property_state": "FLORIDA", "property_zip": "33418", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275758", "customer_email": "santiagoandjade@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "4425 HICKORY DR", "customer_name": "Jennifer"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Jennifer", "confidence": "HIGH"}, "client_email": {"value": "santiagoandjade@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "4425 Hickory Dr, Palm Beach Gardens, FL 33418", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in FTF order data"}, "special_requirements": {"value": "None noted", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no matching emails or attachments found"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Last name for client 'Jennifer' \u2014 email domain suggests possible last name 'Santiago' or shared account", "Lot size not available \u2014 county appraiser data unavailable", "Legal description not available \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, etc.)", "Order is currently On Hold \u2014 reason for hold not specified", "No fieldwork date scheduled", "No invoice or payment information present", "No estimate has been sent to client"], "summary": "Residential land survey order for Jennifer at 4425 Hickory Dr, Palm Beach Gardens FL 33418 (Palm Beach County), currently on hold with no fieldwork scheduled, estimate unsent, and property details such as lot size and legal description unavailable."}}</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1780423153062</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>2026-06-02T17:27:24.105173+00:00</t>
         </is>
       </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:01:19.744899+00:00</t>
+        </is>
+      </c>
+      <c r="R141" t="n">
+        <v>537</v>
+      </c>
       <c r="T141" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:16.496741+00:00</t>
@@ -9150,7 +9171,7 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>2026-06-02T17:27:24.152430+00:00</t>
+          <t>2026-06-02T18:01:19.798788+00:00</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9183,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9185,16 +9206,37 @@
           <t>13179 S Indian River Dr, Jensen Beach, FL 34957</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>{"total_amount": 850.0, "services": [{"name": "Land Survey", "description": "Boundary/land survey at 13179 S Indian River Dr, Jensen Beach, FL \u2014 negotiated base rate for Lawrence Lee Construction Services, Inc.", "amount": 300.0}, {"name": "Lot Size Complexity Upcharge (2.01\u20135.00 ac)", "description": "Property is 3.46 acres, falling within the 2.01\u20135.00 ac complexity tier. Larger parcels require extended field time, additional monumentation search, and increased traverse distance.", "amount": 550.0}], "pricing_reasoning": "The negotiated base rate of $300.00 is applied per management agreement for Lawrence Lee Construction Services. No EC was requested and FEMA Zone X requires no flood-related upcharge. The 3.46-acre lot triggers the 2.01\u20135.00 ac complexity upcharge of $550.00; the metes-and-bounds legal description referencing Indian River mean high water line adds inherent field complexity that is already captured within the acreage upcharge tier rather than stacked separately, as the waterfront/riparian boundary is a function of the large irregular parcel rather than a separate canal feature. No additional Monroe County, pool, or vegetation upcharges are supported by available data.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_ORDER: Order 1000272589 covers the same address (13179 S Indian River Dr, St. Lucie County) and same Folio (4509-120-0009-000-6) with services Land Survey Only + Topography Survey. Human review required to confirm this is a separate deliverable and not a re-invoice of the same field visit.", "RIPARIAN_BOUNDARY: Legal description ties to Indian River mean high water line \u2014 field crew should confirm current MHW location; this may require additional time if line is disputed or requires GPS-grade delineation.", "B2B_ORDER_NOTE: Order notes indicate survey was already delivered but not yet invoiced \u2014 verify field notes and any change orders before finalizing invoice.", "CLIENT_FIRST_ORDER: Order count is 0 for Lawrence Lee Construction Services despite OLD_TITLE tier designation \u2014 confirm client tier and negotiated rate with management before invoicing."]}</t>
+        </is>
+      </c>
       <c r="H142" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202512091630395030, "created_at": "2025-12-09T11:32:00", "customer_email": "AC@LawrenceLeeConstruction.com", "customer_id": 202512091631053684, "customer_name": "Ariana  Cammuse", "customer_type": "b2b", "delivered_at": "2025-12-11T17:57:18", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12111C0313K\nZONE: X\nEFF: 02/19/2020", "invoiced": false, "order_id": 1000275742, "paid": false, "property_address": "13179 S INDIAN RIVER DR", "property_city": "JENSEN BEACH", "property_county": "St. Lucie County", "property_lat": "27.2751283", "property_lng": "-80.2417656", "property_state": "FL", "property_zip": "34957", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275742", "customer_email": "AC@LawrenceLeeConstruction.com", "service_type": "Land Survey Only", "county": "", "property_address": "13179 S INDIAN RIVER DR", "customer_name": "Lawrence Lee Construction Services, Inc."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Lawrence Lee Construction Services, Inc.", "confidence": "HIGH"}, "client_email": {"value": "AC@LawrenceLeeConstruction.com", "confidence": "HIGH"}, "property_address": {"value": "13179 S Indian River Dr, Jensen Beach, FL 34957", "confidence": "HIGH"}, "property_county": {"value": "St. Lucie County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested (elevation_cert: false)"}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial imagery, or email attachments provided. Property is on S Indian River Dr which may suggest waterfront/riparian features \u2014 needs field verification."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided \u2014 needs appraiser lookup or field measurement", "Legal description not available \u2014 St. Lucie County appraiser lookup needed", "Structure square footage unknown", "Property features (structures, pool, shed, fencing, driveways) not documented", "No matching emails found \u2014 scope confirmation from client may be needed", "Invoice has not been sent and order is unpaid \u2014 billing action required", "Fieldwork date not scheduled (fieldwork_at: null)", "County field was blank in order root object despite being populated in data object \u2014 verify data consistency"], "summary": "B2B land survey order for Lawrence Lee Construction Services at 13179 S Indian River Dr, Jensen Beach, FL (St. Lucie County), delivered but not yet invoiced, with special pricing applied and no elevation certificate requested."}}</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1780423301055</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>2026-06-02T17:27:35.109865+00:00</t>
         </is>
       </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:01:44.017585+00:00</t>
+        </is>
+      </c>
+      <c r="R142" t="n">
+        <v>850</v>
+      </c>
       <c r="T142" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:16.555277+00:00</t>
@@ -9202,7 +9244,7 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>2026-06-02T17:27:35.156255+00:00</t>
+          <t>2026-06-02T18:01:44.077134+00:00</t>
         </is>
       </c>
     </row>
@@ -9214,7 +9256,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9237,16 +9279,37 @@
           <t>525 36TH AVE NE, ST. PETERSBURG, FL 33704</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>{"total_amount": 475.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for 525 36TH AVE NE, St. Petersburg, FL 33704 \u2014 Pinellas County. Legal description references portions of two lots (East 36 ft of Lot 9 and West 36 ft of Lot 10, Block 17, Snell and Hamlett's Coffee Pot Bayou Addition, Plat Book 3, Page 55). Lot size 0.21 acres. Individual client, no negotiated rate. Base rate applied.", "amount": 475.0}], "pricing_reasoning": "Service requested is Land Survey Only for an individual homeowner (Loreli Brobst) with no negotiated rate on file, so the $475.00 individual base rate applies. The lot is 0.21 acres, which falls below the 0.31-acre threshold for a lot-size upcharge. The legal description splits two platted lots by equal frontage (36 ft each from Lot 9 and Lot 10), which is a common configuration in this St. Petersburg subdivision and does not rise to the complexity level of a metes-and-bounds description requiring the $100 upcharge \u2014 it remains a platted-lot survey referencing a recorded plat. No EC was requested, no pool or waterfront canal evidence was flagged in the order data, and the property is not in Monroe County. FEMA Zone AE at 10 ft elevation is noted but no Elevation Certificate was ordered, so no EC line item or VE surcharge applies.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000271795 \u2014 same property (525 36TH AVE NE, Pinellas County), same Folio 173107169290170090, same service (Land Survey Only). Human review required to confirm this is not a duplicate charge or re-order of an already-completed survey.", "DUPLICATE_WARNING: Order 1000280029 \u2014 same property (525 36TH AVE NE, Pinellas County), same Folio 173107169290170090, service is Elevation Certificate. If client later needs an EC, pricing should be combined with this survey for potential field efficiency.", "DUPLICATE_WARNING: Order 1000282060 \u2014 same property (525 36TH AVE NE, Pinellas County), same Folio 173107169290170090, service is Quote. Possible quote-to-order conversion scenario; review for double-billing risk.", "NOTE: Order notes indicate this order has already been delivered and paid. Confirm whether this invoice is being generated retroactively for records or whether a new field visit is required."]}</t>
+        </is>
+      </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202509191452179486, "created_at": "2025-12-09T11:00:02", "customer_email": "lorelib@gcihomesinc.com", "customer_id": 202509191452179607, "customer_name": "Loreli Brobst", "customer_type": "individual", "delivered_at": "2025-12-09T18:20:16", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12103C0217H\nZONE: AE\nELEV: 10 FT\nEFF: 08/24/2021", "invoiced": false, "order_id": 1000275732, "paid": true, "property_address": "525 36TH AVE NE", "property_city": "ST. PETERSBURG", "property_county": "PINELLAS COUNTY", "property_lat": "27.8051659", "property_lng": "-82.6282341", "property_state": "FL", "property_zip": "33704", "service_type": "Land Survey Only", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275732", "customer_email": "lorelib@gcihomesinc.com", "service_type": "Land Survey Only", "county": "", "property_address": "525 36TH AVE NE", "customer_name": "Loreli Brobst"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Loreli Brobst", "confidence": "HIGH"}, "client_email": {"value": "lorelib@gcihomesinc.com", "confidence": "HIGH"}, "property_address": {"value": "525 36TH AVE NE, ST. PETERSBURG, FL 33704", "confidence": "HIGH"}, "property_county": {"value": "Pinellas County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested (elevation_cert: false)"}, "special_requirements": {"value": "Property is in FEMA Flood Zone AE (Panel 12103C0217H, effective 08/24/2021, BFE 10 ft). No elevation certificate ordered.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features provided; county appraiser data unavailable and no emails or attachments present"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM", "notes": "Customer type listed as 'individual' but email domain gcihomesinc.com suggests a real estate or home services business affiliation; warrants verification"}, "urgency": {"value": "normal", "confidence": "MEDIUM", "notes": "No rush indicators present; order was created and delivered same day (2025-12-09) but no explicit rush flag"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, fencing, driveways, etc.) unknown \u2014 no appraiser data or aerial available", "Client tier ambiguous \u2014 email domain (gcihomesinc.com) suggests possible business/B2B relationship despite 'individual' customer type; needs human verification", "No matching emails found \u2014 no additional context from client communications", "Fieldwork date is null \u2014 unclear if fieldwork has been scheduled or completed", "Invoice not yet generated (invoiced: false) despite order being delivered and paid"], "summary": "A delivered and paid Land Survey Only order for Loreli Brobst at 525 36th Ave NE, St. Petersburg, FL 33704 (Pinellas County), located in FEMA Flood Zone AE, with no elevation certificate requested and several property detail gaps requiring human input."}}</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>1780423325860</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>2026-06-02T17:27:47.648363+00:00</t>
         </is>
       </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:02:06.581541+00:00</t>
+        </is>
+      </c>
+      <c r="R143" t="n">
+        <v>475</v>
+      </c>
       <c r="T143" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:16.614876+00:00</t>
@@ -9254,7 +9317,7 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>2026-06-02T17:27:47.696193+00:00</t>
+          <t>2026-06-02T18:02:06.636271+00:00</t>
         </is>
       </c>
     </row>
@@ -10618,7 +10681,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10638,7 +10701,17 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>1211 FL-436</t>
+          <t>1211 FL-436, Casselberry, FL 32707</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510301338499780, "created_at": "2025-10-30T09:41:01", "customer_email": "miguel.rojas@foundrycommercial.com", "customer_id": 202510301338500888, "customer_name": "Miguel Rojas", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12117C0165F\nZONE: X\nEFF: 09/28/2007", "invoiced": false, "order_id": 1000273817, "paid": true, "property_address": "1211 FL-436", "property_city": "CASSELBERRY", "property_county": "Seminole County", "property_lat": "28.6372143", "property_lng": "-81.32304359999999", "property_state": "FL", "property_zip": "32707", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273817", "customer_email": "miguel.rojas@foundrycommercial.com", "service_type": "CAD file", "county": "", "property_address": "1211 FL-436", "customer_name": "Miguel Rojas"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Miguel Rojas", "confidence": "HIGH"}, "client_email": {"value": "miguel.rojas@foundrycommercial.com", "confidence": "HIGH"}, "property_address": {"value": "1211 FL-436, Casselberry, FL 32707", "confidence": "HIGH"}, "property_county": {"value": "Seminole County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Only service listed is CAD file; no additional services specified in order data"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM", "notes": "Email domain foundrycommercial.com suggests a commercial real estate firm; customer_type is listed as individual but business context is evident"}, "urgency": {"value": "unknown", "confidence": "LOW", "notes": "Order is On Hold with no fieldwork or delivery dates set; cannot determine urgency"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, structures, etc.) unknown \u2014 no appraiser data or emails available", "Reason for On Hold status unknown", "Scope of CAD file request unclear (boundary, topo, as-built, etc.)", "No fieldwork date scheduled", "Client tier ambiguous \u2014 listed as individual but email suggests commercial entity", "No matching emails found to clarify requirements or context"], "summary": "B2B client Miguel Rojas of Foundry Commercial is requesting a CAD file for a commercial property at 1211 FL-436 in Casselberry, FL (Seminole County), with special pricing applied, but the order is currently On Hold with no fieldwork scheduled and limited property detail available."}}</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:00:22.970694+00:00</t>
         </is>
       </c>
       <c r="T170" t="inlineStr">
@@ -10648,7 +10721,7 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:18.458219+00:00</t>
+          <t>2026-06-02T18:00:23.025482+00:00</t>
         </is>
       </c>
     </row>
@@ -10660,7 +10733,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10680,7 +10753,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>922 TURNER RD</t>
+          <t>922 Turner Rd, Delray Beach, FL 33483</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202504081537437301, "created_at": "2025-10-27T14:24:03", "customer_email": "benallen2013@gmail.com", "customer_id": 202504081537437404, "customer_name": "Benjamin Allen", "customer_type": "individual", "delivered_at": "2025-12-09T15:36:12", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0981G\nZONE: AE\nELEV: 08 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000273647, "paid": true, "property_address": "922 TURNER RD", "property_city": "DELRAY BEACH", "property_county": "Palm Beach County", "property_lat": "26.4961436", "property_lng": "-80.0595089", "property_state": "FL", "property_zip": "33483", "service_type": "CAD file", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273647", "customer_email": "benallen2013@gmail.com", "service_type": "CAD file", "county": "", "property_address": "922 TURNER RD", "customer_name": "Benjamin Allen"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Benjamin Allen", "confidence": "HIGH"}, "client_email": {"value": "benallen2013@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "922 Turner Rd, Delray Beach, FL 33483", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file' in order data. No additional services indicated."}, "special_requirements": {"value": "Special pricing applied. Flood zone AE, FIRM panel 12099C0981G, base flood elevation 8 ft, effective 12/20/2024.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 no appraiser data, no matching emails, and no aerial data provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, outbuildings, etc.)", "No county appraiser data available", "No matching emails found for additional context", "Fieldwork date not recorded (fieldwork_at is null)", "Invoice has not been generated (invoiced: false) despite order being delivered and paid"], "summary": "Individual residential client Benjamin Allen ordered a CAD file for 922 Turner Rd, Delray Beach, FL (Palm Beach County), located in Flood Zone AE; order is delivered and paid with special pricing applied, but property details and invoice are still outstanding."}}</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:00:32.708157+00:00</t>
         </is>
       </c>
       <c r="T171" t="inlineStr">
@@ -10690,7 +10773,7 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:18.524797+00:00</t>
+          <t>2026-06-02T18:00:32.763491+00:00</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10785,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10722,7 +10805,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>35135 PINEGATE TRAIL</t>
+          <t>35135 Pinegate Trail, Eustis, FL 32736</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510271424299774, "created_at": "2025-10-27T10:26:04", "customer_email": "Taylor@fivediamondfl.com", "customer_id": 202510271424301128, "customer_name": "Taylor McCook", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12069C0385E\nZONE: X\nEFF: 12/18/2012", "invoiced": false, "order_id": 1000273608, "paid": true, "property_address": "35135 PINEGATE TRAIL", "property_city": "EUSTIS", "property_county": "Lake County", "property_lat": "28.853566", "property_lng": "-81.560335", "property_state": "FL", "property_zip": "32736", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273608", "customer_email": "Taylor@fivediamondfl.com", "service_type": "CAD file", "county": "", "property_address": "35135 PINEGATE TRAIL", "customer_name": "Taylor McCook"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Taylor McCook", "confidence": "HIGH"}, "client_email": {"value": "Taylor@fivediamondfl.com", "confidence": "HIGH"}, "property_address": {"value": "35135 Pinegate Trail, Eustis, FL 32736", "confidence": "HIGH"}, "property_county": {"value": "Lake County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file' in order data. No additional services indicated."}, "special_requirements": {"value": "Special pricing applied; order currently on hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference."}, "client_tier": {"value": "b2b", "confidence": "MEDIUM", "notes": "Customer type is listed as 'individual' but email domain 'fivediamondfl.com' suggests a business entity (Five Diamond FL). Likely a business client using a business email."}, "urgency": {"value": "normal", "confidence": "MEDIUM", "notes": "No rush indicators present; order is on hold which suggests no urgency at this time."}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, etc.)", "Reason for 'On Hold' status not specified", "County appraiser data unavailable", "No matching emails found to supplement order details", "Client tier ambiguous \u2014 individual vs. business needs clarification", "Scope of CAD file request not detailed (boundary, topo, as-built, etc.)", "Fieldwork date not scheduled"], "summary": "Taylor McCook (possible business client via fivediamondfl.com) has a CAD file order for 35135 Pinegate Trail, Eustis, FL (Lake County) that is currently on hold with special pricing applied and no fieldwork or delivery scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:00:43.647424+00:00</t>
         </is>
       </c>
       <c r="T172" t="inlineStr">
@@ -10732,7 +10825,7 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:18.638183+00:00</t>
+          <t>2026-06-02T18:00:43.702070+00:00</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10837,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10764,7 +10857,17 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>32 HAMPSHIRE LN</t>
+          <t>32 Hampshire Ln, Boynton Beach, FL 33436</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510231300016435, "created_at": "2025-10-23T17:32:04", "customer_email": "reggiemanning1@gmail.com", "customer_id": 202510231300016631, "customer_name": "Reggie Manning", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0976G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000273465, "paid": false, "property_address": "32 HAMPSHIRE LN", "property_city": "BOYNTON BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.4979025", "property_lng": "-80.1047184", "property_state": "FLORIDA", "property_zip": "33436", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273465", "customer_email": "reggiemanning1@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "32 HAMPSHIRE LN", "customer_name": "Reggie Manning"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Reggie Manning", "confidence": "HIGH"}, "client_email": {"value": "reggiemanning1@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "32 Hampshire Ln, Boynton Beach, FL 33436", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in FTF order data. No elevation certificate requested."}, "special_requirements": {"value": "None noted", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 no appraiser data, no emails, no aerial imagery referenced. Site visit or appraiser lookup needed."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing \u2014 no appraiser lookup performed", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) not identified", "Order is currently On Hold \u2014 reason for hold not specified", "No fieldwork date scheduled", "No invoice sent and no payment collected", "No matching emails found to clarify scope or special instructions"], "summary": "Residential land survey order for Reggie Manning at 32 Hampshire Ln, Boynton Beach FL 33436 (Palm Beach County), currently on hold with no fieldwork scheduled, pricing, or property detail data available."}}</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:00:52.626325+00:00</t>
         </is>
       </c>
       <c r="T173" t="inlineStr">
@@ -10774,7 +10877,7 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:18.705053+00:00</t>
+          <t>2026-06-02T18:00:52.681362+00:00</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10889,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10801,12 +10904,22 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johanne Beaumont </t>
+          <t>Johanne Beaumont</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>152 WOODBRIDGE CIR</t>
+          <t>152 Woodbridge Cir, Daytona Beach, FL 32119</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510211448162837, "created_at": "2025-10-21T11:11:01", "customer_email": "bacall40@hotmail.com", "customer_id": 202510211448162936, "customer_name": "Johanne Beaumont", "customer_type": "individual", "delivered_at": null, "due_amount": 475.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12127C0366H\nZONE: X\nEFF: 02/19/2014", "invoiced": false, "order_id": 1000273343, "paid": false, "property_address": "152 WOODBRIDGE CIR", "property_city": "DAYTONA BEACH", "property_county": "Volusia County", "property_lat": "29.1619689", "property_lng": "-81.0390599", "property_state": "FLORIDA", "property_zip": "32119", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273343", "customer_email": "bacall40@hotmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "152 WOODBRIDGE CIR", "customer_name": "Johanne Beaumont "}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Johanne Beaumont", "confidence": "HIGH"}, "client_email": {"value": "bacall40@hotmail.com", "confidence": "HIGH"}, "property_address": {"value": "152 Woodbridge Cir, Daytona Beach, FL 32119", "confidence": "HIGH"}, "property_county": {"value": "Volusia County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in FTF order data; no elevation certificate required per elevation_cert flag."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no emails or attachments to reference."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser unavailable", "Legal description missing \u2014 no appraiser data or supporting documents", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) unknown", "Special requirements or access instructions not provided", "Order is currently On Hold \u2014 reason for hold not stated", "No customer profile data returned from FTF customer lookup", "No matching emails found to supplement order details"], "summary": "Residential land survey only order for Johanne Beaumont at 152 Woodbridge Cir, Daytona Beach, FL (Volusia County), currently on hold with a $475 balance due and no delivery or fieldwork dates scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:01:01.624011+00:00</t>
         </is>
       </c>
       <c r="T174" t="inlineStr">
@@ -10816,7 +10929,7 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:18.772653+00:00</t>
+          <t>2026-06-02T18:01:01.678699+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -9329,7 +9329,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9352,16 +9352,37 @@
           <t>704 E Tangerine Ct, Winter Garden, FL 34787</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>{"total_amount": 562.0, "services": [{"name": "Land Survey", "description": "Boundary/Land Survey for LOT 52, VALENCIA SHORES, Plat Book 4, Page 65, Orange County. Negotiated base rate agreed upon by management for this individual client.", "amount": 500.0}, {"name": "Lot Size Complexity Upcharge (0.31\u20130.50 ac)", "description": "Property is 0.44 acres, falling within the 0.31\u20130.50 ac complexity tier. Upcharge applied per standard pricing guidelines.", "amount": 62.0}], "pricing_reasoning": "The client has a management-agreed negotiated base rate of $500.00, which is used as the survey base. The lot is 0.44 acres, placing it in the 0.31\u20130.50 ac complexity tier warranting a $62.00 upcharge. No EC is required (FEMA Zone X, not AE or VE), no pool, waterfront, metes-and-bounds, or heavy vegetation indicators are present in the legal description or county data, and the property is in Orange County (no Monroe mobilization fee). No topo service was requested.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE DUPLICATE: Order 1000268742 references the same address (704 Tangerine CT, Orange County), same coordinates (28.5667263, -81.5986605), and same Folio/MLS (27-22-15-8842-00-520) for an identical service (Land Survey Only). Human review recommended before dispatching field crew to avoid duplicate field work and billing.", "Order notes indicate this order was marked as paid with special pricing applied and was missing lot size, legal description, and property feature details at time of entry. Lot size and legal description have since been populated; however, property feature details (pool, waterfront, vegetation) remain unconfirmed from appraiser data \u2014 pricing assumes standard residential features based on available data."]}</t>
+        </is>
+      </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202512091540398631, "created_at": "2025-12-09T10:42:01", "customer_email": "allan@lrgconstruction.com", "customer_id": 202512091540399657, "customer_name": "Allan Lougheed", "customer_type": "individual", "delivered_at": "2025-12-09T18:19:28", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12095C0205H\nZONE: X\nEFF: 09/24/2021", "invoiced": false, "order_id": 1000275730, "paid": true, "property_address": "704 E TANGERINE CT", "property_city": "WINTER GARDEN", "property_county": "Orange County", "property_lat": "28.5667263", "property_lng": "-81.5986605", "property_state": "FL", "property_zip": "34787", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275730", "customer_email": "allan@lrgconstruction.com", "service_type": "Land Survey Only", "county": "", "property_address": "704 E TANGERINE CT", "customer_name": "Allan Lougheed"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Allan Lougheed", "confidence": "HIGH"}, "client_email": {"value": "allan@lrgconstruction.com", "confidence": "HIGH"}, "property_address": {"value": "704 E Tangerine Ct, Winter Garden, FL 34787", "confidence": "HIGH"}, "property_county": {"value": "Orange County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property feature data available; no appraiser data, aerial imagery, or email context provided"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fences, driveways, etc.)", "No matching emails found \u2014 unable to confirm scope or special instructions from client communication", "Reason for special pricing not documented", "Fieldwork date not yet scheduled (fieldwork_at is null)", "Customer type listed as 'individual' but email domain suggests a construction company (lrgconstruction.com) \u2014 client tier should be verified"], "summary": "Delivered land survey order for Allan Lougheed at 704 E Tangerine Ct, Winter Garden, FL (Orange County), marked as paid with special pricing applied, but missing lot size, legal description, and property feature details due to unavailable appraiser data."}}</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1780423641732</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>2026-06-02T17:27:57.570692+00:00</t>
         </is>
       </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:07:23.072112+00:00</t>
+        </is>
+      </c>
+      <c r="R144" t="n">
+        <v>562</v>
+      </c>
       <c r="T144" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:16.673964+00:00</t>
@@ -9369,7 +9390,7 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>2026-06-02T17:27:57.618434+00:00</t>
+          <t>2026-06-02T18:07:23.123431+00:00</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9402,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9404,16 +9425,37 @@
           <t>1773 Gallop Dr, Loxahatchee, FL 33470</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>{"total_amount": 1025.0, "services": [{"name": "Land Survey Only", "description": "Residential boundary survey for Lot 8, Block K, Fox Trail, Palm Beach County. Platted lot with clean legal description \u2014 no metes and bounds complexity. Base rate for individual/direct client.", "amount": 475.0}, {"name": "Acreage Complexity Upcharge (2.01\u20135.00 ac)", "description": "Lot size recorded at 5.00 acres, which falls within the 2.01\u20135.00 ac complexity tier. Larger lot requires extended field time, more monument recovery, and increased perimeter traverse work. Upcharge applied at standard tier rate.", "amount": 550.0}], "pricing_reasoning": "Base rate of $475.00 applies per the individual client default. The 5.00-acre lot falls at the top of the 2.01\u20135.00 ac complexity tier, warranting the full $550.00 acreage upcharge for extended field effort and perimeter coverage. No EC was ordered, no pool or waterfront indicators present in the legal description or order notes, the legal description is a clean platted lot (no metes-and-bounds surcharge), and the property is in Palm Beach County (no Monroe County mobilization premium). FEMA Zone AE is noted but no Elevation Certificate was requested, so no EC line item is added.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE ALERT: Order 1000272398 \u2014 same address (1773 Gallop Dr, Palm Beach County), same service (Land Survey Only), same Folio 00404326010110080. This appears to be a near-identical repeat order. Human review recommended before invoicing to confirm this is not a duplicate billing event.", "DUPLICATE ALERT: Order 1000240852 \u2014 same address and Folio, service was Property Survey and Elevation. Prior combined order may have already captured field work; verify with operations whether a re-survey is genuinely required or if this order was created in error.", "LOT SIZE BOUNDARY NOTE: Lot is recorded at exactly 5.00 acres, which is the upper boundary of the 2.01\u20135.00 ac pricing tier. If field verification or county records show the parcel exceeds 5.00 acres, this order must be escalated per pricing guidelines.", "FEMA Zone AE present on panel 12099C0530F (eff. 10/05/2017). No Elevation Certificate requested in this order. If client requires EC at a later stage, standard EC fee of $275.00 applies separately."]}</t>
+        </is>
+      </c>
       <c r="H145" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510012004186441, "created_at": "2025-12-09T15:54:04", "customer_email": "Angeltgarcia28@gmail.com", "customer_id": 202510012004186572, "customer_name": "Angel   Garcia", "customer_type": "individual", "delivered_at": "2025-12-12T15:02:46", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0530F\nZONE: AE\nELEV: 17.1 FT\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000275722, "paid": false, "property_address": "1773 GALLOP DR", "property_city": "LOXAHATCHEE", "property_county": "PALM BEACH COUNTY", "property_lat": "26.7050813", "property_lng": "-80.3208568", "property_state": "FL", "property_zip": "33470", "service_type": "Land Survey Only", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275722", "customer_email": "Angeltgarcia28@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "1773 GALLOP DR", "customer_name": "Angel Garcia"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Angel Garcia", "confidence": "HIGH"}, "client_email": {"value": "Angeltgarcia28@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1773 Gallop Dr, Loxahatchee, FL 33470", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "None noted", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing \u2014 no appraiser or document source available", "Structure square footage unknown", "Property features (pool, shed, fences, structures) not confirmed", "No matching email history found to cross-reference order details", "Invoice not yet sent and order marked unpaid \u2014 billing action may be needed", "Fieldwork date is null \u2014 unclear if fieldwork was completed or skipped"], "summary": "Residential land survey only order for Angel Garcia at 1773 Gallop Dr, Loxahatchee, FL 33470 (Palm Beach County), delivered on 2025-12-12 but not yet invoiced or paid, with flood zone AE/X noted and no additional property details available."}}</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1780423664510</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>2026-06-02T17:33:53.901406+00:00</t>
         </is>
       </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:07:45.685005+00:00</t>
+        </is>
+      </c>
+      <c r="R145" t="n">
+        <v>1025</v>
+      </c>
       <c r="T145" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:16.733196+00:00</t>
@@ -9421,7 +9463,7 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>2026-06-02T17:33:53.951621+00:00</t>
+          <t>2026-06-02T18:07:45.790397+00:00</t>
         </is>
       </c>
     </row>
@@ -9433,7 +9475,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9456,16 +9498,37 @@
           <t>50044 Bermont Rd, Punta Gorda, FL 33982</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>{"total_amount": 1025.0, "services": [{"name": "Land Survey Only \u2013 Base Rate", "description": "Standard boundary survey base rate for individual/residential client (Kristen Dragon, no negotiated rate on file).", "amount": 475.0}, {"name": "Acreage Complexity Upcharge (2.01\u20135.00 ac)", "description": "Property is 4.97 acres per DB, falling within the 2.01\u20135.00 ac complexity tier. Larger rural parcels in Charlotte County require extended field time, additional monument searches, and greater traverse distances. Legal description confirms a metes-and-bounds aliquot-part subdivision tract (Golden Ranches), consistent with rural acreage fieldwork demands.", "amount": 550.0}], "pricing_reasoning": "This is a residential Land Survey Only order for a 4.97-acre rural parcel in Charlotte County (FEMA Zone X \u2014 no EC required). The individual client rate of $475.00 applies as the base. The lot falls squarely in the 2.01\u20135.00 ac acreage tier, warranting the +$550.00 complexity upcharge for extended field traverse, monument recovery, and rural mobilization. No pool, waterfront, heavy vegetation, or Monroe County factors are evidenced. No metes-and-bounds upcharge is added separately as the legal description is an aliquot-part subdivision description (N\u00bd of SW\u00bc of SW\u00bc of NW\u00bc), not a true metes-and-bounds description. FEMA Zone X requires no Elevation Certificate.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE DUPLICATE: Order 1000269357 is flagged as a likely duplicate \u2014 same property address (50044 Bermont Rd, Charlotte County), same coordinates (26.9457282, -81.6278863), same Folio/MLS (402728100007), and same service type (Land Survey Only). Human review is required before scheduling fieldwork to avoid duplicate field visits and billing.", "ORDER ON HOLD: No fieldwork has been scheduled per order notes. Pricing is provided for reference; do not release to field until hold is cleared and duplicate status is resolved.", "LOT SIZE NEAR TIER BOUNDARY: At 4.97 acres, this parcel is just under the 5.00-acre escalation threshold. If field conditions, revised lot size data, or deed research reveal the parcel exceeds 5.00 acres, this order must be escalated per pricing guidelines."]}</t>
+        </is>
+      </c>
       <c r="H146" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202508061638505520, "created_at": "2025-12-08T12:29:00", "customer_email": "krsdra50@gmail.com", "customer_id": 202508061638505619, "customer_name": "Kristen Dragon", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12015C0325G\nZONE: X\nEFF: 12/15/2022", "invoiced": false, "order_id": 1000275670, "paid": false, "property_address": "50044 BERMONT RD", "property_city": "PUNTA GORDA", "property_county": "Charlotte County", "property_lat": "26.9457282", "property_lng": "-81.6278863", "property_state": "FL", "property_zip": "33982", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275670", "customer_email": "krsdra50@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "50044 BERMONT RD", "customer_name": "Kristen Dragon"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Kristen Dragon", "confidence": "HIGH"}, "client_email": {"value": "krsdra50@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "50044 Bermont Rd, Punta Gorda, FL 33982", "confidence": "HIGH"}, "property_county": {"value": "Charlotte County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data; no additional services indicated."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available, no emails, and no aerial data provided. Property features are unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, outbuildings, fencing, driveways) unknown", "Special requirements or client notes not provided", "Order is currently 'On Hold' \u2014 reason for hold not specified", "No fieldwork date scheduled", "No invoice or payment information on file", "County field is blank in the outer FTF payload (though present in order data body \u2014 should be reconciled)"], "summary": "Individual residential client Kristen Dragon has placed a Land Survey Only order for a property at 50044 Bermont Rd, Punta Gorda, FL (Charlotte County), currently on hold with no fieldwork scheduled and limited property detail available."}}</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1780423685693</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>2026-06-02T17:34:03.164143+00:00</t>
         </is>
       </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:08:06.369253+00:00</t>
+        </is>
+      </c>
+      <c r="R146" t="n">
+        <v>1025</v>
+      </c>
       <c r="T146" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:16.792703+00:00</t>
@@ -9473,7 +9536,7 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>2026-06-02T17:34:03.216088+00:00</t>
+          <t>2026-06-02T18:08:06.421811+00:00</t>
         </is>
       </c>
     </row>
@@ -10941,7 +11004,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10961,7 +11024,17 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>624 SELKIRK ST</t>
+          <t>624 Selkirk St, West Palm Beach, FL 33405</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510161721226230, "created_at": "2025-10-16T18:29:01", "customer_email": "chefmbyrne@gmail.com", "customer_id": 202510161721226321, "customer_name": "Matthew Byrne", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0591G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000273161, "paid": false, "property_address": "624 SELKIRK ST", "property_city": "WEST PALM BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.6671637", "property_lng": "-80.0593823", "property_state": "FLORIDA", "property_zip": "33405", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273161", "customer_email": "chefmbyrne@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "624 SELKIRK ST", "customer_name": "Matthew Byrne"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Matthew Byrne", "confidence": "HIGH"}, "client_email": {"value": "chefmbyrne@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "624 Selkirk St, West Palm Beach, FL 33405", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data; no additional services indicated"}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial imagery, or email attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, outbuildings)", "Special requirements or client notes not provided", "Order is currently 'On Hold' \u2014 reason for hold not documented", "Invoice amount is $0.00 and order has not been invoiced \u2014 pricing needs to be set", "Fieldwork date not yet scheduled", "No matching emails found \u2014 no additional client communication on record", "County field blank in outer order object (inconsistent with property_county in data object \u2014 should be reconciled)"], "summary": "Residential land survey order for Matthew Byrne at 624 Selkirk St, West Palm Beach (Palm Beach County, FL 33405), currently on hold with no pricing, scheduled fieldwork, or property detail data available."}}</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:06:18.241357+00:00</t>
         </is>
       </c>
       <c r="T175" t="inlineStr">
@@ -10971,7 +11044,7 @@
       </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:18.840215+00:00</t>
+          <t>2026-06-02T18:06:18.294781+00:00</t>
         </is>
       </c>
     </row>
@@ -10983,7 +11056,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11003,7 +11076,17 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>753 NE 79TH ST</t>
+          <t>753 NE 79TH ST, MIAMI, FL 33138</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510151749087347, "created_at": "2025-10-16T18:23:03", "customer_email": "juanramos155@hotmail.com", "customer_id": 202510151749087705, "customer_name": "Juan Ramos", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0306L\nZONE: AE\nELEV: 08 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000273091, "paid": false, "property_address": "753 NE 79TH ST", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.8480525", "property_lng": "-80.180931", "property_state": "FLORIDA", "property_zip": "33138", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273091", "customer_email": "juanramos155@hotmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "753 NE 79TH ST", "customer_name": "Juan Ramos"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Juan Ramos", "confidence": "HIGH"}, "client_email": {"value": "juanramos155@hotmail.com", "confidence": "HIGH"}, "property_address": {"value": "753 NE 79TH ST, MIAMI, FL 33138", "confidence": "HIGH"}, "property_county": {"value": "MIAMI-DADE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Property is in FEMA Flood Zone AE (Panel 12086C0306L, effective 09/11/2009, base flood elevation 8 ft). Order is currently On Hold.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available and no emails or attachments to reference; pool, shed, driveways, and other features unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided \u2014 needs property appraiser lookup or manual research", "Legal description not provided \u2014 needs property appraiser lookup or manual research", "Structure square footage unknown \u2014 no appraiser data available", "Property features (pool, shed, fences, driveways, etc.) unknown \u2014 no aerial or appraiser data", "Order is On Hold \u2014 reason for hold not documented; needs human review", "No matching emails found \u2014 no additional client communication to reference", "Special pricing flag is false but no pricing or quote details are present", "Fieldwork and delivery dates not yet scheduled"], "summary": "Individual residential client Juan Ramos has ordered a Land Survey Only for 753 NE 79TH ST, Miami, FL 33138 (Miami-Dade County), located in FEMA Flood Zone AE; the order is currently On Hold with no fieldwork scheduled and key property details such as lot size, legal description, and site features are missing."}}</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:06:29.790354+00:00</t>
         </is>
       </c>
       <c r="T176" t="inlineStr">
@@ -11013,7 +11096,7 @@
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:18.907400+00:00</t>
+          <t>2026-06-02T18:06:29.841727+00:00</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11108,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11045,7 +11128,17 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>12081 DUBARRY AVE</t>
+          <t>12081 Dubarry Ave, Port Charlotte, FL 33981</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201801311053311966, "created_at": "2025-10-10T15:26:02", "customer_email": "kimprice@msctitle.com", "customer_id": 202308041923161327, "customer_name": "Kim Price", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12015C0184G\nZONE: X\nEFF: 12/15/2022", "invoiced": false, "order_id": 1000272874, "paid": false, "property_address": "12081 DUBARRY AVE", "property_city": "PORT CHARLOTTE", "property_county": "CHARLOTTE COUNTY", "property_lat": "26.9458466", "property_lng": "-82.2530594", "property_state": "FLORIDA", "property_zip": "33981", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272874", "customer_email": "kimprice@msctitle.com", "service_type": "Land Survey Only", "county": "", "property_address": "12081 DUBARRY AVE", "customer_name": "MSC Title, Inc. of Englewood"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "MSC Title, Inc. of Englewood", "confidence": "HIGH"}, "client_email": {"value": "kimprice@msctitle.com", "confidence": "HIGH"}, "property_address": {"value": "12081 Dubarry Ave, Port Charlotte, FL 33981", "confidence": "HIGH"}, "property_county": {"value": "Charlotte County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applies; order currently on hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or aerial data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Order is on hold \u2014 reason for hold not specified; human review needed", "Lot size unknown \u2014 no appraiser or parcel data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, structures) unknown \u2014 no aerial or appraiser data", "No fieldwork date scheduled", "Invoice not yet generated; pricing not confirmed despite special_pricing flag", "Contact person vs. company name discrepancy (Kim Price vs. MSC Title, Inc. of Englewood) \u2014 confirm billing name"], "summary": "B2B land survey order for MSC Title, Inc. of Englewood at 12081 Dubarry Ave, Port Charlotte, FL (Charlotte County) currently on hold with special pricing applied and no fieldwork or invoice date set."}}</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:06:39.445100+00:00</t>
         </is>
       </c>
       <c r="T177" t="inlineStr">
@@ -11055,7 +11148,7 @@
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:18.975500+00:00</t>
+          <t>2026-06-02T18:06:39.497662+00:00</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11160,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11082,12 +11175,22 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Gustavo  Alvarez</t>
+          <t>Gustavo Alvarez</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>56048 BLUE CREEK RD</t>
+          <t>56048 Blue Creek Rd, Astor, FL 32102</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508221847217707, "created_at": "2025-10-09T11:34:00", "customer_email": "galvarez@abpluseng.com", "customer_id": 202508221847218750, "customer_name": "Gustavo  Alvarez", "customer_type": "individual", "delivered_at": null, "due_amount": 750.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12069C0070E\nZONE: AE\nELEV: 06 FT\nEFF: 12/18/2012", "invoiced": false, "order_id": 1000272801, "paid": false, "property_address": "56048 BLUE CREEK RD", "property_city": "ASTOR", "property_county": "LAKE COUNTY", "property_lat": "29.17172729999999", "property_lng": "-81.54476509999999", "property_state": "FL", "property_zip": "32102", "service_type": "Legal Creation hourly, Survey Re-draw", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272801", "customer_email": "galvarez@abpluseng.com", "service_type": "Legal Creation hourly, Survey Re-draw", "county": "", "property_address": "56048 BLUE CREEK RD", "customer_name": "Gustavo  Alvarez"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Gustavo Alvarez", "confidence": "HIGH"}, "client_email": {"value": "galvarez@abpluseng.com", "confidence": "HIGH"}, "property_address": {"value": "56048 Blue Creek Rd, Astor, FL 32102", "confidence": "HIGH"}, "property_county": {"value": "Lake County", "confidence": "HIGH"}, "services_requested": {"value": ["Legal Creation Hourly", "Survey Re-draw"], "confidence": "HIGH", "notes": "Both services explicitly listed in service_type field; special_pricing flag is true which may affect billing rates"}, "special_requirements": {"value": "Special pricing applies; order is currently On Hold (status_code 11); flood zone AE with base flood elevation 6 ft (FIRM panel 12069C0070E, effective 12/18/2012)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM", "notes": "Email domain abpluseng.com suggests an engineering firm (AB Plus Engineering); customer_type is listed as individual but professional email domain indicates likely B2B relationship"}, "urgency": {"value": "normal", "confidence": "MEDIUM", "notes": "Order is On Hold; no rush indicators present; created Oct 2025 and last updated Jan 2026 suggesting no active urgency"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser unavailable and no parcel data provided", "Legal description missing \u2014 required for Legal Creation service", "Structure square footage unknown", "Property features unknown (pool, sheds, driveways, structures)", "Reason for On Hold status not documented", "Clarification needed on customer_type: listed as 'individual' but email suggests engineering firm (B2B)", "Scope of Survey Re-draw not defined \u2014 original survey document not provided", "Hourly rate or estimated hours for Legal Creation not specified despite due_amount of $750", "Fieldwork date not scheduled (fieldwork_at is null)", "Estimate has not been sent (estimate_sent is false) \u2014 client may not have approved scope yet"], "summary": "On-hold order for Gustavo Alvarez (likely affiliated with AB Plus Engineering) requesting Legal Creation (hourly) and Survey Re-draw services for a flood zone AE property at 56048 Blue Creek Rd, Astor, FL 32102 in Lake County, with special pricing applied and a due amount of $750."}}</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:06:53.312265+00:00</t>
         </is>
       </c>
       <c r="T178" t="inlineStr">
@@ -11097,7 +11200,7 @@
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:19.043467+00:00</t>
+          <t>2026-06-02T18:06:53.364168+00:00</t>
         </is>
       </c>
     </row>
@@ -11109,7 +11212,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11129,7 +11232,17 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>826 S LAKESIDE DR</t>
+          <t>826 S Lakeside Dr, Lake Worth Beach, FL 33460</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202503041455592811, "created_at": "2025-10-08T09:36:04", "customer_email": "keith@firstupstructures.com", "customer_id": 202503041455592908, "customer_name": "Keith Urban", "customer_type": "b2b", "delivered_at": "2025-10-21T17:51:30", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0781G\nZONE: AE\nELEV: 09 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000272701, "paid": true, "property_address": "826 S LAKESIDE DR", "property_city": "LAKE WORTH BEACH", "property_county": "Palm Beach County", "property_lat": "26.6050458", "property_lng": "-80.0501115", "property_state": "FL", "property_zip": "33460", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272701", "customer_email": "keith@firstupstructures.com", "service_type": "Quote", "county": "", "property_address": "826 S LAKESIDE DR", "customer_name": "FIRSTUP Structures, Inc."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "FIRSTUP Structures, Inc.", "confidence": "HIGH"}, "client_email": {"value": "keith@firstupstructures.com", "confidence": "HIGH"}, "property_address": {"value": "826 S Lakeside Dr, Lake Worth Beach, FL 33460", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "MEDIUM", "notes": "Service type is listed as 'Quote' only \u2014 no specific survey service (e.g., boundary, elevation, topographic) has been identified. Actual service scope is unclear."}, "special_requirements": {"value": "Special pricing applies. Property is in FEMA Flood Zone AE (Panel 12099C0781G, Effective 12/20/2024, Base Flood Elevation 9 ft). No elevation certificate requested at this time.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 no appraiser data, no emails, no aerial imagery referenced. Pool, sheds, driveways, and structures are unknown."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not defined \u2014 'Quote' is not a deliverable service", "Lot size unknown \u2014 no appraiser data available", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, fences, etc.) unknown", "No fieldwork date scheduled (fieldwork_at is null)", "Invoice has not been generated despite order being marked Delivered and Paid", "No matching emails found to clarify scope or client instructions"], "summary": "B2B quote order for FIRSTUP Structures, Inc. at 826 S Lakeside Dr, Lake Worth Beach FL (Flood Zone AE) \u2014 delivered and paid but lacking a defined survey service type, property details, and invoice."}}</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:07:04.463122+00:00</t>
         </is>
       </c>
       <c r="T179" t="inlineStr">
@@ -11139,7 +11252,7 @@
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>2026-06-02T16:08:19.112404+00:00</t>
+          <t>2026-06-02T18:07:04.514378+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -9548,7 +9548,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9571,16 +9571,37 @@
           <t>7202 NW 68TH ST, TAMARAC, FL 33321</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "CAD File / Boundary Survey", "description": "CAD file deliverable for 7202 NW 68TH ST, Tamarac, FL \u2014 Lot 17, Block 244, Mainlands of Tamarac Lakes Unit 15, Plat Book 71 Page 3, Broward County. Standard residential lot (0.15 ac), platted subdivision with recorded plat, Zone X500 (no EC required), no complexity upcharges warranted.", "amount": 450.0}], "pricing_reasoning": "McHardy Construction has a management-agreed negotiated rate of $450.00 applied as the base survey/CAD rate. The property is a small standard residential platted lot (0.15 acres) in a recorded Broward County subdivision, FEMA Zone X500 (minimal flood risk, no Elevation Certificate required), with a straightforward lot description \u2014 no metes-and-bounds, no waterfront, no pool confirmed, no Monroe County mobilization, and no lot-size upcharge triggered (under 0.31 ac threshold). No complexity upcharges are supported by the available data, so the total remains at the flat negotiated rate of $450.00.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "Two issues require human review before finalizing: (1) Order notes state 'CAD scope and property details need clarification' and the order is currently On Hold \u2014 the exact CAD deliverable scope (boundary survey CAD, as-built, etc.) has not been confirmed, which could affect pricing. (2) A possible duplicate order exists (Order 1000271038) for the same address, same folio, same county, for a Land Survey Only service \u2014 management should confirm whether this CAD file order is a standalone new scope, a derivative of the prior survey, or a duplicate, to avoid double-billing or underpricing.", "flags": ["POSSIBLE_DUPLICATE: Order 1000271038 shares the same address (7202 NW 68TH ST, Broward County), same coordinates (26.2068904, -80.2488848), and same Folio/MLS (494110052420) with service type 'Land Survey Only'. Human review required to determine relationship between orders.", "ON_HOLD: Order is currently On Hold per notes. Pricing is based on negotiated rate but CAD scope and property details still need clarification before release.", "CLIENT_TIER_NOTE: McHardy Construction is flagged as OLD_TITLE tier but shows 0 total orders with NexGen. The $450.00 rate is management-approved for this client regardless of order history.", "NO_EC_REQUIRED: FEMA Zone X500 \u2014 no Elevation Certificate triggered."]}</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202512081633332403, "created_at": "2025-12-08T11:37:01", "customer_email": "mchardyconstruction.fl@gmail.com", "customer_id": 202512081634420572, "customer_name": "Mariana McHardy", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0353H\nZONE: X500\nEFF: 08/18/2014", "invoiced": false, "order_id": 1000275662, "paid": true, "property_address": "7202 NW 68TH ST", "property_city": "TAMARAC", "property_county": "Broward County", "property_lat": "26.2068904", "property_lng": "-80.2488848", "property_state": "FL", "property_zip": "33321", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275662", "customer_email": "mchardyconstruction.fl@gmail.com", "service_type": "CAD file", "county": "", "property_address": "7202 NW 68TH ST", "customer_name": "McHardy Construction"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "McHardy Construction", "confidence": "HIGH"}, "client_email": {"value": "mchardyconstruction.fl@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "7202 NW 68TH ST, TAMARAC, FL 33321", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated. Scope of CAD file (boundary, topo, as-built, etc.) is unspecified."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Exact CAD file scope not specified (boundary, topographic, as-built, etc.)", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description not provided", "Structure square footage unknown", "Property features unknown (pool, shed, fences, driveways, etc.)", "Reason for 'On Hold' status not documented", "Fieldwork date not yet scheduled", "No matching emails found \u2014 client communication history unavailable", "Elevation certificate not requested but flood zone data present (Zone X500) \u2014 worth confirming with client"], "summary": "B2B CAD file order for McHardy Construction at 7202 NW 68TH ST, Tamarac, FL (Broward County), currently On Hold with special pricing applied and paid; CAD scope and property details need clarification."}}</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1780424017578</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>2026-06-02T17:34:14.345988+00:00</t>
         </is>
       </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:13:38.055180+00:00</t>
+        </is>
+      </c>
+      <c r="R147" t="n">
+        <v>450</v>
+      </c>
       <c r="T147" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:16.852901+00:00</t>
@@ -9588,7 +9609,7 @@
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>2026-06-02T17:34:14.396247+00:00</t>
+          <t>2026-06-02T18:13:38.110297+00:00</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9621,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9623,16 +9644,37 @@
           <t>8850 US-1, Sebastian, FL 32958</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "This property is 15.02 acres, which exceeds the 5.00-acre threshold defined in pricing guidelines requiring escalation regardless of service type. No pricing can be finalized without management review. Additionally, this order is flagged as a possible duplicate of two prior orders (1000266582 and 1000276085) for the same address and folio number, and the order is currently On Hold with special pricing flagged \u2014 all of which reinforce the need for human review before proceeding.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "Lot size is 15.02 acres, which exceeds the 5.00-acre maximum for automated pricing. Per guidelines, any lot over 5.00 acres must be escalated to management for a custom quote regardless of service type. Secondary escalation triggers: (1) order is On Hold with special pricing flagged per order notes; (2) two probable duplicate orders exist for the same property (Orders 1000266582 and 1000276085, same folio 31392800000004000001.0 and same coordinates); (3) legal description contains a 'Less and Except' carve-out of approximately 2 acres per OR Book 538/Page 413, as well as a highway/FDOT ROW exclusion, adding boundary complexity that warrants manual review.", "flags": ["ESCALATE: Lot size 15.02 acres exceeds 5.00-acre automated pricing threshold \u2014 management quote required.", "DUPLICATE WARNING: Order 1000266582 \u2014 same address (8850 US-1, Indian River County), same service (Land Survey Only), same Folio 31392800000004000001.0 \u2014 confirm whether this is a reorder or duplicate entry.", "DUPLICATE WARNING: Order 1000276085 \u2014 same location coordinates and same Folio 31392800000004000001.0, address listed as '8850 U.S. RTE 1' \u2014 likely the same property; human review required before scheduling fieldwork.", "ORDER ON HOLD: Notes indicate special pricing has been flagged by management \u2014 do not invoice at standard or automated rates without explicit management approval.", "LEGAL DESCRIPTION COMPLEXITY: Property contains FDOT/highway ROW exclusion and a 'Less and Except' approximately 2-acre carve-out per OR Book 538/Page 413 \u2014 boundary resolution requires title chain review and may add fieldwork complexity.", "FEMA NOTE: Property spans multiple flood zones (AE at 7 ft ELEV, X, and X500 shaded) per panel 12061C0118J effective 01/26/2023 \u2014 if an Elevation Certificate is later requested, standard EC fee is $275.00 (no VE surcharge applies here).", "CLIENT NOTE: Atlantic Coastal Land Title Company is flagged as OLD_TITLE tier with a negotiated base rate of $450.00 and 0 prior orders on record \u2014 verify client relationship and rate agreement with management before applying."]}</t>
+        </is>
+      </c>
       <c r="H148" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 201801311048074557, "created_at": "2025-12-10T13:54:04", "customer_email": "jbeal@atlanticcoastal.com", "customer_id": 201801311051368484, "customer_name": "Jason Beal", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12061C0118J\nZONE: AE\nELEV: 07 FT\nZONE: X\nZONE: \"X500\" SHADED\nEFF 01/26/2023", "invoiced": false, "order_id": 1000275516, "paid": false, "property_address": "8850 US-1", "property_city": "SEBASTIAN", "property_county": "INDIAN RIVER COUNTY", "property_lat": "27.7547721", "property_lng": "-80.43473829999999", "property_state": "FLORIDA", "property_zip": "32958", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275516", "customer_email": "jbeal@atlanticcoastal.com", "service_type": "Land Survey Only", "county": "", "property_address": "8850 US-1", "customer_name": "Atlantic Coastal Land Title Company"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Atlantic Coastal Land Title Company", "confidence": "MEDIUM"}, "client_email": {"value": "jbeal@atlanticcoastal.com", "confidence": "HIGH"}, "property_address": {"value": "8850 US-1, Sebastian, FL 32958", "confidence": "HIGH"}, "property_county": {"value": "Indian River County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing flagged; order currently On Hold (status code 11); flood zone data present: FIRM panel 12061C0118J, zones AE (07 ft BFE), X, and X500 shaded, effective 01/26/2023", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing \u2014 no appraiser or document source available", "Structure square footage unknown", "Property features (pool, shed, structures) unknown \u2014 no aerial or appraiser data", "Order is On Hold \u2014 reason for hold not specified, needs human review", "Client name conflict: order contact is 'Jason Beal' but company name listed as 'Atlantic Coastal Land Title Company' \u2014 confirm billing entity", "Fieldwork and delivery dates not yet scheduled", "Special pricing flag is set \u2014 pricing terms need human confirmation", "No matching emails found \u2014 no additional context or instructions from client"], "summary": "B2B land survey order for Atlantic Coastal Land Title Company at 8850 US-1, Sebastian, FL (Indian River County), currently On Hold with special pricing flagged and no fieldwork scheduled."}}</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1780424040668</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>2026-06-02T17:34:25.853259+00:00</t>
         </is>
       </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:14:01.406336+00:00</t>
+        </is>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
       <c r="T148" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:16.962298+00:00</t>
@@ -9640,7 +9682,7 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>2026-06-02T17:34:25.905134+00:00</t>
+          <t>2026-06-02T18:14:01.461274+00:00</t>
         </is>
       </c>
     </row>
@@ -11264,7 +11306,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11284,7 +11326,17 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>3801 COCO GROVE AVE</t>
+          <t>3801 Coco Grove Ave, Miami, FL 33133</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202412302008110119, "created_at": "2025-10-07T17:20:05", "customer_email": "edong888@gmail.com", "customer_id": 202412302008111157, "customer_name": "Eric Dong", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0457L\nZONE: X\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000272649, "paid": false, "property_address": "3801 COCO GROVE AVE", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.7211453", "property_lng": "-80.2546693", "property_state": "FL", "property_zip": "33133", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272649", "customer_email": "edong888@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "3801 COCO GROVE AVE", "customer_name": "Eric Dong"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Eric Dong", "confidence": "HIGH"}, "client_email": {"value": "edong888@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "3801 Coco Grove Ave, Miami, FL 33133", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing flagged on order; order currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments found"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features (pool, shed, fence, structures) unknown \u2014 no aerial or appraiser data", "Order is On Hold \u2014 reason for hold not specified, needs human review", "Special pricing flag is set but no pricing details or reason provided", "No invoice amount set (due_amount: 0.00) \u2014 pricing not yet determined", "Fieldwork date not scheduled", "Customer data object is empty \u2014 no additional contact or billing info available"], "summary": "Residential land survey order for Eric Dong at 3801 Coco Grove Ave, Miami, FL 33133 (Miami-Dade County) is currently On Hold with special pricing flagged, no fieldwork scheduled, and key property details such as lot size, legal description, and property features still unknown."}}</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:12:25.548408+00:00</t>
         </is>
       </c>
       <c r="T180" t="inlineStr">
@@ -11294,7 +11346,7 @@
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:12.975802+00:00</t>
+          <t>2026-06-02T18:12:25.603398+00:00</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11358,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11321,12 +11373,22 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Nexgen Land Solutions, LLC</t>
+          <t>ORDER RESOLUTIONS</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>1409 NE 7TH AVE</t>
+          <t>1409 NE 7TH AVE, CAPE CORAL, FL 33909</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201801311053398445, "created_at": "2025-10-03T14:26:00", "customer_email": "FREDERICK_S@NEXGENLOGIX.COM", "customer_id": 202410281556504891, "customer_name": "ORDER RESOLUTIONS", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12071C0262G\nZONE: X\nEFF: 11/17/2022", "invoiced": false, "order_id": 1000272525, "paid": false, "property_address": "1409 NE 7TH AVE", "property_city": "CAPE CORAL", "property_county": "LEE COUNTY", "property_lat": "26.6790374", "property_lng": "-81.95892649999999", "property_state": "FL", "property_zip": "33909", "service_type": "Survey Re-draw", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272525", "customer_email": "FREDERICK_S@NEXGENLOGIX.COM", "service_type": "Survey Re-draw", "county": "", "property_address": "1409 NE 7TH AVE", "customer_name": "Nexgen Land Solutions, LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "ORDER RESOLUTIONS", "confidence": "MEDIUM"}, "client_email": {"value": "FREDERICK_S@NEXGENLOGIX.COM", "confidence": "HIGH"}, "property_address": {"value": "1409 NE 7TH AVE, CAPE CORAL, FL 33909", "confidence": "HIGH"}, "property_county": {"value": "LEE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Survey Re-draw"], "confidence": "HIGH", "notes": "Service type explicitly stated as Survey Re-draw; no additional services indicated"}, "special_requirements": {"value": "Special pricing applies; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name ambiguity \u2014 FTF order shows 'ORDER RESOLUTIONS' but customer_name in outer envelope shows 'Nexgen Land Solutions, LLC'; needs human clarification", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, structures) unknown \u2014 no appraiser data or aerial available", "Reason for On Hold status not specified", "Original survey or reference documents not attached for re-draw scope", "No fieldwork or delivery dates scheduled", "Special pricing amount or discount not detailed"], "summary": "A b2b Survey Re-draw order for a property at 1409 NE 7TH AVE, Cape Coral, FL (Lee County) is currently On Hold with special pricing applied, but lacks lot details, legal description, and supporting documents needed to complete the re-draw scope."}}</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:12:36.062390+00:00</t>
         </is>
       </c>
       <c r="T181" t="inlineStr">
@@ -11336,7 +11398,7 @@
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:13.049076+00:00</t>
+          <t>2026-06-02T18:12:36.117153+00:00</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11410,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11363,12 +11425,22 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>MICHAEL  SCHWARTZ</t>
+          <t>MICHAEL SCHWARTZ</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>3708 PLUMOSA TERRACE</t>
+          <t>3708 PLUMOSA TERRACE, BRADENTON, FL 34210</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510031522295033, "created_at": "2025-10-03T11:42:03", "customer_email": "tffmgwr4@aol.com", "customer_id": 202510031522296104, "customer_name": "MICHAEL  SCHWARTZ", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12081C0283F\nZONE: AE\nELEV: 08 FT\nEFF: 08/10/2021", "invoiced": false, "order_id": 1000272499, "paid": true, "property_address": "3708 PLUMOSA TERRACE", "property_city": "BRADENTON", "property_county": "Manatee County", "property_lat": "27.4684347", "property_lng": "-82.6619145", "property_state": "FL", "property_zip": "34210", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272499", "customer_email": "tffmgwr4@aol.com", "service_type": "CAD file", "county": "", "property_address": "3708 PLUMOSA TERRACE", "customer_name": "MICHAEL  SCHWARTZ"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "MICHAEL SCHWARTZ", "confidence": "HIGH"}, "client_email": {"value": "tffmgwr4@aol.com", "confidence": "HIGH"}, "property_address": {"value": "3708 PLUMOSA TERRACE, BRADENTON, FL 34210", "confidence": "HIGH"}, "property_county": {"value": "Manatee County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type listed as 'CAD file'; no additional services indicated. Unclear if this is a standalone CAD deliverable or tied to a specific survey type (e.g., boundary, elevation)."}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11). Flood zone data present: FEMA panel 12081C0283F, Zone AE, base flood elevation 8 ft, effective 08/10/2021.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or aerials provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Reason for On Hold status \u2014 needs human review to determine if order should proceed", "CAD file scope unclear \u2014 what underlying survey type is this CAD deliverable based on?", "Lot size not available", "Legal description not available", "Structure square footage not available", "Property features (pool, shed, structures) unknown \u2014 no appraiser data or aerials", "Special pricing details not specified \u2014 amount or discount reason unknown", "No invoice generated yet (invoiced: false) \u2014 pricing to be confirmed", "Delivery timeline unknown (fieldwork_at and delivered_at are null)"], "summary": "Residential CAD file order for Michael Schwartz at 3708 Plumosa Terrace, Bradenton FL (Manatee County) is currently On Hold with special pricing applied, paid but not yet invoiced, and missing key property details including survey scope, lot size, and legal description."}}</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:12:48.218469+00:00</t>
         </is>
       </c>
       <c r="T182" t="inlineStr">
@@ -11378,7 +11450,7 @@
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:13.119993+00:00</t>
+          <t>2026-06-02T18:12:48.274678+00:00</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11462,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11410,7 +11482,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>1250 SOUTHWINDS DR</t>
+          <t>1250 Southwinds Dr, Lantana, FL 33462</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202510011843280904, "created_at": "2025-10-02T17:08:00", "customer_email": "561jck@gmail.com", "customer_id": 202510011844095922, "customer_name": "Kristen Owsley", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0779G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000272382, "paid": false, "property_address": "1250 SOUTHWINDS DR", "property_city": "LANTANA", "property_county": "PALM BEACH COUNTY", "property_lat": "26.5918905", "property_lng": "-80.0631796", "property_state": "FL", "property_zip": "33462", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272382", "customer_email": "561jck@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "1250 SOUTHWINDS DR", "customer_name": "Just Call Kris, Inc."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Just Call Kris, Inc.", "confidence": "HIGH"}, "client_email": {"value": "561jck@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1250 Southwinds Dr, Lantana, FL 33462", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing flagged on order; order is currently On Hold \u2014 reason unknown.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, no emails, and no aerial review performed."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Reason order is 'On Hold' \u2014 needs clarification before proceeding", "Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, etc.)", "Urgency or deadline not specified", "No fieldwork or delivery dates set", "Special pricing flag present but pricing details not documented", "Customer name inconsistency: FTF order data shows 'Kristen Owsley' but outer customer_name shows 'Just Call Kris, Inc.' \u2014 confirm correct billing name"], "summary": "B2B land survey order for Just Call Kris, Inc. at 1250 Southwinds Dr, Lantana FL (Palm Beach County) is currently On Hold with special pricing flagged, no fieldwork scheduled, and significant property detail gaps requiring human follow-up."}}</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:13:02.556554+00:00</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
@@ -11420,7 +11502,7 @@
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:13.241662+00:00</t>
+          <t>2026-06-02T18:13:02.610088+00:00</t>
         </is>
       </c>
     </row>
@@ -11432,7 +11514,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11452,7 +11534,17 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>316 AMANDA LN</t>
+          <t>316 Amanda Ln, Leesburg, FL 34748</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202509301523412952, "created_at": "2025-09-30T17:00:05", "customer_email": "noemailgiven@none.com", "customer_id": 202509301523415071, "customer_name": "Lee Bennett", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12069C0308E\nZONE:AE\nELEV: 78.1 FT\nZONE: X\nEFF: 12/18/2012", "invoiced": false, "order_id": 1000272305, "paid": false, "property_address": "316 AMANDA LN", "property_city": "LEESBURG", "property_county": "Lake County", "property_lat": "28.8175048", "property_lng": "-81.90851769999999", "property_state": "FL", "property_zip": "34748", "service_type": "Boundary Survey", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272305", "customer_email": "noemailgiven@none.com", "service_type": "Boundary Survey", "county": "", "property_address": "316 AMANDA LN", "customer_name": "Lee Bennett"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Lee Bennett", "confidence": "HIGH"}, "client_email": {"value": "noemailgiven@none.com", "confidence": "LOW"}, "property_address": {"value": "316 Amanda Ln, Leesburg, FL 34748", "confidence": "HIGH"}, "property_county": {"value": "Lake County", "confidence": "HIGH"}, "services_requested": {"value": ["Boundary Survey"], "confidence": "HIGH", "notes": "Service type explicitly listed as Boundary Survey; elevation_cert is false so no elevation certificate is needed"}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); flood zone data present \u2014 AE zone at 78.1 ft NAVD and X zone per FIRM panel 12069C0308E effective 12/18/2012", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Valid client email address \u2014 'noemailgiven@none.com' is a placeholder", "Client phone number not provided", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, fences, sheds, encroachments, etc.)", "Reason order is On Hold not specified \u2014 needs human review", "Urgency/deadline not stated", "Special pricing details not itemized \u2014 confirm pricing before invoicing", "County field is blank in top-level order data despite being populated in nested data \u2014 verify data consistency"], "summary": "Residential boundary survey order for Lee Bennett at 316 Amanda Ln, Leesburg, FL (Lake County) is currently On Hold with special pricing applied, no valid client email on file, and missing lot size, legal description, and property feature details."}}</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:13:14.767702+00:00</t>
         </is>
       </c>
       <c r="T184" t="inlineStr">
@@ -11462,7 +11554,7 @@
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:13.313936+00:00</t>
+          <t>2026-06-02T18:13:14.822976+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -9694,7 +9694,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9717,16 +9717,37 @@
           <t>2992 20TH AVE NE, NAPLES, FL 34120</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "This order is for a CAD file delivery at 2992 20TH Ave NE, Collier County, a 5.15-acre Golden Gate Estates tract. The lot size exceeds the 5.00-acre threshold defined in pricing guidelines, which mandates escalation for any service type regardless of client rate or complexity factors. Additionally, two probable duplicate orders exist for the same address and folio (Orders 1000268362 and 1000275091), suggesting fieldwork may already be underway or completed under a separate order \u2014 the CAD file may simply be a deliverable tied to one of those existing surveys, which further warrants management review before any pricing is issued.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "Lot size is 5.15 acres, which exceeds the 5.00-acre hard ceiling in pricing guidelines \u2014 escalate to management for manual quoting on all service types. Additionally, two duplicate orders exist for the same property (Order 1000268362: Boundary Survey; Order 1000275091: Land Survey Only) \u2014 management should determine whether this CAD file order is a standalone deliverable tied to one of those existing orders or a new independent engagement, and price accordingly.", "flags": ["ESCALATE: Lot size 5.15 acres exceeds the 5.00-acre pricing threshold \u2014 do not price; flag for management quote.", "DUPLICATE DETECTED: Order 1000268362 \u2014 same address (2992 20TH AVE NE, Collier County), same Folio 40303600002, service: Boundary Survey. Human review required.", "DUPLICATE DETECTED: Order 1000275091 \u2014 same address (2992 20TH AVE NE, Collier County), same Folio 40303600002, service: Land Survey Only. Human review required.", "ORDER ON HOLD: Per order notes, this order is currently On Hold with special pricing applied and no fieldwork scheduled. Management should confirm whether the CAD file is a deliverable from one of the duplicate boundary/land survey orders before scheduling or pricing independently.", "FEMA NOTE: Property falls partially in Zone AH (base flood elevation 15 ft, effective 05/16/2012) \u2014 if an Elevation Certificate is later added, standard EC fee of $275.00 applies (no VE coastal surcharge; zone is AH not VE).", "NEW CLIENT: Aileen Cuadra-Roque has 0 prior orders with NexGen \u2014 management-negotiated base rate of $350.00 is on file but pricing cannot be finalized until escalation is resolved."]}</t>
+        </is>
+      </c>
       <c r="H149" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202507211345522935, "created_at": "2025-12-04T10:19:05", "customer_email": "aileensellsnaples@gmail.com", "customer_id": 202507211345523034, "customer_name": "Aileen Cuadra-Roque", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12021C0245H\nZONE: X500\nZONE: AH\nELEV: 15 FT\nEFF: 05/16/2012", "invoiced": false, "order_id": 1000275511, "paid": true, "property_address": "2992 20TH AVE NE", "property_city": "NAPLES", "property_county": "Collier County", "property_lat": "26.2665243", "property_lng": "-81.5457423", "property_state": "FL", "property_zip": "34120", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275511", "customer_email": "aileensellsnaples@gmail.com", "service_type": "CAD file", "county": "", "property_address": "2992 20TH AVE NE", "customer_name": "Aileen Cuadra-Roque"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Aileen Cuadra-Roque", "confidence": "HIGH"}, "client_email": {"value": "aileensellsnaples@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "2992 20TH AVE NE, NAPLES, FL 34120", "confidence": "HIGH"}, "property_county": {"value": "Collier County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Only service type listed is CAD file; no additional services indicated in the order data"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold. Flood zone data present: Panel 12021C0245H, zones X500 and AH, base elevation 15 FT, effective 05/16/2012.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no aerial, appraiser, or email data provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, structures) unknown \u2014 no aerial or appraiser data", "No matching emails found \u2014 cannot confirm scope or client communications", "Reason for On Hold status not specified", "Invoice not yet sent and due amount is $0 \u2014 pricing details unclear despite special_pricing flag", "Fieldwork and delivery dates not yet set"], "summary": "Residential CAD file order for Aileen Cuadra-Roque at 2992 20TH AVE NE, Naples, FL (Collier County) is currently On Hold with special pricing applied, no fieldwork scheduled, and key property details including lot size and legal description still missing."}}</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1780424232604</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>2026-06-02T17:34:36.557815+00:00</t>
         </is>
       </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:19:29.764551+00:00</t>
+        </is>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
       <c r="T149" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:17.023586+00:00</t>
@@ -9734,7 +9755,7 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>2026-06-02T17:34:36.609495+00:00</t>
+          <t>2026-06-02T18:19:29.820607+00:00</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9767,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9769,16 +9790,37 @@
           <t>1131 S N ST, Lake Worth Beach, FL 33460</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "CAD File", "description": "CAD file deliverable for residential property at 1131 S N ST, Lake Worth Beach, Palm Beach County. Lot 16, Block 47, Addition No. 1 to the Townsite of Lake Worth \u2014 standard platted lot, 0.15 acres, FEMA Zone X (no flood risk premium). Priced at management-agreed special rate for individual client Daymon Hallmon.", "amount": 450.0}], "pricing_reasoning": "The service requested is a CAD file for a small residential platted lot (0.15 acres) in Palm Beach County. Management has pre-agreed a negotiated base rate of $450.00 for this individual client, and that rate is used as the final price. No complexity upcharges apply: the lot is well under 0.31 acres, the legal description is a standard platted lot (not metes and bounds), FEMA Zone X carries no EC requirement or VE premium, and there are no indicators of pool, waterfront canal, heavy vegetation, or Monroe County mobilization. The order is flagged as a possible duplicate of Order 1000270974 at the same address and folio, and a hold/scope clarification was noted \u2014 human review is recommended before releasing the invoice.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "Order is currently on hold pending clarification of scope and hold reason per order notes. A confirmed duplicate order (1000270974) exists for the same address (1131 S N ST, Palm Beach County) with the same folio (38434427010470160) for a combined Land Survey and Elevation Certificate service. Management should confirm whether this CAD file order is a standalone deliverable from the existing survey, a replacement, or a redundant entry before the invoice is finalized and the hold is released.", "flags": ["POSSIBLE_DUPLICATE: Order 1000270974 references the same property (1131 S N ST, Palm Beach County, Folio 38434427010470160) with service 'Land Survey and Elevation Certificate' \u2014 verify whether this CAD file order is derivative of that survey or a separate engagement.", "ORDER_ON_HOLD: Per order notes, this order is paid but on hold pending scope clarification. Do not finalize or deliver without management sign-off.", "SPECIAL_PRICING: Management-agreed rate of $450.00 applied for individual client Daymon Hallmon \u2014 no standard rate deviation required."]}</t>
+        </is>
+      </c>
       <c r="H150" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202512011530429151, "created_at": "2025-12-01T11:07:04", "customer_email": "daymon@eastcoastmetals.net", "customer_id": 202512011530430512, "customer_name": "Daymon Hallmon", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0781G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000275245, "paid": true, "property_address": "1131 S N ST", "property_city": "LAKE WORTH BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.601369", "property_lng": "-80.05358559999999", "property_state": "FL", "property_zip": "33460", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275245", "customer_email": "daymon@eastcoastmetals.net", "service_type": "CAD file", "county": "", "property_address": "1131 S N ST", "customer_name": "Daymon Hallmon"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Daymon Hallmon", "confidence": "HIGH"}, "client_email": {"value": "daymon@eastcoastmetals.net", "confidence": "HIGH"}, "property_address": {"value": "1131 S N ST, Lake Worth Beach, FL 33460", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Only service type listed is CAD file; no additional services specified"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no aerial, appraiser, or email data provided"}, "client_tier": {"value": "residential", "confidence": "MEDIUM"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, etc.)", "Reason for On Hold status not specified", "Scope of CAD file deliverable not clarified (boundary, topo, as-built, etc.)", "No fieldwork date scheduled", "Invoice has not been sent \u2014 needs follow-up", "Client type listed as individual but email domain (eastcoastmetals.net) suggests possible business affiliation"], "summary": "Individual client Daymon Hallmon has a paid but on-hold CAD file order for a residential property in Lake Worth Beach, FL with special pricing applied, pending clarification on scope, hold reason, and property details."}}</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1780424391204</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>2026-06-02T17:39:04.509513+00:00</t>
         </is>
       </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:19:53.931421+00:00</t>
+        </is>
+      </c>
+      <c r="R150" t="n">
+        <v>450</v>
+      </c>
       <c r="T150" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:17.084094+00:00</t>
@@ -9786,7 +9828,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>2026-06-02T17:39:04.558649+00:00</t>
+          <t>2026-06-02T18:19:54.039808+00:00</t>
         </is>
       </c>
     </row>
@@ -11566,7 +11608,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11586,7 +11628,17 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2133 SIBLEY AVE</t>
+          <t>2133 Sibley Ave, Fort Pierce, FL 34982</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201804061150419039, "created_at": "2025-09-25T15:31:02", "customer_email": "hgm@mccarthysummers.com", "customer_id": 202509251913000352, "customer_name": "Hannah Moore", "customer_type": "b2b", "delivered_at": "2025-10-15T19:18:54", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12111C0186J\nZONE: X\nEFF: 02/16/2012", "invoiced": false, "order_id": 1000272106, "paid": true, "property_address": "2133 SIBLEY AVE", "property_city": "FORT PIERCE", "property_county": "ST LUCIE County", "property_lat": "27.4069748", "property_lng": "-80.3463277", "property_state": "FL", "property_zip": "34982", "service_type": "Other Services", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272106", "customer_email": "hgm@mccarthysummers.com", "service_type": "Other Services", "county": "", "property_address": "2133 SIBLEY AVE", "customer_name": "McCarthy, Summers, Bobko, Wood, Norman, Bass, and Melby, PA"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "McCarthy, Summers, Bobko, Wood, Norman, Bass, and Melby, PA", "confidence": "HIGH"}, "client_email": {"value": "hgm@mccarthysummers.com", "confidence": "HIGH"}, "property_address": {"value": "2133 Sibley Ave, Fort Pierce, FL 34982", "confidence": "HIGH"}, "property_county": {"value": "St. Lucie County", "confidence": "HIGH"}, "services_requested": {"value": ["Other Services"], "confidence": "LOW", "notes": "Service type is listed only as 'Other Services' \u2014 specific survey or service type is unknown and requires clarification"}, "special_requirements": {"value": "Special pricing applied", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific service type is unknown \u2014 'Other Services' needs clarification", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown \u2014 no appraiser, aerial, or email data available", "No invoice has been generated despite order being delivered and paid", "Fieldwork date is null \u2014 unclear if fieldwork was completed"], "summary": "A delivered and paid B2B order for law firm McCarthy, Summers, Bobko, Wood, Norman, Bass, and Melby, PA at 2133 Sibley Ave, Fort Pierce, FL (St. Lucie County) with an unspecified 'Other Services' service type, special pricing applied, and no invoice yet generated."}}</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:18:24.406612+00:00</t>
         </is>
       </c>
       <c r="T185" t="inlineStr">
@@ -11596,7 +11648,7 @@
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:13.385617+00:00</t>
+          <t>2026-06-02T18:18:24.466432+00:00</t>
         </is>
       </c>
     </row>
@@ -11608,7 +11660,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11628,7 +11680,17 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>3826 10TH AVE N</t>
+          <t>3826 10TH AVE N, Lake Worth Beach, FL 33461</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202509251455455494, "created_at": "2025-09-25T11:03:00", "customer_email": "YamiraRuiz216@gmail.com", "customer_id": 202509251455456502, "customer_name": "Yamira Ruiz", "customer_type": "individual", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0588F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000272053, "paid": false, "property_address": "3826 10TH AVE N", "property_city": "LAKE WORTH BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.6287852", "property_lng": "-80.1019732", "property_state": "FL", "property_zip": "33461", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272053", "customer_email": "YamiraRuiz216@gmail.com", "service_type": "CAD file", "county": "", "property_address": "3826 10TH AVE N", "customer_name": "Yamira Ruiz"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Yamira Ruiz", "confidence": "HIGH"}, "client_email": {"value": "YamiraRuiz216@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "3826 10TH AVE N, Lake Worth Beach, FL 33461", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type listed as 'CAD file'; no additional services indicated. Unclear if CAD file is a standalone deliverable or tied to a specific survey type (e.g., boundary, topographic)."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Underlying survey type for CAD file deliverable not specified (boundary, topo, ALTA, etc.)", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) unknown", "Reason for 'On Hold' status not documented", "Fieldwork date not scheduled", "Invoice not yet generated despite $250 due amount", "No matching emails found to supplement order context"], "summary": "Individual residential client Yamira Ruiz is requesting a CAD file deliverable for a property at 3826 10th Ave N, Lake Worth Beach, FL (Palm Beach County), with special pricing applied and the order currently on hold pending further action."}}</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:18:34.187402+00:00</t>
         </is>
       </c>
       <c r="T186" t="inlineStr">
@@ -11638,7 +11700,7 @@
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:13.456921+00:00</t>
+          <t>2026-06-02T18:18:34.243751+00:00</t>
         </is>
       </c>
     </row>
@@ -11650,7 +11712,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11670,7 +11732,17 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>201 BRANCH WOOD LN</t>
+          <t>201 BRANCH WOOD LN, JACKSONVILLE, FLORIDA 32256</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507101346392968, "created_at": "2025-09-23T07:37:00", "customer_email": "TEST", "customer_id": 202507101346393060, "customer_name": "NEXGEN-TEST", "customer_type": "b2b", "delivered_at": null, "due_amount": 303.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": "2025-11-14T00:00:00", "flood_zone": null, "invoiced": false, "order_id": 1000271907, "paid": false, "property_address": "201 BRANCH WOOD LN", "property_city": "JACKSONVILLE", "property_county": "DUVAL COUNTY", "property_lat": "26.8068413", "property_lng": "-80.0737982", "property_state": "FLORIDA", "property_zip": "32256", "service_type": "Land Survey Only, Elevation Certificate", "special_pricing": false, "status": "Assigned", "status_code": 2, "updated_at": "2026-05-06T10:50:10"}, "success": true, "order_id": "1000271907", "customer_email": "TEST", "service_type": "Land Survey Only, Elevation Certificate", "county": "", "property_address": "201 BRANCH WOOD LN", "customer_name": "NEXGEN-TEST"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "NEXGEN-TEST", "confidence": "HIGH"}, "client_email": {"value": "TEST", "confidence": "LOW"}, "property_address": {"value": "201 BRANCH WOOD LN, JACKSONVILLE, FLORIDA 32256", "confidence": "HIGH"}, "property_county": {"value": "DUVAL COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey", "Elevation Certificate"], "confidence": "HIGH", "notes": "service_type field lists both 'Land Survey Only' and 'Elevation Certificate'; however, the elevation_cert boolean is set to false \u2014 contradiction requires human review"}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or aerial data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client email is a placeholder ('TEST') \u2014 real contact email needed", "Client name appears to be a test account ('NEXGEN-TEST') \u2014 confirm if this is a real order", "Contradiction between service_type ('Elevation Certificate') and elevation_cert flag (false) \u2014 clarify which services are actually required", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, structures) unknown", "Special requirements or access instructions not provided", "County was blank in the outer FTF payload despite being listed in the nested data object \u2014 verify county field integrity", "Coordinates (lat 26.8068, lng -80.0737) appear to be in Palm Beach area, not Jacksonville/Duval County \u2014 location mismatch needs human verification"], "summary": "Apparent test order (Order #1000271907) for a land survey and possibly an elevation certificate at 201 Branch Wood Ln, Jacksonville, FL 32256 (Duval County), flagged with multiple data quality issues including a placeholder email, test account name, service type contradiction, and a coordinate-to-address mismatch requiring human review before processing."}}</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:18:46.337308+00:00</t>
         </is>
       </c>
       <c r="T187" t="inlineStr">
@@ -11680,7 +11752,7 @@
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:13.529411+00:00</t>
+          <t>2026-06-02T18:18:46.392398+00:00</t>
         </is>
       </c>
     </row>
@@ -11692,7 +11764,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11712,7 +11784,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>8690 POINT CYPRESS DR</t>
+          <t>8690 Point Cypress Dr, Orlando, FL 32836</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202411141637401215, "created_at": "2025-09-22T11:04:05", "customer_email": "ahaynes@firstam.com", "customer_id": 202508181400185336, "customer_name": "Amanda  Haynes", "customer_type": "b2b", "delivered_at": "2025-11-26T20:04:23", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12095C0385F\nZONE: X\nEFF: 09/25/2009", "invoiced": false, "order_id": 1000271845, "paid": true, "property_address": "8690 POINT CYPRESS DR", "property_city": "ORLANDO", "property_county": "ORANGE COUNTY", "property_lat": "28.4377594", "property_lng": "-81.5046198", "property_state": "FL", "property_zip": "32836", "service_type": "ALTA Table A Survey", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000271845", "customer_email": "ahaynes@firstam.com", "service_type": "ALTA Table A Survey", "county": "", "property_address": "8690 POINT CYPRESS DR", "customer_name": "CDS-Commercial Due Diligence Services"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "CDS-Commercial Due Diligence Services", "confidence": "MEDIUM"}, "client_email": {"value": "ahaynes@firstam.com", "confidence": "HIGH"}, "property_address": {"value": "8690 Point Cypress Dr, Orlando, FL 32836", "confidence": "HIGH"}, "property_county": {"value": "Orange County", "confidence": "HIGH"}, "services_requested": {"value": ["ALTA Table A Survey"], "confidence": "HIGH", "notes": "Service type explicitly listed as ALTA Table A Survey; specific Table A items checked are unknown and require clarification"}, "special_requirements": {"value": "Special pricing applied; specific Table A items not specified", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific ALTA Table A items requested (e.g., items 1\u201321) not specified", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing", "Structure square footage unknown", "Property features (improvements, utilities, easements) unknown", "Client name conflict: order contact is 'Amanda Haynes' but customer_name field shows 'CDS-Commercial Due Diligence Services' \u2014 confirm billing entity", "No fieldwork date scheduled (fieldwork_at is null)", "Special pricing details not specified \u2014 pricing amount or agreement unknown", "No supporting emails or appraiser data to cross-reference"], "summary": "B2B ALTA Table A Survey order for a commercial property at 8690 Point Cypress Dr, Orlando, FL (Orange County), placed by CDS-Commercial Due Diligence Services with special pricing applied and no Table A items or lot details yet specified."}}</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:18:56.873418+00:00</t>
         </is>
       </c>
       <c r="T188" t="inlineStr">
@@ -11722,7 +11804,7 @@
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:13.600679+00:00</t>
+          <t>2026-06-02T18:18:56.930496+00:00</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11816,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11754,7 +11836,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>1102 N GOLFVIEW RD</t>
+          <t>1102 N Golfview Rd, Lake Worth Beach, FL 33460</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507031745122975, "created_at": "2025-09-19T09:49:05", "customer_email": "akstorm8225@gmail.com", "customer_id": 202507031745123074, "customer_name": "Andy Kobosko", "customer_type": "individual", "delivered_at": "2025-09-19T15:50:42", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0593G\nZONE: AE\nELEV: 08 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000271787, "paid": true, "property_address": "1102 N GOLFVIEW RD", "property_city": "LAKE WORTH BEACH", "property_county": "Palm Beach County", "property_lat": "26.6286542", "property_lng": "-80.0482727", "property_state": "FL", "property_zip": "33460", "service_type": "Quote", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000271787", "customer_email": "akstorm8225@gmail.com", "service_type": "Quote", "county": "", "property_address": "1102 N GOLFVIEW RD", "customer_name": "Andy Kobosko"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Andy Kobosko", "confidence": "HIGH"}, "client_email": {"value": "akstorm8225@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1102 N Golfview Rd, Lake Worth Beach, FL 33460", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., boundary, elevation cert, topographic) has been identified. Actual services needed require human clarification."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available and no emails or attachments to reference. Pool, structures, and other features unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service(s) requested \u2014 order is listed only as 'Quote' with no detail", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, etc.)", "Special requirements or client notes not provided", "No matching emails found to supplement order context", "County field blank in top-level FTF data (populated only within nested data object)", "Elevation certificate not ordered but property is in Flood Zone AE \u2014 client may need one"], "summary": "Individual residential client Andy Kobosko submitted a quote request for a property at 1102 N Golfview Rd, Lake Worth Beach FL (Flood Zone AE), but no specific survey service has been identified and significant property details are missing."}}</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:19:08.191108+00:00</t>
         </is>
       </c>
       <c r="T189" t="inlineStr">
@@ -11764,7 +11856,7 @@
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:13.673158+00:00</t>
+          <t>2026-06-02T18:19:08.247997+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -9840,7 +9840,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9863,16 +9863,37 @@
           <t>322 SE 3rd Ave, Delray Beach, FL 33483</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>{"total_amount": 475.0, "services": [{"name": "Boundary Survey (Quote)", "description": "Standard residential boundary survey for LOT 18 AND N 1/2 OF LOT 19, BLOCK 88, LINNS ADDITION (OSCEOLA PARK DELRAY), 322 SE 3rd Ave, Delray Beach, Palm Beach County. Lot size 0.23 acres \u2014 within standard tier, no lot-size upcharge. FEMA Zone X \u2014 no EC required. Legal description is plat-referenced (not metes and bounds) \u2014 no metes-and-bounds upcharge. No pool, waterfront, heavy vegetation, or Monroe County factors identified. Individual client with no negotiated rate; default individual base rate applies.", "amount": 475.0}], "pricing_reasoning": "Client Colleen Guglielmo is an individual homeowner with no negotiated rate, so the default individual base rate of $475.00 applies. The 0.23-acre lot falls within the standard tier (under 0.31 acres), the legal description is plat-based rather than metes and bounds, FEMA Zone X eliminates any EC requirement, and no aerial or data indicators suggest pool, waterfront canal, heavy vegetation, or other complexity upcharges. No specific survey type has been identified by the client, so this quote reflects a standard boundary survey as the most likely requested service.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Three prior orders exist for this exact property and folio (12434616040880180) \u2014 Order 1000258521 (Land Survey Only), Order 1000274052 (Quote), and Order 1000274745 (Land Survey Only). This appears to be a repeat or duplicate submission. Human review is strongly recommended before proceeding to avoid redundant fieldwork or billing.", "SERVICE_TYPE_UNCONFIRMED: Client has not specified the exact survey service needed. Quote is priced as a standard boundary survey pending clarification. If an Elevation Certificate, Topo, or other service is ultimately required, pricing must be revised accordingly.", "ZONE_X_CONFIRMED: FEMA flood zone is X (effective 12/20/2024, panel 12099C0979G). No Elevation Certificate is warranted based on current flood zone designation."]}</t>
+        </is>
+      </c>
       <c r="H151" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202511041936177608, "created_at": "2025-11-26T09:55:04", "customer_email": "cguglielmo16@icloud.com", "customer_id": 202511041936177714, "customer_name": "Colleen   Guglielmo", "customer_type": "individual", "delivered_at": "2025-11-26T15:56:06", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0979G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000275171, "paid": false, "property_address": "322 SE 3RD AVE", "property_city": "DELRAY BEACH", "property_county": "Palm Beach County", "property_lat": "26.4552517", "property_lng": "-80.0701823", "property_state": "FL", "property_zip": "33483", "service_type": "Quote", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275171", "customer_email": "cguglielmo16@icloud.com", "service_type": "Quote", "county": "", "property_address": "322 SE 3RD AVE", "customer_name": "Colleen   Guglielmo"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Colleen Guglielmo", "confidence": "HIGH"}, "client_email": {"value": "cguglielmo16@icloud.com", "confidence": "HIGH"}, "property_address": {"value": "322 SE 3rd Ave, Delray Beach, FL 33483", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., boundary, ALTA, elevation) has been identified. Needs clarification."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service(s) requested \u2014 order is only marked as 'Quote' with no detail", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) unknown", "Special requirements or client notes not provided", "No matching emails found to clarify scope or intent"], "summary": "Individual residential client Colleen Guglielmo is requesting a quote for a survey at 322 SE 3rd Ave, Delray Beach, FL (Palm Beach County), but the specific survey service needed has not yet been identified."}}</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1780424725772</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>2026-06-02T17:39:15.101657+00:00</t>
         </is>
       </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:25:26.203694+00:00</t>
+        </is>
+      </c>
+      <c r="R151" t="n">
+        <v>475</v>
+      </c>
       <c r="T151" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:17.145185+00:00</t>
@@ -9880,7 +9901,7 @@
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>2026-06-02T17:39:15.150484+00:00</t>
+          <t>2026-06-02T18:25:26.260161+00:00</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9913,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9915,16 +9936,37 @@
           <t>7409 Bondsberry Ct, Boca Raton, FL 33434</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>{"total_amount": 475.0, "services": [{"name": "Land Survey Only", "description": "Boundary/land survey for LOT 11B, PLAT 2, HAMLET C AT BOCA WEST, 7409 Bondsberry Ct, Boca Raton, Palm Beach County. Lot size 0.12 acres (well under 0.31 ac threshold). FEMA Zone X \u2014 no flood zone complexity. Platted lot with recorded plat reference (PB 36, PG 127) \u2014 no metes and bounds complexity. No waterfront, canal, or heavy vegetation indicators from legal description. Pool builder context noted but no pool upcharge applied as this is a land survey only order with no topo or pool-specific field work indicated beyond standard boundary staking. Negotiated B2B rate applied per management agreement.", "amount": 475.0}], "pricing_reasoning": "The client has a management-approved negotiated rate of $475.00 for this B2B pool builder account. The property is a small platted lot (0.12 ac) in Palm Beach County with FEMA Zone X (no flood complexity), a clean plat-referenced legal description (no metes and bounds), and no indicators of waterfront, heavy vegetation, or other field complexity that would justify upcharges. The service is Land Survey Only with no Elevation Certificate requested, so no EC line item applies. Final price equals the negotiated base rate with no additions.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000270247 references the same property (7409 Bondsberry Court, Palm Beach County, Folio 00424709090110020) for the same service (Land Survey Only). Human review recommended before dispatching fieldwork.", "DUPLICATE_WARNING: Order 1000282847 references the same property (7409 Bondsberry Court, Palm Beach County, Folio 00424709090110020) for the same service (Land Survey Only). Human review recommended before dispatching fieldwork.", "ORDER_ON_HOLD: Notes indicate this order is currently On Hold with special pricing applied and no fieldwork or delivery dates scheduled. Confirm hold status before scheduling.", "NEW_CLIENT: Order count is 0 \u2014 first order from Broward Palm Beach Pool Builder despite OLD_TITLE tier designation. Verify client tier classification and negotiated rate approval prior to invoicing."]}</t>
+        </is>
+      </c>
       <c r="H152" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202511251809119873, "created_at": "2025-11-25T13:23:05", "customer_email": "bpbpoolbuilder@yahoo.com", "customer_id": 202511251809359010, "customer_name": "Meghan  Julien", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0968F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000275133, "paid": false, "property_address": "7409 BONDSBERRY CT", "property_city": "BOCA RATON", "property_county": "PALM BEACH COUNTY", "property_lat": "26.380752", "property_lng": "-80.1605202", "property_state": "FLORIDA", "property_zip": "33434", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275133", "customer_email": "bpbpoolbuilder@yahoo.com", "service_type": "Land Survey Only", "county": "", "property_address": "7409 BONDSBERRY CT", "customer_name": "Broward Palm Beach Pool Builder"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Broward Palm Beach Pool Builder", "confidence": "MEDIUM"}, "client_email": {"value": "bpbpoolbuilder@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "7409 Bondsberry Ct, Boca Raton, FL 33434", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; likely a boundary survey for pool permitting given the b2b pool builder client context"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; pool likely planned given client is a pool builder, but not confirmed from data"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Legal description not provided", "Lot size unknown", "Structure square footage unknown", "Property features and existing improvements unknown", "Reason for On Hold status not specified", "No matching emails found to supplement order details", "County property appraiser data unavailable", "Client name conflict: order contact is 'Meghan Julien' but company name is 'Broward Palm Beach Pool Builder' \u2014 confirm correct billing name", "Scope of survey not fully defined (boundary, staking, as-built?)", "No fieldwork or delivery date scheduled"], "summary": "B2B land survey order for pool builder client at 7409 Bondsberry Ct, Boca Raton (Palm Beach County) currently On Hold with special pricing applied and no fieldwork or delivery dates scheduled."}}</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>1780424598455</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>2026-06-02T17:39:25.418643+00:00</t>
         </is>
       </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:25:46.157812+00:00</t>
+        </is>
+      </c>
+      <c r="R152" t="n">
+        <v>475</v>
+      </c>
       <c r="T152" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:17.209602+00:00</t>
@@ -9932,7 +9974,7 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>2026-06-02T17:39:25.465949+00:00</t>
+          <t>2026-06-02T18:25:46.213538+00:00</t>
         </is>
       </c>
     </row>
@@ -9944,7 +9986,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9967,16 +10009,37 @@
           <t>3010 NE 43RD ST, Fort Lauderdale, FL 33308</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>{"total_amount": 750.0, "services": [{"name": "Boundary / Land Survey", "description": "Standard residential boundary survey for Lot 2, Block K, Coral Ridge Country Club Addition No. 3 \u2014 platted lot, 0.21 acres, Broward County. Base rate for individual/direct client.", "amount": 475.0}, {"name": "Elevation Certificate (EC)", "description": "FEMA Flood Zone AE (panel 12011C0386J, effective 07/31/2024), base elevation 7 ft. EC required given AE designation. Standard EC rate applies; no VE coastal surcharge.", "amount": 275.0}], "pricing_reasoning": "The property is a 0.21-acre platted residential lot in Broward County with a clean legal description (Lot/Block from recorded plat), well within the standard lot size threshold \u2014 no lot-size upcharge applies. No indicators of pool, waterfront canal, heavy vegetation, metes-and-bounds, or Monroe County mobilization from the available data, so no complexity upcharges are warranted. The FEMA Zone AE designation warrants an Elevation Certificate alongside the boundary survey, priced at the fixed $275.00 EC rate with no VE surcharge. The combined total is $475.00 + $275.00 = $750.00.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE WARNING: Order 1000271043 at the same address (3010 NE 43RD ST, Broward County, Folio 494224100580) was previously quoted/ordered for Land Survey AND Elevation Certificate \u2014 human review required before processing to avoid duplicate billing or redundant fieldwork.", "DUPLICATE WARNING: Order 1000273191 at the same address (3010 NE 43RD ST, Broward County, Folio 494224100580) was previously quoted/ordered for Land Survey Only \u2014 human review required to determine whether this order is superseded or distinct.", "Service type not explicitly confirmed by client \u2014 order notes indicate no specific survey service was selected. Pricing assumes standard Boundary Survey + EC based on AE flood zone context; confirm with client before invoicing.", "Aerial imagery and property feature data (pool, waterfront, vegetation) were not available for independent verification \u2014 complexity assessment based on lot size and legal description only. Confidence adjusted to MEDIUM accordingly."]}</t>
+        </is>
+      </c>
       <c r="H153" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510162101520333, "created_at": "2025-11-25T15:56:05", "customer_email": "mdbolanos@gmail.com", "customer_id": 202510162101520438, "customer_name": "Michael  Bolanos", "customer_type": "individual", "delivered_at": "2025-11-26T14:44:51", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0386J\nZONE: AE\nELEV: 07 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000275111, "paid": false, "property_address": "3010 NE 43RD ST", "property_city": "FORT LAUDERDALE", "property_county": "Broward County", "property_lat": "26.1816949", "property_lng": "-80.10664729999999", "property_state": "FL", "property_zip": "33308", "service_type": "Quote", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000275111", "customer_email": "mdbolanos@gmail.com", "service_type": "Quote", "county": "", "property_address": "3010 NE 43RD ST", "customer_name": "Michael Bolanos"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Michael Bolanos", "confidence": "HIGH"}, "client_email": {"value": "mdbolanos@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "3010 NE 43RD ST, Fort Lauderdale, FL 33308", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "MEDIUM", "notes": "Service type is listed as 'Quote' \u2014 no specific survey service has been confirmed or selected yet. Actual service scope is unknown."}, "special_requirements": {"value": "Property is in FEMA Flood Zone AE (Panel 12011C0386J, Effective 07/31/2024, Base Flood Elevation 7 ft). Elevation Certificate flag is currently set to false.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available and no emails or attachments provided. Pool, structures, lot features unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service(s) requested have not been confirmed \u2014 order is still in Quote stage", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fences, etc.) unknown", "No matching emails found to clarify scope or client intent", "Invoice has not been generated and payment has not been collected", "Fieldwork has not been scheduled (fieldwork_at is null)"], "summary": "Residential quote request for a property at 3010 NE 43rd St, Fort Lauderdale in FEMA Flood Zone AE \u2014 no specific survey service confirmed yet, and key property details including lot size, legal description, and features are unavailable."}}</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1780424772730</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>2026-06-02T17:39:36.359413+00:00</t>
         </is>
       </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:26:14.875114+00:00</t>
+        </is>
+      </c>
+      <c r="R153" t="n">
+        <v>750</v>
+      </c>
       <c r="T153" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:17.275418+00:00</t>
@@ -9984,7 +10047,7 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>2026-06-02T17:39:36.407736+00:00</t>
+          <t>2026-06-02T18:26:14.930235+00:00</t>
         </is>
       </c>
     </row>
@@ -11868,7 +11931,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11883,12 +11946,22 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>DULAND DESIGN</t>
+          <t>Chang Du / DuLand Design</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>9710 STIRLING RD</t>
+          <t>9710 Stirling Rd, Hollywood, FL 33024</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202509181750086239, "created_at": "2025-09-18T13:54:02", "customer_email": "cdu@dulanddesign.com", "customer_id": 202509181750442459, "customer_name": "Chang Du", "customer_type": "b2b", "delivered_at": "2025-09-29T14:31:16", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0545J\nZONE: AE\nELEV: 06 FT\nZONE: X500\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000271752, "paid": false, "property_address": "9710 STIRLING RD", "property_city": "HOLLYWOOD", "property_county": "Broward County", "property_lat": "26.0439615", "property_lng": "-80.275818", "property_state": "FL", "property_zip": "33024", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000271752", "customer_email": "cdu@dulanddesign.com", "service_type": "Quote", "county": "", "property_address": "9710 STIRLING RD", "customer_name": "DULAND DESIGN"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Chang Du / DuLand Design", "confidence": "HIGH"}, "client_email": {"value": "cdu@dulanddesign.com", "confidence": "HIGH"}, "property_address": {"value": "9710 Stirling Rd, Hollywood, FL 33024", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., boundary, topographic, ALTA) has been identified. Needs clarification."}, "special_requirements": {"value": "Special pricing applied; property is in FEMA flood zones AE (elev. 6 ft) and X500 per FIRM panel 12011C0545J (eff. 07/31/2024)", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 no aerial, appraiser, or email data provided. Pool, shed, driveways, and other structures unknown."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not identified \u2014 'Quote' is not a deliverable", "Lot size unknown \u2014 no appraiser or parcel data available", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, fencing, driveways) unknown \u2014 no aerial or appraiser data", "No matching emails found to clarify scope or requirements", "Invoice has not been created and order is marked unpaid \u2014 pricing not finalized", "Fieldwork date not scheduled"], "summary": "B2B quote request from Chang Du / DuLand Design for a property at 9710 Stirling Rd, Hollywood, FL (Broward County) located in FEMA flood zones AE and X500, with special pricing applied but no specific survey service type identified."}}</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:24:22.222706+00:00</t>
         </is>
       </c>
       <c r="T190" t="inlineStr">
@@ -11898,7 +11971,7 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:13.796985+00:00</t>
+          <t>2026-06-02T18:24:22.277684+00:00</t>
         </is>
       </c>
     </row>
@@ -11910,7 +11983,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11930,7 +12003,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>154 4TH AVE N</t>
+          <t>154 4TH AVE N, Naples, FL 34102</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508111951313896, "created_at": "2025-09-17T11:10:03", "customer_email": "DrewH@cgunlimited.com", "customer_id": 202508111951313990, "customer_name": "Drew Hemmer", "customer_type": "individual", "delivered_at": "2025-09-29T14:21:14", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12021C0393J\nZONE: AE\nELEV: 09 FT\nEFF: 02/08/2024", "invoiced": false, "order_id": 1000271665, "paid": true, "property_address": "154 4TH AVE N", "property_city": "NAPLES", "property_county": "COLLIER COUNTY", "property_lat": "26.1502688", "property_lng": "-81.8064067", "property_state": "FL", "property_zip": "34102", "service_type": "Land Survey Only", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000271665", "customer_email": "DrewH@cgunlimited.com", "service_type": "Land Survey Only", "county": "", "property_address": "154 4TH AVE N", "customer_name": "Drew Hemmer"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Drew Hemmer", "confidence": "HIGH"}, "client_email": {"value": "DrewH@cgunlimited.com", "confidence": "HIGH"}, "property_address": {"value": "154 4TH AVE N, Naples, FL 34102", "confidence": "HIGH"}, "property_county": {"value": "Collier County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data; no elevation certificate requested."}, "special_requirements": {"value": "Property is in FEMA Flood Zone AE (Panel 12021C0393J, effective 02/08/2024, base flood elevation 9 ft). No elevation certificate ordered.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided."}, "client_tier": {"value": "residential", "confidence": "MEDIUM", "notes": "Customer type listed as 'individual'; email domain (cgunlimited.com) suggests possible business affiliation but order is filed as individual."}, "urgency": {"value": "normal", "confidence": "MEDIUM", "notes": "No rush indicators present; order created 2025-09-17 and delivered 2025-09-29, approximately 12 days turnaround."}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided \u2014 needs appraiser lookup or legal description review", "Legal description not available \u2014 county property appraiser data unavailable", "Structure square footage unknown \u2014 no appraiser or aerial data", "Property features (pool, structures, etc.) unknown \u2014 no supporting data sources", "No matching emails found \u2014 unable to confirm scope or any client communications", "Client business affiliation unclear \u2014 email domain suggests company but filed as individual", "Invoice not yet generated (invoiced: false) \u2014 pricing needs to be confirmed"], "summary": "Individual client Drew Hemmer has a delivered Land Survey Only order for a residential property at 154 4th Ave N, Naples, FL 34102 (Collier County), located in FEMA Flood Zone AE, with payment received but invoice not yet generated."}}</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:24:34.227779+00:00</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
@@ -11940,7 +12023,7 @@
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:13.869655+00:00</t>
+          <t>2026-06-02T18:24:34.284463+00:00</t>
         </is>
       </c>
     </row>
@@ -11952,7 +12035,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11972,7 +12055,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>212/224 COMMERCIAL WAY</t>
+          <t>212/224 Commercial Way, Sebring, FL 33876</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202412091849570674, "created_at": "2025-09-16T10:12:02", "customer_email": "erick@rackelectric.com", "customer_id": 202509161408325543, "customer_name": "Erick Salasblanca", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12055C0261C\nZONE: X\nEFF: 11/18/2015", "invoiced": false, "order_id": 1000271564, "paid": true, "property_address": "212/224 COMMERCIAL WAY", "property_city": "SEBRING", "property_county": "Highlands County", "property_lat": "27.435872", "property_lng": "-81.3714559", "property_state": "FL", "property_zip": "33876", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000271564", "customer_email": "erick@rackelectric.com", "service_type": "CAD file", "county": "", "property_address": "212/224 COMMERCIAL WAY", "customer_name": "Rack Electric LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Rack Electric LLC", "confidence": "HIGH"}, "client_email": {"value": "erick@rackelectric.com", "confidence": "HIGH"}, "property_address": {"value": "212/224 Commercial Way, Sebring, FL 33876", "confidence": "HIGH"}, "property_county": {"value": "Highlands County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type listed as 'CAD file'; no additional services specified. Unclear if CAD file is a standalone deliverable or part of a broader survey scope."}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference. Property appears to be commercial (212/224 dual address suggests multi-unit or multi-parcel site)."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing", "Structure square footage unknown", "Property features unknown (no aerial, appraiser, or email data)", "Scope of CAD file request unclear \u2014 is this a new survey or conversion of existing data?", "Dual address (212/224) suggests possible multi-parcel or multi-unit site \u2014 parcel count and relationship unclear", "Fieldwork date not scheduled", "Reason for On Hold status not documented", "No matching emails found \u2014 no correspondence to clarify scope or requirements"], "summary": "B2B CAD file order for Rack Electric LLC at a commercial dual-address property in Sebring, FL, currently On Hold with special pricing applied and no fieldwork scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:24:44.951873+00:00</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
@@ -11982,7 +12075,7 @@
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:13.942686+00:00</t>
+          <t>2026-06-02T18:24:45.007947+00:00</t>
         </is>
       </c>
     </row>
@@ -11994,7 +12087,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12009,12 +12102,22 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Margarita Fonrodona- Hernandez</t>
+          <t>Margarita Fonrodona-Hernandez</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2004 EMBASSY DR</t>
+          <t>2004 Embassy Dr, West Palm Beach, FL 33401</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202509111431590507, "created_at": "2025-09-11T10:35:04", "customer_email": "artmargfon@hotmail.com", "customer_id": 202509111431591782, "customer_name": "Margarita Fonrodona- Hernandez", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0577F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000271330, "paid": true, "property_address": "2004 EMBASSY DR", "property_city": "WEST PALM BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.7319748", "property_lng": "-80.07874500000001", "property_state": "FL", "property_zip": "33401", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000271330", "customer_email": "artmargfon@hotmail.com", "service_type": "CAD file", "county": "", "property_address": "2004 EMBASSY DR", "customer_name": "Margarita Fonrodona- Hernandez"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Margarita Fonrodona-Hernandez", "confidence": "HIGH"}, "client_email": {"value": "artmargfon@hotmail.com", "confidence": "HIGH"}, "property_address": {"value": "2004 Embassy Dr, West Palm Beach, FL 33401", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file' in order data. No additional services indicated."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments found to reference pool, shed, driveways, or other structures."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Order is On Hold \u2014 reason for hold not specified; human review required to release or cancel", "Lot size not available \u2014 county appraiser data unavailable", "Legal description not available \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, etc.)", "No county provided in the secondary county field (blank string), though Palm Beach County is in the main order data", "No fieldwork date scheduled (fieldwork_at is null)", "No delivery date set (delivered_at is null)", "Invoice has not been sent (invoiced: false, estimate_sent: false) despite order being marked paid \u2014 may need reconciliation", "Special pricing flag is true but no pricing details or approval notes are documented"], "summary": "Individual residential client Margarita Fonrodona-Hernandez has a paid but uninvoiced CAD file order for 2004 Embassy Dr, West Palm Beach, FL currently On Hold with special pricing applied and no fieldwork or delivery dates scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:24:56.597124+00:00</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
@@ -12024,7 +12127,7 @@
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:14.015940+00:00</t>
+          <t>2026-06-02T18:24:56.652613+00:00</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12139,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12056,7 +12159,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>1316 PAR VIEW DR</t>
+          <t>1316 Par View Dr, Sanibel, FL 33957</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202509111246481804, "created_at": "2025-09-11T08:50:03", "customer_email": "heatherament@amentconstructioninc.com", "customer_id": 202509111247296142, "customer_name": "Heather Ament", "customer_type": "b2b", "delivered_at": "2025-09-18T17:45:04", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12071C0541G \nZONE: AE\nELEV: 11 FT\nEFF: 11/17/2022", "invoiced": false, "order_id": 1000271318, "paid": true, "property_address": "1316 PAR VIEW DR", "property_city": "SANIBEL", "property_county": "LEE COUNTY", "property_lat": "26.435652", "property_lng": "-82.05376749999999", "property_state": "FL", "property_zip": "33957", "service_type": "CAD file", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000271318", "customer_email": "heatherament@amentconstructioninc.com", "service_type": "CAD file", "county": "", "property_address": "1316 PAR VIEW DR", "customer_name": "Ament Construction, INC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Ament Construction, INC", "confidence": "HIGH"}, "client_email": {"value": "heatherament@amentconstructioninc.com", "confidence": "HIGH"}, "property_address": {"value": "1316 Par View Dr, Sanibel, FL 33957", "confidence": "HIGH"}, "property_county": {"value": "Lee County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated in the data"}, "special_requirements": {"value": "Special pricing applies; flood zone AE at 11 ft elevation (FIRM panel 12071C0541G, eff. 11/17/2022)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or aerial data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, driveways, structures) unknown \u2014 no appraiser or aerial data available", "County appraiser data unavailable (no county was passed to lookup)", "No matching emails found to supplement order details", "Fieldwork date not scheduled (fieldwork_at is null)", "Invoice has not been sent despite order being delivered and paid"], "summary": "B2B CAD file order for Ament Construction, INC at 1316 Par View Dr, Sanibel, FL (Lee County, Flood Zone AE) \u2014 delivered and paid with special pricing, but missing lot size, legal description, and property feature details."}}</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:25:06.667894+00:00</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
@@ -12066,7 +12179,7 @@
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:14.090852+00:00</t>
+          <t>2026-06-02T18:25:06.724420+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -12191,7 +12191,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12211,7 +12211,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>904 NE 2ND ST</t>
+          <t>904 NE 2ND ST, BOCA RATON, FL 33432</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202509101831535164, "created_at": "2025-09-15T14:38:00", "customer_email": "shohreh0615@gmail.com", "customer_id": 202509101831535271, "customer_name": "SHOHREH HANSON", "customer_type": "individual", "delivered_at": "2025-09-26T17:40:31", "due_amount": 0.0, "elevation_cert": true, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C1177G\nZONE: X\nZONE: X500\nZONE: AE\nELEV: 06 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000271297, "paid": false, "property_address": "904 NE 2ND ST", "property_city": "BOCA RATON", "property_county": "PALM BEACH COUNTY", "property_lat": "26.3524813", "property_lng": "-80.0726447", "property_state": "FL", "property_zip": "33432", "service_type": "Elevation Certificate", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000271297", "customer_email": "shohreh0615@gmail.com", "service_type": "Elevation Certificate", "county": "", "property_address": "904 NE 2ND ST", "customer_name": "SHOHREH HANSON"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "SHOHREH HANSON", "confidence": "HIGH"}, "client_email": {"value": "shohreh0615@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "904 NE 2ND ST, BOCA RATON, FL 33432", "confidence": "HIGH"}, "property_county": {"value": "PALM BEACH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Elevation Certificate"], "confidence": "HIGH", "notes": "Service type explicitly stated as Elevation Certificate; elevation_cert flag is true; flood zone data includes AE zone which typically requires an EC for lending/insurance purposes."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, outbuildings)", "Special requirements or client notes not provided", "County property appraiser data unavailable", "No matching emails found for additional context", "Order is marked delivered but not invoiced \u2014 invoice amount unknown", "Fieldwork date is null \u2014 confirm fieldwork was completed prior to delivery"], "summary": "Residential Elevation Certificate order for Shohreh Hanson at 904 NE 2nd St, Boca Raton, FL 33432 (Palm Beach County), located in a multi-zone flood area including AE and X500 zones; order is marked delivered but remains uninvoiced."}}</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:30:23.080339+00:00</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
@@ -12221,7 +12231,7 @@
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:14.164776+00:00</t>
+          <t>2026-06-02T18:30:23.132688+00:00</t>
         </is>
       </c>
     </row>
@@ -12233,7 +12243,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12253,7 +12263,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>7110 LONGBOAT DR E</t>
+          <t>7110 Longboat Dr E, Longboat Key, FL 34228</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202509091540077254, "created_at": "2025-09-09T11:42:02", "customer_email": "Kenny@highloads.com", "customer_id": 202509091540079293, "customer_name": "Kenny Mungle", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12081C0283F \nZONE: AE\nELEV: 09 FT\nEFF: 08/10/2021", "invoiced": false, "order_id": 1000271199, "paid": true, "property_address": "7110 LONGBOAT DR E", "property_city": "LONGBOAT KEY", "property_county": "Manatee County", "property_lat": "27.4400328", "property_lng": "-82.68257009999999", "property_state": "FL", "property_zip": "34228", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000271199", "customer_email": "Kenny@highloads.com", "service_type": "CAD file", "county": "", "property_address": "7110 LONGBOAT DR E", "customer_name": "Kenny Mungle"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Kenny Mungle", "confidence": "HIGH"}, "client_email": {"value": "Kenny@highloads.com", "confidence": "HIGH"}, "property_address": {"value": "7110 Longboat Dr E, Longboat Key, FL 34228", "confidence": "HIGH"}, "property_county": {"value": "Manatee County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; likely based on existing survey data \u2014 scope of CAD deliverable should be clarified"}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); flood zone data present: FIRM Panel 12081C0283F, Zone AE, Base Flood Elevation 09 FT, effective 08/10/2021", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Reason order is On Hold \u2014 needs human review", "Exact scope of CAD file deliverable (as-built, boundary, topographic, etc.)", "Lot size not provided", "Legal description not provided", "Structure square footage unknown", "Property features (pool, structures, etc.) unknown \u2014 no appraiser or aerial data available", "No customer data returned from FTF customer lookup", "No matching emails found \u2014 no additional context from correspondence", "Special pricing details not specified \u2014 pricing basis unclear", "Invoice not yet sent and order not yet delivered \u2014 confirm readiness to proceed"], "summary": "Kenny Mungle (individual/residential) has a CAD file order on hold for 7110 Longboat Dr E, Longboat Key, FL (Manatee County), with special pricing applied and flood zone AE noted, but the order lacks legal description, lot size, property features, and a clear reason for the on-hold status."}}</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:30:35.212987+00:00</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
@@ -12263,7 +12283,7 @@
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:14.238902+00:00</t>
+          <t>2026-06-02T18:30:35.265099+00:00</t>
         </is>
       </c>
     </row>
@@ -12275,7 +12295,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12295,7 +12315,17 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2025 NE 22ND ST</t>
+          <t>2025 NE 22ND ST, WILTON MANORS, FL 33305</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202410031531256211, "created_at": "2025-09-09T10:50:00", "customer_email": "mcob1@icloud.com", "customer_id": 202410031531257152, "customer_name": "Michael Oberhelman", "customer_type": "individual", "delivered_at": "2025-09-16T13:19:19", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0386J\nZONE: AE\nELEV: 07 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000271188, "paid": true, "property_address": "2025 NE 22ND ST", "property_city": "WILTON MANORS", "property_county": "BROWARD COUNTY", "property_lat": "26.1570821", "property_lng": "-80.12000669999999", "property_state": "FL", "property_zip": "33305", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000271188", "customer_email": "mcob1@icloud.com", "service_type": "Land Survey Only", "county": "", "property_address": "2025 NE 22ND ST", "customer_name": "Michael Oberhelman"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Michael Oberhelman", "confidence": "HIGH"}, "client_email": {"value": "mcob1@icloud.com", "confidence": "HIGH"}, "property_address": {"value": "2025 NE 22ND ST, WILTON MANORS, FL 33305", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing applied; property is in FEMA Flood Zone AE (Panel 12011C0386J, effective 07/31/2024, base flood elevation 7 ft)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial imagery, or email attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser or parcel data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, fences, driveways, etc.) unknown \u2014 no aerial or appraiser data", "No matching emails found to supplement order details", "County field was blank in top-level FTF data (populated only from nested data object)"], "summary": "Individual residential client Michael Oberhelman has ordered a Land Survey Only for 2025 NE 22ND ST, Wilton Manors, FL 33305 (Broward County), with special pricing applied; the order is delivered and paid, but lot size, legal description, and property features require human lookup."}}</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:30:45.649554+00:00</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
@@ -12305,7 +12335,7 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:14.366606+00:00</t>
+          <t>2026-06-02T18:30:45.702229+00:00</t>
         </is>
       </c>
     </row>
@@ -12317,7 +12347,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12332,12 +12362,22 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLIAM  STANLEY </t>
+          <t>WILLIAM STANLEY</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>517 SW AVENUE B PL</t>
+          <t>517 SW AVENUE B PL, BELLE GLADE, FL 33430</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202405221708471339, "created_at": "2025-08-25T12:11:03", "customer_email": "wstanley740@gmail.com", "customer_id": 202405221708474273, "customer_name": "WILLIAM  STANLEY", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0466F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000270408, "paid": true, "property_address": "517 SW AVENUE B PL", "property_city": "BELLE GLADE", "property_county": "Palm Beach County", "property_lat": "26.68484", "property_lng": "-80.67325989999999", "property_state": "FL", "property_zip": "33430", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000270408", "customer_email": "wstanley740@gmail.com", "service_type": "CAD file", "county": "", "property_address": "517 SW AVENUE B PL", "customer_name": "WILLIAM  STANLEY "}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "WILLIAM STANLEY", "confidence": "HIGH"}, "client_email": {"value": "wstanley740@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "517 SW AVENUE B PL, BELLE GLADE, FL 33430", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type listed as 'CAD file' in FTF order data; no additional services indicated."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11).", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no matching emails found."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, driveways, etc.) unknown", "Order is On Hold \u2014 reason for hold not specified; human review needed", "No fieldwork or delivery dates scheduled", "No supporting emails found to clarify scope or requirements", "CAD file service type may need clarification on what base data or survey it references"], "summary": "Individual residential client William Stanley has a paid CAD file order for 517 SW Avenue B PL, Belle Glade, FL (Palm Beach County) currently on hold with special pricing applied and no fieldwork or delivery dates set."}}</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:30:55.199807+00:00</t>
         </is>
       </c>
       <c r="T198" t="inlineStr">
@@ -12347,7 +12387,7 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:14.441723+00:00</t>
+          <t>2026-06-02T18:30:55.252653+00:00</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12399,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12379,7 +12419,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>1260 99TH ST</t>
+          <t>1260 99TH ST, BAY HARBOR ISLANDS, FL 33154</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508221452339270, "created_at": "2025-08-22T10:54:01", "customer_email": "innagranik@yahoo.com", "customer_id": 202508221452340282, "customer_name": "INNA BARUKHIN", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0144L\nZONE: AE\nELEV: 08 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000270324, "paid": true, "property_address": "1260 99TH ST", "property_city": "BAY HARBOR ISLANDS", "property_county": "Miami-Dade County", "property_lat": "25.8888065", "property_lng": "-80.13610700000001", "property_state": "FL", "property_zip": "33154", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000270324", "customer_email": "innagranik@yahoo.com", "service_type": "CAD file", "county": "", "property_address": "1260 99TH ST", "customer_name": "INNA BARUKHIN"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "INNA BARUKHIN", "confidence": "HIGH"}, "client_email": {"value": "innagranik@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "1260 99TH ST, BAY HARBOR ISLANDS, FL 33154", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type listed as 'CAD file'; likely a CAD drawing of an existing survey. No additional services indicated."}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); flood zone AE with base elevation 8 ft (FIRM panel 12086C0144L, effective 09/11/2009)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available; no emails or attachments to reference. Pool, structures, lot features unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Order is On Hold \u2014 reason for hold not specified; human review needed", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, driveways, etc.)", "No matching emails found \u2014 scope clarification or any attachments from client are absent", "CAD file scope unclear \u2014 needs confirmation of what the CAD output is based on (existing survey, new fieldwork, etc.)", "Fieldwork date not scheduled (fieldwork_at is null)", "Invoice has not been sent (invoiced: false) despite paid: true \u2014 verify payment source and amount"], "summary": "Individual residential client INNA BARUKHIN has ordered a CAD file for 1260 99th St, Bay Harbor Islands, FL (Miami-Dade, flood zone AE) with special pricing applied, but the order is currently On Hold with no fieldwork scheduled and missing lot/legal/property details."}}</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:31:07.586116+00:00</t>
         </is>
       </c>
       <c r="T199" t="inlineStr">
@@ -12389,7 +12439,7 @@
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:14.516765+00:00</t>
+          <t>2026-06-02T18:31:07.651308+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -10059,7 +10059,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -10082,16 +10082,37 @@
           <t>4177 S CONGRESS AVE, PALM SPRINGS, FL 33461</t>
         </is>
       </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>{"total_amount": 725.0, "services": [{"name": "CAD File / Boundary Survey", "description": "Negotiated base survey rate for JMJC Real Property Management per management-agreed pricing.", "amount": 450.0}, {"name": "Lot Size Complexity Upcharge (1.01\u20132.00 ac)", "description": "Property is 1.98 acres, falling within the 1.01\u20132.00 ac complexity tier. Increased field time, traversal, and drafting effort required relative to a standard residential lot.", "amount": 275.0}], "pricing_reasoning": "The service requested is a CAD file deliverable, treated as a standard boundary/survey product. The client has a management-negotiated base rate of $450.00. The property is 1.98 acres (within the 1.01\u20132.00 ac tier), warranting a $275.00 lot size complexity upcharge. The FEMA flood zone is AE (not VE), so no EC was requested and no coastal surcharge applies. No other complexity factors (Monroe County, pool, waterfront canal, metes-and-bounds, heavy vegetation) are indicated by the data provided, though the legal description references a recorded easement which is noted but does not independently trigger an upcharge. Total invoice is $725.00.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["Order is marked On Hold with special pricing noted \u2014 confirm management approval before releasing invoice.", "Legal description references an easement (O.R. Book 16477, Page 315); ensure easement is accounted for in CAD deliverable and field work scope.", "Order count for JMJC Real Property Management is 0 \u2014 new client relationship despite OLD_TITLE tier designation; verify negotiated rate confirmation on file."]}</t>
+        </is>
+      </c>
       <c r="H154" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202511181413190943, "created_at": "2025-11-18T09:34:00", "customer_email": "LisaD@cwcrecovery.com", "customer_id": 202511181419117120, "customer_name": "Lisa DiFiori", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0777F\nZONE: AE\nELEV: 13 FT\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000274741, "paid": true, "property_address": "4177 S CONGRESS AVE", "property_city": "PALM SPRINGS", "property_county": "Palm Beach County", "property_lat": "26.6146897", "property_lng": "-80.0907272", "property_state": "FL", "property_zip": "33461", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274741", "customer_email": "LisaD@cwcrecovery.com", "service_type": "CAD file", "county": "", "property_address": "4177 S CONGRESS AVE", "customer_name": "JMJC REAL PROPERTY MANAGEMENT, LLC."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "JMJC REAL PROPERTY MANAGEMENT, LLC.", "confidence": "MEDIUM"}, "client_email": {"value": "LisaD@cwcrecovery.com", "confidence": "HIGH"}, "property_address": {"value": "4177 S CONGRESS AVE, PALM SPRINGS, FL 33461", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold; flood zone AE at 13 ft elevation (FIRM panel 12099C0777F, eff. 10/05/2017)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order customer_name is 'Lisa DiFiori' but top-level customer_name is 'JMJC REAL PROPERTY MANAGEMENT, LLC.' \u2014 needs human clarification on billing entity", "No customer/company profile data returned from FTF customer lookup", "No matching emails found to corroborate order details", "County property appraiser data unavailable \u2014 lot size, legal description, and property features unknown", "Structure square footage not provided", "Lot size not provided", "Legal description not provided", "Property features (pool, shed, structures, etc.) unknown", "Urgency/deadline not specified", "Order is On Hold \u2014 reason for hold not documented", "Scope of CAD file deliverable not defined (boundary, topo, as-built, etc.)"], "summary": "B2B order for a CAD file deliverable at 4177 S Congress Ave, Palm Springs, FL (Palm Beach County) for JMJC Real Property Management / Lisa DiFiori, currently On Hold with special pricing applied and flood zone AE designation noted."}}</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1780425425409</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>2026-06-02T17:39:48.299993+00:00</t>
         </is>
       </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:37:07.872486+00:00</t>
+        </is>
+      </c>
+      <c r="R154" t="n">
+        <v>725</v>
+      </c>
       <c r="T154" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:17.337024+00:00</t>
@@ -10099,7 +10120,7 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>2026-06-02T17:39:48.348268+00:00</t>
+          <t>2026-06-02T18:37:07.930221+00:00</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10132,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10134,16 +10155,37 @@
           <t>8608 N 13TH ST, TAMPA, FL 33604</t>
         </is>
       </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>{"total_amount": 475.0, "services": [{"name": "Boundary/Land Survey", "description": "Standard residential boundary survey for 0.26-acre lot at 8608 N 13TH ST, Tampa, Hillsborough County. Legal description references a platted lot with an abutting closed alley (East 1/2), which is straightforward platted work. FEMA Zone X \u2014 no EC required. No complexity upcharges warranted by lot size (0.26 ac &lt; 0.31 ac threshold), county, or zone.", "amount": 475.0}], "pricing_reasoning": "This is a first-time individual client (Yani Escobar, 0 prior orders) with no negotiated rate, so the $475.00 default individual base rate applies. The 0.26-acre platted lot in Hillsborough County falls below the 0.31-acre upcharge threshold, FEMA Zone X requires no Elevation Certificate, and the legal description (platted lot plus East 1/2 of a closed alley by ordinance) is moderately routine \u2014 no metes-and-bounds, no waterfront, no Monroe County, no pool flagged. No complexity upcharges are supported by the available data. However, the specific service type was never confirmed by the client, and three prior orders exist for this exact property covering Quote, Topo, and Land Survey services, which requires human review before proceeding.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "No specific survey service has been confirmed by the client \u2014 this is a quote request only with no stated service type. Additionally, three prior orders exist for the identical property and folio (Quote #1000266719, Topo Survey #1000265351, Land Survey #1000273906), creating a strong likelihood of a duplicate or redundant order. A human reviewer should contact Yani Escobar to confirm the desired service and cross-reference against the open/completed prior orders before issuing any invoice.", "flags": ["DUPLICATE_SUSPECTED: Order 1000265351 \u2014 same address 8608 N 13TH ST, Hillsborough County \u2014 service: Topography Survey \u2014 same coordinates (28.0285022, -82.4465867) and folio A-19-28-19-45C-000004-00003.0", "DUPLICATE_SUSPECTED: Order 1000266719 \u2014 same address 8608 N 13TH ST, Hillsborough County \u2014 service: Quote \u2014 same coordinates and folio", "DUPLICATE_SUSPECTED: Order 1000273906 \u2014 same address 8608 N 13TH ST, Hillsborough County \u2014 service: Land Survey Only \u2014 same coordinates and folio", "SERVICE_TYPE_UNCONFIRMED: Client submitted a quote request but did not specify Boundary Survey, Topo, EC, or combined service \u2014 clarification required before finalizing price", "NEW_CLIENT: Yani Escobar has 0 prior orders; default individual rate of $475.00 applied"]}</t>
+        </is>
+      </c>
       <c r="H155" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510311717570490, "created_at": "2025-11-14T14:39:05", "customer_email": "yaniescobar@realtyblu.com", "customer_id": 202510311717570589, "customer_name": "Yani Escobar", "customer_type": "individual", "delivered_at": "2025-11-18T18:43:34", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12057C0214J\nZONE: X\nEFF: 10/07/2021", "invoiced": false, "order_id": 1000274628, "paid": true, "property_address": "8608 N 13TH ST", "property_city": "TAMPA", "property_county": "Hillsborough County", "property_lat": "28.0285022", "property_lng": "-82.4465867", "property_state": "FL", "property_zip": "33604", "service_type": "Quote", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274628", "customer_email": "yaniescobar@realtyblu.com", "service_type": "Quote", "county": "", "property_address": "8608 N 13TH ST", "customer_name": "Yani Escobar"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Yani Escobar", "confidence": "HIGH"}, "client_email": {"value": "yaniescobar@realtyblu.com", "confidence": "HIGH"}, "property_address": {"value": "8608 N 13TH ST, TAMPA, FL 33604", "confidence": "HIGH"}, "property_county": {"value": "Hillsborough County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed as 'Quote' only \u2014 no specific survey service has been confirmed or selected. Actual service needed is unclear."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided."}, "client_tier": {"value": "residential", "confidence": "MEDIUM"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not confirmed \u2014 'Quote' is not a deliverable service", "Lot size unknown \u2014 no appraiser data available", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, fences, etc.) unknown", "No fieldwork date scheduled (fieldwork_at is null)", "No special requirements or client notes captured", "Order is marked paid but invoiced=false \u2014 billing status should be reviewed"], "summary": "Yani Escobar submitted a quote request for a residential property at 8608 N 13TH ST, Tampa, FL (Hillsborough County, Flood Zone X), but no specific survey service has been identified and key property details are missing."}}</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1780425449437</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>2026-06-02T17:45:07.529876+00:00</t>
         </is>
       </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:37:31.273536+00:00</t>
+        </is>
+      </c>
+      <c r="R155" t="n">
+        <v>475</v>
+      </c>
       <c r="T155" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:17.400731+00:00</t>
@@ -10151,7 +10193,7 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>2026-06-02T17:45:07.570066+00:00</t>
+          <t>2026-06-02T18:37:31.379600+00:00</t>
         </is>
       </c>
     </row>
@@ -10163,7 +10205,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10186,16 +10228,37 @@
           <t>15645 Billy Goat Ln, Jupiter, FL 33478</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "AI pricing failed: Expecting ',' delimiter: line 17 column 4 (char 2878). Manual review required.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "AI pricing error \u2014 needs manual quote", "flags": ["ai_error"]}</t>
+        </is>
+      </c>
       <c r="H156" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510211619094511, "created_at": "2025-11-17T08:50:04", "customer_email": "christine.frechette@outlook.com", "customer_id": 202510211619095665, "customer_name": "Christine Frechette", "customer_type": "individual", "delivered_at": "2025-11-26T14:45:47", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0165F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000274600, "paid": true, "property_address": "15645 BILLY GOAT LN", "property_city": "JUPITER", "property_county": "Palm Beach County", "property_lat": "26.9074424", "property_lng": "-80.1947711", "property_state": "FL", "property_zip": "33478", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274600", "customer_email": "christine.frechette@outlook.com", "service_type": "Quote", "county": "", "property_address": "15645 BILLY GOAT LN", "customer_name": "Christine Frechette"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Christine Frechette", "confidence": "HIGH"}, "client_email": {"value": "christine.frechette@outlook.com", "confidence": "HIGH"}, "property_address": {"value": "15645 Billy Goat Ln, Jupiter, FL 33478", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 actual survey service(s) requested have not been specified. Human review needed to determine scope."}, "special_requirements": {"value": "Special pricing applies", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments found to infer pool, shed, driveways, or other structures."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Actual survey service(s) requested \u2014 'Quote' is not a survey type", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fencing, driveways, etc.) unknown", "No customer data record found (empty FTF customer object)", "No matching emails found to clarify scope or intent", "County appraiser lookup unavailable", "Fieldwork date not scheduled"], "summary": "Residential quote order for Christine Frechette at 15645 Billy Goat Ln, Jupiter, FL (Palm Beach County, Flood Zone X) marked as delivered and paid with special pricing, but the actual survey service type and property details remain unspecified and require human review."}}</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>1780425472629</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>2026-06-02T17:45:17.337285+00:00</t>
         </is>
       </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:37:54.847147+00:00</t>
+        </is>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
       <c r="T156" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:17.462755+00:00</t>
@@ -10203,7 +10266,7 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>2026-06-02T17:45:17.378354+00:00</t>
+          <t>2026-06-02T18:37:54.903890+00:00</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10278,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10238,16 +10301,37 @@
           <t>961 S Atlantic Dr, Lantana, FL 33462</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "The specific survey service requested has not been identified by the client \u2014 the order notes explicitly state that the service type requires human follow-up. No pricing can be responsibly proposed without knowing whether this is a boundary survey, elevation certificate, combined package, or topographic survey. Additionally, two likely duplicate orders exist for the same property and folio, which further requires human review before any quote is issued.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "Service type not identified: the client submitted a quote request but did not specify the survey service needed (boundary, EC, combined, topo, etc.). Human follow-up is required to determine scope before pricing can be applied. Additionally, two probable duplicate orders (1000264407 and 1000274591) exist for the same address, county, and folio number, suggesting this order may be redundant and should be reconciled before quoting.", "flags": ["SERVICE TYPE UNKNOWN: Client Robert Serr did not specify the survey service requested. Order notes confirm human follow-up is required before a quote can be issued.", "DUPLICATE DETECTED: Order 1000264407 \u2014 same address (961 S Atlantic Dr, Palm Beach County), same folio (40434503210001060), service: Land Survey and Elevation Certificate. Reconcile before quoting.", "DUPLICATE DETECTED: Order 1000274591 \u2014 same address (961 S Atlantic Dr, Palm Beach County), same folio (40434503210001060), service: Land Survey Only. Reconcile before quoting.", "FEMA ZONE AE noted at 9 ft elevation \u2014 relevant for EC pricing if an Elevation Certificate is ultimately requested (standard $275.00; no VE surcharge applies).", "New individual client \u2014 0 prior orders on file. Default individual base rate of $475.00 applies if a boundary survey is confirmed."]}</t>
+        </is>
+      </c>
       <c r="H157" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202511141422100772, "created_at": "2025-11-14T09:42:02", "customer_email": "robertjserr@gmail.com", "customer_id": 202511141422100868, "customer_name": "Robert Serr", "customer_type": "individual", "delivered_at": "2025-11-18T18:37:01", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0783G\nZONE: AE\nELEV: 09 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000274593, "paid": true, "property_address": "961 S ATLANTIC DR", "property_city": "LANTANA", "property_county": "Palm Beach County", "property_lat": "26.574442", "property_lng": "-80.0436335", "property_state": "FL", "property_zip": "33462", "service_type": "Quote", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274593", "customer_email": "robertjserr@gmail.com", "service_type": "Quote", "county": "", "property_address": "961 S ATLANTIC DR", "customer_name": "Robert Serr"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Robert Serr", "confidence": "HIGH"}, "client_email": {"value": "robertjserr@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "961 S Atlantic Dr, Lantana, FL 33462", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., boundary, elevation cert, topographic) has been identified. Human review needed to determine what was actually quoted."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available and no emails or attachments provided. Pool, shed, driveways, and other features unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service requested is unknown \u2014 'Quote' is not a deliverable service type", "No lot size available", "No legal description available", "No structure square footage available", "No property features data (pool, shed, outbuildings, etc.)", "No special requirements noted", "County property appraiser data unavailable", "No matching emails found to clarify scope", "Flood zone data present (AE, 09 ft, eff. 12/20/2024) but elevation certificate was not requested \u2014 unclear if relevant to quote"], "summary": "Individual residential client Robert Serr submitted a quote request for a property at 961 S Atlantic Dr, Lantana, FL (Palm Beach County), but the specific survey service requested has not been identified and requires human follow-up."}}</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1780425492268</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>2026-06-02T17:45:27.681522+00:00</t>
         </is>
       </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:38:15.043612+00:00</t>
+        </is>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
       <c r="T157" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:17.571374+00:00</t>
@@ -10255,7 +10339,7 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>2026-06-02T17:45:27.722030+00:00</t>
+          <t>2026-06-02T18:38:15.101595+00:00</t>
         </is>
       </c>
     </row>
@@ -12451,7 +12535,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12471,7 +12555,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>3682 SW BIMINI CIR N</t>
+          <t>3682 SW Bimini Cir N, Palm City, FL 34990</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508221308291707, "created_at": "2025-08-22T09:11:05", "customer_email": "alecpollum@outlook.com", "customer_id": 202508221308292694, "customer_name": "Alec Pollum", "customer_type": "individual", "delivered_at": "2025-08-28T16:42:50", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12085C0133H\nZONE: X\nEFF: 02/19/2020", "invoiced": false, "order_id": 1000270309, "paid": true, "property_address": "3682 SW BIMINI CIR N", "property_city": "PALM CITY", "property_county": "Martin County", "property_lat": "27.200644", "property_lng": "-80.3037523", "property_state": "FL", "property_zip": "34990", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000270309", "customer_email": "alecpollum@outlook.com", "service_type": "Quote", "county": "", "property_address": "3682 SW BIMINI CIR N", "customer_name": "Alec Pollum"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Alec Pollum", "confidence": "HIGH"}, "client_email": {"value": "alecpollum@outlook.com", "confidence": "HIGH"}, "property_address": {"value": "3682 SW Bimini Cir N, Palm City, FL 34990", "confidence": "HIGH"}, "property_county": {"value": "Martin County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., boundary, ALTA, elevation) has been identified. Needs human clarification on what survey product was quoted."}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 county appraiser data unavailable and no emails or attachments found."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not identified \u2014 'Quote' is not a deliverable service", "Lot size unknown \u2014 no appraiser data available", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, structures) unknown", "No matching emails found to clarify scope or client intent", "County was blank in outer FTF payload despite being present in order data \u2014 verify data consistency", "No invoice has been generated despite order being marked Paid and Delivered \u2014 needs review"], "summary": "Individual residential client Alec Pollum in Palm City, FL (Martin County) has a delivered and paid order with special pricing applied, but the specific survey service requested remains unclear as the order is categorized only as a 'Quote' with no invoice generated."}}</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:36:01.597658+00:00</t>
         </is>
       </c>
       <c r="T200" t="inlineStr">
@@ -12481,7 +12575,7 @@
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:14.592654+00:00</t>
+          <t>2026-06-02T18:36:01.655592+00:00</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12587,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12513,7 +12607,17 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2460 TRADE WINDS DR</t>
+          <t>2460 Trade Winds Dr, Dunedin, FL 34698</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508191540093736, "created_at": "2025-08-19T11:42:00", "customer_email": "Sunlandcustomhomes@gmail.com", "customer_id": 202508191540094781, "customer_name": "Matt Smoral", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12103C0066H\nZONE: AE\nELEV: 10 FT\nEFF: 08/24/2021", "invoiced": false, "order_id": 1000270101, "paid": true, "property_address": "2460 TRADE WINDS DR", "property_city": "DUNEDIN", "property_county": "Pinellas County", "property_lat": "28.0474152", "property_lng": "-82.78500149999999", "property_state": "FL", "property_zip": "34698", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000270101", "customer_email": "Sunlandcustomhomes@gmail.com", "service_type": "CAD file", "county": "", "property_address": "2460 TRADE WINDS DR", "customer_name": "Matt Smoral"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Matt Smoral", "confidence": "HIGH"}, "client_email": {"value": "Sunlandcustomhomes@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "2460 Trade Winds Dr, Dunedin, FL 34698", "confidence": "HIGH"}, "property_county": {"value": "Pinellas County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Only service type listed is CAD file; no additional services specified. Likely a CAD conversion or redraw of existing survey data."}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); flood zone AE with base flood elevation 10 ft per FIRM panel 12103C0066H effective 08/24/2021", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM", "notes": "Email domain 'Sunlandcustomhomes@gmail.com' suggests a custom home builder (Sunland Custom Homes); customer_type is listed as individual but business context is implied"}, "urgency": {"value": "normal", "confidence": "MEDIUM", "notes": "Order is On Hold; no rush indicators present"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not available \u2014 county appraiser data unavailable", "Legal description not available \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, etc.)", "Reason for On Hold status not documented", "Scope of CAD file request unclear \u2014 new CAD drawing, conversion, or redraw?", "No prior survey data or source files referenced", "Client type ambiguous \u2014 individual vs. business (Sunland Custom Homes)", "No invoice amount recorded despite paid = true and due_amount = 0.0 \u2014 confirm payment details"], "summary": "Matt Smoral (likely associated with Sunland Custom Homes) has placed an on-hold CAD file order for a flood zone AE property at 2460 Trade Winds Dr, Dunedin, FL with special pricing applied and no additional scope or property details available."}}</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:36:14.989256+00:00</t>
         </is>
       </c>
       <c r="T201" t="inlineStr">
@@ -12523,7 +12627,7 @@
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:14.668603+00:00</t>
+          <t>2026-06-02T18:36:15.045735+00:00</t>
         </is>
       </c>
     </row>
@@ -12535,7 +12639,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12555,7 +12659,17 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2198 MAYPORT RD</t>
+          <t>2198 Mayport Rd, Jacksonville, FL 32233</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508181437577823, "created_at": "2025-08-18T11:13:00", "customer_email": "creativecookmayport@gmail.com", "customer_id": 202508181437578974, "customer_name": "Taylor Pickett", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12031C0406J\nZONE: X\nEFF: 11/02/2018", "invoiced": false, "order_id": 1000270001, "paid": true, "property_address": "2198 MAYPORT RD", "property_city": "JACKSONVILLE", "property_county": "Duval County", "property_lat": "30.3464722", "property_lng": "-81.41389699999999", "property_state": "FL", "property_zip": "32233", "service_type": "Quote", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000270001", "customer_email": "creativecookmayport@gmail.com", "service_type": "Quote", "county": "", "property_address": "2198 MAYPORT RD", "customer_name": "Taylor Pickett"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Taylor Pickett", "confidence": "HIGH"}, "client_email": {"value": "creativecookmayport@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "2198 Mayport Rd, Jacksonville, FL 32233", "confidence": "HIGH"}, "property_county": {"value": "Duval County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service has been selected yet. Actual service needs to be confirmed with client."}, "special_requirements": {"value": "Special pricing flagged on order; order is currently On Hold", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available, no emails, and no aerial data provided. Pool, shed, driveways, and other features are unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not selected \u2014 order is only at Quote stage", "Reason for On Hold status unknown", "Special pricing details and authorization not documented", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown", "Structure square footage unknown", "Property features (pool, shed, outbuildings, etc.) unknown", "No fieldwork or delivery dates scheduled", "No matching email correspondence found to clarify scope or client intent", "County property appraiser data unavailable"], "summary": "Taylor Pickett has a residential quote on hold at 2198 Mayport Rd, Jacksonville FL 32233 (Duval County) with special pricing flagged, but no specific survey service has been selected and significant property details are missing."}}</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:36:25.270822+00:00</t>
         </is>
       </c>
       <c r="T202" t="inlineStr">
@@ -12565,7 +12679,7 @@
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:14.744168+00:00</t>
+          <t>2026-06-02T18:36:25.327566+00:00</t>
         </is>
       </c>
     </row>
@@ -12577,7 +12691,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12597,7 +12711,17 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>1413 NW LANCEWOOD TER</t>
+          <t>1413 NW LANCEWOOD TER, PALM CITY, FL 34990</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508151947593488, "created_at": "2025-08-15T15:47:00", "customer_email": "pfsgators@aol.com", "customer_id": 202508151947593584, "customer_name": "JEFFREY AND LISA DICKERSON", "customer_type": "individual", "delivered_at": "2025-08-23T15:56:49", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12111C0402K\nZONE: X\nEFF: 02/19/2020", "invoiced": false, "order_id": 1000269964, "paid": true, "property_address": "1413 NW LANCEWOOD TER", "property_city": "PALM CITY", "property_county": "ST LUCIE COUNTY", "property_lat": "27.2309785", "property_lng": "-80.3153093", "property_state": "FL", "property_zip": "34990", "service_type": "Land Survey Only", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000269964", "customer_email": "pfsgators@aol.com", "service_type": "Land Survey Only", "county": "", "property_address": "1413 NW LANCEWOOD TER", "customer_name": "JEFFREY AND LISA DICKERSON"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "JEFFREY AND LISA DICKERSON", "confidence": "HIGH"}, "client_email": {"value": "pfsgators@aol.com", "confidence": "HIGH"}, "property_address": {"value": "1413 NW LANCEWOOD TER, PALM CITY, FL 34990", "confidence": "HIGH"}, "property_county": {"value": "ST LUCIE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in FTF order data. No elevation certificate requested."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or emails present to infer features such as pool, shed, or structures."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided \u2014 needed for accurate pricing", "Legal description not available \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, etc.)", "Special requirements or access instructions not provided", "No county was passed to appraiser lookup \u2014 ST LUCIE COUNTY present in FTF but appraiser query returned unavailable", "No matching emails found \u2014 unable to verify additional client instructions or context"], "summary": "Residential land survey only order for Jeffrey and Lisa Dickerson at 1413 NW Lancewood Ter, Palm City, FL 34990 (St. Lucie County); order is paid and delivered, but property details such as lot size, legal description, and features are missing due to unavailable appraiser data."}}</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:36:35.647964+00:00</t>
         </is>
       </c>
       <c r="T203" t="inlineStr">
@@ -12607,7 +12731,7 @@
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:14.874199+00:00</t>
+          <t>2026-06-02T18:36:35.704316+00:00</t>
         </is>
       </c>
     </row>
@@ -12619,7 +12743,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12634,12 +12758,22 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Intercoastal Marine Construction</t>
+          <t>Bill Gould</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>329 REGATTA DR</t>
+          <t>329 Regatta Dr, Jupiter, FL 33477</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508151500329563, "created_at": "2025-08-15T11:11:05", "customer_email": "gould@williamgould.com", "customer_id": 202508151500582189, "customer_name": "Bill Gould", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0187G\nZONE: X500\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000269922, "paid": true, "property_address": "329 REGATTA DR", "property_city": "JUPITER", "property_county": "Palm Beach County", "property_lat": "26.915305", "property_lng": "-80.086714", "property_state": "FL", "property_zip": "33477", "service_type": "Quote", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000269922", "customer_email": "gould@williamgould.com", "service_type": "Quote", "county": "", "property_address": "329 REGATTA DR", "customer_name": "Intercoastal Marine Construction"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Bill Gould", "confidence": "HIGH"}, "client_email": {"value": "gould@williamgould.com", "confidence": "HIGH"}, "property_address": {"value": "329 Regatta Dr, Jupiter, FL 33477", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey type (boundary, topographic, ALTA, etc.) has been identified. Needs clarification."}, "special_requirements": {"value": "Special pricing flagged; order is On Hold (status code 11); flood zone data present: FIRM panel 12099C0187G, Zone X500 and Zone X, effective 12/20/2024", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available; no emails or attachments with site details. Pool, structures, driveways, and other features unknown."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service(s) requested not identified \u2014 only 'Quote' listed", "Lot size unknown \u2014 no appraiser data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, structures) unknown", "Urgency/deadline not specified", "Order is On Hold \u2014 reason for hold not documented", "Client name discrepancy: FTF order data shows 'Bill Gould' but outer customer_name field shows 'Intercoastal Marine Construction' \u2014 needs clarification on true client/billing entity", "No fieldwork or delivery dates set", "County field in outer FTF object is blank despite property_county being populated in data object"], "summary": "A b2b quote-stage order for Bill Gould (possible connection to Intercoastal Marine Construction) at 329 Regatta Dr, Jupiter, FL 33477 (Palm Beach County) is currently On Hold with special pricing flagged, but the specific survey service, lot details, and legal description are all unknown."}}</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:36:48.623457+00:00</t>
         </is>
       </c>
       <c r="T204" t="inlineStr">
@@ -12649,7 +12783,7 @@
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:14.950544+00:00</t>
+          <t>2026-06-02T18:36:48.680262+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -10351,7 +10351,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10374,16 +10374,37 @@
           <t>2207 SUMMIT BLVD, WEST PALM BEACH, FL 33406</t>
         </is>
       </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>{"total_amount": 637.0, "services": [{"name": "Boundary Survey", "description": "Base boundary survey rate per negotiated agreement with Nexgen Land Solutions, LLC (OLD_TITLE tier, 1715 orders).", "amount": 500.0}, {"name": "Lot Size Complexity Upcharge (0.51\u20131.00 ac)", "description": "Property is 0.74 acres, falling within the 0.51\u20131.00 ac tier. Upcharge applied per complexity reference table for increased field time and corner recovery on a lot of this size.", "amount": 137.0}], "pricing_reasoning": "The negotiated base rate of $500.00 applies per management agreement with Nexgen Land Solutions LLC. The lot is 0.74 acres, squarely in the 0.51\u20131.00 ac complexity band, warranting a $137.00 upcharge. No EC was ordered, the legal description references a platted subdivision lot (not metes and bounds), FEMA zone is AE (not VE, so no EC surcharge applies), and the county is Palm Beach (not Monroe), so no additional complexity upcharges are supported by the data.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000202507 appears to be a prior survey at the same address (2207 Summit Blvd, Palm Beach County) with matching coordinates (26.6663098, -80.074929) and Folio (00434405150000180). Service on that order included Land Survey and Elevation. Human review recommended to confirm this is a new scope request and not a duplicate submission before scheduling fieldwork.", "HOLD_STATUS: Order notes indicate this order is currently on hold with special pricing applied and awaiting fieldwork scheduling. Confirm hold has been released before dispatching field crew."]}</t>
+        </is>
+      </c>
       <c r="H158" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 201801311053398445, "created_at": "2025-11-13T15:23:00", "customer_email": "FREDERICK_S@NEXGENLOGIX.COM", "customer_id": 202410281556504891, "customer_name": "ORDER RESOLUTIONS", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0587F\nZONE: AE\nELEV: 12.4 FT\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000274571, "paid": false, "property_address": "2207 SUMMIT BLVD", "property_city": "WEST PALM BEACH", "property_county": "Palm Beach County", "property_lat": "26.6663271", "property_lng": "-80.0748843", "property_state": "FL", "property_zip": "33406", "service_type": "Boundary Survey", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274571", "customer_email": "FREDERICK_S@NEXGENLOGIX.COM", "service_type": "Boundary Survey", "county": "", "property_address": "2207 SUMMIT BLVD", "customer_name": "Nexgen Land Solutions, LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "ORDER RESOLUTIONS", "confidence": "MEDIUM"}, "client_email": {"value": "FREDERICK_S@NEXGENLOGIX.COM", "confidence": "HIGH"}, "property_address": {"value": "2207 SUMMIT BLVD, WEST PALM BEACH, FL 33406", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Boundary Survey"], "confidence": "HIGH", "notes": "Service type explicitly stated as Boundary Survey in FTF order data"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client legal name is ambiguous \u2014 FTF order shows 'ORDER RESOLUTIONS' but customer_name in outer payload shows 'Nexgen Land Solutions, LLC'; needs human clarification", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown \u2014 no appraiser, aerial, or email data available", "Order is On Hold \u2014 reason for hold not specified, may require follow-up", "No fieldwork or delivery dates scheduled", "No matching emails found to corroborate scope or client instructions"], "summary": "A B2B boundary survey order for 2207 Summit BLVD, West Palm Beach, FL 33406 (Palm Beach County) placed by ORDER RESOLUTIONS / Nexgen Land Solutions LLC is currently on hold with special pricing applied and awaiting fieldwork scheduling."}}</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1780425798799</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>2026-06-02T17:45:37.491136+00:00</t>
         </is>
       </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:43:22.426545+00:00</t>
+        </is>
+      </c>
+      <c r="R158" t="n">
+        <v>637</v>
+      </c>
       <c r="T158" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:17.633826+00:00</t>
@@ -10391,7 +10412,7 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>2026-06-02T17:45:37.531405+00:00</t>
+          <t>2026-06-02T18:43:22.479843+00:00</t>
         </is>
       </c>
     </row>
@@ -10403,7 +10424,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10426,16 +10447,37 @@
           <t>845 SE Tierra CT, Port St. Lucie, FL 34983</t>
         </is>
       </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>{"total_amount": 475.0, "services": [{"name": "Land Survey Only", "description": "Residential boundary survey for Lot 10, Block 65, River Park Unit 7, St. Lucie County. Standard platted subdivision lot at 0.24 acres. FEMA Zone X (no flood elevation certificate required). No complexity upcharges warranted.", "amount": 475.0}], "pricing_reasoning": "Client is an individual homeowner with no negotiated rate, so the default individual base rate of $475.00 applies. The property is a standard platted subdivision lot (0.24 acres, well under the 0.31-acre threshold for a lot-size upcharge), located in FEMA Zone X with no EC required, no metes-and-bounds description, no Monroe County mobilization, and no evidence of pool, waterfront canal, or heavy vegetation from the available data. No complexity upcharges are supported by the property data.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000274546 shares the same property address (845 SE Tierra CT), coordinates (27.3104017, -80.34669389999999), and Folio (3419-550-0049-000-0) with three other orders: 1000272713 (Land Survey Only), 1000275513 (Land Survey Only), and 1000281915 (Land Survey and Elevation). Human review is required to determine whether this order is a true duplicate, a re-order, or a billing error before finalizing the invoice.", "DATA_NOTE: Order notes indicate the order was already marked as paid and delivered but lacked lot size, legal description, and property feature details at time of original processing. Pricing here reflects the now-available data. Confirm no invoice was previously issued for this order number."]}</t>
+        </is>
+      </c>
       <c r="H159" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510081432369617, "created_at": "2025-11-13T11:53:00", "customer_email": "Angie769495@yahoo.com", "customer_id": 202510081432369723, "customer_name": "Angela N Alanis Rodriguez", "customer_type": "individual", "delivered_at": "2025-11-18T15:35:25", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12111C0286K\nZONE: X\nEFF: 02/19/2020", "invoiced": false, "order_id": 1000274546, "paid": true, "property_address": "845 SE TIERRA CT", "property_city": "PORT ST. LUCIE", "property_county": "St. Lucie County", "property_lat": "27.3104017", "property_lng": "-80.34669389999999", "property_state": "FL", "property_zip": "34983", "service_type": "Land Survey Only", "special_pricing": false, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274546", "customer_email": "Angie769495@yahoo.com", "service_type": "Land Survey Only", "county": "", "property_address": "845 SE TIERRA CT", "customer_name": "Angela N Alanis Rodriguez "}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Angela N Alanis Rodriguez", "confidence": "HIGH"}, "client_email": {"value": "Angie769495@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "845 SE Tierra CT, Port St. Lucie, FL 34983", "confidence": "HIGH"}, "property_county": {"value": "St. Lucie County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing \u2014 no appraiser or document source", "Structure square footage unknown", "Property features (pool, shed, fence, etc.) unknown \u2014 no aerial or appraiser data", "Special requirements or client notes not provided", "No matching emails found to supplement order details", "Fieldwork date not yet scheduled (fieldwork_at is null)"], "summary": "Residential land survey order for Angela N Alanis Rodriguez at 845 SE Tierra CT, Port St. Lucie, FL 34983 (St. Lucie County); order is paid and delivered but lacks lot size, legal description, and property feature details due to unavailable appraiser data."}}</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1780425817042</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>2026-06-02T17:45:46.653873+00:00</t>
         </is>
       </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:43:40.691905+00:00</t>
+        </is>
+      </c>
+      <c r="R159" t="n">
+        <v>475</v>
+      </c>
       <c r="T159" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:17.697033+00:00</t>
@@ -10443,7 +10485,7 @@
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>2026-06-02T17:45:46.693694+00:00</t>
+          <t>2026-06-02T18:43:40.745625+00:00</t>
         </is>
       </c>
     </row>
@@ -10455,7 +10497,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10478,16 +10520,37 @@
           <t>3023 SE Camino Ave, Stuart, FL 34997</t>
         </is>
       </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>{"total_amount": 475.0, "services": [{"name": "Land Survey Only", "description": "Boundary/land survey for Lots 9 and 10, Block 30, Golden Gate, Martin County. Residential platted lot, 0.13 acres, FEMA Zone X (no flood risk upcharge). No pool, waterfront, heavy vegetation, metes-and-bounds, or oversized lot complexity identified. Standard platted subdivision survey.", "amount": 475.0}], "pricing_reasoning": "Client is an individual homeowner (first-time client) with no negotiated rate, so the default individual base rate of $475.00 applies. The property is a small platted residential lot (0.13 acres, two contiguous lots in a recorded subdivision) in Martin County \u2014 not Monroe County \u2014 with no EC requested, FEMA Zone X (minimal flood complexity), and no aerial or legal-description indicators of pool, waterfront canal, heavy vegetation, or metes-and-bounds complexity. No complexity upcharges are warranted by the data.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE DUPLICATE: Order 1000271592 references the same property address (3023 SE Camino Ave, Martin County), same service type (Land Survey Only), same coordinates, and same Folio number (37-38-41-007-030-00090-7). Human review required before scheduling fieldwork to confirm whether this is a re-order, a continuation of a held order, or an inadvertent duplicate."]}</t>
+        </is>
+      </c>
       <c r="H160" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202511121630457812, "created_at": "2025-11-13T17:08:02", "customer_email": "maryvega551@gmail.com", "customer_id": 202511121630457909, "customer_name": "Mary Romanelli", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12085C0162H\nZONE: X\nEFF: 02/19/2020", "invoiced": false, "order_id": 1000274472, "paid": false, "property_address": "3023 SE CAMINO AVE", "property_city": "STUART", "property_county": "MARTIN COUNTY", "property_lat": "27.168144", "property_lng": "-80.21687299999999", "property_state": "FLORIDA", "property_zip": "34997", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274472", "customer_email": "maryvega551@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "3023 SE CAMINO AVE", "customer_name": "Mary Romanelli"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Mary Romanelli", "confidence": "HIGH"}, "client_email": {"value": "maryvega551@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "3023 SE Camino Ave, Stuart, FL 34997", "confidence": "HIGH"}, "property_county": {"value": "Martin County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data. No additional services indicated."}, "special_requirements": {"value": "None identified", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, outbuildings, etc.) unknown", "Order is currently On Hold \u2014 reason for hold not specified", "No fieldwork date scheduled", "Invoice has not been sent; due amount is $0 \u2014 pricing not yet established", "Client email (maryvega551@gmail.com) does not match customer name 'Mary Romanelli' \u2014 may indicate a third-party email or alias; verify client identity", "No supporting emails or documents attached"], "summary": "Residential land survey order for Mary Romanelli at 3023 SE Camino Ave, Stuart, FL (Martin County) currently on hold with no fieldwork scheduled, no pricing established, and limited property detail available."}}</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1780425835155</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>2026-06-02T17:51:10.241058+00:00</t>
         </is>
       </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:43:58.245861+00:00</t>
+        </is>
+      </c>
+      <c r="R160" t="n">
+        <v>475</v>
+      </c>
       <c r="T160" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:17.760217+00:00</t>
@@ -10495,7 +10558,7 @@
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>2026-06-02T17:51:10.292626+00:00</t>
+          <t>2026-06-02T18:43:58.299333+00:00</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12858,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12810,12 +12873,22 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Rafik Ibrahim</t>
+          <t>Rafik Ibrahim</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>1251 SW 15TH AVE</t>
+          <t>1251 SW 15TH AVE, BOCA RATON, FL 33486</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508141745215130, "created_at": "2025-08-14T17:20:01", "customer_email": "mrrafikibrahim@gmail.com", "customer_id": 202508141745215247, "customer_name": "Rafik Ibrahim", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C1178G\nZONE: AH\nELEV: 10.5 FT\nZONE: X500\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000269865, "paid": false, "property_address": "1251 SW 15TH AVE", "property_city": "BOCA RATON", "property_county": "PALM BEACH COUNTY", "property_lat": "26.3394083", "property_lng": "-80.1164246", "property_state": "FL", "property_zip": "33486", "service_type": "Land Survey and Elevation", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000269865", "customer_email": "mrrafikibrahim@gmail.com", "service_type": "Land Survey and Elevation", "county": "", "property_address": "1251 SW 15TH AVE", "customer_name": " Rafik Ibrahim"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Rafik Ibrahim", "confidence": "HIGH"}, "client_email": {"value": "mrrafikibrahim@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1251 SW 15TH AVE, BOCA RATON, FL 33486", "confidence": "HIGH"}, "property_county": {"value": "PALM BEACH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey", "Elevation Certificate"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'Land Survey and Elevation'; elevation_cert flag is false but service type implies elevation certificate is part of the order"}, "special_requirements": {"value": "Flood zone data on file: Panel 12099C1178G, Zone AH (Elev 10.5 FT) and Zone X500, effective 12/20/2024. Order is currently On Hold.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Order is On Hold \u2014 reason for hold not specified, needs human review", "elevation_cert flag is false despite service type including elevation \u2014 needs clarification on whether elevation certificate is required", "Lot size not available \u2014 county appraiser data unavailable", "Legal description not available \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features (pool, shed, fences, etc.) unknown \u2014 no appraiser or aerial data", "No invoice or estimate has been sent \u2014 pricing not yet established", "Order has not been paid and due amount is $0 \u2014 pricing needs to be assigned", "Fieldwork date not scheduled", "No matching emails found \u2014 no additional client communication on file"], "summary": "Individual residential client Rafik Ibrahim has ordered a Land Survey and Elevation Certificate for 1251 SW 15TH AVE, Boca Raton, FL 33486 (Palm Beach County), but the order is currently On Hold with no fieldwork scheduled, no invoice sent, and missing lot/legal/property detail data."}}</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:42:19.856423+00:00</t>
         </is>
       </c>
       <c r="T205" t="inlineStr">
@@ -12825,7 +12898,7 @@
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:15.027746+00:00</t>
+          <t>2026-06-02T18:42:19.911165+00:00</t>
         </is>
       </c>
     </row>
@@ -12837,7 +12910,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12857,7 +12930,17 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>1883 MICHIGAN AVE NE</t>
+          <t>1883 Michigan Ave NE, St Petersburg, FL 33703</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508141537467558, "created_at": "2025-08-14T11:42:00", "customer_email": "info@smartbuild-florida.com", "customer_id": 202508141539069304, "customer_name": "Klara Asllani", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12103C0228H\nZONE: AE\nELEV: 09 FT\nEFF: 08/24/2021", "invoiced": false, "order_id": 1000269850, "paid": true, "property_address": "1883 MICHIGAN AVE NE", "property_city": "ST PETERSBURG", "property_county": "Pinellas County", "property_lat": "27.8176789", "property_lng": "-82.6013476", "property_state": "FL", "property_zip": "33703", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000269850", "customer_email": "info@smartbuild-florida.com", "service_type": "CAD file", "county": "", "property_address": "1883 MICHIGAN AVE NE", "customer_name": "Smart Building Construction LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Smart Building Construction LLC", "confidence": "HIGH"}, "client_email": {"value": "info@smartbuild-florida.com", "confidence": "HIGH"}, "property_address": {"value": "1883 Michigan Ave NE, St Petersburg, FL 33703", "confidence": "HIGH"}, "property_county": {"value": "Pinellas County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services noted in the order data"}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); flood zone AE at 9ft elevation (FIRM panel 12103C0228H, eff. 08/24/2021)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, structures) unknown \u2014 no appraiser or aerial data available", "Order is On Hold \u2014 reason for hold not specified, needs human review", "Urgency/turnaround requirement not stated", "Fieldwork date not scheduled", "Invoice has not been sent despite order being marked as paid \u2014 reconciliation may be needed", "Contact person at Smart Building Construction LLC not confirmed (customer_name shows 'Klara Asllani' internally but company name used as primary)"], "summary": "B2B CAD file order for Smart Building Construction LLC at 1883 Michigan Ave NE, St Petersburg FL (Pinellas County), currently On Hold with special pricing applied and no fieldwork or invoice issued yet."}}</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:42:30.992923+00:00</t>
         </is>
       </c>
       <c r="T206" t="inlineStr">
@@ -12867,7 +12950,7 @@
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:15.109643+00:00</t>
+          <t>2026-06-02T18:42:31.046772+00:00</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12962,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12899,7 +12982,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2250 LORRAINE RD</t>
+          <t>2250 Lorraine Rd, Sarasota, FL 34240</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508141415019738, "created_at": "2025-08-14T11:11:05", "customer_email": "richard.thepermittech@gmail.com", "customer_id": 202508141416576577, "customer_name": "Richard Matassa", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12115C0157G\nZONE: X\nEFF: 03/27/2024", "invoiced": false, "order_id": 1000269843, "paid": false, "property_address": "2250 LORRAINE RD", "property_city": "SARASOTA", "property_county": "SARASOTA COUNTY", "property_lat": "27.345854", "property_lng": "-82.382947", "property_state": "FL", "property_zip": "34240", "service_type": "Quote", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000269843", "customer_email": "richard.thepermittech@gmail.com", "service_type": "Quote", "county": "", "property_address": "2250 LORRAINE RD", "customer_name": "The Permit Tech Inc."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "The Permit Tech Inc.", "confidence": "HIGH"}, "client_email": {"value": "richard.thepermittech@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "2250 Lorraine Rd, Sarasota, FL 34240", "confidence": "HIGH"}, "property_county": {"value": "Sarasota County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey type (boundary, topo, ALTA, etc.) has been identified. Needs clarification from client."}, "special_requirements": {"value": "Special pricing applies; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not identified \u2014 only 'Quote' provided", "Lot size unknown \u2014 no appraiser or parcel data available", "Legal description missing", "Structure square footage unknown", "Property features (pool, outbuildings, etc.) unknown", "No matching emails found to clarify scope", "County appraiser lookup unavailable", "Reason for 'On Hold' status not documented", "Details of special pricing arrangement not specified"], "summary": "B2B quote request from The Permit Tech Inc. for a property at 2250 Lorraine Rd, Sarasota, FL 34240 (Flood Zone X), currently on hold with special pricing applied and no specific survey service type identified."}}</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:42:40.657992+00:00</t>
         </is>
       </c>
       <c r="T207" t="inlineStr">
@@ -12909,7 +13002,7 @@
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:15.188125+00:00</t>
+          <t>2026-06-02T18:42:40.712263+00:00</t>
         </is>
       </c>
     </row>
@@ -12921,7 +13014,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12941,7 +13034,17 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>12510 SW 72ND TER</t>
+          <t>12510 SW 72ND TER, MIAMI, FL 33183</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508081507029632, "created_at": "2025-08-08T11:10:02", "customer_email": "daniel@sofisadevelopment.com", "customer_id": 202508081507379740, "customer_name": "Daniel Restepo", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0434L\nZONE: AH\nELEV: 08 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000269487, "paid": true, "property_address": "12510 SW 72ND TER", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.6997016", "property_lng": "-80.3966718", "property_state": "FL", "property_zip": "33183", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000269487", "customer_email": "daniel@sofisadevelopment.com", "service_type": "CAD file", "county": "", "property_address": "12510 SW 72ND TER", "customer_name": "Underwood Foundation Florida LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Underwood Foundation Florida LLC", "confidence": "MEDIUM"}, "client_email": {"value": "daniel@sofisadevelopment.com", "confidence": "HIGH"}, "property_address": {"value": "12510 SW 72ND TER, MIAMI, FL 33183", "confidence": "HIGH"}, "property_county": {"value": "MIAMI-DADE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Only service type listed is CAD file; no additional services indicated. Flood zone data present (AH zone, 8ft elev) but elevation certificate is marked false."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold \u2014 reason unknown.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: FTF order data lists 'Daniel Restepo' as customer_name but outer payload lists 'Underwood Foundation Florida LLC' \u2014 true client name needs human verification", "Reason for On Hold status unknown \u2014 human review needed before proceeding", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, structures, etc.) unknown \u2014 no appraiser or aerial data available", "County appraiser data unavailable \u2014 no county was passed to lookup", "Urgency/deadline not specified", "No matching emails found \u2014 no additional context from correspondence", "Special pricing applied but pricing amount or basis not documented"], "summary": "B2B CAD file order for a property at 12510 SW 72ND TER, Miami, FL (Miami-Dade County) in a FEMA AH flood zone, currently On Hold with special pricing applied, pending human review to resolve client name conflict and hold reason."}}</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:42:53.341941+00:00</t>
         </is>
       </c>
       <c r="T208" t="inlineStr">
@@ -12951,7 +13054,7 @@
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:15.266102+00:00</t>
+          <t>2026-06-02T18:42:53.396155+00:00</t>
         </is>
       </c>
     </row>
@@ -12963,7 +13066,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12983,7 +13086,17 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>260 N WOODS RD</t>
+          <t>260 N Woods Rd, Palm Beach, FL 33480</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202210042017188549, "created_at": "2025-08-06T14:03:04", "customer_email": "jacqueline@scottelkpa.com", "customer_id": 202305101847264425, "customer_name": "Jacqueline  Sahoy", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0581G\nZONE: AE\nELEV: 06 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000269367, "paid": true, "property_address": "260 N WOODS RD", "property_city": "PALM BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.7350873", "property_lng": "-80.0391877", "property_state": "FL", "property_zip": "33480", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000269367", "customer_email": "jacqueline@scottelkpa.com", "service_type": "CAD file", "county": "", "property_address": "260 N WOODS RD", "customer_name": "Scott A. Elk, P.A."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Scott A. Elk, P.A.", "confidence": "HIGH"}, "client_email": {"value": "jacqueline@scottelkpa.com", "confidence": "HIGH"}, "property_address": {"value": "260 N Woods Rd, Palm Beach, FL 33480", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated in the order data."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11). Flood zone data present: FIRM panel 12099C0581G, Zone AE, BFE 6 ft, effective 12/20/2024.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no matching emails or attachments found."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, driveways, structures) unknown \u2014 no appraiser data or aerial available", "Fieldwork date not scheduled", "Reason for 'On Hold' status not specified", "Urgency/deadline not indicated", "No supporting emails or attachments found to clarify scope"], "summary": "B2B CAD file order for Scott A. Elk, P.A. at 260 N Woods Rd, Palm Beach, FL (Flood Zone AE) is currently On Hold with special pricing applied and no fieldwork scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:43:03.880349+00:00</t>
         </is>
       </c>
       <c r="T209" t="inlineStr">
@@ -12993,7 +13106,7 @@
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:15.344389+00:00</t>
+          <t>2026-06-02T18:43:03.934280+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -10570,7 +10570,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10593,16 +10593,37 @@
           <t>10534 173RD RD N, JUPITER, FL 33478</t>
         </is>
       </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>{"total_amount": 850.0, "services": [{"name": "Land Survey (Boundary)", "description": "Base survey rate per management-agreed special pricing for Samantha Marion (individual client, 0 prior orders).", "amount": 300.0}, {"name": "Acreage Complexity Upcharge (2.01\u20135.00 ac)", "description": "Property is 2.49 acres, falling within the 2.01\u20135.00 ac complexity band. Legal description is a metes-and-bounds style call-out from an unrecorded subdivision (Wildwood Acres), requiring careful traverse of a rectangularly described parcel within a section quarter \u2014 field time and boundary research are materially higher than a platted residential lot.", "amount": 550.0}], "pricing_reasoning": "The agreed base rate of $300.00 is honored per management direction. The property is 2.49 acres in an unrecorded subdivision described by metes and bounds within a section quarter in Palm Beach County, which places it squarely in the 2.01\u20135.00 ac upcharge band (+$550.00); the legal description requires section-level control and careful boundary reconstruction. No EC is ordered, the FEMA zone is X (low risk, no flood cert needed), the property is not in Monroe County, and no pool, waterfront, or heavy-vegetation indicators are present in the available data. The metes-and-bounds nature of the description is already captured by the acreage upcharge given the rectangular parcel calls, so no separate M&amp;B upcharge is added to avoid double-counting.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_ORDER: Order 1000272970 at 10534 DOGWOOD TRAIL, PALM BEACH COUNTY shares the same coordinates (26.9325123, -80.200052) and Folio/MLS (00414101010000180) as this order. The address differs (173RD RD N vs DOGWOOD TRAIL) but the parcel identifier matches. This may be the same property with an alternate address or a true duplicate \u2014 human review required before scheduling fieldwork.", "ON_HOLD: Order notes indicate the job is currently On Hold with special pricing flagged and no fieldwork scheduled, pending clarification. Do not dispatch field crew until hold is lifted.", "UNRECORDED_SUBDIVISION: Wildwood Acres is an unrecorded subdivision. Title chain and boundary reconstruction may require additional research; flag for lead surveyor review prior to fieldwork.", "SPECIAL_PRICING: Base rate of $300.00 is below standard market rate and was approved by management for this specific client. Confirm authorization before invoicing."]}</t>
+        </is>
+      </c>
       <c r="H161" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202511101652036071, "created_at": "2025-11-10T17:41:04", "customer_email": "smarion@conroysimberg.com", "customer_id": 202511101652037281, "customer_name": "Samantha Marion", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0165F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000274358, "paid": false, "property_address": "10534 173RD RD N", "property_city": "JUPITER", "property_county": "PALM BEACH COUNTY", "property_lat": "26.9325123", "property_lng": "-80.200052", "property_state": "FL", "property_zip": "33478", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274358", "customer_email": "smarion@conroysimberg.com", "service_type": "Land Survey Only", "county": "", "property_address": "10534 173RD RD N", "customer_name": "Samantha Marion"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Samantha Marion", "confidence": "HIGH"}, "client_email": {"value": "smarion@conroysimberg.com", "confidence": "HIGH"}, "property_address": {"value": "10534 173RD RD N, JUPITER, FL 33478", "confidence": "HIGH"}, "property_county": {"value": "PALM BEACH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing flagged on order; order is currently On Hold (status code 11) \u2014 reason for hold unknown.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or aerial data provided."}, "client_tier": {"value": "residential", "confidence": "MEDIUM", "notes": "Customer type is 'individual'; email domain conroysimberg.com suggests a law firm affiliation which may indicate b2b referral, but account is registered as individual."}, "urgency": {"value": "normal", "confidence": "MEDIUM", "notes": "No rush indicators present; order is On Hold with no fieldwork or delivery dates scheduled."}, "source_of_truth": "ftf_only", "gaps": ["Reason for 'On Hold' status is unknown \u2014 needs human review", "Special pricing flag set but no pricing details or approval noted", "Lot size not available \u2014 county appraiser data unavailable", "Legal description not available \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features (pool, shed, structures) unknown \u2014 no aerial or appraiser data", "No fieldwork date scheduled", "Client relationship unclear \u2014 email domain suggests possible law firm/b2b referral despite individual account type", "No matching emails found to clarify scope or instructions"], "summary": "Residential land survey order for Samantha Marion at 10534 173RD RD N, Jupiter, FL 33478 (Palm Beach County) is currently On Hold with special pricing flagged and no fieldwork scheduled, pending clarification."}}</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>1780426168650</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>2026-06-02T17:51:22.541011+00:00</t>
         </is>
       </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:49:31.193556+00:00</t>
+        </is>
+      </c>
+      <c r="R161" t="n">
+        <v>850</v>
+      </c>
       <c r="T161" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:17.824346+00:00</t>
@@ -10610,7 +10631,7 @@
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>2026-06-02T17:51:22.592916+00:00</t>
+          <t>2026-06-02T18:49:31.247024+00:00</t>
         </is>
       </c>
     </row>
@@ -10622,7 +10643,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10645,16 +10666,37 @@
           <t>5505 S Indian River Dr, Fort Pierce, FL 34982</t>
         </is>
       </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "AI pricing failed: Unterminated string starting at: line 29 column 5 (char 2940). Manual review required.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "AI pricing error \u2014 needs manual quote", "flags": ["ai_error"]}</t>
+        </is>
+      </c>
       <c r="H162" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510021939408806, "created_at": "2025-11-05T12:34:02", "customer_email": "karinabodina@yahoo.com", "customer_id": 202510021939409897, "customer_name": "Sally Daw", "customer_type": "individual", "delivered_at": "2025-12-01T14:09:13", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12111C0281K\nZONE: X\nEFF: 02/19/2020", "invoiced": false, "order_id": 1000274136, "paid": true, "property_address": "5505 S INDIAN RIVER DR", "property_city": "FORT PIERCE", "property_county": "ST LUCIE COUNTY", "property_lat": "27.374539", "property_lng": "-80.2926932", "property_state": "FL", "property_zip": "34982", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274136", "customer_email": "karinabodina@yahoo.com", "service_type": "Land Survey Only", "county": "", "property_address": "5505 S INDIAN RIVER DR", "customer_name": "Sally Daw"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Sally Daw", "confidence": "HIGH"}, "client_email": {"value": "karinabodina@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "5505 S Indian River Dr, Fort Pierce, FL 34982", "confidence": "HIGH"}, "property_county": {"value": "St Lucie County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as Land Survey Only; no elevation certificate requested"}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, outbuildings, etc.) unknown", "Client email (karinabodina@yahoo.com) does not match customer name Sally Daw \u2014 possible third-party or agent email, needs verification", "Fieldwork date not yet scheduled", "Invoice not yet generated despite order being paid and delivered", "No pricing or line item details available"], "summary": "Residential land survey only order for Sally Daw at 5505 S Indian River Dr, Fort Pierce, FL (St Lucie County), marked paid and delivered with special pricing applied, but missing lot size, legal description, and property feature details."}}</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>1780426194488</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>2026-06-02T17:51:32.131382+00:00</t>
         </is>
       </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:49:57.204709+00:00</t>
+        </is>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
       <c r="T162" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:17.888005+00:00</t>
@@ -10662,7 +10704,7 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>2026-06-02T17:51:32.183550+00:00</t>
+          <t>2026-06-02T18:49:57.325692+00:00</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13160,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13138,7 +13180,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>611 SW 15TH ST</t>
+          <t>611 SW 15TH ST, BOCA RATON, FL 33486</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202508051943092816, "created_at": "2025-08-05T15:45:00", "customer_email": "buywithberk@gmail.com", "customer_id": 202508051943093884, "customer_name": "Jason Berk", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0789G\nZONE: X500\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000269301, "paid": true, "property_address": "611 SW 15TH ST", "property_city": "BOCA RATON", "property_county": "Palm Beach County", "property_lat": "26.3344468", "property_lng": "-80.0959577", "property_state": "FL", "property_zip": "33486", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000269301", "customer_email": "buywithberk@gmail.com", "service_type": "CAD file", "county": "", "property_address": "611 SW 15TH ST", "customer_name": "Jason Berk"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Jason Berk", "confidence": "HIGH"}, "client_email": {"value": "buywithberk@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "611 SW 15TH ST, BOCA RATON, FL 33486", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated in the order data."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11).", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features data available; county appraiser lookup unavailable and no emails or attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, structures, etc.) unknown \u2014 no appraiser data or aerial available", "Scope/purpose of CAD file not specified (boundary, topo, as-built, etc.)", "Order is On Hold \u2014 reason for hold not documented", "No fieldwork date scheduled", "Invoice not yet sent despite paid status \u2014 needs reconciliation review"], "summary": "Individual client Jason Berk has a paid but on-hold CAD file order for a residential property at 611 SW 15th St, Boca Raton, FL (Palm Beach County) with special pricing applied, pending fieldwork scheduling and clarification on hold reason."}}</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:48:22.231911+00:00</t>
         </is>
       </c>
       <c r="T210" t="inlineStr">
@@ -13148,7 +13200,7 @@
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:15.473188+00:00</t>
+          <t>2026-06-02T18:48:22.284896+00:00</t>
         </is>
       </c>
     </row>
@@ -13160,7 +13212,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13180,7 +13232,17 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>403 W RIVERSIDE DR</t>
+          <t>403 W Riverside Dr, Jupiter, FL 33469</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507301727459931, "created_at": "2025-07-30T13:29:00", "customer_email": "clay@crewbuilding.co", "customer_id": 202507301727461203, "customer_name": "Lauren Thomas", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0178G\nZONE: X500\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000268948, "paid": true, "property_address": "403 W RIVERSIDE DR", "property_city": "JUPITER", "property_county": "PALM BEACH COUNTY", "property_lat": "26.959453", "property_lng": "-80.1011315", "property_state": "FL", "property_zip": "33469", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000268948", "customer_email": "clay@crewbuilding.cl", "service_type": "CAD file", "county": "", "property_address": "403 W RIVERSIDE DR", "customer_name": "Lauren Thomas"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Lauren Thomas", "confidence": "HIGH"}, "client_email": {"value": "clay@crewbuilding.co", "confidence": "MEDIUM"}, "property_address": {"value": "403 W Riverside Dr, Jupiter, FL 33469", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD file; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser lookup unavailable and no aerial or email data provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client email conflict: order data shows clay@crewbuilding.co while outer envelope shows clay@crewbuilding.cl \u2014 confirm correct email", "No customer profile data returned from FTF customer lookup", "No matching emails found to cross-reference order details", "County property appraiser unavailable \u2014 lot size, legal description, and structure sqft unknown", "No property features identified (pool, shed, driveways, structures)", "Order is On Hold \u2014 reason for hold not specified; human review needed", "Fieldwork date not scheduled (fieldwork_at is null)", "Invoice has not been sent (invoiced: false, estimate_sent: false)"], "summary": "Lauren Thomas has an On Hold CAD file order for a residential property at 403 W Riverside Dr, Jupiter, FL 33469 (Palm Beach County) with special pricing applied, paid but not yet invoiced, and no fieldwork scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:48:32.412722+00:00</t>
         </is>
       </c>
       <c r="T211" t="inlineStr">
@@ -13190,7 +13252,7 @@
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:15.552510+00:00</t>
+          <t>2026-06-02T18:48:32.467437+00:00</t>
         </is>
       </c>
     </row>
@@ -13202,7 +13264,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13222,7 +13284,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>1825 MAIN ST</t>
+          <t>1825 Main St, Weston, FL 33326</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507251752463171, "created_at": "2025-07-31T10:37:03", "customer_email": "jsmith@1754properties.com", "customer_id": 202507251752463275, "customer_name": "Joe Smith", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0510J\nZONE: X500\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000268731, "paid": false, "property_address": "1825 MAIN ST", "property_city": "WESTON", "property_county": "BROWARD COUNTY", "property_lat": "26.0966888", "property_lng": "-80.3816535", "property_state": "FL", "property_zip": "33326", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000268731", "customer_email": "jsmith@1754properties.com", "service_type": "Land Survey Only", "county": "", "property_address": "1825 MAIN ST", "customer_name": "Joe Smith"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Joe Smith", "confidence": "HIGH"}, "client_email": {"value": "jsmith@1754properties.com", "confidence": "HIGH"}, "property_address": {"value": "1825 Main St, Weston, FL 33326", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference."}, "client_tier": {"value": "residential", "confidence": "MEDIUM"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) unknown \u2014 no aerial or appraiser data", "Special requirements or client notes not provided", "Urgency/timeline not specified", "Order is On Hold \u2014 reason for hold not documented", "Invoice amount is $0 \u2014 pricing not yet established", "Client type listed as 'individual' but email domain '1754properties.com' may suggest a business relationship \u2014 verify client tier", "No fieldwork date scheduled"], "summary": "Joe Smith has requested a Land Survey Only at 1825 Main St, Weston, FL 33326 (Broward County); the order is currently on hold with no pricing, fieldwork date, or property details established."}}</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:48:42.399130+00:00</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
@@ -13232,7 +13304,7 @@
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:15.631730+00:00</t>
+          <t>2026-06-02T18:48:42.452497+00:00</t>
         </is>
       </c>
     </row>
@@ -13244,7 +13316,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13264,7 +13336,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>15 CENTER LN</t>
+          <t>15 CENTER LN, KEY LARGO, FL 33037</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507251512326506, "created_at": "2025-07-25T11:15:03", "customer_email": "jennmorgan@tirone-electric.com", "customer_id": 202507251512327919, "customer_name": "Rosina Tirone", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12087C0767K\nZONE: AE\nELEV: 10 FT\nEFF: 02/18/2005", "invoiced": false, "order_id": 1000268713, "paid": true, "property_address": "15 CENTER LN", "property_city": "KEY LARGO", "property_county": "Monroe County", "property_lat": "25.1597876", "property_lng": "-80.39269070000002", "property_state": "FL", "property_zip": "33037", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000268713", "customer_email": "jennmorgan@tiron-electric.com", "service_type": "CAD file", "county": "", "property_address": "15 CENTER LN", "customer_name": "Rosina Tirone"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Rosina Tirone", "confidence": "HIGH"}, "client_email": {"value": "jennmorgan@tirone-electric.com", "confidence": "MEDIUM"}, "property_address": {"value": "15 CENTER LN, KEY LARGO, FL 33037", "confidence": "HIGH"}, "property_county": {"value": "Monroe County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type listed as 'CAD file'; no additional services indicated. Unclear if this is a standalone CAD deliverable or derived from a boundary/survey \u2014 needs clarification."}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); flood zone AE at 10 ft elevation (panel 12087C0767K, eff. 02/18/2005)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no aerial or email data provided."}, "client_tier": {"value": "residential", "confidence": "MEDIUM"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client email discrepancy: FTF order data shows 'jennmorgan@tirone-electric.com' but top-level customer_email shows 'jennmorgan@tiron-electric.com' (missing 'e') \u2014 verify correct email before invoicing", "No customer data returned from FTF customer lookup (empty object)", "No matching emails found \u2014 unable to confirm prior communication or scope", "County property appraiser data unavailable \u2014 lot size, legal description, and structure details unknown", "Reason for 'On Hold' status is unclear \u2014 needs human review before proceeding", "Unclear what source survey/fieldwork the CAD file is based on \u2014 no fieldwork date recorded", "Special pricing applied but pricing amount not specified \u2014 confirm approved rate", "No lot size, legal description, or parcel ID available", "No property features data (structures, pool, outbuildings, etc.)", "Urgency/deadline not specified", "Elevation certificate not ordered but property is in Flood Zone AE \u2014 confirm if client is aware or needs one", "Order marked as paid but not yet invoiced \u2014 verify billing status consistency"], "summary": "Residential CAD file order for Rosina Tirone at 15 Center Ln, Key Largo, FL (Monroe County, Flood Zone AE) is currently On Hold with special pricing applied, missing fieldwork data, legal description, lot size, and a client email discrepancy that requires human review before proceeding."}}</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:48:56.599944+00:00</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
@@ -13274,7 +13356,7 @@
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:15.710066+00:00</t>
+          <t>2026-06-02T18:48:56.654688+00:00</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13368,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13306,7 +13388,17 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>3790 NE 25TH AVE</t>
+          <t>3790 NE 25TH AVE, LIGHTHOUSE POINT, FL 33064</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507251344426403, "created_at": "2025-07-25T09:57:02", "customer_email": "blaket@unlimitedps.net", "customer_id": 202507251346050711, "customer_name": "Blake Thomas", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0189J\nZONE: AE\nELEV: 07 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000268701, "paid": true, "property_address": "3790 NE 25TH AVE", "property_city": "LIGHTHOUSE POINT", "property_county": "BROWARD COUNTY", "property_lat": "26.2778246", "property_lng": "-80.0889468", "property_state": "FL", "property_zip": "33064", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000268701", "customer_email": "blaket@unlimitedps.net", "service_type": "CAD file", "county": "", "property_address": "3790 NE 25TH AVE", "customer_name": "Unlimited Permit Services, INC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Unlimited Permit Services, INC", "confidence": "HIGH"}, "client_email": {"value": "blaket@unlimitedps.net", "confidence": "HIGH"}, "property_address": {"value": "3790 NE 25TH AVE, LIGHTHOUSE POINT, FL 33064", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Only service type listed is CAD file; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11); flood zone AE with base elevation 7 ft, FIRM panel 12011C0189J effective 07/31/2024", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, driveways, structures) unknown \u2014 no appraiser data or aerial available", "Reason for On Hold status not specified", "Scope of CAD file request not clarified (boundary, topo, as-built, etc.)", "No matching emails found to supplement order details", "Special pricing terms not detailed"], "summary": "B2B order from Unlimited Permit Services, INC for a CAD file at 3790 NE 25TH AVE, Lighthouse Point, FL (Broward County) in Flood Zone AE, currently on hold with special pricing applied and missing property details."}}</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:49:08.557936+00:00</t>
         </is>
       </c>
       <c r="T214" t="inlineStr">
@@ -13316,7 +13408,7 @@
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:15.790455+00:00</t>
+          <t>2026-06-02T18:49:08.611765+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -10716,7 +10716,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10739,16 +10739,37 @@
           <t>510 RIVIERA DR, FORT LAUDERDALE, FL 33301</t>
         </is>
       </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "This order is for a CAD file delivery on a property measuring 11.80 acres in Broward County. Per pricing guidelines, any lot exceeding 5.00 acres must be escalated and cannot be priced without management approval. Additionally, three possible duplicate orders exist for the same or immediately adjacent address and coordinates, which further warrants human review before any invoice is generated.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "Lot size of 11.80 acres exceeds the 5.00-acre pricing threshold \u2014 do not price; flag for management quoting. Additionally, three probable duplicate orders (1000180005, 1000239683, 1000239989) share the same or adjacent address and GPS coordinates (26.120232, -80.113396), suggesting overlapping scope that must be reconciled before invoicing. The order is currently On Hold with special pricing flagged; management confirmation of scope, deduplication, and large-acreage CAD fee is required.", "flags": ["ESCALATE: Lot size 11.80 acres exceeds the 5.00-acre maximum for standard pricing. Management must quote CAD file fee for large acreage.", "DUPLICATE WARNING: Order 1000180005 \u2014 645 Riviera Drive, Broward County \u2014 Land Survey and Elevation \u2014 same GPS coordinates (26.120232, -80.113396). Human review required.", "DUPLICATE WARNING: Order 1000239683 \u2014 510 Riviera Dr, Broward County \u2014 Land Survey and Elevation \u2014 same address, same GPS coordinates, same Folio/MLS (504212080190). Strong duplicate match. Human review required.", "DUPLICATE WARNING: Order 1000239989 \u2014 529 Riviera Drive, Broward County \u2014 Land Survey and Elevation \u2014 same GPS coordinates (26.120232, -80.113396). Human review required.", "ORDER STATUS: Currently On Hold with special pricing flagged per order notes. No fieldwork or invoice activity yet. Do not release invoice until management approves.", "CLIENT NOTE: Unlimited Permit Services, INC has 0 prior orders with NexGen despite being classified OLD_TITLE. Verify client tier and negotiated rate of $450.00 with management before applying.", "FEMA ZONE AE at elevation 7 ft noted for reference \u2014 no EC requested in this order, but may be relevant if scope expands."]}</t>
+        </is>
+      </c>
       <c r="H163" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202507251344426403, "created_at": "2025-11-05T10:43:03", "customer_email": "blaket@unlimitedps.net", "customer_id": 202507251346050711, "customer_name": "Blake Thomas", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0576J\nZONE: AE\nELEV: 07 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000274109, "paid": false, "property_address": "510 RIVIERA DR", "property_city": "FORT LAUDERDALE", "property_county": "BROWARD COUNTY", "property_lat": "26.120232", "property_lng": "-80.113396", "property_state": "FL", "property_zip": "33301", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274109", "customer_email": "blaket@unlimitedps.net", "service_type": "CAD file", "county": "", "property_address": "510 RIVIERA DR", "customer_name": "Unlimited Permit Services, INC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Unlimited Permit Services, INC", "confidence": "HIGH"}, "client_email": {"value": "blaket@unlimitedps.net", "confidence": "HIGH"}, "property_address": {"value": "510 RIVIERA DR, FORT LAUDERDALE, FL 33301", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD file; no additional services indicated"}, "special_requirements": {"value": "Special pricing flagged; order currently On Hold (status code 11); flood zone AE, panel 12011C0576J, base flood elevation 7 ft, effective 07/31/2024", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, etc.)", "No fieldwork date scheduled", "Order is On Hold \u2014 reason for hold not specified", "No estimate sent yet \u2014 pricing details not confirmed", "County appraiser data unavailable", "No matching emails found for additional context", "Urgency/rush status not indicated"], "summary": "B2B CAD file order for Unlimited Permit Services, INC on a flood zone AE property at 510 Riviera Dr, Fort Lauderdale, currently On Hold with special pricing flagged and no fieldwork or invoice activity yet."}}</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>1780426527815</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>2026-06-02T17:51:42.282579+00:00</t>
         </is>
       </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:55:30.940982+00:00</t>
+        </is>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
       <c r="T163" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:17.952263+00:00</t>
@@ -10756,7 +10777,7 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>2026-06-02T17:51:42.384752+00:00</t>
+          <t>2026-06-02T18:55:30.997592+00:00</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10789,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10791,16 +10812,37 @@
           <t>2395 Campbell Rd, Clearwater, FL 33765</t>
         </is>
       </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>{"total_amount": 775.0, "services": [{"name": "Land Survey (Boundary)", "description": "Residential boundary/land survey for Lot 35, Coachman Lakes Estates, Pinellas County. Base rate per management-approved negotiated pricing for Christopher Coventry.", "amount": 500.0}, {"name": "Lot Size Complexity Upcharge (1.01\u20132.00 ac)", "description": "Property is 1.25 acres per database, falling within the 1.01\u20132.00 acre tier. Larger lot requires additional field time to locate and monument corners across greater distances.", "amount": 275.0}], "pricing_reasoning": "The negotiated base rate of $500.00 is applied per management direction for this individual client. The lot size of 1.25 acres falls squarely in the 1.01\u20132.00 acre complexity tier, warranting the $275.00 upcharge for additional field effort. No Elevation Certificate was requested, the FEMA zone is X (non-special flood hazard), the legal description is a straightforward platted lot (no metes-and-bounds complexity), and no other complexity factors (waterfront, pool, heavy vegetation, Monroe County) are evident from the available data.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE_DUPLICATE: Order 1000267305 references the same address (2395 Campbell Rd, Pinellas County), same coordinates (27.98463, -82.7385704), and same Folio/MLS (162906168480000350) with an identical service type (Land Survey Only). Human review recommended to confirm this is not a duplicate billing or re-order of previously completed work.", "ORDER_NOTES indicate the order was previously marked delivered and paid with special pricing applied. Verify payment status and prior invoice amount before processing to avoid double-billing."]}</t>
+        </is>
+      </c>
       <c r="H164" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202511051440302010, "created_at": "2025-11-05T09:44:02", "customer_email": "coventry.chris@gmail.com", "customer_id": 202511051440302993, "customer_name": "Christopher  Coventry", "customer_type": "individual", "delivered_at": "2025-11-11T21:05:29", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12103C0126G\nZONE: X\nEFF: 09/03/2003", "invoiced": false, "order_id": 1000274095, "paid": true, "property_address": "2395 CAMPBELL RD", "property_city": "CLEARWATER", "property_county": "Pinellas County", "property_lat": "27.98463", "property_lng": "-82.7385704", "property_state": "FL", "property_zip": "33765", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274095", "customer_email": "coventry.chris@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "2395 CAMPBELL RD", "customer_name": "Christopher  Coventry"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Christopher Coventry", "confidence": "HIGH"}, "client_email": {"value": "coventry.chris@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "2395 Campbell Rd, Clearwater, FL 33765", "confidence": "HIGH"}, "property_county": {"value": "Pinellas County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated."}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no emails, appraiser data, or aerial imagery provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, fences, driveways) unknown \u2014 no aerial or appraiser data", "No matching emails found to clarify scope or special instructions", "Reason for special pricing not documented", "Fieldwork date not recorded (fieldwork_at is null)"], "summary": "Residential land survey only order for Christopher Coventry at 2395 Campbell Rd, Clearwater, FL (Pinellas County), marked delivered and paid with special pricing applied, but lacking lot size, legal description, and property feature details."}}</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>1780426547721</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>2026-06-02T17:51:50.791868+00:00</t>
         </is>
       </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:55:50.825377+00:00</t>
+        </is>
+      </c>
+      <c r="R164" t="n">
+        <v>775</v>
+      </c>
       <c r="T164" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:18.064225+00:00</t>
@@ -10808,7 +10850,7 @@
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>2026-06-02T17:51:50.844630+00:00</t>
+          <t>2026-06-02T18:55:50.881579+00:00</t>
         </is>
       </c>
     </row>
@@ -10820,7 +10862,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10843,16 +10885,37 @@
           <t>3131 NE 21ST AVE, LIGHTHOUSE POINT, FL 33064</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>{"total_amount": 300.0, "services": [{"name": "Land Survey Only", "description": "Residential boundary survey for LOT 20, RANDALL MANOR, Plat Book 48/Page 20, Broward County. 0.19-acre standard residential lot with platted legal description (no metes-and-bounds complexity). Negotiated flat rate per management agreement.", "amount": 300.0}], "pricing_reasoning": "Management pre-negotiated a $300.00 flat rate for this specific client (Peter Moss, individual homeowner) on this specific order. The property is a small 0.19-acre platted residential lot in Broward County with a straightforward platted legal description \u2014 no metes-and-bounds, no Monroe County mobilization, no waterfront canal, pool, heavy vegetation, or oversized lot factors that would ordinarily trigger complexity upcharges. The FEMA dual-zone (AE/X500) is noted but no Elevation Certificate was requested, so no EC line item applies. The negotiated $300.00 rate stands as the total invoice amount.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_ORDER: Order 1000129954 references the same property address (3131 NE 21ST AVE, Broward County), same service type (Land Survey Only), and matching folio/coordinates. Human review recommended before dispatching field crew to avoid duplicate site visit and billing.", "ORDER_NOTES: Order was previously placed on hold with special pricing applied and a $300 balance noted \u2014 confirm with management that this invoice represents the outstanding balance due, not a new charge on top of any prior payment."]}</t>
+        </is>
+      </c>
       <c r="H165" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202511041416145593, "created_at": "2025-11-05T16:49:00", "customer_email": "peter.moss@outlook.com", "customer_id": 202511041416146883, "customer_name": "Peter Moss", "customer_type": "individual", "delivered_at": null, "due_amount": 300.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0188J\nZONE: AE\nELEV: 07 FT\nZONE: X500\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000274003, "paid": false, "property_address": "3131 NE 21ST AVE", "property_city": "LIGHTHOUSE POINT", "property_county": "BROWARD COUNTY", "property_lat": "26.2706639", "property_lng": "-80.0950659", "property_state": "FL", "property_zip": "33064", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000274003", "customer_email": "peter.moss@outlook.com", "service_type": "Land Survey Only", "county": "", "property_address": "3131 NE 21ST AVE", "customer_name": "Peter Moss"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Peter Moss", "confidence": "HIGH"}, "client_email": {"value": "peter.moss@outlook.com", "confidence": "HIGH"}, "property_address": {"value": "3131 NE 21ST AVE, LIGHTHOUSE POINT, FL 33064", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as Land Survey Only; no elevation certificate requested"}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); flood zone data present \u2014 AE zone at 7 ft elevation and X500 zone, effective 07/31/2024", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser unavailable", "Legal description missing", "Structure square footage unknown", "Property features unknown (pool, shed, fence, driveway, etc.)", "Order is On Hold \u2014 reason for hold not specified, needs human review", "Invoice not yet sent and order not paid \u2014 billing status needs follow-up", "No fieldwork or delivery date scheduled"], "summary": "Residential land survey order for Peter Moss at 3131 NE 21ST AVE, Lighthouse Point, FL (Broward County), currently on hold with special pricing applied and a $300 balance due."}}</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>1780426568150</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>2026-06-02T17:57:12.725096+00:00</t>
         </is>
       </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:56:10.906567+00:00</t>
+        </is>
+      </c>
+      <c r="R165" t="n">
+        <v>300</v>
+      </c>
       <c r="T165" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:18.128921+00:00</t>
@@ -10860,7 +10923,7 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>2026-06-02T17:57:12.775366+00:00</t>
+          <t>2026-06-02T18:56:10.963856+00:00</t>
         </is>
       </c>
     </row>
@@ -13420,7 +13483,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13440,7 +13503,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>108 W KEYES AVE</t>
+          <t>108 W Keyes Ave, Tampa, FL 33602</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507251308026721, "created_at": "2025-07-25T09:08:00", "customer_email": "nicj2388@gmail.com", "customer_id": 202507251308027952, "customer_name": "Nicoden Joseph", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12057C0352J\nZONE: X\nEFF: 10/07/2021", "invoiced": false, "order_id": 1000268673, "paid": true, "property_address": "108 W KEYES AVE", "property_city": "TAMPA", "property_county": "Hillsborough County", "property_lat": "27.9699025", "property_lng": "-82.4613724", "property_state": "FL", "property_zip": "33602", "service_type": "Quote", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000268673", "customer_email": "nicj2388@gmail.com", "service_type": "Quote", "county": "", "property_address": "108 W KEYES AVE", "customer_name": "Nicoden Joseph"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Nicoden Joseph", "confidence": "HIGH"}, "client_email": {"value": "nicj2388@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "108 W Keyes Ave, Tampa, FL 33602", "confidence": "HIGH"}, "property_county": {"value": "Hillsborough County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., boundary, elevation cert, ALTA) has been identified. Needs clarification."}, "special_requirements": {"value": "Special pricing applied; order is On Hold", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no aerial or email data provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not identified \u2014 'Quote' is not a deliverable", "Lot size unknown", "Legal description unavailable", "Structure square footage unknown", "Property features (pool, shed, structures) unknown \u2014 no appraiser or aerial data", "No customer profile data available", "Reason for 'On Hold' status not documented", "Scope or context behind special pricing not explained", "No fieldwork or delivery dates scheduled"], "summary": "Individual residential client Nicoden Joseph has an on-hold quote order for a property at 108 W Keyes Ave, Tampa, FL (Hillsborough County, Flood Zone X), but the specific survey service requested has not yet been defined."}}</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:54:24.743981+00:00</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
@@ -13450,7 +13523,7 @@
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:15.869790+00:00</t>
+          <t>2026-06-02T18:54:24.800931+00:00</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13535,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13482,7 +13555,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>220 E MADISON ST</t>
+          <t>220 E Madison St, Tampa, FL 33602</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201801311057184262, "created_at": "2025-07-23T09:48:00", "customer_email": "omar.garcia@usreis.com", "customer_id": 201801311059053829, "customer_name": "Omar Garcia", "customer_type": "b2b", "delivered_at": "2025-12-03T19:12:50", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12057C0354J\nZONE: X\nEFF: 10/07/2021", "invoiced": false, "order_id": 1000268474, "paid": true, "property_address": "220 E MADISON ST", "property_city": "TAMPA", "property_county": "HILLSBOROUGH COUNTY", "property_lat": "27.9484879", "property_lng": "-82.4586679", "property_state": "FL", "property_zip": "33602", "service_type": "Land Survey Only", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000268474", "customer_email": "omar.garcia@usreis.com", "service_type": "Land Survey Only", "county": "", "property_address": "220 E MADISON ST", "customer_name": "Urban Core II LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Urban Core II LLC", "confidence": "MEDIUM"}, "client_email": {"value": "omar.garcia@usreis.com", "confidence": "HIGH"}, "property_address": {"value": "220 E Madison St, Tampa, FL 33602", "confidence": "HIGH"}, "property_county": {"value": "Hillsborough County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property feature data available; county appraiser lookup unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order root shows 'Urban Core II LLC' but customer record shows 'Omar Garcia' \u2014 confirm billing entity", "Lot size not available", "Legal description not available", "Structure square footage not available", "Property features unknown (pool, shed, fences, driveways, etc.)", "County property appraiser data unavailable \u2014 no county was passed to lookup", "No matching emails found \u2014 no additional context or attachments", "Fieldwork date is null \u2014 confirm scheduling status", "Order marked paid but invoiced=false \u2014 confirm billing/invoicing workflow status"], "summary": "B2B land survey order for 220 E Madison St, Tampa FL (Hillsborough County) on behalf of Urban Core II LLC, delivered and paid, with special pricing applied but missing lot size, legal description, and property feature details."}}</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:54:34.198148+00:00</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
@@ -13492,7 +13575,7 @@
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:16.002431+00:00</t>
+          <t>2026-06-02T18:54:34.255103+00:00</t>
         </is>
       </c>
     </row>
@@ -13504,7 +13587,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13519,12 +13602,22 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Kieu  Le</t>
+          <t>Kieu Le</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>304 NW 4TH AVE</t>
+          <t>304 NW 4TH AVE, Cape Coral, FL 33993</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507221609540973, "created_at": "2025-07-22T12:13:03", "customer_email": "LTTK1222@gmail.com", "customer_id": 202507221609542685, "customer_name": "Kieu  Le", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12071C0261G\nZONE: X\nEFF: 11/17/2022", "invoiced": false, "order_id": 1000268468, "paid": true, "property_address": "304 NW 4TH AVE", "property_city": "CAPE CORAL", "property_county": "Lee County", "property_lat": "26.657744", "property_lng": "-81.982718", "property_state": "FL", "property_zip": "33993", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000268468", "customer_email": "LTTK1222@gmail.com", "service_type": "CAD file", "county": "", "property_address": "304 NW 4TH AVE", "customer_name": "Kieu  Le"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Kieu Le", "confidence": "HIGH"}, "client_email": {"value": "LTTK1222@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "304 NW 4TH AVE, Cape Coral, FL 33993", "confidence": "HIGH"}, "property_county": {"value": "Lee County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated. Elevation certificate explicitly marked false."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, driveways, structures) unknown \u2014 no aerial or appraiser data", "Order is On Hold \u2014 reason for hold not specified, needs human review", "Scope of CAD file service unclear \u2014 needs clarification on what deliverable is expected", "No fieldwork date scheduled", "No delivery date set"], "summary": "Individual client Kieu Le has a paid but on-hold CAD file order for a residential property at 304 NW 4TH AVE, Cape Coral, FL (Lee County, Flood Zone X) with special pricing applied and no fieldwork or delivery dates scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:54:44.287664+00:00</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
@@ -13534,7 +13627,7 @@
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:16.082424+00:00</t>
+          <t>2026-06-02T18:54:44.343539+00:00</t>
         </is>
       </c>
     </row>
@@ -13546,7 +13639,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13566,7 +13659,17 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>6020 LE LAC RD</t>
+          <t>6020 Le Lac Rd, Boca Raton, FL 33496</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507221434056809, "created_at": "2025-07-22T10:36:04", "customer_email": "jmas@p1capital.com", "customer_id": 202507221434057979, "customer_name": "Jacqueline Mas", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0967F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000268445, "paid": true, "property_address": "6020 LE LAC RD", "property_city": "BOCA RATON", "property_county": "Palm Beach County", "property_lat": "26.416012", "property_lng": "-80.1378955", "property_state": "FL", "property_zip": "33496", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000268445", "customer_email": "jmas@p1capital.com", "service_type": "CAD file", "county": "", "property_address": "6020 LE LAC RD", "customer_name": "Jacqueline Mas"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Jacqueline Mas", "confidence": "HIGH"}, "client_email": {"value": "jmas@p1capital.com", "confidence": "HIGH"}, "property_address": {"value": "6020 Le Lac Rd, Boca Raton, FL 33496", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type listed as 'CAD file'; no additional services indicated. Unclear if this is a CAD conversion of existing survey or requires new fieldwork \u2014 order is On Hold with no fieldwork date set."}, "special_requirements": {"value": "Special pricing flagged; order is On Hold (status code 11); no elevation certificate requested; flood zone X per FIRM panel 12099C0967F effective 10/05/2017", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available and no emails or attachments to reference; pool, structures, and lot features unknown for this address in Boca Raton 33496."}, "client_tier": {"value": "unknown", "confidence": "MEDIUM", "notes": "Email domain p1capital.com suggests possible business/investment entity (P1 Capital), but customer_type is listed as 'individual'. Possible B2B relationship warrants verification."}, "urgency": {"value": "normal", "confidence": "MEDIUM", "notes": "Order is On Hold with no fieldwork or delivery date set; no rush indicators present, though order was created July 2025 and last updated January 2026 suggesting it has been stalled."}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, outbuildings, driveway, etc.)", "Reason order is On Hold not specified \u2014 needs clarification", "Scope of CAD file service unclear \u2014 new fieldwork required or conversion of existing survey?", "No existing survey or source documents attached or referenced", "Client tier ambiguous \u2014 confirm whether Jacqueline Mas is acting as an individual or on behalf of P1 Capital", "Special pricing terms not detailed \u2014 amount or discount not specified", "No invoice has been generated despite paid=true and due_amount=0 \u2014 needs reconciliation"], "summary": "This is a CAD file order for 6020 Le Lac Rd, Boca Raton FL (Palm Beach County) placed by Jacqueline Mas, currently On Hold since July 2025 with special pricing flagged, no fieldwork scheduled, and key property details including lot size, legal description, and order scope still unknown."}}</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:54:59.033964+00:00</t>
         </is>
       </c>
       <c r="T218" t="inlineStr">
@@ -13576,7 +13679,7 @@
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:16.163096+00:00</t>
+          <t>2026-06-02T18:54:59.089589+00:00</t>
         </is>
       </c>
     </row>
@@ -13588,7 +13691,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13608,7 +13711,17 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>999 ELDERBERRY WAY</t>
+          <t>999 Elderberry Way, Boca Raton, FL 33486</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507221335593435, "created_at": "2025-07-22T09:45:00", "customer_email": "jeb@planestocks.com", "customer_id": 202507221335594645, "customer_name": "Jeb Thomas", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C1178G\nZONE: X500\nZONE: AE\nELEV: 07 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000268436, "paid": true, "property_address": "999 ELDERBERRY WAY", "property_city": "BOCA RATON", "property_county": "Palm Beach County", "property_lat": "26.3411267", "property_lng": "-80.0994102", "property_state": "FL", "property_zip": "33486", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000268436", "customer_email": "jeb@planestocks.com", "service_type": "CAD file", "county": "", "property_address": "999 ELDERBERRY WAY", "customer_name": "Jeb Thomas"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Jeb Thomas", "confidence": "HIGH"}, "client_email": {"value": "jeb@planestocks.com", "confidence": "HIGH"}, "property_address": {"value": "999 Elderberry Way, Boca Raton, FL 33486", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD file; no additional services indicated in order data"}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); flood zone data present \u2014 Panel 12099C1178G, zones X500 and AE, base flood elevation 7 ft, effective 12/20/2024", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, no emails, no aerial data provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fences, driveways, etc.)", "No matching emails found \u2014 unable to confirm scope or client communications", "Order is On Hold \u2014 reason for hold not specified, needs human review", "Elevation certificate not ordered but dual flood zones (X500 and AE) present \u2014 may warrant discussion with client", "Invoice not yet sent and due amount is $0 \u2014 pricing needs to be confirmed given special_pricing flag", "Fieldwork and delivery dates not scheduled"], "summary": "Residential CAD file order for Jeb Thomas at 999 Elderberry Way, Boca Raton FL (Palm Beach County), currently On Hold with special pricing applied, dual flood zones AE and X500, and no supporting appraiser or email data available."}}</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:55:10.620216+00:00</t>
         </is>
       </c>
       <c r="T219" t="inlineStr">
@@ -13618,7 +13731,7 @@
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:16.244456+00:00</t>
+          <t>2026-06-02T18:55:10.674990+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -10935,7 +10935,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10958,16 +10958,37 @@
           <t>1198 INDIAN RIVER DR, COCOA, FL 32922</t>
         </is>
       </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>{"total_amount": 562.0, "services": [{"name": "Land Survey", "description": "Boundary/land survey at 1198 Indian River Dr, Cocoa, FL (Brevard County). Management-agreed negotiated base rate for individual client Carla Quigley.", "amount": 500.0}, {"name": "Complexity Upcharge \u2014 Lot Size (0.31\u20130.50 ac)", "description": "Property is 0.41 acres, falling in the 0.31\u20130.50 ac tier, warranting a standard size upcharge.", "amount": 62.0}], "pricing_reasoning": "The negotiated base survey rate of $500.00 was agreed upon by management for this specific individual client and is used as-is. The lot is 0.41 acres, placing it in the 0.31\u20130.50 ac complexity tier (+$62.00). The property is waterfront (Indian River frontage implied by address and legal description referencing 'Mean Water Level of the Indian River'), however given that a special/negotiated rate is already in place and the base has been reduced from standard, the waterfront upcharge is not layered on top to avoid double-penalizing the client beyond the management-agreed rate \u2014 this is noted for human review. No Elevation Certificate was ordered. FEMA Zone AE does not trigger a VE surcharge. Metes-and-bounds legal description is noted but the negotiated rate is presumed to have accounted for property complexity.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_ORDER: Order 1000217074 at 1198 N Indian River Dr, Brevard County (service: Land Survey and Elevation) shares same coordinates and Folio 24-36-21-BM-0000*.0-0006.00 \u2014 human review required to determine if this is a re-order or redundant job.", "DUPLICATE_ORDER: Order 1000275438 at 1198 Indian River Dr, Brevard County (service: Land Survey Only) shares same coordinates and Folio 24-36-21-BM-0000*.0-0006.00 \u2014 possible duplicate of this order; human review required before dispatching.", "WATERFRONT_NOT_CHARGED: Property legal description references 'Mean Water Level of the Indian River,' indicating waterfront complexity. Waterfront canal upcharge (+$87.00) was intentionally omitted given the management-negotiated base rate already in place \u2014 flag for manager confirmation if upcharge should be added.", "METES_AND_BOUNDS: Legal description is metes-and-bounds style with waterfront boundary reference. Upcharge not applied given negotiated rate; confirm with management.", "ORDER_ON_HOLD: Notes indicate order is currently On Hold with special pricing applied \u2014 confirm hold status is resolved before invoicing.", "NO_EC_ORDERED: Property is in FEMA Flood Zone AE (elevation 4 ft). Client did not order an Elevation Certificate. Consider recommending EC to client given flood zone classification."]}</t>
+        </is>
+      </c>
       <c r="H166" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202511031743205660, "created_at": "2025-11-03T15:48:05", "customer_email": "cquigley@bellsouth.net", "customer_id": 202511031743206718, "customer_name": "CARLA  QUIGLEY", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12009C0340H\nZONE: AE\nELEV: 04 FT\nEFF: 01/29/2021", "invoiced": false, "order_id": 1000273967, "paid": false, "property_address": "1198 INDIAN RIVER DR", "property_city": "COCOA", "property_county": "Brevard County", "property_lat": "28.3802697", "property_lng": "-80.7352536", "property_state": "FL", "property_zip": "32922", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273967", "customer_email": "cquigley@bellsouth.net", "service_type": "Land Survey Only", "county": "", "property_address": "1198 INDIAN RIVER DR", "customer_name": "CARLA  QUIGLEY"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "CARLA QUIGLEY", "confidence": "HIGH"}, "client_email": {"value": "cquigley@bellsouth.net", "confidence": "HIGH"}, "property_address": {"value": "1198 INDIAN RIVER DR, COCOA, FL 32922", "confidence": "HIGH"}, "property_county": {"value": "Brevard County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing applied. Order is On Hold (status code 11). Property is in FEMA Flood Zone AE with base flood elevation 4 FT (FIRM panel 12009C0340H, effective 01/29/2021).", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or aerial data provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, structures, etc.) unknown \u2014 no appraiser or aerial data", "Order is On Hold \u2014 reason for hold not specified, needs human review", "Special pricing flag is true \u2014 pricing details or authorization not documented", "No fieldwork or delivery dates scheduled", "No matching emails found \u2014 no additional client communication available"], "summary": "Residential land survey order for Carla Quigley at 1198 Indian River Dr, Cocoa, FL (Brevard County), currently On Hold with special pricing applied and the property located in FEMA Flood Zone AE."}}</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>1780426901535</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>2026-06-02T17:57:23.218739+00:00</t>
         </is>
       </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:01:44.141377+00:00</t>
+        </is>
+      </c>
+      <c r="R166" t="n">
+        <v>562</v>
+      </c>
       <c r="T166" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:18.193976+00:00</t>
@@ -10975,7 +10996,7 @@
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>2026-06-02T17:57:23.269439+00:00</t>
+          <t>2026-06-02T19:01:44.195842+00:00</t>
         </is>
       </c>
     </row>
@@ -10987,7 +11008,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -11010,16 +11031,37 @@
           <t>321 SW 24TH RD, MIAMI, FL 33129</t>
         </is>
       </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "Boundary Survey", "description": "Standard residential boundary survey at negotiated management-approved rate for individual client Bindu Rammohan. Property is 0.16 acres in Miami-Dade County \u2014 falls within the base lot size tier (\u22640.30 ac), no complexity upcharges supported by available data. No pool, waterfront, heavy vegetation, metes-and-bounds, or Monroe County factors identified. FEMA zone unknown; no EC requested.", "amount": 450.0}], "pricing_reasoning": "Management has agreed to a negotiated base rate of $450.00 for this individual client. The property is a small residential lot (0.16 acres) in Miami-Dade County with no complexity indicators present in the available data \u2014 no waterfront, no pool, no metes-and-bounds legal description, no Monroe County mobilization, and FEMA zone is unknown with no EC requested. The CAD file deliverable is included within the standard survey scope and does not warrant a separate line item at this tier.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE_DUPLICATE: Order 1000237788 is flagged at the same address (321 SW 24TH RD, Miami-Dade County), same Folio/MLS (0141390052220), with a Land Survey Only service type. Human review recommended to confirm whether this is a repeat order, a redelivery request (CAD file from prior survey), or a new independent engagement.", "FEMA_ZONE_UNKNOWN: Flood zone could not be confirmed. If property is later determined to be in a FEMA special flood hazard area and client requests an Elevation Certificate, a separate EC line item at $275.00 should be added.", "MISSING_LEGAL_DESCRIPTION: No legal description was provided. If the parcel requires a metes-and-bounds traverse upon field verification, a +$100.00 complexity upcharge may apply.", "SCOPE_NOTE: Client requested a CAD file deliverable. This has been treated as included in the survey scope under the negotiated rate. If a standalone CAD file from a prior survey (linked to Order 1000237788) is all that is needed, pricing should be re-evaluated by management."]}</t>
+        </is>
+      </c>
       <c r="H167" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202511031731320494, "created_at": "2025-11-03T12:42:01", "customer_email": "BinduRamm@gmail.com", "customer_id": 202511031731321742, "customer_name": "Bindu Rammohan", "customer_type": "individual", "delivered_at": "2025-11-03T17:42:15", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": null, "invoiced": false, "order_id": 1000273966, "paid": false, "property_address": "321 SW 24TH RD", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.7572867", "property_lng": "-80.206683", "property_state": "FL", "property_zip": "33129", "service_type": "Quote, CAD file", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273966", "customer_email": "BinduRamm@gmail.com", "service_type": "Quote, CAD file", "county": "", "property_address": "321 SW 24TH RD", "customer_name": "Bindu Rammohan"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Bindu Rammohan", "confidence": "HIGH"}, "client_email": {"value": "BinduRamm@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "321 SW 24TH RD, MIAMI, FL 33129", "confidence": "HIGH"}, "property_county": {"value": "MIAMI-DADE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Quote", "CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'Quote, CAD file' in order data."}, "special_requirements": {"value": "Special pricing applied to this order.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial imagery, or email attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, driveways, etc.) unknown \u2014 no appraiser or aerial data available", "No matching emails found to supplement order details", "Scope of CAD file not clarified (boundary, topo, as-built, etc.)", "No fieldwork date scheduled", "Invoice amount not set (due_amount: 0.00, invoiced: false)", "Flood zone not determined"], "summary": "Individual residential client Bindu Rammohan has requested a quote and CAD file for a property at 321 SW 24TH RD, Miami, FL 33129 (Miami-Dade County), with special pricing applied, but key property details and scope specifics are missing."}}</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>1780426923920</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>2026-06-02T17:57:33.065198+00:00</t>
         </is>
       </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:02:06.595116+00:00</t>
+        </is>
+      </c>
+      <c r="R167" t="n">
+        <v>450</v>
+      </c>
       <c r="T167" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:18.259420+00:00</t>
@@ -11027,7 +11069,7 @@
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>2026-06-02T17:57:33.116144+00:00</t>
+          <t>2026-06-02T19:02:06.650564+00:00</t>
         </is>
       </c>
     </row>
@@ -13743,7 +13785,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13763,7 +13805,17 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>136 SAN SALVADOR ST</t>
+          <t>136 San Salvador St, Naples, FL 34113</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202503171744142441, "created_at": "2025-07-21T14:00:02", "customer_email": "southernpoolssouth@gmail.com", "customer_id": 202503171744562924, "customer_name": "Austin Akers", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12105C0315G\nZONE: X\nEFF: 12/22/2016", "invoiced": false, "order_id": 1000268401, "paid": true, "property_address": "136 SAN SALVADOR ST", "property_city": "NAPLES", "property_county": "Collier County", "property_lat": "25.9799891", "property_lng": "-81.7284949", "property_state": "FL", "property_zip": "34113", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000268401", "customer_email": "southernpoolssouth@gmail.com", "service_type": "CAD file", "county": "", "property_address": "136 SAN SALVADOR ST", "customer_name": "Austin Akers"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Austin Akers", "confidence": "HIGH"}, "client_email": {"value": "southernpoolssouth@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "136 San Salvador St, Naples, FL 34113", "confidence": "HIGH"}, "property_county": {"value": "Collier County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file' in order data. No additional services indicated."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser lookup unavailable and no emails or attachments provided."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage unknown", "Property features unknown (pool, sheds, driveways, etc.)", "Order is On Hold \u2014 reason for hold not specified, needs human review", "No fieldwork date scheduled", "No delivery date set", "County appraiser data unavailable", "No supporting emails or attachments to reference"], "summary": "B2B client Austin Akers has a paid but On Hold CAD file order for 136 San Salvador St, Naples, FL (Collier County, Flood Zone X) with special pricing applied and no fieldwork or delivery dates scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:00:28.527118+00:00</t>
         </is>
       </c>
       <c r="T220" t="inlineStr">
@@ -13773,7 +13825,7 @@
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:16.336033+00:00</t>
+          <t>2026-06-02T19:00:28.581095+00:00</t>
         </is>
       </c>
     </row>
@@ -13785,7 +13837,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13805,7 +13857,17 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>VERMONT ST</t>
+          <t>VERMONT ST, ALAFAYA, FL 32820</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202506161605533021, "created_at": "2025-07-21T13:14:02", "customer_email": "LTLBunny65@yahoo.com", "customer_id": 202506161605534068, "customer_name": "Diana Cruz", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12095C0315F\nZONE: A\nEFF: 09/25/2009", "invoiced": false, "order_id": 1000268398, "paid": false, "property_address": "VERMONT ST", "property_city": "ALAFAYA", "property_county": "Orange County", "property_lat": "28.5521522", "property_lng": "-81.097552", "property_state": "FL", "property_zip": "32820", "service_type": "Quote", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000268398", "customer_email": "LTLBunny65@yahoo.com", "service_type": "Quote", "county": "", "property_address": "VERMONT ST", "customer_name": "Diana Cruz"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Diana Cruz", "confidence": "HIGH"}, "client_email": {"value": "LTLBunny65@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "VERMONT ST, ALAFAYA, FL 32820", "confidence": "MEDIUM"}, "property_county": {"value": "Orange County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service has been identified. Actual service scope needs clarification from client."}, "special_requirements": {"value": "Special pricing flagged; order is On Hold (status code 11); flood zone identified as 12095C0315F, Zone A, effective 09/25/2009", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 no appraiser data, no emails, no aerial imagery referenced. Street-only address (no house number) suggests possible vacant land."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["No street number on property address \u2014 'VERMONT ST' only, possible vacant/unaddressed lot", "Specific survey service type not identified \u2014 Quote only, needs scope clarification", "Lot size unknown \u2014 no appraiser data available", "Legal description missing", "Structure square footage unknown", "Property features (structures, pool, etc.) unknown", "No customer data returned from FTF customer lookup", "No matching emails found \u2014 no additional context from client communications", "Order is On Hold \u2014 reason for hold not specified", "Elevation certificate flagged as false \u2014 confirm whether one is needed given Zone A flood designation"], "summary": "Individual client Diana Cruz has a quote-only order on hold for an unaddressed parcel on Vermont St in Alafaya, FL (Orange County), located in FEMA Flood Zone A, with no survey scope, lot data, or supporting documentation available."}}</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:00:40.911513+00:00</t>
         </is>
       </c>
       <c r="T221" t="inlineStr">
@@ -13815,7 +13877,7 @@
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:16.417143+00:00</t>
+          <t>2026-06-02T19:00:40.966379+00:00</t>
         </is>
       </c>
     </row>
@@ -13827,7 +13889,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13847,7 +13909,17 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>OAK HARBOUR DR, SLIP D-21</t>
+          <t>OAK HARBOUR DR, SLIP D-21, JUNO BEACH, FL 33408</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201801311052368623, "created_at": "2025-08-06T18:28:05", "customer_email": "susan@rossfelty.com", "customer_id": 202507101700247961, "customer_name": "Susan  Stratton", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0377G\nZONE: AE\nELEV: 07 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000268375, "paid": false, "property_address": "OAK HARBOUR DR, SLIP D-21", "property_city": "JUNO BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.8580111", "property_lng": "-80.0648236", "property_state": "FL", "property_zip": "33408", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000268375", "customer_email": "susan@rossfelty.com", "service_type": "Land Survey Only", "county": "", "property_address": "OAK HARBOUR DR, SLIP D-21", "customer_name": "Law Office of Kyle Felty, P.A."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Law Office of Kyle Felty, P.A.", "confidence": "MEDIUM"}, "client_email": {"value": "susan@rossfelty.com", "confidence": "HIGH"}, "property_address": {"value": "OAK HARBOUR DR, SLIP D-21, JUNO BEACH, FL 33408", "confidence": "HIGH"}, "property_county": {"value": "PALM BEACH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested (elevation_cert: false)"}, "special_requirements": {"value": "Special pricing applied; property is a marina slip (SLIP D-21) which may require specific survey methodology; flood zone AE with base flood elevation 7 FT (FIRM panel 12099C0377G, effective 12/20/2024)", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "Property is a marina/boat slip (SLIP D-21 on OAK HARBOUR DR); no structural or site feature data available \u2014 aerial or appraiser lookup needed"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order contact is 'Susan Stratton' but company name listed as 'Law Office of Kyle Felty, P.A.' \u2014 confirm correct billing entity", "Order is currently ON HOLD \u2014 reason for hold is unknown and should be clarified before proceeding", "Legal description for marina slip not provided", "Lot/slip size or dimensions not available", "No parcel ID or folio number provided \u2014 Palm Beach County PA lookup needed", "Survey scope for a boat slip may differ from a standard land parcel \u2014 confirm deliverable expectations", "Special pricing flag is set but pricing/discount details are not documented", "No fieldwork or delivery date scheduled", "Property features and site conditions unknown \u2014 no aerial or appraiser data available"], "summary": "B2B order for a Land Survey Only at a marina boat slip (SLIP D-21, Oak Harbour Dr, Juno Beach, FL 33408) in Palm Beach County for Law Office of Kyle Felty, P.A., currently on hold with special pricing applied and significant missing parcel and scope details."}}</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:00:55.107755+00:00</t>
         </is>
       </c>
       <c r="T222" t="inlineStr">
@@ -13857,7 +13929,7 @@
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:16.551865+00:00</t>
+          <t>2026-06-02T19:00:55.163407+00:00</t>
         </is>
       </c>
     </row>
@@ -13869,7 +13941,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13889,7 +13961,17 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>930 NE 74TH ST</t>
+          <t>930 NE 74TH ST, MIAMI, FL 33138</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201801311049033113, "created_at": "2025-07-21T14:04:01", "customer_email": "mw@closingexpress.com", "customer_id": 202507141649384681, "customer_name": "Michael Weissman", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0308L\nZONE: AE\nELEV: 09 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000268354, "paid": true, "property_address": "930 NE 74TH ST", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.8432678", "property_lng": "-80.1773817", "property_state": "FL", "property_zip": "33138", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000268354", "customer_email": "mw@closingexpress.com", "service_type": "CAD file", "county": "", "property_address": "930 NE 74TH ST", "customer_name": "Closing Express, Inc."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Closing Express, Inc.", "confidence": "HIGH"}, "client_email": {"value": "mw@closingexpress.com", "confidence": "HIGH"}, "property_address": {"value": "930 NE 74TH ST, MIAMI, FL 33138", "confidence": "HIGH"}, "property_county": {"value": "MIAMI-DADE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status_code 11); flood zone AE at 09 FT elevation per panel 12086C0308L effective 09/11/2009", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no aerial or email data present"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, driveways, structures) unknown \u2014 no appraiser or aerial data", "Order is On Hold \u2014 reason for hold not specified, may require human review", "No fieldwork or delivery dates set", "County field is blank in outer FTF payload (though Miami-Dade is in order data)", "No matching emails found to confirm scope or client instructions"], "summary": "B2B CAD file order for Closing Express, Inc. at 930 NE 74TH ST, Miami, FL (Miami-Dade County) is currently On Hold with special pricing applied, pending fieldwork scheduling and missing property detail data."}}</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:01:05.747211+00:00</t>
         </is>
       </c>
       <c r="T223" t="inlineStr">
@@ -13899,7 +13981,7 @@
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:16.633709+00:00</t>
+          <t>2026-06-02T19:01:05.802590+00:00</t>
         </is>
       </c>
     </row>
@@ -13911,7 +13993,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -13931,7 +14013,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>916 NE 4TH ST</t>
+          <t>916 NE 4TH ST, POMPANO BEACH, FL 33060</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507161554161308, "created_at": "2025-07-16T12:13:05", "customer_email": "Jeff@b90consulting.com", "customer_id": 202507161554162500, "customer_name": "Jeff Becker", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0369J\nZONE: AE\nELEV: 06 FT\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000268167, "paid": true, "property_address": "916 NE 4TH ST", "property_city": "POMPANO BEACH", "property_county": "BROWARD COUNTY", "property_lat": "26.1260145", "property_lng": "-80.1337179", "property_state": "FL", "property_zip": "33060", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000268167", "customer_email": "Jeff@b90consulting.com", "service_type": "CAD file", "county": "", "property_address": "916 NE 4TH ST", "customer_name": "Jeff Becker"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Jeff Becker", "confidence": "HIGH"}, "client_email": {"value": "Jeff@b90consulting.com", "confidence": "HIGH"}, "property_address": {"value": "916 NE 4TH ST, POMPANO BEACH, FL 33060", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Only service listed is CAD file; unclear if this is a standalone deliverable or tied to a prior survey such as a boundary or elevation cert. No elevation certificate requested per order flag."}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); flood zone AE with base flood elevation 6 FT per panel 12011C0369J effective 07/31/2024", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM", "notes": "Email domain b90consulting.com suggests a business/consulting entity despite customer_type being listed as individual"}, "urgency": {"value": "normal", "confidence": "MEDIUM", "notes": "Order is On Hold with no fieldwork or delivery date set; no rush indicators present"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, fence, driveway, etc.) unknown", "Reason for On Hold status not documented", "Unclear what source survey or fieldwork the CAD file deliverable is based on", "No fieldwork date scheduled", "Invoice not yet sent \u2014 pricing details not confirmed beyond special pricing flag", "Customer type listed as individual but email suggests business \u2014 client tier should be verified", "No supporting emails or attachments to clarify scope"], "summary": "Jeff Becker (likely B2B via b90consulting.com) has a paid but On Hold CAD file order for a flood zone AE property at 916 NE 4TH ST, Pompano Beach, FL, with special pricing applied and no fieldwork or delivery date set."}}</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:01:18.358434+00:00</t>
         </is>
       </c>
       <c r="T224" t="inlineStr">
@@ -13941,7 +14033,7 @@
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:16.716232+00:00</t>
+          <t>2026-06-02T19:01:18.413723+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -11081,7 +11081,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -11104,16 +11104,37 @@
           <t>465 Savoie Dr, Palm Beach Gardens, FL 33410</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>{"total_amount": 475.0, "services": [{"name": "Boundary Survey", "description": "Standard residential boundary survey for Lot 33, Frenchman's Reserve PCD-Plat D, 465 Savoie Dr, Palm Beach Gardens, FL. 0.27-acre platted lot with clean legal description. Base rate for individual homeowner client with no prior order history.", "amount": 475.0}], "pricing_reasoning": "No specific survey type was requested, but this is a residential individual client with no negotiated rate, so the default base rate of $475.00 applies for a standard boundary survey. The lot is 0.27 acres (below the 0.31-acre threshold for a size upcharge), the legal description is a clean platted lot reference (no metes and bounds complexity), FEMA Zone X requires no Elevation Certificate, and Palm Beach County carries no remote mobilization premium. No aerial evidence of pool, waterfront canal, or heavy vegetation was available to review, and no complexity upcharges are supported by the data on hand.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "No specific survey service type has been identified by the client \u2014 the order is on hold with significant data gaps per order notes. The quote is priced as a standard boundary survey based on reasonable assumption, but management or client outreach should confirm the actual service requested (boundary survey, TOPO, as-built, etc.) before issuing a formal invoice. Additionally, without aerial imagery review, pool or other site complexity cannot be fully ruled out.", "flags": ["SERVICE TYPE UNCONFIRMED: Client has not specified the survey service type. Quote assumes standard boundary survey. Confirm with client before proceeding.", "ORDER ON HOLD: Per order notes, this order is currently on hold pending clarification of service type and data gaps.", "NO AERIAL REVIEW: Aerial imagery was not available in this context. Field staff should verify for pool, waterfront, or heavy vegetation conditions that could warrant complexity upcharges.", "FIRST-TIME CLIENT: Mary Ann Roberts has 0 prior orders with NexGen Surveying. Default individual rate of $475.00 applied."]}</t>
+        </is>
+      </c>
       <c r="H168" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510302059225948, "created_at": "2025-10-31T09:14:05", "customer_email": "maryannroberts@rogers.com", "customer_id": 202510302059226265, "customer_name": "Mary Ann Roberts", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0377G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000273870, "paid": false, "property_address": "465 SAVOIE DR", "property_city": "PALM BEACH GARDENS", "property_county": "Palm Beach County", "property_lat": "26.8657004", "property_lng": "-80.0808679", "property_state": "FLORIDA", "property_zip": "33410", "service_type": "Quote", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273870", "customer_email": "maryannroberts@rogers.com", "service_type": "Quote", "county": "", "property_address": "465 SAVOIE DR", "customer_name": "Mary Ann Roberts"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Mary Ann Roberts", "confidence": "HIGH"}, "client_email": {"value": "maryannroberts@rogers.com", "confidence": "HIGH"}, "property_address": {"value": "465 Savoie Dr, Palm Beach Gardens, FL 33410", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey type identified. Needs clarification on what survey product is being requested."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available; no emails or attachments to reference. Pool, shed, driveways, and other features unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not identified \u2014 'Quote' is not a survey product", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, etc.)", "No matching emails found \u2014 no additional context from client", "Special requirements or scope notes not provided", "Order is On Hold \u2014 reason for hold not specified", "Elevation certificate not requested but flood zone is present (Zone X) \u2014 may be worth confirming with client"], "summary": "Individual residential client Mary Ann Roberts has requested a quote for a property at 465 Savoie Dr, Palm Beach Gardens, FL 33410 (Palm Beach County), but no specific survey service type has been identified and the order is currently on hold with significant data gaps."}}</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>1780427263284</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>2026-06-02T17:57:42.878672+00:00</t>
         </is>
       </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:07:45.773025+00:00</t>
+        </is>
+      </c>
+      <c r="R168" t="n">
+        <v>475</v>
+      </c>
       <c r="T168" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:18.326413+00:00</t>
@@ -11121,7 +11142,7 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>2026-06-02T17:57:42.930256+00:00</t>
+          <t>2026-06-02T19:07:45.829191+00:00</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11154,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -11156,16 +11177,37 @@
           <t>1607 Lake Downey Dr #25, Orlando, FL 32825</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>{"total_amount": 612.0, "services": [{"name": "Land Survey Only", "description": "Base boundary survey for individual residential client \u2014 default individual rate applied.", "amount": 475.0}, {"name": "Lot Size Complexity Upcharge (0.51\u20131.00 ac)", "description": "Lot size recorded at 0.98 acres per database, falling within the 0.51\u20131.00 ac bracket. Upcharge applied per complexity schedule.", "amount": 137.0}], "pricing_reasoning": "This is a straightforward Land Survey Only order for an individual residential client (Joseph Platten, no negotiated rate, first-time client) in Orange County. The base rate of $475.00 applies. The lot size of 0.98 acres falls within the 0.51\u20131.00 ac complexity bracket, warranting the $137.00 upcharge. No Elevation Certificate was requested, the property is in FEMA Zone X (no flood risk premium), no waterfront canal, pool, metes-and-bounds, Monroe County, or heavy vegetation indicators are present in the data, so no additional upcharges are warranted.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["Order notes indicate pricing, lot data, and legal description were 'not yet established' at time of order creation \u2014 however, the order now carries a valid legal description (Lot 25, Block A, Flowers Manor, Plat Book R, Page 131) and a 0.98-acre lot size from the database. Pricing can proceed on the current data. Confirm lot size against plat if any discrepancy arises in the field.", "Property address includes a unit designator (#25), which corresponds to the platted lot number rather than a condominium or stacked unit \u2014 legal description confirms a platted single-family lot. No condo-complexity flag applied."]}</t>
+        </is>
+      </c>
       <c r="H169" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510301444567148, "created_at": "2025-10-30T11:30:01", "customer_email": "josephplatten9@gmail.com", "customer_id": 202510301444567473, "customer_name": "Joseph Platten", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12095C0280F\nZONE: X\nEFF: 09/25/2009", "invoiced": false, "order_id": 1000273827, "paid": false, "property_address": "1607 LAKE DOWNEY DR #25", "property_city": "ORLANDO", "property_county": "ORANGE COUNTY", "property_lat": "28.566124", "property_lng": "-81.238905", "property_state": "FLORIDA", "property_zip": "32825", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273827", "customer_email": "josephplatten9@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "1607 LAKE DOWNEY DR #25", "customer_name": "Joseph Platten"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Joseph Platten", "confidence": "HIGH"}, "client_email": {"value": "josephplatten9@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1607 Lake Downey Dr #25, Orlando, FL 32825", "confidence": "HIGH"}, "property_county": {"value": "Orange County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data. No elevation certificate requested."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Order is currently On Hold \u2014 reason for hold not specified", "Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 no appraiser or document data available", "Structure square footage unknown", "Property features unknown (pool, shed, fences, etc.)", "Special requirements or client notes not provided", "Urgency/timeline not specified", "Unit #25 suggests condominium or multi-unit complex \u2014 lot/parcel boundaries may differ from standard residential; needs clarification", "No pricing or invoice details established (due amount is $0, not yet invoiced)"], "summary": "Individual residential client Joseph Platten has a Land Survey Only order on hold for a unit property at 1607 Lake Downey Dr #25, Orlando, FL (Orange County), with no pricing, lot data, or legal description yet established."}}</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>1780427283944</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>2026-06-02T17:57:53.262292+00:00</t>
         </is>
       </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:08:06.305324+00:00</t>
+        </is>
+      </c>
+      <c r="R169" t="n">
+        <v>612</v>
+      </c>
       <c r="T169" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:18.391842+00:00</t>
@@ -11173,7 +11215,7 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>2026-06-02T17:57:53.312904+00:00</t>
+          <t>2026-06-02T19:08:06.362460+00:00</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14087,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14065,7 +14107,17 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2530 FAIRWAY DR</t>
+          <t>2530 Fairway Dr, Vero Beach, FL 32960</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507151332405827, "created_at": "2025-07-15T09:38:00", "customer_email": "cmcarc@msn.com", "customer_id": 202507151334263890, "customer_name": "Chris  Crawford", "customer_type": "b2b", "delivered_at": "2025-10-02T00:58:15", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12061C0244J\nZONE: X\nEFF: 01/26/2023", "invoiced": false, "order_id": 1000268064, "paid": false, "property_address": "2530 FAIRWAY DR", "property_city": "VERO BEACH", "property_county": "INDIAN RIVER COUNTY", "property_lat": "27.6455281", "property_lng": "-80.3916215", "property_state": "FL", "property_zip": "32960", "service_type": "CAD file", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000268064", "customer_email": "cmcarc@msn.com", "service_type": "CAD file", "county": "", "property_address": "2530 FAIRWAY DR", "customer_name": "CM Crawford Architect, Inc."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "CM Crawford Architect, Inc.", "confidence": "HIGH"}, "client_email": {"value": "cmcarc@msn.com", "confidence": "HIGH"}, "property_address": {"value": "2530 Fairway Dr, Vero Beach, FL 32960", "confidence": "HIGH"}, "property_county": {"value": "Indian River County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD file; no additional services indicated in the data"}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 county appraiser unavailable", "Structure square footage not provided", "Property features (pool, shed, outbuildings, etc.) unknown \u2014 no aerial or appraiser data", "Scope of CAD file unclear \u2014 boundary only, topographic, or as-built?", "Invoice amount not set (due_amount: 0.00, invoiced: false) \u2014 pricing needs to be confirmed", "Fieldwork not yet scheduled (fieldwork_at: null)", "No matching emails found to clarify project requirements"], "summary": "B2B order from CM Crawford Architect, Inc. for a CAD file deliverable at 2530 Fairway Dr, Vero Beach, FL (Indian River County) \u2014 already delivered but not yet invoiced, with special pricing applied and scope details still unclear."}}</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:06:30.841833+00:00</t>
         </is>
       </c>
       <c r="T225" t="inlineStr">
@@ -14075,7 +14127,7 @@
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:16.804600+00:00</t>
+          <t>2026-06-02T19:06:30.897372+00:00</t>
         </is>
       </c>
     </row>
@@ -14087,7 +14139,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14107,7 +14159,17 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>3737 NW 4TH AVE</t>
+          <t>3737 NW 4TH AVE, BOCA RATON, FL 33431</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202503141457224721, "created_at": "2025-07-14T10:39:02", "customer_email": "denis@beachway.com", "customer_id": 202503141457595126, "customer_name": "Denis Holmes", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0989G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000267983, "paid": true, "property_address": "3737 NW 4TH AVE", "property_city": "BOCA RATON", "property_county": "Palm Beach County", "property_lat": "26.3836291", "property_lng": "-80.09068409999999", "property_state": "FL", "property_zip": "33431", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000267983", "customer_email": "denis@beachway.com", "service_type": "CAD file", "county": "", "property_address": "3737 NW 4TH AVE", "customer_name": "Beachway LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Beachway LLC", "confidence": "MEDIUM"}, "client_email": {"value": "denis@beachway.com", "confidence": "HIGH"}, "property_address": {"value": "3737 NW 4TH AVE, BOCA RATON, FL 33431", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type listed as 'CAD file'; no additional services indicated in the data"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status_code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order contact is 'Denis Holmes' but company name appears to be 'Beachway LLC' \u2014 confirm correct billing name", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, structures, enclosures, etc.) not available", "Reason for On Hold status not documented \u2014 needs human review", "Scope of CAD file service not specified (boundary, topo, as-built, etc.)", "No fieldwork date scheduled", "No delivery date set"], "summary": "B2B order for a CAD file survey at 3737 NW 4TH AVE, Boca Raton, FL for Beachway LLC is currently On Hold with special pricing applied and no fieldwork or delivery dates scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:06:41.284522+00:00</t>
         </is>
       </c>
       <c r="T226" t="inlineStr">
@@ -14117,7 +14179,7 @@
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:16.887513+00:00</t>
+          <t>2026-06-02T19:06:41.341031+00:00</t>
         </is>
       </c>
     </row>
@@ -14129,7 +14191,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14149,7 +14211,17 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>15&amp;17 PALMETTO WAY</t>
+          <t>15 &amp; 17 Palmetto Way, Jupiter, FL 33469</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202405131935092946, "created_at": "2025-07-11T11:34:00", "customer_email": "lynjmac@aol.com", "customer_id": 202405131935094267, "customer_name": "Lyn McCarthy", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0178G\nZONE: X500\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000267922, "paid": true, "property_address": "15&amp;17 PALMETTO WAY", "property_city": "JUPITER ", "property_county": "Palm Beach County", "property_lat": "26.9615427", "property_lng": "-80.110299", "property_state": "FL", "property_zip": "33469", "service_type": "Quote", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000267922", "customer_email": "lynjmac@aol.com", "service_type": "Quote", "county": "", "property_address": "15&amp;17 PALMETTO WAY", "customer_name": "Lyn McCarthy"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Lyn McCarthy", "confidence": "HIGH"}, "client_email": {"value": "lynjmac@aol.com", "confidence": "HIGH"}, "property_address": {"value": "15 &amp; 17 Palmetto Way, Jupiter, FL 33469", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., boundary, topographic, ALTA) has been identified. Requires clarification from client or internal review."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold. Flood zone data present: Panel 12099C0178G, Zones X500 and X, effective 12/20/2024.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available. No appraiser data, aerial data, or email attachments provided. Property involves two parcels (15 &amp; 17) which may indicate a combined or adjacent lot situation requiring clarification."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not defined \u2014 'Quote' is not a deliverable", "Reason order is On Hold is unknown", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, fencing, etc.) unknown \u2014 no appraiser or aerial data", "Two property addresses (15 &amp; 17) \u2014 unclear if one parcel, two parcels, or combined survey scope", "No customer data returned from FTF customer lookup", "No matching emails found \u2014 no additional context from client communication", "County appraiser data unavailable"], "summary": "Individual client Lyn McCarthy is requesting a quote for a survey at a dual-address property (15 &amp; 17 Palmetto Way, Jupiter, FL) in Palm Beach County, but the specific service type, scope, and parcel details remain undefined, and the order is currently On Hold with special pricing applied."}}</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:06:58.734706+00:00</t>
         </is>
       </c>
       <c r="T227" t="inlineStr">
@@ -14159,7 +14231,7 @@
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:16.969688+00:00</t>
+          <t>2026-06-02T19:06:58.791696+00:00</t>
         </is>
       </c>
     </row>
@@ -14171,7 +14243,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14191,7 +14263,17 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>17026 FL-54</t>
+          <t>17026 FL-54, Lutz, FL 33558</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202506181540151362, "created_at": "2025-07-11T10:22:01", "customer_email": "mohit1283@gmail.com", "customer_id": 202506181540152509, "customer_name": "Mohit Garg", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12101C0383F\nZONE: X\nEFF: 09/26/2014", "invoiced": false, "order_id": 1000267907, "paid": true, "property_address": "17026 FL-54", "property_city": "LUTZ", "property_county": "Pasco County", "property_lat": "28.1930894", "property_lng": "-82.5336971", "property_state": "FL", "property_zip": "33558", "service_type": "Quote", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000267907", "customer_email": "mohit1283@gmail.com", "service_type": "Quote", "county": "", "property_address": "17026 FL-54", "customer_name": "Mohit Garg"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Mohit Garg", "confidence": "HIGH"}, "client_email": {"value": "mohit1283@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "17026 FL-54, Lutz, FL 33558", "confidence": "HIGH"}, "property_county": {"value": "Pasco County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service has been selected. Actual service(s) requested require clarification from the client or internal review."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11)", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, no emails, and no aerial imagery provided. Pool, shed, driveways, and other structures unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service(s) requested \u2014 'Quote' is not a deliverable service type", "Reason order is On Hold \u2014 needs internal clarification", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fence, driveway, etc.)", "Urgency or deadline not stated", "No supporting emails or attachments to clarify scope", "Elevation certificate flagged false \u2014 confirm client does not need one given Flood Zone X designation", "County field is blank in the order envelope despite Pasco County being in the nested data \u2014 may indicate a data entry issue"], "summary": "Individual client Mohit Garg has a paid but On Hold quote-stage order for a property at 17026 FL-54 in Lutz, FL (Pasco County), with no specific survey service selected and significant gaps in scope, lot, and property details."}}</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:07:12.167619+00:00</t>
         </is>
       </c>
       <c r="T228" t="inlineStr">
@@ -14201,7 +14283,7 @@
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:17.107557+00:00</t>
+          <t>2026-06-02T19:07:12.223083+00:00</t>
         </is>
       </c>
     </row>
@@ -14213,7 +14295,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14233,7 +14315,17 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>5630 VINTAGE OAKS CIR</t>
+          <t>5630 Vintage Oaks Cir, Delray Beach, FL 33484</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202506171943562782, "created_at": "2025-07-08T12:46:00", "customer_email": "wdeitch1953@gmail.com", "customer_id": 202506171943562880, "customer_name": "Warren Deitch", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0967F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000267661, "paid": true, "property_address": "5630 VINTAGE OAKS CIR", "property_city": "DELRAY BEACH", "property_county": "Palm Beach County", "property_lat": "26.434887", "property_lng": "-80.13265229999999", "property_state": "FL", "property_zip": "33484", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000267661", "customer_email": "wdeitch1953@gmail.com", "service_type": "CAD file", "county": "", "property_address": "5630 VINTAGE OAKS CIR", "customer_name": "Warren Deitch"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Warren Deitch", "confidence": "HIGH"}, "client_email": {"value": "wdeitch1953@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "5630 Vintage Oaks Cir, Delray Beach, FL 33484", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; unclear if this is a standalone deliverable or tied to an underlying survey type \u2014 human clarification recommended"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available; no emails or attachments found; pool, shed, driveways, and other site features unknown"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Underlying survey type is unclear \u2014 CAD file of what survey product (boundary, as-built, topographic, etc.)?", "Reason for On Hold status not documented", "Lot size unknown \u2014 no appraiser data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, fences, driveways) unknown", "No fieldwork date scheduled", "Invoice not yet generated despite paid status \u2014 needs reconciliation", "County field is blank in the top-level order object despite being populated in nested data", "No customer data returned from FTF customer lookup"], "summary": "Residential CAD file order for Warren Deitch at 5630 Vintage Oaks Cir, Delray Beach FL is currently On Hold with special pricing applied, but lacks a defined underlying survey type, fieldwork date, and property detail data."}}</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:07:23.391052+00:00</t>
         </is>
       </c>
       <c r="T229" t="inlineStr">
@@ -14243,7 +14335,7 @@
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:17.192132+00:00</t>
+          <t>2026-06-02T19:07:23.448072+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -11227,7 +11227,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -11250,16 +11250,37 @@
           <t>1211 FL-436, Casselberry, FL 32707</t>
         </is>
       </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "This order requests a CAD file for a commercial property at 8.06 acres, which exceeds the 5.00-acre threshold defined in the pricing guidelines \u2014 any lot over 5.00 acres must be escalated to management regardless of service type. Additionally, the order is currently On Hold with no fieldwork scheduled, the commercial flag is inconsistently marked False despite clear commercial use (Interlachen Corporate Center), and there are three flagged duplicate orders at the same location and folio number requiring human review before any pricing is finalized. The negotiated base rate of $450.00 and client context have been noted for management reference.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "Lot size of 8.06 acres exceeds the 5.00-acre pricing ceiling \u2014 escalate to management for manual quote on all service types. Secondary escalation triggers: (1) order is On Hold with no scheduled fieldwork; (2) commercial flag is set to False despite property being a named corporate center (Interlachen Corporate Center), suggesting a data entry error that should be corrected before invoicing; (3) three duplicate orders exist at the same address and folio (Orders 1000227533, 1000263564, 1000273272) \u2014 management must confirm whether this CAD file request is a standalone deliverable tied to a prior survey or a new scope entirely; (4) client tier is listed as INDIVIDUAL but the order notes reference a B2B client (Foundry Commercial), which may affect applicable rates and contractual terms.", "flags": ["ESCALATE: Lot size 8.06 acres exceeds 5.00-acre pricing threshold \u2014 do not price; requires management quote.", "DUPLICATE: Order 1000227533 \u2014 same address (1211 FL-436, Seminole County), same folio (28213053400000010), service: Land Survey Only.", "DUPLICATE: Order 1000263564 \u2014 same address (1211 FL-436, Seminole County), same folio (28213053400000010), service: Land Survey Only.", "DUPLICATE: Order 1000273272 \u2014 same address (1211 FL-436, Seminole County), same folio (28213053400000010), service: Quote.", "DATA INCONSISTENCY: Commercial flag is False but property is a platted corporate center (Interlachen Corporate Center, Plat Book 66, Page 78) \u2014 flag for correction.", "CLIENT TIER MISMATCH: Client tier listed as INDIVIDUAL but order notes identify client as B2B (Foundry Commercial/Miguel Rojas) \u2014 verify correct tier and applicable rate schedule.", "ORDER STATUS: Currently On Hold with no fieldwork scheduled \u2014 do not invoice until order is activated and scope confirmed."]}</t>
+        </is>
+      </c>
       <c r="H170" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510301338499780, "created_at": "2025-10-30T09:41:01", "customer_email": "miguel.rojas@foundrycommercial.com", "customer_id": 202510301338500888, "customer_name": "Miguel Rojas", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12117C0165F\nZONE: X\nEFF: 09/28/2007", "invoiced": false, "order_id": 1000273817, "paid": true, "property_address": "1211 FL-436", "property_city": "CASSELBERRY", "property_county": "Seminole County", "property_lat": "28.6372143", "property_lng": "-81.32304359999999", "property_state": "FL", "property_zip": "32707", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273817", "customer_email": "miguel.rojas@foundrycommercial.com", "service_type": "CAD file", "county": "", "property_address": "1211 FL-436", "customer_name": "Miguel Rojas"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Miguel Rojas", "confidence": "HIGH"}, "client_email": {"value": "miguel.rojas@foundrycommercial.com", "confidence": "HIGH"}, "property_address": {"value": "1211 FL-436, Casselberry, FL 32707", "confidence": "HIGH"}, "property_county": {"value": "Seminole County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Only service listed is CAD file; no additional services specified in order data"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM", "notes": "Email domain foundrycommercial.com suggests a commercial real estate firm; customer_type is listed as individual but business context is evident"}, "urgency": {"value": "unknown", "confidence": "LOW", "notes": "Order is On Hold with no fieldwork or delivery dates set; cannot determine urgency"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, structures, etc.) unknown \u2014 no appraiser data or emails available", "Reason for On Hold status unknown", "Scope of CAD file request unclear (boundary, topo, as-built, etc.)", "No fieldwork date scheduled", "Client tier ambiguous \u2014 listed as individual but email suggests commercial entity", "No matching emails found to clarify requirements or context"], "summary": "B2B client Miguel Rojas of Foundry Commercial is requesting a CAD file for a commercial property at 1211 FL-436 in Casselberry, FL (Seminole County), with special pricing applied, but the order is currently On Hold with no fieldwork scheduled and limited property detail available."}}</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>1780427623008</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>2026-06-02T18:00:22.970694+00:00</t>
         </is>
       </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:13:46.045390+00:00</t>
+        </is>
+      </c>
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
       <c r="T170" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:18.458219+00:00</t>
@@ -11267,7 +11288,7 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>2026-06-02T18:00:23.025482+00:00</t>
+          <t>2026-06-02T19:13:46.099275+00:00</t>
         </is>
       </c>
     </row>
@@ -11279,7 +11300,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -11302,16 +11323,37 @@
           <t>922 Turner Rd, Delray Beach, FL 33483</t>
         </is>
       </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>{"total_amount": 250.0, "services": [{"name": "CAD File", "description": "Delivery of CAD file for 922 Turner Rd, Delray Beach, FL \u2014 Palm Beach County. Based on management-agreed special pricing for individual client Benjamin Allen.", "amount": 250.0}], "pricing_reasoning": "The service requested is a CAD file delivery only \u2014 no new boundary survey, elevation certificate, or topo survey is being ordered. Management pre-approved a negotiated base rate of $250.00 for this individual client. The lot is 0.22 acres (no size upcharge), Palm Beach County (no Monroe premium), legal description is a platted lot combination (not metes and bounds), and no pool, waterfront, or heavy vegetation complexity is indicated \u2014 so no upcharges apply. The $250.00 flat rate reflects the agreed special pricing noted in the order.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000083966 at 922 Turner Road, Palm Beach County (same Folio 00434604180000971) \u2014 service: Land Survey and Elevation. Human review recommended to confirm prior survey data is being leveraged for this CAD file.", "DUPLICATE_WARNING: Order 1000262434 at 922 Turner Rd, Palm Beach County (same Folio 00434604180000971) \u2014 service: Quote. May represent a prior pricing request for this same client/property.", "DUPLICATE_WARNING: Order 1000262683 at 922 Turner Rd, Palm Beach County (same Folio 00434604180000971) \u2014 service: Land Survey and Elevation. Human review recommended to confirm this CAD file is a derivative deliverable of an already-completed survey rather than a net-new field effort.", "SPECIAL_PRICING: Management-negotiated rate of $250.00 applied per order notes. Invoice and property details noted as still outstanding per order notes \u2014 confirm delivery status before finalizing.", "FEMA_NOTE: Property is in Flood Zone AE (FIRM panel 12099C0981G, effective 12/20/2024, base flood elevation 8 ft). No Elevation Certificate is included in this order; if one is needed separately, standard EC rate of $275.00 applies."]}</t>
+        </is>
+      </c>
       <c r="H171" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202504081537437301, "created_at": "2025-10-27T14:24:03", "customer_email": "benallen2013@gmail.com", "customer_id": 202504081537437404, "customer_name": "Benjamin Allen", "customer_type": "individual", "delivered_at": "2025-12-09T15:36:12", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0981G\nZONE: AE\nELEV: 08 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000273647, "paid": true, "property_address": "922 TURNER RD", "property_city": "DELRAY BEACH", "property_county": "Palm Beach County", "property_lat": "26.4961436", "property_lng": "-80.0595089", "property_state": "FL", "property_zip": "33483", "service_type": "CAD file", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273647", "customer_email": "benallen2013@gmail.com", "service_type": "CAD file", "county": "", "property_address": "922 TURNER RD", "customer_name": "Benjamin Allen"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Benjamin Allen", "confidence": "HIGH"}, "client_email": {"value": "benallen2013@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "922 Turner Rd, Delray Beach, FL 33483", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file' in order data. No additional services indicated."}, "special_requirements": {"value": "Special pricing applied. Flood zone AE, FIRM panel 12099C0981G, base flood elevation 8 ft, effective 12/20/2024.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 no appraiser data, no matching emails, and no aerial data provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, outbuildings, etc.)", "No county appraiser data available", "No matching emails found for additional context", "Fieldwork date not recorded (fieldwork_at is null)", "Invoice has not been generated (invoiced: false) despite order being delivered and paid"], "summary": "Individual residential client Benjamin Allen ordered a CAD file for 922 Turner Rd, Delray Beach, FL (Palm Beach County), located in Flood Zone AE; order is delivered and paid with special pricing applied, but property details and invoice are still outstanding."}}</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1780427643756</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>2026-06-02T18:00:32.708157+00:00</t>
         </is>
       </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:14:06.759899+00:00</t>
+        </is>
+      </c>
+      <c r="R171" t="n">
+        <v>250</v>
+      </c>
       <c r="T171" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:18.524797+00:00</t>
@@ -11319,7 +11361,7 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>2026-06-02T18:00:32.763491+00:00</t>
+          <t>2026-06-02T19:14:06.815216+00:00</t>
         </is>
       </c>
     </row>
@@ -14347,7 +14389,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14367,7 +14409,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>5401 WILES RD</t>
+          <t>5401 WILES RD, COCONUT CREEK, FL 33073</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202411141637401215, "created_at": "2025-07-08T15:26:04", "customer_email": "stefaniebrown@firstam.com", "customer_id": 202503061550487269, "customer_name": "Stefanie Brown", "customer_type": "b2b", "delivered_at": "2025-08-27T12:39:07", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0165H\nZONE: X\nEFF: 08/18/2014", "invoiced": false, "order_id": 1000267659, "paid": true, "property_address": "5401 WILES RD", "property_city": "COCONUT CREEK", "property_county": "BROWARD COUNTY", "property_lat": "26.2864162", "property_lng": "-80.19822909999999", "property_state": "FL", "property_zip": "33073", "service_type": "ALTA Table A Survey", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000267659", "customer_email": "stefaniebrown@firstam.com", "service_type": "ALTA Table A Survey", "county": "", "property_address": "5401 WILES RD", "customer_name": "CDS-Commercial Due Diligence Services"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "CDS-Commercial Due Diligence Services", "confidence": "MEDIUM"}, "client_email": {"value": "stefaniebrown@firstam.com", "confidence": "HIGH"}, "property_address": {"value": "5401 WILES RD, COCONUT CREEK, FL 33073", "confidence": "HIGH"}, "property_county": {"value": "BROWARD COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["ALTA Table A Survey"], "confidence": "HIGH", "notes": "Service type explicitly stated; specific Table A items selected are unknown \u2014 no Table A checklist provided"}, "special_requirements": {"value": "Special pricing applied; Table A items to be confirmed", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data, aerial, or email attachments available to identify pool, shed, driveways, or other visible structures"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order contact is 'Stefanie Brown' at First American, but customer_name field lists 'CDS-Commercial Due Diligence Services' \u2014 clarify billing entity", "Specific ALTA Table A items selected are unknown \u2014 checklist needs to be confirmed", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (improvements, easements, utilities) unknown \u2014 no appraiser or aerial data available", "Fieldwork date is null \u2014 not yet scheduled or data missing", "No matching emails found \u2014 no supplemental scope or instructions available"], "summary": "B2B ALTA Table A Survey order for a commercial property at 5401 Wiles Rd, Coconut Creek, FL (Broward County), placed by Stefanie Brown of First American on behalf of CDS-Commercial Due Diligence Services, with special pricing applied and delivered status confirmed, but Table A item selections and property details still need clarification."}}</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:12:36.317464+00:00</t>
         </is>
       </c>
       <c r="T230" t="inlineStr">
@@ -14377,7 +14429,7 @@
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:17.277153+00:00</t>
+          <t>2026-06-02T19:12:36.373370+00:00</t>
         </is>
       </c>
     </row>
@@ -14389,7 +14441,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14404,12 +14456,22 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Madsen Design</t>
+          <t>Madsen Design (contact: Norberto Loianno)</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2717 SW EAST CALABRIA CIR</t>
+          <t>2717 SW East Calabria Cir, Port St Lucie, FL 34953</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202507021233082783, "created_at": "2025-07-02T08:43:00", "customer_email": "norberto@madsenarchitects.com", "customer_id": 202507021234167424, "customer_name": "Norberto  Loianno", "customer_type": "b2b", "delivered_at": "2025-07-31T20:09:01", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12111C0275J\nZONE: X\nEFF: 02/16/2012", "invoiced": false, "order_id": 1000267373, "paid": true, "property_address": "2717 SW EAST CALABRIA CIR", "property_city": "PORT ST LUCIE", "property_county": "ST. LUCIE COUNTY", "property_lat": "27.2605629", "property_lng": "-80.3839802", "property_state": "FL", "property_zip": "34953", "service_type": "CAD file", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000267373", "customer_email": "norberto@madsenarchitects.com", "service_type": "CAD file", "county": "", "property_address": "2717 SW EAST CALABRIA CIR", "customer_name": "Madsen Design"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Madsen Design (contact: Norberto Loianno)", "confidence": "MEDIUM"}, "client_email": {"value": "norberto@madsenarchitects.com", "confidence": "HIGH"}, "property_address": {"value": "2717 SW East Calabria Cir, Port St Lucie, FL 34953", "confidence": "HIGH"}, "property_county": {"value": "St. Lucie County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file' in order data. No additional services noted."}, "special_requirements": {"value": "Special pricing applied", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, etc.)", "County appraiser data unavailable \u2014 no county passed to lookup", "No matching emails found to corroborate scope or special instructions", "Billing company name ambiguous \u2014 order lists 'Madsen Design' but email domain is 'madsenarchitects.com'; confirm correct client name for invoice", "Fieldwork date is null \u2014 unclear if CAD file was derived from existing survey or new fieldwork", "Invoice not yet generated despite order being delivered and paid \u2014 confirm invoice handling"], "summary": "A delivered and paid CAD file order for b2b client Madsen Design (Norberto Loianno) at 2717 SW East Calabria Cir, Port St Lucie, FL (St. Lucie County), with special pricing applied and no fieldwork date recorded."}}</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:12:46.617373+00:00</t>
         </is>
       </c>
       <c r="T231" t="inlineStr">
@@ -14419,7 +14481,7 @@
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:17.361867+00:00</t>
+          <t>2026-06-02T19:12:46.673125+00:00</t>
         </is>
       </c>
     </row>
@@ -14431,7 +14493,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14446,12 +14508,22 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Pool Renovators</t>
+          <t>Andrew Bernardo / Pool Renovators</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>511 CRYSTAL DR</t>
+          <t>511 Crystal Dr, Madeira Beach, FL 33708</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202506261534585991, "created_at": "2025-06-26T11:40:00", "customer_email": "office@mypoolrenovators.com", "customer_id": 202506261536301331, "customer_name": "Andrew Bernardo", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12103C0191H\nZONE: AE\nELEV: 10 FT\nEFF: 08/24/2021", "invoiced": false, "order_id": 1000267049, "paid": true, "property_address": "511 CRYSTAL DR", "property_city": "MADEIRA BEACH", "property_county": "Pinellas County", "property_lat": "27.7953219", "property_lng": "-82.7840899", "property_state": "FL", "property_zip": "33708", "service_type": "CAD File", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000267049", "customer_email": "office@mypoolrenovators.com", "service_type": "CAD File", "county": "", "property_address": "511 CRYSTAL DR", "customer_name": "Pool Renovators"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Andrew Bernardo / Pool Renovators", "confidence": "MEDIUM"}, "client_email": {"value": "office@mypoolrenovators.com", "confidence": "HIGH"}, "property_address": {"value": "511 Crystal Dr, Madeira Beach, FL 33708", "confidence": "HIGH"}, "property_county": {"value": "Pinellas County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD File'; no additional services specified. Special pricing flag is active."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11); property is in FEMA Flood Zone AE at 10 ft elevation (FIRM panel 12103C0191H, effective 08/24/2021).", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; property appraiser data unavailable and no matching emails found. Pool renovator context suggests a pool may exist on the property."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name discrepancy: FTF order lists 'Andrew Bernardo' as customer_name but 'Pool Renovators' in the outer customer_name field \u2014 confirm correct billing name", "Lot size unknown \u2014 property appraiser data unavailable", "Legal description unknown \u2014 property appraiser data unavailable", "Structure square footage unknown", "Property features unknown (pool, structures, driveway, etc.)", "Reason for On Hold status not specified \u2014 needs human review before proceeding", "Scope of CAD File not defined \u2014 confirm what the CAD file should include (boundary, topo, as-built, etc.)", "Urgency/turnaround not specified", "No fieldwork or delivery dates set", "Invoice has not been sent despite order being marked paid \u2014 verify billing status"], "summary": "B2B CAD File order for a Madeira Beach, FL property in Flood Zone AE, placed by Pool Renovators (contact: Andrew Bernardo), currently On Hold with special pricing applied and several key property details missing."}}</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:12:59.644369+00:00</t>
         </is>
       </c>
       <c r="T232" t="inlineStr">
@@ -14461,7 +14533,7 @@
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:17.446685+00:00</t>
+          <t>2026-06-02T19:12:59.699935+00:00</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14545,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14493,7 +14565,17 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>329 EAGLE DR</t>
+          <t>329 Eagle Dr, Jupiter, FL 33477</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202506251921391561, "created_at": "2025-06-25T15:36:01", "customer_email": "office@shorearchitect.com", "customer_id": 202506251932489007, "customer_name": "Calli Heenan", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0189G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000267001, "paid": true, "property_address": "329 EAGLE DR", "property_city": "JUPITER", "property_county": "Palm Beach County", "property_lat": "26.8977519", "property_lng": "-80.08831409999999", "property_state": "FL", "property_zip": "33477", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000267001", "customer_email": "office@shorearchitect.com", "service_type": "CAD file", "county": "", "property_address": "329 EAGLE DR", "customer_name": "TRB Architects"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "TRB Architects", "confidence": "MEDIUM"}, "client_email": {"value": "office@shorearchitect.com", "confidence": "HIGH"}, "property_address": {"value": "329 Eagle Dr, Jupiter, FL 33477", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Only service type listed is CAD file; scope details (what the CAD file is based on \u2014 boundary, topo, as-built \u2014 is not specified)"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order contact is 'Calli Heenan' but top-level customer_name shows 'TRB Architects' \u2014 confirm correct billing entity", "CAD file scope not defined \u2014 need to know if this is boundary, topographic, as-built, or another type of CAD deliverable", "Reason for 'On Hold' status is unknown \u2014 needs human review", "Lot size not available \u2014 county appraiser data unavailable", "Legal description not available", "Structure square footage not available", "Property features unknown \u2014 no aerial, appraiser, or email data to draw from", "Urgency or deadline not specified", "No fieldwork date scheduled"], "summary": "B2B order from TRB Architects (contact: Calli Heenan) requesting a CAD file for 329 Eagle Dr, Jupiter, FL 33477 (Palm Beach County); order is paid but currently On Hold with special pricing applied and key scope details missing."}}</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:13:11.117911+00:00</t>
         </is>
       </c>
       <c r="T233" t="inlineStr">
@@ -14503,7 +14585,7 @@
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:17.531315+00:00</t>
+          <t>2026-06-02T19:13:11.173677+00:00</t>
         </is>
       </c>
     </row>
@@ -14515,7 +14597,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14530,12 +14612,22 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Pacheco Architecture</t>
+          <t>Pacheco Architecture (contact: Julio Estorino)</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>5810 MAGGIORE ST</t>
+          <t>5810 Maggiore St, Coral Gables, FL 33146</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202506241408122444, "created_at": "2025-06-24T10:11:05", "customer_email": "julio@pachecoarchitecture.com", "customer_id": 202506241409129248, "customer_name": "JULIO  ESTORINO", "customer_type": "b2b", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0459L\nZONE: X\nZONE: X500\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000266847, "paid": false, "property_address": "5810 MAGGIORE ST", "property_city": "CORAL GABLES", "property_county": "Miami-Dade County", "property_lat": "25.7151168", "property_lng": "-80.26381789999999", "property_state": "FL", "property_zip": "33146", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000266847", "customer_email": "julio@pachecoarchitecture.com", "service_type": "CAD file", "county": "", "property_address": "5810 MAGGIORE ST", "customer_name": "Pacheco Architecture"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Pacheco Architecture (contact: Julio Estorino)", "confidence": "HIGH"}, "client_email": {"value": "julio@pachecoarchitects.com", "confidence": "HIGH"}, "property_address": {"value": "5810 Maggiore St, Coral Gables, FL 33146", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; likely a CAD drawing of an existing survey \u2014 scope details not specified"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Scope of CAD file not defined \u2014 based on existing survey, new fieldwork, or specific deliverable format?", "Lot size unknown \u2014 county appraiser unavailable", "Legal description unknown \u2014 county appraiser unavailable", "Structure square footage unknown", "Property features unknown (pool, fence, structures, etc.)", "Fieldwork date not scheduled", "Order is On Hold \u2014 reason for hold not specified", "No matching emails found \u2014 no additional context from client communications", "Due amount is $250 \u2014 confirm if this reflects full scope or partial/special pricing adjustment"], "summary": "B2B order from Pacheco Architecture (Julio Estorino) requesting a CAD file for a residential property at 5810 Maggiore St, Coral Gables, FL 33146 (Miami-Dade County), currently On Hold with special pricing applied and no fieldwork scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:13:22.528721+00:00</t>
         </is>
       </c>
       <c r="T234" t="inlineStr">
@@ -14545,7 +14637,7 @@
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:17.677204+00:00</t>
+          <t>2026-06-02T19:13:22.585321+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -11373,7 +11373,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -11396,16 +11396,37 @@
           <t>35135 Pinegate Trail, Eustis, FL 32736</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>{"total_amount": 1000.0, "services": [{"name": "CAD File / Land Survey", "description": "Boundary survey with CAD file deliverable for LOT 127, LAKEWOOD RANCHES, Lake County. 5.00-acre platted lot. Negotiated base rate per management agreement.", "amount": 450.0}, {"name": "Acreage Complexity Upcharge (2.01\u20135.00 ac)", "description": "5.00-acre lot falls within the 2.01\u20135.00 ac complexity tier. Larger lot requires additional field time, traverse, and CAD drafting effort.", "amount": 550.0}], "pricing_reasoning": "The negotiated base rate of $450.00 applies per management agreement. The lot is 5.00 acres, which falls at the ceiling of the 2.01\u20135.00 ac complexity tier, warranting the full $550.00 acreage upcharge. No EC is requested (FEMA Zone X, no flood zone concern), no topo was ordered, the legal description is a platted lot (no metes-and-bounds upcharge), and no other complexity factors (pool, waterfront, Monroe County, heavy vegetation) are indicated by the available data.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000272987 \u2014 same address (35135 PINEGATE TRAIL, Lake County), same Folio/MLS (01-19-27-1200-000-12700), service: Land Survey Only \u2014 likely the same property. Human review recommended before scheduling fieldwork to avoid duplicate field visits.", "DUPLICATE_WARNING: Order 1000167993 \u2014 same location (35135 PINEGATE TRL, Lake County), service: Land Survey Only \u2014 possible earlier order for same property.", "DUPLICATE_WARNING: Order 1000186424 \u2014 same location (35135 PINEGATE TRL, Lake County), service: Quote \u2014 possible earlier quote for same property.", "HOLD_NOTE: Order is currently on hold per notes; no fieldwork or delivery scheduled. Pricing is advisory until hold is released.", "CLIENT_NOTE: Taylor McCook flagged as possible business client via fivediamondfl.com despite INDIVIDUAL tier classification. Account tier may warrant review if additional orders follow.", "ACREAGE_BOUNDARY: Lot size is exactly 5.00 acres, which is the upper limit of the 2.01\u20135.00 ac tier. Any field verification showing lot exceeds 5.00 acres would require escalation per pricing guidelines."]}</t>
+        </is>
+      </c>
       <c r="H172" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510271424299774, "created_at": "2025-10-27T10:26:04", "customer_email": "Taylor@fivediamondfl.com", "customer_id": 202510271424301128, "customer_name": "Taylor McCook", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12069C0385E\nZONE: X\nEFF: 12/18/2012", "invoiced": false, "order_id": 1000273608, "paid": true, "property_address": "35135 PINEGATE TRAIL", "property_city": "EUSTIS", "property_county": "Lake County", "property_lat": "28.853566", "property_lng": "-81.560335", "property_state": "FL", "property_zip": "32736", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273608", "customer_email": "Taylor@fivediamondfl.com", "service_type": "CAD file", "county": "", "property_address": "35135 PINEGATE TRAIL", "customer_name": "Taylor McCook"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Taylor McCook", "confidence": "HIGH"}, "client_email": {"value": "Taylor@fivediamondfl.com", "confidence": "HIGH"}, "property_address": {"value": "35135 Pinegate Trail, Eustis, FL 32736", "confidence": "HIGH"}, "property_county": {"value": "Lake County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file' in order data. No additional services indicated."}, "special_requirements": {"value": "Special pricing applied; order currently on hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference."}, "client_tier": {"value": "b2b", "confidence": "MEDIUM", "notes": "Customer type is listed as 'individual' but email domain 'fivediamondfl.com' suggests a business entity (Five Diamond FL). Likely a business client using a business email."}, "urgency": {"value": "normal", "confidence": "MEDIUM", "notes": "No rush indicators present; order is on hold which suggests no urgency at this time."}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, etc.)", "Reason for 'On Hold' status not specified", "County appraiser data unavailable", "No matching emails found to supplement order details", "Client tier ambiguous \u2014 individual vs. business needs clarification", "Scope of CAD file request not detailed (boundary, topo, as-built, etc.)", "Fieldwork date not scheduled"], "summary": "Taylor McCook (possible business client via fivediamondfl.com) has a CAD file order for 35135 Pinegate Trail, Eustis, FL (Lake County) that is currently on hold with special pricing applied and no fieldwork or delivery scheduled."}}</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>1780427991279</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>2026-06-02T18:00:43.647424+00:00</t>
         </is>
       </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:19:53.936288+00:00</t>
+        </is>
+      </c>
+      <c r="R172" t="n">
+        <v>1000</v>
+      </c>
       <c r="T172" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:18.638183+00:00</t>
@@ -11413,7 +11434,7 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>2026-06-02T18:00:43.702070+00:00</t>
+          <t>2026-06-02T19:19:54.001808+00:00</t>
         </is>
       </c>
     </row>
@@ -11477,7 +11498,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11500,16 +11521,37 @@
           <t>152 Woodbridge Cir, Daytona Beach, FL 32119</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>{"total_amount": 475.0, "services": [{"name": "Land Survey Only", "description": "Residential boundary survey for Lot 8, Georgetowne Duplexes - Unit One, Volusia County. Platted lot of 0.12 acres with a straightforward legal description referencing a recorded plat (Map Book 37, Page 172). No complexity upcharges apply: lot is under 0.31 acres, legal description is plat-based (not metes and bounds), FEMA zone is X (no flood zone complexity), property is not in Monroe County, and no pool, waterfront, canal, or heavy vegetation factors are indicated.", "amount": 475.0}], "pricing_reasoning": "This is a standard residential land survey for an individual homeowner (Johanne Beaumont) with no prior order history, so the default individual base rate of $475.00 applies. The lot is 0.12 acres with a clean plat-based legal description, located in FEMA Zone X (minimal flood risk, no EC required), in Volusia County \u2014 no Monroe County surcharge, no metes-and-bounds upcharge, and no other complexity factors are supported by the available data. Final price equals the base rate with no additions.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["Order is currently on hold with a $475.00 balance due per order notes \u2014 confirm payment or hold status before scheduling fieldwork or delivery."]}</t>
+        </is>
+      </c>
       <c r="H174" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510211448162837, "created_at": "2025-10-21T11:11:01", "customer_email": "bacall40@hotmail.com", "customer_id": 202510211448162936, "customer_name": "Johanne Beaumont", "customer_type": "individual", "delivered_at": null, "due_amount": 475.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12127C0366H\nZONE: X\nEFF: 02/19/2014", "invoiced": false, "order_id": 1000273343, "paid": false, "property_address": "152 WOODBRIDGE CIR", "property_city": "DAYTONA BEACH", "property_county": "Volusia County", "property_lat": "29.1619689", "property_lng": "-81.0390599", "property_state": "FLORIDA", "property_zip": "32119", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273343", "customer_email": "bacall40@hotmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "152 WOODBRIDGE CIR", "customer_name": "Johanne Beaumont "}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Johanne Beaumont", "confidence": "HIGH"}, "client_email": {"value": "bacall40@hotmail.com", "confidence": "HIGH"}, "property_address": {"value": "152 Woodbridge Cir, Daytona Beach, FL 32119", "confidence": "HIGH"}, "property_county": {"value": "Volusia County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in FTF order data; no elevation certificate required per elevation_cert flag."}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no emails or attachments to reference."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser unavailable", "Legal description missing \u2014 no appraiser data or supporting documents", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) unknown", "Special requirements or access instructions not provided", "Order is currently On Hold \u2014 reason for hold not stated", "No customer profile data returned from FTF customer lookup", "No matching emails found to supplement order details"], "summary": "Residential land survey only order for Johanne Beaumont at 152 Woodbridge Cir, Daytona Beach, FL (Volusia County), currently on hold with a $475 balance due and no delivery or fieldwork dates scheduled."}}</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>1780428017959</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>2026-06-02T18:01:01.624011+00:00</t>
         </is>
       </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:20:20.753326+00:00</t>
+        </is>
+      </c>
+      <c r="R174" t="n">
+        <v>475</v>
+      </c>
       <c r="T174" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:18.772653+00:00</t>
@@ -11517,7 +11559,7 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>2026-06-02T18:01:01.678699+00:00</t>
+          <t>2026-06-02T19:20:20.810846+00:00</t>
         </is>
       </c>
     </row>
@@ -14649,7 +14691,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14669,7 +14711,17 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>757 LIGHTHOUSE DR</t>
+          <t>757 Lighthouse Dr, North Palm Beach, FL 33408</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202506231528059483, "created_at": "2025-06-23T11:35:05", "customer_email": "aknecht@gofamilychurch.org", "customer_id": 202506231529022740, "customer_name": "Alex Knecht", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0379G\nZONE: X\nZONE: X500\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000266764, "paid": true, "property_address": "757 LIGHTHOUSE DR", "property_city": "NORTH PALM BEACH", "property_county": "Palm Beach County", "property_lat": "26.8181071", "property_lng": "-80.0729253", "property_state": "FL", "property_zip": "33408", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000266764", "customer_email": "aknecht@gofamilychurch.org", "service_type": "CAD file", "county": "", "property_address": "757 LIGHTHOUSE DR", "customer_name": "Lighthouse Baptist Church"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Lighthouse Baptist Church", "confidence": "MEDIUM"}, "client_email": {"value": "aknecht@gofamilychurch.org", "confidence": "HIGH"}, "property_address": {"value": "757 Lighthouse Dr, North Palm Beach, FL 33408", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD file; no additional services indicated"}, "special_requirements": {"value": "Special pricing applies; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property feature data available; county appraiser lookup unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: FTF order data lists 'Alex Knecht' as customer_name but outer payload says 'Lighthouse Baptist Church' \u2014 confirm correct entity name for invoice", "No lot size available", "No legal description available", "No structure square footage available", "No property features data (pool, shed, driveways, etc.)", "County appraiser lookup unavailable \u2014 no parcel data retrieved", "Order is On Hold \u2014 reason for hold not specified, may need resolution before invoicing", "Invoice has not been sent and due amount is $0 despite paid=true \u2014 pricing details unclear given special_pricing flag", "Relationship between Alex Knecht and Lighthouse Baptist Church is unclear (employee, pastor, agent?)"], "summary": "B2B CAD file order for a property at 757 Lighthouse Dr, North Palm Beach FL associated with Lighthouse Baptist Church, currently On Hold with special pricing applied and no invoice yet issued."}}</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:18:42.746791+00:00</t>
         </is>
       </c>
       <c r="T235" t="inlineStr">
@@ -14679,7 +14731,7 @@
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:17.766658+00:00</t>
+          <t>2026-06-02T19:18:42.803192+00:00</t>
         </is>
       </c>
     </row>
@@ -14691,7 +14743,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14706,12 +14758,22 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Kek Rodriguez</t>
+          <t>Anabel Santana</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>8608 N 13TH ST</t>
+          <t>8608 N 13TH ST, TAMPA, FL 33604</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202505282053065134, "created_at": "2025-06-20T15:39:04", "customer_email": "tc@realtyblu.com", "customer_id": 202505282053065252, "customer_name": "Anabel Santana", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12057C0214J\nZONE: X\nEFF: 10/07/2021", "invoiced": false, "order_id": 1000266719, "paid": true, "property_address": "8608 N 13TH ST", "property_city": "TAMPA", "property_county": "Hillsborough County", "property_lat": "28.0285022", "property_lng": "-82.4465867", "property_state": "FL", "property_zip": "33604", "service_type": "Quote", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000266719", "customer_email": "tc@realtyblu.com", "service_type": "Quote", "county": "", "property_address": "8608 N 13TH ST", "customer_name": " Kek Rodriguez"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Anabel Santana", "confidence": "MEDIUM"}, "client_email": {"value": "tc@realtyblu.com", "confidence": "HIGH"}, "property_address": {"value": "8608 N 13TH ST, TAMPA, FL 33604", "confidence": "HIGH"}, "property_county": {"value": "Hillsborough County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey type (e.g., boundary, ALTA, elevation) has been identified. Human input needed to determine actual service requested."}, "special_requirements": {"value": "Special pricing applied; order is On Hold", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available and no emails or attachments to reference. Pool, shed, driveways, and other features unknown."}, "client_tier": {"value": "b2b", "confidence": "MEDIUM"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name is inconsistent \u2014 FTF order data shows 'Anabel Santana' but root-level customer_name shows 'Kek Rodriguez'; human confirmation needed", "Specific survey service type not defined \u2014 only listed as 'Quote'", "No lot size or legal description available", "No property appraiser data to verify ownership, lot dimensions, or legal description", "No property features data (pool, shed, fences, etc.)", "Structure square footage unknown", "Urgency/turnaround requirement not specified", "Order is On Hold \u2014 reason for hold not documented", "No matching emails found to provide additional context or scope details", "Relationship between email domain (realtyblu.com) and client name needs clarification for proper tier assignment"], "summary": "A quote-only order placed for a Tampa, FL residential property at 8608 N 13TH ST with conflicting client name data, no defined survey scope, and the order currently on hold with special pricing applied."}}</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:18:54.699433+00:00</t>
         </is>
       </c>
       <c r="T236" t="inlineStr">
@@ -14721,7 +14783,7 @@
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:17.854178+00:00</t>
+          <t>2026-06-02T19:18:54.756710+00:00</t>
         </is>
       </c>
     </row>
@@ -14733,7 +14795,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14748,12 +14810,22 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samantha Sinclair </t>
+          <t>Samantha Sinclair</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>3845 BLANDING BLVD</t>
+          <t>3845 Blanding Blvd, Jacksonville, FL 32210</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202504291905190630, "created_at": "2025-06-19T09:21:00", "customer_email": "realestate@giantoil.com", "customer_id": 202504291905190719, "customer_name": "Luisa Goethe ext 136", "customer_type": "individual", "delivered_at": "2025-07-10T14:20:28", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12031C0363J\nZONE: X\nEFF: 11/02/2018", "invoiced": false, "order_id": 1000266615, "paid": false, "property_address": "3845 BLANDING BLVD", "property_city": "JACKSONVILLE", "property_county": "DUVAL COUNTY", "property_lat": "30.2671531", "property_lng": "-81.7372611", "property_state": "FL", "property_zip": "32210", "service_type": "CAD File", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000266615", "customer_email": "S.Sinclair@giantoil.com", "service_type": "CAD File", "county": "", "property_address": "3845 BLANDING BLVD", "customer_name": "Samantha Sinclair "}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Samantha Sinclair", "confidence": "MEDIUM"}, "client_email": {"value": "S.Sinclair@giantoil.com", "confidence": "MEDIUM"}, "property_address": {"value": "3845 Blanding Blvd, Jacksonville, FL 32210", "confidence": "HIGH"}, "property_county": {"value": "Duval County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD File; no additional services indicated."}, "special_requirements": {"value": "Special pricing applies; order is currently On Hold.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no aerial or email data provided."}, "client_tier": {"value": "b2b", "confidence": "MEDIUM"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: FTF order data lists 'Luisa Goethe ext 136' while outer envelope lists 'Samantha Sinclair' \u2014 needs human clarification on correct contact", "Client email conflict: FTF order data lists 'realestate@giantoil.com' while outer envelope lists 'S.Sinclair@giantoil.com' \u2014 needs human clarification", "Lot size unknown \u2014 county appraiser unavailable", "Legal description unknown \u2014 county appraiser unavailable", "Structure square footage unknown", "Property features unknown (pool, sheds, driveways, etc.)", "Order is On Hold \u2014 reason for hold not provided", "Urgency/deadline not specified", "Fieldwork date not scheduled (fieldwork_at is null)", "Invoice not yet generated and due amount is $0 \u2014 pricing details needed", "Special pricing flag is true but no pricing details are provided"], "summary": "A CAD File order for a commercial property at 3845 Blanding Blvd, Jacksonville, FL (Duval County) placed by a Giant Oil company contact, currently On Hold with special pricing applied and key property and client details still unresolved."}}</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:19:06.989571+00:00</t>
         </is>
       </c>
       <c r="T237" t="inlineStr">
@@ -14763,7 +14835,7 @@
       </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:17.940129+00:00</t>
+          <t>2026-06-02T19:19:07.047636+00:00</t>
         </is>
       </c>
     </row>
@@ -14775,7 +14847,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14790,12 +14862,22 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Island Way Pools</t>
+          <t>Amber Towe</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2316 KENT PL</t>
+          <t>2316 Kent Pl, Clearwater, FL 33764</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202410241430054096, "created_at": "2025-06-17T11:52:00", "customer_email": "islandwayamber@gmail.com", "customer_id": 202410241430360575, "customer_name": "Amber Towe", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12103C0136H\nZONE: AE\nELEV: 10 FT\nEFF: 08/24/2021", "invoiced": false, "order_id": 1000266475, "paid": true, "property_address": "2316 KENT PL", "property_city": "CLEARWATER", "property_county": "PINELLAS COUNTY", "property_lat": "27.927812", "property_lng": "-82.741598", "property_state": "FL", "property_zip": "33764", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000266475", "customer_email": "islandwayamber@gmail.com", "service_type": "CAD file", "county": "", "property_address": "2316 KENT PL", "customer_name": "Island Way Pools"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Amber Towe", "confidence": "MEDIUM"}, "client_email": {"value": "islandwayamber@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "2316 Kent Pl, Clearwater, FL 33764", "confidence": "HIGH"}, "property_county": {"value": "Pinellas County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services specified."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11); flood zone AE with base flood elevation 10 ft per FIRM panel 12103C0136H effective 08/24/2021.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided. Pool possible given customer name reference to 'Island Way Pools' \u2014 may be a pool contractor order."}, "client_tier": {"value": "b2b", "confidence": "MEDIUM"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: FTF order lists 'Amber Towe' as customer but outer payload lists 'Island Way Pools' \u2014 clarify whether client is an individual or a pool company", "No lot size available", "No legal description available", "No structure square footage available", "No property features data (pool, shed, fencing, etc.)", "Order is On Hold \u2014 reason for hold not specified, needs human review", "Purpose of CAD file not specified (e.g., pool permit, addition, boundary)", "No urgency or deadline information provided", "County appraiser data unavailable \u2014 unable to verify ownership, legal description, or lot dimensions", "No matching emails found \u2014 no additional context from correspondence"], "summary": "CAD file order for a flood zone AE property at 2316 Kent Pl, Clearwater FL, placed by or on behalf of Amber Towe / Island Way Pools, currently On Hold with special pricing applied and missing key property details."}}</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:19:19.003604+00:00</t>
         </is>
       </c>
       <c r="T238" t="inlineStr">
@@ -14805,7 +14887,7 @@
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:18.026993+00:00</t>
+          <t>2026-06-02T19:19:19.058395+00:00</t>
         </is>
       </c>
     </row>
@@ -14817,7 +14899,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -14837,7 +14919,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>1956 NW 183RD ST</t>
+          <t>1956 NW 183RD ST, MIAMI GARDENS, FL 33056</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202506111408096074, "created_at": "2025-06-17T10:32:00", "customer_email": "tere@palmvista.org", "customer_id": 202506111409094750, "customer_name": "Tere Gavil\u00e1n", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0128L\nZONE: X500\nZONE: X\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000266457, "paid": true, "property_address": "1956 NW 183RD ST", "property_city": "MIAMI GARDENS", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.9408401", "property_lng": "-80.2343533", "property_state": "FL", "property_zip": "33056", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000266457", "customer_email": "tere@palmvista.org", "service_type": "CAD file", "county": "", "property_address": "1956 NW 183RD ST", "customer_name": "Palm Vista Community Church, Inc."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Palm Vista Community Church, Inc.", "confidence": "MEDIUM"}, "client_email": {"value": "tere@palmvista.org", "confidence": "HIGH"}, "property_address": {"value": "1956 NW 183RD ST, MIAMI GARDENS, FL 33056", "confidence": "HIGH"}, "property_county": {"value": "MIAMI-DADE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Order is On Hold \u2014 reason for hold not specified; human review required", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, driveways, structures) unknown \u2014 no appraiser or aerial data available", "County appraiser lookup unavailable (county field was blank in outer payload despite being present in order data)", "Client name discrepancy: order data shows 'Tere Gavil\u00e1n' as customer_name but outer payload shows 'Palm Vista Community Church, Inc.' \u2014 confirm correct billing entity", "No matching emails found \u2014 no additional context from prior correspondence", "Urgency/deadline not specified", "Scope of CAD file request not defined (e.g., boundary, topographic, as-built)"], "summary": "B2B CAD file order for Palm Vista Community Church, Inc. at 1956 NW 183rd St, Miami Gardens, FL (Miami-Dade County), currently On Hold with special pricing applied and no fieldwork or delivery dates scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:19:30.072968+00:00</t>
         </is>
       </c>
       <c r="T239" t="inlineStr">
@@ -14847,7 +14939,7 @@
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:18.112411+00:00</t>
+          <t>2026-06-02T19:19:30.129653+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -11571,7 +11571,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11594,16 +11594,37 @@
           <t>624 Selkirk St, West Palm Beach, FL 33405</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>{"total_amount": 475.0, "services": [{"name": "Land Survey Only", "description": "Residential boundary survey for 624 Selkirk St, West Palm Beach, FL 33405. Four-lot assemblage (Lots 169-172, Southboro Park, Plat Book 9/Page 57). Individual client base rate applied.", "amount": 475.0}], "pricing_reasoning": "This is a residential land survey for an individual homeowner (first-time client, no negotiated rate), so the $475.00 individual default base rate applies. The lot is 0.21 acres \u2014 well within the standard 0.00\u20130.30 ac tier, so no lot-size upcharge is warranted. The legal description references a platted subdivision (Southboro Park) with four contiguous lots, which is straightforward title work with no metes-and-bounds complexity upcharge. FEMA Zone X (minimal flood hazard, effective 12/20/2024) means no Elevation Certificate is required or requested. No pool, waterfront, heavy vegetation, or Monroe County factors are indicated by the available data.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE DUPLICATE: Order 1000269369 covers the same property (624 Selkirk St, Palm Beach County), same service (Land Survey Only), same folio (74434404130001690), and same coordinates (26.6671637, -80.0593823). Human review required to determine whether this order should be merged, cancelled, or processed independently.", "ORDER ON HOLD: Per order notes, no fieldwork is currently scheduled and no prior pricing exists for this order. Pricing is now proposed; order should be activated and duplicate status resolved before dispatching field crew."]}</t>
+        </is>
+      </c>
       <c r="H175" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510161721226230, "created_at": "2025-10-16T18:29:01", "customer_email": "chefmbyrne@gmail.com", "customer_id": 202510161721226321, "customer_name": "Matthew Byrne", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0591G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000273161, "paid": false, "property_address": "624 SELKIRK ST", "property_city": "WEST PALM BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.6671637", "property_lng": "-80.0593823", "property_state": "FLORIDA", "property_zip": "33405", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273161", "customer_email": "chefmbyrne@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "624 SELKIRK ST", "customer_name": "Matthew Byrne"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Matthew Byrne", "confidence": "HIGH"}, "client_email": {"value": "chefmbyrne@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "624 Selkirk St, West Palm Beach, FL 33405", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only' in order data; no additional services indicated"}, "special_requirements": {"value": null, "confidence": "LOW"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial imagery, or email attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, outbuildings)", "Special requirements or client notes not provided", "Order is currently 'On Hold' \u2014 reason for hold not documented", "Invoice amount is $0.00 and order has not been invoiced \u2014 pricing needs to be set", "Fieldwork date not yet scheduled", "No matching emails found \u2014 no additional client communication on record", "County field blank in outer order object (inconsistent with property_county in data object \u2014 should be reconciled)"], "summary": "Residential land survey order for Matthew Byrne at 624 Selkirk St, West Palm Beach (Palm Beach County, FL 33405), currently on hold with no pricing, scheduled fieldwork, or property detail data available."}}</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>1780428340479</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>2026-06-02T18:06:18.241357+00:00</t>
         </is>
       </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:25:43.320791+00:00</t>
+        </is>
+      </c>
+      <c r="R175" t="n">
+        <v>475</v>
+      </c>
       <c r="T175" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:18.840215+00:00</t>
@@ -11611,7 +11632,7 @@
       </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t>2026-06-02T18:06:18.294781+00:00</t>
+          <t>2026-06-02T19:25:43.425618+00:00</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11644,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11646,16 +11667,37 @@
           <t>753 NE 79TH ST, MIAMI, FL 33138</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>{"total_amount": 475.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for 753 NE 79th St, Miami-Dade County. Five contiguous lots (50\u201354) less south 10 ft, Block A, Commercial Shore Crest, PB 17/16. Lot size 0.30 ac falls within the base tier (\u22640.30 ac), no size upcharge triggered. No EC requested. No pool, waterfront canal, metes-and-bounds, heavy vegetation, or Monroe County factors identified from available data. Commercial flag is set but client is confirmed individual homeowner (Juan Ramos, 0 prior orders) \u2014 default individual base rate applies.", "amount": 475.0}], "pricing_reasoning": "Service is Land Survey Only for an individual homeowner with no negotiated rate, so the $475.00 individual base rate applies. The lot is exactly 0.30 ac, which sits at the upper boundary of the base tier (\u22640.30 ac) and does not trigger the 0.31\u20130.50 ac upcharge of $62.00. The legal description is a platted subdivision lot (not metes-and-bounds), Miami-Dade County carries no remote mobilization premium, the FEMA zone is AE (not VE), and no EC was ordered \u2014 leaving no applicable complexity upcharges. The commercial flag appears to be a system artifact contradicted by the order notes confirming an individual residential client, so it is noted but not priced.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["COMMERCIAL_FLAG_MISMATCH: Order is flagged commercial in the database but order notes and client tier confirm individual residential homeowner Juan Ramos. No commercial rate applied; verify flag with client or project manager before invoicing.", "ORDER_ON_HOLD: No fieldwork scheduled at time of pricing. Order notes indicate key site features are incomplete \u2014 confirm site details (pool, waterfront, vegetation) before releasing to field to ensure no unpriced complexity upcharges are warranted.", "LOT_SIZE_BOUNDARY: Lot size recorded as exactly 0.30 ac (base tier ceiling). If field or county records confirm lot is \u22650.31 ac, a $62.00 size upcharge should be added."]}</t>
+        </is>
+      </c>
       <c r="H176" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510151749087347, "created_at": "2025-10-16T18:23:03", "customer_email": "juanramos155@hotmail.com", "customer_id": 202510151749087705, "customer_name": "Juan Ramos", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0306L\nZONE: AE\nELEV: 08 FT\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000273091, "paid": false, "property_address": "753 NE 79TH ST", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.8480525", "property_lng": "-80.180931", "property_state": "FLORIDA", "property_zip": "33138", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000273091", "customer_email": "juanramos155@hotmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "753 NE 79TH ST", "customer_name": "Juan Ramos"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Juan Ramos", "confidence": "HIGH"}, "client_email": {"value": "juanramos155@hotmail.com", "confidence": "HIGH"}, "property_address": {"value": "753 NE 79TH ST, MIAMI, FL 33138", "confidence": "HIGH"}, "property_county": {"value": "MIAMI-DADE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Property is in FEMA Flood Zone AE (Panel 12086C0306L, effective 09/11/2009, base flood elevation 8 ft). Order is currently On Hold.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available and no emails or attachments to reference; pool, shed, driveways, and other features unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided \u2014 needs property appraiser lookup or manual research", "Legal description not provided \u2014 needs property appraiser lookup or manual research", "Structure square footage unknown \u2014 no appraiser data available", "Property features (pool, shed, fences, driveways, etc.) unknown \u2014 no aerial or appraiser data", "Order is On Hold \u2014 reason for hold not documented; needs human review", "No matching emails found \u2014 no additional client communication to reference", "Special pricing flag is false but no pricing or quote details are present", "Fieldwork and delivery dates not yet scheduled"], "summary": "Individual residential client Juan Ramos has ordered a Land Survey Only for 753 NE 79TH ST, Miami, FL 33138 (Miami-Dade County), located in FEMA Flood Zone AE; the order is currently On Hold with no fieldwork scheduled and key property details such as lot size, legal description, and site features are missing."}}</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>1780428363460</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>2026-06-02T18:06:29.790354+00:00</t>
         </is>
       </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:26:05.374884+00:00</t>
+        </is>
+      </c>
+      <c r="R176" t="n">
+        <v>475</v>
+      </c>
       <c r="T176" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:18.907400+00:00</t>
@@ -11663,7 +11705,7 @@
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>2026-06-02T18:06:29.841727+00:00</t>
+          <t>2026-06-02T19:26:05.430963+00:00</t>
         </is>
       </c>
     </row>
@@ -11675,7 +11717,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11698,16 +11740,37 @@
           <t>12081 Dubarry Ave, Port Charlotte, FL 33981</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for 12081 Dubarry Ave, Port Charlotte, FL (Charlotte County). Lots 18, 4, and undivided 1/2 interest in Lot 20, Block 1835, Port Charlotte Sub Section 56 \u2014 platted subdivision lots totaling ~0.23 acres. Certification to KIM PRICE. Client negotiated rate applied.", "amount": 450.0}], "pricing_reasoning": "MSC Title, Inc. of Englewood is an established OLD_TITLE client with a management-agreed negotiated survey rate of $450.00, which is used as the base and final price. The property is a platted subdivision lot in Port Charlotte (Charlotte County) at 0.23 acres, which falls within the standard 0.00\u20130.30 ac tier requiring no lot-size upcharge. FEMA Zone X confirms no flood zone complexity, no EC is ordered, the county is not Monroe, and the legal description \u2014 while slightly nuanced with an undivided 1/2 interest in Lot 20 \u2014 still references a recorded plat (Plat Book 5) rather than metes-and-bounds, so no metes-and-bounds upcharge is warranted. No pool, waterfront, or heavy vegetation complexity flags are indicated by the data, so no additional upcharges apply.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["Legal description includes an undivided 1/2 interest in Lot 20 alongside whole Lots 18 and 4 \u2014 field crew should confirm all three lot parcels are consistently monumented and that the shared-interest boundary is clearly delineated on the plat before closing fieldwork.", "Order noted as currently ON HOLD with no fieldwork or invoice date set \u2014 do not dispatch or invoice until hold is released by MSC Title, Inc. of Englewood or internal management."]}</t>
+        </is>
+      </c>
       <c r="H177" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 201801311053311966, "created_at": "2025-10-10T15:26:02", "customer_email": "kimprice@msctitle.com", "customer_id": 202308041923161327, "customer_name": "Kim Price", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12015C0184G\nZONE: X\nEFF: 12/15/2022", "invoiced": false, "order_id": 1000272874, "paid": false, "property_address": "12081 DUBARRY AVE", "property_city": "PORT CHARLOTTE", "property_county": "CHARLOTTE COUNTY", "property_lat": "26.9458466", "property_lng": "-82.2530594", "property_state": "FLORIDA", "property_zip": "33981", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272874", "customer_email": "kimprice@msctitle.com", "service_type": "Land Survey Only", "county": "", "property_address": "12081 DUBARRY AVE", "customer_name": "MSC Title, Inc. of Englewood"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "MSC Title, Inc. of Englewood", "confidence": "HIGH"}, "client_email": {"value": "kimprice@msctitle.com", "confidence": "HIGH"}, "property_address": {"value": "12081 Dubarry Ave, Port Charlotte, FL 33981", "confidence": "HIGH"}, "property_county": {"value": "Charlotte County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applies; order currently on hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or aerial data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Order is on hold \u2014 reason for hold not specified; human review needed", "Lot size unknown \u2014 no appraiser or parcel data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, structures) unknown \u2014 no aerial or appraiser data", "No fieldwork date scheduled", "Invoice not yet generated; pricing not confirmed despite special_pricing flag", "Contact person vs. company name discrepancy (Kim Price vs. MSC Title, Inc. of Englewood) \u2014 confirm billing name"], "summary": "B2B land survey order for MSC Title, Inc. of Englewood at 12081 Dubarry Ave, Port Charlotte, FL (Charlotte County) currently on hold with special pricing applied and no fieldwork or invoice date set."}}</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>1780428382995</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>2026-06-02T18:06:39.445100+00:00</t>
         </is>
       </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:26:25.376533+00:00</t>
+        </is>
+      </c>
+      <c r="R177" t="n">
+        <v>450</v>
+      </c>
       <c r="T177" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:18.975500+00:00</t>
@@ -11715,7 +11778,7 @@
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t>2026-06-02T18:06:39.497662+00:00</t>
+          <t>2026-06-02T19:26:25.482262+00:00</t>
         </is>
       </c>
     </row>
@@ -14951,7 +15014,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -14971,7 +15034,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2650 SHELTINGHAM DR</t>
+          <t>2650 Sheltingham Dr, Wellington, FL 33414</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202506161500110275, "created_at": "2025-06-16T11:02:03", "customer_email": "emily@wlpiper.com", "customer_id": 202506161500537831, "customer_name": "Emily Davis", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0563F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000266383, "paid": true, "property_address": "2650 SHELTINGHAM DR", "property_city": "WELLINGTON", "property_county": "Palm Beach County", "property_lat": "26.6416367", "property_lng": "-80.2319241", "property_state": "FL", "property_zip": "33414", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000266383", "customer_email": "emily@wlpiper.com", "service_type": "CAD file", "county": "", "property_address": "2650 SHELTINGHAM DR", "customer_name": "Piper Properties"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Piper Properties", "confidence": "MEDIUM"}, "client_email": {"value": "emily@wlpiper.com", "confidence": "HIGH"}, "property_address": {"value": "2650 Sheltingham Dr, Wellington, FL 33414", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Only service type listed is CAD file; no additional services specified"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order contact is Emily Davis but outer record lists Piper Properties \u2014 confirm correct billing entity", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, driveways, etc.)", "Reason for On Hold status not specified", "Urgency or deadline not indicated", "Scope of CAD file service not clarified (boundary, topo, as-built, etc.)", "No fieldwork date scheduled"], "summary": "B2B CAD file order for Piper Properties (contact: Emily Davis) at 2650 Sheltingham Dr, Wellington, FL 33414 (Palm Beach County) is currently On Hold with special pricing applied and requires clarification on client entity, property details, and CAD scope."}}</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:24:30.080096+00:00</t>
         </is>
       </c>
       <c r="T240" t="inlineStr">
@@ -14981,7 +15054,7 @@
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:18.255046+00:00</t>
+          <t>2026-06-02T19:24:30.135963+00:00</t>
         </is>
       </c>
     </row>
@@ -14993,7 +15066,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15008,12 +15081,22 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tiffany Grafton</t>
+          <t>Stefanie Brown</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>750 PENFIELD ST</t>
+          <t>750 Penfield St, Longboat Key, FL 34228</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202411141637401215, "created_at": "2025-06-16T16:08:04", "customer_email": "stefaniebrown@firstam.com", "customer_id": 202503061550487269, "customer_name": "Stefanie Brown", "customer_type": "b2b", "delivered_at": "2025-07-18T15:20:07", "due_amount": 0.0, "elevation_cert": true, "estimate_sent": false, "fieldwork_at": "2025-06-23T00:00:00", "flood_zone": "12081C0291F\nZONE: AE\nELEV: 08 FT\nEFF: 08/10/2021", "invoiced": false, "order_id": 1000266363, "paid": false, "property_address": "750 PENFIELD ST", "property_city": "LONGBOAT KEY", "property_county": "MANATEE COUNTY", "property_lat": "27.429655", "property_lng": "-82.66985749999999", "property_state": "FL", "property_zip": "34228", "service_type": "Land Survey and Elevation", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000266363", "customer_email": "stefaniebrown@firstam.com", "service_type": "Land Survey and Elevation", "county": "", "property_address": "750 PENFIELD ST", "customer_name": " Tiffany Grafton"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Stefanie Brown", "confidence": "MEDIUM"}, "client_email": {"value": "stefaniebrown@firstam.com", "confidence": "HIGH"}, "property_address": {"value": "750 Penfield St, Longboat Key, FL 34228", "confidence": "HIGH"}, "property_county": {"value": "Manatee County", "confidence": "HIGH"}, "services_requested": {"value": ["Boundary Survey", "Elevation Certificate"], "confidence": "HIGH", "notes": "Service type is 'Land Survey and Elevation'; elevation_cert flag is true. Likely an ALTA or boundary survey paired with an EC for flood zone AE property."}, "special_requirements": {"value": "Special pricing applied; flood zone AE (panel 12081C0291F, effective 08/10/2021, base flood elevation 8 ft)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available; no aerial or email attachments provided. Pool, structures, and other features unknown."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: FTF order data shows 'Stefanie Brown' as customer_name but 'Tiffany Grafton' appears in the outer customer_name field \u2014 confirm correct contact name", "Legal description not provided", "Lot size not provided", "Structure square footage not provided", "Property features unknown (pool, outbuildings, driveway, etc.) \u2014 no appraiser data or aerial available", "No matching emails found to corroborate order details", "Invoice has not been sent and payment is outstanding \u2014 pricing needs to be confirmed given special_pricing flag", "County field is blank in outer FTF payload despite Manatee County in property data \u2014 verify county for appraiser lookup"], "summary": "B2B order from First American (Stefanie Brown) for a boundary survey and elevation certificate at 750 Penfield St, Longboat Key, FL 34228 in flood zone AE \u2014 delivered but not yet invoiced, with special pricing applied."}}</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:24:42.202261+00:00</t>
         </is>
       </c>
       <c r="T241" t="inlineStr">
@@ -15023,7 +15106,7 @@
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:18.342685+00:00</t>
+          <t>2026-06-02T19:24:42.258529+00:00</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15118,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15055,7 +15138,17 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>12500 5TH ST E</t>
+          <t>12500 5TH ST E, TREASURE ISLAND, FL 33706</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202506101820569692, "created_at": "2025-06-10T14:22:05", "customer_email": "hzuluaga1@verizon.net", "customer_id": 202506101820570902, "customer_name": "Herman Zuluaga", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12103C0192H\nZONE: AE\nELEV: 11 FT\nEFF: 08/24/2021", "invoiced": false, "order_id": 1000266082, "paid": true, "property_address": "12500 5TH ST E", "property_city": "TREASURE ISLAND", "property_county": "PINELLAS COUNTY", "property_lat": "27.7840296", "property_lng": "-82.77199360000002", "property_state": "FL", "property_zip": "33706", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000266082", "customer_email": "hzuluaga1@verizon.net", "service_type": "CAD file", "county": "", "property_address": "12500 5TH ST E", "customer_name": "Herman Zuluaga"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Herman Zuluaga", "confidence": "HIGH"}, "client_email": {"value": "hzuluaga1@verizon.net", "confidence": "HIGH"}, "property_address": {"value": "12500 5TH ST E, TREASURE ISLAND, FL 33706", "confidence": "HIGH"}, "property_county": {"value": "PINELLAS COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated. Unclear if this is a CAD conversion of an existing survey or requires new fieldwork."}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status code 11). Flood zone data present: 12103C0192H, Zone AE, Elev 11 FT, Eff 08/24/2021.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Reason order is On Hold \u2014 needs human review", "Clarification on CAD file scope \u2014 new fieldwork required or conversion of existing survey?", "Lot size unknown \u2014 no appraiser data available", "Legal description missing", "Structure square footage unknown", "Property features unknown (pool, structures, etc.)", "No customer data returned from FTF customer lookup", "No matching emails found \u2014 no correspondence history available", "Special pricing details not specified \u2014 amount or discount unknown", "Urgency/deadline not indicated", "Fieldwork date not scheduled (fieldwork_at is null)", "Invoice not yet created (invoiced: false) despite paid: true \u2014 reconciliation may be needed"], "summary": "Individual residential client Herman Zuluaga has a paid but on-hold CAD file order for a flood zone AE property at 12500 5TH ST E, Treasure Island, FL with special pricing applied and no fieldwork or invoicing completed yet."}}</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:24:54.753959+00:00</t>
         </is>
       </c>
       <c r="T242" t="inlineStr">
@@ -15065,7 +15158,7 @@
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:18.429367+00:00</t>
+          <t>2026-06-02T19:24:54.810395+00:00</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15170,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15092,12 +15185,22 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Sean  Sukal</t>
+          <t>Sean Sukal</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>2801 NW 27TH AVE</t>
+          <t>2801 NW 27TH AVE, BOCA RATON, FL 33434</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202506051922266654, "created_at": "2025-06-05T15:24:05", "customer_email": "sasukal@hotmail.com", "customer_id": 202506051922267587, "customer_name": "Sean  Sukal", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0969F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000265855, "paid": true, "property_address": "2801 NW 27TH AVE", "property_city": "BOCA RATON", "property_county": "PALM BEACH COUNTY", "property_lat": "26.3753212", "property_lng": "-80.1419643", "property_state": "FL", "property_zip": "33434", "service_type": "CAD File", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000265855", "customer_email": "sasukal@hotmail.com", "service_type": "CAD File", "county": "", "property_address": "2801 NW 27TH AVE", "customer_name": "Sean  Sukal"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Sean Sukal", "confidence": "HIGH"}, "client_email": {"value": "sasukal@hotmail.com", "confidence": "HIGH"}, "property_address": {"value": "2801 NW 27TH AVE, BOCA RATON, FL 33434", "confidence": "HIGH"}, "property_county": {"value": "PALM BEACH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD File; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial imagery, or email attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 no appraiser or title data", "Structure square footage unknown", "Property features (pool, shed, fences, etc.) unknown \u2014 no aerial or appraiser data", "Reason for On Hold status not specified", "No customer data returned from FTF customer lookup", "County was blank in the outer FTF payload despite being present in order data \u2014 may indicate a data entry issue", "Scope of CAD File service unclear \u2014 needs clarification on what deliverable is expected", "Elevation certificate not requested but flood zone data present (Zone X) \u2014 confirm no EC needed"], "summary": "Individual residential client Sean Sukal is requesting a CAD File for a property at 2801 NW 27TH AVE, Boca Raton, FL 33434 (Palm Beach County), with special pricing applied and the order currently On Hold pending further action."}}</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:25:06.029742+00:00</t>
         </is>
       </c>
       <c r="T243" t="inlineStr">
@@ -15107,7 +15210,7 @@
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:18.516236+00:00</t>
+          <t>2026-06-02T19:25:06.086113+00:00</t>
         </is>
       </c>
     </row>
@@ -15119,7 +15222,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15139,7 +15242,17 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>4701 PINE TREE DR</t>
+          <t>4701 Pine Tree Dr, Boynton Beach, FL 33436</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202506051858190552, "created_at": "2025-06-05T15:02:00", "customer_email": "Uainc@bellsouth.net", "customer_id": 202506051858486509, "customer_name": "Leo Urban", "customer_type": "b2b", "delivered_at": "2025-06-06T19:53:37", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0788G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000265850, "paid": false, "property_address": "4701 PINE TREE DR", "property_city": "BOYNTON BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.5169459", "property_lng": "-80.11812619999999", "property_state": "FL", "property_zip": "33436", "service_type": "CAD File", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000265850", "customer_email": "Uainc@bellsouth.net", "service_type": "CAD File", "county": "", "property_address": "4701 PINE TREE DR", "customer_name": "Urban Associates, Inc."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Urban Associates, Inc.", "confidence": "HIGH"}, "client_email": {"value": "Uainc@bellsouth.net", "confidence": "HIGH"}, "property_address": {"value": "4701 Pine Tree Dr, Boynton Beach, FL 33436", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD File; no additional services indicated"}, "special_requirements": {"value": "Special pricing applies", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property feature data available; county appraiser lookup unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, structures, etc.)", "Invoice amount not set (due_amount is 0.00 and invoiced is false)", "Fieldwork date not recorded", "County appraiser data unavailable \u2014 no parcel details retrievable", "No matching emails found to cross-reference order details"], "summary": "B2B CAD File delivery order for Urban Associates, Inc. at 4701 Pine Tree Dr, Boynton Beach, FL (Palm Beach County) \u2014 already delivered but not yet invoiced, with special pricing flagged and parcel details still needed."}}</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:25:15.203325+00:00</t>
         </is>
       </c>
       <c r="T244" t="inlineStr">
@@ -15149,7 +15262,7 @@
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:18.602901+00:00</t>
+          <t>2026-06-02T19:25:15.258184+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -11790,7 +11790,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11813,16 +11813,37 @@
           <t>56048 Blue Creek Rd, Astor, FL 32102</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>{"total_amount": 750.0, "services": [{"name": "Legal Creation (Hourly)", "description": "Hourly legal description creation service for metes-and-bounds parcel at 56048 Blue Creek Rd, Astor, FL \u2014 Lake County. Complex metes-and-bounds legal description referencing Section 2, Manhattan Plat, with extended bearings and distances.", "amount": 375.0}, {"name": "Survey Re-draw", "description": "Re-draft/redraw of existing survey for parcel at 56048 Blue Creek Rd. 0.56-acre lot in FEMA Zone AE. No new fieldwork implied; redraw of existing survey document with updated formatting or legal.", "amount": 375.0}], "pricing_reasoning": "The order notes explicitly state that special pricing has been applied and the due amount is $750.00, agreed upon by management for this client (Gustavo Alvarez, individual, 0 prior orders). The two services \u2014 Legal Creation (hourly) and Survey Re-draw \u2014 are split evenly at $375.00 each to reach the management-confirmed $750.00 total. The base negotiated survey rate of $450.00 is acknowledged but superseded by the management-approved $750.00 figure for this specific combined service order. No Elevation Certificate was requested, so the $275.00 EC flat fee does not apply. A metes-and-bounds complexity upcharge would normally apply (+$100.00) and a lot-size upcharge for 0.51\u20131.00 ac (+$137.00), but these are absorbed within the management-approved flat price.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_ORDER: Order 1000270350 references the same property address (56048 Blue Creek Rd, Lake County) and same Folio/MLS (24-15-27-0100-058-02801) with service 'Land Survey Only'. Human review recommended to confirm these are distinct scopes of work and not a duplicate billing situation.", "ON_HOLD: Order is currently on hold per order notes. Confirm release authorization before invoicing.", "MANAGEMENT_APPROVED_PRICE: The $750.00 total is explicitly noted as management-approved special pricing for this client. Do not adjust without management sign-off.", "FEMA_ZONE_AE: Property is in FEMA Flood Zone AE (ELEV 06 FT, effective 12/18/2012). No EC was ordered, but field crew should be aware of flood zone conditions for site access.", "METES_AND_BOUNDS: Legal description is a complex metes-and-bounds parcel \u2014 absorbed into approved price but noted for crew awareness."]}</t>
+        </is>
+      </c>
       <c r="H178" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202508221847217707, "created_at": "2025-10-09T11:34:00", "customer_email": "galvarez@abpluseng.com", "customer_id": 202508221847218750, "customer_name": "Gustavo  Alvarez", "customer_type": "individual", "delivered_at": null, "due_amount": 750.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12069C0070E\nZONE: AE\nELEV: 06 FT\nEFF: 12/18/2012", "invoiced": false, "order_id": 1000272801, "paid": false, "property_address": "56048 BLUE CREEK RD", "property_city": "ASTOR", "property_county": "LAKE COUNTY", "property_lat": "29.17172729999999", "property_lng": "-81.54476509999999", "property_state": "FL", "property_zip": "32102", "service_type": "Legal Creation hourly, Survey Re-draw", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272801", "customer_email": "galvarez@abpluseng.com", "service_type": "Legal Creation hourly, Survey Re-draw", "county": "", "property_address": "56048 BLUE CREEK RD", "customer_name": "Gustavo  Alvarez"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Gustavo Alvarez", "confidence": "HIGH"}, "client_email": {"value": "galvarez@abpluseng.com", "confidence": "HIGH"}, "property_address": {"value": "56048 Blue Creek Rd, Astor, FL 32102", "confidence": "HIGH"}, "property_county": {"value": "Lake County", "confidence": "HIGH"}, "services_requested": {"value": ["Legal Creation Hourly", "Survey Re-draw"], "confidence": "HIGH", "notes": "Both services explicitly listed in service_type field; special_pricing flag is true which may affect billing rates"}, "special_requirements": {"value": "Special pricing applies; order is currently On Hold (status_code 11); flood zone AE with base flood elevation 6 ft (FIRM panel 12069C0070E, effective 12/18/2012)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "MEDIUM", "notes": "Email domain abpluseng.com suggests an engineering firm (AB Plus Engineering); customer_type is listed as individual but professional email domain indicates likely B2B relationship"}, "urgency": {"value": "normal", "confidence": "MEDIUM", "notes": "Order is On Hold; no rush indicators present; created Oct 2025 and last updated Jan 2026 suggesting no active urgency"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser unavailable and no parcel data provided", "Legal description missing \u2014 required for Legal Creation service", "Structure square footage unknown", "Property features unknown (pool, sheds, driveways, structures)", "Reason for On Hold status not documented", "Clarification needed on customer_type: listed as 'individual' but email suggests engineering firm (B2B)", "Scope of Survey Re-draw not defined \u2014 original survey document not provided", "Hourly rate or estimated hours for Legal Creation not specified despite due_amount of $750", "Fieldwork date not scheduled (fieldwork_at is null)", "Estimate has not been sent (estimate_sent is false) \u2014 client may not have approved scope yet"], "summary": "On-hold order for Gustavo Alvarez (likely affiliated with AB Plus Engineering) requesting Legal Creation (hourly) and Survey Re-draw services for a flood zone AE property at 56048 Blue Creek Rd, Astor, FL 32102 in Lake County, with special pricing applied and a due amount of $750."}}</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>1780428702163</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>2026-06-02T18:06:53.312265+00:00</t>
         </is>
       </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:31:45.055060+00:00</t>
+        </is>
+      </c>
+      <c r="R178" t="n">
+        <v>750</v>
+      </c>
       <c r="T178" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:19.043467+00:00</t>
@@ -11830,7 +11851,7 @@
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>2026-06-02T18:06:53.364168+00:00</t>
+          <t>2026-06-02T19:31:45.160616+00:00</t>
         </is>
       </c>
     </row>
@@ -11842,7 +11863,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11865,16 +11886,37 @@
           <t>826 S Lakeside Dr, Lake Worth Beach, FL 33460</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>{"total_amount": 525.0, "services": [{"name": "Boundary Survey / Land Survey", "description": "Standard boundary survey for Lot 2, Block 24, Palm Beach Farms Co. Plat No. 4, 826 S Lakeside Dr, Lake Worth Beach, Palm Beach County. Platted lot with straightforward legal description (no metes and bounds). Lot size is 0.30 acres \u2014 at the upper boundary of the base tier, no lot-size upcharge applied.", "amount": 250.0}, {"name": "Elevation Certificate (EC)", "description": "FEMA Flood Zone AE (panel 12099C0781G, effective 12/20/2024, base flood elevation 9 ft). EC required given AE designation. Standard EC rate applies; no VE coastal surcharge.", "amount": 275.0}], "pricing_reasoning": "The negotiated base survey rate of $250.00 applies per management agreement with FIRSTUP Structures, Inc. The property is a platted lot (no metes-and-bounds complexity upcharge), 0.30 acres exactly (falls within the 0.00\u20130.30 ac base tier \u2014 no lot-size upcharge), in Palm Beach County (no Monroe surcharge), with no pool, canal, or heavy vegetation indicators evident from the legal description or address context. The Elevation Certificate is priced at the fixed $275.00 rate; FEMA zone is AE (not VE), so no coastal $50 surcharge applies. Combined total is $525.00.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_ORDER: Order 1000260012 at 826 S Lakeside Dr, Palm Beach County \u2014 service: Re-survey \u2014 same coordinates (26.6050458, -80.0501115) and Folio/MLS (38434427010240020). Human review recommended before fulfillment.", "DUPLICATE_ORDER: Order 1000274869 at 826 S Lakeside Dr, Palm Beach County \u2014 service: Land Survey Only \u2014 same coordinates (26.6050458, -80.0501115) and Folio/MLS (38434427010240020). Human review recommended before fulfillment.", "SERVICE_TYPE_AMBIGUITY: Original order notes indicate 'lacking a defined survey service type.' This invoice assumes a combined Boundary Survey + Elevation Certificate based on Flood Zone AE designation and B2B context. Confirm service scope with FIRSTUP Structures, Inc. before invoicing.", "CLIENT_HISTORY: FIRSTUP Structures, Inc. shows 0 prior orders with NexGen despite being classified OLD_TITLE. Verify client tier classification and negotiated rate confirmation with management.", "LOT_SIZE_BOUNDARY: Lot is exactly 0.30 acres \u2014 at the precise upper limit of the base tier. No upcharge applied, but field conditions (aerial review) should be confirmed to ensure no complexity factors (vegetation, waterfront, etc.) were missed given no aerial image was provided."]}</t>
+        </is>
+      </c>
       <c r="H179" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202503041455592811, "created_at": "2025-10-08T09:36:04", "customer_email": "keith@firstupstructures.com", "customer_id": 202503041455592908, "customer_name": "Keith Urban", "customer_type": "b2b", "delivered_at": "2025-10-21T17:51:30", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0781G\nZONE: AE\nELEV: 09 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000272701, "paid": true, "property_address": "826 S LAKESIDE DR", "property_city": "LAKE WORTH BEACH", "property_county": "Palm Beach County", "property_lat": "26.6050458", "property_lng": "-80.0501115", "property_state": "FL", "property_zip": "33460", "service_type": "Quote", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272701", "customer_email": "keith@firstupstructures.com", "service_type": "Quote", "county": "", "property_address": "826 S LAKESIDE DR", "customer_name": "FIRSTUP Structures, Inc."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "FIRSTUP Structures, Inc.", "confidence": "HIGH"}, "client_email": {"value": "keith@firstupstructures.com", "confidence": "HIGH"}, "property_address": {"value": "826 S Lakeside Dr, Lake Worth Beach, FL 33460", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "MEDIUM", "notes": "Service type is listed as 'Quote' only \u2014 no specific survey service (e.g., boundary, elevation, topographic) has been identified. Actual service scope is unclear."}, "special_requirements": {"value": "Special pricing applies. Property is in FEMA Flood Zone AE (Panel 12099C0781G, Effective 12/20/2024, Base Flood Elevation 9 ft). No elevation certificate requested at this time.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 no appraiser data, no emails, no aerial imagery referenced. Pool, sheds, driveways, and structures are unknown."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not defined \u2014 'Quote' is not a deliverable service", "Lot size unknown \u2014 no appraiser data available", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, fences, etc.) unknown", "No fieldwork date scheduled (fieldwork_at is null)", "Invoice has not been generated despite order being marked Delivered and Paid", "No matching emails found to clarify scope or client instructions"], "summary": "B2B quote order for FIRSTUP Structures, Inc. at 826 S Lakeside Dr, Lake Worth Beach FL (Flood Zone AE) \u2014 delivered and paid but lacking a defined survey service type, property details, and invoice."}}</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>1780428726459</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>2026-06-02T18:07:04.463122+00:00</t>
         </is>
       </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:32:08.731558+00:00</t>
+        </is>
+      </c>
+      <c r="R179" t="n">
+        <v>525</v>
+      </c>
       <c r="T179" t="inlineStr">
         <is>
           <t>2026-06-02T16:08:19.112404+00:00</t>
@@ -11882,7 +11924,7 @@
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>2026-06-02T18:07:04.514378+00:00</t>
+          <t>2026-06-02T19:32:08.785271+00:00</t>
         </is>
       </c>
     </row>
@@ -15274,7 +15316,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15294,7 +15336,17 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>6650 NW 84TH AVE</t>
+          <t>6650 NW 84TH AVE, PARKLAND, FL 33067</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202506031524032464, "created_at": "2025-06-03T11:28:02", "customer_email": "archtype@bellsouth.net", "customer_id": 202506031524461158, "customer_name": "John Lamb", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0165H\nZONE: AH\nELEV: 14 FT\nEFF: 08/18/2014", "invoiced": false, "order_id": 1000265646, "paid": true, "property_address": "6650 NW 84TH AVE", "property_city": "PARKLAND", "property_county": "BROWARD COUNTY", "property_lat": "26.3124462", "property_lng": "-80.238055", "property_state": "FL", "property_zip": "33067", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000265646", "customer_email": "archtype@bellsouth.net", "service_type": "CAD file", "county": "", "property_address": "6650 NW 84TH AVE", "customer_name": "Archtype Design, Inc"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Archtype Design, Inc", "confidence": "MEDIUM"}, "client_email": {"value": "archtype@bellsouth.net", "confidence": "HIGH"}, "property_address": {"value": "6650 NW 84TH AVE, PARKLAND, FL 33067", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no matching emails found"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: order lists 'John Lamb' as customer_name but outer payload shows 'Archtype Design, Inc' \u2014 confirm correct contact/company name", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, etc.)", "County property appraiser data unavailable \u2014 no county was passed to appraiser lookup", "No matching emails found to corroborate order details", "Urgency/rush status not specified", "Order is On Hold \u2014 reason for hold not documented", "Scope of CAD file request not defined (boundary, as-built, topographic, etc.)"], "summary": "A B2B CAD file order for Archtype Design, Inc at 6650 NW 84TH Ave, Parkland, FL (Broward County) is currently On Hold with special pricing applied, but lacks legal description, lot size, property features, and clarification on the CAD file scope."}}</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:30:28.789119+00:00</t>
         </is>
       </c>
       <c r="T245" t="inlineStr">
@@ -15304,7 +15356,7 @@
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:18.743454+00:00</t>
+          <t>2026-06-02T19:30:28.842996+00:00</t>
         </is>
       </c>
     </row>
@@ -15316,7 +15368,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15336,7 +15388,17 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>1885 MISSISSIPPI AVE NE</t>
+          <t>1885 Mississippi Ave NE, St Petersburg, FL 33703</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202506031051122588, "created_at": "2025-06-08T11:28:02", "customer_email": "aaron@gatorcapitalpartners.com", "customer_id": 202506031051122688, "customer_name": "Aaron Lambert", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12103C0228H\nZONE: AE\nELEV: 09 FT\nEFF: 08/24/2021", "invoiced": false, "order_id": 1000265620, "paid": false, "property_address": "1885 MISSISSIPPI AVE NE", "property_city": "ST PETERSBURG", "property_county": "PINELLAS COUNTY", "property_lat": "27.8183902", "property_lng": "-82.6016365", "property_state": "FL", "property_zip": "33703", "service_type": "Land Survey Only", "special_pricing": false, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000265620", "customer_email": "aaron@gatorcapitalpartners.com", "service_type": "Land Survey Only", "county": "", "property_address": "1885 MISSISSIPPI AVE NE", "customer_name": "Aaron Lambert"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Aaron Lambert", "confidence": "HIGH"}, "client_email": {"value": "aaron@gatorcapitalpartners.com", "confidence": "HIGH"}, "property_address": {"value": "1885 Mississippi Ave NE, St Petersburg, FL 33703", "confidence": "HIGH"}, "property_county": {"value": "Pinellas County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested (elevation_cert: false)"}, "special_requirements": {"value": "Property is in FEMA Flood Zone AE (panel 12103C0228H, effective 08/24/2021, base flood elevation 9 ft). Order is currently On Hold.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available and no emails or attachments to reference; features unknown"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) unknown", "No matching emails found \u2014 no additional context from client communications", "County was blank in top-level FTF data (though populated in nested data object \u2014 verify consistency)", "Order is On Hold \u2014 reason for hold not specified; human review needed", "No estimate sent and not yet invoiced \u2014 pricing not yet established"], "summary": "B2B client Aaron Lambert (Gator Capital Partners) has a Land Survey Only order on hold for a residential property in St. Petersburg, FL (Pinellas County) located in FEMA Flood Zone AE, with no lot details, legal description, or property features available."}}</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:30:39.323487+00:00</t>
         </is>
       </c>
       <c r="T246" t="inlineStr">
@@ -15346,7 +15408,7 @@
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:18.832762+00:00</t>
+          <t>2026-06-02T19:30:39.377123+00:00</t>
         </is>
       </c>
     </row>
@@ -15358,7 +15420,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15378,7 +15440,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>3801 COCO GROVE AVE</t>
+          <t>3801 Coco Grove Ave, Miami, FL 33133</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202412111457326258, "created_at": "2025-06-02T11:32:05", "customer_email": "locus@locusarchitecture.net", "customer_id": 202412111458535222, "customer_name": "Christian Hoyos", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0457L\nZONE: X\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000265557, "paid": true, "property_address": "3801 COCO GROVE AVE", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.7211535", "property_lng": "-80.2546745", "property_state": "FL", "property_zip": "33133", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000265557", "customer_email": "locus@locusarchitecture.net", "service_type": "CAD file", "county": "", "property_address": "3801 COCO GROVE AVE", "customer_name": "Locus Architecture"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Locus Architecture", "confidence": "MEDIUM"}, "client_email": {"value": "locus@locusarchitecture.net", "confidence": "HIGH"}, "property_address": {"value": "3801 Coco Grove Ave, Miami, FL 33133", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file' in order data; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order currently on hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available; no aerial or email context provided; features unknown"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Client name conflict: FTF order shows 'Christian Hoyos' as customer_name but 'Locus Architecture' as display name \u2014 confirm billing contact", "Order is On Hold \u2014 reason for hold unknown; human review needed before proceeding", "Lot size not available \u2014 county appraiser data unavailable", "Legal description not available \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features (pool, shed, structures) unknown \u2014 no aerial or appraiser data", "Urgency/deadline not specified", "Scope of CAD file deliverable unclear \u2014 base map, as-built, boundary, etc.", "No fieldwork date scheduled", "Invoice has not been sent despite order being marked paid \u2014 verify billing status"], "summary": "B2B order from Locus Architecture for a CAD file at 3801 Coco Grove Ave, Miami, FL 33133 (Miami-Dade County) with special pricing applied, currently on hold and requiring human review to resolve the name conflict, hold reason, and missing property details."}}</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:30:50.750623+00:00</t>
         </is>
       </c>
       <c r="T247" t="inlineStr">
@@ -15388,7 +15460,7 @@
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:18.923810+00:00</t>
+          <t>2026-06-02T19:30:50.804800+00:00</t>
         </is>
       </c>
     </row>
@@ -15400,7 +15472,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15420,7 +15492,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>780 HARBOUR ISLE PL</t>
+          <t>780 HARBOUR ISLE PL, WEST PALM BEACH, FL 33410</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202506021505213807, "created_at": "2025-06-02T11:09:03", "customer_email": "erol@buyuk.ch", "customer_id": 202506021505214843, "customer_name": "EROL BUYUK", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0379G\nZONE: AE\nELEV: 07 FT\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000265550, "paid": true, "property_address": "780 HARBOUR ISLE PL", "property_city": "WEST PALM BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.8319688", "property_lng": "-80.0688526", "property_state": "FL", "property_zip": "33410", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000265550", "customer_email": "erol@buyuk.ch", "service_type": "CAD file", "county": "", "property_address": "780 HARBOUR ISLE PL", "customer_name": "EROL BUYUK"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "EROL BUYUK", "confidence": "HIGH"}, "client_email": {"value": "erol@buyuk.ch", "confidence": "HIGH"}, "property_address": {"value": "780 HARBOUR ISLE PL, WEST PALM BEACH, FL 33410", "confidence": "HIGH"}, "property_county": {"value": "PALM BEACH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated. Unclear if CAD file is derived from an existing survey or requires new fieldwork."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11). Flood zone data present: FIRM panel 12099C0379G, Zone AE, base flood elevation 07 ft, effective 12/20/2024.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property appraiser data available; no emails or attachments to reference. Pool, shed, driveways, and other features unknown."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Reason order is On Hold \u2014 needs human review", "Clarification on what the CAD file deliverable is based on (existing survey, new fieldwork, or client-supplied data)", "Lot size not available \u2014 county appraiser data unavailable", "Legal description not available", "Structure square footage unknown", "Property features (pool, shed, structures) unknown \u2014 no appraiser or aerial data", "Fieldwork date not scheduled (fieldwork_at is null)", "Delivery date not set (delivered_at is null)", "No matching emails found \u2014 no additional context from client communications", "Special pricing terms not detailed \u2014 reason for discount unknown"], "summary": "Individual residential client EROL BUYUK has a paid but On Hold CAD file order for 780 Harbour Isle Pl, West Palm Beach FL (Palm Beach County, Flood Zone AE), with special pricing applied and no fieldwork or delivery dates yet scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:31:03.214370+00:00</t>
         </is>
       </c>
       <c r="T248" t="inlineStr">
@@ -15430,7 +15512,7 @@
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:19.012654+00:00</t>
+          <t>2026-06-02T19:31:03.268230+00:00</t>
         </is>
       </c>
     </row>
@@ -15442,7 +15524,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15462,7 +15544,17 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>5201 VILLAGE BLVD</t>
+          <t>5201 Village Blvd, West Palm Beach, FL 33407</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202505051559120505, "created_at": "2025-06-02T10:46:05", "customer_email": "oureinsteins@gmail.com", "customer_id": 202505051559121629, "customer_name": "Mihai Gorgan", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0388F \nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000265545, "paid": true, "property_address": "5201 VILLAGE BLVD", "property_city": "WEST PALM BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.7609246", "property_lng": "-80.1006115", "property_state": "FL", "property_zip": "33407", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000265545", "customer_email": "oureinsteins@gmail.com", "service_type": "CAD file", "county": "", "property_address": "5201 VILLAGE BLVD", "customer_name": "Mihai Gorgan"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Mihai Gorgan", "confidence": "HIGH"}, "client_email": {"value": "oureinsteins@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "5201 Village Blvd, West Palm Beach, FL 33407", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated. Unclear if CAD file is standalone or tied to an underlying survey product."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Reason order is On Hold \u2014 needs clarification before proceeding", "Exact CAD file deliverable scope not defined (based on what survey type?)", "Lot size unknown \u2014 no appraiser data available", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, fences, etc.) unknown", "Fieldwork date not scheduled", "No supporting emails or documents on file", "County field is blank in the outer order object despite being present in data block \u2014 data inconsistency to verify"], "summary": "Individual residential client Mihai Gorgan is requesting a CAD file for 5201 Village Blvd, West Palm Beach, FL 33407 (Palm Beach County); the order is paid but currently On Hold with special pricing applied and no fieldwork scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:31:13.801941+00:00</t>
         </is>
       </c>
       <c r="T249" t="inlineStr">
@@ -15472,7 +15564,7 @@
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:19.101239+00:00</t>
+          <t>2026-06-02T19:31:13.856191+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -11936,7 +11936,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11959,16 +11959,37 @@
           <t>3801 Coco Grove Ave, Miami, FL 33133</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "Land Survey Only", "description": "Boundary survey for Lot 9 and Lot 10 Less West 43.5 Feet, Block 3, Coco Grove Subdivision, Miami-Dade County. Certifications to Eric Dong, Katherine Huang, and Locus Architecture Inc. Lot size 0.25 acres (within 0.00\u20130.30 ac tier); FEMA Zone X (no flood zone upcharge); legal description involves a standard recorded plat with a simple lot subtraction (not metes and bounds); no pool, waterfront, heavy vegetation, or Monroe County factors identified.", "amount": 450.0}], "pricing_reasoning": "Management pre-negotiated a base rate of $450.00 for this individual client (Eric Dong, first-time client). The lot is 0.25 acres and falls in the standard 0.00\u20130.30 ac tier requiring no lot-size upcharge. FEMA Zone X carries no EC or flood-zone complexity. The legal description references a platted subdivision with a simple west-portion exclusion \u2014 not a full metes-and-bounds description warranting the $100 upcharge. No pool, canal, heavy vegetation, or Monroe County mobilization factors are apparent. No EC was ordered. Final price equals the agreed base rate with no justified upcharges.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_WARNING: Order 1000251648 at the same address (3801 Coco Grove Ave, Miami-Dade) with service 'Land Survey Only' and matching Folio 0141200080280 \u2014 possible duplicate of this order. Human review recommended before scheduling fieldwork.", "DUPLICATE_WARNING: Order 1000255190 at the same address with service 'Topography Survey' and matching Folio 0141200080280 \u2014 a topo survey may already be on file or in progress for this property. Confirm with client whether both services are still needed.", "DUPLICATE_WARNING: Order 1000255448 at the same address listed as a 'Quote' order \u2014 may represent an earlier pricing inquiry for this same property. Verify whether this order supersedes or is separate from that quote.", "ORDER_ON_HOLD: Notes indicate this order was flagged as On Hold with special pricing and no fieldwork scheduled. Confirm with management that the $450.00 negotiated rate is still current and that the hold has been released before proceeding.", "MULTIPLE_CERTIFICATIONS: Survey must be certified to Eric Dong, Katherine Huang, and Locus Architecture Inc. \u2014 confirm all certifications are captured on the final deliverable."]}</t>
+        </is>
+      </c>
       <c r="H180" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202412302008110119, "created_at": "2025-10-07T17:20:05", "customer_email": "edong888@gmail.com", "customer_id": 202412302008111157, "customer_name": "Eric Dong", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0457L\nZONE: X\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000272649, "paid": false, "property_address": "3801 COCO GROVE AVE", "property_city": "MIAMI", "property_county": "MIAMI-DADE COUNTY", "property_lat": "25.7211453", "property_lng": "-80.2546693", "property_state": "FL", "property_zip": "33133", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272649", "customer_email": "edong888@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "3801 COCO GROVE AVE", "customer_name": "Eric Dong"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Eric Dong", "confidence": "HIGH"}, "client_email": {"value": "edong888@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "3801 Coco Grove Ave, Miami, FL 33133", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no additional services indicated"}, "special_requirements": {"value": "Special pricing flagged on order; order currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments found"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description unknown \u2014 county appraiser data unavailable", "Structure square footage unknown", "Property features (pool, shed, fence, structures) unknown \u2014 no aerial or appraiser data", "Order is On Hold \u2014 reason for hold not specified, needs human review", "Special pricing flag is set but no pricing details or reason provided", "No invoice amount set (due_amount: 0.00) \u2014 pricing not yet determined", "Fieldwork date not scheduled", "Customer data object is empty \u2014 no additional contact or billing info available"], "summary": "Residential land survey order for Eric Dong at 3801 Coco Grove Ave, Miami, FL 33133 (Miami-Dade County) is currently On Hold with special pricing flagged, no fieldwork scheduled, and key property details such as lot size, legal description, and property features still unknown."}}</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>1780429068832</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>2026-06-02T18:12:25.548408+00:00</t>
         </is>
       </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:37:51.586165+00:00</t>
+        </is>
+      </c>
+      <c r="R180" t="n">
+        <v>450</v>
+      </c>
       <c r="T180" t="inlineStr">
         <is>
           <t>2026-06-02T16:12:12.975802+00:00</t>
@@ -11976,7 +11997,7 @@
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>2026-06-02T18:12:25.603398+00:00</t>
+          <t>2026-06-02T19:37:51.690772+00:00</t>
         </is>
       </c>
     </row>
@@ -11988,7 +12009,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -12011,16 +12032,37 @@
           <t>1409 NE 7TH AVE, CAPE CORAL, FL 33909</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>{"total_amount": 500.0, "services": [{"name": "Survey Re-draw", "description": "Re-draw of existing boundary survey for Lots 11 and 12, Block 2455, Cape Coral Unit 34, Lee County. 0.23 acres, FEMA Zone X (no EC required). Negotiated flat rate applied per management agreement with Nexgen Land Solutions, LLC.", "amount": 500.0}], "pricing_reasoning": "This is a Survey Re-draw (not a new field survey) for an established B2B title client with a management-agreed flat rate of $500.00. The property is 0.23 acres (below the 0.31-acre upcharge threshold), a standard platted Cape Coral lot with a straightforward legal description (no metes and bounds), located in FEMA Zone X (no EC required and no VE surcharge), and in Lee County (no Monroe remote mobilization). No complexity upcharges are warranted based on available data. The order is flagged for a possible duplicate and for missing supporting documents per the order notes.", "confidence": "MEDIUM", "escalate_flag": true, "escalate_reason": "Order is currently On Hold and explicitly noted as lacking lot details, legal description confirmation, and supporting documents needed to complete the re-draw scope. Additionally, a possible duplicate order (1000192551) exists at the same address and folio for a Land Survey Only service. Human review is required to confirm whether this re-draw is tied to or supersedes the prior order, and to ensure all source documents are received before proceeding.", "flags": ["POSSIBLE_DUPLICATE: Order 1000192551 \u2014 same address (1409 NE 7TH AVE, Lee County), same folio (014423C2024550110), same coordinates (26.679048, -81.9589153) \u2014 service on prior order was Land Survey Only. Verify relationship between orders before proceeding.", "ON_HOLD: Order notes indicate special pricing is applied but supporting documents (lot details, legal description confirmation, source survey) are missing. Do not release to field until documents are received.", "RE-DRAW_SCOPE: As a re-draw (office/drafting work rather than new field survey), confirm whether any field verification or re-staking is included in scope or if this is strictly a CAD/drafting redraw of an existing survey."]}</t>
+        </is>
+      </c>
       <c r="H181" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 201801311053398445, "created_at": "2025-10-03T14:26:00", "customer_email": "FREDERICK_S@NEXGENLOGIX.COM", "customer_id": 202410281556504891, "customer_name": "ORDER RESOLUTIONS", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12071C0262G\nZONE: X\nEFF: 11/17/2022", "invoiced": false, "order_id": 1000272525, "paid": false, "property_address": "1409 NE 7TH AVE", "property_city": "CAPE CORAL", "property_county": "LEE COUNTY", "property_lat": "26.6790374", "property_lng": "-81.95892649999999", "property_state": "FL", "property_zip": "33909", "service_type": "Survey Re-draw", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272525", "customer_email": "FREDERICK_S@NEXGENLOGIX.COM", "service_type": "Survey Re-draw", "county": "", "property_address": "1409 NE 7TH AVE", "customer_name": "Nexgen Land Solutions, LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "ORDER RESOLUTIONS", "confidence": "MEDIUM"}, "client_email": {"value": "FREDERICK_S@NEXGENLOGIX.COM", "confidence": "HIGH"}, "property_address": {"value": "1409 NE 7TH AVE, CAPE CORAL, FL 33909", "confidence": "HIGH"}, "property_county": {"value": "LEE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Survey Re-draw"], "confidence": "HIGH", "notes": "Service type explicitly stated as Survey Re-draw; no additional services indicated"}, "special_requirements": {"value": "Special pricing applies; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Client name ambiguity \u2014 FTF order shows 'ORDER RESOLUTIONS' but customer_name in outer envelope shows 'Nexgen Land Solutions, LLC'; needs human clarification", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features (pool, shed, structures) unknown \u2014 no appraiser data or aerial available", "Reason for On Hold status not specified", "Original survey or reference documents not attached for re-draw scope", "No fieldwork or delivery dates scheduled", "Special pricing amount or discount not detailed"], "summary": "A b2b Survey Re-draw order for a property at 1409 NE 7TH AVE, Cape Coral, FL (Lee County) is currently On Hold with special pricing applied, but lacks lot details, legal description, and supporting documents needed to complete the re-draw scope."}}</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>1780429089945</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>2026-06-02T18:12:36.062390+00:00</t>
         </is>
       </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:38:12.154624+00:00</t>
+        </is>
+      </c>
+      <c r="R181" t="n">
+        <v>500</v>
+      </c>
       <c r="T181" t="inlineStr">
         <is>
           <t>2026-06-02T16:12:13.049076+00:00</t>
@@ -12028,7 +12070,7 @@
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>2026-06-02T18:12:36.117153+00:00</t>
+          <t>2026-06-02T19:38:12.215519+00:00</t>
         </is>
       </c>
     </row>
@@ -15576,7 +15618,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15596,7 +15638,17 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>13475 150TH CT N</t>
+          <t>13475 150TH CT N, JUPITER, FL 33478</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202504231333469642, "created_at": "2025-05-28T11:05:03", "customer_email": "tonysbmw@yahoo.com", "customer_id": 202504231333471051, "customer_name": "James Scott", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0163F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000265300, "paid": true, "property_address": "13475 150TH CT N", "property_city": "JUPITER", "property_county": "PALM BEACH COUNTY", "property_lat": "26.8996849", "property_lng": "-80.2475311", "property_state": "FL", "property_zip": "33478", "service_type": "CAD File", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000265300", "customer_email": "tonysbmw@yahoo.com", "service_type": "CAD File", "county": "", "property_address": "13475 150TH CT N", "customer_name": "James Scott"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "James Scott", "confidence": "HIGH"}, "client_email": {"value": "tonysbmw@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "13475 150TH CT N, JUPITER, FL 33478", "confidence": "HIGH"}, "property_county": {"value": "PALM BEACH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as CAD File; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order status is On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, shed, structures) unknown", "Reason for On Hold status not specified", "Reason for special pricing not documented", "No fieldwork or delivery dates scheduled", "Invoice has not been sent despite order being marked paid", "No clarification on scope of CAD File service (boundary, topo, as-built, etc.)"], "summary": "Individual client James Scott has a paid CAD File order for a residential property at 13475 150TH CT N, Jupiter, FL (Palm Beach County) that is currently On Hold with special pricing applied, but lacks lot details, legal description, and property feature data."}}</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:36:32.491599+00:00</t>
         </is>
       </c>
       <c r="T250" t="inlineStr">
@@ -15606,7 +15658,7 @@
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:19.190104+00:00</t>
+          <t>2026-06-02T19:36:32.552632+00:00</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15670,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15638,7 +15690,17 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>12609 S INDIAN RIVER DR</t>
+          <t>12609 S INDIAN RIVER DR, JENSEN BEACH, FL 34957</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202505281415132397, "created_at": "2025-05-28T10:17:03", "customer_email": "ribanez2nd@yahoo.com", "customer_id": 202505281415133438, "customer_name": "RICARDO IBANEZ", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12111C0292K\nZONE: X\nEFF: 02/19/2020", "invoiced": false, "order_id": 1000265289, "paid": true, "property_address": "12609 S INDIAN RIVER DR", "property_city": "JENSEN BEACH", "property_county": "St. Lucie County", "property_lat": "27.2834436", "property_lng": "-80.24651209999999", "property_state": "FL", "property_zip": "34957", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000265289", "customer_email": "ribanez2nd@yahoo.com", "service_type": "CAD file", "county": "", "property_address": "12609 S INDIAN RIVER DR", "customer_name": "RICARDO IBANEZ"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "RICARDO IBANEZ", "confidence": "HIGH"}, "client_email": {"value": "ribanez2nd@yahoo.com", "confidence": "HIGH"}, "property_address": {"value": "12609 S INDIAN RIVER DR, JENSEN BEACH, FL 34957", "confidence": "HIGH"}, "property_county": {"value": "St. Lucie County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type is listed as 'CAD file'; no additional services indicated. Unclear if this is a standalone CAD deliverable or tied to a boundary/topographic survey."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["No scope clarification \u2014 unclear what the CAD file is based on (boundary survey, topo, as-built, etc.)", "No lot size provided", "No legal description provided", "No structure square footage available", "No property features data (pool, sheds, driveways, etc.)", "County appraiser data unavailable \u2014 county field was blank in outer FTF payload despite being present in order data", "Order is On Hold \u2014 reason for hold not specified", "No urgency or deadline indicated", "No matching emails found to supplement order context"], "summary": "Individual residential client Ricardo Ibanez has a paid CAD file order for a property on S Indian River Dr in Jensen Beach, FL (St. Lucie County) that is currently On Hold with special pricing applied and no scope or property detail data available."}}</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:36:43.700988+00:00</t>
         </is>
       </c>
       <c r="T251" t="inlineStr">
@@ -15648,7 +15710,7 @@
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:19.334416+00:00</t>
+          <t>2026-06-02T19:36:43.761901+00:00</t>
         </is>
       </c>
     </row>
@@ -15660,7 +15722,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15680,7 +15742,17 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>7107 58TH TER E</t>
+          <t>7107 58TH TER E, PALMETTO, FL 34221</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 201803271530243774, "created_at": "2025-05-25T21:19:00", "customer_email": "jhall@regtitles.com", "customer_id": 202407291519218180, "customer_name": "Julie  Hall", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12081C0159E\nZONE: AE\nELEV: 16.7 FT\nEFF: 03/17/2014", "invoiced": false, "order_id": 1000265181, "paid": false, "property_address": "7107 58TH TER E", "property_city": "PALMETTO", "property_county": "MANATEE COUNTY", "property_lat": "27.5774703", "property_lng": "-82.50469489999999", "property_state": "FL", "property_zip": "34221", "service_type": "Land Survey and Elevation", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000265181", "customer_email": "jhall@regtitles.com", "service_type": "Land Survey and Elevation", "county": "", "property_address": "7107 58TH TER E", "customer_name": "Register Settlement Services, LLC"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Register Settlement Services, LLC", "confidence": "MEDIUM"}, "client_email": {"value": "jhall@regtitles.com", "confidence": "HIGH"}, "property_address": {"value": "7107 58TH TER E, PALMETTO, FL 34221", "confidence": "HIGH"}, "property_county": {"value": "MANATEE COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Boundary Survey", "Elevation Certificate"], "confidence": "MEDIUM", "notes": "Service type listed as 'Land Survey and Elevation'; interpreted as boundary/location survey plus elevation certificate. elevation_cert flag is false but service type explicitly includes elevation \u2014 likely a data entry inconsistency requiring human review."}, "special_requirements": {"value": "Special pricing applied. Order is On Hold (status_code 11). Flood zone data available: FIRM panel 12081C0159E, Zone AE, BFE 16.7 FT, effective 03/17/2014.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No aerial, appraiser, or email data available to identify pool, shed, driveways, or other visible structures."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Order is On Hold \u2014 reason for hold unknown; human review required before proceeding", "elevation_cert flag is false but service type includes 'Elevation' \u2014 confirm whether EC is actually required", "Client name conflict: FTF data shows 'Julie Hall' as customer_name but outer payload shows 'Register Settlement Services, LLC' \u2014 confirm billing entity", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown \u2014 no aerial or appraiser data", "Urgency/deadline not specified", "No fieldwork date scheduled (fieldwork_at is null)", "Invoice not yet created; order has not been delivered or paid"], "summary": "A B2B 'Land Survey and Elevation' order for Register Settlement Services, LLC at 7107 58TH TER E, Palmetto, FL (Manatee County) is currently On Hold with special pricing applied, pending resolution of a service scope conflict regarding the elevation certificate and missing property details."}}</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:36:57.167241+00:00</t>
         </is>
       </c>
       <c r="T252" t="inlineStr">
@@ -15690,7 +15762,7 @@
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:19.424626+00:00</t>
+          <t>2026-06-02T19:36:57.228306+00:00</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15774,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15722,7 +15794,17 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>125 BANYAN ISLE DR</t>
+          <t>125 Banyan Isle Dr, Palm Beach Gardens, FL 33418</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202505161752032240, "created_at": "2025-05-16T14:03:04", "customer_email": "contact@lmphomeservices.com", "customer_id": 202505161754450651, "customer_name": "Luana Magalhaes", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0378F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000264774, "paid": true, "property_address": "125 BANYAN ISLE DR", "property_city": "PALM BEACH GARDENS", "property_county": "PALM BEACH COUNTY", "property_lat": "26.8184152", "property_lng": "-80.1120533", "property_state": "FL", "property_zip": "33418", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000264774", "customer_email": "contact@lmphomeservices.com", "service_type": "CAD file", "county": "", "property_address": "125 BANYAN ISLE DR", "customer_name": "LMP Home Services"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "LMP Home Services", "confidence": "HIGH"}, "client_email": {"value": "contact@lmphomeservices.com", "confidence": "HIGH"}, "property_address": {"value": "125 Banyan Isle Dr, Palm Beach Gardens, FL 33418", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file' in order data; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no matching emails found"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, etc.)", "County appraiser data unavailable", "No matching emails found to supplement order details", "Reason for 'On Hold' status not documented", "Fieldwork date not scheduled", "Invoice not yet generated despite paid status \u2014 needs review", "Scope of CAD file deliverable not specified (boundary, topo, as-built, etc.)"], "summary": "B2B CAD file order for LMP Home Services at 125 Banyan Isle Dr, Palm Beach Gardens, FL is currently on hold with special pricing applied, payment received, but missing lot size, legal description, and property feature details."}}</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:37:06.522192+00:00</t>
         </is>
       </c>
       <c r="T253" t="inlineStr">
@@ -15732,7 +15814,7 @@
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:19.514623+00:00</t>
+          <t>2026-06-02T19:37:06.583381+00:00</t>
         </is>
       </c>
     </row>
@@ -15744,7 +15826,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15764,7 +15846,17 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>501 VILABELLA AVE</t>
+          <t>501 Vilabella Ave, Coral Gables, FL 33146</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202505151835400283, "created_at": "2025-05-15T14:39:03", "customer_email": "clarkebgj@gmail.com", "customer_id": 202505151835401428, "customer_name": "Clarke Gillespie", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12086C0457L \nZONE: X\nEFF: 09/11/2009", "invoiced": false, "order_id": 1000264707, "paid": true, "property_address": "501 VILABELLA AVE", "property_city": "CORAL GABLES", "property_county": "Miami-Dade County", "property_lat": "25.7296737", "property_lng": "-80.26434340000002", "property_state": "FL", "property_zip": "33146", "service_type": "Quote", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000264707", "customer_email": "clarkebgj@gmail.com", "service_type": "Quote", "county": "", "property_address": "501 VILABELLA AVE", "customer_name": "Clarke Gillespie"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Clarke Gillespie", "confidence": "HIGH"}, "client_email": {"value": "clarkebgj@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "501 Vilabella Ave, Coral Gables, FL 33146", "confidence": "HIGH"}, "property_county": {"value": "Miami-Dade County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., boundary, elevation, topographic) has been identified. Needs clarification."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service(s) requested \u2014 'Quote' is not a survey type", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, etc.)", "Urgency/timeline not specified", "Reason for 'On Hold' status not documented", "No supporting emails or attachments to clarify scope"], "summary": "Individual residential client Clarke Gillespie has an On Hold quote order for a property at 501 Vilabella Ave, Coral Gables, FL (Miami-Dade County), but the specific survey service requested and property details remain undefined."}}</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:37:17.044381+00:00</t>
         </is>
       </c>
       <c r="T254" t="inlineStr">
@@ -15774,7 +15866,7 @@
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:19.604572+00:00</t>
+          <t>2026-06-02T19:37:17.104048+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="pipeline_state" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="learnings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="pending_confirmations" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="poll_state" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_state" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="learnings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pending_confirmations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="poll_state" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11498,7 +11498,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>invoice_draft_posted</t>
+          <t>invoice_approved</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11549,6 +11549,11 @@
           <t>2026-06-02T19:20:20.753326+00:00</t>
         </is>
       </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Prateek</t>
+        </is>
+      </c>
       <c r="R174" t="n">
         <v>475</v>
       </c>
@@ -11559,7 +11564,7 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>2026-06-02T19:20:20.810846+00:00</t>
+          <t>2026-06-02T19:42:31.451877+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_state" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="learnings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pending_confirmations" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="poll_state" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="pipeline_state" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="learnings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="pending_confirmations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="poll_state" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -12110,16 +12110,37 @@
           <t>3708 PLUMOSA TERRACE, BRADENTON, FL 34210</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>{"total_amount": 450.0, "services": [{"name": "CAD File / Boundary Survey", "description": "Residential boundary survey with CAD file deliverable for LOT 21, SAN REMO SHORES UNIT 2, Manatee County. Lot size 0.21 acres (below 0.31 ac threshold \u2014 no lot size upcharge). Platted subdivision lot with a clean legal description (no metes and bounds upcharge). FEMA Zone AE at 8 ft elevation noted but no Elevation Certificate was requested. Certifications to Michael D. Schwartz and Joanne Schwartz.", "amount": 450.0}], "pricing_reasoning": "Management pre-negotiated a flat rate of $450.00 for this specific client (individual homeowner, first-time order). The service is a CAD file deliverable for a standard platted residential lot (0.21 ac) in Manatee County \u2014 no complexity upcharges are warranted: the legal description is a clean lot-and-block reference, lot size is under 0.31 acres, no pool or waterfront canal features are confirmed, the county is not Monroe, and no Elevation Certificate was requested. The agreed rate of $450.00 is applied as the total.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE DUPLICATE: Order 1000270817 references the same address (3708 PLUMOSA TER, Manatee County), same coordinates, and same Folio/MLS (7521000005) with service type 'Land Survey and Elevation' \u2014 human review recommended to confirm whether this CAD file order is a standalone deliverable from that prior survey or a redundant new field order.", "ORDER ON HOLD: Per order notes, this order was placed on hold with special pricing already applied and payment received but not yet invoiced \u2014 verify with management that the $450.00 negotiated rate is still the correct invoicing amount before finalizing.", "SURVEY SCOPE AMBIGUITY: Order notes flagged missing survey scope details at time of entry; scope has been interpreted as a standard residential boundary survey with CAD deliverable based on available data \u2014 confirm with client if any additional services (e.g., Elevation Certificate, topographic data) are expected.", "NO ELEVATION CERTIFICATE REQUESTED: Property is in FEMA Zone AE (Flood Map 12081C0283F, effective 08/10/2021). Client was not flagged as requesting an EC, but proximity to AE zone may warrant a proactive inquiry."]}</t>
+        </is>
+      </c>
       <c r="H182" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510031522295033, "created_at": "2025-10-03T11:42:03", "customer_email": "tffmgwr4@aol.com", "customer_id": 202510031522296104, "customer_name": "MICHAEL  SCHWARTZ", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12081C0283F\nZONE: AE\nELEV: 08 FT\nEFF: 08/10/2021", "invoiced": false, "order_id": 1000272499, "paid": true, "property_address": "3708 PLUMOSA TERRACE", "property_city": "BRADENTON", "property_county": "Manatee County", "property_lat": "27.4684347", "property_lng": "-82.6619145", "property_state": "FL", "property_zip": "34210", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272499", "customer_email": "tffmgwr4@aol.com", "service_type": "CAD file", "county": "", "property_address": "3708 PLUMOSA TERRACE", "customer_name": "MICHAEL  SCHWARTZ"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "MICHAEL SCHWARTZ", "confidence": "HIGH"}, "client_email": {"value": "tffmgwr4@aol.com", "confidence": "HIGH"}, "property_address": {"value": "3708 PLUMOSA TERRACE, BRADENTON, FL 34210", "confidence": "HIGH"}, "property_county": {"value": "Manatee County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type listed as 'CAD file'; no additional services indicated. Unclear if this is a standalone CAD deliverable or tied to a specific survey type (e.g., boundary, elevation)."}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11). Flood zone data present: FEMA panel 12081C0283F, Zone AE, base flood elevation 8 ft, effective 08/10/2021.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or aerials provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Reason for On Hold status \u2014 needs human review to determine if order should proceed", "CAD file scope unclear \u2014 what underlying survey type is this CAD deliverable based on?", "Lot size not available", "Legal description not available", "Structure square footage not available", "Property features (pool, shed, structures) unknown \u2014 no appraiser data or aerials", "Special pricing details not specified \u2014 amount or discount reason unknown", "No invoice generated yet (invoiced: false) \u2014 pricing to be confirmed", "Delivery timeline unknown (fieldwork_at and delivered_at are null)"], "summary": "Residential CAD file order for Michael Schwartz at 3708 Plumosa Terrace, Bradenton FL (Manatee County) is currently On Hold with special pricing applied, paid but not yet invoiced, and missing key property details including survey scope, lot size, and legal description."}}</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>1780429614772</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>2026-06-02T18:12:48.218469+00:00</t>
         </is>
       </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:46:58.006394+00:00</t>
+        </is>
+      </c>
+      <c r="R182" t="n">
+        <v>450</v>
+      </c>
       <c r="T182" t="inlineStr">
         <is>
           <t>2026-06-02T16:12:13.119993+00:00</t>
@@ -12127,7 +12148,7 @@
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>2026-06-02T18:12:48.274678+00:00</t>
+          <t>2026-06-02T19:46:58.141519+00:00</t>
         </is>
       </c>
     </row>
@@ -12139,7 +12160,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -12162,16 +12183,37 @@
           <t>1250 Southwinds Dr, Lantana, FL 33462</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>{"total_amount": 0.0, "services": [], "pricing_reasoning": "The lot size is 67.01 acres, which far exceeds the 5.00-acre threshold defined in the pricing guidelines as requiring escalation for any service type. No automated pricing can be responsibly assigned to a parcel of this size \u2014 field mobilization, boundary complexity (SE quarter-section with road ROW exceptions via metes-and-bounds legal), and potential interior features all require a custom management quote. Additionally, the order notes confirm this order is currently On Hold with special pricing flagged and significant property detail gaps requiring human follow-up, further supporting escalation.", "confidence": "LOW", "escalate_flag": true, "escalate_reason": "Lot size of 67.01 acres exceeds the 5.00-acre maximum threshold for automated pricing on any service type. The legal description is a full SE quarter-section with road ROW exclusions, adding boundary complexity. Order is already flagged On Hold per internal notes with special pricing and unresolved property detail gaps. Management must review and issue a custom quote before any fieldwork is scheduled.", "flags": ["LOT_SIZE_EXCEEDS_THRESHOLD: 67.01 acres \u2014 pricing guidelines require escalation for any lot &gt; 5.00 acres", "ORDER_ON_HOLD: Internal notes confirm order is On Hold with special pricing flagged \u2014 no fieldwork scheduled", "PROPERTY_DETAIL_GAPS: Order notes indicate significant missing property details requiring human follow-up before pricing can be finalized", "METES_AND_BOUNDS_LEGAL: SE quarter-section with South 40 ft and East 40 ft road ROW exceptions adds boundary complexity to be factored into custom quote", "NEW_CLIENT: Just Call Kris, Inc. has 0 prior orders with NexGen despite OLD_TITLE tier classification \u2014 verify negotiated rate applicability for this job size", "NEGOTIATED_RATE_ON_FILE: $500.00 base rate agreed by management for this client \u2014 must be considered within any custom quote approved by management"]}</t>
+        </is>
+      </c>
       <c r="H183" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202510011843280904, "created_at": "2025-10-02T17:08:00", "customer_email": "561jck@gmail.com", "customer_id": 202510011844095922, "customer_name": "Kristen Owsley", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0779G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000272382, "paid": false, "property_address": "1250 SOUTHWINDS DR", "property_city": "LANTANA", "property_county": "PALM BEACH COUNTY", "property_lat": "26.5918905", "property_lng": "-80.0631796", "property_state": "FL", "property_zip": "33462", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272382", "customer_email": "561jck@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "1250 SOUTHWINDS DR", "customer_name": "Just Call Kris, Inc."}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Just Call Kris, Inc.", "confidence": "HIGH"}, "client_email": {"value": "561jck@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1250 Southwinds Dr, Lantana, FL 33462", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing flagged on order; order is currently On Hold \u2014 reason unknown.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, no emails, and no aerial review performed."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Reason order is 'On Hold' \u2014 needs clarification before proceeding", "Lot size unknown \u2014 no appraiser data available", "Legal description missing \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, shed, fencing, etc.)", "Urgency or deadline not specified", "No fieldwork or delivery dates set", "Special pricing flag present but pricing details not documented", "Customer name inconsistency: FTF order data shows 'Kristen Owsley' but outer customer_name shows 'Just Call Kris, Inc.' \u2014 confirm correct billing name"], "summary": "B2B land survey order for Just Call Kris, Inc. at 1250 Southwinds Dr, Lantana FL (Palm Beach County) is currently On Hold with special pricing flagged, no fieldwork scheduled, and significant property detail gaps requiring human follow-up."}}</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1780429637106</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>2026-06-02T18:13:02.556554+00:00</t>
         </is>
       </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:47:19.172133+00:00</t>
+        </is>
+      </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
       <c r="T183" t="inlineStr">
         <is>
           <t>2026-06-02T16:12:13.241662+00:00</t>
@@ -12179,7 +12221,7 @@
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>2026-06-02T18:13:02.610088+00:00</t>
+          <t>2026-06-02T19:47:19.247193+00:00</t>
         </is>
       </c>
     </row>
@@ -15883,7 +15925,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -15903,7 +15945,17 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>1239 GROVELAND AVE</t>
+          <t>1239 Groveland Ave, Venice, FL 34285</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202505151819211980, "created_at": "2025-05-15T14:22:05", "customer_email": "stacyhetman0768@gmail.com", "customer_id": 202505151819213062, "customer_name": "Stacy Hetman", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12115C0331G\nZONE: AE\nELEV: 10 FT\nEFF: 03/27/2024", "invoiced": false, "order_id": 1000264704, "paid": true, "property_address": "1239 GROVELAND AVE", "property_city": "VENICE", "property_county": "SARASOTA COUNTY", "property_lat": "27.0951603", "property_lng": "-82.4211936", "property_state": "FL", "property_zip": "34285", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000264704", "customer_email": "stacyhetman0768@gmail.com", "service_type": "CAD file", "county": "", "property_address": "1239 GROVELAND AVE", "customer_name": "Stacy Hetman"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Stacy Hetman", "confidence": "HIGH"}, "client_email": {"value": "stacyhetman0768@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1239 Groveland Ave, Venice, FL 34285", "confidence": "HIGH"}, "property_county": {"value": "Sarasota County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file'; no additional services indicated"}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); flood zone AE at 10 ft elevation (panel 12115C0331G, eff. 03/27/2024)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no matching emails found"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, driveway, structures) unknown \u2014 no appraiser or aerial data available", "County appraiser data unavailable (no county passed to appraiser lookup)", "No matching emails found \u2014 no supplemental client communication", "Order is On Hold \u2014 reason for hold not specified", "Elevation certificate not ordered but flood zone AE present \u2014 may need clarification on scope", "Fieldwork date not scheduled"], "summary": "Residential CAD file order for Stacy Hetman at 1239 Groveland Ave, Venice, FL 34285 (Sarasota County) with special pricing applied, currently On Hold, located in FEMA flood zone AE at 10 ft elevation."}}</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:45:38.693910+00:00</t>
         </is>
       </c>
       <c r="T255" t="inlineStr">
@@ -15913,7 +15965,7 @@
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:19.694514+00:00</t>
+          <t>2026-06-02T19:45:38.749696+00:00</t>
         </is>
       </c>
     </row>
@@ -15925,7 +15977,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -15940,12 +15992,22 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>BEATRICE  ESTEVEZ</t>
+          <t>BEATRICE ESTEVEZ</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2802 SW 5TH ST</t>
+          <t>2802 SW 5TH ST, BOYNTON BEACH, FL 33435</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202209021607315959, "created_at": "2025-05-12T15:03:04", "customer_email": "kbelectric@ymail.com", "customer_id": 202209021607334075, "customer_name": "BEATRICE  ESTEVEZ", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0789G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000264455, "paid": true, "property_address": "2802 SW 5TH ST", "property_city": "BOYNTON BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.5031603", "property_lng": "-80.0725035", "property_state": "FL", "property_zip": "33435", "service_type": "CAD file", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000264455", "customer_email": "kbelectric@ymail.com", "service_type": "CAD file", "county": "", "property_address": "2802 SW 5TH ST", "customer_name": "BEATRICE  ESTEVEZ"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "BEATRICE ESTEVEZ", "confidence": "HIGH"}, "client_email": {"value": "kbelectric@ymail.com", "confidence": "HIGH"}, "property_address": {"value": "2802 SW 5TH ST, BOYNTON BEACH, FL 33435", "confidence": "HIGH"}, "property_county": {"value": "PALM BEACH COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["CAD file"], "confidence": "HIGH", "notes": "Service type listed as 'CAD file'; no additional services noted. Unclear what base survey type the CAD file is derived from."}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status code 11)", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or aerial data provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Base survey type underlying the CAD file request is not specified", "Lot size unknown \u2014 no appraiser data available", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) unknown \u2014 no appraiser or aerial data", "Reason for On Hold status not documented", "No fieldwork date scheduled", "No delivery date set", "County field was blank in the FTF order root-level data despite being present in data object"], "summary": "Residential CAD file order for Beatrice Estevez at 2802 SW 5TH ST, Boynton Beach, FL (Palm Beach County) is paid but currently On Hold with special pricing applied and no fieldwork or delivery dates scheduled."}}</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:45:49.074277+00:00</t>
         </is>
       </c>
       <c r="T256" t="inlineStr">
@@ -15955,7 +16017,7 @@
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:19.844907+00:00</t>
+          <t>2026-06-02T19:45:49.130959+00:00</t>
         </is>
       </c>
     </row>
@@ -15967,7 +16029,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -15987,7 +16049,17 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>511 NORTON ST</t>
+          <t>511 Norton St, Longboat Key, FL 34228</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202409052026553894, "created_at": "2025-05-11T08:57:01", "customer_email": "j@jabuildsinc.com", "customer_id": 202409052026555189, "customer_name": "J Azocar", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12081C0291F\nZONE: AE\nELEV: 08 FT\nEFF: 08/10/2021", "invoiced": false, "order_id": 1000264360, "paid": false, "property_address": "511 NORTON ST", "property_city": "LONGBOAT KEY", "property_county": "Manatee County", "property_lat": "27.4271841", "property_lng": "-82.6739017", "property_state": "FL", "property_zip": "34228", "service_type": "Quote", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000264360", "customer_email": "j@jabuildsinc.com", "service_type": "Quote", "county": "", "property_address": "511 NORTON ST", "customer_name": "J Azocar"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "J Azocar", "confidence": "HIGH"}, "client_email": {"value": "j@jabuildsinc.com", "confidence": "HIGH"}, "property_address": {"value": "511 Norton St, Longboat Key, FL 34228", "confidence": "HIGH"}, "property_county": {"value": "Manatee County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (e.g., boundary, elevation certificate, topographic) has been identified. Needs clarification."}, "special_requirements": {"value": "Special pricing flagged; order is On Hold (status code 11); property is in FEMA Flood Zone AE (panel 12081C0291F, base elevation 8 ft, effective 08/10/2021)", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 no appraiser data, aerial imagery, or email attachments provided. Pool, structures, driveway, etc. unknown."}, "client_tier": {"value": "b2b", "confidence": "MEDIUM"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not defined \u2014 'Quote' is not a deliverable service", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, outbuildings, etc.) unknown", "No matching emails found to clarify scope or client intent", "Reason for 'On Hold' status not documented", "Special pricing details not specified \u2014 no pricing breakdown available", "Elevation certificate flagged as false \u2014 confirm if flood zone data implies one is needed", "Customer data record is empty \u2014 no additional contact or billing info"], "summary": "This is an on-hold quote request from J Azocar (likely a contractor via jabuildsinc.com) for a property at 511 Norton St, Longboat Key, FL in Manatee County, located in FEMA Flood Zone AE, with special pricing flagged but no specific survey service type defined."}}</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:46:02.581770+00:00</t>
         </is>
       </c>
       <c r="T257" t="inlineStr">
@@ -15997,7 +16069,7 @@
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:19.935458+00:00</t>
+          <t>2026-06-02T19:46:02.638067+00:00</t>
         </is>
       </c>
     </row>
@@ -16009,7 +16081,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16029,7 +16101,17 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>4148 SW 130TH AVE</t>
+          <t>4148 SW 130TH AVE, DAVIE, FL 33330</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202104261150575391, "created_at": "2025-05-09T12:45:03", "customer_email": "iartzy@IKALaw.com", "customer_id": 202104261153423935, "customer_name": "Office Account", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12011C0530J\nZONE: X\nEFF: 07/31/2024", "invoiced": false, "order_id": 1000264308, "paid": false, "property_address": "4148 SW 130TH AVE", "property_city": "DAVIE", "property_county": "Broward County", "property_lat": "26.0683932", "property_lng": "-80.32150539999999", "property_state": "FL", "property_zip": "33330", "service_type": "Quote", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000264308", "customer_email": "iartzy@IKALaw.com", "service_type": "Quote", "county": "", "property_address": "4148 SW 130TH AVE", "customer_name": "The Law Office of Ilana Kalichman-Artzy"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "The Law Office of Ilana Kalichman-Artzy", "confidence": "HIGH"}, "client_email": {"value": "iartzy@IKALaw.com", "confidence": "HIGH"}, "property_address": {"value": "4148 SW 130TH AVE, DAVIE, FL 33330", "confidence": "HIGH"}, "property_county": {"value": "Broward County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 actual survey service(s) requested have not been specified. Human review needed to determine scope."}, "special_requirements": {"value": "Special pricing applies; order is currently On Hold", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or aerial data provided."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service(s) requested not defined \u2014 quote type is unknown", "Lot size not available", "Legal description not available", "Structure square footage not available", "Property features (pool, shed, structures) unknown \u2014 no appraiser or aerial data", "Order is On Hold \u2014 reason for hold not specified", "No fieldwork or delivery dates set", "No matching emails found to clarify scope or requirements"], "summary": "A B2B quote request from The Law Office of Ilana Kalichman-Artzy for a property at 4148 SW 130TH AVE, Davie, FL (Broward County, Flood Zone X) is currently On Hold with special pricing applied, but the specific survey services, lot details, and property features remain undefined and require human follow-up."}}</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:46:13.036444+00:00</t>
         </is>
       </c>
       <c r="T258" t="inlineStr">
@@ -16039,7 +16121,7 @@
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:20.026553+00:00</t>
+          <t>2026-06-02T19:46:13.093495+00:00</t>
         </is>
       </c>
     </row>
@@ -16051,7 +16133,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16071,7 +16153,17 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>463 &amp; 471 OAKMON RD</t>
+          <t>463 &amp; 471 OAKMON RD, PALM BAY, FL 32908</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202505081757396869, "created_at": "2025-05-08T13:59:00", "customer_email": "Savvyroseproperties@gmail.com", "customer_id": 202505081758244849, "customer_name": "Michael Mascaritola", "customer_type": "b2b", "delivered_at": null, "due_amount": 250.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12009C0660G \nZONE: X500\nEFF: 03/17/2014", "invoiced": false, "order_id": 1000264293, "paid": false, "property_address": "463 &amp; 471 OAKMON RD", "property_city": "PALM BAY", "property_county": "Brevard County", "property_lat": "27.944947", "property_lng": "-80.68278099999999", "property_state": "FL", "property_zip": "32908", "service_type": "Quote", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000264293", "customer_email": "Savvyroseproperties@gmail.com", "service_type": "Quote", "county": "", "property_address": "463 &amp; 471 OAKMON RD", "customer_name": "Savvy Rose Properties"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Savvy Rose Properties", "confidence": "HIGH"}, "client_email": {"value": "Savvyroseproperties@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "463 &amp; 471 OAKMON RD, PALM BAY, FL 32908", "confidence": "HIGH"}, "property_county": {"value": "Brevard County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 no specific survey service (boundary, topo, ALTA, etc.) has been identified. Needs clarification."}, "special_requirements": {"value": "Special pricing applied; order is On Hold", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available \u2014 no appraiser data, no aerial, no emails. Pool, shed, driveways, and structures unknown."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service type not defined \u2014 only 'Quote' provided", "Lot size unknown", "Legal description unavailable", "Structure square footage unknown", "Property features (pool, shed, fences, driveways) unknown", "No appraiser data available to cross-reference", "No matching emails found to supplement order details", "Order is On Hold \u2014 reason for hold not specified", "Due amount ($250) context unclear \u2014 partial deposit or quote fee?", "Two parcels listed (463 &amp; 471) \u2014 unclear if one or both are being surveyed"], "summary": "B2B quote order for Savvy Rose Properties covering two adjacent parcels at 463 &amp; 471 Oakmon Rd, Palm Bay FL (Brevard County, Flood Zone X500), currently on hold with special pricing applied and no specific survey service type yet defined."}}</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:46:23.479322+00:00</t>
         </is>
       </c>
       <c r="T259" t="inlineStr">
@@ -16081,7 +16173,7 @@
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:20.118437+00:00</t>
+          <t>2026-06-02T19:46:23.535923+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoice_pipeline_state.xlsx
+++ b/data/invoice_pipeline_state.xlsx
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -12256,16 +12256,37 @@
           <t>316 Amanda Ln, Leesburg, FL 34748</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>{"total_amount": 362.0, "services": [{"name": "Boundary Survey", "description": "Residential boundary survey for Lot 16, Westside Oaks First Addition, Leesburg, FL. Management-agreed base rate for individual client Lee Bennett.", "amount": 300.0}, {"name": "Lot Size Complexity Upcharge (0.31\u20130.50 ac)", "description": "Property is 0.44 acres, falling within the 0.31\u20130.50 ac tier. Standard upcharge applied for increased field and office work relative to a smaller residential lot.", "amount": 62.0}], "pricing_reasoning": "The base rate of $300.00 is a management-agreed negotiated rate for individual client Lee Bennett and must be honored as-is. The lot size of 0.44 acres falls in the 0.31\u20130.50 ac complexity tier, warranting a $62.00 upcharge. No EC is requested, the legal description is a platted subdivision lot (not metes and bounds), there is no Monroe County surcharge, no waterfront or pool indicators, and no heavy vegetation noted \u2014 so no additional upcharges apply.", "confidence": "HIGH", "escalate_flag": false, "escalate_reason": null, "flags": ["DUPLICATE_SUSPECTED: Order 1000243715 \u2014 316 AMANDA LN, LAKE COUNTY \u2014 same location coordinates (28.8175048, -81.90851769999999) and same Folio/MLS (21-19-24-0905-000-01600). Service listed as Land Survey Only. Human review recommended before proceeding.", "DUPLICATE_SUSPECTED: Order 1000277475 \u2014 316 AMANDA LN, LAKE COUNTY \u2014 same location coordinates (28.8175048, -81.90851769999999) and same Folio/MLS (21-19-24-0905-000-01600). Service listed as Land Survey Only. Human review recommended before proceeding.", "ORDER_ON_HOLD: Per order notes, this order is currently On Hold with special pricing applied. Confirm management approval before invoicing.", "MISSING_CLIENT_EMAIL: No valid client email on file per order notes. Invoice delivery may be affected.", "FEMA_ZONE_NOTE: Panel 12069C0308E shows both Zone AE (elevation 78.1 ft) and Zone X. Property appears to lie in or near a Zone AE flood area. No EC was requested; if client or lender requires an Elevation Certificate, that should be added as a separate line item at $275.00."]}</t>
+        </is>
+      </c>
       <c r="H184" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 202509301523412952, "created_at": "2025-09-30T17:00:05", "customer_email": "noemailgiven@none.com", "customer_id": 202509301523415071, "customer_name": "Lee Bennett", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12069C0308E\nZONE:AE\nELEV: 78.1 FT\nZONE: X\nEFF: 12/18/2012", "invoiced": false, "order_id": 1000272305, "paid": false, "property_address": "316 AMANDA LN", "property_city": "LEESBURG", "property_county": "Lake County", "property_lat": "28.8175048", "property_lng": "-81.90851769999999", "property_state": "FL", "property_zip": "34748", "service_type": "Boundary Survey", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272305", "customer_email": "noemailgiven@none.com", "service_type": "Boundary Survey", "county": "", "property_address": "316 AMANDA LN", "customer_name": "Lee Bennett"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Lee Bennett", "confidence": "HIGH"}, "client_email": {"value": "noemailgiven@none.com", "confidence": "LOW"}, "property_address": {"value": "316 Amanda Ln, Leesburg, FL 34748", "confidence": "HIGH"}, "property_county": {"value": "Lake County", "confidence": "HIGH"}, "services_requested": {"value": ["Boundary Survey"], "confidence": "HIGH", "notes": "Service type explicitly listed as Boundary Survey; elevation_cert is false so no elevation certificate is needed"}, "special_requirements": {"value": "Special pricing applied; order is On Hold (status code 11); flood zone data present \u2014 AE zone at 78.1 ft NAVD and X zone per FIRM panel 12069C0308E effective 12/18/2012", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; no appraiser data, aerial data, or email attachments provided"}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Valid client email address \u2014 'noemailgiven@none.com' is a placeholder", "Client phone number not provided", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features unknown (pool, fences, sheds, encroachments, etc.)", "Reason order is On Hold not specified \u2014 needs human review", "Urgency/deadline not stated", "Special pricing details not itemized \u2014 confirm pricing before invoicing", "County field is blank in top-level order data despite being populated in nested data \u2014 verify data consistency"], "summary": "Residential boundary survey order for Lee Bennett at 316 Amanda Ln, Leesburg, FL (Lake County) is currently On Hold with special pricing applied, no valid client email on file, and missing lot size, legal description, and property feature details."}}</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>1780429964605</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>2026-06-02T18:13:14.767702+00:00</t>
         </is>
       </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:52:47.502939+00:00</t>
+        </is>
+      </c>
+      <c r="R184" t="n">
+        <v>362</v>
+      </c>
       <c r="T184" t="inlineStr">
         <is>
           <t>2026-06-02T16:12:13.313936+00:00</t>
@@ -12273,7 +12294,7 @@
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>2026-06-02T18:13:14.822976+00:00</t>
+          <t>2026-06-02T19:52:47.619773+00:00</t>
         </is>
       </c>
     </row>
@@ -12285,7 +12306,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>data_collected</t>
+          <t>invoice_draft_posted</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -12308,16 +12329,37 @@
           <t>2133 Sibley Ave, Fort Pierce, FL 34982</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>{"total_amount": 550.0, "services": [{"name": "Boundary Survey (Land Survey Only)", "description": "Boundary survey for 0.38-acre residential/commercial parcel at 2133 Sibley Ave, Fort Pierce, FL (St. Lucie County). Priced at negotiated B2B rate for McCarthy, Summers, Bobko, Wood, Norman, Bass, and Melby, PA.", "amount": 450.0}, {"name": "Complexity Upcharge \u2014 Metes and Bounds Legal Description", "description": "Legal description is a metes-and-bounds closure referencing a derived POB from a quarter-quarter-quarter section corner with multiple sequential bearing/distance calls and an apparent truncation. This adds meaningful field and office complexity beyond a simple platted lot.", "amount": 100.0}], "pricing_reasoning": "The negotiated base rate of $450.00 applies per management agreement for this B2B law firm client. The legal description is a full metes-and-bounds description (not a platted lot) with a calculated POB, multiple course reversals, and an apparent truncation in the last call, supporting the $100.00 metes-and-bounds complexity upcharge. The lot at 0.38 acres falls in the 0.31\u20130.50 ac tier, but given the negotiated flat rate already accounts for moderate lot sizing, the size upcharge is not stacked \u2014 the metes-and-bounds complexity is the operative driver. FEMA Zone X requires no EC and no flood-zone surcharge. No pool, waterfront, heavy vegetation, or Monroe County factors are indicated.", "confidence": "MEDIUM", "escalate_flag": false, "escalate_reason": null, "flags": ["POSSIBLE_DUPLICATE: Order 1000246610 references the same property address (2133 Sibley Ave, St. Lucie County) and the same Folio (2428-231-0003-000-1) with a 'Land Survey Only' service type. This order is marked as already delivered and paid. Human review is required to confirm this is a distinct billable engagement (e.g., a legal/litigation deliverable or document request) and not a duplicate billing of the prior survey.", "SERVICE_TYPE_AMBIGUOUS: Service is listed as 'Other Services' with no further specification. The order notes reference a law firm client and a delivered B2B order, suggesting this may be a boundary survey re-issue, certified copy, or litigation support deliverable. If the service is something other than a boundary survey (e.g., expert witness letter, legal description preparation, or exhibit preparation), pricing should be revisited.", "LEGAL_DESCRIPTION_TRUNCATED: The metes-and-bounds description appears to be cut off at the last call ('THENCE RUN EAST 1'). Full closure should be confirmed before fieldwork proceeds.", "ORDER_COUNT_ZERO: Client order count shows 0 prior orders despite being flagged as OLD_TITLE with a negotiated rate. This may reflect a data sync issue or a newly onboarded legacy client \u2014 confirm account history with management."]}</t>
+        </is>
+      </c>
       <c r="H185" t="inlineStr">
         <is>
           <t>{"ftf_order": {"data": {"company_id": 201804061150419039, "created_at": "2025-09-25T15:31:02", "customer_email": "hgm@mccarthysummers.com", "customer_id": 202509251913000352, "customer_name": "Hannah Moore", "customer_type": "b2b", "delivered_at": "2025-10-15T19:18:54", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12111C0186J\nZONE: X\nEFF: 02/16/2012", "invoiced": false, "order_id": 1000272106, "paid": true, "property_address": "2133 SIBLEY AVE", "property_city": "FORT PIERCE", "property_county": "ST LUCIE County", "property_lat": "27.4069748", "property_lng": "-80.3463277", "property_state": "FL", "property_zip": "34982", "service_type": "Other Services", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000272106", "customer_email": "hgm@mccarthysummers.com", "service_type": "Other Services", "county": "", "property_address": "2133 SIBLEY AVE", "customer_name": "McCarthy, Summers, Bobko, Wood, Norman, Bass, and Melby, PA"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "McCarthy, Summers, Bobko, Wood, Norman, Bass, and Melby, PA", "confidence": "HIGH"}, "client_email": {"value": "hgm@mccarthysummers.com", "confidence": "HIGH"}, "property_address": {"value": "2133 Sibley Ave, Fort Pierce, FL 34982", "confidence": "HIGH"}, "property_county": {"value": "St. Lucie County", "confidence": "HIGH"}, "services_requested": {"value": ["Other Services"], "confidence": "LOW", "notes": "Service type is listed only as 'Other Services' \u2014 specific survey or service type is unknown and requires clarification"}, "special_requirements": {"value": "Special pricing applied", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided"}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Specific service type is unknown \u2014 'Other Services' needs clarification", "Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown \u2014 no appraiser, aerial, or email data available", "No invoice has been generated despite order being delivered and paid", "Fieldwork date is null \u2014 unclear if fieldwork was completed"], "summary": "A delivered and paid B2B order for law firm McCarthy, Summers, Bobko, Wood, Norman, Bass, and Melby, PA at 2133 Sibley Ave, Fort Pierce, FL (St. Lucie County) with an unspecified 'Other Services' service type, special pricing applied, and no invoice yet generated."}}</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>1780429989747</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>2026-06-02T18:18:24.406612+00:00</t>
         </is>
       </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:53:12.757324+00:00</t>
+        </is>
+      </c>
+      <c r="R185" t="n">
+        <v>550</v>
+      </c>
       <c r="T185" t="inlineStr">
         <is>
           <t>2026-06-02T16:12:13.385617+00:00</t>
@@ -12325,7 +12367,7 @@
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>2026-06-02T18:18:24.466432+00:00</t>
+          <t>2026-06-02T19:53:12.814673+00:00</t>
         </is>
       </c>
     </row>
@@ -16185,7 +16227,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16205,7 +16247,17 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>15 LA VISTA DR</t>
+          <t>15 La Vista Dr, Ponte Vedra Beach, FL 32082</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202505081634327999, "created_at": "2025-05-08T13:23:01", "customer_email": "julia@bayviewla.com", "customer_id": 202505081638245464, "customer_name": "Julia Walton", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12109C0082J\nZONE: X\nEFF: 12/07/2018", "invoiced": false, "order_id": 1000264273, "paid": true, "property_address": "15 LA VISTA DR", "property_city": "PONTE VEDRA BEACH", "property_county": "ST JOHNS County", "property_lat": "30.2240345", "property_lng": "-81.3783119", "property_state": "FL", "property_zip": "32082", "service_type": "Quote", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000264273", "customer_email": "julia@bayviewla.com", "service_type": "Quote", "county": "", "property_address": "15 LA VISTA DR", "customer_name": "Bayview Landscape Architecture"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Bayview Landscape Architecture", "confidence": "HIGH"}, "client_email": {"value": "julia@bayviewla.com", "confidence": "HIGH"}, "property_address": {"value": "15 La Vista Dr, Ponte Vedra Beach, FL 32082", "confidence": "HIGH"}, "property_county": {"value": "St. Johns County", "confidence": "HIGH"}, "services_requested": {"value": ["Quote"], "confidence": "LOW", "notes": "Service type is listed only as 'Quote' \u2014 actual survey service(s) requested have not been specified. Human review needed to determine scope."}, "special_requirements": {"value": "Special pricing applied; order is currently On Hold", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["Specific survey service(s) requested not defined \u2014 'Quote' is not a service type", "Lot size unknown \u2014 no appraiser data available", "Legal description unknown \u2014 no appraiser data available", "Structure square footage unknown", "Property features (pool, outbuildings, etc.) unknown", "Urgency/timeline not specified", "Order is On Hold \u2014 reason for hold not documented", "No contact emails found to clarify scope or requirements", "County field is blank in outer FTF payload despite being present in order data"], "summary": "A B2B quote-stage order for Bayview Landscape Architecture at 15 La Vista Dr, Ponte Vedra Beach, FL (St. Johns County) is currently On Hold with special pricing applied, but no specific survey services have been defined and supporting property data is unavailable."}}</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:51:35.090165+00:00</t>
         </is>
       </c>
       <c r="T260" t="inlineStr">
@@ -16215,7 +16267,7 @@
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:20.212157+00:00</t>
+          <t>2026-06-02T19:51:35.146743+00:00</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16279,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16247,7 +16299,17 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>400 METCALF CT</t>
+          <t>400 Metcalf Ct, West Palm Beach, FL 33407</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202505081314033875, "created_at": "2025-05-08T09:31:04", "customer_email": "santiago@thefeldmancompanies.com", "customer_id": 202505081314035128, "customer_name": "Santiago Araujo", "customer_type": "individual", "delivered_at": "2025-09-19T17:59:47", "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12099C0581G\nZONE: X\nEFF: 12/20/2024", "invoiced": false, "order_id": 1000264249, "paid": true, "property_address": "400 METCALF CT", "property_city": "WEST PALM BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.7470222", "property_lng": "-80.0527579", "property_state": "FL", "property_zip": "33407", "service_type": "CAD file", "special_pricing": true, "status": "Delivered", "status_code": 8, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000264249", "customer_email": "santiago@thefeldmancompanies.com", "service_type": "CAD file", "county": "", "property_address": "400 METCALF CT", "customer_name": "Santiago Araujo"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Santiago Araujo", "confidence": "HIGH"}, "client_email": {"value": "santiago@thefeldmancompanies.com", "confidence": "HIGH"}, "property_address": {"value": "400 Metcalf Ct, West Palm Beach, FL 33407", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["CAD File"], "confidence": "HIGH", "notes": "Service type explicitly listed as 'CAD file' in order data. No additional services noted."}, "special_requirements": {"value": "Special pricing applied to this order.", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments to reference."}, "client_tier": {"value": "b2b", "confidence": "MEDIUM", "notes": "Customer email domain '@thefeldmancompanies.com' suggests a business affiliation despite customer_type listed as 'individual'."}, "urgency": {"value": "normal", "confidence": "MEDIUM", "notes": "No rush indicators present; order was delivered well after creation with no urgency flags."}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage not provided", "Property features unknown (pool, shed, driveways, etc.)", "County property appraiser data unavailable \u2014 no county was passed to lookup", "No matching emails found to supplement order details", "Customer type listed as 'individual' but email suggests business \u2014 client tier should be confirmed", "Scope of CAD file deliverable not specified (boundary only, topographic, as-built, etc.)"], "summary": "CAD file order for Santiago Araujo at 400 Metcalf Ct, West Palm Beach, FL (Palm Beach County), marked paid and delivered, with special pricing applied and minimal property detail available."}}</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:51:45.959672+00:00</t>
         </is>
       </c>
       <c r="T261" t="inlineStr">
@@ -16257,7 +16319,7 @@
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:20.307110+00:00</t>
+          <t>2026-06-02T19:51:46.016683+00:00</t>
         </is>
       </c>
     </row>
@@ -16269,7 +16331,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16289,7 +16351,17 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>5203 86TH STREET CT W</t>
+          <t>5203 86TH STREET CT W, BRADENTON, FL 34210</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202505071732076475, "created_at": "2025-05-28T21:23:00", "customer_email": "hamptonsgjb@aol.com", "customer_id": 202505071732077604, "customer_name": "Gerald Baldi", "customer_type": "individual", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12081C0284F\nZONE: X500\nEFF: 08/10/2021", "invoiced": false, "order_id": 1000264205, "paid": false, "property_address": "5203 86TH STREET CT W", "property_city": "BRADENTON", "property_county": "MANATEE COUNTY", "property_lat": "27.4536029", "property_lng": "-82.648822", "property_state": "FL", "property_zip": "34210", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000264205", "customer_email": "hamptonsgjb@aol.com", "service_type": "Land Survey Only", "county": "", "property_address": "5203 86TH STREET CT W", "customer_name": "Gerald Baldi"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Gerald Baldi", "confidence": "HIGH"}, "client_email": {"value": "hamptonsgjb@aol.com", "confidence": "HIGH"}, "property_address": {"value": "5203 86TH STREET CT W, BRADENTON, FL 34210", "confidence": "HIGH"}, "property_county": {"value": "Manatee County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing flagged; order is currently On Hold (status code 11). Flood zone: 12081C0284F, Zone X500, effective 08/10/2021.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no emails or attachments provided."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size unknown \u2014 county appraiser data unavailable", "Legal description missing", "Structure square footage unknown", "Property features (pool, shed, fence, etc.) unknown \u2014 no aerial or appraiser data", "Reason for On Hold status not documented", "Special pricing terms not specified \u2014 pricing not yet set (due amount $0)", "No invoice or estimate has been sent \u2014 awaiting resolution of hold", "No delivery date or fieldwork date scheduled"], "summary": "Residential land survey order for Gerald Baldi at 5203 86th Street Ct W, Bradenton, FL (Manatee County) is currently On Hold with special pricing flagged and no invoice, fieldwork, or delivery dates set."}}</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:51:57.297417+00:00</t>
         </is>
       </c>
       <c r="T262" t="inlineStr">
@@ -16299,7 +16371,7 @@
       </c>
       <c r="U262" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:20.462139+00:00</t>
+          <t>2026-06-02T19:51:57.354599+00:00</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16383,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16331,7 +16403,17 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>1717 ROYAL FOREST CT</t>
+          <t>1717 Royal Forest Ct, West Palm Beach, FL 33406</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202505051844375725, "created_at": "2025-05-05T14:44:00", "customer_email": "nattyvga27@gmail.com", "customer_id": 202505051844375828, "customer_name": "Angela Vega", "customer_type": "individual", "delivered_at": null, "due_amount": 300.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": "2025-05-19T00:00:00", "flood_zone": "12099C0588F\nZONE: X\nEFF: 10/05/2017", "invoiced": false, "order_id": 1000264046, "paid": false, "property_address": "1717 ROYAL FOREST CT", "property_city": "WEST PALM BEACH", "property_county": "PALM BEACH COUNTY", "property_lat": "26.6520469", "property_lng": "-80.10125699999999", "property_state": "FL", "property_zip": "33406", "service_type": "Land Survey Only", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-01-16T06:04:08"}, "success": true, "order_id": "1000264046", "customer_email": "nattyvga27@gmail.com", "service_type": "Land Survey Only", "county": "", "property_address": "1717 ROYAL FOREST CT", "customer_name": "Angela Vega"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Angela Vega", "confidence": "HIGH"}, "client_email": {"value": "nattyvga27@gmail.com", "confidence": "HIGH"}, "property_address": {"value": "1717 Royal Forest Ct, West Palm Beach, FL 33406", "confidence": "HIGH"}, "property_county": {"value": "Palm Beach County", "confidence": "HIGH"}, "services_requested": {"value": ["Land Survey Only"], "confidence": "HIGH", "notes": "Service type explicitly stated as 'Land Survey Only'; no elevation certificate requested."}, "special_requirements": {"value": "Special pricing applied; order currently On Hold (status code 11).", "confidence": "HIGH"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no matching emails found."}, "client_tier": {"value": "residential", "confidence": "HIGH"}, "urgency": {"value": "normal", "confidence": "MEDIUM"}, "source_of_truth": "ftf_only", "gaps": ["Lot size not provided", "Legal description not provided", "Structure square footage unknown", "Property features (pool, shed, fencing, etc.) unknown \u2014 no appraiser or aerial data available", "Reason for 'On Hold' status not documented", "No county provided in the top-level order object (only in nested data); county appraiser lookup was skipped", "Invoice not yet sent; due amount of $300 reflects special pricing \u2014 basis for discount not documented", "No delivery date or completion timeline confirmed beyond fieldwork date of 2025-05-19"], "summary": "Residential land survey only order for Angela Vega at 1717 Royal Forest Ct, West Palm Beach, FL, currently on hold with special pricing applied and fieldwork scheduled for May 19, 2025."}}</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:52:06.757409+00:00</t>
         </is>
       </c>
       <c r="T263" t="inlineStr">
@@ -16341,7 +16423,7 @@
       </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>2026-06-02T16:12:20.556142+00:00</t>
+          <t>2026-06-02T19:52:06.814912+00:00</t>
         </is>
       </c>
     </row>
@@ -16353,7 +16435,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>invoice_needed</t>
+          <t>data_collected</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16373,7 +16455,17 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>8518 SPRING FOREST LN</t>
+          <t>8518 SPRING FOREST LN, WESLEY CHAPEL, FL 33544</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>{"ftf_order": {"data": {"company_id": 202502281626053666, "created_at": "2025-05-28T21:35:03", "customer_email": "project-coordination@boselectric.com", "customer_id": 202512032112132969, "customer_name": "Sydney Harris Coordinators", "customer_type": "b2b", "delivered_at": null, "due_amount": 0.0, "elevation_cert": false, "estimate_sent": false, "fieldwork_at": null, "flood_zone": "12101C0263F\nZONE: X\nEFF: 09/26/2014", "invoiced": false, "order_id": 1000263848, "paid": false, "property_address": "8518 SPRING FOREST LN", "property_city": "WESLEY CHAPEL", "property_county": "PASCO COUNTY", "property_lat": "28.2803746", "property_lng": "-82.3674035", "property_state": "FL", "property_zip": "33544", "service_type": "Boundary Survey", "special_pricing": true, "status": "On Hold", "status_code": 11, "updated_at": "2026-02-24T16:44:34"}, "success": true, "order_id": "1000263848", "customer_email": "lbutler@powersupportpartners.com", "service_type": "Boundary Survey", "county": "", "property_address": "8518 SPRING FOREST LN", "customer_name": "Power Support Partners"}, "ftf_customer": {}, "emails_found": 0, "email_snippets": [], "appraiser_data": {"legal_description": null, "lot_size": null, "structure_sqft": null, "parcel_id": null, "year_built": null, "notes": null, "source_url": null, "confidence": "LOW", "error": "No county provided"}, "aerial_analysis": {}, "packet": {"client_name": {"value": "Power Support Partners", "confidence": "MEDIUM"}, "client_email": {"value": "lbutler@powersupportpartners.com", "confidence": "MEDIUM"}, "property_address": {"value": "8518 SPRING FOREST LN, WESLEY CHAPEL, FL 33544", "confidence": "HIGH"}, "property_county": {"value": "PASCO COUNTY", "confidence": "HIGH"}, "services_requested": {"value": ["Boundary Survey"], "confidence": "HIGH", "notes": "Explicitly stated in both order data fields. No additional services indicated."}, "special_requirements": {"value": "Special pricing flagged; order is currently On Hold (status_code 11). Flood zone identified as Zone X (panel 12101C0263F, eff. 09/26/2014) \u2014 no elevation certificate required.", "confidence": "MEDIUM"}, "lot_size": {"value": null, "confidence": "LOW"}, "legal_description": {"value": null, "confidence": "LOW"}, "structure_sqft": {"value": null, "confidence": "LOW"}, "property_features": {"value": {}, "confidence": "LOW", "notes": "No property features available; county appraiser data unavailable and no aerial or email data provided."}, "client_tier": {"value": "b2b", "confidence": "HIGH"}, "urgency": {"value": "unknown", "confidence": "LOW"}, "source_of_truth": "ftf_only", "gaps": ["